--- a/工程量清单/工程量清单及计算书.xlsx
+++ b/工程量清单/工程量清单及计算书.xlsx
@@ -21,9 +21,8 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <numFmts count="2">
-    <numFmt numFmtId="164" formatCode="0.00##"/>
-    <numFmt numFmtId="165" formatCode="0.000"/>
+  <numFmts count="1">
+    <numFmt numFmtId="164" formatCode="0.000"/>
   </numFmts>
   <fonts count="4">
     <font>
@@ -87,7 +86,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="15">
+  <cellXfs count="14">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
@@ -101,7 +100,7 @@
     <xf numFmtId="0" fontId="3" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="164" fontId="3" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="2" fontId="2" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
@@ -110,16 +109,13 @@
     <xf numFmtId="0" fontId="2" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="164" fontId="2" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="2" fontId="3" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="165" fontId="3" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="164" fontId="2" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="165" fontId="2" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="2" fontId="3" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="164" fontId="3" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
@@ -569,17 +565,13 @@
         </is>
       </c>
       <c r="F3" s="5" t="n">
-        <v>200.4156</v>
+        <v>200.42</v>
       </c>
     </row>
     <row r="4" ht="18" customHeight="1">
       <c r="A4" s="3" t="n"/>
       <c r="B4" s="3" t="n"/>
-      <c r="C4" s="6" t="inlineStr">
-        <is>
-          <t>小计</t>
-        </is>
-      </c>
+      <c r="C4" s="6" t="n"/>
       <c r="D4" s="7" t="inlineStr">
         <is>
           <t>m³</t>
@@ -590,9 +582,7 @@
           <t>200.4156 ≈ 200.42</t>
         </is>
       </c>
-      <c r="F4" s="8" t="n">
-        <v>200.42</v>
-      </c>
+      <c r="F4" s="8" t="n"/>
     </row>
     <row r="5" ht="46" customHeight="1">
       <c r="A5" s="3" t="n">
@@ -619,17 +609,13 @@
         </is>
       </c>
       <c r="F5" s="5" t="n">
-        <v>168.2978</v>
+        <v>168.3</v>
       </c>
     </row>
     <row r="6" ht="18" customHeight="1">
       <c r="A6" s="3" t="n"/>
       <c r="B6" s="3" t="n"/>
-      <c r="C6" s="6" t="inlineStr">
-        <is>
-          <t>小计</t>
-        </is>
-      </c>
+      <c r="C6" s="6" t="n"/>
       <c r="D6" s="7" t="inlineStr">
         <is>
           <t>m³</t>
@@ -640,9 +626,7 @@
           <t>168.2978 ≈ 168.30</t>
         </is>
       </c>
-      <c r="F6" s="8" t="n">
-        <v>168.3</v>
-      </c>
+      <c r="F6" s="8" t="n"/>
     </row>
     <row r="7" ht="18" customHeight="1">
       <c r="A7" s="3" t="n">
@@ -669,17 +653,13 @@
         </is>
       </c>
       <c r="F7" s="5" t="n">
-        <v>192.882</v>
+        <v>192.88</v>
       </c>
     </row>
     <row r="8" ht="18" customHeight="1">
       <c r="A8" s="3" t="n"/>
       <c r="B8" s="3" t="n"/>
-      <c r="C8" s="6" t="inlineStr">
-        <is>
-          <t>小计</t>
-        </is>
-      </c>
+      <c r="C8" s="6" t="n"/>
       <c r="D8" s="7" t="inlineStr">
         <is>
           <t>m³</t>
@@ -690,9 +670,7 @@
           <t>192.882 ≈ 192.88</t>
         </is>
       </c>
-      <c r="F8" s="8" t="n">
-        <v>192.88</v>
-      </c>
+      <c r="F8" s="8" t="n"/>
     </row>
     <row r="9" ht="18" customHeight="1">
       <c r="A9" s="3" t="n">
@@ -719,17 +697,13 @@
         </is>
       </c>
       <c r="F9" s="5" t="n">
-        <v>32.1178</v>
+        <v>32.12</v>
       </c>
     </row>
     <row r="10" ht="18" customHeight="1">
       <c r="A10" s="3" t="n"/>
       <c r="B10" s="3" t="n"/>
-      <c r="C10" s="6" t="inlineStr">
-        <is>
-          <t>小计</t>
-        </is>
-      </c>
+      <c r="C10" s="6" t="n"/>
       <c r="D10" s="7" t="inlineStr">
         <is>
           <t>m³</t>
@@ -740,9 +714,7 @@
           <t>32.1178 ≈ 32.12</t>
         </is>
       </c>
-      <c r="F10" s="8" t="n">
-        <v>32.12</v>
-      </c>
+      <c r="F10" s="8" t="n"/>
     </row>
     <row r="11" ht="32" customHeight="1">
       <c r="A11" s="3" t="n">
@@ -769,7 +741,7 @@
         </is>
       </c>
       <c r="F11" s="5" t="n">
-        <v>27.0403</v>
+        <v>113.02</v>
       </c>
     </row>
     <row r="12" ht="32" customHeight="1">
@@ -790,9 +762,7 @@
           <t>(13.625×3.6×0.24)-0.8784-0.9936-1.5972-0.096-0.023 + (15.38×3.6×0.24)-3.6288-1.1923-1.1712-0.4992 + (13.5×3.6×0.24)-0.8784-1.3167-1.5313-0.096-0.023 + (15.5×3.6×0.24)-5.4144-1.392-0.648-0.1382-0.0027 = 28.5958</t>
         </is>
       </c>
-      <c r="F12" s="5" t="n">
-        <v>28.5958</v>
-      </c>
+      <c r="F12" s="8" t="n"/>
     </row>
     <row r="13" ht="32" customHeight="1">
       <c r="A13" s="3" t="n"/>
@@ -812,9 +782,7 @@
           <t>(15.5×3.6×0.24)-5.4144-1.392-0.648-0.1382-0.0027 + (13.5×3.6×0.24)-0.8784-1.3167-1.5313-0.096-0.023 + (15.38×3.6×0.24)-3.6288-1.1923-1.1712-0.4992 + (13.625×3.6×0.24)-0.8784-0.9936-1.5972-0.096-0.023 = 28.5958</t>
         </is>
       </c>
-      <c r="F13" s="5" t="n">
-        <v>28.5958</v>
-      </c>
+      <c r="F13" s="8" t="n"/>
     </row>
     <row r="14" ht="32" customHeight="1">
       <c r="A14" s="3" t="n"/>
@@ -834,18 +802,12 @@
           <t>(15.5×3.6×0.24)-5.4144-1.392-0.648-0.1382-0.003 + (13.5×3.6×0.24)-0.8784-1.3167-1.5313-0.096-0.023 + (15.38×3.6×0.24)-3.2616-1.1923-1.344-0.4992 + (13.625×3.6×0.24)-0.8784-0.9936-1.5972-0.096-0.023 = 28.7899</t>
         </is>
       </c>
-      <c r="F14" s="5" t="n">
-        <v>28.7899</v>
-      </c>
+      <c r="F14" s="8" t="n"/>
     </row>
     <row r="15" ht="18" customHeight="1">
       <c r="A15" s="3" t="n"/>
       <c r="B15" s="3" t="n"/>
-      <c r="C15" s="6" t="inlineStr">
-        <is>
-          <t>小计</t>
-        </is>
-      </c>
+      <c r="C15" s="6" t="n"/>
       <c r="D15" s="7" t="inlineStr">
         <is>
           <t>m³</t>
@@ -856,9 +818,7 @@
           <t>27.0403 + 28.5958 + 28.5958 + 28.7899 = 113.0218 ≈ 113.02</t>
         </is>
       </c>
-      <c r="F15" s="8" t="n">
-        <v>113.02</v>
-      </c>
+      <c r="F15" s="8" t="n"/>
     </row>
     <row r="16" ht="18" customHeight="1">
       <c r="A16" s="3" t="n">
@@ -885,7 +845,7 @@
         </is>
       </c>
       <c r="F16" s="5" t="n">
-        <v>5.6237</v>
+        <v>16.33</v>
       </c>
     </row>
     <row r="17" ht="18" customHeight="1">
@@ -906,9 +866,7 @@
           <t>(5.85×3.6×0.24)-0.8424-0.6435 = 3.5685</t>
         </is>
       </c>
-      <c r="F17" s="5" t="n">
-        <v>3.5685</v>
-      </c>
+      <c r="F17" s="8" t="n"/>
     </row>
     <row r="18" ht="18" customHeight="1">
       <c r="A18" s="3" t="n"/>
@@ -928,9 +886,7 @@
           <t>(5.85×3.6×0.24)-0.8424-0.6435 = 3.5685</t>
         </is>
       </c>
-      <c r="F18" s="5" t="n">
-        <v>3.5685</v>
-      </c>
+      <c r="F18" s="8" t="n"/>
     </row>
     <row r="19" ht="18" customHeight="1">
       <c r="A19" s="3" t="n"/>
@@ -950,18 +906,12 @@
           <t>(5.85×3.6×0.24)-0.8424-0.6435 = 3.5685</t>
         </is>
       </c>
-      <c r="F19" s="5" t="n">
-        <v>3.5685</v>
-      </c>
+      <c r="F19" s="8" t="n"/>
     </row>
     <row r="20" ht="18" customHeight="1">
       <c r="A20" s="3" t="n"/>
       <c r="B20" s="3" t="n"/>
-      <c r="C20" s="6" t="inlineStr">
-        <is>
-          <t>小计</t>
-        </is>
-      </c>
+      <c r="C20" s="6" t="n"/>
       <c r="D20" s="7" t="inlineStr">
         <is>
           <t>m³</t>
@@ -972,9 +922,7 @@
           <t>5.6237 + 3.5685 + 3.5685 + 3.5685 = 16.3292 ≈ 16.33</t>
         </is>
       </c>
-      <c r="F20" s="8" t="n">
-        <v>16.33</v>
-      </c>
+      <c r="F20" s="8" t="n"/>
     </row>
     <row r="21" ht="46" customHeight="1">
       <c r="A21" s="3" t="n">
@@ -1001,17 +949,13 @@
         </is>
       </c>
       <c r="F21" s="5" t="n">
-        <v>25.3624</v>
+        <v>25.36</v>
       </c>
     </row>
     <row r="22" ht="18" customHeight="1">
       <c r="A22" s="3" t="n"/>
       <c r="B22" s="3" t="n"/>
-      <c r="C22" s="6" t="inlineStr">
-        <is>
-          <t>小计</t>
-        </is>
-      </c>
+      <c r="C22" s="6" t="n"/>
       <c r="D22" s="7" t="inlineStr">
         <is>
           <t>m³</t>
@@ -1022,9 +966,7 @@
           <t>25.3624 ≈ 25.36</t>
         </is>
       </c>
-      <c r="F22" s="8" t="n">
-        <v>25.36</v>
-      </c>
+      <c r="F22" s="8" t="n"/>
     </row>
     <row r="23" ht="18" customHeight="1">
       <c r="A23" s="3" t="n">
@@ -1051,17 +993,13 @@
         </is>
       </c>
       <c r="F23" s="5" t="n">
-        <v>6.832</v>
+        <v>6.83</v>
       </c>
     </row>
     <row r="24" ht="18" customHeight="1">
       <c r="A24" s="3" t="n"/>
       <c r="B24" s="3" t="n"/>
-      <c r="C24" s="6" t="inlineStr">
-        <is>
-          <t>小计</t>
-        </is>
-      </c>
+      <c r="C24" s="6" t="n"/>
       <c r="D24" s="7" t="inlineStr">
         <is>
           <t>m³</t>
@@ -1072,9 +1010,7 @@
           <t>6.832 ≈ 6.83</t>
         </is>
       </c>
-      <c r="F24" s="8" t="n">
-        <v>6.83</v>
-      </c>
+      <c r="F24" s="8" t="n"/>
     </row>
     <row r="25" ht="18" customHeight="1">
       <c r="A25" s="3" t="n">
@@ -1101,17 +1037,13 @@
         </is>
       </c>
       <c r="F25" s="5" t="n">
-        <v>17.6666</v>
+        <v>17.67</v>
       </c>
     </row>
     <row r="26" ht="18" customHeight="1">
       <c r="A26" s="3" t="n"/>
       <c r="B26" s="3" t="n"/>
-      <c r="C26" s="6" t="inlineStr">
-        <is>
-          <t>小计</t>
-        </is>
-      </c>
+      <c r="C26" s="6" t="n"/>
       <c r="D26" s="7" t="inlineStr">
         <is>
           <t>m³</t>
@@ -1122,9 +1054,7 @@
           <t>17.6666 ≈ 17.67</t>
         </is>
       </c>
-      <c r="F26" s="8" t="n">
-        <v>17.67</v>
-      </c>
+      <c r="F26" s="8" t="n"/>
     </row>
     <row r="27" ht="18" customHeight="1">
       <c r="A27" s="3" t="n">
@@ -1151,17 +1081,13 @@
         </is>
       </c>
       <c r="F27" s="5" t="n">
-        <v>26.4999</v>
+        <v>26.5</v>
       </c>
     </row>
     <row r="28" ht="18" customHeight="1">
       <c r="A28" s="3" t="n"/>
       <c r="B28" s="3" t="n"/>
-      <c r="C28" s="6" t="inlineStr">
-        <is>
-          <t>小计</t>
-        </is>
-      </c>
+      <c r="C28" s="6" t="n"/>
       <c r="D28" s="7" t="inlineStr">
         <is>
           <t>m³</t>
@@ -1172,9 +1098,7 @@
           <t>26.4999 ≈ 26.50</t>
         </is>
       </c>
-      <c r="F28" s="8" t="n">
-        <v>26.5</v>
-      </c>
+      <c r="F28" s="8" t="n"/>
     </row>
     <row r="29" ht="18" customHeight="1">
       <c r="A29" s="3" t="n">
@@ -1201,7 +1125,7 @@
         </is>
       </c>
       <c r="F29" s="5" t="n">
-        <v>8.614000000000001</v>
+        <v>22.71</v>
       </c>
     </row>
     <row r="30" ht="18" customHeight="1">
@@ -1222,9 +1146,7 @@
           <t>[1.5412]×8 = 12.3296</t>
         </is>
       </c>
-      <c r="F30" s="5" t="n">
-        <v>12.3296</v>
-      </c>
+      <c r="F30" s="8" t="n"/>
     </row>
     <row r="31" ht="18" customHeight="1">
       <c r="A31" s="3" t="n"/>
@@ -1244,18 +1166,12 @@
           <t>[0.8837]×2 = 1.7674</t>
         </is>
       </c>
-      <c r="F31" s="5" t="n">
-        <v>1.7674</v>
-      </c>
+      <c r="F31" s="8" t="n"/>
     </row>
     <row r="32" ht="18" customHeight="1">
       <c r="A32" s="3" t="n"/>
       <c r="B32" s="3" t="n"/>
-      <c r="C32" s="6" t="inlineStr">
-        <is>
-          <t>小计</t>
-        </is>
-      </c>
+      <c r="C32" s="6" t="n"/>
       <c r="D32" s="7" t="inlineStr">
         <is>
           <t>m³</t>
@@ -1266,9 +1182,7 @@
           <t>8.614 + 12.3296 + 1.7674 = 22.711 ≈ 22.71</t>
         </is>
       </c>
-      <c r="F32" s="8" t="n">
-        <v>22.71</v>
-      </c>
+      <c r="F32" s="8" t="n"/>
     </row>
     <row r="33" ht="18" customHeight="1">
       <c r="A33" s="3" t="n">
@@ -1295,7 +1209,7 @@
         </is>
       </c>
       <c r="F33" s="5" t="n">
-        <v>0.456</v>
+        <v>35.05</v>
       </c>
     </row>
     <row r="34" ht="18" customHeight="1">
@@ -1316,9 +1230,7 @@
           <t>[(0.35×0.4×1.55)-0.07]×9 = 1.323</t>
         </is>
       </c>
-      <c r="F34" s="5" t="n">
-        <v>1.323</v>
-      </c>
+      <c r="F34" s="8" t="n"/>
     </row>
     <row r="35" ht="18" customHeight="1">
       <c r="A35" s="3" t="n"/>
@@ -1338,9 +1250,7 @@
           <t>(0.4×0.4×1.55)-0.096 = 0.152</t>
         </is>
       </c>
-      <c r="F35" s="5" t="n">
-        <v>0.152</v>
-      </c>
+      <c r="F35" s="8" t="n"/>
     </row>
     <row r="36" ht="18" customHeight="1">
       <c r="A36" s="3" t="n"/>
@@ -1360,9 +1270,7 @@
           <t>(0.35×0.4×1.55)-0.07 = 0.147</t>
         </is>
       </c>
-      <c r="F36" s="5" t="n">
-        <v>0.147</v>
-      </c>
+      <c r="F36" s="8" t="n"/>
     </row>
     <row r="37" ht="18" customHeight="1">
       <c r="A37" s="3" t="n"/>
@@ -1382,9 +1290,7 @@
           <t>[(0.4×0.4×3.6)]×3 = 1.728</t>
         </is>
       </c>
-      <c r="F37" s="5" t="n">
-        <v>1.728</v>
-      </c>
+      <c r="F37" s="8" t="n"/>
     </row>
     <row r="38" ht="18" customHeight="1">
       <c r="A38" s="3" t="n"/>
@@ -1404,9 +1310,7 @@
           <t>[(0.35×0.4×3.6)]×9 = 4.536</t>
         </is>
       </c>
-      <c r="F38" s="5" t="n">
-        <v>4.536</v>
-      </c>
+      <c r="F38" s="8" t="n"/>
     </row>
     <row r="39" ht="18" customHeight="1">
       <c r="A39" s="3" t="n"/>
@@ -1426,9 +1330,7 @@
           <t>(0.4×0.4×3.6) = 0.576</t>
         </is>
       </c>
-      <c r="F39" s="5" t="n">
-        <v>0.576</v>
-      </c>
+      <c r="F39" s="8" t="n"/>
     </row>
     <row r="40" ht="18" customHeight="1">
       <c r="A40" s="3" t="n"/>
@@ -1448,9 +1350,7 @@
           <t>(0.35×0.4×3.6) = 0.504</t>
         </is>
       </c>
-      <c r="F40" s="5" t="n">
-        <v>0.504</v>
-      </c>
+      <c r="F40" s="8" t="n"/>
     </row>
     <row r="41" ht="18" customHeight="1">
       <c r="A41" s="3" t="n"/>
@@ -1470,9 +1370,7 @@
           <t>[(0.25×0.25×3.6)]×4 = 0.9</t>
         </is>
       </c>
-      <c r="F41" s="5" t="n">
-        <v>0.9</v>
-      </c>
+      <c r="F41" s="8" t="n"/>
     </row>
     <row r="42" ht="18" customHeight="1">
       <c r="A42" s="3" t="n"/>
@@ -1492,9 +1390,7 @@
           <t>[(0.4×0.4×3.6)]×3 = 1.728</t>
         </is>
       </c>
-      <c r="F42" s="5" t="n">
-        <v>1.728</v>
-      </c>
+      <c r="F42" s="8" t="n"/>
     </row>
     <row r="43" ht="18" customHeight="1">
       <c r="A43" s="3" t="n"/>
@@ -1514,9 +1410,7 @@
           <t>[(0.35×0.4×3.6)]×9 = 4.536</t>
         </is>
       </c>
-      <c r="F43" s="5" t="n">
-        <v>4.536</v>
-      </c>
+      <c r="F43" s="8" t="n"/>
     </row>
     <row r="44" ht="18" customHeight="1">
       <c r="A44" s="3" t="n"/>
@@ -1536,9 +1430,7 @@
           <t>(0.4×0.4×3.6) = 0.576</t>
         </is>
       </c>
-      <c r="F44" s="5" t="n">
-        <v>0.576</v>
-      </c>
+      <c r="F44" s="8" t="n"/>
     </row>
     <row r="45" ht="18" customHeight="1">
       <c r="A45" s="3" t="n"/>
@@ -1558,9 +1450,7 @@
           <t>(0.35×0.4×3.6) = 0.504</t>
         </is>
       </c>
-      <c r="F45" s="5" t="n">
-        <v>0.504</v>
-      </c>
+      <c r="F45" s="8" t="n"/>
     </row>
     <row r="46" ht="18" customHeight="1">
       <c r="A46" s="3" t="n"/>
@@ -1580,9 +1470,7 @@
           <t>[(0.25×0.25×3.6)]×4 = 0.9</t>
         </is>
       </c>
-      <c r="F46" s="5" t="n">
-        <v>0.9</v>
-      </c>
+      <c r="F46" s="8" t="n"/>
     </row>
     <row r="47" ht="18" customHeight="1">
       <c r="A47" s="3" t="n"/>
@@ -1602,9 +1490,7 @@
           <t>[(0.4×0.4×3.6)]×3 = 1.728</t>
         </is>
       </c>
-      <c r="F47" s="5" t="n">
-        <v>1.728</v>
-      </c>
+      <c r="F47" s="8" t="n"/>
     </row>
     <row r="48" ht="18" customHeight="1">
       <c r="A48" s="3" t="n"/>
@@ -1624,9 +1510,7 @@
           <t>[(0.35×0.4×3.6)]×9 = 4.536</t>
         </is>
       </c>
-      <c r="F48" s="5" t="n">
-        <v>4.536</v>
-      </c>
+      <c r="F48" s="8" t="n"/>
     </row>
     <row r="49" ht="18" customHeight="1">
       <c r="A49" s="3" t="n"/>
@@ -1646,9 +1530,7 @@
           <t>(0.4×0.4×3.6) = 0.576</t>
         </is>
       </c>
-      <c r="F49" s="5" t="n">
-        <v>0.576</v>
-      </c>
+      <c r="F49" s="8" t="n"/>
     </row>
     <row r="50" ht="18" customHeight="1">
       <c r="A50" s="3" t="n"/>
@@ -1668,9 +1550,7 @@
           <t>(0.35×0.4×3.6) = 0.504</t>
         </is>
       </c>
-      <c r="F50" s="5" t="n">
-        <v>0.504</v>
-      </c>
+      <c r="F50" s="8" t="n"/>
     </row>
     <row r="51" ht="18" customHeight="1">
       <c r="A51" s="3" t="n"/>
@@ -1690,9 +1570,7 @@
           <t>[(0.25×0.25×3.6)]×4 = 0.9</t>
         </is>
       </c>
-      <c r="F51" s="5" t="n">
-        <v>0.9</v>
-      </c>
+      <c r="F51" s="8" t="n"/>
     </row>
     <row r="52" ht="18" customHeight="1">
       <c r="A52" s="3" t="n"/>
@@ -1712,9 +1590,7 @@
           <t>[(0.4×0.4×3.6)]×3 = 1.728</t>
         </is>
       </c>
-      <c r="F52" s="5" t="n">
-        <v>1.728</v>
-      </c>
+      <c r="F52" s="8" t="n"/>
     </row>
     <row r="53" ht="18" customHeight="1">
       <c r="A53" s="3" t="n"/>
@@ -1734,9 +1610,7 @@
           <t>[(0.35×0.4×3.6)]×9 = 4.536</t>
         </is>
       </c>
-      <c r="F53" s="5" t="n">
-        <v>4.536</v>
-      </c>
+      <c r="F53" s="8" t="n"/>
     </row>
     <row r="54" ht="18" customHeight="1">
       <c r="A54" s="3" t="n"/>
@@ -1756,9 +1630,7 @@
           <t>(0.4×0.4×3.6) = 0.576</t>
         </is>
       </c>
-      <c r="F54" s="5" t="n">
-        <v>0.576</v>
-      </c>
+      <c r="F54" s="8" t="n"/>
     </row>
     <row r="55" ht="18" customHeight="1">
       <c r="A55" s="3" t="n"/>
@@ -1778,9 +1650,7 @@
           <t>(0.35×0.4×3.6) = 0.504</t>
         </is>
       </c>
-      <c r="F55" s="5" t="n">
-        <v>0.504</v>
-      </c>
+      <c r="F55" s="8" t="n"/>
     </row>
     <row r="56" ht="18" customHeight="1">
       <c r="A56" s="3" t="n"/>
@@ -1800,18 +1670,12 @@
           <t>[(0.25×0.25×3.6)]×4 = 0.9</t>
         </is>
       </c>
-      <c r="F56" s="5" t="n">
-        <v>0.9</v>
-      </c>
+      <c r="F56" s="8" t="n"/>
     </row>
     <row r="57" ht="32" customHeight="1">
       <c r="A57" s="3" t="n"/>
       <c r="B57" s="3" t="n"/>
-      <c r="C57" s="6" t="inlineStr">
-        <is>
-          <t>小计</t>
-        </is>
-      </c>
+      <c r="C57" s="6" t="n"/>
       <c r="D57" s="7" t="inlineStr">
         <is>
           <t>m³</t>
@@ -1822,9 +1686,7 @@
           <t>0.456 + 1.323 + 0.152 + 0.147 + 1.728 + 4.536 + 0.576 + 0.504 + 0.9 + 1.728 + 4.536 + 0.576 + 0.504 + 0.9 + 1.728 + 4.536 + 0.576 + 0.504 + 0.9 + 1.728 + 4.536 + 0.576 + 0.504 + 0.9 = 35.054 ≈ 35.05</t>
         </is>
       </c>
-      <c r="F57" s="8" t="n">
-        <v>35.05</v>
-      </c>
+      <c r="F57" s="8" t="n"/>
     </row>
     <row r="58" ht="18" customHeight="1">
       <c r="A58" s="3" t="n">
@@ -1851,7 +1713,7 @@
         </is>
       </c>
       <c r="F58" s="5" t="n">
-        <v>2.7183</v>
+        <v>70.15000000000001</v>
       </c>
     </row>
     <row r="59" ht="18" customHeight="1">
@@ -1872,9 +1734,7 @@
           <t>(0.3×0.55×12.25)-0.1897 = 1.8315</t>
         </is>
       </c>
-      <c r="F59" s="5" t="n">
-        <v>1.8315</v>
-      </c>
+      <c r="F59" s="8" t="n"/>
     </row>
     <row r="60" ht="18" customHeight="1">
       <c r="A60" s="3" t="n"/>
@@ -1894,9 +1754,7 @@
           <t>(0.25×0.4×8.875)-0.075 + (0.3×0.55×6.575)-0.066 = 1.8314</t>
         </is>
       </c>
-      <c r="F60" s="5" t="n">
-        <v>1.8314</v>
-      </c>
+      <c r="F60" s="8" t="n"/>
     </row>
     <row r="61" ht="18" customHeight="1">
       <c r="A61" s="3" t="n"/>
@@ -1916,9 +1774,7 @@
           <t>(0.25×0.35×3.375)-0.0394-0.0031 = 0.2528</t>
         </is>
       </c>
-      <c r="F61" s="5" t="n">
-        <v>0.2528</v>
-      </c>
+      <c r="F61" s="8" t="n"/>
     </row>
     <row r="62" ht="18" customHeight="1">
       <c r="A62" s="3" t="n"/>
@@ -1938,9 +1794,7 @@
           <t>(0.25×0.4×15.45)-0.145 = 1.4</t>
         </is>
       </c>
-      <c r="F62" s="5" t="n">
-        <v>1.4</v>
-      </c>
+      <c r="F62" s="8" t="n"/>
     </row>
     <row r="63" ht="18" customHeight="1">
       <c r="A63" s="3" t="n"/>
@@ -1960,9 +1814,7 @@
           <t>(0.25×0.35×3.4)-0.0284 = 0.2691</t>
         </is>
       </c>
-      <c r="F63" s="5" t="n">
-        <v>0.2691</v>
-      </c>
+      <c r="F63" s="8" t="n"/>
     </row>
     <row r="64" ht="18" customHeight="1">
       <c r="A64" s="3" t="n"/>
@@ -1982,9 +1834,7 @@
           <t>[(0.25×0.4×1.7)-0.02]×2 + (0.25×0.55×12.25)-0.1581 + (0.25×0.55×12.05)-0.1991-0.0009 = 3.2832</t>
         </is>
       </c>
-      <c r="F64" s="5" t="n">
-        <v>3.2832</v>
-      </c>
+      <c r="F64" s="8" t="n"/>
     </row>
     <row r="65" ht="18" customHeight="1">
       <c r="A65" s="3" t="n"/>
@@ -2004,9 +1854,7 @@
           <t>[(0.25×0.4×1.7)-0.02]×2 + (0.25×0.55×12.25)-0.165 + (0.25×0.55×12.05)-0.1375 = 3.3388</t>
         </is>
       </c>
-      <c r="F65" s="5" t="n">
-        <v>3.3388</v>
-      </c>
+      <c r="F65" s="8" t="n"/>
     </row>
     <row r="66" ht="18" customHeight="1">
       <c r="A66" s="3" t="n"/>
@@ -2026,9 +1874,7 @@
           <t>(0.25×0.4×1.625)-0.0125 + (0.25×0.55×12.125)-0.1787-0.0172 = 1.6213</t>
         </is>
       </c>
-      <c r="F66" s="5" t="n">
-        <v>1.6213</v>
-      </c>
+      <c r="F66" s="8" t="n"/>
     </row>
     <row r="67" ht="18" customHeight="1">
       <c r="A67" s="3" t="n"/>
@@ -2048,9 +1894,7 @@
           <t>(0.25×0.4×8.9)-0.0775 + (0.25×0.65×6.85)-0.1097 = 1.8159</t>
         </is>
       </c>
-      <c r="F67" s="5" t="n">
-        <v>1.8159</v>
-      </c>
+      <c r="F67" s="8" t="n"/>
     </row>
     <row r="68" ht="18" customHeight="1">
       <c r="A68" s="3" t="n"/>
@@ -2070,9 +1914,7 @@
           <t>(0.25×0.4×15.5)-0.175 = 1.375</t>
         </is>
       </c>
-      <c r="F68" s="5" t="n">
-        <v>1.375</v>
-      </c>
+      <c r="F68" s="8" t="n"/>
     </row>
     <row r="69" ht="18" customHeight="1">
       <c r="A69" s="3" t="n"/>
@@ -2092,9 +1934,7 @@
           <t>(0.25×0.4×15.5)-0.15 = 1.4</t>
         </is>
       </c>
-      <c r="F69" s="5" t="n">
-        <v>1.4</v>
-      </c>
+      <c r="F69" s="8" t="n"/>
     </row>
     <row r="70" ht="18" customHeight="1">
       <c r="A70" s="3" t="n"/>
@@ -2114,9 +1954,7 @@
           <t>(0.25×0.4×8.9)-0.05 + (0.25×0.4×3.2)-0.025 + (0.25×0.4×3.4)-0.025 = 1.45</t>
         </is>
       </c>
-      <c r="F70" s="5" t="n">
-        <v>1.45</v>
-      </c>
+      <c r="F70" s="8" t="n"/>
     </row>
     <row r="71" ht="18" customHeight="1">
       <c r="A71" s="3" t="n"/>
@@ -2136,9 +1974,7 @@
           <t>(0.25×0.4×1.7)-0.02 + (0.25×0.55×12.25)-0.1581 = 1.6763</t>
         </is>
       </c>
-      <c r="F71" s="5" t="n">
-        <v>1.6763</v>
-      </c>
+      <c r="F71" s="8" t="n"/>
     </row>
     <row r="72" ht="18" customHeight="1">
       <c r="A72" s="3" t="n"/>
@@ -2158,9 +1994,7 @@
           <t>(0.25×0.4×1.7)-0.02 + (0.25×0.55×12.25)-0.165 = 1.6694</t>
         </is>
       </c>
-      <c r="F72" s="5" t="n">
-        <v>1.6694</v>
-      </c>
+      <c r="F72" s="8" t="n"/>
     </row>
     <row r="73" ht="18" customHeight="1">
       <c r="A73" s="3" t="n"/>
@@ -2180,9 +2014,7 @@
           <t>(0.25×0.4×1.7)-0.02 + (0.25×0.55×12.05)-0.1375 = 1.6694</t>
         </is>
       </c>
-      <c r="F73" s="5" t="n">
-        <v>1.6694</v>
-      </c>
+      <c r="F73" s="8" t="n"/>
     </row>
     <row r="74" ht="18" customHeight="1">
       <c r="A74" s="3" t="n"/>
@@ -2202,9 +2034,7 @@
           <t>(0.25×0.4×1.625)-0.0125 + (0.25×0.55×12.125)-0.1787-0.0172 = 1.6213</t>
         </is>
       </c>
-      <c r="F74" s="5" t="n">
-        <v>1.6213</v>
-      </c>
+      <c r="F74" s="8" t="n"/>
     </row>
     <row r="75" ht="18" customHeight="1">
       <c r="A75" s="3" t="n"/>
@@ -2224,9 +2054,7 @@
           <t>(0.25×0.4×1.7)-0.02 + (0.25×0.55×12.05)-0.1986-0.0006 = 1.6077</t>
         </is>
       </c>
-      <c r="F75" s="5" t="n">
-        <v>1.6077</v>
-      </c>
+      <c r="F75" s="8" t="n"/>
     </row>
     <row r="76" ht="18" customHeight="1">
       <c r="A76" s="3" t="n"/>
@@ -2246,9 +2074,7 @@
           <t>(0.25×0.4×8.9)-0.0775 + (0.25×0.65×6.85)-0.1097 = 1.8159</t>
         </is>
       </c>
-      <c r="F76" s="5" t="n">
-        <v>1.8159</v>
-      </c>
+      <c r="F76" s="8" t="n"/>
     </row>
     <row r="77" ht="18" customHeight="1">
       <c r="A77" s="3" t="n"/>
@@ -2268,9 +2094,7 @@
           <t>(0.25×0.4×15.5)-0.175 = 1.375</t>
         </is>
       </c>
-      <c r="F77" s="5" t="n">
-        <v>1.375</v>
-      </c>
+      <c r="F77" s="8" t="n"/>
     </row>
     <row r="78" ht="18" customHeight="1">
       <c r="A78" s="3" t="n"/>
@@ -2290,9 +2114,7 @@
           <t>(0.25×0.4×15.5)-0.15 = 1.4</t>
         </is>
       </c>
-      <c r="F78" s="5" t="n">
-        <v>1.4</v>
-      </c>
+      <c r="F78" s="8" t="n"/>
     </row>
     <row r="79" ht="18" customHeight="1">
       <c r="A79" s="3" t="n"/>
@@ -2312,9 +2134,7 @@
           <t>(0.25×0.3×3)-0.0188 = 0.2062</t>
         </is>
       </c>
-      <c r="F79" s="5" t="n">
-        <v>0.2062</v>
-      </c>
+      <c r="F79" s="8" t="n"/>
     </row>
     <row r="80" ht="18" customHeight="1">
       <c r="A80" s="3" t="n"/>
@@ -2334,9 +2154,7 @@
           <t>(0.25×0.4×15.5)-0.1 = 1.45</t>
         </is>
       </c>
-      <c r="F80" s="5" t="n">
-        <v>1.45</v>
-      </c>
+      <c r="F80" s="8" t="n"/>
     </row>
     <row r="81" ht="18" customHeight="1">
       <c r="A81" s="3" t="n"/>
@@ -2356,9 +2174,7 @@
           <t>(0.25×0.4×4.45)-0.025 = 0.42</t>
         </is>
       </c>
-      <c r="F81" s="5" t="n">
-        <v>0.42</v>
-      </c>
+      <c r="F81" s="8" t="n"/>
     </row>
     <row r="82" ht="18" customHeight="1">
       <c r="A82" s="3" t="n"/>
@@ -2378,9 +2194,7 @@
           <t>(0.25×0.3×2.05)-0.0188 = 0.135</t>
         </is>
       </c>
-      <c r="F82" s="5" t="n">
-        <v>0.135</v>
-      </c>
+      <c r="F82" s="8" t="n"/>
     </row>
     <row r="83" ht="18" customHeight="1">
       <c r="A83" s="3" t="n"/>
@@ -2400,9 +2214,7 @@
           <t>(0.25×0.35×3.4)-0.0219 + (0.25×0.35×3.2)-0.0219 = 0.5337</t>
         </is>
       </c>
-      <c r="F83" s="5" t="n">
-        <v>0.5337</v>
-      </c>
+      <c r="F83" s="8" t="n"/>
     </row>
     <row r="84" ht="18" customHeight="1">
       <c r="A84" s="3" t="n"/>
@@ -2422,9 +2234,7 @@
           <t>(0.25×0.4×1.7)-0.02 + (0.25×0.55×12.25)-0.1581 = 1.6763</t>
         </is>
       </c>
-      <c r="F84" s="5" t="n">
-        <v>1.6763</v>
-      </c>
+      <c r="F84" s="8" t="n"/>
     </row>
     <row r="85" ht="18" customHeight="1">
       <c r="A85" s="3" t="n"/>
@@ -2444,9 +2254,7 @@
           <t>(0.25×0.4×1.7)-0.02 + (0.25×0.55×12.25)-0.165 = 1.6694</t>
         </is>
       </c>
-      <c r="F85" s="5" t="n">
-        <v>1.6694</v>
-      </c>
+      <c r="F85" s="8" t="n"/>
     </row>
     <row r="86" ht="18" customHeight="1">
       <c r="A86" s="3" t="n"/>
@@ -2466,9 +2274,7 @@
           <t>(0.25×0.4×1.7)-0.02 + (0.25×0.55×12.05)-0.1375 = 1.6694</t>
         </is>
       </c>
-      <c r="F86" s="5" t="n">
-        <v>1.6694</v>
-      </c>
+      <c r="F86" s="8" t="n"/>
     </row>
     <row r="87" ht="18" customHeight="1">
       <c r="A87" s="3" t="n"/>
@@ -2488,9 +2294,7 @@
           <t>(0.25×0.4×1.625)-0.0125 + (0.25×0.55×12.125)-0.1787-0.0172 = 1.6213</t>
         </is>
       </c>
-      <c r="F87" s="5" t="n">
-        <v>1.6213</v>
-      </c>
+      <c r="F87" s="8" t="n"/>
     </row>
     <row r="88" ht="18" customHeight="1">
       <c r="A88" s="3" t="n"/>
@@ -2510,9 +2314,7 @@
           <t>(0.25×0.4×1.7)-0.02 + (0.25×0.55×12.05)-0.1986-0.0006 = 1.6077</t>
         </is>
       </c>
-      <c r="F88" s="5" t="n">
-        <v>1.6077</v>
-      </c>
+      <c r="F88" s="8" t="n"/>
     </row>
     <row r="89" ht="18" customHeight="1">
       <c r="A89" s="3" t="n"/>
@@ -2532,9 +2334,7 @@
           <t>(0.25×0.4×8.9)-0.0775 + (0.25×0.65×6.85)-0.1097 = 1.8159</t>
         </is>
       </c>
-      <c r="F89" s="5" t="n">
-        <v>1.8159</v>
-      </c>
+      <c r="F89" s="8" t="n"/>
     </row>
     <row r="90" ht="18" customHeight="1">
       <c r="A90" s="3" t="n"/>
@@ -2554,9 +2354,7 @@
           <t>(0.25×0.4×15.5)-0.175 = 1.375</t>
         </is>
       </c>
-      <c r="F90" s="5" t="n">
-        <v>1.375</v>
-      </c>
+      <c r="F90" s="8" t="n"/>
     </row>
     <row r="91" ht="18" customHeight="1">
       <c r="A91" s="3" t="n"/>
@@ -2576,9 +2374,7 @@
           <t>(0.25×0.4×15.5)-0.15 = 1.4</t>
         </is>
       </c>
-      <c r="F91" s="5" t="n">
-        <v>1.4</v>
-      </c>
+      <c r="F91" s="8" t="n"/>
     </row>
     <row r="92" ht="18" customHeight="1">
       <c r="A92" s="3" t="n"/>
@@ -2598,9 +2394,7 @@
           <t>(0.25×0.3×3)-0.0188 = 0.2062</t>
         </is>
       </c>
-      <c r="F92" s="5" t="n">
-        <v>0.2062</v>
-      </c>
+      <c r="F92" s="8" t="n"/>
     </row>
     <row r="93" ht="18" customHeight="1">
       <c r="A93" s="3" t="n"/>
@@ -2620,9 +2414,7 @@
           <t>(0.25×0.4×15.5)-0.1 = 1.45</t>
         </is>
       </c>
-      <c r="F93" s="5" t="n">
-        <v>1.45</v>
-      </c>
+      <c r="F93" s="8" t="n"/>
     </row>
     <row r="94" ht="18" customHeight="1">
       <c r="A94" s="3" t="n"/>
@@ -2642,9 +2434,7 @@
           <t>(0.25×0.4×4.45)-0.025 = 0.42</t>
         </is>
       </c>
-      <c r="F94" s="5" t="n">
-        <v>0.42</v>
-      </c>
+      <c r="F94" s="8" t="n"/>
     </row>
     <row r="95" ht="18" customHeight="1">
       <c r="A95" s="3" t="n"/>
@@ -2664,9 +2454,7 @@
           <t>(0.25×0.3×2.05)-0.0188 = 0.135</t>
         </is>
       </c>
-      <c r="F95" s="5" t="n">
-        <v>0.135</v>
-      </c>
+      <c r="F95" s="8" t="n"/>
     </row>
     <row r="96" ht="18" customHeight="1">
       <c r="A96" s="3" t="n"/>
@@ -2686,9 +2474,7 @@
           <t>(0.25×0.35×3.2)-0.0219 + (0.25×0.35×3.4)-0.0219 = 0.5337</t>
         </is>
       </c>
-      <c r="F96" s="5" t="n">
-        <v>0.5337</v>
-      </c>
+      <c r="F96" s="8" t="n"/>
     </row>
     <row r="97" ht="18" customHeight="1">
       <c r="A97" s="3" t="n"/>
@@ -2708,9 +2494,7 @@
           <t>[(0.25×0.4×1.7)-0.02]×2 + (0.25×0.55×12.25)-0.1581 + (0.25×0.55×12.05)-0.1986-0.0006 = 3.284</t>
         </is>
       </c>
-      <c r="F97" s="5" t="n">
-        <v>3.284</v>
-      </c>
+      <c r="F97" s="8" t="n"/>
     </row>
     <row r="98" ht="18" customHeight="1">
       <c r="A98" s="3" t="n"/>
@@ -2730,9 +2514,7 @@
           <t>[(0.25×0.4×1.7)-0.02]×2 + (0.25×0.55×12.25)-0.165 + (0.25×0.55×12.05)-0.1375 = 3.3388</t>
         </is>
       </c>
-      <c r="F98" s="5" t="n">
-        <v>3.3388</v>
-      </c>
+      <c r="F98" s="8" t="n"/>
     </row>
     <row r="99" ht="18" customHeight="1">
       <c r="A99" s="3" t="n"/>
@@ -2752,9 +2534,7 @@
           <t>(0.25×0.4×1.625)-0.0125 + (0.25×0.55×12.125)-0.1787-0.0172 = 1.6213</t>
         </is>
       </c>
-      <c r="F99" s="5" t="n">
-        <v>1.6213</v>
-      </c>
+      <c r="F99" s="8" t="n"/>
     </row>
     <row r="100" ht="18" customHeight="1">
       <c r="A100" s="3" t="n"/>
@@ -2774,9 +2554,7 @@
           <t>(0.25×0.4×8.9)-0.0775 + (0.25×0.65×6.85)-0.1097 = 1.8159</t>
         </is>
       </c>
-      <c r="F100" s="5" t="n">
-        <v>1.8159</v>
-      </c>
+      <c r="F100" s="8" t="n"/>
     </row>
     <row r="101" ht="18" customHeight="1">
       <c r="A101" s="3" t="n"/>
@@ -2796,9 +2574,7 @@
           <t>(0.25×0.4×15.5)-0.175 = 1.375</t>
         </is>
       </c>
-      <c r="F101" s="5" t="n">
-        <v>1.375</v>
-      </c>
+      <c r="F101" s="8" t="n"/>
     </row>
     <row r="102" ht="18" customHeight="1">
       <c r="A102" s="3" t="n"/>
@@ -2818,9 +2594,7 @@
           <t>(0.25×0.4×15.5)-0.15 = 1.4</t>
         </is>
       </c>
-      <c r="F102" s="5" t="n">
-        <v>1.4</v>
-      </c>
+      <c r="F102" s="8" t="n"/>
     </row>
     <row r="103" ht="18" customHeight="1">
       <c r="A103" s="3" t="n"/>
@@ -2840,9 +2614,7 @@
           <t>(0.25×0.4×15.5)-0.1 = 1.45</t>
         </is>
       </c>
-      <c r="F103" s="5" t="n">
-        <v>1.45</v>
-      </c>
+      <c r="F103" s="8" t="n"/>
     </row>
     <row r="104" ht="18" customHeight="1">
       <c r="A104" s="3" t="n"/>
@@ -2862,9 +2634,7 @@
           <t>(0.25×0.35×3.4)-0.0219 = 0.2756</t>
         </is>
       </c>
-      <c r="F104" s="5" t="n">
-        <v>0.2756</v>
-      </c>
+      <c r="F104" s="8" t="n"/>
     </row>
     <row r="105" ht="18" customHeight="1">
       <c r="A105" s="3" t="n"/>
@@ -2884,9 +2654,7 @@
           <t>(0.25×0.4×12.1)-0.075 = 1.135</t>
         </is>
       </c>
-      <c r="F105" s="5" t="n">
-        <v>1.135</v>
-      </c>
+      <c r="F105" s="8" t="n"/>
     </row>
     <row r="106" ht="18" customHeight="1">
       <c r="A106" s="3" t="n"/>
@@ -2906,9 +2674,7 @@
           <t>(0.25×0.4×3.4) = 0.34</t>
         </is>
       </c>
-      <c r="F106" s="5" t="n">
-        <v>0.34</v>
-      </c>
+      <c r="F106" s="8" t="n"/>
     </row>
     <row r="107" ht="18" customHeight="1">
       <c r="A107" s="3" t="n"/>
@@ -2928,18 +2694,12 @@
           <t>(0.25×0.4×3.65) = 0.365</t>
         </is>
       </c>
-      <c r="F107" s="5" t="n">
-        <v>0.365</v>
-      </c>
+      <c r="F107" s="8" t="n"/>
     </row>
     <row r="108" ht="46" customHeight="1">
       <c r="A108" s="3" t="n"/>
       <c r="B108" s="3" t="n"/>
-      <c r="C108" s="6" t="inlineStr">
-        <is>
-          <t>小计</t>
-        </is>
-      </c>
+      <c r="C108" s="6" t="n"/>
       <c r="D108" s="7" t="inlineStr">
         <is>
           <t>m³</t>
@@ -2950,9 +2710,7 @@
           <t>2.7183 + 1.8315 + 1.8314 + 0.2528 + 1.4 + 0.2691 + 3.2832 + 3.3388 + 1.6213 + 1.8159 + 1.375 + 1.4 + 1.45 + 1.6763 + 1.6694 + 1.6694 + 1.6213 + 1.6077 + 1.8159 + 1.375 + 1.4 + 0.2062 + 1.45 + 0.42 + 0.135 + 0.5337 + 1.6763 + 1.6694 + 1.6694 + 1.6213 + 1.6077 + 1.8159 + 1.375 + 1.4 + 0.2062 + 1.45 + 0.42 + 0.135 + 0.5337 + 3.284 + 3.3388 + 1.6213 + 1.8159 + 1.375 + 1.4 + 1.45 + 0.2756 + 1.135 + 0.34 + 0.365 = 70.1477 ≈ 70.15</t>
         </is>
       </c>
-      <c r="F108" s="8" t="n">
-        <v>70.15000000000001</v>
-      </c>
+      <c r="F108" s="8" t="n"/>
     </row>
     <row r="109" ht="18" customHeight="1">
       <c r="A109" s="3" t="n">
@@ -2979,7 +2737,7 @@
         </is>
       </c>
       <c r="F109" s="5" t="n">
-        <v>5.2434</v>
+        <v>75.48999999999999</v>
       </c>
     </row>
     <row r="110" ht="32" customHeight="1">
@@ -3000,9 +2758,7 @@
           <t>((5.85×4.45)×0.12)-0.0238-0.282 + ((5.85×4.45)×0.12)-0.0211-0.2835 + ((6.15×4.45)×0.12)-0.022-0.2921 + ((6.15×4.45)×0.12)-0.0238-0.291 + ((3.4×1.945)×0.12)-0.0181-0.1382-0.0172 = 12.1968</t>
         </is>
       </c>
-      <c r="F110" s="5" t="n">
-        <v>12.1968</v>
-      </c>
+      <c r="F110" s="8" t="n"/>
     </row>
     <row r="111" ht="18" customHeight="1">
       <c r="A111" s="3" t="n"/>
@@ -3022,9 +2778,7 @@
           <t>((3.4×1.5)×0.09)-0.0025-0.1021 + ((3.2×1.5)×0.09)-0.0023-0.0979 + ((4.45×1.5)×0.09)-0.0042-0.124 + ((4.45×1.5)×0.09)-0.0045-0.1237 = 1.6313</t>
         </is>
       </c>
-      <c r="F111" s="5" t="n">
-        <v>1.6313</v>
-      </c>
+      <c r="F111" s="8" t="n"/>
     </row>
     <row r="112" ht="32" customHeight="1">
       <c r="A112" s="3" t="n"/>
@@ -3044,9 +2798,7 @@
           <t>((4.45×3.15)×0.1)-0.011-0.175 + ((6.15×3.2)×0.1)-0.0135-0.2162 + ((4.35×3.4)×0.1)-0.0062-0.1828 + ((3.2×2.4)×0.1)-0.0111-0.1237 + ((3.45×3.2)×0.1)-0.0127-0.1488 = 5.8196</t>
         </is>
       </c>
-      <c r="F112" s="5" t="n">
-        <v>5.8196</v>
-      </c>
+      <c r="F112" s="8" t="n"/>
     </row>
     <row r="113" ht="32" customHeight="1">
       <c r="A113" s="3" t="n"/>
@@ -3066,9 +2818,7 @@
           <t>((5.85×4.45)×0.12)-0.0238-0.282 + ((5.85×4.45)×0.12)-0.0211-0.2835 + ((2.05×1.8)×0.12)-0.0048-0.1039 + ((2.05×1.2)×0.12)-0.09 + ((6.15×4.45)×0.12)-0.022-0.2921 = 9.1466</t>
         </is>
       </c>
-      <c r="F113" s="5" t="n">
-        <v>9.146599999999999</v>
-      </c>
+      <c r="F113" s="8" t="n"/>
     </row>
     <row r="114" ht="32" customHeight="1">
       <c r="A114" s="3" t="n"/>
@@ -3088,9 +2838,7 @@
           <t>((3×2.4)×0.09)-0.0043-0.1122 + ((3.4×1.8)×0.09)-0.0079-0.1046 + ((3.2×1.5)×0.09)-0.0023-0.0979 + ((3.4×1.5)×0.09)-0.0025-0.1021 + ((4.45×1.5)×0.09)-0.0042-0.124 + ((4.45×1.5)×0.09)-0.0045-0.1237 + ((3.4×1.31)×0.09)-0.0107-0.0918 = 2.8992</t>
         </is>
       </c>
-      <c r="F114" s="5" t="n">
-        <v>2.8992</v>
-      </c>
+      <c r="F114" s="8" t="n"/>
     </row>
     <row r="115" ht="32" customHeight="1">
       <c r="A115" s="3" t="n"/>
@@ -3110,9 +2858,7 @@
           <t>((3.2×2.4)×0.1)-0.0111-0.1237 + ((6.15×3.2)×0.1)-0.0135-0.2162 + ((3.45×3.2)×0.1)-0.0127-0.1488 + ((4.35×3.4)×0.1)-0.0062-0.1828 + ((4.45×3.15)×0.1)-0.011-0.175 = 5.8196</t>
         </is>
       </c>
-      <c r="F115" s="5" t="n">
-        <v>5.8196</v>
-      </c>
+      <c r="F115" s="8" t="n"/>
     </row>
     <row r="116" ht="32" customHeight="1">
       <c r="A116" s="3" t="n"/>
@@ -3132,9 +2878,7 @@
           <t>((6.15×4.45)×0.12)-0.022-0.2921 + ((2.05×1.2)×0.12)-0.09 + ((5.85×4.45)×0.12)-0.0238-0.282 + ((2.05×1.8)×0.12)-0.0048-0.1039 + ((5.85×4.45)×0.12)-0.0211-0.2835 = 9.1466</t>
         </is>
       </c>
-      <c r="F116" s="5" t="n">
-        <v>9.146599999999999</v>
-      </c>
+      <c r="F116" s="8" t="n"/>
     </row>
     <row r="117" ht="32" customHeight="1">
       <c r="A117" s="3" t="n"/>
@@ -3154,9 +2898,7 @@
           <t>((4.45×1.5)×0.09)-0.0045-0.1237 + ((4.45×1.5)×0.09)-0.0042-0.124 + ((3.4×1.5)×0.09)-0.0025-0.1021 + ((3.2×1.5)×0.09)-0.0023-0.0979 + ((3.4×1.8)×0.09)-0.0079-0.1046 + ((3×2.4)×0.09)-0.0043-0.1122 + ((3.4×1.31)×0.09)-0.0107-0.0918 = 2.8992</t>
         </is>
       </c>
-      <c r="F117" s="5" t="n">
-        <v>2.8992</v>
-      </c>
+      <c r="F117" s="8" t="n"/>
     </row>
     <row r="118" ht="46" customHeight="1">
       <c r="A118" s="3" t="n"/>
@@ -3176,9 +2918,7 @@
           <t>((4.45×0.65)×0.1)-0.011-0.1125 + ((4.45×0.65)×0.1)-0.0096-0.1131 + ((3.2×0.65)×0.1)-0.0096-0.0819 + ((5.2×3.2)×0.1)-0.0142-0.1906 + ((6.15×3.2)×0.1)-0.0135-0.2163 + ((4.35×3.4)×0.1)-0.0062-0.1828 + ((3.4×1.5)×0.1)-0.0028-0.1134 + ((3.2×1.5)×0.1)-0.0025-0.1088 + ((4.45×1.5)×0.1)-0.0047-0.1378 + ((4.45×1.5)×0.1)-0.005-0.1375 = 6.7486</t>
         </is>
       </c>
-      <c r="F118" s="5" t="n">
-        <v>6.7486</v>
-      </c>
+      <c r="F118" s="8" t="n"/>
     </row>
     <row r="119" ht="18" customHeight="1">
       <c r="A119" s="3" t="n"/>
@@ -3198,9 +2938,7 @@
           <t>((5.2×4.45)×0.12)-0.0106-0.273 + ((5.2×4.45)×0.12)-0.0096-0.2737 + ((6.15×4.45)×0.12)-0.022-0.2921 + ((6.15×4.45)×0.12)-0.0238-0.291 = 10.9259</t>
         </is>
       </c>
-      <c r="F119" s="5" t="n">
-        <v>10.9259</v>
-      </c>
+      <c r="F119" s="8" t="n"/>
     </row>
     <row r="120" ht="18" customHeight="1">
       <c r="A120" s="3" t="n"/>
@@ -3220,9 +2958,7 @@
           <t>((3.4×1.8)×0.09)-0.0079-0.1046 + ((3.4×1.31)×0.09)-0.0107-0.0918 = 0.7365</t>
         </is>
       </c>
-      <c r="F120" s="5" t="n">
-        <v>0.7365</v>
-      </c>
+      <c r="F120" s="8" t="n"/>
     </row>
     <row r="121" ht="18" customHeight="1">
       <c r="A121" s="3" t="n"/>
@@ -3242,18 +2978,12 @@
           <t>((3.41×0.655)×0.1)-0.0426-0.0409 + ((7.005×3.41)×0.1)-0.07-0.1778 = 2.2807</t>
         </is>
       </c>
-      <c r="F121" s="5" t="n">
-        <v>2.2807</v>
-      </c>
+      <c r="F121" s="8" t="n"/>
     </row>
     <row r="122" ht="18" customHeight="1">
       <c r="A122" s="3" t="n"/>
       <c r="B122" s="3" t="n"/>
-      <c r="C122" s="6" t="inlineStr">
-        <is>
-          <t>小计</t>
-        </is>
-      </c>
+      <c r="C122" s="6" t="n"/>
       <c r="D122" s="7" t="inlineStr">
         <is>
           <t>m³</t>
@@ -3264,9 +2994,7 @@
           <t>5.2434 + 12.1968 + 1.6313 + 5.8196 + 9.1466 + 2.8992 + 5.8196 + 9.1466 + 2.8992 + 6.7486 + 10.9259 + 0.7365 + 2.2807 = 75.494 ≈ 75.49</t>
         </is>
       </c>
-      <c r="F122" s="8" t="n">
-        <v>75.48999999999999</v>
-      </c>
+      <c r="F122" s="8" t="n"/>
     </row>
     <row r="123" ht="18" customHeight="1">
       <c r="A123" s="3" t="n">
@@ -3293,7 +3021,7 @@
         </is>
       </c>
       <c r="F123" s="5" t="n">
-        <v>0.189</v>
+        <v>0.38</v>
       </c>
     </row>
     <row r="124" ht="18" customHeight="1">
@@ -3314,18 +3042,12 @@
           <t>(0.25×0.35×2.225) = 0.1947</t>
         </is>
       </c>
-      <c r="F124" s="5" t="n">
-        <v>0.1947</v>
-      </c>
+      <c r="F124" s="8" t="n"/>
     </row>
     <row r="125" ht="18" customHeight="1">
       <c r="A125" s="3" t="n"/>
       <c r="B125" s="3" t="n"/>
-      <c r="C125" s="6" t="inlineStr">
-        <is>
-          <t>小计</t>
-        </is>
-      </c>
+      <c r="C125" s="6" t="n"/>
       <c r="D125" s="7" t="inlineStr">
         <is>
           <t>m³</t>
@@ -3336,9 +3058,7 @@
           <t>0.189 + 0.1947 = 0.3837 ≈ 0.38</t>
         </is>
       </c>
-      <c r="F125" s="8" t="n">
-        <v>0.38</v>
-      </c>
+      <c r="F125" s="8" t="n"/>
     </row>
     <row r="126" ht="18" customHeight="1">
       <c r="A126" s="3" t="n">
@@ -3365,7 +3085,7 @@
         </is>
       </c>
       <c r="F126" s="5" t="n">
-        <v>2.8942</v>
+        <v>11.14</v>
       </c>
     </row>
     <row r="127" ht="18" customHeight="1">
@@ -3386,9 +3106,7 @@
           <t>1.8087+0.5499+0.3899 = 2.7485</t>
         </is>
       </c>
-      <c r="F127" s="5" t="n">
-        <v>2.7485</v>
-      </c>
+      <c r="F127" s="8" t="n"/>
     </row>
     <row r="128" ht="18" customHeight="1">
       <c r="A128" s="3" t="n"/>
@@ -3408,9 +3126,7 @@
           <t>1.8087+0.5499+0.3899 = 2.7485</t>
         </is>
       </c>
-      <c r="F128" s="5" t="n">
-        <v>2.7485</v>
-      </c>
+      <c r="F128" s="8" t="n"/>
     </row>
     <row r="129" ht="18" customHeight="1">
       <c r="A129" s="3" t="n"/>
@@ -3430,18 +3146,12 @@
           <t>1.8087+0.5499+0.3899 = 2.7485</t>
         </is>
       </c>
-      <c r="F129" s="5" t="n">
-        <v>2.7485</v>
-      </c>
+      <c r="F129" s="8" t="n"/>
     </row>
     <row r="130" ht="18" customHeight="1">
       <c r="A130" s="3" t="n"/>
       <c r="B130" s="3" t="n"/>
-      <c r="C130" s="6" t="inlineStr">
-        <is>
-          <t>小计</t>
-        </is>
-      </c>
+      <c r="C130" s="6" t="n"/>
       <c r="D130" s="7" t="inlineStr">
         <is>
           <t>m³</t>
@@ -3452,9 +3162,7 @@
           <t>2.8942 + 2.7485 + 2.7485 + 2.7485 = 11.1397 ≈ 11.14</t>
         </is>
       </c>
-      <c r="F130" s="8" t="n">
-        <v>11.14</v>
-      </c>
+      <c r="F130" s="8" t="n"/>
     </row>
     <row r="131" ht="18" customHeight="1">
       <c r="A131" s="3" t="n">
@@ -3481,7 +3189,7 @@
         </is>
       </c>
       <c r="F131" s="5" t="n">
-        <v>0.0969</v>
+        <v>6.9</v>
       </c>
     </row>
     <row r="132" ht="18" customHeight="1">
@@ -3502,9 +3210,7 @@
           <t>[(0.25×0.37)×1.55]×3 = 0.4302</t>
         </is>
       </c>
-      <c r="F132" s="5" t="n">
-        <v>0.4302</v>
-      </c>
+      <c r="F132" s="8" t="n"/>
     </row>
     <row r="133" ht="18" customHeight="1">
       <c r="A133" s="3" t="n"/>
@@ -3524,9 +3230,7 @@
           <t>(0.25×0.25)×3.6-0.025 = 0.2</t>
         </is>
       </c>
-      <c r="F133" s="5" t="n">
-        <v>0.2</v>
-      </c>
+      <c r="F133" s="8" t="n"/>
     </row>
     <row r="134" ht="18" customHeight="1">
       <c r="A134" s="3" t="n"/>
@@ -3546,9 +3250,7 @@
           <t>[(0.25×0.37)×3.6-0.025]×3 = 0.924</t>
         </is>
       </c>
-      <c r="F134" s="5" t="n">
-        <v>0.924</v>
-      </c>
+      <c r="F134" s="8" t="n"/>
     </row>
     <row r="135" ht="18" customHeight="1">
       <c r="A135" s="3" t="n"/>
@@ -3568,9 +3270,7 @@
           <t>(0.25×0.25)×3.6+0.0461-0.025 = 0.2461</t>
         </is>
       </c>
-      <c r="F135" s="5" t="n">
-        <v>0.2461</v>
-      </c>
+      <c r="F135" s="8" t="n"/>
     </row>
     <row r="136" ht="18" customHeight="1">
       <c r="A136" s="3" t="n"/>
@@ -3590,9 +3290,7 @@
           <t>[(0.25×0.37)×3.6+0.0461-0.025]×3 = 1.0623</t>
         </is>
       </c>
-      <c r="F136" s="5" t="n">
-        <v>1.0623</v>
-      </c>
+      <c r="F136" s="8" t="n"/>
     </row>
     <row r="137" ht="18" customHeight="1">
       <c r="A137" s="3" t="n"/>
@@ -3612,9 +3310,7 @@
           <t>(0.25×0.25)×3.6+0.0461-0.025 = 0.2461</t>
         </is>
       </c>
-      <c r="F137" s="5" t="n">
-        <v>0.2461</v>
-      </c>
+      <c r="F137" s="8" t="n"/>
     </row>
     <row r="138" ht="18" customHeight="1">
       <c r="A138" s="3" t="n"/>
@@ -3634,9 +3330,7 @@
           <t>[(0.25×0.37)×3.6+0.0461-0.025]×3 = 1.0623</t>
         </is>
       </c>
-      <c r="F138" s="5" t="n">
-        <v>1.0623</v>
-      </c>
+      <c r="F138" s="8" t="n"/>
     </row>
     <row r="139" ht="18" customHeight="1">
       <c r="A139" s="3" t="n"/>
@@ -3656,9 +3350,7 @@
           <t>(0.25×0.25)×3.6+0.0461-0.025 = 0.2461</t>
         </is>
       </c>
-      <c r="F139" s="5" t="n">
-        <v>0.2461</v>
-      </c>
+      <c r="F139" s="8" t="n"/>
     </row>
     <row r="140" ht="18" customHeight="1">
       <c r="A140" s="3" t="n"/>
@@ -3678,9 +3370,7 @@
           <t>[(0.25×0.37)×3.6+0.0461-0.025]×3 = 1.0623</t>
         </is>
       </c>
-      <c r="F140" s="5" t="n">
-        <v>1.0623</v>
-      </c>
+      <c r="F140" s="8" t="n"/>
     </row>
     <row r="141" ht="32" customHeight="1">
       <c r="A141" s="3" t="n"/>
@@ -3700,9 +3390,7 @@
           <t>(0.25×0.25)×3+0.0496-0.0049-0.0004-0.0002-0.0017 + (0.25×0.25)×3+0.0432-0.0049-0.0004-0.0017 + (0.25×0.25)×3+0.0496-0.0042-0.0002-0.0017 + (0.25×0.25)×3+0.0407-0.0021-0.0219-0.0065 = 0.8823</t>
         </is>
       </c>
-      <c r="F141" s="5" t="n">
-        <v>0.8823</v>
-      </c>
+      <c r="F141" s="8" t="n"/>
     </row>
     <row r="142" ht="18" customHeight="1">
       <c r="A142" s="3" t="n"/>
@@ -3722,18 +3410,12 @@
           <t>[(0.25×0.37)×1.6+0.0128-0.0121]×2 + (0.25×0.37)×1.6+0.0128-0.012 = 0.4462</t>
         </is>
       </c>
-      <c r="F142" s="5" t="n">
-        <v>0.4462</v>
-      </c>
+      <c r="F142" s="8" t="n"/>
     </row>
     <row r="143" ht="18" customHeight="1">
       <c r="A143" s="3" t="n"/>
       <c r="B143" s="3" t="n"/>
-      <c r="C143" s="6" t="inlineStr">
-        <is>
-          <t>小计</t>
-        </is>
-      </c>
+      <c r="C143" s="6" t="n"/>
       <c r="D143" s="7" t="inlineStr">
         <is>
           <t>m³</t>
@@ -3744,9 +3426,7 @@
           <t>0.0969 + 0.4302 + 0.2 + 0.924 + 0.2461 + 1.0623 + 0.2461 + 1.0623 + 0.2461 + 1.0623 + 0.8823 + 0.4462 = 6.9048 ≈ 6.90</t>
         </is>
       </c>
-      <c r="F143" s="8" t="n">
-        <v>6.9</v>
-      </c>
+      <c r="F143" s="8" t="n"/>
     </row>
     <row r="144" ht="18" customHeight="1">
       <c r="A144" s="3" t="n">
@@ -3773,7 +3453,7 @@
         </is>
       </c>
       <c r="F144" s="5" t="n">
-        <v>1.1142</v>
+        <v>1.42</v>
       </c>
     </row>
     <row r="145" ht="18" customHeight="1">
@@ -3794,18 +3474,12 @@
           <t>(0.24×0.4×3.65)-0.048 = 0.3024</t>
         </is>
       </c>
-      <c r="F145" s="5" t="n">
-        <v>0.3024</v>
-      </c>
+      <c r="F145" s="8" t="n"/>
     </row>
     <row r="146" ht="18" customHeight="1">
       <c r="A146" s="3" t="n"/>
       <c r="B146" s="3" t="n"/>
-      <c r="C146" s="6" t="inlineStr">
-        <is>
-          <t>小计</t>
-        </is>
-      </c>
+      <c r="C146" s="6" t="n"/>
       <c r="D146" s="7" t="inlineStr">
         <is>
           <t>m³</t>
@@ -3816,9 +3490,7 @@
           <t>1.1142 + 0.3024 = 1.4166 ≈ 1.42</t>
         </is>
       </c>
-      <c r="F146" s="8" t="n">
-        <v>1.42</v>
-      </c>
+      <c r="F146" s="8" t="n"/>
     </row>
     <row r="147" ht="18" customHeight="1">
       <c r="A147" s="3" t="n">
@@ -3845,7 +3517,7 @@
         </is>
       </c>
       <c r="F147" s="5" t="n">
-        <v>0.0022</v>
+        <v>2.37</v>
       </c>
     </row>
     <row r="148" ht="18" customHeight="1">
@@ -3866,9 +3538,7 @@
           <t>[(0.048×2.3)]×2 = 0.2208</t>
         </is>
       </c>
-      <c r="F148" s="5" t="n">
-        <v>0.2208</v>
-      </c>
+      <c r="F148" s="8" t="n"/>
     </row>
     <row r="149" ht="18" customHeight="1">
       <c r="A149" s="3" t="n"/>
@@ -3888,9 +3558,7 @@
           <t>[(0.048×2.9)]×4 = 0.5568</t>
         </is>
       </c>
-      <c r="F149" s="5" t="n">
-        <v>0.5568</v>
-      </c>
+      <c r="F149" s="8" t="n"/>
     </row>
     <row r="150" ht="18" customHeight="1">
       <c r="A150" s="3" t="n"/>
@@ -3910,9 +3578,7 @@
           <t>[(0.048×2.3)]×2 = 0.2208</t>
         </is>
       </c>
-      <c r="F150" s="5" t="n">
-        <v>0.2208</v>
-      </c>
+      <c r="F150" s="8" t="n"/>
     </row>
     <row r="151" ht="18" customHeight="1">
       <c r="A151" s="3" t="n"/>
@@ -3932,9 +3598,7 @@
           <t>[(0.048×2.9)]×2 = 0.2784</t>
         </is>
       </c>
-      <c r="F151" s="5" t="n">
-        <v>0.2784</v>
-      </c>
+      <c r="F151" s="8" t="n"/>
     </row>
     <row r="152" ht="18" customHeight="1">
       <c r="A152" s="3" t="n"/>
@@ -3954,9 +3618,7 @@
           <t>[(0.048×2.3)]×2 = 0.2208</t>
         </is>
       </c>
-      <c r="F152" s="5" t="n">
-        <v>0.2208</v>
-      </c>
+      <c r="F152" s="8" t="n"/>
     </row>
     <row r="153" ht="18" customHeight="1">
       <c r="A153" s="3" t="n"/>
@@ -3976,9 +3638,7 @@
           <t>[(0.048×2.9)]×2 = 0.2784</t>
         </is>
       </c>
-      <c r="F153" s="5" t="n">
-        <v>0.2784</v>
-      </c>
+      <c r="F153" s="8" t="n"/>
     </row>
     <row r="154" ht="18" customHeight="1">
       <c r="A154" s="3" t="n"/>
@@ -3998,9 +3658,7 @@
           <t>[(0.048×2.3)]×2 = 0.2208</t>
         </is>
       </c>
-      <c r="F154" s="5" t="n">
-        <v>0.2208</v>
-      </c>
+      <c r="F154" s="8" t="n"/>
     </row>
     <row r="155" ht="18" customHeight="1">
       <c r="A155" s="3" t="n"/>
@@ -4020,9 +3678,7 @@
           <t>[(0.048×2.9)]×2 = 0.2784</t>
         </is>
       </c>
-      <c r="F155" s="5" t="n">
-        <v>0.2784</v>
-      </c>
+      <c r="F155" s="8" t="n"/>
     </row>
     <row r="156" ht="18" customHeight="1">
       <c r="A156" s="3" t="n"/>
@@ -4042,18 +3698,12 @@
           <t>(0.048×2) = 0.096</t>
         </is>
       </c>
-      <c r="F156" s="5" t="n">
-        <v>0.096</v>
-      </c>
+      <c r="F156" s="8" t="n"/>
     </row>
     <row r="157" ht="18" customHeight="1">
       <c r="A157" s="3" t="n"/>
       <c r="B157" s="3" t="n"/>
-      <c r="C157" s="6" t="inlineStr">
-        <is>
-          <t>小计</t>
-        </is>
-      </c>
+      <c r="C157" s="6" t="n"/>
       <c r="D157" s="7" t="inlineStr">
         <is>
           <t>m³</t>
@@ -4064,9 +3714,7 @@
           <t>0.0022 + 0.2208 + 0.5568 + 0.2208 + 0.2784 + 0.2208 + 0.2784 + 0.2208 + 0.2784 + 0.096 = 2.3734 ≈ 2.37</t>
         </is>
       </c>
-      <c r="F157" s="8" t="n">
-        <v>2.37</v>
-      </c>
+      <c r="F157" s="8" t="n"/>
     </row>
     <row r="158" ht="18" customHeight="1">
       <c r="A158" s="3" t="n">
@@ -4093,17 +3741,13 @@
         </is>
       </c>
       <c r="F158" s="5" t="n">
-        <v>31.7629</v>
+        <v>31.76</v>
       </c>
     </row>
     <row r="159" ht="18" customHeight="1">
       <c r="A159" s="3" t="n"/>
       <c r="B159" s="3" t="n"/>
-      <c r="C159" s="6" t="inlineStr">
-        <is>
-          <t>小计</t>
-        </is>
-      </c>
+      <c r="C159" s="6" t="n"/>
       <c r="D159" s="7" t="inlineStr">
         <is>
           <t>㎡</t>
@@ -4114,9 +3758,7 @@
           <t>31.7629 ≈ 31.76</t>
         </is>
       </c>
-      <c r="F159" s="8" t="n">
-        <v>31.76</v>
-      </c>
+      <c r="F159" s="8" t="n"/>
     </row>
     <row r="160" ht="18" customHeight="1">
       <c r="A160" s="3" t="n">
@@ -4143,17 +3785,13 @@
         </is>
       </c>
       <c r="F160" s="5" t="n">
-        <v>7.641</v>
+        <v>7.64</v>
       </c>
     </row>
     <row r="161" ht="18" customHeight="1">
       <c r="A161" s="3" t="n"/>
       <c r="B161" s="3" t="n"/>
-      <c r="C161" s="6" t="inlineStr">
-        <is>
-          <t>小计</t>
-        </is>
-      </c>
+      <c r="C161" s="6" t="n"/>
       <c r="D161" s="7" t="inlineStr">
         <is>
           <t>㎡</t>
@@ -4164,9 +3802,7 @@
           <t>7.641 ≈ 7.64</t>
         </is>
       </c>
-      <c r="F161" s="8" t="n">
-        <v>7.64</v>
-      </c>
+      <c r="F161" s="8" t="n"/>
     </row>
     <row r="162" ht="18" customHeight="1">
       <c r="A162" s="3" t="n">
@@ -4193,7 +3829,7 @@
         </is>
       </c>
       <c r="F162" s="5" t="n">
-        <v>0.536</v>
+        <v>2.78</v>
       </c>
     </row>
     <row r="163" ht="18" customHeight="1">
@@ -4214,18 +3850,12 @@
           <t>(0.048×13.53) + (0.048×5.745) + (0.048×15.53) + (0.048×11.995) = 2.2464</t>
         </is>
       </c>
-      <c r="F163" s="5" t="n">
-        <v>2.2464</v>
-      </c>
+      <c r="F163" s="8" t="n"/>
     </row>
     <row r="164" ht="18" customHeight="1">
       <c r="A164" s="3" t="n"/>
       <c r="B164" s="3" t="n"/>
-      <c r="C164" s="6" t="inlineStr">
-        <is>
-          <t>小计</t>
-        </is>
-      </c>
+      <c r="C164" s="6" t="n"/>
       <c r="D164" s="7" t="inlineStr">
         <is>
           <t>m³</t>
@@ -4236,9 +3866,7 @@
           <t>0.536 + 2.2464 = 2.7824 ≈ 2.78</t>
         </is>
       </c>
-      <c r="F164" s="8" t="n">
-        <v>2.78</v>
-      </c>
+      <c r="F164" s="8" t="n"/>
     </row>
     <row r="165" ht="18" customHeight="1">
       <c r="A165" s="3" t="n">
@@ -4265,7 +3893,7 @@
         </is>
       </c>
       <c r="F165" s="9" t="n">
-        <v>290.472</v>
+        <v>0.709</v>
       </c>
     </row>
     <row r="166" ht="18" customHeight="1">
@@ -4286,9 +3914,7 @@
           <t>179.984 + 185.64 = 365.624</t>
         </is>
       </c>
-      <c r="F166" s="9" t="n">
-        <v>365.624</v>
-      </c>
+      <c r="F166" s="10" t="n"/>
     </row>
     <row r="167" ht="18" customHeight="1">
       <c r="A167" s="3" t="n"/>
@@ -4308,18 +3934,12 @@
           <t>25.586 + 26.82 = 52.406</t>
         </is>
       </c>
-      <c r="F167" s="9" t="n">
-        <v>52.406</v>
-      </c>
+      <c r="F167" s="10" t="n"/>
     </row>
     <row r="168" ht="18" customHeight="1">
       <c r="A168" s="3" t="n"/>
       <c r="B168" s="3" t="n"/>
-      <c r="C168" s="6" t="inlineStr">
-        <is>
-          <t>小计</t>
-        </is>
-      </c>
+      <c r="C168" s="6" t="n"/>
       <c r="D168" s="7" t="inlineStr">
         <is>
           <t>t</t>
@@ -4330,9 +3950,7 @@
           <t>(290.472 + 365.624 + 52.406) ÷ 1000 = 0.709</t>
         </is>
       </c>
-      <c r="F168" s="10" t="n">
-        <v>0.709</v>
-      </c>
+      <c r="F168" s="10" t="n"/>
     </row>
     <row r="169" ht="18" customHeight="1">
       <c r="A169" s="3" t="n">
@@ -4359,7 +3977,7 @@
         </is>
       </c>
       <c r="F169" s="9" t="n">
-        <v>34.047</v>
+        <v>0.492</v>
       </c>
     </row>
     <row r="170" ht="18" customHeight="1">
@@ -4380,9 +3998,7 @@
           <t>3.783 = 3.783</t>
         </is>
       </c>
-      <c r="F170" s="9" t="n">
-        <v>3.783</v>
-      </c>
+      <c r="F170" s="10" t="n"/>
     </row>
     <row r="171" ht="18" customHeight="1">
       <c r="A171" s="3" t="n"/>
@@ -4402,9 +4018,7 @@
           <t>44.523 = 44.523</t>
         </is>
       </c>
-      <c r="F171" s="9" t="n">
-        <v>44.523</v>
-      </c>
+      <c r="F171" s="10" t="n"/>
     </row>
     <row r="172" ht="18" customHeight="1">
       <c r="A172" s="3" t="n"/>
@@ -4424,9 +4038,7 @@
           <t>4.947 = 4.947</t>
         </is>
       </c>
-      <c r="F172" s="9" t="n">
-        <v>4.947</v>
-      </c>
+      <c r="F172" s="10" t="n"/>
     </row>
     <row r="173" ht="18" customHeight="1">
       <c r="A173" s="3" t="n"/>
@@ -4446,9 +4058,7 @@
           <t>12.96 + 19.584 + 12.96 + 19.584 = 65.088</t>
         </is>
       </c>
-      <c r="F173" s="9" t="n">
-        <v>65.08799999999999</v>
-      </c>
+      <c r="F173" s="10" t="n"/>
     </row>
     <row r="174" ht="18" customHeight="1">
       <c r="A174" s="3" t="n"/>
@@ -4468,9 +4078,7 @@
           <t>44.523 = 44.523</t>
         </is>
       </c>
-      <c r="F174" s="9" t="n">
-        <v>44.523</v>
-      </c>
+      <c r="F174" s="10" t="n"/>
     </row>
     <row r="175" ht="18" customHeight="1">
       <c r="A175" s="3" t="n"/>
@@ -4490,9 +4098,7 @@
           <t>4.947 = 4.947</t>
         </is>
       </c>
-      <c r="F175" s="9" t="n">
-        <v>4.947</v>
-      </c>
+      <c r="F175" s="10" t="n"/>
     </row>
     <row r="176" ht="18" customHeight="1">
       <c r="A176" s="3" t="n"/>
@@ -4512,9 +4118,7 @@
           <t>12.24 + 19.584 + 12.24 + 19.584 = 63.648</t>
         </is>
       </c>
-      <c r="F176" s="9" t="n">
-        <v>63.648</v>
-      </c>
+      <c r="F176" s="10" t="n"/>
     </row>
     <row r="177" ht="18" customHeight="1">
       <c r="A177" s="3" t="n"/>
@@ -4534,9 +4138,7 @@
           <t>44.523 = 44.523</t>
         </is>
       </c>
-      <c r="F177" s="9" t="n">
-        <v>44.523</v>
-      </c>
+      <c r="F177" s="10" t="n"/>
     </row>
     <row r="178" ht="18" customHeight="1">
       <c r="A178" s="3" t="n"/>
@@ -4556,9 +4158,7 @@
           <t>4.947 = 4.947</t>
         </is>
       </c>
-      <c r="F178" s="9" t="n">
-        <v>4.947</v>
-      </c>
+      <c r="F178" s="10" t="n"/>
     </row>
     <row r="179" ht="18" customHeight="1">
       <c r="A179" s="3" t="n"/>
@@ -4578,9 +4178,7 @@
           <t>24.48 + 39.168 = 63.648</t>
         </is>
       </c>
-      <c r="F179" s="9" t="n">
-        <v>63.648</v>
-      </c>
+      <c r="F179" s="10" t="n"/>
     </row>
     <row r="180" ht="18" customHeight="1">
       <c r="A180" s="3" t="n"/>
@@ -4600,9 +4198,7 @@
           <t>44.523 = 44.523</t>
         </is>
       </c>
-      <c r="F180" s="9" t="n">
-        <v>44.523</v>
-      </c>
+      <c r="F180" s="10" t="n"/>
     </row>
     <row r="181" ht="18" customHeight="1">
       <c r="A181" s="3" t="n"/>
@@ -4622,9 +4218,7 @@
           <t>4.947 = 4.947</t>
         </is>
       </c>
-      <c r="F181" s="9" t="n">
-        <v>4.947</v>
-      </c>
+      <c r="F181" s="10" t="n"/>
     </row>
     <row r="182" ht="18" customHeight="1">
       <c r="A182" s="3" t="n"/>
@@ -4644,18 +4238,12 @@
           <t>24.48 + 39.168 = 63.648</t>
         </is>
       </c>
-      <c r="F182" s="9" t="n">
-        <v>63.648</v>
-      </c>
+      <c r="F182" s="10" t="n"/>
     </row>
     <row r="183" ht="18" customHeight="1">
       <c r="A183" s="3" t="n"/>
       <c r="B183" s="3" t="n"/>
-      <c r="C183" s="6" t="inlineStr">
-        <is>
-          <t>小计</t>
-        </is>
-      </c>
+      <c r="C183" s="6" t="n"/>
       <c r="D183" s="7" t="inlineStr">
         <is>
           <t>t</t>
@@ -4666,9 +4254,7 @@
           <t>(34.047 + 3.783 + 44.523 + 4.947 + 65.088 + 44.523 + 4.947 + 63.648 + 44.523 + 4.947 + 63.648 + 44.523 + 4.947 + 63.648) ÷ 1000 = 0.492</t>
         </is>
       </c>
-      <c r="F183" s="10" t="n">
-        <v>0.492</v>
-      </c>
+      <c r="F183" s="10" t="n"/>
     </row>
     <row r="184" ht="18" customHeight="1">
       <c r="A184" s="3" t="n">
@@ -4695,7 +4281,7 @@
         </is>
       </c>
       <c r="F184" s="9" t="n">
-        <v>9.023999999999999</v>
+        <v>0.175</v>
       </c>
     </row>
     <row r="185" ht="18" customHeight="1">
@@ -4716,9 +4302,7 @@
           <t>6.768 = 6.768</t>
         </is>
       </c>
-      <c r="F185" s="9" t="n">
-        <v>6.768</v>
-      </c>
+      <c r="F185" s="10" t="n"/>
     </row>
     <row r="186" ht="18" customHeight="1">
       <c r="A186" s="3" t="n"/>
@@ -4738,9 +4322,7 @@
           <t>24.816 + 9.588 = 34.404</t>
         </is>
       </c>
-      <c r="F186" s="9" t="n">
-        <v>34.404</v>
-      </c>
+      <c r="F186" s="10" t="n"/>
     </row>
     <row r="187" ht="18" customHeight="1">
       <c r="A187" s="3" t="n"/>
@@ -4760,9 +4342,7 @@
           <t>9.588 = 9.588</t>
         </is>
       </c>
-      <c r="F187" s="9" t="n">
-        <v>9.587999999999999</v>
-      </c>
+      <c r="F187" s="10" t="n"/>
     </row>
     <row r="188" ht="18" customHeight="1">
       <c r="A188" s="3" t="n"/>
@@ -4782,9 +4362,7 @@
           <t>28.764 = 28.764</t>
         </is>
       </c>
-      <c r="F188" s="9" t="n">
-        <v>28.764</v>
-      </c>
+      <c r="F188" s="10" t="n"/>
     </row>
     <row r="189" ht="18" customHeight="1">
       <c r="A189" s="3" t="n"/>
@@ -4804,9 +4382,7 @@
           <t>9.588 = 9.588</t>
         </is>
       </c>
-      <c r="F189" s="9" t="n">
-        <v>9.587999999999999</v>
-      </c>
+      <c r="F189" s="10" t="n"/>
     </row>
     <row r="190" ht="18" customHeight="1">
       <c r="A190" s="3" t="n"/>
@@ -4826,9 +4402,7 @@
           <t>28.764 = 28.764</t>
         </is>
       </c>
-      <c r="F190" s="9" t="n">
-        <v>28.764</v>
-      </c>
+      <c r="F190" s="10" t="n"/>
     </row>
     <row r="191" ht="18" customHeight="1">
       <c r="A191" s="3" t="n"/>
@@ -4848,9 +4422,7 @@
           <t>9.588 = 9.588</t>
         </is>
       </c>
-      <c r="F191" s="9" t="n">
-        <v>9.587999999999999</v>
-      </c>
+      <c r="F191" s="10" t="n"/>
     </row>
     <row r="192" ht="18" customHeight="1">
       <c r="A192" s="3" t="n"/>
@@ -4870,9 +4442,7 @@
           <t>28.764 = 28.764</t>
         </is>
       </c>
-      <c r="F192" s="9" t="n">
-        <v>28.764</v>
-      </c>
+      <c r="F192" s="10" t="n"/>
     </row>
     <row r="193" ht="18" customHeight="1">
       <c r="A193" s="3" t="n"/>
@@ -4892,18 +4462,12 @@
           <t>9.588 = 9.588</t>
         </is>
       </c>
-      <c r="F193" s="9" t="n">
-        <v>9.587999999999999</v>
-      </c>
+      <c r="F193" s="10" t="n"/>
     </row>
     <row r="194" ht="18" customHeight="1">
       <c r="A194" s="3" t="n"/>
       <c r="B194" s="3" t="n"/>
-      <c r="C194" s="6" t="inlineStr">
-        <is>
-          <t>小计</t>
-        </is>
-      </c>
+      <c r="C194" s="6" t="n"/>
       <c r="D194" s="7" t="inlineStr">
         <is>
           <t>t</t>
@@ -4914,9 +4478,7 @@
           <t>(9.024 + 6.768 + 34.404 + 9.588 + 28.764 + 9.588 + 28.764 + 9.588 + 28.764 + 9.588) ÷ 1000 = 0.175</t>
         </is>
       </c>
-      <c r="F194" s="10" t="n">
-        <v>0.175</v>
-      </c>
+      <c r="F194" s="10" t="n"/>
     </row>
     <row r="195" ht="18" customHeight="1">
       <c r="A195" s="3" t="n">
@@ -4942,7 +4504,7 @@
           <t>计算书中无依据，需补充</t>
         </is>
       </c>
-      <c r="F195" s="9" t="inlineStr">
+      <c r="F195" s="10" t="inlineStr">
         <is>
           <t>需补充</t>
         </is>
@@ -4973,7 +4535,7 @@
         </is>
       </c>
       <c r="F196" s="9" t="n">
-        <v>111.692</v>
+        <v>0.345</v>
       </c>
     </row>
     <row r="197" ht="18" customHeight="1">
@@ -4994,9 +4556,7 @@
           <t>41.08 + 2.9 + 4.924 + 41.08 = 89.984</t>
         </is>
       </c>
-      <c r="F197" s="9" t="n">
-        <v>89.98399999999999</v>
-      </c>
+      <c r="F197" s="10" t="n"/>
     </row>
     <row r="198" ht="18" customHeight="1">
       <c r="A198" s="3" t="n"/>
@@ -5016,9 +4576,7 @@
           <t>82.16 = 82.16</t>
         </is>
       </c>
-      <c r="F198" s="9" t="n">
-        <v>82.16</v>
-      </c>
+      <c r="F198" s="10" t="n"/>
     </row>
     <row r="199" ht="18" customHeight="1">
       <c r="A199" s="3" t="n"/>
@@ -5038,18 +4596,12 @@
           <t>34.56 + 26.456 = 61.016</t>
         </is>
       </c>
-      <c r="F199" s="9" t="n">
-        <v>61.016</v>
-      </c>
+      <c r="F199" s="10" t="n"/>
     </row>
     <row r="200" ht="18" customHeight="1">
       <c r="A200" s="3" t="n"/>
       <c r="B200" s="3" t="n"/>
-      <c r="C200" s="6" t="inlineStr">
-        <is>
-          <t>小计</t>
-        </is>
-      </c>
+      <c r="C200" s="6" t="n"/>
       <c r="D200" s="7" t="inlineStr">
         <is>
           <t>t</t>
@@ -5060,9 +4612,7 @@
           <t>(111.692 + 89.984 + 82.16 + 61.016) ÷ 1000 = 0.345</t>
         </is>
       </c>
-      <c r="F200" s="10" t="n">
-        <v>0.345</v>
-      </c>
+      <c r="F200" s="10" t="n"/>
     </row>
     <row r="201" ht="18" customHeight="1">
       <c r="A201" s="3" t="n">
@@ -5089,7 +4639,7 @@
         </is>
       </c>
       <c r="F201" s="9" t="n">
-        <v>367.632</v>
+        <v>2.989</v>
       </c>
     </row>
     <row r="202" ht="18" customHeight="1">
@@ -5110,9 +4660,7 @@
           <t>21.18 + 27.48 = 48.66</t>
         </is>
       </c>
-      <c r="F202" s="9" t="n">
-        <v>48.66</v>
-      </c>
+      <c r="F202" s="10" t="n"/>
     </row>
     <row r="203" ht="18" customHeight="1">
       <c r="A203" s="3" t="n"/>
@@ -5132,9 +4680,7 @@
           <t>22.38 + 28.68 = 51.06</t>
         </is>
       </c>
-      <c r="F203" s="9" t="n">
-        <v>51.06</v>
-      </c>
+      <c r="F203" s="10" t="n"/>
     </row>
     <row r="204" ht="18" customHeight="1">
       <c r="A204" s="3" t="n"/>
@@ -5154,9 +4700,7 @@
           <t>518.4 = 518.4</t>
         </is>
       </c>
-      <c r="F204" s="9" t="n">
-        <v>518.4</v>
-      </c>
+      <c r="F204" s="10" t="n"/>
     </row>
     <row r="205" ht="18" customHeight="1">
       <c r="A205" s="3" t="n"/>
@@ -5176,9 +4720,7 @@
           <t>72 = 72</t>
         </is>
       </c>
-      <c r="F205" s="9" t="n">
-        <v>72</v>
-      </c>
+      <c r="F205" s="10" t="n"/>
     </row>
     <row r="206" ht="18" customHeight="1">
       <c r="A206" s="3" t="n"/>
@@ -5198,9 +4740,7 @@
           <t>72 = 72</t>
         </is>
       </c>
-      <c r="F206" s="9" t="n">
-        <v>72</v>
-      </c>
+      <c r="F206" s="10" t="n"/>
     </row>
     <row r="207" ht="18" customHeight="1">
       <c r="A207" s="3" t="n"/>
@@ -5220,9 +4760,7 @@
           <t>518.4 = 518.4</t>
         </is>
       </c>
-      <c r="F207" s="9" t="n">
-        <v>518.4</v>
-      </c>
+      <c r="F207" s="10" t="n"/>
     </row>
     <row r="208" ht="18" customHeight="1">
       <c r="A208" s="3" t="n"/>
@@ -5242,9 +4780,7 @@
           <t>72 = 72</t>
         </is>
       </c>
-      <c r="F208" s="9" t="n">
-        <v>72</v>
-      </c>
+      <c r="F208" s="10" t="n"/>
     </row>
     <row r="209" ht="18" customHeight="1">
       <c r="A209" s="3" t="n"/>
@@ -5264,9 +4800,7 @@
           <t>72 = 72</t>
         </is>
       </c>
-      <c r="F209" s="9" t="n">
-        <v>72</v>
-      </c>
+      <c r="F209" s="10" t="n"/>
     </row>
     <row r="210" ht="18" customHeight="1">
       <c r="A210" s="3" t="n"/>
@@ -5286,9 +4820,7 @@
           <t>518.4 = 518.4</t>
         </is>
       </c>
-      <c r="F210" s="9" t="n">
-        <v>518.4</v>
-      </c>
+      <c r="F210" s="10" t="n"/>
     </row>
     <row r="211" ht="18" customHeight="1">
       <c r="A211" s="3" t="n"/>
@@ -5308,9 +4840,7 @@
           <t>72 = 72</t>
         </is>
       </c>
-      <c r="F211" s="9" t="n">
-        <v>72</v>
-      </c>
+      <c r="F211" s="10" t="n"/>
     </row>
     <row r="212" ht="18" customHeight="1">
       <c r="A212" s="3" t="n"/>
@@ -5330,9 +4860,7 @@
           <t>72 = 72</t>
         </is>
       </c>
-      <c r="F212" s="9" t="n">
-        <v>72</v>
-      </c>
+      <c r="F212" s="10" t="n"/>
     </row>
     <row r="213" ht="18" customHeight="1">
       <c r="A213" s="3" t="n"/>
@@ -5352,9 +4880,7 @@
           <t>233.928 + 188.568 = 422.496</t>
         </is>
       </c>
-      <c r="F213" s="9" t="n">
-        <v>422.496</v>
-      </c>
+      <c r="F213" s="10" t="n"/>
     </row>
     <row r="214" ht="18" customHeight="1">
       <c r="A214" s="3" t="n"/>
@@ -5374,9 +4900,7 @@
           <t>18.42 + 10.476 + 14.64 + 12.996 = 56.532</t>
         </is>
       </c>
-      <c r="F214" s="9" t="n">
-        <v>56.532</v>
-      </c>
+      <c r="F214" s="10" t="n"/>
     </row>
     <row r="215" ht="18" customHeight="1">
       <c r="A215" s="3" t="n"/>
@@ -5396,18 +4920,12 @@
           <t>24.56 + 19.52 + 5.238 + 6.498 = 55.816</t>
         </is>
       </c>
-      <c r="F215" s="9" t="n">
-        <v>55.816</v>
-      </c>
+      <c r="F215" s="10" t="n"/>
     </row>
     <row r="216" ht="18" customHeight="1">
       <c r="A216" s="3" t="n"/>
       <c r="B216" s="3" t="n"/>
-      <c r="C216" s="6" t="inlineStr">
-        <is>
-          <t>小计</t>
-        </is>
-      </c>
+      <c r="C216" s="6" t="n"/>
       <c r="D216" s="7" t="inlineStr">
         <is>
           <t>t</t>
@@ -5418,9 +4936,7 @@
           <t>(367.632 + 48.66 + 51.06 + 518.4 + 72 + 72 + 518.4 + 72 + 72 + 518.4 + 72 + 72 + 422.496 + 56.532 + 55.816) ÷ 1000 = 2.989</t>
         </is>
       </c>
-      <c r="F216" s="10" t="n">
-        <v>2.989</v>
-      </c>
+      <c r="F216" s="10" t="n"/>
     </row>
     <row r="217" ht="18" customHeight="1">
       <c r="A217" s="3" t="n">
@@ -5447,7 +4963,7 @@
         </is>
       </c>
       <c r="F217" s="9" t="n">
-        <v>117.356</v>
+        <v>0.968</v>
       </c>
     </row>
     <row r="218" ht="18" customHeight="1">
@@ -5468,9 +4984,7 @@
           <t>179.824 + 71.136 = 250.96</t>
         </is>
       </c>
-      <c r="F218" s="9" t="n">
-        <v>250.96</v>
-      </c>
+      <c r="F218" s="10" t="n"/>
     </row>
     <row r="219" ht="18" customHeight="1">
       <c r="A219" s="3" t="n"/>
@@ -5490,9 +5004,7 @@
           <t>213.408 = 213.408</t>
         </is>
       </c>
-      <c r="F219" s="9" t="n">
-        <v>213.408</v>
-      </c>
+      <c r="F219" s="10" t="n"/>
     </row>
     <row r="220" ht="18" customHeight="1">
       <c r="A220" s="3" t="n"/>
@@ -5512,9 +5024,7 @@
           <t>213.408 = 213.408</t>
         </is>
       </c>
-      <c r="F220" s="9" t="n">
-        <v>213.408</v>
-      </c>
+      <c r="F220" s="10" t="n"/>
     </row>
     <row r="221" ht="18" customHeight="1">
       <c r="A221" s="3" t="n"/>
@@ -5534,18 +5044,12 @@
           <t>96.864 + 76.116 = 172.98</t>
         </is>
       </c>
-      <c r="F221" s="9" t="n">
-        <v>172.98</v>
-      </c>
+      <c r="F221" s="10" t="n"/>
     </row>
     <row r="222" ht="18" customHeight="1">
       <c r="A222" s="3" t="n"/>
       <c r="B222" s="3" t="n"/>
-      <c r="C222" s="6" t="inlineStr">
-        <is>
-          <t>小计</t>
-        </is>
-      </c>
+      <c r="C222" s="6" t="n"/>
       <c r="D222" s="7" t="inlineStr">
         <is>
           <t>t</t>
@@ -5556,9 +5060,7 @@
           <t>(117.356 + 250.96 + 213.408 + 213.408 + 172.98) ÷ 1000 = 0.968</t>
         </is>
       </c>
-      <c r="F222" s="10" t="n">
-        <v>0.968</v>
-      </c>
+      <c r="F222" s="10" t="n"/>
     </row>
     <row r="223" ht="18" customHeight="1">
       <c r="A223" s="3" t="n">
@@ -5585,7 +5087,7 @@
         </is>
       </c>
       <c r="F223" s="9" t="n">
-        <v>3.24</v>
+        <v>0.307</v>
       </c>
     </row>
     <row r="224" ht="18" customHeight="1">
@@ -5606,9 +5108,7 @@
           <t>2.16 = 2.16</t>
         </is>
       </c>
-      <c r="F224" s="9" t="n">
-        <v>2.16</v>
-      </c>
+      <c r="F224" s="10" t="n"/>
     </row>
     <row r="225" ht="18" customHeight="1">
       <c r="A225" s="3" t="n"/>
@@ -5628,9 +5128,7 @@
           <t>10.374 + 1.224 = 11.598</t>
         </is>
       </c>
-      <c r="F225" s="9" t="n">
-        <v>11.598</v>
-      </c>
+      <c r="F225" s="10" t="n"/>
     </row>
     <row r="226" ht="18" customHeight="1">
       <c r="A226" s="3" t="n"/>
@@ -5650,9 +5148,7 @@
           <t>3.584 = 3.584</t>
         </is>
       </c>
-      <c r="F226" s="9" t="n">
-        <v>3.584</v>
-      </c>
+      <c r="F226" s="10" t="n"/>
     </row>
     <row r="227" ht="18" customHeight="1">
       <c r="A227" s="3" t="n"/>
@@ -5672,9 +5168,7 @@
           <t>18.031 = 18.031</t>
         </is>
       </c>
-      <c r="F227" s="9" t="n">
-        <v>18.031</v>
-      </c>
+      <c r="F227" s="10" t="n"/>
     </row>
     <row r="228" ht="18" customHeight="1">
       <c r="A228" s="3" t="n"/>
@@ -5694,9 +5188,7 @@
           <t>3.584 = 3.584</t>
         </is>
       </c>
-      <c r="F228" s="9" t="n">
-        <v>3.584</v>
-      </c>
+      <c r="F228" s="10" t="n"/>
     </row>
     <row r="229" ht="18" customHeight="1">
       <c r="A229" s="3" t="n"/>
@@ -5716,9 +5208,7 @@
           <t>0.504 = 0.504</t>
         </is>
       </c>
-      <c r="F229" s="9" t="n">
-        <v>0.504</v>
-      </c>
+      <c r="F229" s="10" t="n"/>
     </row>
     <row r="230" ht="18" customHeight="1">
       <c r="A230" s="3" t="n"/>
@@ -5738,9 +5228,7 @@
           <t>4.788 = 4.788</t>
         </is>
       </c>
-      <c r="F230" s="9" t="n">
-        <v>4.788</v>
-      </c>
+      <c r="F230" s="10" t="n"/>
     </row>
     <row r="231" ht="18" customHeight="1">
       <c r="A231" s="3" t="n"/>
@@ -5760,9 +5248,7 @@
           <t>2.457 = 2.457</t>
         </is>
       </c>
-      <c r="F231" s="9" t="n">
-        <v>2.457</v>
-      </c>
+      <c r="F231" s="10" t="n"/>
     </row>
     <row r="232" ht="18" customHeight="1">
       <c r="A232" s="3" t="n"/>
@@ -5782,9 +5268,7 @@
           <t>2.142 = 2.142</t>
         </is>
       </c>
-      <c r="F232" s="9" t="n">
-        <v>2.142</v>
-      </c>
+      <c r="F232" s="10" t="n"/>
     </row>
     <row r="233" ht="18" customHeight="1">
       <c r="A233" s="3" t="n"/>
@@ -5804,9 +5288,7 @@
           <t>19.712 = 19.712</t>
         </is>
       </c>
-      <c r="F233" s="9" t="n">
-        <v>19.712</v>
-      </c>
+      <c r="F233" s="10" t="n"/>
     </row>
     <row r="234" ht="18" customHeight="1">
       <c r="A234" s="3" t="n"/>
@@ -5826,9 +5308,7 @@
           <t>2.394 = 2.394</t>
         </is>
       </c>
-      <c r="F234" s="9" t="n">
-        <v>2.394</v>
-      </c>
+      <c r="F234" s="10" t="n"/>
     </row>
     <row r="235" ht="18" customHeight="1">
       <c r="A235" s="3" t="n"/>
@@ -5848,9 +5328,7 @@
           <t>2.394 = 2.394</t>
         </is>
       </c>
-      <c r="F235" s="9" t="n">
-        <v>2.394</v>
-      </c>
+      <c r="F235" s="10" t="n"/>
     </row>
     <row r="236" ht="18" customHeight="1">
       <c r="A236" s="3" t="n"/>
@@ -5870,9 +5348,7 @@
           <t>2.394 = 2.394</t>
         </is>
       </c>
-      <c r="F236" s="9" t="n">
-        <v>2.394</v>
-      </c>
+      <c r="F236" s="10" t="n"/>
     </row>
     <row r="237" ht="18" customHeight="1">
       <c r="A237" s="3" t="n"/>
@@ -5892,9 +5368,7 @@
           <t>2.457 = 2.457</t>
         </is>
       </c>
-      <c r="F237" s="9" t="n">
-        <v>2.457</v>
-      </c>
+      <c r="F237" s="10" t="n"/>
     </row>
     <row r="238" ht="18" customHeight="1">
       <c r="A238" s="3" t="n"/>
@@ -5914,9 +5388,7 @@
           <t>2.394 = 2.394</t>
         </is>
       </c>
-      <c r="F238" s="9" t="n">
-        <v>2.394</v>
-      </c>
+      <c r="F238" s="10" t="n"/>
     </row>
     <row r="239" ht="18" customHeight="1">
       <c r="A239" s="3" t="n"/>
@@ -5936,9 +5408,7 @@
           <t>4.914 = 4.914</t>
         </is>
       </c>
-      <c r="F239" s="9" t="n">
-        <v>4.914</v>
-      </c>
+      <c r="F239" s="10" t="n"/>
     </row>
     <row r="240" ht="18" customHeight="1">
       <c r="A240" s="3" t="n"/>
@@ -5958,9 +5428,7 @@
           <t>18.688 = 18.688</t>
         </is>
       </c>
-      <c r="F240" s="9" t="n">
-        <v>18.688</v>
-      </c>
+      <c r="F240" s="10" t="n"/>
     </row>
     <row r="241" ht="18" customHeight="1">
       <c r="A241" s="3" t="n"/>
@@ -5980,9 +5448,7 @@
           <t>3.165 = 3.165</t>
         </is>
       </c>
-      <c r="F241" s="9" t="n">
-        <v>3.165</v>
-      </c>
+      <c r="F241" s="10" t="n"/>
     </row>
     <row r="242" ht="18" customHeight="1">
       <c r="A242" s="3" t="n"/>
@@ -6002,9 +5468,7 @@
           <t>19.712 = 19.712</t>
         </is>
       </c>
-      <c r="F242" s="9" t="n">
-        <v>19.712</v>
-      </c>
+      <c r="F242" s="10" t="n"/>
     </row>
     <row r="243" ht="18" customHeight="1">
       <c r="A243" s="3" t="n"/>
@@ -6024,9 +5488,7 @@
           <t>7.168 = 7.168</t>
         </is>
       </c>
-      <c r="F243" s="9" t="n">
-        <v>7.168</v>
-      </c>
+      <c r="F243" s="10" t="n"/>
     </row>
     <row r="244" ht="18" customHeight="1">
       <c r="A244" s="3" t="n"/>
@@ -6046,9 +5508,7 @@
           <t>2.11 = 2.11</t>
         </is>
       </c>
-      <c r="F244" s="9" t="n">
-        <v>2.11</v>
-      </c>
+      <c r="F244" s="10" t="n"/>
     </row>
     <row r="245" ht="18" customHeight="1">
       <c r="A245" s="3" t="n"/>
@@ -6068,9 +5528,7 @@
           <t>3.961 + 3.728 = 7.689</t>
         </is>
       </c>
-      <c r="F245" s="9" t="n">
-        <v>7.689</v>
-      </c>
+      <c r="F245" s="10" t="n"/>
     </row>
     <row r="246" ht="18" customHeight="1">
       <c r="A246" s="3" t="n"/>
@@ -6090,9 +5548,7 @@
           <t>2.394 = 2.394</t>
         </is>
       </c>
-      <c r="F246" s="9" t="n">
-        <v>2.394</v>
-      </c>
+      <c r="F246" s="10" t="n"/>
     </row>
     <row r="247" ht="18" customHeight="1">
       <c r="A247" s="3" t="n"/>
@@ -6112,9 +5568,7 @@
           <t>2.394 = 2.394</t>
         </is>
       </c>
-      <c r="F247" s="9" t="n">
-        <v>2.394</v>
-      </c>
+      <c r="F247" s="10" t="n"/>
     </row>
     <row r="248" ht="18" customHeight="1">
       <c r="A248" s="3" t="n"/>
@@ -6134,9 +5588,7 @@
           <t>2.394 = 2.394</t>
         </is>
       </c>
-      <c r="F248" s="9" t="n">
-        <v>2.394</v>
-      </c>
+      <c r="F248" s="10" t="n"/>
     </row>
     <row r="249" ht="18" customHeight="1">
       <c r="A249" s="3" t="n"/>
@@ -6156,9 +5608,7 @@
           <t>2.457 = 2.457</t>
         </is>
       </c>
-      <c r="F249" s="9" t="n">
-        <v>2.457</v>
-      </c>
+      <c r="F249" s="10" t="n"/>
     </row>
     <row r="250" ht="18" customHeight="1">
       <c r="A250" s="3" t="n"/>
@@ -6178,9 +5628,7 @@
           <t>2.394 = 2.394</t>
         </is>
       </c>
-      <c r="F250" s="9" t="n">
-        <v>2.394</v>
-      </c>
+      <c r="F250" s="10" t="n"/>
     </row>
     <row r="251" ht="18" customHeight="1">
       <c r="A251" s="3" t="n"/>
@@ -6200,9 +5648,7 @@
           <t>4.914 = 4.914</t>
         </is>
       </c>
-      <c r="F251" s="9" t="n">
-        <v>4.914</v>
-      </c>
+      <c r="F251" s="10" t="n"/>
     </row>
     <row r="252" ht="18" customHeight="1">
       <c r="A252" s="3" t="n"/>
@@ -6222,9 +5668,7 @@
           <t>18.688 = 18.688</t>
         </is>
       </c>
-      <c r="F252" s="9" t="n">
-        <v>18.688</v>
-      </c>
+      <c r="F252" s="10" t="n"/>
     </row>
     <row r="253" ht="18" customHeight="1">
       <c r="A253" s="3" t="n"/>
@@ -6244,9 +5688,7 @@
           <t>3.165 = 3.165</t>
         </is>
       </c>
-      <c r="F253" s="9" t="n">
-        <v>3.165</v>
-      </c>
+      <c r="F253" s="10" t="n"/>
     </row>
     <row r="254" ht="18" customHeight="1">
       <c r="A254" s="3" t="n"/>
@@ -6266,9 +5708,7 @@
           <t>19.712 = 19.712</t>
         </is>
       </c>
-      <c r="F254" s="9" t="n">
-        <v>19.712</v>
-      </c>
+      <c r="F254" s="10" t="n"/>
     </row>
     <row r="255" ht="18" customHeight="1">
       <c r="A255" s="3" t="n"/>
@@ -6288,9 +5728,7 @@
           <t>7.168 = 7.168</t>
         </is>
       </c>
-      <c r="F255" s="9" t="n">
-        <v>7.168</v>
-      </c>
+      <c r="F255" s="10" t="n"/>
     </row>
     <row r="256" ht="18" customHeight="1">
       <c r="A256" s="3" t="n"/>
@@ -6310,9 +5748,7 @@
           <t>2.11 = 2.11</t>
         </is>
       </c>
-      <c r="F256" s="9" t="n">
-        <v>2.11</v>
-      </c>
+      <c r="F256" s="10" t="n"/>
     </row>
     <row r="257" ht="18" customHeight="1">
       <c r="A257" s="3" t="n"/>
@@ -6332,9 +5768,7 @@
           <t>3.728 + 3.961 = 7.689</t>
         </is>
       </c>
-      <c r="F257" s="9" t="n">
-        <v>7.689</v>
-      </c>
+      <c r="F257" s="10" t="n"/>
     </row>
     <row r="258" ht="18" customHeight="1">
       <c r="A258" s="3" t="n"/>
@@ -6354,9 +5788,7 @@
           <t>2.394 + 2.394 = 4.788</t>
         </is>
       </c>
-      <c r="F258" s="9" t="n">
-        <v>4.788</v>
-      </c>
+      <c r="F258" s="10" t="n"/>
     </row>
     <row r="259" ht="18" customHeight="1">
       <c r="A259" s="3" t="n"/>
@@ -6376,9 +5808,7 @@
           <t>2.394 + 2.394 = 4.788</t>
         </is>
       </c>
-      <c r="F259" s="9" t="n">
-        <v>4.788</v>
-      </c>
+      <c r="F259" s="10" t="n"/>
     </row>
     <row r="260" ht="18" customHeight="1">
       <c r="A260" s="3" t="n"/>
@@ -6398,9 +5828,7 @@
           <t>2.457 = 2.457</t>
         </is>
       </c>
-      <c r="F260" s="9" t="n">
-        <v>2.457</v>
-      </c>
+      <c r="F260" s="10" t="n"/>
     </row>
     <row r="261" ht="18" customHeight="1">
       <c r="A261" s="3" t="n"/>
@@ -6420,9 +5848,7 @@
           <t>2.142 = 2.142</t>
         </is>
       </c>
-      <c r="F261" s="9" t="n">
-        <v>2.142</v>
-      </c>
+      <c r="F261" s="10" t="n"/>
     </row>
     <row r="262" ht="18" customHeight="1">
       <c r="A262" s="3" t="n"/>
@@ -6442,9 +5868,7 @@
           <t>18.688 = 18.688</t>
         </is>
       </c>
-      <c r="F262" s="9" t="n">
-        <v>18.688</v>
-      </c>
+      <c r="F262" s="10" t="n"/>
     </row>
     <row r="263" ht="18" customHeight="1">
       <c r="A263" s="3" t="n"/>
@@ -6464,9 +5888,7 @@
           <t>19.712 = 19.712</t>
         </is>
       </c>
-      <c r="F263" s="9" t="n">
-        <v>19.712</v>
-      </c>
+      <c r="F263" s="10" t="n"/>
     </row>
     <row r="264" ht="18" customHeight="1">
       <c r="A264" s="3" t="n"/>
@@ -6486,9 +5908,7 @@
           <t>3.961 = 3.961</t>
         </is>
       </c>
-      <c r="F264" s="9" t="n">
-        <v>3.961</v>
-      </c>
+      <c r="F264" s="10" t="n"/>
     </row>
     <row r="265" ht="18" customHeight="1">
       <c r="A265" s="3" t="n"/>
@@ -6508,9 +5928,7 @@
           <t>15.36 = 15.36</t>
         </is>
       </c>
-      <c r="F265" s="9" t="n">
-        <v>15.36</v>
-      </c>
+      <c r="F265" s="10" t="n"/>
     </row>
     <row r="266" ht="18" customHeight="1">
       <c r="A266" s="3" t="n"/>
@@ -6530,9 +5948,7 @@
           <t>4.608 = 4.608</t>
         </is>
       </c>
-      <c r="F266" s="9" t="n">
-        <v>4.608</v>
-      </c>
+      <c r="F266" s="10" t="n"/>
     </row>
     <row r="267" ht="18" customHeight="1">
       <c r="A267" s="3" t="n"/>
@@ -6552,9 +5968,7 @@
           <t>4.608 = 4.608</t>
         </is>
       </c>
-      <c r="F267" s="9" t="n">
-        <v>4.608</v>
-      </c>
+      <c r="F267" s="10" t="n"/>
     </row>
     <row r="268" ht="18" customHeight="1">
       <c r="A268" s="3" t="n"/>
@@ -6574,18 +5988,12 @@
           <t>3.495 = 3.495</t>
         </is>
       </c>
-      <c r="F268" s="9" t="n">
-        <v>3.495</v>
-      </c>
+      <c r="F268" s="10" t="n"/>
     </row>
     <row r="269" ht="46" customHeight="1">
       <c r="A269" s="3" t="n"/>
       <c r="B269" s="3" t="n"/>
-      <c r="C269" s="6" t="inlineStr">
-        <is>
-          <t>小计</t>
-        </is>
-      </c>
+      <c r="C269" s="6" t="n"/>
       <c r="D269" s="7" t="inlineStr">
         <is>
           <t>t</t>
@@ -6596,9 +6004,7 @@
           <t>(3.24 + 2.16 + 11.598 + 3.584 + 18.031 + 3.584 + 0.504 + 4.788 + 2.457 + 2.142 + 19.712 + 2.394 + 2.394 + 2.394 + 2.457 + 2.394 + 4.914 + 18.688 + 3.165 + 19.712 + 7.168 + 2.11 + 7.689 + 2.394 + 2.394 + 2.394 + 2.457 + 2.394 + 4.914 + 18.688 + 3.165 + 19.712 + 7.168 + 2.11 + 7.689 + 4.788 + 4.788 + 2.457 + 2.142 + 18.688 + 19.712 + 3.961 + 15.36 + 4.608 + 4.608 + 3.495) ÷ 1000 = 0.307</t>
         </is>
       </c>
-      <c r="F269" s="10" t="n">
-        <v>0.307</v>
-      </c>
+      <c r="F269" s="10" t="n"/>
     </row>
     <row r="270" ht="18" customHeight="1">
       <c r="A270" s="3" t="n">
@@ -6625,7 +6031,7 @@
         </is>
       </c>
       <c r="F270" s="9" t="n">
-        <v>51.34</v>
+        <v>1.428</v>
       </c>
     </row>
     <row r="271" ht="18" customHeight="1">
@@ -6646,9 +6052,7 @@
           <t>34.428 = 34.428</t>
         </is>
       </c>
-      <c r="F271" s="9" t="n">
-        <v>34.428</v>
-      </c>
+      <c r="F271" s="10" t="n"/>
     </row>
     <row r="272" ht="18" customHeight="1">
       <c r="A272" s="3" t="n"/>
@@ -6668,9 +6072,7 @@
           <t>19.328 = 19.328</t>
         </is>
       </c>
-      <c r="F272" s="9" t="n">
-        <v>19.328</v>
-      </c>
+      <c r="F272" s="10" t="n"/>
     </row>
     <row r="273" ht="18" customHeight="1">
       <c r="A273" s="3" t="n"/>
@@ -6690,9 +6092,7 @@
           <t>6.454 = 6.454</t>
         </is>
       </c>
-      <c r="F273" s="9" t="n">
-        <v>6.454</v>
-      </c>
+      <c r="F273" s="10" t="n"/>
     </row>
     <row r="274" ht="18" customHeight="1">
       <c r="A274" s="3" t="n"/>
@@ -6712,9 +6112,7 @@
           <t>12.908 + 85.84 = 98.748</t>
         </is>
       </c>
-      <c r="F274" s="9" t="n">
-        <v>98.748</v>
-      </c>
+      <c r="F274" s="10" t="n"/>
     </row>
     <row r="275" ht="18" customHeight="1">
       <c r="A275" s="3" t="n"/>
@@ -6734,9 +6132,7 @@
           <t>6.454 + 42.92 = 49.374</t>
         </is>
       </c>
-      <c r="F275" s="9" t="n">
-        <v>49.374</v>
-      </c>
+      <c r="F275" s="10" t="n"/>
     </row>
     <row r="276" ht="18" customHeight="1">
       <c r="A276" s="3" t="n"/>
@@ -6756,9 +6152,7 @@
           <t>19.362 + 25.042 = 44.404</t>
         </is>
       </c>
-      <c r="F276" s="9" t="n">
-        <v>44.404</v>
-      </c>
+      <c r="F276" s="10" t="n"/>
     </row>
     <row r="277" ht="18" customHeight="1">
       <c r="A277" s="3" t="n"/>
@@ -6778,9 +6172,7 @@
           <t>45.178 = 45.178</t>
         </is>
       </c>
-      <c r="F277" s="9" t="n">
-        <v>45.178</v>
-      </c>
+      <c r="F277" s="10" t="n"/>
     </row>
     <row r="278" ht="18" customHeight="1">
       <c r="A278" s="3" t="n"/>
@@ -6800,9 +6192,7 @@
           <t>33.653 = 33.653</t>
         </is>
       </c>
-      <c r="F278" s="9" t="n">
-        <v>33.653</v>
-      </c>
+      <c r="F278" s="10" t="n"/>
     </row>
     <row r="279" ht="18" customHeight="1">
       <c r="A279" s="3" t="n"/>
@@ -6822,9 +6212,7 @@
           <t>6.454 + 36.54 = 42.994</t>
         </is>
       </c>
-      <c r="F279" s="9" t="n">
-        <v>42.994</v>
-      </c>
+      <c r="F279" s="10" t="n"/>
     </row>
     <row r="280" ht="18" customHeight="1">
       <c r="A280" s="3" t="n"/>
@@ -6844,9 +6232,7 @@
           <t>6.454 + 49.88 = 56.334</t>
         </is>
       </c>
-      <c r="F280" s="9" t="n">
-        <v>56.334</v>
-      </c>
+      <c r="F280" s="10" t="n"/>
     </row>
     <row r="281" ht="18" customHeight="1">
       <c r="A281" s="3" t="n"/>
@@ -6866,9 +6252,7 @@
           <t>6.454 + 46.4 = 52.854</t>
         </is>
       </c>
-      <c r="F281" s="9" t="n">
-        <v>52.854</v>
-      </c>
+      <c r="F281" s="10" t="n"/>
     </row>
     <row r="282" ht="18" customHeight="1">
       <c r="A282" s="3" t="n"/>
@@ -6888,9 +6272,7 @@
           <t>6.454 + 49.88 = 56.334</t>
         </is>
       </c>
-      <c r="F282" s="9" t="n">
-        <v>56.334</v>
-      </c>
+      <c r="F282" s="10" t="n"/>
     </row>
     <row r="283" ht="18" customHeight="1">
       <c r="A283" s="3" t="n"/>
@@ -6910,9 +6292,7 @@
           <t>6.454 + 46.4 = 52.854</t>
         </is>
       </c>
-      <c r="F283" s="9" t="n">
-        <v>52.854</v>
-      </c>
+      <c r="F283" s="10" t="n"/>
     </row>
     <row r="284" ht="18" customHeight="1">
       <c r="A284" s="3" t="n"/>
@@ -6932,9 +6312,7 @@
           <t>19.362 + 25.042 = 44.404</t>
         </is>
       </c>
-      <c r="F284" s="9" t="n">
-        <v>44.404</v>
-      </c>
+      <c r="F284" s="10" t="n"/>
     </row>
     <row r="285" ht="18" customHeight="1">
       <c r="A285" s="3" t="n"/>
@@ -6954,9 +6332,7 @@
           <t>47.944 = 47.944</t>
         </is>
       </c>
-      <c r="F285" s="9" t="n">
-        <v>47.944</v>
-      </c>
+      <c r="F285" s="10" t="n"/>
     </row>
     <row r="286" ht="18" customHeight="1">
       <c r="A286" s="3" t="n"/>
@@ -6976,9 +6352,7 @@
           <t>6.454 + 36.54 = 42.994</t>
         </is>
       </c>
-      <c r="F286" s="9" t="n">
-        <v>42.994</v>
-      </c>
+      <c r="F286" s="10" t="n"/>
     </row>
     <row r="287" ht="18" customHeight="1">
       <c r="A287" s="3" t="n"/>
@@ -6998,9 +6372,7 @@
           <t>6.454 + 49.88 = 56.334</t>
         </is>
       </c>
-      <c r="F287" s="9" t="n">
-        <v>56.334</v>
-      </c>
+      <c r="F287" s="10" t="n"/>
     </row>
     <row r="288" ht="18" customHeight="1">
       <c r="A288" s="3" t="n"/>
@@ -7020,9 +6392,7 @@
           <t>6.454 + 46.4 = 52.854</t>
         </is>
       </c>
-      <c r="F288" s="9" t="n">
-        <v>52.854</v>
-      </c>
+      <c r="F288" s="10" t="n"/>
     </row>
     <row r="289" ht="18" customHeight="1">
       <c r="A289" s="3" t="n"/>
@@ -7042,9 +6412,7 @@
           <t>6.454 + 49.88 = 56.334</t>
         </is>
       </c>
-      <c r="F289" s="9" t="n">
-        <v>56.334</v>
-      </c>
+      <c r="F289" s="10" t="n"/>
     </row>
     <row r="290" ht="18" customHeight="1">
       <c r="A290" s="3" t="n"/>
@@ -7064,9 +6432,7 @@
           <t>6.454 + 46.4 = 52.854</t>
         </is>
       </c>
-      <c r="F290" s="9" t="n">
-        <v>52.854</v>
-      </c>
+      <c r="F290" s="10" t="n"/>
     </row>
     <row r="291" ht="18" customHeight="1">
       <c r="A291" s="3" t="n"/>
@@ -7086,9 +6452,7 @@
           <t>19.362 + 25.042 = 44.404</t>
         </is>
       </c>
-      <c r="F291" s="9" t="n">
-        <v>44.404</v>
-      </c>
+      <c r="F291" s="10" t="n"/>
     </row>
     <row r="292" ht="18" customHeight="1">
       <c r="A292" s="3" t="n"/>
@@ -7108,9 +6472,7 @@
           <t>47.944 = 47.944</t>
         </is>
       </c>
-      <c r="F292" s="9" t="n">
-        <v>47.944</v>
-      </c>
+      <c r="F292" s="10" t="n"/>
     </row>
     <row r="293" ht="18" customHeight="1">
       <c r="A293" s="3" t="n"/>
@@ -7130,9 +6492,7 @@
           <t>6.454 + 36.54 + 6.454 + 36.54 = 85.988</t>
         </is>
       </c>
-      <c r="F293" s="9" t="n">
-        <v>85.988</v>
-      </c>
+      <c r="F293" s="10" t="n"/>
     </row>
     <row r="294" ht="18" customHeight="1">
       <c r="A294" s="3" t="n"/>
@@ -7152,9 +6512,7 @@
           <t>6.454 + 46.4 + 6.454 + 46.4 = 105.708</t>
         </is>
       </c>
-      <c r="F294" s="9" t="n">
-        <v>105.708</v>
-      </c>
+      <c r="F294" s="10" t="n"/>
     </row>
     <row r="295" ht="18" customHeight="1">
       <c r="A295" s="3" t="n"/>
@@ -7174,9 +6532,7 @@
           <t>6.454 + 49.88 = 56.334</t>
         </is>
       </c>
-      <c r="F295" s="9" t="n">
-        <v>56.334</v>
-      </c>
+      <c r="F295" s="10" t="n"/>
     </row>
     <row r="296" ht="18" customHeight="1">
       <c r="A296" s="3" t="n"/>
@@ -7196,9 +6552,7 @@
           <t>19.362 + 25.042 = 44.404</t>
         </is>
       </c>
-      <c r="F296" s="9" t="n">
-        <v>44.404</v>
-      </c>
+      <c r="F296" s="10" t="n"/>
     </row>
     <row r="297" ht="18" customHeight="1">
       <c r="A297" s="3" t="n"/>
@@ -7218,18 +6572,12 @@
           <t>45.178 = 45.178</t>
         </is>
       </c>
-      <c r="F297" s="9" t="n">
-        <v>45.178</v>
-      </c>
+      <c r="F297" s="10" t="n"/>
     </row>
     <row r="298" ht="32" customHeight="1">
       <c r="A298" s="3" t="n"/>
       <c r="B298" s="3" t="n"/>
-      <c r="C298" s="6" t="inlineStr">
-        <is>
-          <t>小计</t>
-        </is>
-      </c>
+      <c r="C298" s="6" t="n"/>
       <c r="D298" s="7" t="inlineStr">
         <is>
           <t>t</t>
@@ -7240,9 +6588,7 @@
           <t>(51.34 + 34.428 + 19.328 + 6.454 + 98.748 + 49.374 + 44.404 + 45.178 + 33.653 + 42.994 + 56.334 + 52.854 + 56.334 + 52.854 + 44.404 + 47.944 + 42.994 + 56.334 + 52.854 + 56.334 + 52.854 + 44.404 + 47.944 + 85.988 + 105.708 + 56.334 + 44.404 + 45.178) ÷ 1000 = 1.428</t>
         </is>
       </c>
-      <c r="F298" s="10" t="n">
-        <v>1.428</v>
-      </c>
+      <c r="F298" s="10" t="n"/>
     </row>
     <row r="299" ht="18" customHeight="1">
       <c r="A299" s="3" t="n">
@@ -7269,7 +6615,7 @@
         </is>
       </c>
       <c r="F299" s="9" t="n">
-        <v>31.48</v>
+        <v>0.717</v>
       </c>
     </row>
     <row r="300" ht="18" customHeight="1">
@@ -7290,9 +6636,7 @@
           <t>21.294 = 21.294</t>
         </is>
       </c>
-      <c r="F300" s="9" t="n">
-        <v>21.294</v>
-      </c>
+      <c r="F300" s="10" t="n"/>
     </row>
     <row r="301" ht="18" customHeight="1">
       <c r="A301" s="3" t="n"/>
@@ -7312,9 +6656,7 @@
           <t>11.606 = 11.606</t>
         </is>
       </c>
-      <c r="F301" s="9" t="n">
-        <v>11.606</v>
-      </c>
+      <c r="F301" s="10" t="n"/>
     </row>
     <row r="302" ht="18" customHeight="1">
       <c r="A302" s="3" t="n"/>
@@ -7334,9 +6676,7 @@
           <t>24.304 + 24.082 = 48.386</t>
         </is>
       </c>
-      <c r="F302" s="9" t="n">
-        <v>48.386</v>
-      </c>
+      <c r="F302" s="10" t="n"/>
     </row>
     <row r="303" ht="18" customHeight="1">
       <c r="A303" s="3" t="n"/>
@@ -7356,9 +6696,7 @@
           <t>48.164 = 48.164</t>
         </is>
       </c>
-      <c r="F303" s="9" t="n">
-        <v>48.164</v>
-      </c>
+      <c r="F303" s="10" t="n"/>
     </row>
     <row r="304" ht="18" customHeight="1">
       <c r="A304" s="3" t="n"/>
@@ -7378,9 +6716,7 @@
           <t>24.082 = 24.082</t>
         </is>
       </c>
-      <c r="F304" s="9" t="n">
-        <v>24.082</v>
-      </c>
+      <c r="F304" s="10" t="n"/>
     </row>
     <row r="305" ht="18" customHeight="1">
       <c r="A305" s="3" t="n"/>
@@ -7400,9 +6736,7 @@
           <t>23.212 = 23.212</t>
         </is>
       </c>
-      <c r="F305" s="9" t="n">
-        <v>23.212</v>
-      </c>
+      <c r="F305" s="10" t="n"/>
     </row>
     <row r="306" ht="18" customHeight="1">
       <c r="A306" s="3" t="n"/>
@@ -7422,9 +6756,7 @@
           <t>24.082 = 24.082</t>
         </is>
       </c>
-      <c r="F306" s="9" t="n">
-        <v>24.082</v>
-      </c>
+      <c r="F306" s="10" t="n"/>
     </row>
     <row r="307" ht="18" customHeight="1">
       <c r="A307" s="3" t="n"/>
@@ -7444,9 +6776,7 @@
           <t>24.082 = 24.082</t>
         </is>
       </c>
-      <c r="F307" s="9" t="n">
-        <v>24.082</v>
-      </c>
+      <c r="F307" s="10" t="n"/>
     </row>
     <row r="308" ht="18" customHeight="1">
       <c r="A308" s="3" t="n"/>
@@ -7466,9 +6796,7 @@
           <t>24.082 = 24.082</t>
         </is>
       </c>
-      <c r="F308" s="9" t="n">
-        <v>24.082</v>
-      </c>
+      <c r="F308" s="10" t="n"/>
     </row>
     <row r="309" ht="18" customHeight="1">
       <c r="A309" s="3" t="n"/>
@@ -7488,9 +6816,7 @@
           <t>24.082 + 2.718 = 26.8</t>
         </is>
       </c>
-      <c r="F309" s="9" t="n">
-        <v>26.8</v>
-      </c>
+      <c r="F309" s="10" t="n"/>
     </row>
     <row r="310" ht="18" customHeight="1">
       <c r="A310" s="3" t="n"/>
@@ -7510,9 +6836,7 @@
           <t>24.082 = 24.082</t>
         </is>
       </c>
-      <c r="F310" s="9" t="n">
-        <v>24.082</v>
-      </c>
+      <c r="F310" s="10" t="n"/>
     </row>
     <row r="311" ht="18" customHeight="1">
       <c r="A311" s="3" t="n"/>
@@ -7532,9 +6856,7 @@
           <t>55.376 = 55.376</t>
         </is>
       </c>
-      <c r="F311" s="9" t="n">
-        <v>55.376</v>
-      </c>
+      <c r="F311" s="10" t="n"/>
     </row>
     <row r="312" ht="18" customHeight="1">
       <c r="A312" s="3" t="n"/>
@@ -7554,9 +6876,7 @@
           <t>24.082 = 24.082</t>
         </is>
       </c>
-      <c r="F312" s="9" t="n">
-        <v>24.082</v>
-      </c>
+      <c r="F312" s="10" t="n"/>
     </row>
     <row r="313" ht="18" customHeight="1">
       <c r="A313" s="3" t="n"/>
@@ -7576,9 +6896,7 @@
           <t>24.082 = 24.082</t>
         </is>
       </c>
-      <c r="F313" s="9" t="n">
-        <v>24.082</v>
-      </c>
+      <c r="F313" s="10" t="n"/>
     </row>
     <row r="314" ht="18" customHeight="1">
       <c r="A314" s="3" t="n"/>
@@ -7598,9 +6916,7 @@
           <t>24.082 = 24.082</t>
         </is>
       </c>
-      <c r="F314" s="9" t="n">
-        <v>24.082</v>
-      </c>
+      <c r="F314" s="10" t="n"/>
     </row>
     <row r="315" ht="18" customHeight="1">
       <c r="A315" s="3" t="n"/>
@@ -7620,9 +6936,7 @@
           <t>24.082 + 2.718 = 26.8</t>
         </is>
       </c>
-      <c r="F315" s="9" t="n">
-        <v>26.8</v>
-      </c>
+      <c r="F315" s="10" t="n"/>
     </row>
     <row r="316" ht="18" customHeight="1">
       <c r="A316" s="3" t="n"/>
@@ -7642,9 +6956,7 @@
           <t>24.082 = 24.082</t>
         </is>
       </c>
-      <c r="F316" s="9" t="n">
-        <v>24.082</v>
-      </c>
+      <c r="F316" s="10" t="n"/>
     </row>
     <row r="317" ht="18" customHeight="1">
       <c r="A317" s="3" t="n"/>
@@ -7664,9 +6976,7 @@
           <t>55.376 = 55.376</t>
         </is>
       </c>
-      <c r="F317" s="9" t="n">
-        <v>55.376</v>
-      </c>
+      <c r="F317" s="10" t="n"/>
     </row>
     <row r="318" ht="18" customHeight="1">
       <c r="A318" s="3" t="n"/>
@@ -7686,9 +6996,7 @@
           <t>24.082 + 2.718 + 24.082 = 50.882</t>
         </is>
       </c>
-      <c r="F318" s="9" t="n">
-        <v>50.882</v>
-      </c>
+      <c r="F318" s="10" t="n"/>
     </row>
     <row r="319" ht="18" customHeight="1">
       <c r="A319" s="3" t="n"/>
@@ -7708,9 +7016,7 @@
           <t>24.082 + 2.718 + 24.082 = 50.882</t>
         </is>
       </c>
-      <c r="F319" s="9" t="n">
-        <v>50.882</v>
-      </c>
+      <c r="F319" s="10" t="n"/>
     </row>
     <row r="320" ht="18" customHeight="1">
       <c r="A320" s="3" t="n"/>
@@ -7730,9 +7036,7 @@
           <t>24.082 + 2.718 = 26.8</t>
         </is>
       </c>
-      <c r="F320" s="9" t="n">
-        <v>26.8</v>
-      </c>
+      <c r="F320" s="10" t="n"/>
     </row>
     <row r="321" ht="18" customHeight="1">
       <c r="A321" s="3" t="n"/>
@@ -7752,18 +7056,12 @@
           <t>23.212 = 23.212</t>
         </is>
       </c>
-      <c r="F321" s="9" t="n">
-        <v>23.212</v>
-      </c>
+      <c r="F321" s="10" t="n"/>
     </row>
     <row r="322" ht="32" customHeight="1">
       <c r="A322" s="3" t="n"/>
       <c r="B322" s="3" t="n"/>
-      <c r="C322" s="6" t="inlineStr">
-        <is>
-          <t>小计</t>
-        </is>
-      </c>
+      <c r="C322" s="6" t="n"/>
       <c r="D322" s="7" t="inlineStr">
         <is>
           <t>t</t>
@@ -7774,9 +7072,7 @@
           <t>(31.48 + 21.294 + 11.606 + 48.386 + 48.164 + 24.082 + 23.212 + 24.082 + 24.082 + 24.082 + 26.8 + 24.082 + 55.376 + 24.082 + 24.082 + 24.082 + 26.8 + 24.082 + 55.376 + 50.882 + 50.882 + 26.8 + 23.212) ÷ 1000 = 0.717</t>
         </is>
       </c>
-      <c r="F322" s="10" t="n">
-        <v>0.717</v>
-      </c>
+      <c r="F322" s="10" t="n"/>
     </row>
     <row r="323" ht="18" customHeight="1">
       <c r="A323" s="3" t="n">
@@ -7803,7 +7099,7 @@
         </is>
       </c>
       <c r="F323" s="9" t="n">
-        <v>8.619999999999999</v>
+        <v>0.134</v>
       </c>
     </row>
     <row r="324" ht="18" customHeight="1">
@@ -7824,9 +7120,7 @@
           <t>12.13 = 12.13</t>
         </is>
       </c>
-      <c r="F324" s="9" t="n">
-        <v>12.13</v>
-      </c>
+      <c r="F324" s="10" t="n"/>
     </row>
     <row r="325" ht="18" customHeight="1">
       <c r="A325" s="3" t="n"/>
@@ -7846,9 +7140,7 @@
           <t>6.322 + 7.755 = 14.077</t>
         </is>
       </c>
-      <c r="F325" s="9" t="n">
-        <v>14.077</v>
-      </c>
+      <c r="F325" s="10" t="n"/>
     </row>
     <row r="326" ht="18" customHeight="1">
       <c r="A326" s="3" t="n"/>
@@ -7868,9 +7160,7 @@
           <t>9.588 + 9.104 = 18.692</t>
         </is>
       </c>
-      <c r="F326" s="9" t="n">
-        <v>18.692</v>
-      </c>
+      <c r="F326" s="10" t="n"/>
     </row>
     <row r="327" ht="18" customHeight="1">
       <c r="A327" s="3" t="n"/>
@@ -7890,9 +7180,7 @@
           <t>8.62 = 8.62</t>
         </is>
       </c>
-      <c r="F327" s="9" t="n">
-        <v>8.619999999999999</v>
-      </c>
+      <c r="F327" s="10" t="n"/>
     </row>
     <row r="328" ht="18" customHeight="1">
       <c r="A328" s="3" t="n"/>
@@ -7912,9 +7200,7 @@
           <t>12.13 = 12.13</t>
         </is>
       </c>
-      <c r="F328" s="9" t="n">
-        <v>12.13</v>
-      </c>
+      <c r="F328" s="10" t="n"/>
     </row>
     <row r="329" ht="18" customHeight="1">
       <c r="A329" s="3" t="n"/>
@@ -7934,9 +7220,7 @@
           <t>6.322 + 7.755 = 14.077</t>
         </is>
       </c>
-      <c r="F329" s="9" t="n">
-        <v>14.077</v>
-      </c>
+      <c r="F329" s="10" t="n"/>
     </row>
     <row r="330" ht="18" customHeight="1">
       <c r="A330" s="3" t="n"/>
@@ -7956,9 +7240,7 @@
           <t>9.104 + 9.588 = 18.692</t>
         </is>
       </c>
-      <c r="F330" s="9" t="n">
-        <v>18.692</v>
-      </c>
+      <c r="F330" s="10" t="n"/>
     </row>
     <row r="331" ht="18" customHeight="1">
       <c r="A331" s="3" t="n"/>
@@ -7978,9 +7260,7 @@
           <t>9.588 = 9.588</t>
         </is>
       </c>
-      <c r="F331" s="9" t="n">
-        <v>9.587999999999999</v>
-      </c>
+      <c r="F331" s="10" t="n"/>
     </row>
     <row r="332" ht="18" customHeight="1">
       <c r="A332" s="3" t="n"/>
@@ -8000,18 +7280,12 @@
           <t>8.757 + 8.241 = 16.998</t>
         </is>
       </c>
-      <c r="F332" s="9" t="n">
-        <v>16.998</v>
-      </c>
+      <c r="F332" s="10" t="n"/>
     </row>
     <row r="333" ht="18" customHeight="1">
       <c r="A333" s="3" t="n"/>
       <c r="B333" s="3" t="n"/>
-      <c r="C333" s="6" t="inlineStr">
-        <is>
-          <t>小计</t>
-        </is>
-      </c>
+      <c r="C333" s="6" t="n"/>
       <c r="D333" s="7" t="inlineStr">
         <is>
           <t>t</t>
@@ -8022,9 +7296,7 @@
           <t>(8.62 + 12.13 + 14.077 + 18.692 + 8.62 + 12.13 + 14.077 + 18.692 + 9.588 + 16.998) ÷ 1000 = 0.134</t>
         </is>
       </c>
-      <c r="F333" s="10" t="n">
-        <v>0.134</v>
-      </c>
+      <c r="F333" s="10" t="n"/>
     </row>
     <row r="334" ht="18" customHeight="1">
       <c r="A334" s="3" t="n">
@@ -8051,7 +7323,7 @@
         </is>
       </c>
       <c r="F334" s="9" t="n">
-        <v>90.342</v>
+        <v>2.347</v>
       </c>
     </row>
     <row r="335" ht="18" customHeight="1">
@@ -8072,9 +7344,7 @@
           <t>38.658 = 38.658</t>
         </is>
       </c>
-      <c r="F335" s="9" t="n">
-        <v>38.658</v>
-      </c>
+      <c r="F335" s="10" t="n"/>
     </row>
     <row r="336" ht="18" customHeight="1">
       <c r="A336" s="3" t="n"/>
@@ -8094,9 +7364,7 @@
           <t>152.658 = 152.658</t>
         </is>
       </c>
-      <c r="F336" s="9" t="n">
-        <v>152.658</v>
-      </c>
+      <c r="F336" s="10" t="n"/>
     </row>
     <row r="337" ht="18" customHeight="1">
       <c r="A337" s="3" t="n"/>
@@ -8116,9 +7384,7 @@
           <t>12.728 + 16.395 = 29.123</t>
         </is>
       </c>
-      <c r="F337" s="9" t="n">
-        <v>29.123</v>
-      </c>
+      <c r="F337" s="10" t="n"/>
     </row>
     <row r="338" ht="18" customHeight="1">
       <c r="A338" s="3" t="n"/>
@@ -8138,9 +7404,7 @@
           <t>24.222 + 24.321 + 8.428 = 56.971</t>
         </is>
       </c>
-      <c r="F338" s="9" t="n">
-        <v>56.971</v>
-      </c>
+      <c r="F338" s="10" t="n"/>
     </row>
     <row r="339" ht="18" customHeight="1">
       <c r="A339" s="3" t="n"/>
@@ -8160,9 +7424,7 @@
           <t>76.377 = 76.377</t>
         </is>
       </c>
-      <c r="F339" s="9" t="n">
-        <v>76.377</v>
-      </c>
+      <c r="F339" s="10" t="n"/>
     </row>
     <row r="340" ht="18" customHeight="1">
       <c r="A340" s="3" t="n"/>
@@ -8182,9 +7444,7 @@
           <t>152.754 = 152.754</t>
         </is>
       </c>
-      <c r="F340" s="9" t="n">
-        <v>152.754</v>
-      </c>
+      <c r="F340" s="10" t="n"/>
     </row>
     <row r="341" ht="18" customHeight="1">
       <c r="A341" s="3" t="n"/>
@@ -8204,9 +7464,7 @@
           <t>76.377 + 74.106 = 150.483</t>
         </is>
       </c>
-      <c r="F341" s="9" t="n">
-        <v>150.483</v>
-      </c>
+      <c r="F341" s="10" t="n"/>
     </row>
     <row r="342" ht="18" customHeight="1">
       <c r="A342" s="3" t="n"/>
@@ -8226,9 +7484,7 @@
           <t>7.534 = 7.534</t>
         </is>
       </c>
-      <c r="F342" s="9" t="n">
-        <v>7.534</v>
-      </c>
+      <c r="F342" s="10" t="n"/>
     </row>
     <row r="343" ht="18" customHeight="1">
       <c r="A343" s="3" t="n"/>
@@ -8248,9 +7504,7 @@
           <t>15.068 = 15.068</t>
         </is>
       </c>
-      <c r="F343" s="9" t="n">
-        <v>15.068</v>
-      </c>
+      <c r="F343" s="10" t="n"/>
     </row>
     <row r="344" ht="18" customHeight="1">
       <c r="A344" s="3" t="n"/>
@@ -8270,9 +7524,7 @@
           <t>7.534 = 7.534</t>
         </is>
       </c>
-      <c r="F344" s="9" t="n">
-        <v>7.534</v>
-      </c>
+      <c r="F344" s="10" t="n"/>
     </row>
     <row r="345" ht="18" customHeight="1">
       <c r="A345" s="3" t="n"/>
@@ -8292,9 +7544,7 @@
           <t>15.068 = 15.068</t>
         </is>
       </c>
-      <c r="F345" s="9" t="n">
-        <v>15.068</v>
-      </c>
+      <c r="F345" s="10" t="n"/>
     </row>
     <row r="346" ht="18" customHeight="1">
       <c r="A346" s="3" t="n"/>
@@ -8314,9 +7564,7 @@
           <t>7.534 = 7.534</t>
         </is>
       </c>
-      <c r="F346" s="9" t="n">
-        <v>7.534</v>
-      </c>
+      <c r="F346" s="10" t="n"/>
     </row>
     <row r="347" ht="18" customHeight="1">
       <c r="A347" s="3" t="n"/>
@@ -8336,9 +7584,7 @@
           <t>24.222 + 24.321 + 8.428 = 56.971</t>
         </is>
       </c>
-      <c r="F347" s="9" t="n">
-        <v>56.971</v>
-      </c>
+      <c r="F347" s="10" t="n"/>
     </row>
     <row r="348" ht="18" customHeight="1">
       <c r="A348" s="3" t="n"/>
@@ -8358,9 +7604,7 @@
           <t>24.201 + 18.276 + 19.125 + 6.194 = 67.796</t>
         </is>
       </c>
-      <c r="F348" s="9" t="n">
-        <v>67.79600000000001</v>
-      </c>
+      <c r="F348" s="10" t="n"/>
     </row>
     <row r="349" ht="18" customHeight="1">
       <c r="A349" s="3" t="n"/>
@@ -8380,9 +7624,7 @@
           <t>152.754 = 152.754</t>
         </is>
       </c>
-      <c r="F349" s="9" t="n">
-        <v>152.754</v>
-      </c>
+      <c r="F349" s="10" t="n"/>
     </row>
     <row r="350" ht="18" customHeight="1">
       <c r="A350" s="3" t="n"/>
@@ -8402,9 +7644,7 @@
           <t>76.377 + 74.106 = 150.483</t>
         </is>
       </c>
-      <c r="F350" s="9" t="n">
-        <v>150.483</v>
-      </c>
+      <c r="F350" s="10" t="n"/>
     </row>
     <row r="351" ht="18" customHeight="1">
       <c r="A351" s="3" t="n"/>
@@ -8424,9 +7664,7 @@
           <t>6.194 = 6.194</t>
         </is>
       </c>
-      <c r="F351" s="9" t="n">
-        <v>6.194</v>
-      </c>
+      <c r="F351" s="10" t="n"/>
     </row>
     <row r="352" ht="18" customHeight="1">
       <c r="A352" s="3" t="n"/>
@@ -8446,9 +7684,7 @@
           <t>7.534 = 7.534</t>
         </is>
       </c>
-      <c r="F352" s="9" t="n">
-        <v>7.534</v>
-      </c>
+      <c r="F352" s="10" t="n"/>
     </row>
     <row r="353" ht="18" customHeight="1">
       <c r="A353" s="3" t="n"/>
@@ -8468,9 +7704,7 @@
           <t>15.068 = 15.068</t>
         </is>
       </c>
-      <c r="F353" s="9" t="n">
-        <v>15.068</v>
-      </c>
+      <c r="F353" s="10" t="n"/>
     </row>
     <row r="354" ht="18" customHeight="1">
       <c r="A354" s="3" t="n"/>
@@ -8490,9 +7724,7 @@
           <t>7.534 = 7.534</t>
         </is>
       </c>
-      <c r="F354" s="9" t="n">
-        <v>7.534</v>
-      </c>
+      <c r="F354" s="10" t="n"/>
     </row>
     <row r="355" ht="18" customHeight="1">
       <c r="A355" s="3" t="n"/>
@@ -8512,9 +7744,7 @@
           <t>15.068 = 15.068</t>
         </is>
       </c>
-      <c r="F355" s="9" t="n">
-        <v>15.068</v>
-      </c>
+      <c r="F355" s="10" t="n"/>
     </row>
     <row r="356" ht="18" customHeight="1">
       <c r="A356" s="3" t="n"/>
@@ -8534,9 +7764,7 @@
           <t>7.534 = 7.534</t>
         </is>
       </c>
-      <c r="F356" s="9" t="n">
-        <v>7.534</v>
-      </c>
+      <c r="F356" s="10" t="n"/>
     </row>
     <row r="357" ht="18" customHeight="1">
       <c r="A357" s="3" t="n"/>
@@ -8556,9 +7784,7 @@
           <t>24.222 + 24.321 + 8.428 = 56.971</t>
         </is>
       </c>
-      <c r="F357" s="9" t="n">
-        <v>56.971</v>
-      </c>
+      <c r="F357" s="10" t="n"/>
     </row>
     <row r="358" ht="18" customHeight="1">
       <c r="A358" s="3" t="n"/>
@@ -8578,9 +7804,7 @@
           <t>24.201 + 18.276 + 19.125 + 6.194 = 67.796</t>
         </is>
       </c>
-      <c r="F358" s="9" t="n">
-        <v>67.79600000000001</v>
-      </c>
+      <c r="F358" s="10" t="n"/>
     </row>
     <row r="359" ht="18" customHeight="1">
       <c r="A359" s="3" t="n"/>
@@ -8600,9 +7824,7 @@
           <t>152.754 = 152.754</t>
         </is>
       </c>
-      <c r="F359" s="9" t="n">
-        <v>152.754</v>
-      </c>
+      <c r="F359" s="10" t="n"/>
     </row>
     <row r="360" ht="18" customHeight="1">
       <c r="A360" s="3" t="n"/>
@@ -8622,9 +7844,7 @@
           <t>76.377 + 74.106 = 150.483</t>
         </is>
       </c>
-      <c r="F360" s="9" t="n">
-        <v>150.483</v>
-      </c>
+      <c r="F360" s="10" t="n"/>
     </row>
     <row r="361" ht="18" customHeight="1">
       <c r="A361" s="3" t="n"/>
@@ -8644,9 +7864,7 @@
           <t>6.194 = 6.194</t>
         </is>
       </c>
-      <c r="F361" s="9" t="n">
-        <v>6.194</v>
-      </c>
+      <c r="F361" s="10" t="n"/>
     </row>
     <row r="362" ht="18" customHeight="1">
       <c r="A362" s="3" t="n"/>
@@ -8666,9 +7884,7 @@
           <t>7.534 + 7.534 = 15.068</t>
         </is>
       </c>
-      <c r="F362" s="9" t="n">
-        <v>15.068</v>
-      </c>
+      <c r="F362" s="10" t="n"/>
     </row>
     <row r="363" ht="18" customHeight="1">
       <c r="A363" s="3" t="n"/>
@@ -8688,9 +7904,7 @@
           <t>7.534 + 7.534 = 15.068</t>
         </is>
       </c>
-      <c r="F363" s="9" t="n">
-        <v>15.068</v>
-      </c>
+      <c r="F363" s="10" t="n"/>
     </row>
     <row r="364" ht="18" customHeight="1">
       <c r="A364" s="3" t="n"/>
@@ -8710,9 +7924,7 @@
           <t>15.068 = 15.068</t>
         </is>
       </c>
-      <c r="F364" s="9" t="n">
-        <v>15.068</v>
-      </c>
+      <c r="F364" s="10" t="n"/>
     </row>
     <row r="365" ht="18" customHeight="1">
       <c r="A365" s="3" t="n"/>
@@ -8732,9 +7944,7 @@
           <t>24.222 + 24.321 + 8.428 = 56.971</t>
         </is>
       </c>
-      <c r="F365" s="9" t="n">
-        <v>56.971</v>
-      </c>
+      <c r="F365" s="10" t="n"/>
     </row>
     <row r="366" ht="18" customHeight="1">
       <c r="A366" s="3" t="n"/>
@@ -8754,9 +7964,7 @@
           <t>76.377 = 76.377</t>
         </is>
       </c>
-      <c r="F366" s="9" t="n">
-        <v>76.377</v>
-      </c>
+      <c r="F366" s="10" t="n"/>
     </row>
     <row r="367" ht="18" customHeight="1">
       <c r="A367" s="3" t="n"/>
@@ -8776,9 +7984,7 @@
           <t>77.655 + 76.377 = 154.032</t>
         </is>
       </c>
-      <c r="F367" s="9" t="n">
-        <v>154.032</v>
-      </c>
+      <c r="F367" s="10" t="n"/>
     </row>
     <row r="368" ht="18" customHeight="1">
       <c r="A368" s="3" t="n"/>
@@ -8798,9 +8004,7 @@
           <t>50.918 + 49.404 = 100.322</t>
         </is>
       </c>
-      <c r="F368" s="9" t="n">
-        <v>100.322</v>
-      </c>
+      <c r="F368" s="10" t="n"/>
     </row>
     <row r="369" ht="18" customHeight="1">
       <c r="A369" s="3" t="n"/>
@@ -8820,9 +8024,7 @@
           <t>16.752 = 16.752</t>
         </is>
       </c>
-      <c r="F369" s="9" t="n">
-        <v>16.752</v>
-      </c>
+      <c r="F369" s="10" t="n"/>
     </row>
     <row r="370" ht="18" customHeight="1">
       <c r="A370" s="3" t="n"/>
@@ -8842,9 +8044,7 @@
           <t>60.261 + 57.99 = 118.251</t>
         </is>
       </c>
-      <c r="F370" s="9" t="n">
-        <v>118.251</v>
-      </c>
+      <c r="F370" s="10" t="n"/>
     </row>
     <row r="371" ht="18" customHeight="1">
       <c r="A371" s="3" t="n"/>
@@ -8864,9 +8064,7 @@
           <t>11.892 + 17.073 = 28.965</t>
         </is>
       </c>
-      <c r="F371" s="9" t="n">
-        <v>28.965</v>
-      </c>
+      <c r="F371" s="10" t="n"/>
     </row>
     <row r="372" ht="18" customHeight="1">
       <c r="A372" s="3" t="n"/>
@@ -8886,18 +8084,12 @@
           <t>11.892 + 17.073 = 28.965</t>
         </is>
       </c>
-      <c r="F372" s="9" t="n">
-        <v>28.965</v>
-      </c>
+      <c r="F372" s="10" t="n"/>
     </row>
     <row r="373" ht="46" customHeight="1">
       <c r="A373" s="3" t="n"/>
       <c r="B373" s="3" t="n"/>
-      <c r="C373" s="6" t="inlineStr">
-        <is>
-          <t>小计</t>
-        </is>
-      </c>
+      <c r="C373" s="6" t="n"/>
       <c r="D373" s="7" t="inlineStr">
         <is>
           <t>t</t>
@@ -8908,9 +8100,7 @@
           <t>(90.342 + 38.658 + 152.658 + 29.123 + 56.971 + 76.377 + 152.754 + 150.483 + 7.534 + 15.068 + 7.534 + 15.068 + 7.534 + 56.971 + 67.796 + 152.754 + 150.483 + 6.194 + 7.534 + 15.068 + 7.534 + 15.068 + 7.534 + 56.971 + 67.796 + 152.754 + 150.483 + 6.194 + 15.068 + 15.068 + 15.068 + 56.971 + 76.377 + 154.032 + 100.322 + 16.752 + 118.251 + 28.965 + 28.965) ÷ 1000 = 2.347</t>
         </is>
       </c>
-      <c r="F373" s="10" t="n">
-        <v>2.347</v>
-      </c>
+      <c r="F373" s="10" t="n"/>
     </row>
     <row r="374" ht="18" customHeight="1">
       <c r="A374" s="3" t="n">
@@ -8937,7 +8127,7 @@
         </is>
       </c>
       <c r="F374" s="9" t="n">
-        <v>327.572</v>
+        <v>2.172</v>
       </c>
     </row>
     <row r="375" ht="18" customHeight="1">
@@ -8958,9 +8148,7 @@
           <t>19.44 + 151.98 = 171.42</t>
         </is>
       </c>
-      <c r="F375" s="9" t="n">
-        <v>171.42</v>
-      </c>
+      <c r="F375" s="10" t="n"/>
     </row>
     <row r="376" ht="18" customHeight="1">
       <c r="A376" s="3" t="n"/>
@@ -8980,9 +8168,7 @@
           <t>41.262 = 41.262</t>
         </is>
       </c>
-      <c r="F376" s="9" t="n">
-        <v>41.262</v>
-      </c>
+      <c r="F376" s="10" t="n"/>
     </row>
     <row r="377" ht="18" customHeight="1">
       <c r="A377" s="3" t="n"/>
@@ -9002,9 +8188,7 @@
           <t>64.66 + 3.866 + 12.4 + 4.7 + 3.166 = 88.792</t>
         </is>
       </c>
-      <c r="F377" s="9" t="n">
-        <v>88.792</v>
-      </c>
+      <c r="F377" s="10" t="n"/>
     </row>
     <row r="378" ht="18" customHeight="1">
       <c r="A378" s="3" t="n"/>
@@ -9024,9 +8208,7 @@
           <t>55.944 + 7.658 + 13.94 + 16.6 + 4.816 + 39.612 = 138.57</t>
         </is>
       </c>
-      <c r="F378" s="9" t="n">
-        <v>138.57</v>
-      </c>
+      <c r="F378" s="10" t="n"/>
     </row>
     <row r="379" ht="18" customHeight="1">
       <c r="A379" s="3" t="n"/>
@@ -9046,9 +8228,7 @@
           <t>41.262 = 41.262</t>
         </is>
       </c>
-      <c r="F379" s="9" t="n">
-        <v>41.262</v>
-      </c>
+      <c r="F379" s="10" t="n"/>
     </row>
     <row r="380" ht="18" customHeight="1">
       <c r="A380" s="3" t="n"/>
@@ -9068,9 +8248,7 @@
           <t>41.262 = 41.262</t>
         </is>
       </c>
-      <c r="F380" s="9" t="n">
-        <v>41.262</v>
-      </c>
+      <c r="F380" s="10" t="n"/>
     </row>
     <row r="381" ht="18" customHeight="1">
       <c r="A381" s="3" t="n"/>
@@ -9090,9 +8268,7 @@
           <t>55.944 + 7.658 + 13.94 + 8.3 + 12.8 + 41.412 + 4.816 + 39.612 = 184.482</t>
         </is>
       </c>
-      <c r="F381" s="9" t="n">
-        <v>184.482</v>
-      </c>
+      <c r="F381" s="10" t="n"/>
     </row>
     <row r="382" ht="18" customHeight="1">
       <c r="A382" s="3" t="n"/>
@@ -9112,9 +8288,7 @@
           <t>21.492 + 20.292 = 41.784</t>
         </is>
       </c>
-      <c r="F382" s="9" t="n">
-        <v>41.784</v>
-      </c>
+      <c r="F382" s="10" t="n"/>
     </row>
     <row r="383" ht="18" customHeight="1">
       <c r="A383" s="3" t="n"/>
@@ -9134,9 +8308,7 @@
           <t>55.944 + 7.658 + 13.94 + 16.6 + 4.816 + 39.612 = 138.57</t>
         </is>
       </c>
-      <c r="F383" s="9" t="n">
-        <v>138.57</v>
-      </c>
+      <c r="F383" s="10" t="n"/>
     </row>
     <row r="384" ht="18" customHeight="1">
       <c r="A384" s="3" t="n"/>
@@ -9156,9 +8328,7 @@
           <t>41.262 = 41.262</t>
         </is>
       </c>
-      <c r="F384" s="9" t="n">
-        <v>41.262</v>
-      </c>
+      <c r="F384" s="10" t="n"/>
     </row>
     <row r="385" ht="18" customHeight="1">
       <c r="A385" s="3" t="n"/>
@@ -9178,9 +8348,7 @@
           <t>41.262 = 41.262</t>
         </is>
       </c>
-      <c r="F385" s="9" t="n">
-        <v>41.262</v>
-      </c>
+      <c r="F385" s="10" t="n"/>
     </row>
     <row r="386" ht="18" customHeight="1">
       <c r="A386" s="3" t="n"/>
@@ -9200,9 +8368,7 @@
           <t>55.944 + 7.658 + 13.94 + 8.3 + 12.8 + 41.412 + 4.816 + 39.612 = 184.482</t>
         </is>
       </c>
-      <c r="F386" s="9" t="n">
-        <v>184.482</v>
-      </c>
+      <c r="F386" s="10" t="n"/>
     </row>
     <row r="387" ht="18" customHeight="1">
       <c r="A387" s="3" t="n"/>
@@ -9222,9 +8388,7 @@
           <t>20.292 + 21.492 = 41.784</t>
         </is>
       </c>
-      <c r="F387" s="9" t="n">
-        <v>41.784</v>
-      </c>
+      <c r="F387" s="10" t="n"/>
     </row>
     <row r="388" ht="18" customHeight="1">
       <c r="A388" s="3" t="n"/>
@@ -9244,9 +8408,7 @@
           <t>56.964 + 15.136 + 16.6 + 75.99 + 56.964 + 15.136 + 9.72 + 16.6 + 75.99 = 339.1</t>
         </is>
       </c>
-      <c r="F388" s="9" t="n">
-        <v>339.1</v>
-      </c>
+      <c r="F388" s="10" t="n"/>
     </row>
     <row r="389" ht="18" customHeight="1">
       <c r="A389" s="3" t="n"/>
@@ -9266,9 +8428,7 @@
           <t>75.99 + 9.72 + 75.99 = 161.7</t>
         </is>
       </c>
-      <c r="F389" s="9" t="n">
-        <v>161.7</v>
-      </c>
+      <c r="F389" s="10" t="n"/>
     </row>
     <row r="390" ht="18" customHeight="1">
       <c r="A390" s="3" t="n"/>
@@ -9288,9 +8448,7 @@
           <t>75.99 = 75.99</t>
         </is>
       </c>
-      <c r="F390" s="9" t="n">
-        <v>75.98999999999999</v>
-      </c>
+      <c r="F390" s="10" t="n"/>
     </row>
     <row r="391" ht="18" customHeight="1">
       <c r="A391" s="3" t="n"/>
@@ -9310,18 +8468,12 @@
           <t>65.5 + 6.2 = 71.7</t>
         </is>
       </c>
-      <c r="F391" s="9" t="n">
-        <v>71.7</v>
-      </c>
+      <c r="F391" s="10" t="n"/>
     </row>
     <row r="392" ht="32" customHeight="1">
       <c r="A392" s="3" t="n"/>
       <c r="B392" s="3" t="n"/>
-      <c r="C392" s="6" t="inlineStr">
-        <is>
-          <t>小计</t>
-        </is>
-      </c>
+      <c r="C392" s="6" t="n"/>
       <c r="D392" s="7" t="inlineStr">
         <is>
           <t>t</t>
@@ -9332,9 +8484,7 @@
           <t>(327.572 + 171.42 + 41.262 + 88.792 + 138.57 + 41.262 + 41.262 + 184.482 + 41.784 + 138.57 + 41.262 + 41.262 + 184.482 + 41.784 + 339.1 + 161.7 + 75.99 + 71.7) ÷ 1000 = 2.172</t>
         </is>
       </c>
-      <c r="F392" s="10" t="n">
-        <v>2.172</v>
-      </c>
+      <c r="F392" s="10" t="n"/>
     </row>
     <row r="393" ht="18" customHeight="1">
       <c r="A393" s="3" t="n">
@@ -9361,7 +8511,7 @@
         </is>
       </c>
       <c r="F393" s="9" t="n">
-        <v>286.602</v>
+        <v>2.778</v>
       </c>
     </row>
     <row r="394" ht="18" customHeight="1">
@@ -9382,9 +8532,7 @@
           <t>188.316 = 188.316</t>
         </is>
       </c>
-      <c r="F394" s="9" t="n">
-        <v>188.316</v>
-      </c>
+      <c r="F394" s="10" t="n"/>
     </row>
     <row r="395" ht="18" customHeight="1">
       <c r="A395" s="3" t="n"/>
@@ -9404,9 +8552,7 @@
           <t>54.93 + 54.702 = 109.632</t>
         </is>
       </c>
-      <c r="F395" s="9" t="n">
-        <v>109.632</v>
-      </c>
+      <c r="F395" s="10" t="n"/>
     </row>
     <row r="396" ht="18" customHeight="1">
       <c r="A396" s="3" t="n"/>
@@ -9426,9 +8572,7 @@
           <t>5.692 + 109.776 + 20.668 = 136.136</t>
         </is>
       </c>
-      <c r="F396" s="9" t="n">
-        <v>136.136</v>
-      </c>
+      <c r="F396" s="10" t="n"/>
     </row>
     <row r="397" ht="18" customHeight="1">
       <c r="A397" s="3" t="n"/>
@@ -9448,9 +8592,7 @@
           <t>69.318 + 18.476 + 10.581 + 16.362 + 5.99 + 49.41 = 170.137</t>
         </is>
       </c>
-      <c r="F397" s="9" t="n">
-        <v>170.137</v>
-      </c>
+      <c r="F397" s="10" t="n"/>
     </row>
     <row r="398" ht="18" customHeight="1">
       <c r="A398" s="3" t="n"/>
@@ -9470,9 +8612,7 @@
           <t>80.112 + 22.31 + 6.523 = 108.945</t>
         </is>
       </c>
-      <c r="F398" s="9" t="n">
-        <v>108.945</v>
-      </c>
+      <c r="F398" s="10" t="n"/>
     </row>
     <row r="399" ht="18" customHeight="1">
       <c r="A399" s="3" t="n"/>
@@ -9492,9 +8632,7 @@
           <t>2.846 + 54.888 + 10.334 + 15.996 + 5.99 + 49.41 = 139.464</t>
         </is>
       </c>
-      <c r="F399" s="9" t="n">
-        <v>139.464</v>
-      </c>
+      <c r="F399" s="10" t="n"/>
     </row>
     <row r="400" ht="18" customHeight="1">
       <c r="A400" s="3" t="n"/>
@@ -9514,9 +8652,7 @@
           <t>2.846 + 54.888 + 10.334 + 15.996 + 5.99 + 49.41 = 139.464</t>
         </is>
       </c>
-      <c r="F400" s="9" t="n">
-        <v>139.464</v>
-      </c>
+      <c r="F400" s="10" t="n"/>
     </row>
     <row r="401" ht="18" customHeight="1">
       <c r="A401" s="3" t="n"/>
@@ -9536,9 +8672,7 @@
           <t>69.318 + 18.15 + 10.581 + 16.362 + 5.99 + 49.41 = 169.811</t>
         </is>
       </c>
-      <c r="F401" s="9" t="n">
-        <v>169.811</v>
-      </c>
+      <c r="F401" s="10" t="n"/>
     </row>
     <row r="402" ht="18" customHeight="1">
       <c r="A402" s="3" t="n"/>
@@ -9558,9 +8692,7 @@
           <t>80.112 + 22.31 + 6.523 = 108.945</t>
         </is>
       </c>
-      <c r="F402" s="9" t="n">
-        <v>108.945</v>
-      </c>
+      <c r="F402" s="10" t="n"/>
     </row>
     <row r="403" ht="18" customHeight="1">
       <c r="A403" s="3" t="n"/>
@@ -9580,9 +8712,7 @@
           <t>80.112 + 4.836 + 15.314 + 39.036 = 139.298</t>
         </is>
       </c>
-      <c r="F403" s="9" t="n">
-        <v>139.298</v>
-      </c>
+      <c r="F403" s="10" t="n"/>
     </row>
     <row r="404" ht="18" customHeight="1">
       <c r="A404" s="3" t="n"/>
@@ -9602,9 +8732,7 @@
           <t>26.055 = 26.055</t>
         </is>
       </c>
-      <c r="F404" s="9" t="n">
-        <v>26.055</v>
-      </c>
+      <c r="F404" s="10" t="n"/>
     </row>
     <row r="405" ht="18" customHeight="1">
       <c r="A405" s="3" t="n"/>
@@ -9624,9 +8752,7 @@
           <t>2.846 + 54.888 + 10.334 + 15.996 + 5.99 + 49.41 = 139.464</t>
         </is>
       </c>
-      <c r="F405" s="9" t="n">
-        <v>139.464</v>
-      </c>
+      <c r="F405" s="10" t="n"/>
     </row>
     <row r="406" ht="18" customHeight="1">
       <c r="A406" s="3" t="n"/>
@@ -9646,9 +8772,7 @@
           <t>2.846 + 54.888 + 10.334 + 15.996 + 5.99 + 49.41 = 139.464</t>
         </is>
       </c>
-      <c r="F406" s="9" t="n">
-        <v>139.464</v>
-      </c>
+      <c r="F406" s="10" t="n"/>
     </row>
     <row r="407" ht="18" customHeight="1">
       <c r="A407" s="3" t="n"/>
@@ -9668,9 +8792,7 @@
           <t>69.318 + 18.15 + 10.581 + 16.362 + 5.99 + 49.41 = 169.811</t>
         </is>
       </c>
-      <c r="F407" s="9" t="n">
-        <v>169.811</v>
-      </c>
+      <c r="F407" s="10" t="n"/>
     </row>
     <row r="408" ht="18" customHeight="1">
       <c r="A408" s="3" t="n"/>
@@ -9690,9 +8812,7 @@
           <t>80.112 + 22.31 + 6.523 = 108.945</t>
         </is>
       </c>
-      <c r="F408" s="9" t="n">
-        <v>108.945</v>
-      </c>
+      <c r="F408" s="10" t="n"/>
     </row>
     <row r="409" ht="18" customHeight="1">
       <c r="A409" s="3" t="n"/>
@@ -9712,9 +8832,7 @@
           <t>80.112 + 4.836 + 15.314 + 39.036 = 139.298</t>
         </is>
       </c>
-      <c r="F409" s="9" t="n">
-        <v>139.298</v>
-      </c>
+      <c r="F409" s="10" t="n"/>
     </row>
     <row r="410" ht="18" customHeight="1">
       <c r="A410" s="3" t="n"/>
@@ -9734,9 +8852,7 @@
           <t>26.055 = 26.055</t>
         </is>
       </c>
-      <c r="F410" s="9" t="n">
-        <v>26.055</v>
-      </c>
+      <c r="F410" s="10" t="n"/>
     </row>
     <row r="411" ht="18" customHeight="1">
       <c r="A411" s="3" t="n"/>
@@ -9756,9 +8872,7 @@
           <t>56 + 10.334 + 56 + 10.334 = 132.668</t>
         </is>
       </c>
-      <c r="F411" s="9" t="n">
-        <v>132.668</v>
-      </c>
+      <c r="F411" s="10" t="n"/>
     </row>
     <row r="412" ht="18" customHeight="1">
       <c r="A412" s="3" t="n"/>
@@ -9778,9 +8892,7 @@
           <t>70.43 + 9.075 + 10.581 + 16.362 = 106.448</t>
         </is>
       </c>
-      <c r="F412" s="9" t="n">
-        <v>106.448</v>
-      </c>
+      <c r="F412" s="10" t="n"/>
     </row>
     <row r="413" ht="18" customHeight="1">
       <c r="A413" s="3" t="n"/>
@@ -9800,18 +8912,12 @@
           <t>82.088 + 11.155 = 93.243</t>
         </is>
       </c>
-      <c r="F413" s="9" t="n">
-        <v>93.24299999999999</v>
-      </c>
+      <c r="F413" s="10" t="n"/>
     </row>
     <row r="414" ht="32" customHeight="1">
       <c r="A414" s="3" t="n"/>
       <c r="B414" s="3" t="n"/>
-      <c r="C414" s="6" t="inlineStr">
-        <is>
-          <t>小计</t>
-        </is>
-      </c>
+      <c r="C414" s="6" t="n"/>
       <c r="D414" s="7" t="inlineStr">
         <is>
           <t>t</t>
@@ -9822,9 +8928,7 @@
           <t>(286.602 + 188.316 + 109.632 + 136.136 + 170.137 + 108.945 + 139.464 + 139.464 + 169.811 + 108.945 + 139.298 + 26.055 + 139.464 + 139.464 + 169.811 + 108.945 + 139.298 + 26.055 + 132.668 + 106.448 + 93.243) ÷ 1000 = 2.778</t>
         </is>
       </c>
-      <c r="F414" s="10" t="n">
-        <v>2.778</v>
-      </c>
+      <c r="F414" s="10" t="n"/>
     </row>
     <row r="415" ht="18" customHeight="1">
       <c r="A415" s="3" t="n">
@@ -9851,7 +8955,7 @@
         </is>
       </c>
       <c r="F415" s="9" t="n">
-        <v>63.339</v>
+        <v>0.319</v>
       </c>
     </row>
     <row r="416" ht="18" customHeight="1">
@@ -9872,9 +8976,7 @@
           <t>63.117 = 63.117</t>
         </is>
       </c>
-      <c r="F416" s="9" t="n">
-        <v>63.117</v>
-      </c>
+      <c r="F416" s="10" t="n"/>
     </row>
     <row r="417" ht="18" customHeight="1">
       <c r="A417" s="3" t="n"/>
@@ -9894,9 +8996,7 @@
           <t>63.339 = 63.339</t>
         </is>
       </c>
-      <c r="F417" s="9" t="n">
-        <v>63.339</v>
-      </c>
+      <c r="F417" s="10" t="n"/>
     </row>
     <row r="418" ht="18" customHeight="1">
       <c r="A418" s="3" t="n"/>
@@ -9916,9 +9016,7 @@
           <t>63.117 = 63.117</t>
         </is>
       </c>
-      <c r="F418" s="9" t="n">
-        <v>63.117</v>
-      </c>
+      <c r="F418" s="10" t="n"/>
     </row>
     <row r="419" ht="18" customHeight="1">
       <c r="A419" s="3" t="n"/>
@@ -9938,18 +9036,12 @@
           <t>66.54 = 66.54</t>
         </is>
       </c>
-      <c r="F419" s="9" t="n">
-        <v>66.54000000000001</v>
-      </c>
+      <c r="F419" s="10" t="n"/>
     </row>
     <row r="420" ht="18" customHeight="1">
       <c r="A420" s="3" t="n"/>
       <c r="B420" s="3" t="n"/>
-      <c r="C420" s="6" t="inlineStr">
-        <is>
-          <t>小计</t>
-        </is>
-      </c>
+      <c r="C420" s="6" t="n"/>
       <c r="D420" s="7" t="inlineStr">
         <is>
           <t>t</t>
@@ -9960,9 +9052,7 @@
           <t>(63.339 + 63.117 + 63.339 + 63.117 + 66.54) ÷ 1000 = 0.319</t>
         </is>
       </c>
-      <c r="F420" s="10" t="n">
-        <v>0.319</v>
-      </c>
+      <c r="F420" s="10" t="n"/>
     </row>
     <row r="421" ht="18" customHeight="1">
       <c r="A421" s="3" t="n">
@@ -9989,7 +9079,7 @@
         </is>
       </c>
       <c r="F421" s="9" t="n">
-        <v>3.08</v>
+        <v>1.029</v>
       </c>
     </row>
     <row r="422" ht="18" customHeight="1">
@@ -10010,9 +9100,7 @@
           <t>59.908 + 81.864 + 6.16 = 147.932</t>
         </is>
       </c>
-      <c r="F422" s="9" t="n">
-        <v>147.932</v>
-      </c>
+      <c r="F422" s="10" t="n"/>
     </row>
     <row r="423" ht="18" customHeight="1">
       <c r="A423" s="3" t="n"/>
@@ -10032,9 +9120,7 @@
           <t>3.08 = 3.08</t>
         </is>
       </c>
-      <c r="F423" s="9" t="n">
-        <v>3.08</v>
-      </c>
+      <c r="F423" s="10" t="n"/>
     </row>
     <row r="424" ht="18" customHeight="1">
       <c r="A424" s="3" t="n"/>
@@ -10054,9 +9140,7 @@
           <t>86.868 = 86.868</t>
         </is>
       </c>
-      <c r="F424" s="9" t="n">
-        <v>86.86799999999999</v>
-      </c>
+      <c r="F424" s="10" t="n"/>
     </row>
     <row r="425" ht="18" customHeight="1">
       <c r="A425" s="3" t="n"/>
@@ -10076,9 +9160,7 @@
           <t>3.08 = 3.08</t>
         </is>
       </c>
-      <c r="F425" s="9" t="n">
-        <v>3.08</v>
-      </c>
+      <c r="F425" s="10" t="n"/>
     </row>
     <row r="426" ht="18" customHeight="1">
       <c r="A426" s="3" t="n"/>
@@ -10098,9 +9180,7 @@
           <t>44.931 + 27.288 + 6.16 = 78.379</t>
         </is>
       </c>
-      <c r="F426" s="9" t="n">
-        <v>78.379</v>
-      </c>
+      <c r="F426" s="10" t="n"/>
     </row>
     <row r="427" ht="18" customHeight="1">
       <c r="A427" s="3" t="n"/>
@@ -10120,9 +9200,7 @@
           <t>44.931 + 27.288 + 6.16 = 78.379</t>
         </is>
       </c>
-      <c r="F427" s="9" t="n">
-        <v>78.379</v>
-      </c>
+      <c r="F427" s="10" t="n"/>
     </row>
     <row r="428" ht="18" customHeight="1">
       <c r="A428" s="3" t="n"/>
@@ -10142,9 +9220,7 @@
           <t>3.08 = 3.08</t>
         </is>
       </c>
-      <c r="F428" s="9" t="n">
-        <v>3.08</v>
-      </c>
+      <c r="F428" s="10" t="n"/>
     </row>
     <row r="429" ht="18" customHeight="1">
       <c r="A429" s="3" t="n"/>
@@ -10164,9 +9240,7 @@
           <t>6.16 = 6.16</t>
         </is>
       </c>
-      <c r="F429" s="9" t="n">
-        <v>6.16</v>
-      </c>
+      <c r="F429" s="10" t="n"/>
     </row>
     <row r="430" ht="18" customHeight="1">
       <c r="A430" s="3" t="n"/>
@@ -10186,9 +9260,7 @@
           <t>86.868 = 86.868</t>
         </is>
       </c>
-      <c r="F430" s="9" t="n">
-        <v>86.86799999999999</v>
-      </c>
+      <c r="F430" s="10" t="n"/>
     </row>
     <row r="431" ht="18" customHeight="1">
       <c r="A431" s="3" t="n"/>
@@ -10208,9 +9280,7 @@
           <t>77.676 = 77.676</t>
         </is>
       </c>
-      <c r="F431" s="9" t="n">
-        <v>77.676</v>
-      </c>
+      <c r="F431" s="10" t="n"/>
     </row>
     <row r="432" ht="18" customHeight="1">
       <c r="A432" s="3" t="n"/>
@@ -10230,9 +9300,7 @@
           <t>3.08 = 3.08</t>
         </is>
       </c>
-      <c r="F432" s="9" t="n">
-        <v>3.08</v>
-      </c>
+      <c r="F432" s="10" t="n"/>
     </row>
     <row r="433" ht="18" customHeight="1">
       <c r="A433" s="3" t="n"/>
@@ -10252,9 +9320,7 @@
           <t>44.931 + 27.288 + 6.16 = 78.379</t>
         </is>
       </c>
-      <c r="F433" s="9" t="n">
-        <v>78.379</v>
-      </c>
+      <c r="F433" s="10" t="n"/>
     </row>
     <row r="434" ht="18" customHeight="1">
       <c r="A434" s="3" t="n"/>
@@ -10274,9 +9340,7 @@
           <t>44.931 + 27.288 + 6.16 = 78.379</t>
         </is>
       </c>
-      <c r="F434" s="9" t="n">
-        <v>78.379</v>
-      </c>
+      <c r="F434" s="10" t="n"/>
     </row>
     <row r="435" ht="18" customHeight="1">
       <c r="A435" s="3" t="n"/>
@@ -10296,9 +9360,7 @@
           <t>3.08 = 3.08</t>
         </is>
       </c>
-      <c r="F435" s="9" t="n">
-        <v>3.08</v>
-      </c>
+      <c r="F435" s="10" t="n"/>
     </row>
     <row r="436" ht="18" customHeight="1">
       <c r="A436" s="3" t="n"/>
@@ -10318,9 +9380,7 @@
           <t>6.16 = 6.16</t>
         </is>
       </c>
-      <c r="F436" s="9" t="n">
-        <v>6.16</v>
-      </c>
+      <c r="F436" s="10" t="n"/>
     </row>
     <row r="437" ht="18" customHeight="1">
       <c r="A437" s="3" t="n"/>
@@ -10340,9 +9400,7 @@
           <t>86.868 = 86.868</t>
         </is>
       </c>
-      <c r="F437" s="9" t="n">
-        <v>86.86799999999999</v>
-      </c>
+      <c r="F437" s="10" t="n"/>
     </row>
     <row r="438" ht="18" customHeight="1">
       <c r="A438" s="3" t="n"/>
@@ -10362,9 +9420,7 @@
           <t>77.676 = 77.676</t>
         </is>
       </c>
-      <c r="F438" s="9" t="n">
-        <v>77.676</v>
-      </c>
+      <c r="F438" s="10" t="n"/>
     </row>
     <row r="439" ht="18" customHeight="1">
       <c r="A439" s="3" t="n"/>
@@ -10384,9 +9440,7 @@
           <t>29.036 + 29.954 + 29.036 + 29.954 = 117.98</t>
         </is>
       </c>
-      <c r="F439" s="9" t="n">
-        <v>117.98</v>
-      </c>
+      <c r="F439" s="10" t="n"/>
     </row>
     <row r="440" ht="18" customHeight="1">
       <c r="A440" s="3" t="n"/>
@@ -10406,18 +9460,12 @@
           <t>3.08 = 3.08</t>
         </is>
       </c>
-      <c r="F440" s="9" t="n">
-        <v>3.08</v>
-      </c>
+      <c r="F440" s="10" t="n"/>
     </row>
     <row r="441" ht="32" customHeight="1">
       <c r="A441" s="3" t="n"/>
       <c r="B441" s="3" t="n"/>
-      <c r="C441" s="6" t="inlineStr">
-        <is>
-          <t>小计</t>
-        </is>
-      </c>
+      <c r="C441" s="6" t="n"/>
       <c r="D441" s="7" t="inlineStr">
         <is>
           <t>t</t>
@@ -10428,9 +9476,7 @@
           <t>(3.08 + 147.932 + 3.08 + 86.868 + 3.08 + 78.379 + 78.379 + 3.08 + 6.16 + 86.868 + 77.676 + 3.08 + 78.379 + 78.379 + 3.08 + 6.16 + 86.868 + 77.676 + 117.98 + 3.08) ÷ 1000 = 1.029</t>
         </is>
       </c>
-      <c r="F441" s="10" t="n">
-        <v>1.029</v>
-      </c>
+      <c r="F441" s="10" t="n"/>
     </row>
     <row r="442" ht="18" customHeight="1">
       <c r="A442" s="3" t="n">
@@ -10457,7 +9503,7 @@
         </is>
       </c>
       <c r="F442" s="9" t="n">
-        <v>72.411</v>
+        <v>2.37</v>
       </c>
     </row>
     <row r="443" ht="18" customHeight="1">
@@ -10478,9 +9524,7 @@
           <t>56.826 + 61.304 + 58.284 + 77.115 = 253.529</t>
         </is>
       </c>
-      <c r="F443" s="9" t="n">
-        <v>253.529</v>
-      </c>
+      <c r="F443" s="10" t="n"/>
     </row>
     <row r="444" ht="18" customHeight="1">
       <c r="A444" s="3" t="n"/>
@@ -10500,9 +9544,7 @@
           <t>35.94 + 39.2 + 48.248 + 47 + 54.242 + 50.26 = 274.89</t>
         </is>
       </c>
-      <c r="F444" s="9" t="n">
-        <v>274.89</v>
-      </c>
+      <c r="F444" s="10" t="n"/>
     </row>
     <row r="445" ht="18" customHeight="1">
       <c r="A445" s="3" t="n"/>
@@ -10522,9 +9564,7 @@
           <t>15.213 + 15.771 + 16.995 + 19.173 + 30.549 + 1.976 + 33.075 + 33.32 + 2.3 + 37.449 + 56.826 + 61.304 + 58.284 + 77.115 + 9.681 + 11.655 + 10.815 + 15.078 = 506.579</t>
         </is>
       </c>
-      <c r="F445" s="9" t="n">
-        <v>506.579</v>
-      </c>
+      <c r="F445" s="10" t="n"/>
     </row>
     <row r="446" ht="18" customHeight="1">
       <c r="A446" s="3" t="n"/>
@@ -10544,9 +9584,7 @@
           <t>50.26 + 54.242 + 47 + 48.248 + 39.2 + 35.94 = 274.89</t>
         </is>
       </c>
-      <c r="F446" s="9" t="n">
-        <v>274.89</v>
-      </c>
+      <c r="F446" s="10" t="n"/>
     </row>
     <row r="447" ht="18" customHeight="1">
       <c r="A447" s="3" t="n"/>
@@ -10566,9 +9604,7 @@
           <t>77.115 + 58.284 + 61.304 + 56.826 + 37.449 + 33.32 + 2.3 + 33.075 + 30.549 + 1.976 + 19.173 + 16.995 + 15.771 + 15.213 + 9.681 + 11.655 + 10.815 + 15.078 = 506.579</t>
         </is>
       </c>
-      <c r="F447" s="9" t="n">
-        <v>506.579</v>
-      </c>
+      <c r="F447" s="10" t="n"/>
     </row>
     <row r="448" ht="18" customHeight="1">
       <c r="A448" s="3" t="n"/>
@@ -10588,9 +9624,7 @@
           <t>14.913 + 22.496 + 15.399 + 34.884 + 56.826 + 61.304 + 58.284 + 77.115 = 341.221</t>
         </is>
       </c>
-      <c r="F448" s="9" t="n">
-        <v>341.221</v>
-      </c>
+      <c r="F448" s="10" t="n"/>
     </row>
     <row r="449" ht="18" customHeight="1">
       <c r="A449" s="3" t="n"/>
@@ -10610,9 +9644,7 @@
           <t>15.213 + 15.771 + 16.995 + 19.173 + 9.681 + 11.655 + 10.815 + 15.078 = 114.381</t>
         </is>
       </c>
-      <c r="F449" s="9" t="n">
-        <v>114.381</v>
-      </c>
+      <c r="F449" s="10" t="n"/>
     </row>
     <row r="450" ht="18" customHeight="1">
       <c r="A450" s="3" t="n"/>
@@ -10632,18 +9664,12 @@
           <t>4.125 + 6.854 + 4.137 + 10.557 = 25.673</t>
         </is>
       </c>
-      <c r="F450" s="9" t="n">
-        <v>25.673</v>
-      </c>
+      <c r="F450" s="10" t="n"/>
     </row>
     <row r="451" ht="18" customHeight="1">
       <c r="A451" s="3" t="n"/>
       <c r="B451" s="3" t="n"/>
-      <c r="C451" s="6" t="inlineStr">
-        <is>
-          <t>小计</t>
-        </is>
-      </c>
+      <c r="C451" s="6" t="n"/>
       <c r="D451" s="7" t="inlineStr">
         <is>
           <t>t</t>
@@ -10654,9 +9680,7 @@
           <t>(72.411 + 253.529 + 274.89 + 506.579 + 274.89 + 506.579 + 341.221 + 114.381 + 25.673) ÷ 1000 = 2.370</t>
         </is>
       </c>
-      <c r="F451" s="10" t="n">
-        <v>2.37</v>
-      </c>
+      <c r="F451" s="10" t="n"/>
     </row>
     <row r="452" ht="18" customHeight="1">
       <c r="A452" s="3" t="n">
@@ -10683,7 +9707,7 @@
         </is>
       </c>
       <c r="F452" s="9" t="n">
-        <v>625.867</v>
+        <v>2.808</v>
       </c>
     </row>
     <row r="453" ht="18" customHeight="1">
@@ -10704,9 +9728,7 @@
           <t>40.824 + 46.746 + 17.766 + 85.512 + 42.944 + 27.084 + 121.94 + 62.307 + 56.925 + 81.54 = 583.588</t>
         </is>
       </c>
-      <c r="F453" s="9" t="n">
-        <v>583.588</v>
-      </c>
+      <c r="F453" s="10" t="n"/>
     </row>
     <row r="454" ht="18" customHeight="1">
       <c r="A454" s="3" t="n"/>
@@ -10726,9 +9748,7 @@
           <t>46.746 + 40.824 + 56.925 + 81.54 + 42.944 + 17.766 + 85.512 + 62.307 + 27.084 + 121.94 = 583.588</t>
         </is>
       </c>
-      <c r="F454" s="9" t="n">
-        <v>583.588</v>
-      </c>
+      <c r="F454" s="10" t="n"/>
     </row>
     <row r="455" ht="18" customHeight="1">
       <c r="A455" s="3" t="n"/>
@@ -10748,9 +9768,7 @@
           <t>48.12 + 49.35 + 69.82 + 56.925 + 81.54 + 42.944 + 17.766 + 85.512 + 62.307 + 27.084 + 121.94 = 663.308</t>
         </is>
       </c>
-      <c r="F455" s="9" t="n">
-        <v>663.308</v>
-      </c>
+      <c r="F455" s="10" t="n"/>
     </row>
     <row r="456" ht="18" customHeight="1">
       <c r="A456" s="3" t="n"/>
@@ -10770,18 +9788,12 @@
           <t>50.496 + 21.01 + 69.152 + 109.48 + 101.244 = 351.382</t>
         </is>
       </c>
-      <c r="F456" s="9" t="n">
-        <v>351.382</v>
-      </c>
+      <c r="F456" s="10" t="n"/>
     </row>
     <row r="457" ht="18" customHeight="1">
       <c r="A457" s="3" t="n"/>
       <c r="B457" s="3" t="n"/>
-      <c r="C457" s="6" t="inlineStr">
-        <is>
-          <t>小计</t>
-        </is>
-      </c>
+      <c r="C457" s="6" t="n"/>
       <c r="D457" s="7" t="inlineStr">
         <is>
           <t>t</t>
@@ -10792,9 +9804,7 @@
           <t>(625.867 + 583.588 + 583.588 + 663.308 + 351.382) ÷ 1000 = 2.808</t>
         </is>
       </c>
-      <c r="F457" s="10" t="n">
-        <v>2.808</v>
-      </c>
+      <c r="F457" s="10" t="n"/>
     </row>
     <row r="458" ht="18" customHeight="1">
       <c r="A458" s="3" t="n">
@@ -10821,7 +9831,7 @@
         </is>
       </c>
       <c r="F458" s="9" t="n">
-        <v>1567.423</v>
+        <v>6.289</v>
       </c>
     </row>
     <row r="459" ht="18" customHeight="1">
@@ -10842,9 +9852,7 @@
           <t>252.896 + 124.68 + 336.148 + 131.064 + 130.416 + 176.16 + 165.592 + 158.144 = 1475.1</t>
         </is>
       </c>
-      <c r="F459" s="9" t="n">
-        <v>1475.1</v>
-      </c>
+      <c r="F459" s="10" t="n"/>
     </row>
     <row r="460" ht="18" customHeight="1">
       <c r="A460" s="3" t="n"/>
@@ -10864,9 +9872,7 @@
           <t>130.416 + 131.064 + 165.592 + 176.16 + 124.68 + 252.896 + 336.148 + 158.144 = 1475.1</t>
         </is>
       </c>
-      <c r="F460" s="9" t="n">
-        <v>1475.1</v>
-      </c>
+      <c r="F460" s="10" t="n"/>
     </row>
     <row r="461" ht="18" customHeight="1">
       <c r="A461" s="3" t="n"/>
@@ -10886,18 +9892,12 @@
           <t>221.284 + 110.832 + 385.704 + 260.799 + 353.84 + 165.592 + 131.064 + 141.96 = 1771.075</t>
         </is>
       </c>
-      <c r="F461" s="9" t="n">
-        <v>1771.075</v>
-      </c>
+      <c r="F461" s="10" t="n"/>
     </row>
     <row r="462" ht="18" customHeight="1">
       <c r="A462" s="3" t="n"/>
       <c r="B462" s="3" t="n"/>
-      <c r="C462" s="6" t="inlineStr">
-        <is>
-          <t>小计</t>
-        </is>
-      </c>
+      <c r="C462" s="6" t="n"/>
       <c r="D462" s="7" t="inlineStr">
         <is>
           <t>t</t>
@@ -10908,9 +9908,7 @@
           <t>(1567.423 + 1475.1 + 1475.1 + 1771.075) ÷ 1000 = 6.289</t>
         </is>
       </c>
-      <c r="F462" s="10" t="n">
-        <v>6.289</v>
-      </c>
+      <c r="F462" s="10" t="n"/>
     </row>
     <row r="463" ht="18" customHeight="1">
       <c r="A463" s="3" t="n">
@@ -10937,7 +9935,7 @@
         </is>
       </c>
       <c r="F463" s="9" t="n">
-        <v>18.836</v>
+        <v>0.089</v>
       </c>
     </row>
     <row r="464" ht="18" customHeight="1">
@@ -10958,9 +9956,7 @@
           <t>15.408 + 7.922 = 23.33</t>
         </is>
       </c>
-      <c r="F464" s="9" t="n">
-        <v>23.33</v>
-      </c>
+      <c r="F464" s="10" t="n"/>
     </row>
     <row r="465" ht="18" customHeight="1">
       <c r="A465" s="3" t="n"/>
@@ -10980,9 +9976,7 @@
           <t>15.408 + 7.922 = 23.33</t>
         </is>
       </c>
-      <c r="F465" s="9" t="n">
-        <v>23.33</v>
-      </c>
+      <c r="F465" s="10" t="n"/>
     </row>
     <row r="466" ht="18" customHeight="1">
       <c r="A466" s="3" t="n"/>
@@ -11002,18 +9996,12 @@
           <t>15.408 + 7.922 = 23.33</t>
         </is>
       </c>
-      <c r="F466" s="9" t="n">
-        <v>23.33</v>
-      </c>
+      <c r="F466" s="10" t="n"/>
     </row>
     <row r="467" ht="18" customHeight="1">
       <c r="A467" s="3" t="n"/>
       <c r="B467" s="3" t="n"/>
-      <c r="C467" s="6" t="inlineStr">
-        <is>
-          <t>小计</t>
-        </is>
-      </c>
+      <c r="C467" s="6" t="n"/>
       <c r="D467" s="7" t="inlineStr">
         <is>
           <t>t</t>
@@ -11024,9 +10012,7 @@
           <t>(18.836 + 23.33 + 23.33 + 23.33) ÷ 1000 = 0.089</t>
         </is>
       </c>
-      <c r="F467" s="10" t="n">
-        <v>0.089</v>
-      </c>
+      <c r="F467" s="10" t="n"/>
     </row>
     <row r="468" ht="18" customHeight="1">
       <c r="A468" s="3" t="n">
@@ -11053,7 +10039,7 @@
         </is>
       </c>
       <c r="F468" s="9" t="n">
-        <v>63.941</v>
+        <v>0.209</v>
       </c>
     </row>
     <row r="469" ht="18" customHeight="1">
@@ -11074,9 +10060,7 @@
           <t>13.587 + 11.277 + 11.991 + 11.376 = 48.231</t>
         </is>
       </c>
-      <c r="F469" s="9" t="n">
-        <v>48.231</v>
-      </c>
+      <c r="F469" s="10" t="n"/>
     </row>
     <row r="470" ht="18" customHeight="1">
       <c r="A470" s="3" t="n"/>
@@ -11096,9 +10080,7 @@
           <t>13.587 + 11.277 + 11.991 + 11.376 = 48.231</t>
         </is>
       </c>
-      <c r="F470" s="9" t="n">
-        <v>48.231</v>
-      </c>
+      <c r="F470" s="10" t="n"/>
     </row>
     <row r="471" ht="18" customHeight="1">
       <c r="A471" s="3" t="n"/>
@@ -11118,18 +10100,12 @@
           <t>13.587 + 11.277 + 11.991 + 11.376 = 48.231</t>
         </is>
       </c>
-      <c r="F471" s="9" t="n">
-        <v>48.231</v>
-      </c>
+      <c r="F471" s="10" t="n"/>
     </row>
     <row r="472" ht="18" customHeight="1">
       <c r="A472" s="3" t="n"/>
       <c r="B472" s="3" t="n"/>
-      <c r="C472" s="6" t="inlineStr">
-        <is>
-          <t>小计</t>
-        </is>
-      </c>
+      <c r="C472" s="6" t="n"/>
       <c r="D472" s="7" t="inlineStr">
         <is>
           <t>t</t>
@@ -11140,9 +10116,7 @@
           <t>(63.941 + 48.231 + 48.231 + 48.231) ÷ 1000 = 0.209</t>
         </is>
       </c>
-      <c r="F472" s="10" t="n">
-        <v>0.209</v>
-      </c>
+      <c r="F472" s="10" t="n"/>
     </row>
     <row r="473" ht="18" customHeight="1">
       <c r="A473" s="3" t="n">
@@ -11169,7 +10143,7 @@
         </is>
       </c>
       <c r="F473" s="9" t="n">
-        <v>111.07</v>
+        <v>0.417</v>
       </c>
     </row>
     <row r="474" ht="18" customHeight="1">
@@ -11190,9 +10164,7 @@
           <t>22.24 + 7.39 + 29.83 + 11.12 + 31.37 = 101.95</t>
         </is>
       </c>
-      <c r="F474" s="9" t="n">
-        <v>101.95</v>
-      </c>
+      <c r="F474" s="10" t="n"/>
     </row>
     <row r="475" ht="18" customHeight="1">
       <c r="A475" s="3" t="n"/>
@@ -11212,9 +10184,7 @@
           <t>22.24 + 7.39 + 29.83 + 11.12 + 31.37 = 101.95</t>
         </is>
       </c>
-      <c r="F475" s="9" t="n">
-        <v>101.95</v>
-      </c>
+      <c r="F475" s="10" t="n"/>
     </row>
     <row r="476" ht="18" customHeight="1">
       <c r="A476" s="3" t="n"/>
@@ -11234,18 +10204,12 @@
           <t>22.24 + 7.39 + 29.83 + 11.12 + 31.37 = 101.95</t>
         </is>
       </c>
-      <c r="F476" s="9" t="n">
-        <v>101.95</v>
-      </c>
+      <c r="F476" s="10" t="n"/>
     </row>
     <row r="477" ht="18" customHeight="1">
       <c r="A477" s="3" t="n"/>
       <c r="B477" s="3" t="n"/>
-      <c r="C477" s="6" t="inlineStr">
-        <is>
-          <t>小计</t>
-        </is>
-      </c>
+      <c r="C477" s="6" t="n"/>
       <c r="D477" s="7" t="inlineStr">
         <is>
           <t>t</t>
@@ -11256,9 +10220,7 @@
           <t>(111.07 + 101.95 + 101.95 + 101.95) ÷ 1000 = 0.417</t>
         </is>
       </c>
-      <c r="F477" s="10" t="n">
-        <v>0.417</v>
-      </c>
+      <c r="F477" s="10" t="n"/>
     </row>
     <row r="478" ht="18" customHeight="1">
       <c r="A478" s="3" t="n">
@@ -11285,7 +10247,7 @@
         </is>
       </c>
       <c r="F478" s="9" t="n">
-        <v>66.556</v>
+        <v>0.266</v>
       </c>
     </row>
     <row r="479" ht="18" customHeight="1">
@@ -11306,9 +10268,7 @@
           <t>11.704 + 5.783 + 15.741 + 11.724 + 5.792 + 15.771 = 66.515</t>
         </is>
       </c>
-      <c r="F479" s="9" t="n">
-        <v>66.515</v>
-      </c>
+      <c r="F479" s="10" t="n"/>
     </row>
     <row r="480" ht="18" customHeight="1">
       <c r="A480" s="3" t="n"/>
@@ -11328,9 +10288,7 @@
           <t>11.704 + 5.783 + 15.741 + 11.724 + 5.792 + 15.771 = 66.515</t>
         </is>
       </c>
-      <c r="F480" s="9" t="n">
-        <v>66.515</v>
-      </c>
+      <c r="F480" s="10" t="n"/>
     </row>
     <row r="481" ht="18" customHeight="1">
       <c r="A481" s="3" t="n"/>
@@ -11350,18 +10308,12 @@
           <t>11.704 + 5.783 + 15.741 + 11.724 + 5.792 + 15.771 = 66.515</t>
         </is>
       </c>
-      <c r="F481" s="9" t="n">
-        <v>66.515</v>
-      </c>
+      <c r="F481" s="10" t="n"/>
     </row>
     <row r="482" ht="18" customHeight="1">
       <c r="A482" s="3" t="n"/>
       <c r="B482" s="3" t="n"/>
-      <c r="C482" s="6" t="inlineStr">
-        <is>
-          <t>小计</t>
-        </is>
-      </c>
+      <c r="C482" s="6" t="n"/>
       <c r="D482" s="7" t="inlineStr">
         <is>
           <t>t</t>
@@ -11372,9 +10324,7 @@
           <t>(66.556 + 66.515 + 66.515 + 66.515) ÷ 1000 = 0.266</t>
         </is>
       </c>
-      <c r="F482" s="10" t="n">
-        <v>0.266</v>
-      </c>
+      <c r="F482" s="10" t="n"/>
     </row>
     <row r="483" ht="18" customHeight="1">
       <c r="A483" s="3" t="n">
@@ -11401,7 +10351,7 @@
         </is>
       </c>
       <c r="F483" s="9" t="n">
-        <v>1.701</v>
+        <v>0.08799999999999999</v>
       </c>
     </row>
     <row r="484" ht="18" customHeight="1">
@@ -11422,9 +10372,7 @@
           <t>6.534 = 6.534</t>
         </is>
       </c>
-      <c r="F484" s="9" t="n">
-        <v>6.534</v>
-      </c>
+      <c r="F484" s="10" t="n"/>
     </row>
     <row r="485" ht="18" customHeight="1">
       <c r="A485" s="3" t="n"/>
@@ -11444,9 +10392,7 @@
           <t>3.213 = 3.213</t>
         </is>
       </c>
-      <c r="F485" s="9" t="n">
-        <v>3.213</v>
-      </c>
+      <c r="F485" s="10" t="n"/>
     </row>
     <row r="486" ht="18" customHeight="1">
       <c r="A486" s="3" t="n"/>
@@ -11466,9 +10412,7 @@
           <t>12.342 = 12.342</t>
         </is>
       </c>
-      <c r="F486" s="9" t="n">
-        <v>12.342</v>
-      </c>
+      <c r="F486" s="10" t="n"/>
     </row>
     <row r="487" ht="18" customHeight="1">
       <c r="A487" s="3" t="n"/>
@@ -11488,9 +10432,7 @@
           <t>3.213 = 3.213</t>
         </is>
       </c>
-      <c r="F487" s="9" t="n">
-        <v>3.213</v>
-      </c>
+      <c r="F487" s="10" t="n"/>
     </row>
     <row r="488" ht="18" customHeight="1">
       <c r="A488" s="3" t="n"/>
@@ -11510,9 +10452,7 @@
           <t>12.342 = 12.342</t>
         </is>
       </c>
-      <c r="F488" s="9" t="n">
-        <v>12.342</v>
-      </c>
+      <c r="F488" s="10" t="n"/>
     </row>
     <row r="489" ht="18" customHeight="1">
       <c r="A489" s="3" t="n"/>
@@ -11532,9 +10472,7 @@
           <t>3.213 = 3.213</t>
         </is>
       </c>
-      <c r="F489" s="9" t="n">
-        <v>3.213</v>
-      </c>
+      <c r="F489" s="10" t="n"/>
     </row>
     <row r="490" ht="18" customHeight="1">
       <c r="A490" s="3" t="n"/>
@@ -11554,9 +10492,7 @@
           <t>12.342 = 12.342</t>
         </is>
       </c>
-      <c r="F490" s="9" t="n">
-        <v>12.342</v>
-      </c>
+      <c r="F490" s="10" t="n"/>
     </row>
     <row r="491" ht="18" customHeight="1">
       <c r="A491" s="3" t="n"/>
@@ -11576,9 +10512,7 @@
           <t>3.213 = 3.213</t>
         </is>
       </c>
-      <c r="F491" s="9" t="n">
-        <v>3.213</v>
-      </c>
+      <c r="F491" s="10" t="n"/>
     </row>
     <row r="492" ht="18" customHeight="1">
       <c r="A492" s="3" t="n"/>
@@ -11598,9 +10532,7 @@
           <t>12.342 = 12.342</t>
         </is>
       </c>
-      <c r="F492" s="9" t="n">
-        <v>12.342</v>
-      </c>
+      <c r="F492" s="10" t="n"/>
     </row>
     <row r="493" ht="18" customHeight="1">
       <c r="A493" s="3" t="n"/>
@@ -11620,9 +10552,7 @@
           <t>5.292 + 2.835 + 2.646 = 10.773</t>
         </is>
       </c>
-      <c r="F493" s="9" t="n">
-        <v>10.773</v>
-      </c>
+      <c r="F493" s="10" t="n"/>
     </row>
     <row r="494" ht="18" customHeight="1">
       <c r="A494" s="3" t="n"/>
@@ -11642,18 +10572,12 @@
           <t>6.534 = 6.534</t>
         </is>
       </c>
-      <c r="F494" s="9" t="n">
-        <v>6.534</v>
-      </c>
+      <c r="F494" s="10" t="n"/>
     </row>
     <row r="495" ht="18" customHeight="1">
       <c r="A495" s="3" t="n"/>
       <c r="B495" s="3" t="n"/>
-      <c r="C495" s="6" t="inlineStr">
-        <is>
-          <t>小计</t>
-        </is>
-      </c>
+      <c r="C495" s="6" t="n"/>
       <c r="D495" s="7" t="inlineStr">
         <is>
           <t>t</t>
@@ -11664,9 +10588,7 @@
           <t>(1.701 + 6.534 + 3.213 + 12.342 + 3.213 + 12.342 + 3.213 + 12.342 + 3.213 + 12.342 + 10.773 + 6.534) ÷ 1000 = 0.088</t>
         </is>
       </c>
-      <c r="F495" s="10" t="n">
-        <v>0.08799999999999999</v>
-      </c>
+      <c r="F495" s="10" t="n"/>
     </row>
     <row r="496" ht="18" customHeight="1">
       <c r="A496" s="3" t="n">
@@ -11693,7 +10615,7 @@
         </is>
       </c>
       <c r="F496" s="9" t="n">
-        <v>9.212</v>
+        <v>0.357</v>
       </c>
     </row>
     <row r="497" ht="18" customHeight="1">
@@ -11714,9 +10636,7 @@
           <t>17.532 + 10.104 = 27.636</t>
         </is>
       </c>
-      <c r="F497" s="9" t="n">
-        <v>27.636</v>
-      </c>
+      <c r="F497" s="10" t="n"/>
     </row>
     <row r="498" ht="18" customHeight="1">
       <c r="A498" s="3" t="n"/>
@@ -11736,9 +10656,7 @@
           <t>11.704 + 3.368 = 15.072</t>
         </is>
       </c>
-      <c r="F498" s="9" t="n">
-        <v>15.072</v>
-      </c>
+      <c r="F498" s="10" t="n"/>
     </row>
     <row r="499" ht="18" customHeight="1">
       <c r="A499" s="3" t="n"/>
@@ -11758,9 +10676,7 @@
           <t>35.112 + 10.104 = 45.216</t>
         </is>
       </c>
-      <c r="F499" s="9" t="n">
-        <v>45.216</v>
-      </c>
+      <c r="F499" s="10" t="n"/>
     </row>
     <row r="500" ht="18" customHeight="1">
       <c r="A500" s="3" t="n"/>
@@ -11780,9 +10696,7 @@
           <t>11.704 + 3.28 = 14.984</t>
         </is>
       </c>
-      <c r="F500" s="9" t="n">
-        <v>14.984</v>
-      </c>
+      <c r="F500" s="10" t="n"/>
     </row>
     <row r="501" ht="18" customHeight="1">
       <c r="A501" s="3" t="n"/>
@@ -11802,9 +10716,7 @@
           <t>35.112 + 9.84 = 44.952</t>
         </is>
       </c>
-      <c r="F501" s="9" t="n">
-        <v>44.952</v>
-      </c>
+      <c r="F501" s="10" t="n"/>
     </row>
     <row r="502" ht="18" customHeight="1">
       <c r="A502" s="3" t="n"/>
@@ -11824,9 +10736,7 @@
           <t>11.704 + 3.28 = 14.984</t>
         </is>
       </c>
-      <c r="F502" s="9" t="n">
-        <v>14.984</v>
-      </c>
+      <c r="F502" s="10" t="n"/>
     </row>
     <row r="503" ht="18" customHeight="1">
       <c r="A503" s="3" t="n"/>
@@ -11846,9 +10756,7 @@
           <t>35.112 + 9.84 = 44.952</t>
         </is>
       </c>
-      <c r="F503" s="9" t="n">
-        <v>44.952</v>
-      </c>
+      <c r="F503" s="10" t="n"/>
     </row>
     <row r="504" ht="18" customHeight="1">
       <c r="A504" s="3" t="n"/>
@@ -11868,9 +10776,7 @@
           <t>11.704 + 3.28 = 14.984</t>
         </is>
       </c>
-      <c r="F504" s="9" t="n">
-        <v>14.984</v>
-      </c>
+      <c r="F504" s="10" t="n"/>
     </row>
     <row r="505" ht="18" customHeight="1">
       <c r="A505" s="3" t="n"/>
@@ -11890,9 +10796,7 @@
           <t>35.112 + 9.84 = 44.952</t>
         </is>
       </c>
-      <c r="F505" s="9" t="n">
-        <v>44.952</v>
-      </c>
+      <c r="F505" s="10" t="n"/>
     </row>
     <row r="506" ht="18" customHeight="1">
       <c r="A506" s="3" t="n"/>
@@ -11912,9 +10816,7 @@
           <t>19.144 + 6.736 + 9.928 + 3.368 + 9.752 + 3.368 = 52.296</t>
         </is>
       </c>
-      <c r="F506" s="9" t="n">
-        <v>52.296</v>
-      </c>
+      <c r="F506" s="10" t="n"/>
     </row>
     <row r="507" ht="18" customHeight="1">
       <c r="A507" s="3" t="n"/>
@@ -11934,18 +10836,12 @@
           <t>18.06 + 9.84 = 27.9</t>
         </is>
       </c>
-      <c r="F507" s="9" t="n">
-        <v>27.9</v>
-      </c>
+      <c r="F507" s="10" t="n"/>
     </row>
     <row r="508" ht="18" customHeight="1">
       <c r="A508" s="3" t="n"/>
       <c r="B508" s="3" t="n"/>
-      <c r="C508" s="6" t="inlineStr">
-        <is>
-          <t>小计</t>
-        </is>
-      </c>
+      <c r="C508" s="6" t="n"/>
       <c r="D508" s="7" t="inlineStr">
         <is>
           <t>t</t>
@@ -11956,9 +10852,7 @@
           <t>(9.212 + 27.636 + 15.072 + 45.216 + 14.984 + 44.952 + 14.984 + 44.952 + 14.984 + 44.952 + 52.296 + 27.9) ÷ 1000 = 0.357</t>
         </is>
       </c>
-      <c r="F508" s="10" t="n">
-        <v>0.357</v>
-      </c>
+      <c r="F508" s="10" t="n"/>
     </row>
     <row r="509" ht="18" customHeight="1">
       <c r="A509" s="3" t="n">
@@ -11985,17 +10879,13 @@
         </is>
       </c>
       <c r="F509" s="9" t="n">
-        <v>0.275</v>
+        <v>0</v>
       </c>
     </row>
     <row r="510" ht="18" customHeight="1">
       <c r="A510" s="3" t="n"/>
       <c r="B510" s="3" t="n"/>
-      <c r="C510" s="6" t="inlineStr">
-        <is>
-          <t>小计</t>
-        </is>
-      </c>
+      <c r="C510" s="6" t="n"/>
       <c r="D510" s="7" t="inlineStr">
         <is>
           <t>t</t>
@@ -12006,9 +10896,7 @@
           <t>(0.275) ÷ 1000 = 0.000</t>
         </is>
       </c>
-      <c r="F510" s="10" t="n">
-        <v>0</v>
-      </c>
+      <c r="F510" s="10" t="n"/>
     </row>
     <row r="511" ht="18" customHeight="1">
       <c r="A511" s="3" t="n">
@@ -12035,7 +10923,7 @@
         </is>
       </c>
       <c r="F511" s="9" t="n">
-        <v>4.212</v>
+        <v>0.044</v>
       </c>
     </row>
     <row r="512" ht="18" customHeight="1">
@@ -12056,9 +10944,7 @@
           <t>10.368 = 10.368</t>
         </is>
       </c>
-      <c r="F512" s="9" t="n">
-        <v>10.368</v>
-      </c>
+      <c r="F512" s="10" t="n"/>
     </row>
     <row r="513" ht="18" customHeight="1">
       <c r="A513" s="3" t="n"/>
@@ -12078,9 +10964,7 @@
           <t>4.212 = 4.212</t>
         </is>
       </c>
-      <c r="F513" s="9" t="n">
-        <v>4.212</v>
-      </c>
+      <c r="F513" s="10" t="n"/>
     </row>
     <row r="514" ht="18" customHeight="1">
       <c r="A514" s="3" t="n"/>
@@ -12100,9 +10984,7 @@
           <t>5.184 = 5.184</t>
         </is>
       </c>
-      <c r="F514" s="9" t="n">
-        <v>5.184</v>
-      </c>
+      <c r="F514" s="10" t="n"/>
     </row>
     <row r="515" ht="18" customHeight="1">
       <c r="A515" s="3" t="n"/>
@@ -12122,9 +11004,7 @@
           <t>4.212 = 4.212</t>
         </is>
       </c>
-      <c r="F515" s="9" t="n">
-        <v>4.212</v>
-      </c>
+      <c r="F515" s="10" t="n"/>
     </row>
     <row r="516" ht="18" customHeight="1">
       <c r="A516" s="3" t="n"/>
@@ -12144,9 +11024,7 @@
           <t>5.184 = 5.184</t>
         </is>
       </c>
-      <c r="F516" s="9" t="n">
-        <v>5.184</v>
-      </c>
+      <c r="F516" s="10" t="n"/>
     </row>
     <row r="517" ht="18" customHeight="1">
       <c r="A517" s="3" t="n"/>
@@ -12166,9 +11044,7 @@
           <t>4.212 = 4.212</t>
         </is>
       </c>
-      <c r="F517" s="9" t="n">
-        <v>4.212</v>
-      </c>
+      <c r="F517" s="10" t="n"/>
     </row>
     <row r="518" ht="18" customHeight="1">
       <c r="A518" s="3" t="n"/>
@@ -12188,9 +11064,7 @@
           <t>5.184 = 5.184</t>
         </is>
       </c>
-      <c r="F518" s="9" t="n">
-        <v>5.184</v>
-      </c>
+      <c r="F518" s="10" t="n"/>
     </row>
     <row r="519" ht="18" customHeight="1">
       <c r="A519" s="3" t="n"/>
@@ -12210,18 +11084,12 @@
           <t>1.62 = 1.62</t>
         </is>
       </c>
-      <c r="F519" s="9" t="n">
-        <v>1.62</v>
-      </c>
+      <c r="F519" s="10" t="n"/>
     </row>
     <row r="520" ht="18" customHeight="1">
       <c r="A520" s="3" t="n"/>
       <c r="B520" s="3" t="n"/>
-      <c r="C520" s="6" t="inlineStr">
-        <is>
-          <t>小计</t>
-        </is>
-      </c>
+      <c r="C520" s="6" t="n"/>
       <c r="D520" s="7" t="inlineStr">
         <is>
           <t>t</t>
@@ -12232,9 +11100,7 @@
           <t>(4.212 + 10.368 + 4.212 + 5.184 + 4.212 + 5.184 + 4.212 + 5.184 + 1.62) ÷ 1000 = 0.044</t>
         </is>
       </c>
-      <c r="F520" s="10" t="n">
-        <v>0.044</v>
-      </c>
+      <c r="F520" s="10" t="n"/>
     </row>
     <row r="521" ht="18" customHeight="1">
       <c r="A521" s="3" t="n">
@@ -12261,17 +11127,13 @@
         </is>
       </c>
       <c r="F521" s="9" t="n">
-        <v>1.224</v>
+        <v>0.001</v>
       </c>
     </row>
     <row r="522" ht="18" customHeight="1">
       <c r="A522" s="3" t="n"/>
       <c r="B522" s="3" t="n"/>
-      <c r="C522" s="6" t="inlineStr">
-        <is>
-          <t>小计</t>
-        </is>
-      </c>
+      <c r="C522" s="6" t="n"/>
       <c r="D522" s="7" t="inlineStr">
         <is>
           <t>t</t>
@@ -12282,9 +11144,7 @@
           <t>(1.224) ÷ 1000 = 0.001</t>
         </is>
       </c>
-      <c r="F522" s="10" t="n">
-        <v>0.001</v>
-      </c>
+      <c r="F522" s="10" t="n"/>
     </row>
     <row r="523" ht="18" customHeight="1">
       <c r="A523" s="3" t="n">
@@ -12311,7 +11171,7 @@
         </is>
       </c>
       <c r="F523" s="9" t="n">
-        <v>17.048</v>
+        <v>0.077</v>
       </c>
     </row>
     <row r="524" ht="18" customHeight="1">
@@ -12332,9 +11192,7 @@
           <t>17.048 = 17.048</t>
         </is>
       </c>
-      <c r="F524" s="9" t="n">
-        <v>17.048</v>
-      </c>
+      <c r="F524" s="10" t="n"/>
     </row>
     <row r="525" ht="18" customHeight="1">
       <c r="A525" s="3" t="n"/>
@@ -12354,9 +11212,7 @@
           <t>17.048 = 17.048</t>
         </is>
       </c>
-      <c r="F525" s="9" t="n">
-        <v>17.048</v>
-      </c>
+      <c r="F525" s="10" t="n"/>
     </row>
     <row r="526" ht="18" customHeight="1">
       <c r="A526" s="3" t="n"/>
@@ -12376,9 +11232,7 @@
           <t>17.048 = 17.048</t>
         </is>
       </c>
-      <c r="F526" s="9" t="n">
-        <v>17.048</v>
-      </c>
+      <c r="F526" s="10" t="n"/>
     </row>
     <row r="527" ht="18" customHeight="1">
       <c r="A527" s="3" t="n"/>
@@ -12398,18 +11252,12 @@
           <t>8.444 = 8.444</t>
         </is>
       </c>
-      <c r="F527" s="9" t="n">
-        <v>8.444000000000001</v>
-      </c>
+      <c r="F527" s="10" t="n"/>
     </row>
     <row r="528" ht="18" customHeight="1">
       <c r="A528" s="3" t="n"/>
       <c r="B528" s="3" t="n"/>
-      <c r="C528" s="6" t="inlineStr">
-        <is>
-          <t>小计</t>
-        </is>
-      </c>
+      <c r="C528" s="6" t="n"/>
       <c r="D528" s="7" t="inlineStr">
         <is>
           <t>t</t>
@@ -12420,9 +11268,7 @@
           <t>(17.048 + 17.048 + 17.048 + 17.048 + 8.444) ÷ 1000 = 0.077</t>
         </is>
       </c>
-      <c r="F528" s="10" t="n">
-        <v>0.077</v>
-      </c>
+      <c r="F528" s="10" t="n"/>
     </row>
     <row r="529" ht="18" customHeight="1">
       <c r="A529" s="3" t="n">
@@ -12449,7 +11295,7 @@
         </is>
       </c>
       <c r="F529" s="9" t="n">
-        <v>58.56</v>
+        <v>0.146</v>
       </c>
     </row>
     <row r="530" ht="18" customHeight="1">
@@ -12470,9 +11316,7 @@
           <t>29.28 = 29.28</t>
         </is>
       </c>
-      <c r="F530" s="9" t="n">
-        <v>29.28</v>
-      </c>
+      <c r="F530" s="10" t="n"/>
     </row>
     <row r="531" ht="18" customHeight="1">
       <c r="A531" s="3" t="n"/>
@@ -12492,9 +11336,7 @@
           <t>29.28 = 29.28</t>
         </is>
       </c>
-      <c r="F531" s="9" t="n">
-        <v>29.28</v>
-      </c>
+      <c r="F531" s="10" t="n"/>
     </row>
     <row r="532" ht="18" customHeight="1">
       <c r="A532" s="3" t="n"/>
@@ -12514,18 +11356,12 @@
           <t>29.28 = 29.28</t>
         </is>
       </c>
-      <c r="F532" s="9" t="n">
-        <v>29.28</v>
-      </c>
+      <c r="F532" s="10" t="n"/>
     </row>
     <row r="533" ht="18" customHeight="1">
       <c r="A533" s="3" t="n"/>
       <c r="B533" s="3" t="n"/>
-      <c r="C533" s="6" t="inlineStr">
-        <is>
-          <t>小计</t>
-        </is>
-      </c>
+      <c r="C533" s="6" t="n"/>
       <c r="D533" s="7" t="inlineStr">
         <is>
           <t>t</t>
@@ -12536,9 +11372,7 @@
           <t>(58.56 + 29.28 + 29.28 + 29.28) ÷ 1000 = 0.146</t>
         </is>
       </c>
-      <c r="F533" s="10" t="n">
-        <v>0.146</v>
-      </c>
+      <c r="F533" s="10" t="n"/>
     </row>
     <row r="534" ht="18" customHeight="1">
       <c r="A534" s="3" t="n">
@@ -12565,7 +11399,7 @@
         </is>
       </c>
       <c r="F534" s="9" t="n">
-        <v>17.181</v>
+        <v>0.021</v>
       </c>
     </row>
     <row r="535" ht="18" customHeight="1">
@@ -12586,18 +11420,12 @@
           <t>4.267 = 4.267</t>
         </is>
       </c>
-      <c r="F535" s="9" t="n">
-        <v>4.267</v>
-      </c>
+      <c r="F535" s="10" t="n"/>
     </row>
     <row r="536" ht="18" customHeight="1">
       <c r="A536" s="3" t="n"/>
       <c r="B536" s="3" t="n"/>
-      <c r="C536" s="6" t="inlineStr">
-        <is>
-          <t>小计</t>
-        </is>
-      </c>
+      <c r="C536" s="6" t="n"/>
       <c r="D536" s="7" t="inlineStr">
         <is>
           <t>t</t>
@@ -12608,9 +11436,7 @@
           <t>(17.181 + 4.267) ÷ 1000 = 0.021</t>
         </is>
       </c>
-      <c r="F536" s="10" t="n">
-        <v>0.021</v>
-      </c>
+      <c r="F536" s="10" t="n"/>
     </row>
     <row r="537" ht="18" customHeight="1">
       <c r="A537" s="3" t="n">
@@ -12637,7 +11463,7 @@
         </is>
       </c>
       <c r="F537" s="9" t="n">
-        <v>70.66200000000001</v>
+        <v>0.08400000000000001</v>
       </c>
     </row>
     <row r="538" ht="18" customHeight="1">
@@ -12658,18 +11484,12 @@
           <t>6.394 + 6.948 = 13.342</t>
         </is>
       </c>
-      <c r="F538" s="9" t="n">
-        <v>13.342</v>
-      </c>
+      <c r="F538" s="10" t="n"/>
     </row>
     <row r="539" ht="18" customHeight="1">
       <c r="A539" s="3" t="n"/>
       <c r="B539" s="3" t="n"/>
-      <c r="C539" s="6" t="inlineStr">
-        <is>
-          <t>小计</t>
-        </is>
-      </c>
+      <c r="C539" s="6" t="n"/>
       <c r="D539" s="7" t="inlineStr">
         <is>
           <t>t</t>
@@ -12680,9 +11500,7 @@
           <t>(70.662 + 13.342) ÷ 1000 = 0.084</t>
         </is>
       </c>
-      <c r="F539" s="10" t="n">
-        <v>0.08400000000000001</v>
-      </c>
+      <c r="F539" s="10" t="n"/>
     </row>
     <row r="540" ht="18" customHeight="1">
       <c r="A540" s="3" t="n">
@@ -12709,17 +11527,13 @@
         </is>
       </c>
       <c r="F540" s="9" t="n">
-        <v>6.04</v>
+        <v>0.006</v>
       </c>
     </row>
     <row r="541" ht="18" customHeight="1">
       <c r="A541" s="3" t="n"/>
       <c r="B541" s="3" t="n"/>
-      <c r="C541" s="6" t="inlineStr">
-        <is>
-          <t>小计</t>
-        </is>
-      </c>
+      <c r="C541" s="6" t="n"/>
       <c r="D541" s="7" t="inlineStr">
         <is>
           <t>t</t>
@@ -12730,9 +11544,7 @@
           <t>(6.04) ÷ 1000 = 0.006</t>
         </is>
       </c>
-      <c r="F541" s="10" t="n">
-        <v>0.006</v>
-      </c>
+      <c r="F541" s="10" t="n"/>
     </row>
     <row r="542" ht="18" customHeight="1">
       <c r="A542" s="3" t="n">
@@ -12759,17 +11571,13 @@
         </is>
       </c>
       <c r="F542" s="9" t="n">
-        <v>263.369</v>
+        <v>0.263</v>
       </c>
     </row>
     <row r="543" ht="18" customHeight="1">
       <c r="A543" s="3" t="n"/>
       <c r="B543" s="3" t="n"/>
-      <c r="C543" s="6" t="inlineStr">
-        <is>
-          <t>小计</t>
-        </is>
-      </c>
+      <c r="C543" s="6" t="n"/>
       <c r="D543" s="7" t="inlineStr">
         <is>
           <t>t</t>
@@ -12780,9 +11588,7 @@
           <t>(263.369) ÷ 1000 = 0.263</t>
         </is>
       </c>
-      <c r="F543" s="10" t="n">
-        <v>0.263</v>
-      </c>
+      <c r="F543" s="10" t="n"/>
     </row>
     <row r="544" ht="18" customHeight="1">
       <c r="A544" s="3" t="n">
@@ -12809,7 +11615,7 @@
         </is>
       </c>
       <c r="F544" s="5" t="n">
-        <v>9</v>
+        <v>13.83</v>
       </c>
     </row>
     <row r="545" ht="18" customHeight="1">
@@ -12830,9 +11636,7 @@
           <t>(0.8×2.1) = 1.68</t>
         </is>
       </c>
-      <c r="F545" s="5" t="n">
-        <v>1.68</v>
-      </c>
+      <c r="F545" s="8" t="n"/>
     </row>
     <row r="546" ht="18" customHeight="1">
       <c r="A546" s="3" t="n"/>
@@ -12852,18 +11656,12 @@
           <t>(1.5×2.1) = 3.15</t>
         </is>
       </c>
-      <c r="F546" s="5" t="n">
-        <v>3.15</v>
-      </c>
+      <c r="F546" s="8" t="n"/>
     </row>
     <row r="547" ht="18" customHeight="1">
       <c r="A547" s="3" t="n"/>
       <c r="B547" s="3" t="n"/>
-      <c r="C547" s="6" t="inlineStr">
-        <is>
-          <t>小计</t>
-        </is>
-      </c>
+      <c r="C547" s="6" t="n"/>
       <c r="D547" s="7" t="inlineStr">
         <is>
           <t>㎡</t>
@@ -12874,9 +11672,7 @@
           <t>9 + 1.68 + 3.15 = 13.83 ≈ 13.83</t>
         </is>
       </c>
-      <c r="F547" s="8" t="n">
-        <v>13.83</v>
-      </c>
+      <c r="F547" s="8" t="n"/>
     </row>
     <row r="548" ht="18" customHeight="1">
       <c r="A548" s="3" t="n">
@@ -12903,7 +11699,7 @@
         </is>
       </c>
       <c r="F548" s="5" t="n">
-        <v>8.640000000000001</v>
+        <v>164.64</v>
       </c>
     </row>
     <row r="549" ht="18" customHeight="1">
@@ -12924,9 +11720,7 @@
           <t>[(2.4×1.8)]×2 = 8.64</t>
         </is>
       </c>
-      <c r="F549" s="5" t="n">
-        <v>8.640000000000001</v>
-      </c>
+      <c r="F549" s="8" t="n"/>
     </row>
     <row r="550" ht="18" customHeight="1">
       <c r="A550" s="3" t="n"/>
@@ -12946,9 +11740,7 @@
           <t>(1.8×1.8) = 3.24</t>
         </is>
       </c>
-      <c r="F550" s="5" t="n">
-        <v>3.24</v>
-      </c>
+      <c r="F550" s="8" t="n"/>
     </row>
     <row r="551" ht="18" customHeight="1">
       <c r="A551" s="3" t="n"/>
@@ -12968,9 +11760,7 @@
           <t>(1.8×1) = 1.8</t>
         </is>
       </c>
-      <c r="F551" s="5" t="n">
-        <v>1.8</v>
-      </c>
+      <c r="F551" s="8" t="n"/>
     </row>
     <row r="552" ht="18" customHeight="1">
       <c r="A552" s="3" t="n"/>
@@ -12990,9 +11780,7 @@
           <t>[(1.2×3.05)]×2 = 7.32</t>
         </is>
       </c>
-      <c r="F552" s="5" t="n">
-        <v>7.32</v>
-      </c>
+      <c r="F552" s="8" t="n"/>
     </row>
     <row r="553" ht="18" customHeight="1">
       <c r="A553" s="3" t="n"/>
@@ -13012,9 +11800,7 @@
           <t>(4×1.8) = 7.2</t>
         </is>
       </c>
-      <c r="F553" s="5" t="n">
-        <v>7.2</v>
-      </c>
+      <c r="F553" s="8" t="n"/>
     </row>
     <row r="554" ht="18" customHeight="1">
       <c r="A554" s="3" t="n"/>
@@ -13034,9 +11820,7 @@
           <t>[(2.4×3.2)]×2 = 15.36</t>
         </is>
       </c>
-      <c r="F554" s="5" t="n">
-        <v>15.36</v>
-      </c>
+      <c r="F554" s="8" t="n"/>
     </row>
     <row r="555" ht="18" customHeight="1">
       <c r="A555" s="3" t="n"/>
@@ -13056,9 +11840,7 @@
           <t>[(2.4×1.8)]×2 = 8.64</t>
         </is>
       </c>
-      <c r="F555" s="5" t="n">
-        <v>8.640000000000001</v>
-      </c>
+      <c r="F555" s="8" t="n"/>
     </row>
     <row r="556" ht="18" customHeight="1">
       <c r="A556" s="3" t="n"/>
@@ -13078,9 +11860,7 @@
           <t>[(1.8×1.8)]×2 = 6.48</t>
         </is>
       </c>
-      <c r="F556" s="5" t="n">
-        <v>6.48</v>
-      </c>
+      <c r="F556" s="8" t="n"/>
     </row>
     <row r="557" ht="18" customHeight="1">
       <c r="A557" s="3" t="n"/>
@@ -13100,9 +11880,7 @@
           <t>[(1.2×3.05)]×2 = 7.32</t>
         </is>
       </c>
-      <c r="F557" s="5" t="n">
-        <v>7.32</v>
-      </c>
+      <c r="F557" s="8" t="n"/>
     </row>
     <row r="558" ht="18" customHeight="1">
       <c r="A558" s="3" t="n"/>
@@ -13122,9 +11900,7 @@
           <t>(4×1.8) = 7.2</t>
         </is>
       </c>
-      <c r="F558" s="5" t="n">
-        <v>7.2</v>
-      </c>
+      <c r="F558" s="8" t="n"/>
     </row>
     <row r="559" ht="18" customHeight="1">
       <c r="A559" s="3" t="n"/>
@@ -13144,9 +11920,7 @@
           <t>[(2.4×3.2)]×2 = 15.36</t>
         </is>
       </c>
-      <c r="F559" s="5" t="n">
-        <v>15.36</v>
-      </c>
+      <c r="F559" s="8" t="n"/>
     </row>
     <row r="560" ht="18" customHeight="1">
       <c r="A560" s="3" t="n"/>
@@ -13166,9 +11940,7 @@
           <t>[(2.4×1.8)]×2 = 8.64</t>
         </is>
       </c>
-      <c r="F560" s="5" t="n">
-        <v>8.640000000000001</v>
-      </c>
+      <c r="F560" s="8" t="n"/>
     </row>
     <row r="561" ht="18" customHeight="1">
       <c r="A561" s="3" t="n"/>
@@ -13188,9 +11960,7 @@
           <t>[(1.8×1.8)]×2 = 6.48</t>
         </is>
       </c>
-      <c r="F561" s="5" t="n">
-        <v>6.48</v>
-      </c>
+      <c r="F561" s="8" t="n"/>
     </row>
     <row r="562" ht="18" customHeight="1">
       <c r="A562" s="3" t="n"/>
@@ -13210,9 +11980,7 @@
           <t>[(1.2×3.05)]×2 = 7.32</t>
         </is>
       </c>
-      <c r="F562" s="5" t="n">
-        <v>7.32</v>
-      </c>
+      <c r="F562" s="8" t="n"/>
     </row>
     <row r="563" ht="18" customHeight="1">
       <c r="A563" s="3" t="n"/>
@@ -13232,9 +12000,7 @@
           <t>(4×1.8) = 7.2</t>
         </is>
       </c>
-      <c r="F563" s="5" t="n">
-        <v>7.2</v>
-      </c>
+      <c r="F563" s="8" t="n"/>
     </row>
     <row r="564" ht="18" customHeight="1">
       <c r="A564" s="3" t="n"/>
@@ -13254,9 +12020,7 @@
           <t>[(2.4×3.2)]×2 = 15.36</t>
         </is>
       </c>
-      <c r="F564" s="5" t="n">
-        <v>15.36</v>
-      </c>
+      <c r="F564" s="8" t="n"/>
     </row>
     <row r="565" ht="18" customHeight="1">
       <c r="A565" s="3" t="n"/>
@@ -13276,9 +12040,7 @@
           <t>[(2.4×1.8)]×2 = 8.64</t>
         </is>
       </c>
-      <c r="F565" s="5" t="n">
-        <v>8.640000000000001</v>
-      </c>
+      <c r="F565" s="8" t="n"/>
     </row>
     <row r="566" ht="18" customHeight="1">
       <c r="A566" s="3" t="n"/>
@@ -13298,9 +12060,7 @@
           <t>[(1.8×1.8)]×2 = 6.48</t>
         </is>
       </c>
-      <c r="F566" s="5" t="n">
-        <v>6.48</v>
-      </c>
+      <c r="F566" s="8" t="n"/>
     </row>
     <row r="567" ht="18" customHeight="1">
       <c r="A567" s="3" t="n"/>
@@ -13320,18 +12080,12 @@
           <t>[(1.2×3.05)]×2 = 7.32</t>
         </is>
       </c>
-      <c r="F567" s="5" t="n">
-        <v>7.32</v>
-      </c>
+      <c r="F567" s="8" t="n"/>
     </row>
     <row r="568" ht="18" customHeight="1">
       <c r="A568" s="3" t="n"/>
       <c r="B568" s="3" t="n"/>
-      <c r="C568" s="6" t="inlineStr">
-        <is>
-          <t>小计</t>
-        </is>
-      </c>
+      <c r="C568" s="6" t="n"/>
       <c r="D568" s="7" t="inlineStr">
         <is>
           <t>㎡</t>
@@ -13342,9 +12096,7 @@
           <t>8.64 + 8.64 + 3.24 + 1.8 + 7.32 + 7.2 + 15.36 + 8.64 + 6.48 + 7.32 + 7.2 + 15.36 + 8.64 + 6.48 + 7.32 + 7.2 + 15.36 + 8.64 + 6.48 + 7.32 = 164.64 ≈ 164.64</t>
         </is>
       </c>
-      <c r="F568" s="8" t="n">
-        <v>164.64</v>
-      </c>
+      <c r="F568" s="8" t="n"/>
     </row>
     <row r="569" ht="18" customHeight="1">
       <c r="A569" s="3" t="n">
@@ -13371,17 +12123,13 @@
         </is>
       </c>
       <c r="F569" s="5" t="n">
-        <v>219.2982</v>
+        <v>219.3</v>
       </c>
     </row>
     <row r="570" ht="18" customHeight="1">
       <c r="A570" s="3" t="n"/>
       <c r="B570" s="3" t="n"/>
-      <c r="C570" s="6" t="inlineStr">
-        <is>
-          <t>小计</t>
-        </is>
-      </c>
+      <c r="C570" s="6" t="n"/>
       <c r="D570" s="7" t="inlineStr">
         <is>
           <t>㎡</t>
@@ -13392,9 +12140,7 @@
           <t>219.2982 ≈ 219.30</t>
         </is>
       </c>
-      <c r="F570" s="8" t="n">
-        <v>219.3</v>
-      </c>
+      <c r="F570" s="8" t="n"/>
     </row>
     <row r="571" ht="18" customHeight="1">
       <c r="A571" s="3" t="n">
@@ -13421,17 +12167,13 @@
         </is>
       </c>
       <c r="F571" s="5" t="n">
-        <v>200.1282</v>
+        <v>200.13</v>
       </c>
     </row>
     <row r="572" ht="18" customHeight="1">
       <c r="A572" s="3" t="n"/>
       <c r="B572" s="3" t="n"/>
-      <c r="C572" s="6" t="inlineStr">
-        <is>
-          <t>小计</t>
-        </is>
-      </c>
+      <c r="C572" s="6" t="n"/>
       <c r="D572" s="7" t="inlineStr">
         <is>
           <t>㎡</t>
@@ -13442,9 +12184,7 @@
           <t>200.1282 ≈ 200.13</t>
         </is>
       </c>
-      <c r="F572" s="8" t="n">
-        <v>200.13</v>
-      </c>
+      <c r="F572" s="8" t="n"/>
     </row>
     <row r="573" ht="18" customHeight="1">
       <c r="A573" s="3" t="n">
@@ -13470,7 +12210,7 @@
           <t>计算书中无依据，需补充</t>
         </is>
       </c>
-      <c r="F573" s="5" t="inlineStr">
+      <c r="F573" s="8" t="inlineStr">
         <is>
           <t>需补充</t>
         </is>
@@ -13501,17 +12241,13 @@
         </is>
       </c>
       <c r="F574" s="5" t="n">
-        <v>4.5787</v>
+        <v>4.58</v>
       </c>
     </row>
     <row r="575" ht="18" customHeight="1">
       <c r="A575" s="3" t="n"/>
       <c r="B575" s="3" t="n"/>
-      <c r="C575" s="6" t="inlineStr">
-        <is>
-          <t>小计</t>
-        </is>
-      </c>
+      <c r="C575" s="6" t="n"/>
       <c r="D575" s="7" t="inlineStr">
         <is>
           <t>㎡</t>
@@ -13522,9 +12258,7 @@
           <t>4.5787 ≈ 4.58</t>
         </is>
       </c>
-      <c r="F575" s="8" t="n">
-        <v>4.58</v>
-      </c>
+      <c r="F575" s="8" t="n"/>
     </row>
     <row r="576" ht="18" customHeight="1">
       <c r="A576" s="3" t="n">
@@ -13551,17 +12285,13 @@
         </is>
       </c>
       <c r="F576" s="5" t="n">
-        <v>200.1282</v>
+        <v>200.13</v>
       </c>
     </row>
     <row r="577" ht="18" customHeight="1">
       <c r="A577" s="3" t="n"/>
       <c r="B577" s="3" t="n"/>
-      <c r="C577" s="6" t="inlineStr">
-        <is>
-          <t>小计</t>
-        </is>
-      </c>
+      <c r="C577" s="6" t="n"/>
       <c r="D577" s="7" t="inlineStr">
         <is>
           <t>㎡</t>
@@ -13572,9 +12302,7 @@
           <t>200.1282 ≈ 200.13</t>
         </is>
       </c>
-      <c r="F577" s="8" t="n">
-        <v>200.13</v>
-      </c>
+      <c r="F577" s="8" t="n"/>
     </row>
     <row r="578" ht="18" customHeight="1">
       <c r="A578" s="3" t="n">
@@ -13601,7 +12329,7 @@
         </is>
       </c>
       <c r="F578" s="5" t="n">
-        <v>172.0871</v>
+        <v>796.17</v>
       </c>
     </row>
     <row r="579" ht="18" customHeight="1">
@@ -13622,9 +12350,7 @@
           <t>(15.26×13.26)+1.8131-1.404-0.62-0.4428-0.7875 = 200.9065</t>
         </is>
       </c>
-      <c r="F579" s="5" t="n">
-        <v>200.9065</v>
-      </c>
+      <c r="F579" s="8" t="n"/>
     </row>
     <row r="580" ht="18" customHeight="1">
       <c r="A580" s="3" t="n"/>
@@ -13644,9 +12370,7 @@
           <t>(15.26×13.26)-1.404-0.62-0.4428 = 199.8808</t>
         </is>
       </c>
-      <c r="F580" s="5" t="n">
-        <v>199.8808</v>
-      </c>
+      <c r="F580" s="8" t="n"/>
     </row>
     <row r="581" ht="18" customHeight="1">
       <c r="A581" s="3" t="n"/>
@@ -13666,9 +12390,7 @@
           <t>(15.26×13.26)-1.404-0.62-0.4428 = 199.8808</t>
         </is>
       </c>
-      <c r="F581" s="5" t="n">
-        <v>199.8808</v>
-      </c>
+      <c r="F581" s="8" t="n"/>
     </row>
     <row r="582" ht="18" customHeight="1">
       <c r="A582" s="3" t="n"/>
@@ -13688,18 +12410,12 @@
           <t>(7.41×3.16) = 23.4156</t>
         </is>
       </c>
-      <c r="F582" s="5" t="n">
-        <v>23.4156</v>
-      </c>
+      <c r="F582" s="8" t="n"/>
     </row>
     <row r="583" ht="18" customHeight="1">
       <c r="A583" s="3" t="n"/>
       <c r="B583" s="3" t="n"/>
-      <c r="C583" s="6" t="inlineStr">
-        <is>
-          <t>小计</t>
-        </is>
-      </c>
+      <c r="C583" s="6" t="n"/>
       <c r="D583" s="7" t="inlineStr">
         <is>
           <t>㎡</t>
@@ -13710,9 +12426,7 @@
           <t>172.0871 + 200.9065 + 199.8808 + 199.8808 + 23.4156 = 796.1708 ≈ 796.17</t>
         </is>
       </c>
-      <c r="F583" s="8" t="n">
-        <v>796.17</v>
-      </c>
+      <c r="F583" s="8" t="n"/>
     </row>
     <row r="584" ht="18" customHeight="1">
       <c r="A584" s="3" t="n">
@@ -13739,17 +12453,13 @@
         </is>
       </c>
       <c r="F584" s="5" t="n">
-        <v>4.5787</v>
+        <v>4.58</v>
       </c>
     </row>
     <row r="585" ht="18" customHeight="1">
       <c r="A585" s="3" t="n"/>
       <c r="B585" s="3" t="n"/>
-      <c r="C585" s="6" t="inlineStr">
-        <is>
-          <t>小计</t>
-        </is>
-      </c>
+      <c r="C585" s="6" t="n"/>
       <c r="D585" s="7" t="inlineStr">
         <is>
           <t>㎡</t>
@@ -13760,9 +12470,7 @@
           <t>4.5787 ≈ 4.58</t>
         </is>
       </c>
-      <c r="F585" s="8" t="n">
-        <v>4.58</v>
-      </c>
+      <c r="F585" s="8" t="n"/>
     </row>
     <row r="586" ht="18" customHeight="1">
       <c r="A586" s="3" t="n">
@@ -13789,7 +12497,7 @@
         </is>
       </c>
       <c r="F586" s="5" t="n">
-        <v>58.63</v>
+        <v>264.13</v>
       </c>
     </row>
     <row r="587" ht="18" customHeight="1">
@@ -13810,9 +12518,7 @@
           <t>13.26+1.425-0.905-1.2 + 15.02+1.64-1.02-1.8 + 13.26+1.9569-1.405-1.2 + 15.26-4.8 + [5.85+1.355-0.975]×2 = 61.9519</t>
         </is>
       </c>
-      <c r="F587" s="5" t="n">
-        <v>61.9519</v>
-      </c>
+      <c r="F587" s="8" t="n"/>
     </row>
     <row r="588" ht="18" customHeight="1">
       <c r="A588" s="3" t="n"/>
@@ -13832,9 +12538,7 @@
           <t>[5.85+1.355-0.975]×2 + 15.26-4.8 + 13.26+1.9569-1.405-1.2 + 15.02+1.64-1.02-1.8 + 13.26+1.425-0.905-1.2 = 61.9519</t>
         </is>
       </c>
-      <c r="F588" s="5" t="n">
-        <v>61.9519</v>
-      </c>
+      <c r="F588" s="8" t="n"/>
     </row>
     <row r="589" ht="18" customHeight="1">
       <c r="A589" s="3" t="n"/>
@@ -13854,9 +12558,7 @@
           <t>[5.85+1.355-0.975]×2 + 15.26-4.8 + 13.26+1.9569-1.405-1.2 + 15.02+1.64-1.02-1.8 + 13.26+1.425-0.905-1.2 = 61.9519</t>
         </is>
       </c>
-      <c r="F589" s="5" t="n">
-        <v>61.9519</v>
-      </c>
+      <c r="F589" s="8" t="n"/>
     </row>
     <row r="590" ht="18" customHeight="1">
       <c r="A590" s="3" t="n"/>
@@ -13876,18 +12578,12 @@
           <t>[3.16]×2 + 7.41 + 7.41-1.5 = 19.64</t>
         </is>
       </c>
-      <c r="F590" s="5" t="n">
-        <v>19.64</v>
-      </c>
+      <c r="F590" s="8" t="n"/>
     </row>
     <row r="591" ht="18" customHeight="1">
       <c r="A591" s="3" t="n"/>
       <c r="B591" s="3" t="n"/>
-      <c r="C591" s="6" t="inlineStr">
-        <is>
-          <t>小计</t>
-        </is>
-      </c>
+      <c r="C591" s="6" t="n"/>
       <c r="D591" s="7" t="inlineStr">
         <is>
           <t>m</t>
@@ -13898,9 +12594,7 @@
           <t>58.63 + 61.9519 + 61.9519 + 61.9519 + 19.64 = 264.1257 ≈ 264.13</t>
         </is>
       </c>
-      <c r="F591" s="8" t="n">
-        <v>264.13</v>
-      </c>
+      <c r="F591" s="8" t="n"/>
     </row>
     <row r="592" ht="18" customHeight="1">
       <c r="A592" s="3" t="n">
@@ -13927,7 +12621,7 @@
         </is>
       </c>
       <c r="F592" s="5" t="n">
-        <v>161.8592</v>
+        <v>770.35</v>
       </c>
     </row>
     <row r="593" ht="32" customHeight="1">
@@ -13948,9 +12642,7 @@
           <t>13.74×3.6-5.004+5.565-6.605+6.7285-3.66 + 15.74×3.6-3.564+5.424-5.9+6.0475-22.56 + 13.74×3.6-5.904+6.4955-6.4675+6.5885-3.66 + 15.5×3.6-5.4+6.428-5.6+5.74-14.4 = 171.6845</t>
         </is>
       </c>
-      <c r="F593" s="5" t="n">
-        <v>171.6845</v>
-      </c>
+      <c r="F593" s="8" t="n"/>
     </row>
     <row r="594" ht="32" customHeight="1">
       <c r="A594" s="3" t="n"/>
@@ -13970,9 +12662,7 @@
           <t>13.74×3.6-5.004+5.565-6.605+6.7285-3.66 + 15.74×3.6-3.564+5.424-5.9+6.0475-22.56 + 13.74×3.6-5.904+6.4955-6.4675+6.5885-3.66 + 15.5×3.6-5.4+6.428-5.6+5.74-14.4 = 171.6845</t>
         </is>
       </c>
-      <c r="F594" s="5" t="n">
-        <v>171.6845</v>
-      </c>
+      <c r="F594" s="8" t="n"/>
     </row>
     <row r="595" ht="32" customHeight="1">
       <c r="A595" s="3" t="n"/>
@@ -13992,9 +12682,7 @@
           <t>13.74×3.6-5.004+5.565-6.605+6.7285-3.66 + 15.74×3.6-3.564+5.424-5.9+6.0475-22.56 + 13.74×3.6-5.904+6.4955-6.4675+6.5873-3.66 + 15.5×3.6-5.4+6.428-5.6+5.74-13.59 = 172.4933</t>
         </is>
       </c>
-      <c r="F595" s="5" t="n">
-        <v>172.4933</v>
-      </c>
+      <c r="F595" s="8" t="n"/>
     </row>
     <row r="596" ht="32" customHeight="1">
       <c r="A596" s="3" t="n"/>
@@ -14014,18 +12702,12 @@
           <t>(13.74×1.07+1.6344)-0.2843+0.4013+1.9356-4.0413 + (15.74×1.07+1.8744)-0.8662+1.3375+2.1118-4.5 + (5.85×1.07+0.6948)-0.2903+0.5403+0.8243-1.68 + (7.65×3.642+0.9108)-0.75+1.3932-2.22+2.2927+1.1166-1.5228 + (3.642×3.64+0.444)-1.47+1.3922-1.26+1.2915+0.5228-0.7352 + (12.1×1.07+1.4448)-0.0059+0.1391+1.7006-3.6213 = 92.6237</t>
         </is>
       </c>
-      <c r="F596" s="5" t="n">
-        <v>92.6237</v>
-      </c>
+      <c r="F596" s="8" t="n"/>
     </row>
     <row r="597" ht="18" customHeight="1">
       <c r="A597" s="3" t="n"/>
       <c r="B597" s="3" t="n"/>
-      <c r="C597" s="6" t="inlineStr">
-        <is>
-          <t>小计</t>
-        </is>
-      </c>
+      <c r="C597" s="6" t="n"/>
       <c r="D597" s="7" t="inlineStr">
         <is>
           <t>㎡</t>
@@ -14036,9 +12718,7 @@
           <t>161.8592 + 171.6845 + 171.6845 + 172.4933 + 92.6237 = 770.3452 ≈ 770.35</t>
         </is>
       </c>
-      <c r="F597" s="8" t="n">
-        <v>770.35</v>
-      </c>
+      <c r="F597" s="8" t="n"/>
     </row>
     <row r="598" ht="32" customHeight="1">
       <c r="A598" s="3" t="n">
@@ -14065,7 +12745,7 @@
         </is>
       </c>
       <c r="F598" s="5" t="n">
-        <v>187.5849</v>
+        <v>962.71</v>
       </c>
     </row>
     <row r="599" ht="18" customHeight="1">
@@ -14086,9 +12766,7 @@
           <t>3.165×1.5-0.2475+0.2242-1.53-0.48+1.2 + [1.5×1.455-0.24+0.2205-0.7122+0.7122]×2 + 3.165×1.5-0.315 = 12.6727</t>
         </is>
       </c>
-      <c r="F599" s="5" t="n">
-        <v>12.6727</v>
-      </c>
+      <c r="F599" s="8" t="n"/>
     </row>
     <row r="600" ht="32" customHeight="1">
       <c r="A600" s="3" t="n"/>
@@ -14108,9 +12786,7 @@
           <t>46.3392-3.1814+4.8397-3.66-5.3027+5.2265 + (3.6×3.16+41.3344)-3.5734+5.486-15.12-3.617+4.337 + 46.8969-4.994+6.5147-3.66-5.5729+5.5078-0.11-0.4277 + 15.26×3.51-1.7901+1.696-22.56-4.5725+4.495 + 20.9313-3.47+4.6402-2.5926+2.5926 + 5.85×3.5-3.4125+4.5985-2.1938+2.1313 = 203.1701</t>
         </is>
       </c>
-      <c r="F600" s="5" t="n">
-        <v>203.1701</v>
-      </c>
+      <c r="F600" s="8" t="n"/>
     </row>
     <row r="601" ht="32" customHeight="1">
       <c r="A601" s="3" t="n"/>
@@ -14130,9 +12806,7 @@
           <t>20.9313-3.47+4.6402-2.5926+2.5926 + 5.85×3.5-3.4125+4.5985-2.1938+2.1313 + 15.26×3.51-1.7901+1.696-22.56-4.5725+4.495 + 46.8969-4.994+6.5147-3.66-5.5729+5.5078-0.11-0.4277 + (3.6×3.16+41.3344)-3.5734+5.486-15.12-3.617+4.337 + 46.3392-3.1814+4.8397-3.66-5.3027+5.2265 = 203.1701</t>
         </is>
       </c>
-      <c r="F601" s="5" t="n">
-        <v>203.1701</v>
-      </c>
+      <c r="F601" s="8" t="n"/>
     </row>
     <row r="602" ht="32" customHeight="1">
       <c r="A602" s="3" t="n"/>
@@ -14152,9 +12826,7 @@
           <t>20.9313-3.47+4.6402-2.5926+2.5926 + 20.528-3.428+4.5985-2.2313+2.1187 + 15.26×3.6-1.836+1.696-22.56-5.9+4.35 + 47.0211-5.0058+6.5137-3.66-5.6854+5.4953-0.11-0.4277 + (3.6×3.16+11.86×3.6)-3.672+5.5-13.59-5.6+4.5 + 46.374-3.201+4.8307-3.66-5.318+5.083 = 203.8336</t>
         </is>
       </c>
-      <c r="F602" s="5" t="n">
-        <v>203.8336</v>
-      </c>
+      <c r="F602" s="8" t="n"/>
     </row>
     <row r="603" ht="18" customHeight="1">
       <c r="A603" s="3" t="n"/>
@@ -14174,9 +12846,7 @@
           <t>3.16×3-0.03+0.029-0.315 + 21.542-0.0295+0.029-0.0525 + 3.16×2.9-0.029+0.0278 + 21.542-0.0295+0.029-3.15-0.4937+0.4937-0.0525 = 58.1547</t>
         </is>
       </c>
-      <c r="F603" s="5" t="n">
-        <v>58.1547</v>
-      </c>
+      <c r="F603" s="8" t="n"/>
     </row>
     <row r="604" ht="32" customHeight="1">
       <c r="A604" s="3" t="n"/>
@@ -14196,18 +12866,12 @@
           <t>(27.6045+0.9108)-0.4932+1.2343-3.15-2.3188+2.194 + (5.61×(1.07+0.12))-0.0107+0.0107 + (15.26×(1.07+0.12))-0.3082+0.2889 + (13.26×(1.07+0.12))-0.0053+0.0053 + (12.563+0.4152)-0.8532+1.272-0.945+0.9765 + (11.86×(1.07+0.12))-0.0053+0.0053 = 94.1189</t>
         </is>
       </c>
-      <c r="F604" s="5" t="n">
-        <v>94.1189</v>
-      </c>
+      <c r="F604" s="8" t="n"/>
     </row>
     <row r="605" ht="18" customHeight="1">
       <c r="A605" s="3" t="n"/>
       <c r="B605" s="3" t="n"/>
-      <c r="C605" s="6" t="inlineStr">
-        <is>
-          <t>小计</t>
-        </is>
-      </c>
+      <c r="C605" s="6" t="n"/>
       <c r="D605" s="7" t="inlineStr">
         <is>
           <t>㎡</t>
@@ -14218,9 +12882,7 @@
           <t>187.5849 + 12.6727 + 203.1701 + 203.1701 + 203.8336 + 58.1547 + 94.1189 = 962.705 ≈ 962.71</t>
         </is>
       </c>
-      <c r="F605" s="8" t="n">
-        <v>962.71</v>
-      </c>
+      <c r="F605" s="8" t="n"/>
     </row>
     <row r="606" ht="18" customHeight="1">
       <c r="A606" s="3" t="n">
@@ -14247,17 +12909,13 @@
         </is>
       </c>
       <c r="F606" s="5" t="n">
-        <v>16.878</v>
+        <v>16.88</v>
       </c>
     </row>
     <row r="607" ht="18" customHeight="1">
       <c r="A607" s="3" t="n"/>
       <c r="B607" s="3" t="n"/>
-      <c r="C607" s="6" t="inlineStr">
-        <is>
-          <t>小计</t>
-        </is>
-      </c>
+      <c r="C607" s="6" t="n"/>
       <c r="D607" s="7" t="inlineStr">
         <is>
           <t>㎡</t>
@@ -14268,9 +12926,7 @@
           <t>16.878 ≈ 16.88</t>
         </is>
       </c>
-      <c r="F607" s="8" t="n">
-        <v>16.88</v>
-      </c>
+      <c r="F607" s="8" t="n"/>
     </row>
     <row r="608" ht="18" customHeight="1">
       <c r="A608" s="3" t="n">
@@ -14297,7 +12953,7 @@
         </is>
       </c>
       <c r="F608" s="5" t="n">
-        <v>192.2586</v>
+        <v>908.76</v>
       </c>
     </row>
     <row r="609" ht="32" customHeight="1">
@@ -14318,9 +12974,7 @@
           <t>(3×2.28)+2.7827+0.0141-0.9137-0.0137 + (15.26×1.38)+10.9493+0.0863-2.8487-0.085 + (4.33×3.15)+5.1219+0.0144-1.445-0.0145 + (5.73×2.28+8.73×2.05+11.88×4.45)+26.639+0.0678-7.4369-0.07 + (1.68×0.12+3.16×1.8)+4.661+0.0081-0.9994-0.0077 + (6.48×4.35+3.2×1.68+5.85×3.08)+21.8681+0.059-5.4175-0.062 = 235.7941</t>
         </is>
       </c>
-      <c r="F609" s="5" t="n">
-        <v>235.7941</v>
-      </c>
+      <c r="F609" s="8" t="n"/>
     </row>
     <row r="610" ht="32" customHeight="1">
       <c r="A610" s="3" t="n"/>
@@ -14340,9 +12994,7 @@
           <t>(8.78×5.73+6.5×3+4.45×3.15)+26.639+0.0678-7.4369-0.07 + (4.33×3.15)+5.1219+0.0144-1.445-0.0145 + (15.26×1.38)+10.9492+0.0863-2.8487-0.085 + (3×2.28)+2.7827+0.0141-0.9137-0.0137 + (6.48×4.35+3.2×1.68+5.85×3.08)+21.8681+0.059-5.4175-0.062 + (1.68×0.12+3.16×1.8)+4.661+0.0081-0.9994-0.0077 = 235.7941</t>
         </is>
       </c>
-      <c r="F610" s="5" t="n">
-        <v>235.7941</v>
-      </c>
+      <c r="F610" s="8" t="n"/>
     </row>
     <row r="611" ht="18" customHeight="1">
       <c r="A611" s="3" t="n"/>
@@ -14362,9 +13014,7 @@
           <t>77.2942+18.6475+0.1879-9.1212-0.1917 + (11.35×8.78)+30.8617+0.0536-8.4587-0.0542 + (1.68×0.12+3.16×1.8)+5.8422+0.0081-0.9994-0.0077 = 219.6049</t>
         </is>
       </c>
-      <c r="F611" s="5" t="n">
-        <v>219.6049</v>
-      </c>
+      <c r="F611" s="8" t="n"/>
     </row>
     <row r="612" ht="18" customHeight="1">
       <c r="A612" s="3" t="n"/>
@@ -14384,18 +13034,12 @@
           <t>(7.41×3.16)+2.686+0.0099-0.79-0.0099 = 25.3116</t>
         </is>
       </c>
-      <c r="F612" s="5" t="n">
-        <v>25.3116</v>
-      </c>
+      <c r="F612" s="8" t="n"/>
     </row>
     <row r="613" ht="18" customHeight="1">
       <c r="A613" s="3" t="n"/>
       <c r="B613" s="3" t="n"/>
-      <c r="C613" s="6" t="inlineStr">
-        <is>
-          <t>小计</t>
-        </is>
-      </c>
+      <c r="C613" s="6" t="n"/>
       <c r="D613" s="7" t="inlineStr">
         <is>
           <t>㎡</t>
@@ -14406,9 +13050,7 @@
           <t>192.2586 + 235.7941 + 235.7941 + 219.6049 + 25.3116 = 908.7633 ≈ 908.76</t>
         </is>
       </c>
-      <c r="F613" s="8" t="n">
-        <v>908.76</v>
-      </c>
+      <c r="F613" s="8" t="n"/>
     </row>
     <row r="614" ht="18" customHeight="1">
       <c r="A614" s="3" t="n">
@@ -14435,7 +13077,7 @@
         </is>
       </c>
       <c r="F614" s="5" t="n">
-        <v>161.8592</v>
+        <v>770.35</v>
       </c>
     </row>
     <row r="615" ht="32" customHeight="1">
@@ -14456,9 +13098,7 @@
           <t>13.74×3.6-5.004+5.565-6.605+6.7285-3.66 + 15.74×3.6-3.564+5.424-5.9+6.0475-22.56 + 13.74×3.6-5.904+6.4955-6.4675+6.5885-3.66 + 15.5×3.6-5.4+6.428-5.6+5.74-14.4 = 171.6845</t>
         </is>
       </c>
-      <c r="F615" s="5" t="n">
-        <v>171.6845</v>
-      </c>
+      <c r="F615" s="8" t="n"/>
     </row>
     <row r="616" ht="32" customHeight="1">
       <c r="A616" s="3" t="n"/>
@@ -14478,9 +13118,7 @@
           <t>13.74×3.6-5.004+5.565-6.605+6.7285-3.66 + 15.74×3.6-3.564+5.424-5.9+6.0475-22.56 + 13.74×3.6-5.904+6.4955-6.4675+6.5885-3.66 + 15.5×3.6-5.4+6.428-5.6+5.74-14.4 = 171.6845</t>
         </is>
       </c>
-      <c r="F616" s="5" t="n">
-        <v>171.6845</v>
-      </c>
+      <c r="F616" s="8" t="n"/>
     </row>
     <row r="617" ht="32" customHeight="1">
       <c r="A617" s="3" t="n"/>
@@ -14500,9 +13138,7 @@
           <t>13.74×3.6-5.004+5.565-6.605+6.7285-3.66 + 15.74×3.6-3.564+5.424-5.9+6.0475-22.56 + 13.74×3.6-5.904+6.4955-6.4675+6.5873-3.66 + 15.5×3.6-5.4+6.428-5.6+5.74-13.59 = 172.4933</t>
         </is>
       </c>
-      <c r="F617" s="5" t="n">
-        <v>172.4933</v>
-      </c>
+      <c r="F617" s="8" t="n"/>
     </row>
     <row r="618" ht="32" customHeight="1">
       <c r="A618" s="3" t="n"/>
@@ -14522,18 +13158,12 @@
           <t>(13.74×1.07+1.6344)-0.2843+0.4013+1.9356-4.0413 + (15.74×1.07+1.8744)-0.8662+1.3375+2.1118-4.5 + (5.85×1.07+0.6948)-0.2903+0.5403+0.8243-1.68 + (7.65×3.642+0.9108)-0.75+1.3932-2.22+2.2927+1.1166-1.5228 + (3.642×3.64+0.444)-1.47+1.3922-1.26+1.2915+0.5228-0.7352 + (12.1×1.07+1.4448)-0.0059+0.1391+1.7006-3.6213 = 92.6237</t>
         </is>
       </c>
-      <c r="F618" s="5" t="n">
-        <v>92.6237</v>
-      </c>
+      <c r="F618" s="8" t="n"/>
     </row>
     <row r="619" ht="18" customHeight="1">
       <c r="A619" s="3" t="n"/>
       <c r="B619" s="3" t="n"/>
-      <c r="C619" s="6" t="inlineStr">
-        <is>
-          <t>小计</t>
-        </is>
-      </c>
+      <c r="C619" s="6" t="n"/>
       <c r="D619" s="7" t="inlineStr">
         <is>
           <t>㎡</t>
@@ -14544,9 +13174,7 @@
           <t>161.8592 + 171.6845 + 171.6845 + 172.4933 + 92.6237 = 770.3452 ≈ 770.35</t>
         </is>
       </c>
-      <c r="F619" s="8" t="n">
-        <v>770.35</v>
-      </c>
+      <c r="F619" s="8" t="n"/>
     </row>
     <row r="620" ht="32" customHeight="1">
       <c r="A620" s="3" t="n">
@@ -14573,7 +13201,7 @@
         </is>
       </c>
       <c r="F620" s="5" t="n">
-        <v>187.5849</v>
+        <v>962.71</v>
       </c>
     </row>
     <row r="621" ht="18" customHeight="1">
@@ -14594,9 +13222,7 @@
           <t>3.165×1.5-0.2475+0.2242-1.53-0.48+1.2 + [1.5×1.455-0.24+0.2205-0.7122+0.7122]×2 + 3.165×1.5-0.315 = 12.6727</t>
         </is>
       </c>
-      <c r="F621" s="5" t="n">
-        <v>12.6727</v>
-      </c>
+      <c r="F621" s="8" t="n"/>
     </row>
     <row r="622" ht="32" customHeight="1">
       <c r="A622" s="3" t="n"/>
@@ -14616,9 +13242,7 @@
           <t>46.3392-3.1814+4.8397-3.66-5.3027+5.2265 + (3.6×3.16+41.3344)-3.5734+5.486-15.12-3.617+4.337 + 46.8969-4.994+6.5147-3.66-5.5729+5.5078-0.11-0.4277 + 15.26×3.51-1.7901+1.696-22.56-4.5725+4.495 + 20.9313-3.47+4.6402-2.5926+2.5926 + 5.85×3.5-3.4125+4.5985-2.1938+2.1313 = 203.1701</t>
         </is>
       </c>
-      <c r="F622" s="5" t="n">
-        <v>203.1701</v>
-      </c>
+      <c r="F622" s="8" t="n"/>
     </row>
     <row r="623" ht="32" customHeight="1">
       <c r="A623" s="3" t="n"/>
@@ -14638,9 +13262,7 @@
           <t>20.9313-3.47+4.6402-2.5926+2.5926 + 5.85×3.5-3.4125+4.5985-2.1938+2.1313 + 15.26×3.51-1.7901+1.696-22.56-4.5725+4.495 + 46.8969-4.994+6.5147-3.66-5.5729+5.5078-0.11-0.4277 + (3.6×3.16+41.3344)-3.5734+5.486-15.12-3.617+4.337 + 46.3392-3.1814+4.8397-3.66-5.3027+5.2265 = 203.1701</t>
         </is>
       </c>
-      <c r="F623" s="5" t="n">
-        <v>203.1701</v>
-      </c>
+      <c r="F623" s="8" t="n"/>
     </row>
     <row r="624" ht="32" customHeight="1">
       <c r="A624" s="3" t="n"/>
@@ -14660,9 +13282,7 @@
           <t>20.9313-3.47+4.6402-2.5926+2.5926 + 20.528-3.428+4.5985-2.2313+2.1187 + 15.26×3.6-1.836+1.696-22.56-5.9+4.35 + 47.0211-5.0058+6.5137-3.66-5.6854+5.4953-0.11-0.4277 + (3.6×3.16+11.86×3.6)-3.672+5.5-13.59-5.6+4.5 + 46.374-3.201+4.8307-3.66-5.318+5.083 = 203.8336</t>
         </is>
       </c>
-      <c r="F624" s="5" t="n">
-        <v>203.8336</v>
-      </c>
+      <c r="F624" s="8" t="n"/>
     </row>
     <row r="625" ht="18" customHeight="1">
       <c r="A625" s="3" t="n"/>
@@ -14682,9 +13302,7 @@
           <t>3.16×3-0.03+0.029-0.315 + 21.542-0.0295+0.029-0.0525 + 3.16×2.9-0.029+0.0278 + 21.542-0.0295+0.029-3.15-0.4937+0.4937-0.0525 = 58.1547</t>
         </is>
       </c>
-      <c r="F625" s="5" t="n">
-        <v>58.1547</v>
-      </c>
+      <c r="F625" s="8" t="n"/>
     </row>
     <row r="626" ht="32" customHeight="1">
       <c r="A626" s="3" t="n"/>
@@ -14704,18 +13322,12 @@
           <t>(27.6045+0.9108)-0.4932+1.2343-3.15-2.3188+2.194 + (5.61×(1.07+0.12))-0.0107+0.0107 + (15.26×(1.07+0.12))-0.3082+0.2889 + (13.26×(1.07+0.12))-0.0053+0.0053 + (12.563+0.4152)-0.8532+1.272-0.945+0.9765 + (11.86×(1.07+0.12))-0.0053+0.0053 = 94.1189</t>
         </is>
       </c>
-      <c r="F626" s="5" t="n">
-        <v>94.1189</v>
-      </c>
+      <c r="F626" s="8" t="n"/>
     </row>
     <row r="627" ht="18" customHeight="1">
       <c r="A627" s="3" t="n"/>
       <c r="B627" s="3" t="n"/>
-      <c r="C627" s="6" t="inlineStr">
-        <is>
-          <t>小计</t>
-        </is>
-      </c>
+      <c r="C627" s="6" t="n"/>
       <c r="D627" s="7" t="inlineStr">
         <is>
           <t>㎡</t>
@@ -14726,9 +13338,7 @@
           <t>187.5849 + 12.6727 + 203.1701 + 203.1701 + 203.8336 + 58.1547 + 94.1189 = 962.705 ≈ 962.71</t>
         </is>
       </c>
-      <c r="F627" s="8" t="n">
-        <v>962.71</v>
-      </c>
+      <c r="F627" s="8" t="n"/>
     </row>
     <row r="628" ht="18" customHeight="1">
       <c r="A628" s="3" t="n">
@@ -14755,7 +13365,7 @@
         </is>
       </c>
       <c r="F628" s="5" t="n">
-        <v>192.2586</v>
+        <v>908.76</v>
       </c>
     </row>
     <row r="629" ht="32" customHeight="1">
@@ -14776,9 +13386,7 @@
           <t>(3×2.28)+2.7827+0.0141-0.9137-0.0137 + (15.26×1.38)+10.9493+0.0863-2.8487-0.085 + (4.33×3.15)+5.1219+0.0144-1.445-0.0145 + (5.73×2.28+8.73×2.05+11.88×4.45)+26.639+0.0678-7.4369-0.07 + (1.68×0.12+3.16×1.8)+4.661+0.0081-0.9994-0.0077 + (6.48×4.35+3.2×1.68+5.85×3.08)+21.8681+0.059-5.4175-0.062 = 235.7941</t>
         </is>
       </c>
-      <c r="F629" s="5" t="n">
-        <v>235.7941</v>
-      </c>
+      <c r="F629" s="8" t="n"/>
     </row>
     <row r="630" ht="32" customHeight="1">
       <c r="A630" s="3" t="n"/>
@@ -14798,9 +13406,7 @@
           <t>(8.78×5.73+6.5×3+4.45×3.15)+26.639+0.0678-7.4369-0.07 + (4.33×3.15)+5.1219+0.0144-1.445-0.0145 + (15.26×1.38)+10.9492+0.0863-2.8487-0.085 + (3×2.28)+2.7827+0.0141-0.9137-0.0137 + (6.48×4.35+3.2×1.68+5.85×3.08)+21.8681+0.059-5.4175-0.062 + (1.68×0.12+3.16×1.8)+4.661+0.0081-0.9994-0.0077 = 235.7941</t>
         </is>
       </c>
-      <c r="F630" s="5" t="n">
-        <v>235.7941</v>
-      </c>
+      <c r="F630" s="8" t="n"/>
     </row>
     <row r="631" ht="18" customHeight="1">
       <c r="A631" s="3" t="n"/>
@@ -14820,9 +13426,7 @@
           <t>77.2942+18.6475+0.1879-9.1212-0.1917 + (11.35×8.78)+30.8617+0.0536-8.4587-0.0542 + (1.68×0.12+3.16×1.8)+5.8422+0.0081-0.9994-0.0077 = 219.6049</t>
         </is>
       </c>
-      <c r="F631" s="5" t="n">
-        <v>219.6049</v>
-      </c>
+      <c r="F631" s="8" t="n"/>
     </row>
     <row r="632" ht="18" customHeight="1">
       <c r="A632" s="3" t="n"/>
@@ -14842,18 +13446,12 @@
           <t>(7.41×3.16)+2.686+0.0099-0.79-0.0099 = 25.3116</t>
         </is>
       </c>
-      <c r="F632" s="5" t="n">
-        <v>25.3116</v>
-      </c>
+      <c r="F632" s="8" t="n"/>
     </row>
     <row r="633" ht="18" customHeight="1">
       <c r="A633" s="3" t="n"/>
       <c r="B633" s="3" t="n"/>
-      <c r="C633" s="6" t="inlineStr">
-        <is>
-          <t>小计</t>
-        </is>
-      </c>
+      <c r="C633" s="6" t="n"/>
       <c r="D633" s="7" t="inlineStr">
         <is>
           <t>㎡</t>
@@ -14864,54 +13462,82 @@
           <t>192.2586 + 235.7941 + 235.7941 + 219.6049 + 25.3116 = 908.7633 ≈ 908.76</t>
         </is>
       </c>
-      <c r="F633" s="8" t="n">
-        <v>908.76</v>
-      </c>
+      <c r="F633" s="8" t="n"/>
     </row>
   </sheetData>
-  <mergeCells count="143">
+  <mergeCells count="214">
     <mergeCell ref="A223:A269"/>
     <mergeCell ref="B374:B392"/>
     <mergeCell ref="B571:B572"/>
     <mergeCell ref="A144:A146"/>
+    <mergeCell ref="F109:F122"/>
     <mergeCell ref="B529:B533"/>
+    <mergeCell ref="F574:F575"/>
+    <mergeCell ref="F578:F583"/>
+    <mergeCell ref="F3:F4"/>
     <mergeCell ref="A7:A8"/>
+    <mergeCell ref="F584:F585"/>
+    <mergeCell ref="F571:F572"/>
     <mergeCell ref="B123:B125"/>
     <mergeCell ref="B23:B24"/>
     <mergeCell ref="A27:A28"/>
+    <mergeCell ref="F521:F522"/>
     <mergeCell ref="B299:B322"/>
     <mergeCell ref="B463:B467"/>
+    <mergeCell ref="F58:F108"/>
     <mergeCell ref="A534:A536"/>
     <mergeCell ref="A123:A125"/>
     <mergeCell ref="B126:B130"/>
+    <mergeCell ref="F184:F194"/>
+    <mergeCell ref="F270:F298"/>
     <mergeCell ref="A393:A414"/>
+    <mergeCell ref="F169:F183"/>
+    <mergeCell ref="B29:B32"/>
     <mergeCell ref="A620:A627"/>
-    <mergeCell ref="B29:B32"/>
+    <mergeCell ref="F483:F495"/>
     <mergeCell ref="A217:A222"/>
     <mergeCell ref="B540:B541"/>
+    <mergeCell ref="F523:F528"/>
     <mergeCell ref="B421:B441"/>
     <mergeCell ref="A442:A451"/>
     <mergeCell ref="B496:B508"/>
     <mergeCell ref="B458:B462"/>
+    <mergeCell ref="F11:F15"/>
     <mergeCell ref="A586:A591"/>
+    <mergeCell ref="F196:F200"/>
     <mergeCell ref="A323:A333"/>
+    <mergeCell ref="F548:F568"/>
     <mergeCell ref="A544:A547"/>
+    <mergeCell ref="F223:F269"/>
+    <mergeCell ref="F201:F216"/>
     <mergeCell ref="A473:A477"/>
+    <mergeCell ref="F144:F146"/>
     <mergeCell ref="B614:B619"/>
     <mergeCell ref="A165:A168"/>
     <mergeCell ref="A16:A20"/>
+    <mergeCell ref="F33:F57"/>
     <mergeCell ref="A334:A373"/>
+    <mergeCell ref="F334:F373"/>
     <mergeCell ref="B25:B26"/>
     <mergeCell ref="A463:A467"/>
+    <mergeCell ref="F569:F570"/>
+    <mergeCell ref="F458:F462"/>
+    <mergeCell ref="F7:F8"/>
     <mergeCell ref="A584:A585"/>
     <mergeCell ref="A540:A541"/>
+    <mergeCell ref="F598:F605"/>
     <mergeCell ref="B131:B143"/>
+    <mergeCell ref="F452:F457"/>
     <mergeCell ref="B27:B28"/>
     <mergeCell ref="B162:B164"/>
     <mergeCell ref="B509:B510"/>
     <mergeCell ref="B3:B4"/>
     <mergeCell ref="A608:A613"/>
+    <mergeCell ref="F534:F536"/>
     <mergeCell ref="A169:A183"/>
+    <mergeCell ref="F393:F414"/>
+    <mergeCell ref="F5:F6"/>
+    <mergeCell ref="F217:F222"/>
     <mergeCell ref="A628:A633"/>
     <mergeCell ref="A452:A457"/>
     <mergeCell ref="A158:A159"/>
@@ -14920,25 +13546,36 @@
     <mergeCell ref="B442:B451"/>
     <mergeCell ref="B270:B298"/>
     <mergeCell ref="B592:B597"/>
+    <mergeCell ref="F442:F451"/>
     <mergeCell ref="A511:A520"/>
     <mergeCell ref="A574:A575"/>
+    <mergeCell ref="F415:F420"/>
+    <mergeCell ref="F586:F591"/>
+    <mergeCell ref="F323:F333"/>
     <mergeCell ref="A21:A22"/>
     <mergeCell ref="B523:B528"/>
     <mergeCell ref="B537:B539"/>
+    <mergeCell ref="F592:F597"/>
     <mergeCell ref="A548:A568"/>
     <mergeCell ref="B109:B122"/>
+    <mergeCell ref="F9:F10"/>
     <mergeCell ref="A201:A216"/>
     <mergeCell ref="B473:B477"/>
     <mergeCell ref="A542:A543"/>
     <mergeCell ref="B574:B575"/>
     <mergeCell ref="B578:B583"/>
+    <mergeCell ref="F473:F477"/>
     <mergeCell ref="A23:A24"/>
+    <mergeCell ref="F165:F168"/>
     <mergeCell ref="A415:A420"/>
     <mergeCell ref="A569:A570"/>
+    <mergeCell ref="F463:F467"/>
+    <mergeCell ref="F147:F157"/>
     <mergeCell ref="B628:B633"/>
     <mergeCell ref="B158:B159"/>
     <mergeCell ref="A374:A392"/>
     <mergeCell ref="B223:B269"/>
+    <mergeCell ref="F540:F541"/>
     <mergeCell ref="A9:A10"/>
     <mergeCell ref="B58:B108"/>
     <mergeCell ref="B11:B15"/>
@@ -14948,14 +13585,18 @@
     <mergeCell ref="B160:B161"/>
     <mergeCell ref="A521:A522"/>
     <mergeCell ref="B483:B495"/>
+    <mergeCell ref="F608:F613"/>
     <mergeCell ref="A537:A539"/>
     <mergeCell ref="A496:A508"/>
     <mergeCell ref="A576:A577"/>
     <mergeCell ref="A126:A130"/>
     <mergeCell ref="B534:B536"/>
     <mergeCell ref="A109:A122"/>
+    <mergeCell ref="F511:F520"/>
     <mergeCell ref="B542:B543"/>
     <mergeCell ref="A614:A619"/>
+    <mergeCell ref="F21:F22"/>
+    <mergeCell ref="F123:F125"/>
     <mergeCell ref="A571:A572"/>
     <mergeCell ref="A421:A441"/>
     <mergeCell ref="B201:B216"/>
@@ -14963,9 +13604,15 @@
     <mergeCell ref="A529:A533"/>
     <mergeCell ref="B334:B373"/>
     <mergeCell ref="B569:B570"/>
+    <mergeCell ref="F468:F472"/>
+    <mergeCell ref="F542:F543"/>
+    <mergeCell ref="F23:F24"/>
     <mergeCell ref="A147:A157"/>
+    <mergeCell ref="F620:F627"/>
     <mergeCell ref="A483:A495"/>
     <mergeCell ref="B9:B10"/>
+    <mergeCell ref="F606:F607"/>
+    <mergeCell ref="F374:F392"/>
     <mergeCell ref="B544:B547"/>
     <mergeCell ref="B393:B414"/>
     <mergeCell ref="A29:A32"/>
@@ -14973,33 +13620,51 @@
     <mergeCell ref="A131:A143"/>
     <mergeCell ref="A458:A462"/>
     <mergeCell ref="B217:B222"/>
+    <mergeCell ref="F537:F539"/>
+    <mergeCell ref="F544:F547"/>
     <mergeCell ref="A162:A164"/>
+    <mergeCell ref="F496:F508"/>
     <mergeCell ref="A598:A605"/>
     <mergeCell ref="A509:A510"/>
+    <mergeCell ref="F16:F20"/>
+    <mergeCell ref="F299:F322"/>
     <mergeCell ref="A1:F1"/>
     <mergeCell ref="B608:B613"/>
+    <mergeCell ref="F126:F130"/>
     <mergeCell ref="B586:B591"/>
     <mergeCell ref="B323:B333"/>
+    <mergeCell ref="F29:F32"/>
     <mergeCell ref="A33:A57"/>
     <mergeCell ref="B21:B22"/>
     <mergeCell ref="A478:A482"/>
+    <mergeCell ref="F25:F26"/>
+    <mergeCell ref="F421:F441"/>
     <mergeCell ref="A468:A472"/>
     <mergeCell ref="B165:B168"/>
     <mergeCell ref="B511:B520"/>
+    <mergeCell ref="F529:F533"/>
     <mergeCell ref="B33:B57"/>
     <mergeCell ref="B147:B157"/>
+    <mergeCell ref="F628:F633"/>
+    <mergeCell ref="F158:F159"/>
     <mergeCell ref="B196:B200"/>
     <mergeCell ref="A606:A607"/>
     <mergeCell ref="A25:A26"/>
     <mergeCell ref="A3:A4"/>
+    <mergeCell ref="F160:F161"/>
+    <mergeCell ref="F614:F619"/>
     <mergeCell ref="B16:B20"/>
     <mergeCell ref="B606:B607"/>
     <mergeCell ref="A5:A6"/>
+    <mergeCell ref="F131:F143"/>
     <mergeCell ref="B598:B605"/>
+    <mergeCell ref="F27:F28"/>
+    <mergeCell ref="F162:F164"/>
+    <mergeCell ref="A58:A108"/>
     <mergeCell ref="B452:B457"/>
-    <mergeCell ref="A58:A108"/>
     <mergeCell ref="B548:B568"/>
     <mergeCell ref="A184:A194"/>
+    <mergeCell ref="F509:F510"/>
     <mergeCell ref="A578:A583"/>
     <mergeCell ref="A270:A298"/>
     <mergeCell ref="A592:A597"/>
@@ -15007,10 +13672,12 @@
     <mergeCell ref="A299:A322"/>
     <mergeCell ref="B5:B6"/>
     <mergeCell ref="B576:B577"/>
+    <mergeCell ref="F478:F482"/>
     <mergeCell ref="A196:A200"/>
     <mergeCell ref="B468:B472"/>
     <mergeCell ref="B521:B522"/>
     <mergeCell ref="B415:B420"/>
+    <mergeCell ref="F576:F577"/>
     <mergeCell ref="B620:B627"/>
     <mergeCell ref="B584:B585"/>
   </mergeCells>
@@ -15110,7 +13777,7 @@
           <t>m³</t>
         </is>
       </c>
-      <c r="F3" s="11" t="n">
+      <c r="F3" s="8" t="n">
         <v>200.42</v>
       </c>
     </row>
@@ -15139,7 +13806,7 @@
           <t>m³</t>
         </is>
       </c>
-      <c r="F4" s="11" t="n">
+      <c r="F4" s="8" t="n">
         <v>168.3</v>
       </c>
     </row>
@@ -15167,7 +13834,7 @@
           <t>m³</t>
         </is>
       </c>
-      <c r="F5" s="11" t="n">
+      <c r="F5" s="8" t="n">
         <v>192.88</v>
       </c>
     </row>
@@ -15195,7 +13862,7 @@
           <t>m³</t>
         </is>
       </c>
-      <c r="F6" s="11" t="n">
+      <c r="F6" s="8" t="n">
         <v>32.12</v>
       </c>
     </row>
@@ -15226,7 +13893,7 @@
           <t>m³</t>
         </is>
       </c>
-      <c r="F7" s="11" t="n">
+      <c r="F7" s="8" t="n">
         <v>113.02</v>
       </c>
     </row>
@@ -15257,7 +13924,7 @@
           <t>m³</t>
         </is>
       </c>
-      <c r="F8" s="11" t="n">
+      <c r="F8" s="8" t="n">
         <v>16.33</v>
       </c>
     </row>
@@ -15288,7 +13955,7 @@
           <t>m³</t>
         </is>
       </c>
-      <c r="F9" s="11" t="n">
+      <c r="F9" s="8" t="n">
         <v>25.36</v>
       </c>
     </row>
@@ -15318,7 +13985,7 @@
           <t>m³</t>
         </is>
       </c>
-      <c r="F10" s="11" t="n">
+      <c r="F10" s="8" t="n">
         <v>6.83</v>
       </c>
     </row>
@@ -15348,7 +14015,7 @@
           <t>m³</t>
         </is>
       </c>
-      <c r="F11" s="11" t="n">
+      <c r="F11" s="8" t="n">
         <v>17.67</v>
       </c>
     </row>
@@ -15378,7 +14045,7 @@
           <t>m³</t>
         </is>
       </c>
-      <c r="F12" s="11" t="n">
+      <c r="F12" s="8" t="n">
         <v>26.5</v>
       </c>
     </row>
@@ -15408,7 +14075,7 @@
           <t>m³</t>
         </is>
       </c>
-      <c r="F13" s="11" t="n">
+      <c r="F13" s="8" t="n">
         <v>22.71</v>
       </c>
     </row>
@@ -15438,7 +14105,7 @@
           <t>m³</t>
         </is>
       </c>
-      <c r="F14" s="11" t="n">
+      <c r="F14" s="8" t="n">
         <v>35.05</v>
       </c>
     </row>
@@ -15468,7 +14135,7 @@
           <t>m³</t>
         </is>
       </c>
-      <c r="F15" s="11" t="n">
+      <c r="F15" s="8" t="n">
         <v>70.15000000000001</v>
       </c>
     </row>
@@ -15497,7 +14164,7 @@
           <t>m³</t>
         </is>
       </c>
-      <c r="F16" s="11" t="n">
+      <c r="F16" s="8" t="n">
         <v>75.48999999999999</v>
       </c>
     </row>
@@ -15527,7 +14194,7 @@
           <t>m³</t>
         </is>
       </c>
-      <c r="F17" s="11" t="n">
+      <c r="F17" s="8" t="n">
         <v>0.38</v>
       </c>
     </row>
@@ -15557,7 +14224,7 @@
           <t>m³</t>
         </is>
       </c>
-      <c r="F18" s="11" t="n">
+      <c r="F18" s="8" t="n">
         <v>11.14</v>
       </c>
     </row>
@@ -15586,7 +14253,7 @@
           <t>m³</t>
         </is>
       </c>
-      <c r="F19" s="11" t="n">
+      <c r="F19" s="8" t="n">
         <v>6.9</v>
       </c>
     </row>
@@ -15616,7 +14283,7 @@
           <t>m³</t>
         </is>
       </c>
-      <c r="F20" s="11" t="n">
+      <c r="F20" s="8" t="n">
         <v>1.42</v>
       </c>
     </row>
@@ -15645,7 +14312,7 @@
           <t>m³</t>
         </is>
       </c>
-      <c r="F21" s="11" t="n">
+      <c r="F21" s="8" t="n">
         <v>2.37</v>
       </c>
     </row>
@@ -15674,7 +14341,7 @@
           <t>㎡</t>
         </is>
       </c>
-      <c r="F22" s="11" t="n">
+      <c r="F22" s="8" t="n">
         <v>31.76</v>
       </c>
     </row>
@@ -15703,7 +14370,7 @@
           <t>㎡</t>
         </is>
       </c>
-      <c r="F23" s="11" t="n">
+      <c r="F23" s="8" t="n">
         <v>7.64</v>
       </c>
     </row>
@@ -15733,7 +14400,7 @@
           <t>m³</t>
         </is>
       </c>
-      <c r="F24" s="11" t="n">
+      <c r="F24" s="8" t="n">
         <v>2.78</v>
       </c>
     </row>
@@ -15761,7 +14428,7 @@
           <t>t</t>
         </is>
       </c>
-      <c r="F25" s="9" t="n">
+      <c r="F25" s="10" t="n">
         <v>0.709</v>
       </c>
     </row>
@@ -15789,7 +14456,7 @@
           <t>t</t>
         </is>
       </c>
-      <c r="F26" s="9" t="n">
+      <c r="F26" s="10" t="n">
         <v>0.492</v>
       </c>
     </row>
@@ -15817,7 +14484,7 @@
           <t>t</t>
         </is>
       </c>
-      <c r="F27" s="9" t="n">
+      <c r="F27" s="10" t="n">
         <v>0.175</v>
       </c>
     </row>
@@ -15845,7 +14512,7 @@
           <t>t</t>
         </is>
       </c>
-      <c r="F28" s="9" t="n">
+      <c r="F28" s="10" t="n">
         <v>0</v>
       </c>
     </row>
@@ -15873,7 +14540,7 @@
           <t>t</t>
         </is>
       </c>
-      <c r="F29" s="9" t="n">
+      <c r="F29" s="10" t="n">
         <v>0.345</v>
       </c>
     </row>
@@ -15901,7 +14568,7 @@
           <t>t</t>
         </is>
       </c>
-      <c r="F30" s="9" t="n">
+      <c r="F30" s="10" t="n">
         <v>2.989</v>
       </c>
     </row>
@@ -15929,7 +14596,7 @@
           <t>t</t>
         </is>
       </c>
-      <c r="F31" s="9" t="n">
+      <c r="F31" s="10" t="n">
         <v>0.968</v>
       </c>
     </row>
@@ -15957,7 +14624,7 @@
           <t>t</t>
         </is>
       </c>
-      <c r="F32" s="9" t="n">
+      <c r="F32" s="10" t="n">
         <v>0.307</v>
       </c>
     </row>
@@ -15985,7 +14652,7 @@
           <t>t</t>
         </is>
       </c>
-      <c r="F33" s="9" t="n">
+      <c r="F33" s="10" t="n">
         <v>1.428</v>
       </c>
     </row>
@@ -16013,7 +14680,7 @@
           <t>t</t>
         </is>
       </c>
-      <c r="F34" s="9" t="n">
+      <c r="F34" s="10" t="n">
         <v>0.717</v>
       </c>
     </row>
@@ -16041,7 +14708,7 @@
           <t>t</t>
         </is>
       </c>
-      <c r="F35" s="9" t="n">
+      <c r="F35" s="10" t="n">
         <v>0.134</v>
       </c>
     </row>
@@ -16069,7 +14736,7 @@
           <t>t</t>
         </is>
       </c>
-      <c r="F36" s="9" t="n">
+      <c r="F36" s="10" t="n">
         <v>2.347</v>
       </c>
     </row>
@@ -16097,7 +14764,7 @@
           <t>t</t>
         </is>
       </c>
-      <c r="F37" s="9" t="n">
+      <c r="F37" s="10" t="n">
         <v>2.172</v>
       </c>
     </row>
@@ -16125,7 +14792,7 @@
           <t>t</t>
         </is>
       </c>
-      <c r="F38" s="9" t="n">
+      <c r="F38" s="10" t="n">
         <v>2.778</v>
       </c>
     </row>
@@ -16153,7 +14820,7 @@
           <t>t</t>
         </is>
       </c>
-      <c r="F39" s="9" t="n">
+      <c r="F39" s="10" t="n">
         <v>0.319</v>
       </c>
     </row>
@@ -16181,7 +14848,7 @@
           <t>t</t>
         </is>
       </c>
-      <c r="F40" s="9" t="n">
+      <c r="F40" s="10" t="n">
         <v>1.029</v>
       </c>
     </row>
@@ -16209,7 +14876,7 @@
           <t>t</t>
         </is>
       </c>
-      <c r="F41" s="9" t="n">
+      <c r="F41" s="10" t="n">
         <v>2.37</v>
       </c>
     </row>
@@ -16237,7 +14904,7 @@
           <t>t</t>
         </is>
       </c>
-      <c r="F42" s="9" t="n">
+      <c r="F42" s="10" t="n">
         <v>2.808</v>
       </c>
     </row>
@@ -16265,7 +14932,7 @@
           <t>t</t>
         </is>
       </c>
-      <c r="F43" s="9" t="n">
+      <c r="F43" s="10" t="n">
         <v>6.289</v>
       </c>
     </row>
@@ -16293,7 +14960,7 @@
           <t>t</t>
         </is>
       </c>
-      <c r="F44" s="9" t="n">
+      <c r="F44" s="10" t="n">
         <v>0.089</v>
       </c>
     </row>
@@ -16321,7 +14988,7 @@
           <t>t</t>
         </is>
       </c>
-      <c r="F45" s="9" t="n">
+      <c r="F45" s="10" t="n">
         <v>0.209</v>
       </c>
     </row>
@@ -16349,7 +15016,7 @@
           <t>t</t>
         </is>
       </c>
-      <c r="F46" s="9" t="n">
+      <c r="F46" s="10" t="n">
         <v>0.417</v>
       </c>
     </row>
@@ -16377,7 +15044,7 @@
           <t>t</t>
         </is>
       </c>
-      <c r="F47" s="9" t="n">
+      <c r="F47" s="10" t="n">
         <v>0.266</v>
       </c>
     </row>
@@ -16406,7 +15073,7 @@
           <t>t</t>
         </is>
       </c>
-      <c r="F48" s="9" t="n">
+      <c r="F48" s="10" t="n">
         <v>0.08799999999999999</v>
       </c>
     </row>
@@ -16435,7 +15102,7 @@
           <t>t</t>
         </is>
       </c>
-      <c r="F49" s="9" t="n">
+      <c r="F49" s="10" t="n">
         <v>0.357</v>
       </c>
     </row>
@@ -16464,7 +15131,7 @@
           <t>t</t>
         </is>
       </c>
-      <c r="F50" s="9" t="n">
+      <c r="F50" s="10" t="n">
         <v>0</v>
       </c>
     </row>
@@ -16493,7 +15160,7 @@
           <t>t</t>
         </is>
       </c>
-      <c r="F51" s="9" t="n">
+      <c r="F51" s="10" t="n">
         <v>0.044</v>
       </c>
     </row>
@@ -16522,7 +15189,7 @@
           <t>t</t>
         </is>
       </c>
-      <c r="F52" s="9" t="n">
+      <c r="F52" s="10" t="n">
         <v>0.001</v>
       </c>
     </row>
@@ -16551,7 +15218,7 @@
           <t>t</t>
         </is>
       </c>
-      <c r="F53" s="9" t="n">
+      <c r="F53" s="10" t="n">
         <v>0.077</v>
       </c>
     </row>
@@ -16580,7 +15247,7 @@
           <t>t</t>
         </is>
       </c>
-      <c r="F54" s="9" t="n">
+      <c r="F54" s="10" t="n">
         <v>0.146</v>
       </c>
     </row>
@@ -16609,7 +15276,7 @@
           <t>t</t>
         </is>
       </c>
-      <c r="F55" s="9" t="n">
+      <c r="F55" s="10" t="n">
         <v>0.021</v>
       </c>
     </row>
@@ -16638,7 +15305,7 @@
           <t>t</t>
         </is>
       </c>
-      <c r="F56" s="9" t="n">
+      <c r="F56" s="10" t="n">
         <v>0.08400000000000001</v>
       </c>
     </row>
@@ -16667,7 +15334,7 @@
           <t>t</t>
         </is>
       </c>
-      <c r="F57" s="9" t="n">
+      <c r="F57" s="10" t="n">
         <v>0.006</v>
       </c>
     </row>
@@ -16696,7 +15363,7 @@
           <t>t</t>
         </is>
       </c>
-      <c r="F58" s="9" t="n">
+      <c r="F58" s="10" t="n">
         <v>0.263</v>
       </c>
     </row>
@@ -16728,7 +15395,7 @@
           <t>㎡</t>
         </is>
       </c>
-      <c r="F59" s="11" t="n">
+      <c r="F59" s="8" t="n">
         <v>13.83</v>
       </c>
     </row>
@@ -16764,7 +15431,7 @@
           <t>㎡</t>
         </is>
       </c>
-      <c r="F60" s="11" t="n">
+      <c r="F60" s="8" t="n">
         <v>164.64</v>
       </c>
     </row>
@@ -16794,7 +15461,7 @@
           <t>㎡</t>
         </is>
       </c>
-      <c r="F61" s="11" t="n">
+      <c r="F61" s="8" t="n">
         <v>219.3</v>
       </c>
     </row>
@@ -16823,7 +15490,7 @@
           <t>㎡</t>
         </is>
       </c>
-      <c r="F62" s="11" t="n">
+      <c r="F62" s="8" t="n">
         <v>200.13</v>
       </c>
     </row>
@@ -16882,7 +15549,7 @@
           <t>㎡</t>
         </is>
       </c>
-      <c r="F64" s="11" t="n">
+      <c r="F64" s="8" t="n">
         <v>4.58</v>
       </c>
     </row>
@@ -16913,7 +15580,7 @@
           <t>㎡</t>
         </is>
       </c>
-      <c r="F65" s="11" t="n">
+      <c r="F65" s="8" t="n">
         <v>200.13</v>
       </c>
     </row>
@@ -16943,7 +15610,7 @@
           <t>㎡</t>
         </is>
       </c>
-      <c r="F66" s="11" t="n">
+      <c r="F66" s="8" t="n">
         <v>796.17</v>
       </c>
     </row>
@@ -16973,7 +15640,7 @@
           <t>㎡</t>
         </is>
       </c>
-      <c r="F67" s="11" t="n">
+      <c r="F67" s="8" t="n">
         <v>4.58</v>
       </c>
     </row>
@@ -17003,7 +15670,7 @@
           <t>m</t>
         </is>
       </c>
-      <c r="F68" s="11" t="n">
+      <c r="F68" s="8" t="n">
         <v>264.13</v>
       </c>
     </row>
@@ -17033,7 +15700,7 @@
           <t>㎡</t>
         </is>
       </c>
-      <c r="F69" s="11" t="n">
+      <c r="F69" s="8" t="n">
         <v>770.35</v>
       </c>
     </row>
@@ -17063,7 +15730,7 @@
           <t>㎡</t>
         </is>
       </c>
-      <c r="F70" s="11" t="n">
+      <c r="F70" s="8" t="n">
         <v>962.71</v>
       </c>
     </row>
@@ -17096,7 +15763,7 @@
           <t>㎡</t>
         </is>
       </c>
-      <c r="F71" s="11" t="n">
+      <c r="F71" s="8" t="n">
         <v>16.88</v>
       </c>
     </row>
@@ -17126,7 +15793,7 @@
           <t>㎡</t>
         </is>
       </c>
-      <c r="F72" s="11" t="n">
+      <c r="F72" s="8" t="n">
         <v>908.76</v>
       </c>
     </row>
@@ -17156,7 +15823,7 @@
           <t>㎡</t>
         </is>
       </c>
-      <c r="F73" s="11" t="n">
+      <c r="F73" s="8" t="n">
         <v>770.35</v>
       </c>
     </row>
@@ -17186,7 +15853,7 @@
           <t>㎡</t>
         </is>
       </c>
-      <c r="F74" s="11" t="n">
+      <c r="F74" s="8" t="n">
         <v>962.71</v>
       </c>
     </row>
@@ -17217,7 +15884,7 @@
           <t>㎡</t>
         </is>
       </c>
-      <c r="F75" s="11" t="n">
+      <c r="F75" s="8" t="n">
         <v>908.76</v>
       </c>
     </row>
@@ -17254,541 +15921,541 @@
   </cols>
   <sheetData>
     <row r="1">
-      <c r="A1" s="12" t="inlineStr">
+      <c r="A1" s="11" t="inlineStr">
         <is>
           <t>编制说明</t>
         </is>
       </c>
     </row>
     <row r="2">
-      <c r="A2" s="13" t="inlineStr">
+      <c r="A2" s="12" t="inlineStr">
         <is>
           <t>总体</t>
         </is>
       </c>
-      <c r="B2" s="13" t="n"/>
-      <c r="C2" s="13" t="inlineStr">
+      <c r="B2" s="12" t="n"/>
+      <c r="C2" s="12" t="inlineStr">
         <is>
           <t>数据来源：①广联达《绘图输入构件工程量计算书》（基础层~第5层）；②广联达《钢筋明细表》；③清单模板（74 项）。</t>
         </is>
       </c>
     </row>
     <row r="3">
-      <c r="A3" s="13" t="inlineStr">
+      <c r="A3" s="12" t="inlineStr">
         <is>
           <t>总体</t>
         </is>
       </c>
-      <c r="B3" s="13" t="n"/>
-      <c r="C3" s="13" t="inlineStr">
+      <c r="B3" s="12" t="n"/>
+      <c r="C3" s="12" t="inlineStr">
         <is>
           <t>计算书粒度：每层每个构件编号一行，同编号下计算式相同的图元合并为 [计算式]×n；每个清单项末行为小计。</t>
         </is>
       </c>
     </row>
     <row r="4">
-      <c r="A4" s="13" t="inlineStr">
+      <c r="A4" s="12" t="inlineStr">
         <is>
           <t>总体</t>
         </is>
       </c>
-      <c r="B4" s="13" t="n"/>
-      <c r="C4" s="13" t="inlineStr">
+      <c r="B4" s="12" t="n"/>
+      <c r="C4" s="12" t="inlineStr">
         <is>
           <t>计算式已去掉广联达的尖括号注释，仅保留数值式；各图元结果取广联达原值（4 位小数），清单工程量 m³/㎡/m 取 2 位小数，钢筋 t 取 3 位小数。</t>
         </is>
       </c>
     </row>
     <row r="5">
-      <c r="A5" s="13" t="inlineStr">
+      <c r="A5" s="12" t="inlineStr">
         <is>
           <t>总体</t>
         </is>
       </c>
-      <c r="B5" s="13" t="n"/>
-      <c r="C5" s="13" t="inlineStr">
+      <c r="B5" s="12" t="n"/>
+      <c r="C5" s="12" t="inlineStr">
         <is>
           <t>钢筋明细表导出的“级别”列为空，钢筋级别按清单模板“构件类型+直径→级别”对应关系归类；直径 12/14 过梁钢筋按模板标注 HPB300 保留。</t>
         </is>
       </c>
     </row>
     <row r="6">
-      <c r="A6" s="13" t="inlineStr">
+      <c r="A6" s="12" t="inlineStr">
         <is>
           <t>总体</t>
         </is>
       </c>
-      <c r="B6" s="13" t="n"/>
-      <c r="C6" s="13" t="inlineStr">
+      <c r="B6" s="12" t="n"/>
+      <c r="C6" s="12" t="inlineStr">
         <is>
           <t>钢筋校核：钢筋明细表总重 30182.028kg，已全部分配到各钢筋清单项（不含估算的屋面钢筋网片），分配合计 30182.028kg。</t>
         </is>
       </c>
     </row>
     <row r="7">
-      <c r="A7" s="13" t="inlineStr">
+      <c r="A7" s="12" t="inlineStr">
         <is>
           <t>总体</t>
         </is>
       </c>
-      <c r="B7" s="13" t="n"/>
-      <c r="C7" s="13" t="inlineStr">
+      <c r="B7" s="12" t="n"/>
+      <c r="C7" s="12" t="inlineStr">
         <is>
           <t>标注“需补充”的项目在计算书/钢筋表中无依据，需按图纸另行计算。</t>
         </is>
       </c>
     </row>
     <row r="8">
-      <c r="A8" s="13" t="n"/>
-      <c r="B8" s="13" t="n"/>
-      <c r="C8" s="13" t="n"/>
+      <c r="A8" s="12" t="n"/>
+      <c r="B8" s="12" t="n"/>
+      <c r="C8" s="12" t="n"/>
     </row>
     <row r="9">
-      <c r="A9" s="14" t="inlineStr">
+      <c r="A9" s="13" t="inlineStr">
         <is>
           <t>项目编码</t>
         </is>
       </c>
-      <c r="B9" s="14" t="inlineStr">
+      <c r="B9" s="13" t="inlineStr">
         <is>
           <t>项目名称</t>
         </is>
       </c>
-      <c r="C9" s="14" t="inlineStr">
+      <c r="C9" s="13" t="inlineStr">
         <is>
           <t>说明</t>
         </is>
       </c>
     </row>
     <row r="10">
-      <c r="A10" s="13" t="inlineStr">
+      <c r="A10" s="12" t="inlineStr">
         <is>
           <t>010102007001</t>
         </is>
       </c>
-      <c r="B10" s="13" t="inlineStr">
+      <c r="B10" s="12" t="inlineStr">
         <is>
           <t>回填方</t>
         </is>
       </c>
-      <c r="C10" s="13" t="inlineStr">
+      <c r="C10" s="12" t="inlineStr">
         <is>
           <t>按广联达大开挖土方的“素土回填体积”（基坑回填）汇总；房心回填未含。</t>
         </is>
       </c>
     </row>
     <row r="11">
-      <c r="A11" s="13" t="inlineStr">
+      <c r="A11" s="12" t="inlineStr">
         <is>
           <t>010103001001</t>
         </is>
       </c>
-      <c r="B11" s="13" t="inlineStr">
+      <c r="B11" s="12" t="inlineStr">
         <is>
           <t>平整场地</t>
         </is>
       </c>
-      <c r="C11" s="13" t="inlineStr">
+      <c r="C11" s="12" t="inlineStr">
         <is>
           <t>计算书中无平整场地构件，按首层建筑面积计取；清单模板单位为 m³，规范应为 m²，请核对。</t>
         </is>
       </c>
     </row>
     <row r="12">
-      <c r="A12" s="13" t="inlineStr">
+      <c r="A12" s="12" t="inlineStr">
         <is>
           <t>010103002001</t>
         </is>
       </c>
-      <c r="B12" s="13" t="inlineStr">
+      <c r="B12" s="12" t="inlineStr">
         <is>
           <t>余方弃置</t>
         </is>
       </c>
-      <c r="C12" s="13" t="inlineStr">
+      <c r="C12" s="12" t="inlineStr">
         <is>
           <t>余方弃置 = 挖方总量 − 基坑回填总量（推导值）。</t>
         </is>
       </c>
     </row>
     <row r="13">
-      <c r="A13" s="13" t="inlineStr">
+      <c r="A13" s="12" t="inlineStr">
         <is>
           <t>010501002001</t>
         </is>
       </c>
-      <c r="B13" s="13" t="inlineStr">
+      <c r="B13" s="12" t="inlineStr">
         <is>
           <t>楼地面垫层</t>
         </is>
       </c>
-      <c r="C13" s="13" t="inlineStr">
+      <c r="C13" s="12" t="inlineStr">
         <is>
           <t>计算书中无楼地面垫层构件，按首层各房间地面积×0.10m 推导。</t>
         </is>
       </c>
     </row>
     <row r="14">
-      <c r="A14" s="13" t="inlineStr">
+      <c r="A14" s="12" t="inlineStr">
         <is>
           <t>010501002002</t>
         </is>
       </c>
-      <c r="B14" s="13" t="inlineStr">
+      <c r="B14" s="12" t="inlineStr">
         <is>
           <t>楼地面垫层</t>
         </is>
       </c>
-      <c r="C14" s="13" t="inlineStr">
+      <c r="C14" s="12" t="inlineStr">
         <is>
           <t>计算书中无楼地面垫层构件，按首层各房间地面积×0.15m 推导。</t>
         </is>
       </c>
     </row>
     <row r="15">
-      <c r="A15" s="13" t="inlineStr">
+      <c r="A15" s="12" t="inlineStr">
         <is>
           <t>010502006001</t>
         </is>
       </c>
-      <c r="B15" s="13" t="inlineStr">
+      <c r="B15" s="12" t="inlineStr">
         <is>
           <t>钢筋混凝土柱</t>
         </is>
       </c>
-      <c r="C15" s="13" t="inlineStr">
+      <c r="C15" s="12" t="inlineStr">
         <is>
           <t>含各层框架柱 1KZ1~1KZ4 及梯柱 TZ；基础层柱为基础顶至±0.000 段。</t>
         </is>
       </c>
     </row>
     <row r="16">
-      <c r="A16" s="13" t="inlineStr">
+      <c r="A16" s="12" t="inlineStr">
         <is>
           <t>010502011001</t>
         </is>
       </c>
-      <c r="B16" s="13" t="inlineStr">
+      <c r="B16" s="12" t="inlineStr">
         <is>
           <t>钢筋混凝土梁</t>
         </is>
       </c>
-      <c r="C16" s="13" t="inlineStr">
+      <c r="C16" s="12" t="inlineStr">
         <is>
           <t>含基础梁 DKL/DL、各层框架梁 KL/WKL、次梁 L/WL；雨棚梁 YPL 计入“其他板(雨棚板)”。</t>
         </is>
       </c>
     </row>
     <row r="17">
-      <c r="A17" s="13" t="inlineStr">
+      <c r="A17" s="12" t="inlineStr">
         <is>
           <t>010502019001</t>
         </is>
       </c>
-      <c r="B17" s="13" t="inlineStr">
+      <c r="B17" s="12" t="inlineStr">
         <is>
           <t>其他板</t>
         </is>
       </c>
-      <c r="C17" s="13" t="inlineStr">
+      <c r="C17" s="12" t="inlineStr">
         <is>
           <t>广联达模型中未绘制雨棚板本体，仅有雨棚梁 YPL 与雨棚栏板 YP，此处为两者体积之和；雨棚板本体需补充。</t>
         </is>
       </c>
     </row>
     <row r="18">
-      <c r="A18" s="13" t="inlineStr">
+      <c r="A18" s="12" t="inlineStr">
         <is>
           <t>010502020001</t>
         </is>
       </c>
-      <c r="B18" s="13" t="inlineStr">
+      <c r="B18" s="12" t="inlineStr">
         <is>
           <t>楼梯</t>
         </is>
       </c>
-      <c r="C18" s="13" t="inlineStr">
+      <c r="C18" s="12" t="inlineStr">
         <is>
           <t>楼梯按广联达“梯段+梯梁+平台板”体积汇总（清单模板单位为 m³）。</t>
         </is>
       </c>
     </row>
     <row r="19">
-      <c r="A19" s="13" t="inlineStr">
+      <c r="A19" s="12" t="inlineStr">
         <is>
           <t>010506001001</t>
         </is>
       </c>
-      <c r="B19" s="13" t="inlineStr">
+      <c r="B19" s="12" t="inlineStr">
         <is>
           <t>现浇混凝土基础及联系梁钢筋</t>
         </is>
       </c>
-      <c r="C19" s="13" t="inlineStr">
+      <c r="C19" s="12" t="inlineStr">
         <is>
           <t>基础钢筋按独立基础 J-1/J-2/J-3 汇总（均为Φ12）；基础梁 DKL/DL 钢筋计入“现浇混凝土梁钢筋”对应直径。</t>
         </is>
       </c>
     </row>
     <row r="20">
-      <c r="A20" s="13" t="inlineStr">
+      <c r="A20" s="12" t="inlineStr">
         <is>
           <t>010506002003</t>
         </is>
       </c>
-      <c r="B20" s="13" t="inlineStr">
+      <c r="B20" s="12" t="inlineStr">
         <is>
           <t>现浇混凝土柱钢筋</t>
         </is>
       </c>
-      <c r="C20" s="13" t="inlineStr">
+      <c r="C20" s="12" t="inlineStr">
         <is>
           <t>钢筋明细表中柱构件无Φ16钢筋，工程量为 0。</t>
         </is>
       </c>
     </row>
     <row r="21">
-      <c r="A21" s="13" t="inlineStr">
+      <c r="A21" s="12" t="inlineStr">
         <is>
           <t>010506005001</t>
         </is>
       </c>
-      <c r="B21" s="13" t="inlineStr">
+      <c r="B21" s="12" t="inlineStr">
         <is>
           <t>现浇混凝土梁钢筋</t>
         </is>
       </c>
-      <c r="C21" s="13" t="inlineStr">
+      <c r="C21" s="12" t="inlineStr">
         <is>
           <t>含雨棚梁 YPL 钢筋（清单模板“雨蓬”项仅列Φ8）。</t>
         </is>
       </c>
     </row>
     <row r="22">
-      <c r="A22" s="13" t="inlineStr">
+      <c r="A22" s="12" t="inlineStr">
         <is>
           <t>010506005004</t>
         </is>
       </c>
-      <c r="B22" s="13" t="inlineStr">
+      <c r="B22" s="12" t="inlineStr">
         <is>
           <t>现浇混凝土梁钢筋</t>
         </is>
       </c>
-      <c r="C22" s="13" t="inlineStr">
+      <c r="C22" s="12" t="inlineStr">
         <is>
           <t>含雨棚梁 YPL 钢筋（清单模板“雨蓬”项仅列Φ8）。</t>
         </is>
       </c>
     </row>
     <row r="23">
-      <c r="A23" s="13" t="inlineStr">
+      <c r="A23" s="12" t="inlineStr">
         <is>
           <t>010506020001</t>
         </is>
       </c>
-      <c r="B23" s="13" t="inlineStr">
+      <c r="B23" s="12" t="inlineStr">
         <is>
           <t>钢筋网片</t>
         </is>
       </c>
-      <c r="C23" s="13" t="inlineStr">
+      <c r="C23" s="12" t="inlineStr">
         <is>
           <t>钢筋明细表中无屋面网片；按刚性层面积×Φ4@150双向估算：Φ4 单重 0.099kg/m，每 m² 用量 2/0.15×0.099≈1.316kg/m²。</t>
         </is>
       </c>
     </row>
     <row r="24">
-      <c r="A24" s="13" t="inlineStr">
+      <c r="A24" s="12" t="inlineStr">
         <is>
           <t>010902001001</t>
         </is>
       </c>
-      <c r="B24" s="13" t="inlineStr">
+      <c r="B24" s="12" t="inlineStr">
         <is>
           <t>屋面卷材防水</t>
         </is>
       </c>
-      <c r="C24" s="13" t="inlineStr">
+      <c r="C24" s="12" t="inlineStr">
         <is>
           <t>按广联达屋面“防水面积”（含 250 高卷边）汇总。</t>
         </is>
       </c>
     </row>
     <row r="25">
-      <c r="A25" s="13" t="inlineStr">
+      <c r="A25" s="12" t="inlineStr">
         <is>
           <t>010902004001</t>
         </is>
       </c>
-      <c r="B25" s="13" t="inlineStr">
+      <c r="B25" s="12" t="inlineStr">
         <is>
           <t>屋面刚性层</t>
         </is>
       </c>
-      <c r="C25" s="13" t="inlineStr">
+      <c r="C25" s="12" t="inlineStr">
         <is>
           <t>刚性层 = 屋面防水面积 − 卷边面积（水平投影）。</t>
         </is>
       </c>
     </row>
     <row r="26">
-      <c r="A26" s="13" t="inlineStr">
+      <c r="A26" s="12" t="inlineStr">
         <is>
           <t>010902005001</t>
         </is>
       </c>
-      <c r="B26" s="13" t="inlineStr">
+      <c r="B26" s="12" t="inlineStr">
         <is>
           <t>屋面排水管</t>
         </is>
       </c>
-      <c r="C26" s="13" t="inlineStr">
+      <c r="C26" s="12" t="inlineStr">
         <is>
           <t>计算书与钢筋表中均无雨水管信息，无法计取，需按图纸补充（根数×长度）。</t>
         </is>
       </c>
     </row>
     <row r="27">
-      <c r="A27" s="13" t="inlineStr">
+      <c r="A27" s="12" t="inlineStr">
         <is>
           <t>010904002001</t>
         </is>
       </c>
-      <c r="B27" s="13" t="inlineStr">
+      <c r="B27" s="12" t="inlineStr">
         <is>
           <t>楼地面涂膜防水</t>
         </is>
       </c>
-      <c r="C27" s="13" t="inlineStr">
+      <c r="C27" s="12" t="inlineStr">
         <is>
           <t>按首层卫生间地面积计取，未含上翻高度部分。</t>
         </is>
       </c>
     </row>
     <row r="28">
-      <c r="A28" s="13" t="inlineStr">
+      <c r="A28" s="12" t="inlineStr">
         <is>
           <t>011001001001</t>
         </is>
       </c>
-      <c r="B28" s="13" t="inlineStr">
+      <c r="B28" s="12" t="inlineStr">
         <is>
           <t>保温隔热屋面</t>
         </is>
       </c>
-      <c r="C28" s="13" t="inlineStr">
+      <c r="C28" s="12" t="inlineStr">
         <is>
           <t>保温层 = 屋面防水面积 − 卷边面积（水平投影）。</t>
         </is>
       </c>
     </row>
     <row r="29">
-      <c r="A29" s="13" t="inlineStr">
+      <c r="A29" s="12" t="inlineStr">
         <is>
           <t>011101001001</t>
         </is>
       </c>
-      <c r="B29" s="13" t="inlineStr">
+      <c r="B29" s="12" t="inlineStr">
         <is>
           <t>水泥砂浆楼地面</t>
         </is>
       </c>
-      <c r="C29" s="13" t="inlineStr">
+      <c r="C29" s="12" t="inlineStr">
         <is>
           <t>按各层“其他”房间地面积汇总（首层地面一并计入）。</t>
         </is>
       </c>
     </row>
     <row r="30">
-      <c r="A30" s="13" t="inlineStr">
+      <c r="A30" s="12" t="inlineStr">
         <is>
           <t>011105001001</t>
         </is>
       </c>
-      <c r="B30" s="13" t="inlineStr">
+      <c r="B30" s="12" t="inlineStr">
         <is>
           <t>水泥砂浆踢脚线</t>
         </is>
       </c>
-      <c r="C30" s="13" t="inlineStr">
+      <c r="C30" s="12" t="inlineStr">
         <is>
           <t>仅计“其他”房间踢脚；卫生间 2.1m 以下为瓷砖墙裙，不计踢脚。</t>
         </is>
       </c>
     </row>
     <row r="31">
-      <c r="A31" s="13" t="inlineStr">
+      <c r="A31" s="12" t="inlineStr">
         <is>
           <t>011201001002</t>
         </is>
       </c>
-      <c r="B31" s="13" t="inlineStr">
+      <c r="B31" s="12" t="inlineStr">
         <is>
           <t>墙、柱面一般抹灰</t>
         </is>
       </c>
-      <c r="C31" s="13" t="inlineStr">
+      <c r="C31" s="12" t="inlineStr">
         <is>
           <t>含各层房间内墙面（卫生间为墙裙以上部分）及第5层女儿墙内侧/楼梯间墙面。</t>
         </is>
       </c>
     </row>
     <row r="32">
-      <c r="A32" s="13" t="inlineStr">
+      <c r="A32" s="12" t="inlineStr">
         <is>
           <t>011404001001</t>
         </is>
       </c>
-      <c r="B32" s="13" t="inlineStr">
+      <c r="B32" s="12" t="inlineStr">
         <is>
           <t>墙面喷刷涂料</t>
         </is>
       </c>
-      <c r="C32" s="13" t="inlineStr">
+      <c r="C32" s="12" t="inlineStr">
         <is>
           <t>外墙涂料面积 = 外墙一般抹灰面积。</t>
         </is>
       </c>
     </row>
     <row r="33">
-      <c r="A33" s="13" t="inlineStr">
+      <c r="A33" s="12" t="inlineStr">
         <is>
           <t>011404001002</t>
         </is>
       </c>
-      <c r="B33" s="13" t="inlineStr">
+      <c r="B33" s="12" t="inlineStr">
         <is>
           <t>墙面喷刷涂料</t>
         </is>
       </c>
-      <c r="C33" s="13" t="inlineStr">
+      <c r="C33" s="12" t="inlineStr">
         <is>
           <t>内墙涂料面积 = 内墙一般抹灰面积。</t>
         </is>
       </c>
     </row>
     <row r="34">
-      <c r="A34" s="13" t="inlineStr">
+      <c r="A34" s="12" t="inlineStr">
         <is>
           <t>011404002001</t>
         </is>
       </c>
-      <c r="B34" s="13" t="inlineStr">
+      <c r="B34" s="12" t="inlineStr">
         <is>
           <t>天棚喷刷涂料</t>
         </is>
       </c>
-      <c r="C34" s="13" t="inlineStr">
+      <c r="C34" s="12" t="inlineStr">
         <is>
           <t>天棚涂料面积 = 天棚抹灰面积。</t>
         </is>
       </c>
     </row>
     <row r="35">
-      <c r="A35" s="13" t="n"/>
-      <c r="B35" s="13" t="n"/>
-      <c r="C35" s="13" t="n"/>
+      <c r="A35" s="12" t="n"/>
+      <c r="B35" s="12" t="n"/>
+      <c r="C35" s="12" t="n"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/工程量清单/工程量清单及计算书.xlsx
+++ b/工程量清单/工程量清单及计算书.xlsx
@@ -21,8 +21,9 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <numFmts count="1">
-    <numFmt numFmtId="164" formatCode="0.000"/>
+  <numFmts count="2">
+    <numFmt numFmtId="164" formatCode="0.00##"/>
+    <numFmt numFmtId="165" formatCode="0.000"/>
   </numFmts>
   <fonts count="4">
     <font>
@@ -86,7 +87,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="14">
+  <cellXfs count="15">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
@@ -100,7 +101,7 @@
     <xf numFmtId="0" fontId="3" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="2" fontId="2" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="164" fontId="3" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
@@ -109,13 +110,16 @@
     <xf numFmtId="0" fontId="2" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="2" fontId="3" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="164" fontId="2" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="164" fontId="2" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="165" fontId="3" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="164" fontId="3" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="165" fontId="2" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="2" fontId="3" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
@@ -565,7 +569,7 @@
         </is>
       </c>
       <c r="F3" s="5" t="n">
-        <v>200.42</v>
+        <v>200.4156</v>
       </c>
     </row>
     <row r="4" ht="18" customHeight="1">
@@ -582,7 +586,9 @@
           <t>200.4156 ≈ 200.42</t>
         </is>
       </c>
-      <c r="F4" s="8" t="n"/>
+      <c r="F4" s="8" t="n">
+        <v>200.42</v>
+      </c>
     </row>
     <row r="5" ht="46" customHeight="1">
       <c r="A5" s="3" t="n">
@@ -609,7 +615,7 @@
         </is>
       </c>
       <c r="F5" s="5" t="n">
-        <v>168.3</v>
+        <v>168.2978</v>
       </c>
     </row>
     <row r="6" ht="18" customHeight="1">
@@ -626,7 +632,9 @@
           <t>168.2978 ≈ 168.30</t>
         </is>
       </c>
-      <c r="F6" s="8" t="n"/>
+      <c r="F6" s="8" t="n">
+        <v>168.3</v>
+      </c>
     </row>
     <row r="7" ht="18" customHeight="1">
       <c r="A7" s="3" t="n">
@@ -653,7 +661,7 @@
         </is>
       </c>
       <c r="F7" s="5" t="n">
-        <v>192.88</v>
+        <v>192.882</v>
       </c>
     </row>
     <row r="8" ht="18" customHeight="1">
@@ -670,7 +678,9 @@
           <t>192.882 ≈ 192.88</t>
         </is>
       </c>
-      <c r="F8" s="8" t="n"/>
+      <c r="F8" s="8" t="n">
+        <v>192.88</v>
+      </c>
     </row>
     <row r="9" ht="18" customHeight="1">
       <c r="A9" s="3" t="n">
@@ -697,7 +707,7 @@
         </is>
       </c>
       <c r="F9" s="5" t="n">
-        <v>32.12</v>
+        <v>32.1178</v>
       </c>
     </row>
     <row r="10" ht="18" customHeight="1">
@@ -714,7 +724,9 @@
           <t>32.1178 ≈ 32.12</t>
         </is>
       </c>
-      <c r="F10" s="8" t="n"/>
+      <c r="F10" s="8" t="n">
+        <v>32.12</v>
+      </c>
     </row>
     <row r="11" ht="32" customHeight="1">
       <c r="A11" s="3" t="n">
@@ -741,7 +753,7 @@
         </is>
       </c>
       <c r="F11" s="5" t="n">
-        <v>113.02</v>
+        <v>27.0403</v>
       </c>
     </row>
     <row r="12" ht="32" customHeight="1">
@@ -762,7 +774,9 @@
           <t>(13.625×3.6×0.24)-0.8784-0.9936-1.5972-0.096-0.023 + (15.38×3.6×0.24)-3.6288-1.1923-1.1712-0.4992 + (13.5×3.6×0.24)-0.8784-1.3167-1.5313-0.096-0.023 + (15.5×3.6×0.24)-5.4144-1.392-0.648-0.1382-0.0027 = 28.5958</t>
         </is>
       </c>
-      <c r="F12" s="8" t="n"/>
+      <c r="F12" s="5" t="n">
+        <v>28.5958</v>
+      </c>
     </row>
     <row r="13" ht="32" customHeight="1">
       <c r="A13" s="3" t="n"/>
@@ -782,7 +796,9 @@
           <t>(15.5×3.6×0.24)-5.4144-1.392-0.648-0.1382-0.0027 + (13.5×3.6×0.24)-0.8784-1.3167-1.5313-0.096-0.023 + (15.38×3.6×0.24)-3.6288-1.1923-1.1712-0.4992 + (13.625×3.6×0.24)-0.8784-0.9936-1.5972-0.096-0.023 = 28.5958</t>
         </is>
       </c>
-      <c r="F13" s="8" t="n"/>
+      <c r="F13" s="5" t="n">
+        <v>28.5958</v>
+      </c>
     </row>
     <row r="14" ht="32" customHeight="1">
       <c r="A14" s="3" t="n"/>
@@ -802,7 +818,9 @@
           <t>(15.5×3.6×0.24)-5.4144-1.392-0.648-0.1382-0.003 + (13.5×3.6×0.24)-0.8784-1.3167-1.5313-0.096-0.023 + (15.38×3.6×0.24)-3.2616-1.1923-1.344-0.4992 + (13.625×3.6×0.24)-0.8784-0.9936-1.5972-0.096-0.023 = 28.7899</t>
         </is>
       </c>
-      <c r="F14" s="8" t="n"/>
+      <c r="F14" s="5" t="n">
+        <v>28.7899</v>
+      </c>
     </row>
     <row r="15" ht="18" customHeight="1">
       <c r="A15" s="3" t="n"/>
@@ -818,7 +836,9 @@
           <t>27.0403 + 28.5958 + 28.5958 + 28.7899 = 113.0218 ≈ 113.02</t>
         </is>
       </c>
-      <c r="F15" s="8" t="n"/>
+      <c r="F15" s="8" t="n">
+        <v>113.02</v>
+      </c>
     </row>
     <row r="16" ht="18" customHeight="1">
       <c r="A16" s="3" t="n">
@@ -845,7 +865,7 @@
         </is>
       </c>
       <c r="F16" s="5" t="n">
-        <v>16.33</v>
+        <v>5.6237</v>
       </c>
     </row>
     <row r="17" ht="18" customHeight="1">
@@ -866,7 +886,9 @@
           <t>(5.85×3.6×0.24)-0.8424-0.6435 = 3.5685</t>
         </is>
       </c>
-      <c r="F17" s="8" t="n"/>
+      <c r="F17" s="5" t="n">
+        <v>3.5685</v>
+      </c>
     </row>
     <row r="18" ht="18" customHeight="1">
       <c r="A18" s="3" t="n"/>
@@ -886,7 +908,9 @@
           <t>(5.85×3.6×0.24)-0.8424-0.6435 = 3.5685</t>
         </is>
       </c>
-      <c r="F18" s="8" t="n"/>
+      <c r="F18" s="5" t="n">
+        <v>3.5685</v>
+      </c>
     </row>
     <row r="19" ht="18" customHeight="1">
       <c r="A19" s="3" t="n"/>
@@ -906,7 +930,9 @@
           <t>(5.85×3.6×0.24)-0.8424-0.6435 = 3.5685</t>
         </is>
       </c>
-      <c r="F19" s="8" t="n"/>
+      <c r="F19" s="5" t="n">
+        <v>3.5685</v>
+      </c>
     </row>
     <row r="20" ht="18" customHeight="1">
       <c r="A20" s="3" t="n"/>
@@ -922,7 +948,9 @@
           <t>5.6237 + 3.5685 + 3.5685 + 3.5685 = 16.3292 ≈ 16.33</t>
         </is>
       </c>
-      <c r="F20" s="8" t="n"/>
+      <c r="F20" s="8" t="n">
+        <v>16.33</v>
+      </c>
     </row>
     <row r="21" ht="46" customHeight="1">
       <c r="A21" s="3" t="n">
@@ -949,7 +977,7 @@
         </is>
       </c>
       <c r="F21" s="5" t="n">
-        <v>25.36</v>
+        <v>25.3624</v>
       </c>
     </row>
     <row r="22" ht="18" customHeight="1">
@@ -966,7 +994,9 @@
           <t>25.3624 ≈ 25.36</t>
         </is>
       </c>
-      <c r="F22" s="8" t="n"/>
+      <c r="F22" s="8" t="n">
+        <v>25.36</v>
+      </c>
     </row>
     <row r="23" ht="18" customHeight="1">
       <c r="A23" s="3" t="n">
@@ -993,7 +1023,7 @@
         </is>
       </c>
       <c r="F23" s="5" t="n">
-        <v>6.83</v>
+        <v>6.832</v>
       </c>
     </row>
     <row r="24" ht="18" customHeight="1">
@@ -1010,7 +1040,9 @@
           <t>6.832 ≈ 6.83</t>
         </is>
       </c>
-      <c r="F24" s="8" t="n"/>
+      <c r="F24" s="8" t="n">
+        <v>6.83</v>
+      </c>
     </row>
     <row r="25" ht="18" customHeight="1">
       <c r="A25" s="3" t="n">
@@ -1037,7 +1069,7 @@
         </is>
       </c>
       <c r="F25" s="5" t="n">
-        <v>17.67</v>
+        <v>17.6666</v>
       </c>
     </row>
     <row r="26" ht="18" customHeight="1">
@@ -1054,7 +1086,9 @@
           <t>17.6666 ≈ 17.67</t>
         </is>
       </c>
-      <c r="F26" s="8" t="n"/>
+      <c r="F26" s="8" t="n">
+        <v>17.67</v>
+      </c>
     </row>
     <row r="27" ht="18" customHeight="1">
       <c r="A27" s="3" t="n">
@@ -1081,7 +1115,7 @@
         </is>
       </c>
       <c r="F27" s="5" t="n">
-        <v>26.5</v>
+        <v>26.4999</v>
       </c>
     </row>
     <row r="28" ht="18" customHeight="1">
@@ -1098,7 +1132,9 @@
           <t>26.4999 ≈ 26.50</t>
         </is>
       </c>
-      <c r="F28" s="8" t="n"/>
+      <c r="F28" s="8" t="n">
+        <v>26.5</v>
+      </c>
     </row>
     <row r="29" ht="18" customHeight="1">
       <c r="A29" s="3" t="n">
@@ -1125,7 +1161,7 @@
         </is>
       </c>
       <c r="F29" s="5" t="n">
-        <v>22.71</v>
+        <v>8.614000000000001</v>
       </c>
     </row>
     <row r="30" ht="18" customHeight="1">
@@ -1146,7 +1182,9 @@
           <t>[1.5412]×8 = 12.3296</t>
         </is>
       </c>
-      <c r="F30" s="8" t="n"/>
+      <c r="F30" s="5" t="n">
+        <v>12.3296</v>
+      </c>
     </row>
     <row r="31" ht="18" customHeight="1">
       <c r="A31" s="3" t="n"/>
@@ -1166,7 +1204,9 @@
           <t>[0.8837]×2 = 1.7674</t>
         </is>
       </c>
-      <c r="F31" s="8" t="n"/>
+      <c r="F31" s="5" t="n">
+        <v>1.7674</v>
+      </c>
     </row>
     <row r="32" ht="18" customHeight="1">
       <c r="A32" s="3" t="n"/>
@@ -1182,7 +1222,9 @@
           <t>8.614 + 12.3296 + 1.7674 = 22.711 ≈ 22.71</t>
         </is>
       </c>
-      <c r="F32" s="8" t="n"/>
+      <c r="F32" s="8" t="n">
+        <v>22.71</v>
+      </c>
     </row>
     <row r="33" ht="18" customHeight="1">
       <c r="A33" s="3" t="n">
@@ -1209,7 +1251,7 @@
         </is>
       </c>
       <c r="F33" s="5" t="n">
-        <v>35.05</v>
+        <v>0.456</v>
       </c>
     </row>
     <row r="34" ht="18" customHeight="1">
@@ -1230,7 +1272,9 @@
           <t>[(0.35×0.4×1.55)-0.07]×9 = 1.323</t>
         </is>
       </c>
-      <c r="F34" s="8" t="n"/>
+      <c r="F34" s="5" t="n">
+        <v>1.323</v>
+      </c>
     </row>
     <row r="35" ht="18" customHeight="1">
       <c r="A35" s="3" t="n"/>
@@ -1250,7 +1294,9 @@
           <t>(0.4×0.4×1.55)-0.096 = 0.152</t>
         </is>
       </c>
-      <c r="F35" s="8" t="n"/>
+      <c r="F35" s="5" t="n">
+        <v>0.152</v>
+      </c>
     </row>
     <row r="36" ht="18" customHeight="1">
       <c r="A36" s="3" t="n"/>
@@ -1270,7 +1316,9 @@
           <t>(0.35×0.4×1.55)-0.07 = 0.147</t>
         </is>
       </c>
-      <c r="F36" s="8" t="n"/>
+      <c r="F36" s="5" t="n">
+        <v>0.147</v>
+      </c>
     </row>
     <row r="37" ht="18" customHeight="1">
       <c r="A37" s="3" t="n"/>
@@ -1290,7 +1338,9 @@
           <t>[(0.4×0.4×3.6)]×3 = 1.728</t>
         </is>
       </c>
-      <c r="F37" s="8" t="n"/>
+      <c r="F37" s="5" t="n">
+        <v>1.728</v>
+      </c>
     </row>
     <row r="38" ht="18" customHeight="1">
       <c r="A38" s="3" t="n"/>
@@ -1310,7 +1360,9 @@
           <t>[(0.35×0.4×3.6)]×9 = 4.536</t>
         </is>
       </c>
-      <c r="F38" s="8" t="n"/>
+      <c r="F38" s="5" t="n">
+        <v>4.536</v>
+      </c>
     </row>
     <row r="39" ht="18" customHeight="1">
       <c r="A39" s="3" t="n"/>
@@ -1330,7 +1382,9 @@
           <t>(0.4×0.4×3.6) = 0.576</t>
         </is>
       </c>
-      <c r="F39" s="8" t="n"/>
+      <c r="F39" s="5" t="n">
+        <v>0.576</v>
+      </c>
     </row>
     <row r="40" ht="18" customHeight="1">
       <c r="A40" s="3" t="n"/>
@@ -1350,7 +1404,9 @@
           <t>(0.35×0.4×3.6) = 0.504</t>
         </is>
       </c>
-      <c r="F40" s="8" t="n"/>
+      <c r="F40" s="5" t="n">
+        <v>0.504</v>
+      </c>
     </row>
     <row r="41" ht="18" customHeight="1">
       <c r="A41" s="3" t="n"/>
@@ -1370,7 +1426,9 @@
           <t>[(0.25×0.25×3.6)]×4 = 0.9</t>
         </is>
       </c>
-      <c r="F41" s="8" t="n"/>
+      <c r="F41" s="5" t="n">
+        <v>0.9</v>
+      </c>
     </row>
     <row r="42" ht="18" customHeight="1">
       <c r="A42" s="3" t="n"/>
@@ -1390,7 +1448,9 @@
           <t>[(0.4×0.4×3.6)]×3 = 1.728</t>
         </is>
       </c>
-      <c r="F42" s="8" t="n"/>
+      <c r="F42" s="5" t="n">
+        <v>1.728</v>
+      </c>
     </row>
     <row r="43" ht="18" customHeight="1">
       <c r="A43" s="3" t="n"/>
@@ -1410,7 +1470,9 @@
           <t>[(0.35×0.4×3.6)]×9 = 4.536</t>
         </is>
       </c>
-      <c r="F43" s="8" t="n"/>
+      <c r="F43" s="5" t="n">
+        <v>4.536</v>
+      </c>
     </row>
     <row r="44" ht="18" customHeight="1">
       <c r="A44" s="3" t="n"/>
@@ -1430,7 +1492,9 @@
           <t>(0.4×0.4×3.6) = 0.576</t>
         </is>
       </c>
-      <c r="F44" s="8" t="n"/>
+      <c r="F44" s="5" t="n">
+        <v>0.576</v>
+      </c>
     </row>
     <row r="45" ht="18" customHeight="1">
       <c r="A45" s="3" t="n"/>
@@ -1450,7 +1514,9 @@
           <t>(0.35×0.4×3.6) = 0.504</t>
         </is>
       </c>
-      <c r="F45" s="8" t="n"/>
+      <c r="F45" s="5" t="n">
+        <v>0.504</v>
+      </c>
     </row>
     <row r="46" ht="18" customHeight="1">
       <c r="A46" s="3" t="n"/>
@@ -1470,7 +1536,9 @@
           <t>[(0.25×0.25×3.6)]×4 = 0.9</t>
         </is>
       </c>
-      <c r="F46" s="8" t="n"/>
+      <c r="F46" s="5" t="n">
+        <v>0.9</v>
+      </c>
     </row>
     <row r="47" ht="18" customHeight="1">
       <c r="A47" s="3" t="n"/>
@@ -1490,7 +1558,9 @@
           <t>[(0.4×0.4×3.6)]×3 = 1.728</t>
         </is>
       </c>
-      <c r="F47" s="8" t="n"/>
+      <c r="F47" s="5" t="n">
+        <v>1.728</v>
+      </c>
     </row>
     <row r="48" ht="18" customHeight="1">
       <c r="A48" s="3" t="n"/>
@@ -1510,7 +1580,9 @@
           <t>[(0.35×0.4×3.6)]×9 = 4.536</t>
         </is>
       </c>
-      <c r="F48" s="8" t="n"/>
+      <c r="F48" s="5" t="n">
+        <v>4.536</v>
+      </c>
     </row>
     <row r="49" ht="18" customHeight="1">
       <c r="A49" s="3" t="n"/>
@@ -1530,7 +1602,9 @@
           <t>(0.4×0.4×3.6) = 0.576</t>
         </is>
       </c>
-      <c r="F49" s="8" t="n"/>
+      <c r="F49" s="5" t="n">
+        <v>0.576</v>
+      </c>
     </row>
     <row r="50" ht="18" customHeight="1">
       <c r="A50" s="3" t="n"/>
@@ -1550,7 +1624,9 @@
           <t>(0.35×0.4×3.6) = 0.504</t>
         </is>
       </c>
-      <c r="F50" s="8" t="n"/>
+      <c r="F50" s="5" t="n">
+        <v>0.504</v>
+      </c>
     </row>
     <row r="51" ht="18" customHeight="1">
       <c r="A51" s="3" t="n"/>
@@ -1570,7 +1646,9 @@
           <t>[(0.25×0.25×3.6)]×4 = 0.9</t>
         </is>
       </c>
-      <c r="F51" s="8" t="n"/>
+      <c r="F51" s="5" t="n">
+        <v>0.9</v>
+      </c>
     </row>
     <row r="52" ht="18" customHeight="1">
       <c r="A52" s="3" t="n"/>
@@ -1590,7 +1668,9 @@
           <t>[(0.4×0.4×3.6)]×3 = 1.728</t>
         </is>
       </c>
-      <c r="F52" s="8" t="n"/>
+      <c r="F52" s="5" t="n">
+        <v>1.728</v>
+      </c>
     </row>
     <row r="53" ht="18" customHeight="1">
       <c r="A53" s="3" t="n"/>
@@ -1610,7 +1690,9 @@
           <t>[(0.35×0.4×3.6)]×9 = 4.536</t>
         </is>
       </c>
-      <c r="F53" s="8" t="n"/>
+      <c r="F53" s="5" t="n">
+        <v>4.536</v>
+      </c>
     </row>
     <row r="54" ht="18" customHeight="1">
       <c r="A54" s="3" t="n"/>
@@ -1630,7 +1712,9 @@
           <t>(0.4×0.4×3.6) = 0.576</t>
         </is>
       </c>
-      <c r="F54" s="8" t="n"/>
+      <c r="F54" s="5" t="n">
+        <v>0.576</v>
+      </c>
     </row>
     <row r="55" ht="18" customHeight="1">
       <c r="A55" s="3" t="n"/>
@@ -1650,7 +1734,9 @@
           <t>(0.35×0.4×3.6) = 0.504</t>
         </is>
       </c>
-      <c r="F55" s="8" t="n"/>
+      <c r="F55" s="5" t="n">
+        <v>0.504</v>
+      </c>
     </row>
     <row r="56" ht="18" customHeight="1">
       <c r="A56" s="3" t="n"/>
@@ -1670,7 +1756,9 @@
           <t>[(0.25×0.25×3.6)]×4 = 0.9</t>
         </is>
       </c>
-      <c r="F56" s="8" t="n"/>
+      <c r="F56" s="5" t="n">
+        <v>0.9</v>
+      </c>
     </row>
     <row r="57" ht="32" customHeight="1">
       <c r="A57" s="3" t="n"/>
@@ -1686,7 +1774,9 @@
           <t>0.456 + 1.323 + 0.152 + 0.147 + 1.728 + 4.536 + 0.576 + 0.504 + 0.9 + 1.728 + 4.536 + 0.576 + 0.504 + 0.9 + 1.728 + 4.536 + 0.576 + 0.504 + 0.9 + 1.728 + 4.536 + 0.576 + 0.504 + 0.9 = 35.054 ≈ 35.05</t>
         </is>
       </c>
-      <c r="F57" s="8" t="n"/>
+      <c r="F57" s="8" t="n">
+        <v>35.05</v>
+      </c>
     </row>
     <row r="58" ht="18" customHeight="1">
       <c r="A58" s="3" t="n">
@@ -1713,7 +1803,7 @@
         </is>
       </c>
       <c r="F58" s="5" t="n">
-        <v>70.15000000000001</v>
+        <v>2.7183</v>
       </c>
     </row>
     <row r="59" ht="18" customHeight="1">
@@ -1734,7 +1824,9 @@
           <t>(0.3×0.55×12.25)-0.1897 = 1.8315</t>
         </is>
       </c>
-      <c r="F59" s="8" t="n"/>
+      <c r="F59" s="5" t="n">
+        <v>1.8315</v>
+      </c>
     </row>
     <row r="60" ht="18" customHeight="1">
       <c r="A60" s="3" t="n"/>
@@ -1754,7 +1846,9 @@
           <t>(0.25×0.4×8.875)-0.075 + (0.3×0.55×6.575)-0.066 = 1.8314</t>
         </is>
       </c>
-      <c r="F60" s="8" t="n"/>
+      <c r="F60" s="5" t="n">
+        <v>1.8314</v>
+      </c>
     </row>
     <row r="61" ht="18" customHeight="1">
       <c r="A61" s="3" t="n"/>
@@ -1774,7 +1868,9 @@
           <t>(0.25×0.35×3.375)-0.0394-0.0031 = 0.2528</t>
         </is>
       </c>
-      <c r="F61" s="8" t="n"/>
+      <c r="F61" s="5" t="n">
+        <v>0.2528</v>
+      </c>
     </row>
     <row r="62" ht="18" customHeight="1">
       <c r="A62" s="3" t="n"/>
@@ -1794,7 +1890,9 @@
           <t>(0.25×0.4×15.45)-0.145 = 1.4</t>
         </is>
       </c>
-      <c r="F62" s="8" t="n"/>
+      <c r="F62" s="5" t="n">
+        <v>1.4</v>
+      </c>
     </row>
     <row r="63" ht="18" customHeight="1">
       <c r="A63" s="3" t="n"/>
@@ -1814,7 +1912,9 @@
           <t>(0.25×0.35×3.4)-0.0284 = 0.2691</t>
         </is>
       </c>
-      <c r="F63" s="8" t="n"/>
+      <c r="F63" s="5" t="n">
+        <v>0.2691</v>
+      </c>
     </row>
     <row r="64" ht="18" customHeight="1">
       <c r="A64" s="3" t="n"/>
@@ -1834,7 +1934,9 @@
           <t>[(0.25×0.4×1.7)-0.02]×2 + (0.25×0.55×12.25)-0.1581 + (0.25×0.55×12.05)-0.1991-0.0009 = 3.2832</t>
         </is>
       </c>
-      <c r="F64" s="8" t="n"/>
+      <c r="F64" s="5" t="n">
+        <v>3.2832</v>
+      </c>
     </row>
     <row r="65" ht="18" customHeight="1">
       <c r="A65" s="3" t="n"/>
@@ -1854,7 +1956,9 @@
           <t>[(0.25×0.4×1.7)-0.02]×2 + (0.25×0.55×12.25)-0.165 + (0.25×0.55×12.05)-0.1375 = 3.3388</t>
         </is>
       </c>
-      <c r="F65" s="8" t="n"/>
+      <c r="F65" s="5" t="n">
+        <v>3.3388</v>
+      </c>
     </row>
     <row r="66" ht="18" customHeight="1">
       <c r="A66" s="3" t="n"/>
@@ -1874,7 +1978,9 @@
           <t>(0.25×0.4×1.625)-0.0125 + (0.25×0.55×12.125)-0.1787-0.0172 = 1.6213</t>
         </is>
       </c>
-      <c r="F66" s="8" t="n"/>
+      <c r="F66" s="5" t="n">
+        <v>1.6213</v>
+      </c>
     </row>
     <row r="67" ht="18" customHeight="1">
       <c r="A67" s="3" t="n"/>
@@ -1894,7 +2000,9 @@
           <t>(0.25×0.4×8.9)-0.0775 + (0.25×0.65×6.85)-0.1097 = 1.8159</t>
         </is>
       </c>
-      <c r="F67" s="8" t="n"/>
+      <c r="F67" s="5" t="n">
+        <v>1.8159</v>
+      </c>
     </row>
     <row r="68" ht="18" customHeight="1">
       <c r="A68" s="3" t="n"/>
@@ -1914,7 +2022,9 @@
           <t>(0.25×0.4×15.5)-0.175 = 1.375</t>
         </is>
       </c>
-      <c r="F68" s="8" t="n"/>
+      <c r="F68" s="5" t="n">
+        <v>1.375</v>
+      </c>
     </row>
     <row r="69" ht="18" customHeight="1">
       <c r="A69" s="3" t="n"/>
@@ -1934,7 +2044,9 @@
           <t>(0.25×0.4×15.5)-0.15 = 1.4</t>
         </is>
       </c>
-      <c r="F69" s="8" t="n"/>
+      <c r="F69" s="5" t="n">
+        <v>1.4</v>
+      </c>
     </row>
     <row r="70" ht="18" customHeight="1">
       <c r="A70" s="3" t="n"/>
@@ -1954,7 +2066,9 @@
           <t>(0.25×0.4×8.9)-0.05 + (0.25×0.4×3.2)-0.025 + (0.25×0.4×3.4)-0.025 = 1.45</t>
         </is>
       </c>
-      <c r="F70" s="8" t="n"/>
+      <c r="F70" s="5" t="n">
+        <v>1.45</v>
+      </c>
     </row>
     <row r="71" ht="18" customHeight="1">
       <c r="A71" s="3" t="n"/>
@@ -1974,7 +2088,9 @@
           <t>(0.25×0.4×1.7)-0.02 + (0.25×0.55×12.25)-0.1581 = 1.6763</t>
         </is>
       </c>
-      <c r="F71" s="8" t="n"/>
+      <c r="F71" s="5" t="n">
+        <v>1.6763</v>
+      </c>
     </row>
     <row r="72" ht="18" customHeight="1">
       <c r="A72" s="3" t="n"/>
@@ -1994,7 +2110,9 @@
           <t>(0.25×0.4×1.7)-0.02 + (0.25×0.55×12.25)-0.165 = 1.6694</t>
         </is>
       </c>
-      <c r="F72" s="8" t="n"/>
+      <c r="F72" s="5" t="n">
+        <v>1.6694</v>
+      </c>
     </row>
     <row r="73" ht="18" customHeight="1">
       <c r="A73" s="3" t="n"/>
@@ -2014,7 +2132,9 @@
           <t>(0.25×0.4×1.7)-0.02 + (0.25×0.55×12.05)-0.1375 = 1.6694</t>
         </is>
       </c>
-      <c r="F73" s="8" t="n"/>
+      <c r="F73" s="5" t="n">
+        <v>1.6694</v>
+      </c>
     </row>
     <row r="74" ht="18" customHeight="1">
       <c r="A74" s="3" t="n"/>
@@ -2034,7 +2154,9 @@
           <t>(0.25×0.4×1.625)-0.0125 + (0.25×0.55×12.125)-0.1787-0.0172 = 1.6213</t>
         </is>
       </c>
-      <c r="F74" s="8" t="n"/>
+      <c r="F74" s="5" t="n">
+        <v>1.6213</v>
+      </c>
     </row>
     <row r="75" ht="18" customHeight="1">
       <c r="A75" s="3" t="n"/>
@@ -2054,7 +2176,9 @@
           <t>(0.25×0.4×1.7)-0.02 + (0.25×0.55×12.05)-0.1986-0.0006 = 1.6077</t>
         </is>
       </c>
-      <c r="F75" s="8" t="n"/>
+      <c r="F75" s="5" t="n">
+        <v>1.6077</v>
+      </c>
     </row>
     <row r="76" ht="18" customHeight="1">
       <c r="A76" s="3" t="n"/>
@@ -2074,7 +2198,9 @@
           <t>(0.25×0.4×8.9)-0.0775 + (0.25×0.65×6.85)-0.1097 = 1.8159</t>
         </is>
       </c>
-      <c r="F76" s="8" t="n"/>
+      <c r="F76" s="5" t="n">
+        <v>1.8159</v>
+      </c>
     </row>
     <row r="77" ht="18" customHeight="1">
       <c r="A77" s="3" t="n"/>
@@ -2094,7 +2220,9 @@
           <t>(0.25×0.4×15.5)-0.175 = 1.375</t>
         </is>
       </c>
-      <c r="F77" s="8" t="n"/>
+      <c r="F77" s="5" t="n">
+        <v>1.375</v>
+      </c>
     </row>
     <row r="78" ht="18" customHeight="1">
       <c r="A78" s="3" t="n"/>
@@ -2114,7 +2242,9 @@
           <t>(0.25×0.4×15.5)-0.15 = 1.4</t>
         </is>
       </c>
-      <c r="F78" s="8" t="n"/>
+      <c r="F78" s="5" t="n">
+        <v>1.4</v>
+      </c>
     </row>
     <row r="79" ht="18" customHeight="1">
       <c r="A79" s="3" t="n"/>
@@ -2134,7 +2264,9 @@
           <t>(0.25×0.3×3)-0.0188 = 0.2062</t>
         </is>
       </c>
-      <c r="F79" s="8" t="n"/>
+      <c r="F79" s="5" t="n">
+        <v>0.2062</v>
+      </c>
     </row>
     <row r="80" ht="18" customHeight="1">
       <c r="A80" s="3" t="n"/>
@@ -2154,7 +2286,9 @@
           <t>(0.25×0.4×15.5)-0.1 = 1.45</t>
         </is>
       </c>
-      <c r="F80" s="8" t="n"/>
+      <c r="F80" s="5" t="n">
+        <v>1.45</v>
+      </c>
     </row>
     <row r="81" ht="18" customHeight="1">
       <c r="A81" s="3" t="n"/>
@@ -2174,7 +2308,9 @@
           <t>(0.25×0.4×4.45)-0.025 = 0.42</t>
         </is>
       </c>
-      <c r="F81" s="8" t="n"/>
+      <c r="F81" s="5" t="n">
+        <v>0.42</v>
+      </c>
     </row>
     <row r="82" ht="18" customHeight="1">
       <c r="A82" s="3" t="n"/>
@@ -2194,7 +2330,9 @@
           <t>(0.25×0.3×2.05)-0.0188 = 0.135</t>
         </is>
       </c>
-      <c r="F82" s="8" t="n"/>
+      <c r="F82" s="5" t="n">
+        <v>0.135</v>
+      </c>
     </row>
     <row r="83" ht="18" customHeight="1">
       <c r="A83" s="3" t="n"/>
@@ -2214,7 +2352,9 @@
           <t>(0.25×0.35×3.4)-0.0219 + (0.25×0.35×3.2)-0.0219 = 0.5337</t>
         </is>
       </c>
-      <c r="F83" s="8" t="n"/>
+      <c r="F83" s="5" t="n">
+        <v>0.5337</v>
+      </c>
     </row>
     <row r="84" ht="18" customHeight="1">
       <c r="A84" s="3" t="n"/>
@@ -2234,7 +2374,9 @@
           <t>(0.25×0.4×1.7)-0.02 + (0.25×0.55×12.25)-0.1581 = 1.6763</t>
         </is>
       </c>
-      <c r="F84" s="8" t="n"/>
+      <c r="F84" s="5" t="n">
+        <v>1.6763</v>
+      </c>
     </row>
     <row r="85" ht="18" customHeight="1">
       <c r="A85" s="3" t="n"/>
@@ -2254,7 +2396,9 @@
           <t>(0.25×0.4×1.7)-0.02 + (0.25×0.55×12.25)-0.165 = 1.6694</t>
         </is>
       </c>
-      <c r="F85" s="8" t="n"/>
+      <c r="F85" s="5" t="n">
+        <v>1.6694</v>
+      </c>
     </row>
     <row r="86" ht="18" customHeight="1">
       <c r="A86" s="3" t="n"/>
@@ -2274,7 +2418,9 @@
           <t>(0.25×0.4×1.7)-0.02 + (0.25×0.55×12.05)-0.1375 = 1.6694</t>
         </is>
       </c>
-      <c r="F86" s="8" t="n"/>
+      <c r="F86" s="5" t="n">
+        <v>1.6694</v>
+      </c>
     </row>
     <row r="87" ht="18" customHeight="1">
       <c r="A87" s="3" t="n"/>
@@ -2294,7 +2440,9 @@
           <t>(0.25×0.4×1.625)-0.0125 + (0.25×0.55×12.125)-0.1787-0.0172 = 1.6213</t>
         </is>
       </c>
-      <c r="F87" s="8" t="n"/>
+      <c r="F87" s="5" t="n">
+        <v>1.6213</v>
+      </c>
     </row>
     <row r="88" ht="18" customHeight="1">
       <c r="A88" s="3" t="n"/>
@@ -2314,7 +2462,9 @@
           <t>(0.25×0.4×1.7)-0.02 + (0.25×0.55×12.05)-0.1986-0.0006 = 1.6077</t>
         </is>
       </c>
-      <c r="F88" s="8" t="n"/>
+      <c r="F88" s="5" t="n">
+        <v>1.6077</v>
+      </c>
     </row>
     <row r="89" ht="18" customHeight="1">
       <c r="A89" s="3" t="n"/>
@@ -2334,7 +2484,9 @@
           <t>(0.25×0.4×8.9)-0.0775 + (0.25×0.65×6.85)-0.1097 = 1.8159</t>
         </is>
       </c>
-      <c r="F89" s="8" t="n"/>
+      <c r="F89" s="5" t="n">
+        <v>1.8159</v>
+      </c>
     </row>
     <row r="90" ht="18" customHeight="1">
       <c r="A90" s="3" t="n"/>
@@ -2354,7 +2506,9 @@
           <t>(0.25×0.4×15.5)-0.175 = 1.375</t>
         </is>
       </c>
-      <c r="F90" s="8" t="n"/>
+      <c r="F90" s="5" t="n">
+        <v>1.375</v>
+      </c>
     </row>
     <row r="91" ht="18" customHeight="1">
       <c r="A91" s="3" t="n"/>
@@ -2374,7 +2528,9 @@
           <t>(0.25×0.4×15.5)-0.15 = 1.4</t>
         </is>
       </c>
-      <c r="F91" s="8" t="n"/>
+      <c r="F91" s="5" t="n">
+        <v>1.4</v>
+      </c>
     </row>
     <row r="92" ht="18" customHeight="1">
       <c r="A92" s="3" t="n"/>
@@ -2394,7 +2550,9 @@
           <t>(0.25×0.3×3)-0.0188 = 0.2062</t>
         </is>
       </c>
-      <c r="F92" s="8" t="n"/>
+      <c r="F92" s="5" t="n">
+        <v>0.2062</v>
+      </c>
     </row>
     <row r="93" ht="18" customHeight="1">
       <c r="A93" s="3" t="n"/>
@@ -2414,7 +2572,9 @@
           <t>(0.25×0.4×15.5)-0.1 = 1.45</t>
         </is>
       </c>
-      <c r="F93" s="8" t="n"/>
+      <c r="F93" s="5" t="n">
+        <v>1.45</v>
+      </c>
     </row>
     <row r="94" ht="18" customHeight="1">
       <c r="A94" s="3" t="n"/>
@@ -2434,7 +2594,9 @@
           <t>(0.25×0.4×4.45)-0.025 = 0.42</t>
         </is>
       </c>
-      <c r="F94" s="8" t="n"/>
+      <c r="F94" s="5" t="n">
+        <v>0.42</v>
+      </c>
     </row>
     <row r="95" ht="18" customHeight="1">
       <c r="A95" s="3" t="n"/>
@@ -2454,7 +2616,9 @@
           <t>(0.25×0.3×2.05)-0.0188 = 0.135</t>
         </is>
       </c>
-      <c r="F95" s="8" t="n"/>
+      <c r="F95" s="5" t="n">
+        <v>0.135</v>
+      </c>
     </row>
     <row r="96" ht="18" customHeight="1">
       <c r="A96" s="3" t="n"/>
@@ -2474,7 +2638,9 @@
           <t>(0.25×0.35×3.2)-0.0219 + (0.25×0.35×3.4)-0.0219 = 0.5337</t>
         </is>
       </c>
-      <c r="F96" s="8" t="n"/>
+      <c r="F96" s="5" t="n">
+        <v>0.5337</v>
+      </c>
     </row>
     <row r="97" ht="18" customHeight="1">
       <c r="A97" s="3" t="n"/>
@@ -2494,7 +2660,9 @@
           <t>[(0.25×0.4×1.7)-0.02]×2 + (0.25×0.55×12.25)-0.1581 + (0.25×0.55×12.05)-0.1986-0.0006 = 3.284</t>
         </is>
       </c>
-      <c r="F97" s="8" t="n"/>
+      <c r="F97" s="5" t="n">
+        <v>3.284</v>
+      </c>
     </row>
     <row r="98" ht="18" customHeight="1">
       <c r="A98" s="3" t="n"/>
@@ -2514,7 +2682,9 @@
           <t>[(0.25×0.4×1.7)-0.02]×2 + (0.25×0.55×12.25)-0.165 + (0.25×0.55×12.05)-0.1375 = 3.3388</t>
         </is>
       </c>
-      <c r="F98" s="8" t="n"/>
+      <c r="F98" s="5" t="n">
+        <v>3.3388</v>
+      </c>
     </row>
     <row r="99" ht="18" customHeight="1">
       <c r="A99" s="3" t="n"/>
@@ -2534,7 +2704,9 @@
           <t>(0.25×0.4×1.625)-0.0125 + (0.25×0.55×12.125)-0.1787-0.0172 = 1.6213</t>
         </is>
       </c>
-      <c r="F99" s="8" t="n"/>
+      <c r="F99" s="5" t="n">
+        <v>1.6213</v>
+      </c>
     </row>
     <row r="100" ht="18" customHeight="1">
       <c r="A100" s="3" t="n"/>
@@ -2554,7 +2726,9 @@
           <t>(0.25×0.4×8.9)-0.0775 + (0.25×0.65×6.85)-0.1097 = 1.8159</t>
         </is>
       </c>
-      <c r="F100" s="8" t="n"/>
+      <c r="F100" s="5" t="n">
+        <v>1.8159</v>
+      </c>
     </row>
     <row r="101" ht="18" customHeight="1">
       <c r="A101" s="3" t="n"/>
@@ -2574,7 +2748,9 @@
           <t>(0.25×0.4×15.5)-0.175 = 1.375</t>
         </is>
       </c>
-      <c r="F101" s="8" t="n"/>
+      <c r="F101" s="5" t="n">
+        <v>1.375</v>
+      </c>
     </row>
     <row r="102" ht="18" customHeight="1">
       <c r="A102" s="3" t="n"/>
@@ -2594,7 +2770,9 @@
           <t>(0.25×0.4×15.5)-0.15 = 1.4</t>
         </is>
       </c>
-      <c r="F102" s="8" t="n"/>
+      <c r="F102" s="5" t="n">
+        <v>1.4</v>
+      </c>
     </row>
     <row r="103" ht="18" customHeight="1">
       <c r="A103" s="3" t="n"/>
@@ -2614,7 +2792,9 @@
           <t>(0.25×0.4×15.5)-0.1 = 1.45</t>
         </is>
       </c>
-      <c r="F103" s="8" t="n"/>
+      <c r="F103" s="5" t="n">
+        <v>1.45</v>
+      </c>
     </row>
     <row r="104" ht="18" customHeight="1">
       <c r="A104" s="3" t="n"/>
@@ -2634,7 +2814,9 @@
           <t>(0.25×0.35×3.4)-0.0219 = 0.2756</t>
         </is>
       </c>
-      <c r="F104" s="8" t="n"/>
+      <c r="F104" s="5" t="n">
+        <v>0.2756</v>
+      </c>
     </row>
     <row r="105" ht="18" customHeight="1">
       <c r="A105" s="3" t="n"/>
@@ -2654,7 +2836,9 @@
           <t>(0.25×0.4×12.1)-0.075 = 1.135</t>
         </is>
       </c>
-      <c r="F105" s="8" t="n"/>
+      <c r="F105" s="5" t="n">
+        <v>1.135</v>
+      </c>
     </row>
     <row r="106" ht="18" customHeight="1">
       <c r="A106" s="3" t="n"/>
@@ -2674,7 +2858,9 @@
           <t>(0.25×0.4×3.4) = 0.34</t>
         </is>
       </c>
-      <c r="F106" s="8" t="n"/>
+      <c r="F106" s="5" t="n">
+        <v>0.34</v>
+      </c>
     </row>
     <row r="107" ht="18" customHeight="1">
       <c r="A107" s="3" t="n"/>
@@ -2694,7 +2880,9 @@
           <t>(0.25×0.4×3.65) = 0.365</t>
         </is>
       </c>
-      <c r="F107" s="8" t="n"/>
+      <c r="F107" s="5" t="n">
+        <v>0.365</v>
+      </c>
     </row>
     <row r="108" ht="46" customHeight="1">
       <c r="A108" s="3" t="n"/>
@@ -2710,7 +2898,9 @@
           <t>2.7183 + 1.8315 + 1.8314 + 0.2528 + 1.4 + 0.2691 + 3.2832 + 3.3388 + 1.6213 + 1.8159 + 1.375 + 1.4 + 1.45 + 1.6763 + 1.6694 + 1.6694 + 1.6213 + 1.6077 + 1.8159 + 1.375 + 1.4 + 0.2062 + 1.45 + 0.42 + 0.135 + 0.5337 + 1.6763 + 1.6694 + 1.6694 + 1.6213 + 1.6077 + 1.8159 + 1.375 + 1.4 + 0.2062 + 1.45 + 0.42 + 0.135 + 0.5337 + 3.284 + 3.3388 + 1.6213 + 1.8159 + 1.375 + 1.4 + 1.45 + 0.2756 + 1.135 + 0.34 + 0.365 = 70.1477 ≈ 70.15</t>
         </is>
       </c>
-      <c r="F108" s="8" t="n"/>
+      <c r="F108" s="8" t="n">
+        <v>70.15000000000001</v>
+      </c>
     </row>
     <row r="109" ht="18" customHeight="1">
       <c r="A109" s="3" t="n">
@@ -2737,7 +2927,7 @@
         </is>
       </c>
       <c r="F109" s="5" t="n">
-        <v>75.48999999999999</v>
+        <v>5.2434</v>
       </c>
     </row>
     <row r="110" ht="32" customHeight="1">
@@ -2758,7 +2948,9 @@
           <t>((5.85×4.45)×0.12)-0.0238-0.282 + ((5.85×4.45)×0.12)-0.0211-0.2835 + ((6.15×4.45)×0.12)-0.022-0.2921 + ((6.15×4.45)×0.12)-0.0238-0.291 + ((3.4×1.945)×0.12)-0.0181-0.1382-0.0172 = 12.1968</t>
         </is>
       </c>
-      <c r="F110" s="8" t="n"/>
+      <c r="F110" s="5" t="n">
+        <v>12.1968</v>
+      </c>
     </row>
     <row r="111" ht="18" customHeight="1">
       <c r="A111" s="3" t="n"/>
@@ -2778,7 +2970,9 @@
           <t>((3.4×1.5)×0.09)-0.0025-0.1021 + ((3.2×1.5)×0.09)-0.0023-0.0979 + ((4.45×1.5)×0.09)-0.0042-0.124 + ((4.45×1.5)×0.09)-0.0045-0.1237 = 1.6313</t>
         </is>
       </c>
-      <c r="F111" s="8" t="n"/>
+      <c r="F111" s="5" t="n">
+        <v>1.6313</v>
+      </c>
     </row>
     <row r="112" ht="32" customHeight="1">
       <c r="A112" s="3" t="n"/>
@@ -2798,7 +2992,9 @@
           <t>((4.45×3.15)×0.1)-0.011-0.175 + ((6.15×3.2)×0.1)-0.0135-0.2162 + ((4.35×3.4)×0.1)-0.0062-0.1828 + ((3.2×2.4)×0.1)-0.0111-0.1237 + ((3.45×3.2)×0.1)-0.0127-0.1488 = 5.8196</t>
         </is>
       </c>
-      <c r="F112" s="8" t="n"/>
+      <c r="F112" s="5" t="n">
+        <v>5.8196</v>
+      </c>
     </row>
     <row r="113" ht="32" customHeight="1">
       <c r="A113" s="3" t="n"/>
@@ -2818,7 +3014,9 @@
           <t>((5.85×4.45)×0.12)-0.0238-0.282 + ((5.85×4.45)×0.12)-0.0211-0.2835 + ((2.05×1.8)×0.12)-0.0048-0.1039 + ((2.05×1.2)×0.12)-0.09 + ((6.15×4.45)×0.12)-0.022-0.2921 = 9.1466</t>
         </is>
       </c>
-      <c r="F113" s="8" t="n"/>
+      <c r="F113" s="5" t="n">
+        <v>9.146599999999999</v>
+      </c>
     </row>
     <row r="114" ht="32" customHeight="1">
       <c r="A114" s="3" t="n"/>
@@ -2838,7 +3036,9 @@
           <t>((3×2.4)×0.09)-0.0043-0.1122 + ((3.4×1.8)×0.09)-0.0079-0.1046 + ((3.2×1.5)×0.09)-0.0023-0.0979 + ((3.4×1.5)×0.09)-0.0025-0.1021 + ((4.45×1.5)×0.09)-0.0042-0.124 + ((4.45×1.5)×0.09)-0.0045-0.1237 + ((3.4×1.31)×0.09)-0.0107-0.0918 = 2.8992</t>
         </is>
       </c>
-      <c r="F114" s="8" t="n"/>
+      <c r="F114" s="5" t="n">
+        <v>2.8992</v>
+      </c>
     </row>
     <row r="115" ht="32" customHeight="1">
       <c r="A115" s="3" t="n"/>
@@ -2858,7 +3058,9 @@
           <t>((3.2×2.4)×0.1)-0.0111-0.1237 + ((6.15×3.2)×0.1)-0.0135-0.2162 + ((3.45×3.2)×0.1)-0.0127-0.1488 + ((4.35×3.4)×0.1)-0.0062-0.1828 + ((4.45×3.15)×0.1)-0.011-0.175 = 5.8196</t>
         </is>
       </c>
-      <c r="F115" s="8" t="n"/>
+      <c r="F115" s="5" t="n">
+        <v>5.8196</v>
+      </c>
     </row>
     <row r="116" ht="32" customHeight="1">
       <c r="A116" s="3" t="n"/>
@@ -2878,7 +3080,9 @@
           <t>((6.15×4.45)×0.12)-0.022-0.2921 + ((2.05×1.2)×0.12)-0.09 + ((5.85×4.45)×0.12)-0.0238-0.282 + ((2.05×1.8)×0.12)-0.0048-0.1039 + ((5.85×4.45)×0.12)-0.0211-0.2835 = 9.1466</t>
         </is>
       </c>
-      <c r="F116" s="8" t="n"/>
+      <c r="F116" s="5" t="n">
+        <v>9.146599999999999</v>
+      </c>
     </row>
     <row r="117" ht="32" customHeight="1">
       <c r="A117" s="3" t="n"/>
@@ -2898,7 +3102,9 @@
           <t>((4.45×1.5)×0.09)-0.0045-0.1237 + ((4.45×1.5)×0.09)-0.0042-0.124 + ((3.4×1.5)×0.09)-0.0025-0.1021 + ((3.2×1.5)×0.09)-0.0023-0.0979 + ((3.4×1.8)×0.09)-0.0079-0.1046 + ((3×2.4)×0.09)-0.0043-0.1122 + ((3.4×1.31)×0.09)-0.0107-0.0918 = 2.8992</t>
         </is>
       </c>
-      <c r="F117" s="8" t="n"/>
+      <c r="F117" s="5" t="n">
+        <v>2.8992</v>
+      </c>
     </row>
     <row r="118" ht="46" customHeight="1">
       <c r="A118" s="3" t="n"/>
@@ -2918,7 +3124,9 @@
           <t>((4.45×0.65)×0.1)-0.011-0.1125 + ((4.45×0.65)×0.1)-0.0096-0.1131 + ((3.2×0.65)×0.1)-0.0096-0.0819 + ((5.2×3.2)×0.1)-0.0142-0.1906 + ((6.15×3.2)×0.1)-0.0135-0.2163 + ((4.35×3.4)×0.1)-0.0062-0.1828 + ((3.4×1.5)×0.1)-0.0028-0.1134 + ((3.2×1.5)×0.1)-0.0025-0.1088 + ((4.45×1.5)×0.1)-0.0047-0.1378 + ((4.45×1.5)×0.1)-0.005-0.1375 = 6.7486</t>
         </is>
       </c>
-      <c r="F118" s="8" t="n"/>
+      <c r="F118" s="5" t="n">
+        <v>6.7486</v>
+      </c>
     </row>
     <row r="119" ht="18" customHeight="1">
       <c r="A119" s="3" t="n"/>
@@ -2938,7 +3146,9 @@
           <t>((5.2×4.45)×0.12)-0.0106-0.273 + ((5.2×4.45)×0.12)-0.0096-0.2737 + ((6.15×4.45)×0.12)-0.022-0.2921 + ((6.15×4.45)×0.12)-0.0238-0.291 = 10.9259</t>
         </is>
       </c>
-      <c r="F119" s="8" t="n"/>
+      <c r="F119" s="5" t="n">
+        <v>10.9259</v>
+      </c>
     </row>
     <row r="120" ht="18" customHeight="1">
       <c r="A120" s="3" t="n"/>
@@ -2958,7 +3168,9 @@
           <t>((3.4×1.8)×0.09)-0.0079-0.1046 + ((3.4×1.31)×0.09)-0.0107-0.0918 = 0.7365</t>
         </is>
       </c>
-      <c r="F120" s="8" t="n"/>
+      <c r="F120" s="5" t="n">
+        <v>0.7365</v>
+      </c>
     </row>
     <row r="121" ht="18" customHeight="1">
       <c r="A121" s="3" t="n"/>
@@ -2978,7 +3190,9 @@
           <t>((3.41×0.655)×0.1)-0.0426-0.0409 + ((7.005×3.41)×0.1)-0.07-0.1778 = 2.2807</t>
         </is>
       </c>
-      <c r="F121" s="8" t="n"/>
+      <c r="F121" s="5" t="n">
+        <v>2.2807</v>
+      </c>
     </row>
     <row r="122" ht="18" customHeight="1">
       <c r="A122" s="3" t="n"/>
@@ -2994,7 +3208,9 @@
           <t>5.2434 + 12.1968 + 1.6313 + 5.8196 + 9.1466 + 2.8992 + 5.8196 + 9.1466 + 2.8992 + 6.7486 + 10.9259 + 0.7365 + 2.2807 = 75.494 ≈ 75.49</t>
         </is>
       </c>
-      <c r="F122" s="8" t="n"/>
+      <c r="F122" s="8" t="n">
+        <v>75.48999999999999</v>
+      </c>
     </row>
     <row r="123" ht="18" customHeight="1">
       <c r="A123" s="3" t="n">
@@ -3021,7 +3237,7 @@
         </is>
       </c>
       <c r="F123" s="5" t="n">
-        <v>0.38</v>
+        <v>0.189</v>
       </c>
     </row>
     <row r="124" ht="18" customHeight="1">
@@ -3042,7 +3258,9 @@
           <t>(0.25×0.35×2.225) = 0.1947</t>
         </is>
       </c>
-      <c r="F124" s="8" t="n"/>
+      <c r="F124" s="5" t="n">
+        <v>0.1947</v>
+      </c>
     </row>
     <row r="125" ht="18" customHeight="1">
       <c r="A125" s="3" t="n"/>
@@ -3058,7 +3276,9 @@
           <t>0.189 + 0.1947 = 0.3837 ≈ 0.38</t>
         </is>
       </c>
-      <c r="F125" s="8" t="n"/>
+      <c r="F125" s="8" t="n">
+        <v>0.38</v>
+      </c>
     </row>
     <row r="126" ht="18" customHeight="1">
       <c r="A126" s="3" t="n">
@@ -3085,7 +3305,7 @@
         </is>
       </c>
       <c r="F126" s="5" t="n">
-        <v>11.14</v>
+        <v>2.8942</v>
       </c>
     </row>
     <row r="127" ht="18" customHeight="1">
@@ -3106,7 +3326,9 @@
           <t>1.8087+0.5499+0.3899 = 2.7485</t>
         </is>
       </c>
-      <c r="F127" s="8" t="n"/>
+      <c r="F127" s="5" t="n">
+        <v>2.7485</v>
+      </c>
     </row>
     <row r="128" ht="18" customHeight="1">
       <c r="A128" s="3" t="n"/>
@@ -3126,7 +3348,9 @@
           <t>1.8087+0.5499+0.3899 = 2.7485</t>
         </is>
       </c>
-      <c r="F128" s="8" t="n"/>
+      <c r="F128" s="5" t="n">
+        <v>2.7485</v>
+      </c>
     </row>
     <row r="129" ht="18" customHeight="1">
       <c r="A129" s="3" t="n"/>
@@ -3146,7 +3370,9 @@
           <t>1.8087+0.5499+0.3899 = 2.7485</t>
         </is>
       </c>
-      <c r="F129" s="8" t="n"/>
+      <c r="F129" s="5" t="n">
+        <v>2.7485</v>
+      </c>
     </row>
     <row r="130" ht="18" customHeight="1">
       <c r="A130" s="3" t="n"/>
@@ -3162,7 +3388,9 @@
           <t>2.8942 + 2.7485 + 2.7485 + 2.7485 = 11.1397 ≈ 11.14</t>
         </is>
       </c>
-      <c r="F130" s="8" t="n"/>
+      <c r="F130" s="8" t="n">
+        <v>11.14</v>
+      </c>
     </row>
     <row r="131" ht="18" customHeight="1">
       <c r="A131" s="3" t="n">
@@ -3189,7 +3417,7 @@
         </is>
       </c>
       <c r="F131" s="5" t="n">
-        <v>6.9</v>
+        <v>0.0969</v>
       </c>
     </row>
     <row r="132" ht="18" customHeight="1">
@@ -3210,7 +3438,9 @@
           <t>[(0.25×0.37)×1.55]×3 = 0.4302</t>
         </is>
       </c>
-      <c r="F132" s="8" t="n"/>
+      <c r="F132" s="5" t="n">
+        <v>0.4302</v>
+      </c>
     </row>
     <row r="133" ht="18" customHeight="1">
       <c r="A133" s="3" t="n"/>
@@ -3230,7 +3460,9 @@
           <t>(0.25×0.25)×3.6-0.025 = 0.2</t>
         </is>
       </c>
-      <c r="F133" s="8" t="n"/>
+      <c r="F133" s="5" t="n">
+        <v>0.2</v>
+      </c>
     </row>
     <row r="134" ht="18" customHeight="1">
       <c r="A134" s="3" t="n"/>
@@ -3250,7 +3482,9 @@
           <t>[(0.25×0.37)×3.6-0.025]×3 = 0.924</t>
         </is>
       </c>
-      <c r="F134" s="8" t="n"/>
+      <c r="F134" s="5" t="n">
+        <v>0.924</v>
+      </c>
     </row>
     <row r="135" ht="18" customHeight="1">
       <c r="A135" s="3" t="n"/>
@@ -3270,7 +3504,9 @@
           <t>(0.25×0.25)×3.6+0.0461-0.025 = 0.2461</t>
         </is>
       </c>
-      <c r="F135" s="8" t="n"/>
+      <c r="F135" s="5" t="n">
+        <v>0.2461</v>
+      </c>
     </row>
     <row r="136" ht="18" customHeight="1">
       <c r="A136" s="3" t="n"/>
@@ -3290,7 +3526,9 @@
           <t>[(0.25×0.37)×3.6+0.0461-0.025]×3 = 1.0623</t>
         </is>
       </c>
-      <c r="F136" s="8" t="n"/>
+      <c r="F136" s="5" t="n">
+        <v>1.0623</v>
+      </c>
     </row>
     <row r="137" ht="18" customHeight="1">
       <c r="A137" s="3" t="n"/>
@@ -3310,7 +3548,9 @@
           <t>(0.25×0.25)×3.6+0.0461-0.025 = 0.2461</t>
         </is>
       </c>
-      <c r="F137" s="8" t="n"/>
+      <c r="F137" s="5" t="n">
+        <v>0.2461</v>
+      </c>
     </row>
     <row r="138" ht="18" customHeight="1">
       <c r="A138" s="3" t="n"/>
@@ -3330,7 +3570,9 @@
           <t>[(0.25×0.37)×3.6+0.0461-0.025]×3 = 1.0623</t>
         </is>
       </c>
-      <c r="F138" s="8" t="n"/>
+      <c r="F138" s="5" t="n">
+        <v>1.0623</v>
+      </c>
     </row>
     <row r="139" ht="18" customHeight="1">
       <c r="A139" s="3" t="n"/>
@@ -3350,7 +3592,9 @@
           <t>(0.25×0.25)×3.6+0.0461-0.025 = 0.2461</t>
         </is>
       </c>
-      <c r="F139" s="8" t="n"/>
+      <c r="F139" s="5" t="n">
+        <v>0.2461</v>
+      </c>
     </row>
     <row r="140" ht="18" customHeight="1">
       <c r="A140" s="3" t="n"/>
@@ -3370,7 +3614,9 @@
           <t>[(0.25×0.37)×3.6+0.0461-0.025]×3 = 1.0623</t>
         </is>
       </c>
-      <c r="F140" s="8" t="n"/>
+      <c r="F140" s="5" t="n">
+        <v>1.0623</v>
+      </c>
     </row>
     <row r="141" ht="32" customHeight="1">
       <c r="A141" s="3" t="n"/>
@@ -3390,7 +3636,9 @@
           <t>(0.25×0.25)×3+0.0496-0.0049-0.0004-0.0002-0.0017 + (0.25×0.25)×3+0.0432-0.0049-0.0004-0.0017 + (0.25×0.25)×3+0.0496-0.0042-0.0002-0.0017 + (0.25×0.25)×3+0.0407-0.0021-0.0219-0.0065 = 0.8823</t>
         </is>
       </c>
-      <c r="F141" s="8" t="n"/>
+      <c r="F141" s="5" t="n">
+        <v>0.8823</v>
+      </c>
     </row>
     <row r="142" ht="18" customHeight="1">
       <c r="A142" s="3" t="n"/>
@@ -3410,7 +3658,9 @@
           <t>[(0.25×0.37)×1.6+0.0128-0.0121]×2 + (0.25×0.37)×1.6+0.0128-0.012 = 0.4462</t>
         </is>
       </c>
-      <c r="F142" s="8" t="n"/>
+      <c r="F142" s="5" t="n">
+        <v>0.4462</v>
+      </c>
     </row>
     <row r="143" ht="18" customHeight="1">
       <c r="A143" s="3" t="n"/>
@@ -3426,7 +3676,9 @@
           <t>0.0969 + 0.4302 + 0.2 + 0.924 + 0.2461 + 1.0623 + 0.2461 + 1.0623 + 0.2461 + 1.0623 + 0.8823 + 0.4462 = 6.9048 ≈ 6.90</t>
         </is>
       </c>
-      <c r="F143" s="8" t="n"/>
+      <c r="F143" s="8" t="n">
+        <v>6.9</v>
+      </c>
     </row>
     <row r="144" ht="18" customHeight="1">
       <c r="A144" s="3" t="n">
@@ -3453,7 +3705,7 @@
         </is>
       </c>
       <c r="F144" s="5" t="n">
-        <v>1.42</v>
+        <v>1.1142</v>
       </c>
     </row>
     <row r="145" ht="18" customHeight="1">
@@ -3474,7 +3726,9 @@
           <t>(0.24×0.4×3.65)-0.048 = 0.3024</t>
         </is>
       </c>
-      <c r="F145" s="8" t="n"/>
+      <c r="F145" s="5" t="n">
+        <v>0.3024</v>
+      </c>
     </row>
     <row r="146" ht="18" customHeight="1">
       <c r="A146" s="3" t="n"/>
@@ -3490,7 +3744,9 @@
           <t>1.1142 + 0.3024 = 1.4166 ≈ 1.42</t>
         </is>
       </c>
-      <c r="F146" s="8" t="n"/>
+      <c r="F146" s="8" t="n">
+        <v>1.42</v>
+      </c>
     </row>
     <row r="147" ht="18" customHeight="1">
       <c r="A147" s="3" t="n">
@@ -3517,7 +3773,7 @@
         </is>
       </c>
       <c r="F147" s="5" t="n">
-        <v>2.37</v>
+        <v>0.0022</v>
       </c>
     </row>
     <row r="148" ht="18" customHeight="1">
@@ -3538,7 +3794,9 @@
           <t>[(0.048×2.3)]×2 = 0.2208</t>
         </is>
       </c>
-      <c r="F148" s="8" t="n"/>
+      <c r="F148" s="5" t="n">
+        <v>0.2208</v>
+      </c>
     </row>
     <row r="149" ht="18" customHeight="1">
       <c r="A149" s="3" t="n"/>
@@ -3558,7 +3816,9 @@
           <t>[(0.048×2.9)]×4 = 0.5568</t>
         </is>
       </c>
-      <c r="F149" s="8" t="n"/>
+      <c r="F149" s="5" t="n">
+        <v>0.5568</v>
+      </c>
     </row>
     <row r="150" ht="18" customHeight="1">
       <c r="A150" s="3" t="n"/>
@@ -3578,7 +3838,9 @@
           <t>[(0.048×2.3)]×2 = 0.2208</t>
         </is>
       </c>
-      <c r="F150" s="8" t="n"/>
+      <c r="F150" s="5" t="n">
+        <v>0.2208</v>
+      </c>
     </row>
     <row r="151" ht="18" customHeight="1">
       <c r="A151" s="3" t="n"/>
@@ -3598,7 +3860,9 @@
           <t>[(0.048×2.9)]×2 = 0.2784</t>
         </is>
       </c>
-      <c r="F151" s="8" t="n"/>
+      <c r="F151" s="5" t="n">
+        <v>0.2784</v>
+      </c>
     </row>
     <row r="152" ht="18" customHeight="1">
       <c r="A152" s="3" t="n"/>
@@ -3618,7 +3882,9 @@
           <t>[(0.048×2.3)]×2 = 0.2208</t>
         </is>
       </c>
-      <c r="F152" s="8" t="n"/>
+      <c r="F152" s="5" t="n">
+        <v>0.2208</v>
+      </c>
     </row>
     <row r="153" ht="18" customHeight="1">
       <c r="A153" s="3" t="n"/>
@@ -3638,7 +3904,9 @@
           <t>[(0.048×2.9)]×2 = 0.2784</t>
         </is>
       </c>
-      <c r="F153" s="8" t="n"/>
+      <c r="F153" s="5" t="n">
+        <v>0.2784</v>
+      </c>
     </row>
     <row r="154" ht="18" customHeight="1">
       <c r="A154" s="3" t="n"/>
@@ -3658,7 +3926,9 @@
           <t>[(0.048×2.3)]×2 = 0.2208</t>
         </is>
       </c>
-      <c r="F154" s="8" t="n"/>
+      <c r="F154" s="5" t="n">
+        <v>0.2208</v>
+      </c>
     </row>
     <row r="155" ht="18" customHeight="1">
       <c r="A155" s="3" t="n"/>
@@ -3678,7 +3948,9 @@
           <t>[(0.048×2.9)]×2 = 0.2784</t>
         </is>
       </c>
-      <c r="F155" s="8" t="n"/>
+      <c r="F155" s="5" t="n">
+        <v>0.2784</v>
+      </c>
     </row>
     <row r="156" ht="18" customHeight="1">
       <c r="A156" s="3" t="n"/>
@@ -3698,7 +3970,9 @@
           <t>(0.048×2) = 0.096</t>
         </is>
       </c>
-      <c r="F156" s="8" t="n"/>
+      <c r="F156" s="5" t="n">
+        <v>0.096</v>
+      </c>
     </row>
     <row r="157" ht="18" customHeight="1">
       <c r="A157" s="3" t="n"/>
@@ -3714,7 +3988,9 @@
           <t>0.0022 + 0.2208 + 0.5568 + 0.2208 + 0.2784 + 0.2208 + 0.2784 + 0.2208 + 0.2784 + 0.096 = 2.3734 ≈ 2.37</t>
         </is>
       </c>
-      <c r="F157" s="8" t="n"/>
+      <c r="F157" s="8" t="n">
+        <v>2.37</v>
+      </c>
     </row>
     <row r="158" ht="18" customHeight="1">
       <c r="A158" s="3" t="n">
@@ -3741,7 +4017,7 @@
         </is>
       </c>
       <c r="F158" s="5" t="n">
-        <v>31.76</v>
+        <v>31.7629</v>
       </c>
     </row>
     <row r="159" ht="18" customHeight="1">
@@ -3758,7 +4034,9 @@
           <t>31.7629 ≈ 31.76</t>
         </is>
       </c>
-      <c r="F159" s="8" t="n"/>
+      <c r="F159" s="8" t="n">
+        <v>31.76</v>
+      </c>
     </row>
     <row r="160" ht="18" customHeight="1">
       <c r="A160" s="3" t="n">
@@ -3785,7 +4063,7 @@
         </is>
       </c>
       <c r="F160" s="5" t="n">
-        <v>7.64</v>
+        <v>7.641</v>
       </c>
     </row>
     <row r="161" ht="18" customHeight="1">
@@ -3802,7 +4080,9 @@
           <t>7.641 ≈ 7.64</t>
         </is>
       </c>
-      <c r="F161" s="8" t="n"/>
+      <c r="F161" s="8" t="n">
+        <v>7.64</v>
+      </c>
     </row>
     <row r="162" ht="18" customHeight="1">
       <c r="A162" s="3" t="n">
@@ -3829,7 +4109,7 @@
         </is>
       </c>
       <c r="F162" s="5" t="n">
-        <v>2.78</v>
+        <v>0.536</v>
       </c>
     </row>
     <row r="163" ht="18" customHeight="1">
@@ -3850,7 +4130,9 @@
           <t>(0.048×13.53) + (0.048×5.745) + (0.048×15.53) + (0.048×11.995) = 2.2464</t>
         </is>
       </c>
-      <c r="F163" s="8" t="n"/>
+      <c r="F163" s="5" t="n">
+        <v>2.2464</v>
+      </c>
     </row>
     <row r="164" ht="18" customHeight="1">
       <c r="A164" s="3" t="n"/>
@@ -3866,7 +4148,9 @@
           <t>0.536 + 2.2464 = 2.7824 ≈ 2.78</t>
         </is>
       </c>
-      <c r="F164" s="8" t="n"/>
+      <c r="F164" s="8" t="n">
+        <v>2.78</v>
+      </c>
     </row>
     <row r="165" ht="18" customHeight="1">
       <c r="A165" s="3" t="n">
@@ -3893,7 +4177,7 @@
         </is>
       </c>
       <c r="F165" s="9" t="n">
-        <v>0.709</v>
+        <v>290.472</v>
       </c>
     </row>
     <row r="166" ht="18" customHeight="1">
@@ -3914,7 +4198,9 @@
           <t>179.984 + 185.64 = 365.624</t>
         </is>
       </c>
-      <c r="F166" s="10" t="n"/>
+      <c r="F166" s="9" t="n">
+        <v>365.624</v>
+      </c>
     </row>
     <row r="167" ht="18" customHeight="1">
       <c r="A167" s="3" t="n"/>
@@ -3934,7 +4220,9 @@
           <t>25.586 + 26.82 = 52.406</t>
         </is>
       </c>
-      <c r="F167" s="10" t="n"/>
+      <c r="F167" s="9" t="n">
+        <v>52.406</v>
+      </c>
     </row>
     <row r="168" ht="18" customHeight="1">
       <c r="A168" s="3" t="n"/>
@@ -3950,7 +4238,9 @@
           <t>(290.472 + 365.624 + 52.406) ÷ 1000 = 0.709</t>
         </is>
       </c>
-      <c r="F168" s="10" t="n"/>
+      <c r="F168" s="10" t="n">
+        <v>0.709</v>
+      </c>
     </row>
     <row r="169" ht="18" customHeight="1">
       <c r="A169" s="3" t="n">
@@ -3977,7 +4267,7 @@
         </is>
       </c>
       <c r="F169" s="9" t="n">
-        <v>0.492</v>
+        <v>34.047</v>
       </c>
     </row>
     <row r="170" ht="18" customHeight="1">
@@ -3998,7 +4288,9 @@
           <t>3.783 = 3.783</t>
         </is>
       </c>
-      <c r="F170" s="10" t="n"/>
+      <c r="F170" s="9" t="n">
+        <v>3.783</v>
+      </c>
     </row>
     <row r="171" ht="18" customHeight="1">
       <c r="A171" s="3" t="n"/>
@@ -4018,7 +4310,9 @@
           <t>44.523 = 44.523</t>
         </is>
       </c>
-      <c r="F171" s="10" t="n"/>
+      <c r="F171" s="9" t="n">
+        <v>44.523</v>
+      </c>
     </row>
     <row r="172" ht="18" customHeight="1">
       <c r="A172" s="3" t="n"/>
@@ -4038,7 +4332,9 @@
           <t>4.947 = 4.947</t>
         </is>
       </c>
-      <c r="F172" s="10" t="n"/>
+      <c r="F172" s="9" t="n">
+        <v>4.947</v>
+      </c>
     </row>
     <row r="173" ht="18" customHeight="1">
       <c r="A173" s="3" t="n"/>
@@ -4058,7 +4354,9 @@
           <t>12.96 + 19.584 + 12.96 + 19.584 = 65.088</t>
         </is>
       </c>
-      <c r="F173" s="10" t="n"/>
+      <c r="F173" s="9" t="n">
+        <v>65.08799999999999</v>
+      </c>
     </row>
     <row r="174" ht="18" customHeight="1">
       <c r="A174" s="3" t="n"/>
@@ -4078,7 +4376,9 @@
           <t>44.523 = 44.523</t>
         </is>
       </c>
-      <c r="F174" s="10" t="n"/>
+      <c r="F174" s="9" t="n">
+        <v>44.523</v>
+      </c>
     </row>
     <row r="175" ht="18" customHeight="1">
       <c r="A175" s="3" t="n"/>
@@ -4098,7 +4398,9 @@
           <t>4.947 = 4.947</t>
         </is>
       </c>
-      <c r="F175" s="10" t="n"/>
+      <c r="F175" s="9" t="n">
+        <v>4.947</v>
+      </c>
     </row>
     <row r="176" ht="18" customHeight="1">
       <c r="A176" s="3" t="n"/>
@@ -4118,7 +4420,9 @@
           <t>12.24 + 19.584 + 12.24 + 19.584 = 63.648</t>
         </is>
       </c>
-      <c r="F176" s="10" t="n"/>
+      <c r="F176" s="9" t="n">
+        <v>63.648</v>
+      </c>
     </row>
     <row r="177" ht="18" customHeight="1">
       <c r="A177" s="3" t="n"/>
@@ -4138,7 +4442,9 @@
           <t>44.523 = 44.523</t>
         </is>
       </c>
-      <c r="F177" s="10" t="n"/>
+      <c r="F177" s="9" t="n">
+        <v>44.523</v>
+      </c>
     </row>
     <row r="178" ht="18" customHeight="1">
       <c r="A178" s="3" t="n"/>
@@ -4158,7 +4464,9 @@
           <t>4.947 = 4.947</t>
         </is>
       </c>
-      <c r="F178" s="10" t="n"/>
+      <c r="F178" s="9" t="n">
+        <v>4.947</v>
+      </c>
     </row>
     <row r="179" ht="18" customHeight="1">
       <c r="A179" s="3" t="n"/>
@@ -4178,7 +4486,9 @@
           <t>24.48 + 39.168 = 63.648</t>
         </is>
       </c>
-      <c r="F179" s="10" t="n"/>
+      <c r="F179" s="9" t="n">
+        <v>63.648</v>
+      </c>
     </row>
     <row r="180" ht="18" customHeight="1">
       <c r="A180" s="3" t="n"/>
@@ -4198,7 +4508,9 @@
           <t>44.523 = 44.523</t>
         </is>
       </c>
-      <c r="F180" s="10" t="n"/>
+      <c r="F180" s="9" t="n">
+        <v>44.523</v>
+      </c>
     </row>
     <row r="181" ht="18" customHeight="1">
       <c r="A181" s="3" t="n"/>
@@ -4218,7 +4530,9 @@
           <t>4.947 = 4.947</t>
         </is>
       </c>
-      <c r="F181" s="10" t="n"/>
+      <c r="F181" s="9" t="n">
+        <v>4.947</v>
+      </c>
     </row>
     <row r="182" ht="18" customHeight="1">
       <c r="A182" s="3" t="n"/>
@@ -4238,7 +4552,9 @@
           <t>24.48 + 39.168 = 63.648</t>
         </is>
       </c>
-      <c r="F182" s="10" t="n"/>
+      <c r="F182" s="9" t="n">
+        <v>63.648</v>
+      </c>
     </row>
     <row r="183" ht="18" customHeight="1">
       <c r="A183" s="3" t="n"/>
@@ -4254,7 +4570,9 @@
           <t>(34.047 + 3.783 + 44.523 + 4.947 + 65.088 + 44.523 + 4.947 + 63.648 + 44.523 + 4.947 + 63.648 + 44.523 + 4.947 + 63.648) ÷ 1000 = 0.492</t>
         </is>
       </c>
-      <c r="F183" s="10" t="n"/>
+      <c r="F183" s="10" t="n">
+        <v>0.492</v>
+      </c>
     </row>
     <row r="184" ht="18" customHeight="1">
       <c r="A184" s="3" t="n">
@@ -4281,7 +4599,7 @@
         </is>
       </c>
       <c r="F184" s="9" t="n">
-        <v>0.175</v>
+        <v>9.023999999999999</v>
       </c>
     </row>
     <row r="185" ht="18" customHeight="1">
@@ -4302,7 +4620,9 @@
           <t>6.768 = 6.768</t>
         </is>
       </c>
-      <c r="F185" s="10" t="n"/>
+      <c r="F185" s="9" t="n">
+        <v>6.768</v>
+      </c>
     </row>
     <row r="186" ht="18" customHeight="1">
       <c r="A186" s="3" t="n"/>
@@ -4322,7 +4642,9 @@
           <t>24.816 + 9.588 = 34.404</t>
         </is>
       </c>
-      <c r="F186" s="10" t="n"/>
+      <c r="F186" s="9" t="n">
+        <v>34.404</v>
+      </c>
     </row>
     <row r="187" ht="18" customHeight="1">
       <c r="A187" s="3" t="n"/>
@@ -4342,7 +4664,9 @@
           <t>9.588 = 9.588</t>
         </is>
       </c>
-      <c r="F187" s="10" t="n"/>
+      <c r="F187" s="9" t="n">
+        <v>9.587999999999999</v>
+      </c>
     </row>
     <row r="188" ht="18" customHeight="1">
       <c r="A188" s="3" t="n"/>
@@ -4362,7 +4686,9 @@
           <t>28.764 = 28.764</t>
         </is>
       </c>
-      <c r="F188" s="10" t="n"/>
+      <c r="F188" s="9" t="n">
+        <v>28.764</v>
+      </c>
     </row>
     <row r="189" ht="18" customHeight="1">
       <c r="A189" s="3" t="n"/>
@@ -4382,7 +4708,9 @@
           <t>9.588 = 9.588</t>
         </is>
       </c>
-      <c r="F189" s="10" t="n"/>
+      <c r="F189" s="9" t="n">
+        <v>9.587999999999999</v>
+      </c>
     </row>
     <row r="190" ht="18" customHeight="1">
       <c r="A190" s="3" t="n"/>
@@ -4402,7 +4730,9 @@
           <t>28.764 = 28.764</t>
         </is>
       </c>
-      <c r="F190" s="10" t="n"/>
+      <c r="F190" s="9" t="n">
+        <v>28.764</v>
+      </c>
     </row>
     <row r="191" ht="18" customHeight="1">
       <c r="A191" s="3" t="n"/>
@@ -4422,7 +4752,9 @@
           <t>9.588 = 9.588</t>
         </is>
       </c>
-      <c r="F191" s="10" t="n"/>
+      <c r="F191" s="9" t="n">
+        <v>9.587999999999999</v>
+      </c>
     </row>
     <row r="192" ht="18" customHeight="1">
       <c r="A192" s="3" t="n"/>
@@ -4442,7 +4774,9 @@
           <t>28.764 = 28.764</t>
         </is>
       </c>
-      <c r="F192" s="10" t="n"/>
+      <c r="F192" s="9" t="n">
+        <v>28.764</v>
+      </c>
     </row>
     <row r="193" ht="18" customHeight="1">
       <c r="A193" s="3" t="n"/>
@@ -4462,7 +4796,9 @@
           <t>9.588 = 9.588</t>
         </is>
       </c>
-      <c r="F193" s="10" t="n"/>
+      <c r="F193" s="9" t="n">
+        <v>9.587999999999999</v>
+      </c>
     </row>
     <row r="194" ht="18" customHeight="1">
       <c r="A194" s="3" t="n"/>
@@ -4478,7 +4814,9 @@
           <t>(9.024 + 6.768 + 34.404 + 9.588 + 28.764 + 9.588 + 28.764 + 9.588 + 28.764 + 9.588) ÷ 1000 = 0.175</t>
         </is>
       </c>
-      <c r="F194" s="10" t="n"/>
+      <c r="F194" s="10" t="n">
+        <v>0.175</v>
+      </c>
     </row>
     <row r="195" ht="18" customHeight="1">
       <c r="A195" s="3" t="n">
@@ -4504,7 +4842,7 @@
           <t>计算书中无依据，需补充</t>
         </is>
       </c>
-      <c r="F195" s="10" t="inlineStr">
+      <c r="F195" s="9" t="inlineStr">
         <is>
           <t>需补充</t>
         </is>
@@ -4535,7 +4873,7 @@
         </is>
       </c>
       <c r="F196" s="9" t="n">
-        <v>0.345</v>
+        <v>111.692</v>
       </c>
     </row>
     <row r="197" ht="18" customHeight="1">
@@ -4556,7 +4894,9 @@
           <t>41.08 + 2.9 + 4.924 + 41.08 = 89.984</t>
         </is>
       </c>
-      <c r="F197" s="10" t="n"/>
+      <c r="F197" s="9" t="n">
+        <v>89.98399999999999</v>
+      </c>
     </row>
     <row r="198" ht="18" customHeight="1">
       <c r="A198" s="3" t="n"/>
@@ -4576,7 +4916,9 @@
           <t>82.16 = 82.16</t>
         </is>
       </c>
-      <c r="F198" s="10" t="n"/>
+      <c r="F198" s="9" t="n">
+        <v>82.16</v>
+      </c>
     </row>
     <row r="199" ht="18" customHeight="1">
       <c r="A199" s="3" t="n"/>
@@ -4596,7 +4938,9 @@
           <t>34.56 + 26.456 = 61.016</t>
         </is>
       </c>
-      <c r="F199" s="10" t="n"/>
+      <c r="F199" s="9" t="n">
+        <v>61.016</v>
+      </c>
     </row>
     <row r="200" ht="18" customHeight="1">
       <c r="A200" s="3" t="n"/>
@@ -4612,7 +4956,9 @@
           <t>(111.692 + 89.984 + 82.16 + 61.016) ÷ 1000 = 0.345</t>
         </is>
       </c>
-      <c r="F200" s="10" t="n"/>
+      <c r="F200" s="10" t="n">
+        <v>0.345</v>
+      </c>
     </row>
     <row r="201" ht="18" customHeight="1">
       <c r="A201" s="3" t="n">
@@ -4639,7 +4985,7 @@
         </is>
       </c>
       <c r="F201" s="9" t="n">
-        <v>2.989</v>
+        <v>367.632</v>
       </c>
     </row>
     <row r="202" ht="18" customHeight="1">
@@ -4660,7 +5006,9 @@
           <t>21.18 + 27.48 = 48.66</t>
         </is>
       </c>
-      <c r="F202" s="10" t="n"/>
+      <c r="F202" s="9" t="n">
+        <v>48.66</v>
+      </c>
     </row>
     <row r="203" ht="18" customHeight="1">
       <c r="A203" s="3" t="n"/>
@@ -4680,7 +5028,9 @@
           <t>22.38 + 28.68 = 51.06</t>
         </is>
       </c>
-      <c r="F203" s="10" t="n"/>
+      <c r="F203" s="9" t="n">
+        <v>51.06</v>
+      </c>
     </row>
     <row r="204" ht="18" customHeight="1">
       <c r="A204" s="3" t="n"/>
@@ -4700,7 +5050,9 @@
           <t>518.4 = 518.4</t>
         </is>
       </c>
-      <c r="F204" s="10" t="n"/>
+      <c r="F204" s="9" t="n">
+        <v>518.4</v>
+      </c>
     </row>
     <row r="205" ht="18" customHeight="1">
       <c r="A205" s="3" t="n"/>
@@ -4720,7 +5072,9 @@
           <t>72 = 72</t>
         </is>
       </c>
-      <c r="F205" s="10" t="n"/>
+      <c r="F205" s="9" t="n">
+        <v>72</v>
+      </c>
     </row>
     <row r="206" ht="18" customHeight="1">
       <c r="A206" s="3" t="n"/>
@@ -4740,7 +5094,9 @@
           <t>72 = 72</t>
         </is>
       </c>
-      <c r="F206" s="10" t="n"/>
+      <c r="F206" s="9" t="n">
+        <v>72</v>
+      </c>
     </row>
     <row r="207" ht="18" customHeight="1">
       <c r="A207" s="3" t="n"/>
@@ -4760,7 +5116,9 @@
           <t>518.4 = 518.4</t>
         </is>
       </c>
-      <c r="F207" s="10" t="n"/>
+      <c r="F207" s="9" t="n">
+        <v>518.4</v>
+      </c>
     </row>
     <row r="208" ht="18" customHeight="1">
       <c r="A208" s="3" t="n"/>
@@ -4780,7 +5138,9 @@
           <t>72 = 72</t>
         </is>
       </c>
-      <c r="F208" s="10" t="n"/>
+      <c r="F208" s="9" t="n">
+        <v>72</v>
+      </c>
     </row>
     <row r="209" ht="18" customHeight="1">
       <c r="A209" s="3" t="n"/>
@@ -4800,7 +5160,9 @@
           <t>72 = 72</t>
         </is>
       </c>
-      <c r="F209" s="10" t="n"/>
+      <c r="F209" s="9" t="n">
+        <v>72</v>
+      </c>
     </row>
     <row r="210" ht="18" customHeight="1">
       <c r="A210" s="3" t="n"/>
@@ -4820,7 +5182,9 @@
           <t>518.4 = 518.4</t>
         </is>
       </c>
-      <c r="F210" s="10" t="n"/>
+      <c r="F210" s="9" t="n">
+        <v>518.4</v>
+      </c>
     </row>
     <row r="211" ht="18" customHeight="1">
       <c r="A211" s="3" t="n"/>
@@ -4840,7 +5204,9 @@
           <t>72 = 72</t>
         </is>
       </c>
-      <c r="F211" s="10" t="n"/>
+      <c r="F211" s="9" t="n">
+        <v>72</v>
+      </c>
     </row>
     <row r="212" ht="18" customHeight="1">
       <c r="A212" s="3" t="n"/>
@@ -4860,7 +5226,9 @@
           <t>72 = 72</t>
         </is>
       </c>
-      <c r="F212" s="10" t="n"/>
+      <c r="F212" s="9" t="n">
+        <v>72</v>
+      </c>
     </row>
     <row r="213" ht="18" customHeight="1">
       <c r="A213" s="3" t="n"/>
@@ -4880,7 +5248,9 @@
           <t>233.928 + 188.568 = 422.496</t>
         </is>
       </c>
-      <c r="F213" s="10" t="n"/>
+      <c r="F213" s="9" t="n">
+        <v>422.496</v>
+      </c>
     </row>
     <row r="214" ht="18" customHeight="1">
       <c r="A214" s="3" t="n"/>
@@ -4900,7 +5270,9 @@
           <t>18.42 + 10.476 + 14.64 + 12.996 = 56.532</t>
         </is>
       </c>
-      <c r="F214" s="10" t="n"/>
+      <c r="F214" s="9" t="n">
+        <v>56.532</v>
+      </c>
     </row>
     <row r="215" ht="18" customHeight="1">
       <c r="A215" s="3" t="n"/>
@@ -4920,7 +5292,9 @@
           <t>24.56 + 19.52 + 5.238 + 6.498 = 55.816</t>
         </is>
       </c>
-      <c r="F215" s="10" t="n"/>
+      <c r="F215" s="9" t="n">
+        <v>55.816</v>
+      </c>
     </row>
     <row r="216" ht="18" customHeight="1">
       <c r="A216" s="3" t="n"/>
@@ -4936,7 +5310,9 @@
           <t>(367.632 + 48.66 + 51.06 + 518.4 + 72 + 72 + 518.4 + 72 + 72 + 518.4 + 72 + 72 + 422.496 + 56.532 + 55.816) ÷ 1000 = 2.989</t>
         </is>
       </c>
-      <c r="F216" s="10" t="n"/>
+      <c r="F216" s="10" t="n">
+        <v>2.989</v>
+      </c>
     </row>
     <row r="217" ht="18" customHeight="1">
       <c r="A217" s="3" t="n">
@@ -4963,7 +5339,7 @@
         </is>
       </c>
       <c r="F217" s="9" t="n">
-        <v>0.968</v>
+        <v>117.356</v>
       </c>
     </row>
     <row r="218" ht="18" customHeight="1">
@@ -4984,7 +5360,9 @@
           <t>179.824 + 71.136 = 250.96</t>
         </is>
       </c>
-      <c r="F218" s="10" t="n"/>
+      <c r="F218" s="9" t="n">
+        <v>250.96</v>
+      </c>
     </row>
     <row r="219" ht="18" customHeight="1">
       <c r="A219" s="3" t="n"/>
@@ -5004,7 +5382,9 @@
           <t>213.408 = 213.408</t>
         </is>
       </c>
-      <c r="F219" s="10" t="n"/>
+      <c r="F219" s="9" t="n">
+        <v>213.408</v>
+      </c>
     </row>
     <row r="220" ht="18" customHeight="1">
       <c r="A220" s="3" t="n"/>
@@ -5024,7 +5404,9 @@
           <t>213.408 = 213.408</t>
         </is>
       </c>
-      <c r="F220" s="10" t="n"/>
+      <c r="F220" s="9" t="n">
+        <v>213.408</v>
+      </c>
     </row>
     <row r="221" ht="18" customHeight="1">
       <c r="A221" s="3" t="n"/>
@@ -5044,7 +5426,9 @@
           <t>96.864 + 76.116 = 172.98</t>
         </is>
       </c>
-      <c r="F221" s="10" t="n"/>
+      <c r="F221" s="9" t="n">
+        <v>172.98</v>
+      </c>
     </row>
     <row r="222" ht="18" customHeight="1">
       <c r="A222" s="3" t="n"/>
@@ -5060,7 +5444,9 @@
           <t>(117.356 + 250.96 + 213.408 + 213.408 + 172.98) ÷ 1000 = 0.968</t>
         </is>
       </c>
-      <c r="F222" s="10" t="n"/>
+      <c r="F222" s="10" t="n">
+        <v>0.968</v>
+      </c>
     </row>
     <row r="223" ht="18" customHeight="1">
       <c r="A223" s="3" t="n">
@@ -5087,7 +5473,7 @@
         </is>
       </c>
       <c r="F223" s="9" t="n">
-        <v>0.307</v>
+        <v>3.24</v>
       </c>
     </row>
     <row r="224" ht="18" customHeight="1">
@@ -5108,7 +5494,9 @@
           <t>2.16 = 2.16</t>
         </is>
       </c>
-      <c r="F224" s="10" t="n"/>
+      <c r="F224" s="9" t="n">
+        <v>2.16</v>
+      </c>
     </row>
     <row r="225" ht="18" customHeight="1">
       <c r="A225" s="3" t="n"/>
@@ -5128,7 +5516,9 @@
           <t>10.374 + 1.224 = 11.598</t>
         </is>
       </c>
-      <c r="F225" s="10" t="n"/>
+      <c r="F225" s="9" t="n">
+        <v>11.598</v>
+      </c>
     </row>
     <row r="226" ht="18" customHeight="1">
       <c r="A226" s="3" t="n"/>
@@ -5148,7 +5538,9 @@
           <t>3.584 = 3.584</t>
         </is>
       </c>
-      <c r="F226" s="10" t="n"/>
+      <c r="F226" s="9" t="n">
+        <v>3.584</v>
+      </c>
     </row>
     <row r="227" ht="18" customHeight="1">
       <c r="A227" s="3" t="n"/>
@@ -5168,7 +5560,9 @@
           <t>18.031 = 18.031</t>
         </is>
       </c>
-      <c r="F227" s="10" t="n"/>
+      <c r="F227" s="9" t="n">
+        <v>18.031</v>
+      </c>
     </row>
     <row r="228" ht="18" customHeight="1">
       <c r="A228" s="3" t="n"/>
@@ -5188,7 +5582,9 @@
           <t>3.584 = 3.584</t>
         </is>
       </c>
-      <c r="F228" s="10" t="n"/>
+      <c r="F228" s="9" t="n">
+        <v>3.584</v>
+      </c>
     </row>
     <row r="229" ht="18" customHeight="1">
       <c r="A229" s="3" t="n"/>
@@ -5208,7 +5604,9 @@
           <t>0.504 = 0.504</t>
         </is>
       </c>
-      <c r="F229" s="10" t="n"/>
+      <c r="F229" s="9" t="n">
+        <v>0.504</v>
+      </c>
     </row>
     <row r="230" ht="18" customHeight="1">
       <c r="A230" s="3" t="n"/>
@@ -5228,7 +5626,9 @@
           <t>4.788 = 4.788</t>
         </is>
       </c>
-      <c r="F230" s="10" t="n"/>
+      <c r="F230" s="9" t="n">
+        <v>4.788</v>
+      </c>
     </row>
     <row r="231" ht="18" customHeight="1">
       <c r="A231" s="3" t="n"/>
@@ -5248,7 +5648,9 @@
           <t>2.457 = 2.457</t>
         </is>
       </c>
-      <c r="F231" s="10" t="n"/>
+      <c r="F231" s="9" t="n">
+        <v>2.457</v>
+      </c>
     </row>
     <row r="232" ht="18" customHeight="1">
       <c r="A232" s="3" t="n"/>
@@ -5268,7 +5670,9 @@
           <t>2.142 = 2.142</t>
         </is>
       </c>
-      <c r="F232" s="10" t="n"/>
+      <c r="F232" s="9" t="n">
+        <v>2.142</v>
+      </c>
     </row>
     <row r="233" ht="18" customHeight="1">
       <c r="A233" s="3" t="n"/>
@@ -5288,7 +5692,9 @@
           <t>19.712 = 19.712</t>
         </is>
       </c>
-      <c r="F233" s="10" t="n"/>
+      <c r="F233" s="9" t="n">
+        <v>19.712</v>
+      </c>
     </row>
     <row r="234" ht="18" customHeight="1">
       <c r="A234" s="3" t="n"/>
@@ -5308,7 +5714,9 @@
           <t>2.394 = 2.394</t>
         </is>
       </c>
-      <c r="F234" s="10" t="n"/>
+      <c r="F234" s="9" t="n">
+        <v>2.394</v>
+      </c>
     </row>
     <row r="235" ht="18" customHeight="1">
       <c r="A235" s="3" t="n"/>
@@ -5328,7 +5736,9 @@
           <t>2.394 = 2.394</t>
         </is>
       </c>
-      <c r="F235" s="10" t="n"/>
+      <c r="F235" s="9" t="n">
+        <v>2.394</v>
+      </c>
     </row>
     <row r="236" ht="18" customHeight="1">
       <c r="A236" s="3" t="n"/>
@@ -5348,7 +5758,9 @@
           <t>2.394 = 2.394</t>
         </is>
       </c>
-      <c r="F236" s="10" t="n"/>
+      <c r="F236" s="9" t="n">
+        <v>2.394</v>
+      </c>
     </row>
     <row r="237" ht="18" customHeight="1">
       <c r="A237" s="3" t="n"/>
@@ -5368,7 +5780,9 @@
           <t>2.457 = 2.457</t>
         </is>
       </c>
-      <c r="F237" s="10" t="n"/>
+      <c r="F237" s="9" t="n">
+        <v>2.457</v>
+      </c>
     </row>
     <row r="238" ht="18" customHeight="1">
       <c r="A238" s="3" t="n"/>
@@ -5388,7 +5802,9 @@
           <t>2.394 = 2.394</t>
         </is>
       </c>
-      <c r="F238" s="10" t="n"/>
+      <c r="F238" s="9" t="n">
+        <v>2.394</v>
+      </c>
     </row>
     <row r="239" ht="18" customHeight="1">
       <c r="A239" s="3" t="n"/>
@@ -5408,7 +5824,9 @@
           <t>4.914 = 4.914</t>
         </is>
       </c>
-      <c r="F239" s="10" t="n"/>
+      <c r="F239" s="9" t="n">
+        <v>4.914</v>
+      </c>
     </row>
     <row r="240" ht="18" customHeight="1">
       <c r="A240" s="3" t="n"/>
@@ -5428,7 +5846,9 @@
           <t>18.688 = 18.688</t>
         </is>
       </c>
-      <c r="F240" s="10" t="n"/>
+      <c r="F240" s="9" t="n">
+        <v>18.688</v>
+      </c>
     </row>
     <row r="241" ht="18" customHeight="1">
       <c r="A241" s="3" t="n"/>
@@ -5448,7 +5868,9 @@
           <t>3.165 = 3.165</t>
         </is>
       </c>
-      <c r="F241" s="10" t="n"/>
+      <c r="F241" s="9" t="n">
+        <v>3.165</v>
+      </c>
     </row>
     <row r="242" ht="18" customHeight="1">
       <c r="A242" s="3" t="n"/>
@@ -5468,7 +5890,9 @@
           <t>19.712 = 19.712</t>
         </is>
       </c>
-      <c r="F242" s="10" t="n"/>
+      <c r="F242" s="9" t="n">
+        <v>19.712</v>
+      </c>
     </row>
     <row r="243" ht="18" customHeight="1">
       <c r="A243" s="3" t="n"/>
@@ -5488,7 +5912,9 @@
           <t>7.168 = 7.168</t>
         </is>
       </c>
-      <c r="F243" s="10" t="n"/>
+      <c r="F243" s="9" t="n">
+        <v>7.168</v>
+      </c>
     </row>
     <row r="244" ht="18" customHeight="1">
       <c r="A244" s="3" t="n"/>
@@ -5508,7 +5934,9 @@
           <t>2.11 = 2.11</t>
         </is>
       </c>
-      <c r="F244" s="10" t="n"/>
+      <c r="F244" s="9" t="n">
+        <v>2.11</v>
+      </c>
     </row>
     <row r="245" ht="18" customHeight="1">
       <c r="A245" s="3" t="n"/>
@@ -5528,7 +5956,9 @@
           <t>3.961 + 3.728 = 7.689</t>
         </is>
       </c>
-      <c r="F245" s="10" t="n"/>
+      <c r="F245" s="9" t="n">
+        <v>7.689</v>
+      </c>
     </row>
     <row r="246" ht="18" customHeight="1">
       <c r="A246" s="3" t="n"/>
@@ -5548,7 +5978,9 @@
           <t>2.394 = 2.394</t>
         </is>
       </c>
-      <c r="F246" s="10" t="n"/>
+      <c r="F246" s="9" t="n">
+        <v>2.394</v>
+      </c>
     </row>
     <row r="247" ht="18" customHeight="1">
       <c r="A247" s="3" t="n"/>
@@ -5568,7 +6000,9 @@
           <t>2.394 = 2.394</t>
         </is>
       </c>
-      <c r="F247" s="10" t="n"/>
+      <c r="F247" s="9" t="n">
+        <v>2.394</v>
+      </c>
     </row>
     <row r="248" ht="18" customHeight="1">
       <c r="A248" s="3" t="n"/>
@@ -5588,7 +6022,9 @@
           <t>2.394 = 2.394</t>
         </is>
       </c>
-      <c r="F248" s="10" t="n"/>
+      <c r="F248" s="9" t="n">
+        <v>2.394</v>
+      </c>
     </row>
     <row r="249" ht="18" customHeight="1">
       <c r="A249" s="3" t="n"/>
@@ -5608,7 +6044,9 @@
           <t>2.457 = 2.457</t>
         </is>
       </c>
-      <c r="F249" s="10" t="n"/>
+      <c r="F249" s="9" t="n">
+        <v>2.457</v>
+      </c>
     </row>
     <row r="250" ht="18" customHeight="1">
       <c r="A250" s="3" t="n"/>
@@ -5628,7 +6066,9 @@
           <t>2.394 = 2.394</t>
         </is>
       </c>
-      <c r="F250" s="10" t="n"/>
+      <c r="F250" s="9" t="n">
+        <v>2.394</v>
+      </c>
     </row>
     <row r="251" ht="18" customHeight="1">
       <c r="A251" s="3" t="n"/>
@@ -5648,7 +6088,9 @@
           <t>4.914 = 4.914</t>
         </is>
       </c>
-      <c r="F251" s="10" t="n"/>
+      <c r="F251" s="9" t="n">
+        <v>4.914</v>
+      </c>
     </row>
     <row r="252" ht="18" customHeight="1">
       <c r="A252" s="3" t="n"/>
@@ -5668,7 +6110,9 @@
           <t>18.688 = 18.688</t>
         </is>
       </c>
-      <c r="F252" s="10" t="n"/>
+      <c r="F252" s="9" t="n">
+        <v>18.688</v>
+      </c>
     </row>
     <row r="253" ht="18" customHeight="1">
       <c r="A253" s="3" t="n"/>
@@ -5688,7 +6132,9 @@
           <t>3.165 = 3.165</t>
         </is>
       </c>
-      <c r="F253" s="10" t="n"/>
+      <c r="F253" s="9" t="n">
+        <v>3.165</v>
+      </c>
     </row>
     <row r="254" ht="18" customHeight="1">
       <c r="A254" s="3" t="n"/>
@@ -5708,7 +6154,9 @@
           <t>19.712 = 19.712</t>
         </is>
       </c>
-      <c r="F254" s="10" t="n"/>
+      <c r="F254" s="9" t="n">
+        <v>19.712</v>
+      </c>
     </row>
     <row r="255" ht="18" customHeight="1">
       <c r="A255" s="3" t="n"/>
@@ -5728,7 +6176,9 @@
           <t>7.168 = 7.168</t>
         </is>
       </c>
-      <c r="F255" s="10" t="n"/>
+      <c r="F255" s="9" t="n">
+        <v>7.168</v>
+      </c>
     </row>
     <row r="256" ht="18" customHeight="1">
       <c r="A256" s="3" t="n"/>
@@ -5748,7 +6198,9 @@
           <t>2.11 = 2.11</t>
         </is>
       </c>
-      <c r="F256" s="10" t="n"/>
+      <c r="F256" s="9" t="n">
+        <v>2.11</v>
+      </c>
     </row>
     <row r="257" ht="18" customHeight="1">
       <c r="A257" s="3" t="n"/>
@@ -5768,7 +6220,9 @@
           <t>3.728 + 3.961 = 7.689</t>
         </is>
       </c>
-      <c r="F257" s="10" t="n"/>
+      <c r="F257" s="9" t="n">
+        <v>7.689</v>
+      </c>
     </row>
     <row r="258" ht="18" customHeight="1">
       <c r="A258" s="3" t="n"/>
@@ -5788,7 +6242,9 @@
           <t>2.394 + 2.394 = 4.788</t>
         </is>
       </c>
-      <c r="F258" s="10" t="n"/>
+      <c r="F258" s="9" t="n">
+        <v>4.788</v>
+      </c>
     </row>
     <row r="259" ht="18" customHeight="1">
       <c r="A259" s="3" t="n"/>
@@ -5808,7 +6264,9 @@
           <t>2.394 + 2.394 = 4.788</t>
         </is>
       </c>
-      <c r="F259" s="10" t="n"/>
+      <c r="F259" s="9" t="n">
+        <v>4.788</v>
+      </c>
     </row>
     <row r="260" ht="18" customHeight="1">
       <c r="A260" s="3" t="n"/>
@@ -5828,7 +6286,9 @@
           <t>2.457 = 2.457</t>
         </is>
       </c>
-      <c r="F260" s="10" t="n"/>
+      <c r="F260" s="9" t="n">
+        <v>2.457</v>
+      </c>
     </row>
     <row r="261" ht="18" customHeight="1">
       <c r="A261" s="3" t="n"/>
@@ -5848,7 +6308,9 @@
           <t>2.142 = 2.142</t>
         </is>
       </c>
-      <c r="F261" s="10" t="n"/>
+      <c r="F261" s="9" t="n">
+        <v>2.142</v>
+      </c>
     </row>
     <row r="262" ht="18" customHeight="1">
       <c r="A262" s="3" t="n"/>
@@ -5868,7 +6330,9 @@
           <t>18.688 = 18.688</t>
         </is>
       </c>
-      <c r="F262" s="10" t="n"/>
+      <c r="F262" s="9" t="n">
+        <v>18.688</v>
+      </c>
     </row>
     <row r="263" ht="18" customHeight="1">
       <c r="A263" s="3" t="n"/>
@@ -5888,7 +6352,9 @@
           <t>19.712 = 19.712</t>
         </is>
       </c>
-      <c r="F263" s="10" t="n"/>
+      <c r="F263" s="9" t="n">
+        <v>19.712</v>
+      </c>
     </row>
     <row r="264" ht="18" customHeight="1">
       <c r="A264" s="3" t="n"/>
@@ -5908,7 +6374,9 @@
           <t>3.961 = 3.961</t>
         </is>
       </c>
-      <c r="F264" s="10" t="n"/>
+      <c r="F264" s="9" t="n">
+        <v>3.961</v>
+      </c>
     </row>
     <row r="265" ht="18" customHeight="1">
       <c r="A265" s="3" t="n"/>
@@ -5928,7 +6396,9 @@
           <t>15.36 = 15.36</t>
         </is>
       </c>
-      <c r="F265" s="10" t="n"/>
+      <c r="F265" s="9" t="n">
+        <v>15.36</v>
+      </c>
     </row>
     <row r="266" ht="18" customHeight="1">
       <c r="A266" s="3" t="n"/>
@@ -5948,7 +6418,9 @@
           <t>4.608 = 4.608</t>
         </is>
       </c>
-      <c r="F266" s="10" t="n"/>
+      <c r="F266" s="9" t="n">
+        <v>4.608</v>
+      </c>
     </row>
     <row r="267" ht="18" customHeight="1">
       <c r="A267" s="3" t="n"/>
@@ -5968,7 +6440,9 @@
           <t>4.608 = 4.608</t>
         </is>
       </c>
-      <c r="F267" s="10" t="n"/>
+      <c r="F267" s="9" t="n">
+        <v>4.608</v>
+      </c>
     </row>
     <row r="268" ht="18" customHeight="1">
       <c r="A268" s="3" t="n"/>
@@ -5988,7 +6462,9 @@
           <t>3.495 = 3.495</t>
         </is>
       </c>
-      <c r="F268" s="10" t="n"/>
+      <c r="F268" s="9" t="n">
+        <v>3.495</v>
+      </c>
     </row>
     <row r="269" ht="46" customHeight="1">
       <c r="A269" s="3" t="n"/>
@@ -6004,7 +6480,9 @@
           <t>(3.24 + 2.16 + 11.598 + 3.584 + 18.031 + 3.584 + 0.504 + 4.788 + 2.457 + 2.142 + 19.712 + 2.394 + 2.394 + 2.394 + 2.457 + 2.394 + 4.914 + 18.688 + 3.165 + 19.712 + 7.168 + 2.11 + 7.689 + 2.394 + 2.394 + 2.394 + 2.457 + 2.394 + 4.914 + 18.688 + 3.165 + 19.712 + 7.168 + 2.11 + 7.689 + 4.788 + 4.788 + 2.457 + 2.142 + 18.688 + 19.712 + 3.961 + 15.36 + 4.608 + 4.608 + 3.495) ÷ 1000 = 0.307</t>
         </is>
       </c>
-      <c r="F269" s="10" t="n"/>
+      <c r="F269" s="10" t="n">
+        <v>0.307</v>
+      </c>
     </row>
     <row r="270" ht="18" customHeight="1">
       <c r="A270" s="3" t="n">
@@ -6031,7 +6509,7 @@
         </is>
       </c>
       <c r="F270" s="9" t="n">
-        <v>1.428</v>
+        <v>51.34</v>
       </c>
     </row>
     <row r="271" ht="18" customHeight="1">
@@ -6052,7 +6530,9 @@
           <t>34.428 = 34.428</t>
         </is>
       </c>
-      <c r="F271" s="10" t="n"/>
+      <c r="F271" s="9" t="n">
+        <v>34.428</v>
+      </c>
     </row>
     <row r="272" ht="18" customHeight="1">
       <c r="A272" s="3" t="n"/>
@@ -6072,7 +6552,9 @@
           <t>19.328 = 19.328</t>
         </is>
       </c>
-      <c r="F272" s="10" t="n"/>
+      <c r="F272" s="9" t="n">
+        <v>19.328</v>
+      </c>
     </row>
     <row r="273" ht="18" customHeight="1">
       <c r="A273" s="3" t="n"/>
@@ -6092,7 +6574,9 @@
           <t>6.454 = 6.454</t>
         </is>
       </c>
-      <c r="F273" s="10" t="n"/>
+      <c r="F273" s="9" t="n">
+        <v>6.454</v>
+      </c>
     </row>
     <row r="274" ht="18" customHeight="1">
       <c r="A274" s="3" t="n"/>
@@ -6112,7 +6596,9 @@
           <t>12.908 + 85.84 = 98.748</t>
         </is>
       </c>
-      <c r="F274" s="10" t="n"/>
+      <c r="F274" s="9" t="n">
+        <v>98.748</v>
+      </c>
     </row>
     <row r="275" ht="18" customHeight="1">
       <c r="A275" s="3" t="n"/>
@@ -6132,7 +6618,9 @@
           <t>6.454 + 42.92 = 49.374</t>
         </is>
       </c>
-      <c r="F275" s="10" t="n"/>
+      <c r="F275" s="9" t="n">
+        <v>49.374</v>
+      </c>
     </row>
     <row r="276" ht="18" customHeight="1">
       <c r="A276" s="3" t="n"/>
@@ -6152,7 +6640,9 @@
           <t>19.362 + 25.042 = 44.404</t>
         </is>
       </c>
-      <c r="F276" s="10" t="n"/>
+      <c r="F276" s="9" t="n">
+        <v>44.404</v>
+      </c>
     </row>
     <row r="277" ht="18" customHeight="1">
       <c r="A277" s="3" t="n"/>
@@ -6172,7 +6662,9 @@
           <t>45.178 = 45.178</t>
         </is>
       </c>
-      <c r="F277" s="10" t="n"/>
+      <c r="F277" s="9" t="n">
+        <v>45.178</v>
+      </c>
     </row>
     <row r="278" ht="18" customHeight="1">
       <c r="A278" s="3" t="n"/>
@@ -6192,7 +6684,9 @@
           <t>33.653 = 33.653</t>
         </is>
       </c>
-      <c r="F278" s="10" t="n"/>
+      <c r="F278" s="9" t="n">
+        <v>33.653</v>
+      </c>
     </row>
     <row r="279" ht="18" customHeight="1">
       <c r="A279" s="3" t="n"/>
@@ -6212,7 +6706,9 @@
           <t>6.454 + 36.54 = 42.994</t>
         </is>
       </c>
-      <c r="F279" s="10" t="n"/>
+      <c r="F279" s="9" t="n">
+        <v>42.994</v>
+      </c>
     </row>
     <row r="280" ht="18" customHeight="1">
       <c r="A280" s="3" t="n"/>
@@ -6232,7 +6728,9 @@
           <t>6.454 + 49.88 = 56.334</t>
         </is>
       </c>
-      <c r="F280" s="10" t="n"/>
+      <c r="F280" s="9" t="n">
+        <v>56.334</v>
+      </c>
     </row>
     <row r="281" ht="18" customHeight="1">
       <c r="A281" s="3" t="n"/>
@@ -6252,7 +6750,9 @@
           <t>6.454 + 46.4 = 52.854</t>
         </is>
       </c>
-      <c r="F281" s="10" t="n"/>
+      <c r="F281" s="9" t="n">
+        <v>52.854</v>
+      </c>
     </row>
     <row r="282" ht="18" customHeight="1">
       <c r="A282" s="3" t="n"/>
@@ -6272,7 +6772,9 @@
           <t>6.454 + 49.88 = 56.334</t>
         </is>
       </c>
-      <c r="F282" s="10" t="n"/>
+      <c r="F282" s="9" t="n">
+        <v>56.334</v>
+      </c>
     </row>
     <row r="283" ht="18" customHeight="1">
       <c r="A283" s="3" t="n"/>
@@ -6292,7 +6794,9 @@
           <t>6.454 + 46.4 = 52.854</t>
         </is>
       </c>
-      <c r="F283" s="10" t="n"/>
+      <c r="F283" s="9" t="n">
+        <v>52.854</v>
+      </c>
     </row>
     <row r="284" ht="18" customHeight="1">
       <c r="A284" s="3" t="n"/>
@@ -6312,7 +6816,9 @@
           <t>19.362 + 25.042 = 44.404</t>
         </is>
       </c>
-      <c r="F284" s="10" t="n"/>
+      <c r="F284" s="9" t="n">
+        <v>44.404</v>
+      </c>
     </row>
     <row r="285" ht="18" customHeight="1">
       <c r="A285" s="3" t="n"/>
@@ -6332,7 +6838,9 @@
           <t>47.944 = 47.944</t>
         </is>
       </c>
-      <c r="F285" s="10" t="n"/>
+      <c r="F285" s="9" t="n">
+        <v>47.944</v>
+      </c>
     </row>
     <row r="286" ht="18" customHeight="1">
       <c r="A286" s="3" t="n"/>
@@ -6352,7 +6860,9 @@
           <t>6.454 + 36.54 = 42.994</t>
         </is>
       </c>
-      <c r="F286" s="10" t="n"/>
+      <c r="F286" s="9" t="n">
+        <v>42.994</v>
+      </c>
     </row>
     <row r="287" ht="18" customHeight="1">
       <c r="A287" s="3" t="n"/>
@@ -6372,7 +6882,9 @@
           <t>6.454 + 49.88 = 56.334</t>
         </is>
       </c>
-      <c r="F287" s="10" t="n"/>
+      <c r="F287" s="9" t="n">
+        <v>56.334</v>
+      </c>
     </row>
     <row r="288" ht="18" customHeight="1">
       <c r="A288" s="3" t="n"/>
@@ -6392,7 +6904,9 @@
           <t>6.454 + 46.4 = 52.854</t>
         </is>
       </c>
-      <c r="F288" s="10" t="n"/>
+      <c r="F288" s="9" t="n">
+        <v>52.854</v>
+      </c>
     </row>
     <row r="289" ht="18" customHeight="1">
       <c r="A289" s="3" t="n"/>
@@ -6412,7 +6926,9 @@
           <t>6.454 + 49.88 = 56.334</t>
         </is>
       </c>
-      <c r="F289" s="10" t="n"/>
+      <c r="F289" s="9" t="n">
+        <v>56.334</v>
+      </c>
     </row>
     <row r="290" ht="18" customHeight="1">
       <c r="A290" s="3" t="n"/>
@@ -6432,7 +6948,9 @@
           <t>6.454 + 46.4 = 52.854</t>
         </is>
       </c>
-      <c r="F290" s="10" t="n"/>
+      <c r="F290" s="9" t="n">
+        <v>52.854</v>
+      </c>
     </row>
     <row r="291" ht="18" customHeight="1">
       <c r="A291" s="3" t="n"/>
@@ -6452,7 +6970,9 @@
           <t>19.362 + 25.042 = 44.404</t>
         </is>
       </c>
-      <c r="F291" s="10" t="n"/>
+      <c r="F291" s="9" t="n">
+        <v>44.404</v>
+      </c>
     </row>
     <row r="292" ht="18" customHeight="1">
       <c r="A292" s="3" t="n"/>
@@ -6472,7 +6992,9 @@
           <t>47.944 = 47.944</t>
         </is>
       </c>
-      <c r="F292" s="10" t="n"/>
+      <c r="F292" s="9" t="n">
+        <v>47.944</v>
+      </c>
     </row>
     <row r="293" ht="18" customHeight="1">
       <c r="A293" s="3" t="n"/>
@@ -6492,7 +7014,9 @@
           <t>6.454 + 36.54 + 6.454 + 36.54 = 85.988</t>
         </is>
       </c>
-      <c r="F293" s="10" t="n"/>
+      <c r="F293" s="9" t="n">
+        <v>85.988</v>
+      </c>
     </row>
     <row r="294" ht="18" customHeight="1">
       <c r="A294" s="3" t="n"/>
@@ -6512,7 +7036,9 @@
           <t>6.454 + 46.4 + 6.454 + 46.4 = 105.708</t>
         </is>
       </c>
-      <c r="F294" s="10" t="n"/>
+      <c r="F294" s="9" t="n">
+        <v>105.708</v>
+      </c>
     </row>
     <row r="295" ht="18" customHeight="1">
       <c r="A295" s="3" t="n"/>
@@ -6532,7 +7058,9 @@
           <t>6.454 + 49.88 = 56.334</t>
         </is>
       </c>
-      <c r="F295" s="10" t="n"/>
+      <c r="F295" s="9" t="n">
+        <v>56.334</v>
+      </c>
     </row>
     <row r="296" ht="18" customHeight="1">
       <c r="A296" s="3" t="n"/>
@@ -6552,7 +7080,9 @@
           <t>19.362 + 25.042 = 44.404</t>
         </is>
       </c>
-      <c r="F296" s="10" t="n"/>
+      <c r="F296" s="9" t="n">
+        <v>44.404</v>
+      </c>
     </row>
     <row r="297" ht="18" customHeight="1">
       <c r="A297" s="3" t="n"/>
@@ -6572,7 +7102,9 @@
           <t>45.178 = 45.178</t>
         </is>
       </c>
-      <c r="F297" s="10" t="n"/>
+      <c r="F297" s="9" t="n">
+        <v>45.178</v>
+      </c>
     </row>
     <row r="298" ht="32" customHeight="1">
       <c r="A298" s="3" t="n"/>
@@ -6588,7 +7120,9 @@
           <t>(51.34 + 34.428 + 19.328 + 6.454 + 98.748 + 49.374 + 44.404 + 45.178 + 33.653 + 42.994 + 56.334 + 52.854 + 56.334 + 52.854 + 44.404 + 47.944 + 42.994 + 56.334 + 52.854 + 56.334 + 52.854 + 44.404 + 47.944 + 85.988 + 105.708 + 56.334 + 44.404 + 45.178) ÷ 1000 = 1.428</t>
         </is>
       </c>
-      <c r="F298" s="10" t="n"/>
+      <c r="F298" s="10" t="n">
+        <v>1.428</v>
+      </c>
     </row>
     <row r="299" ht="18" customHeight="1">
       <c r="A299" s="3" t="n">
@@ -6615,7 +7149,7 @@
         </is>
       </c>
       <c r="F299" s="9" t="n">
-        <v>0.717</v>
+        <v>31.48</v>
       </c>
     </row>
     <row r="300" ht="18" customHeight="1">
@@ -6636,7 +7170,9 @@
           <t>21.294 = 21.294</t>
         </is>
       </c>
-      <c r="F300" s="10" t="n"/>
+      <c r="F300" s="9" t="n">
+        <v>21.294</v>
+      </c>
     </row>
     <row r="301" ht="18" customHeight="1">
       <c r="A301" s="3" t="n"/>
@@ -6656,7 +7192,9 @@
           <t>11.606 = 11.606</t>
         </is>
       </c>
-      <c r="F301" s="10" t="n"/>
+      <c r="F301" s="9" t="n">
+        <v>11.606</v>
+      </c>
     </row>
     <row r="302" ht="18" customHeight="1">
       <c r="A302" s="3" t="n"/>
@@ -6676,7 +7214,9 @@
           <t>24.304 + 24.082 = 48.386</t>
         </is>
       </c>
-      <c r="F302" s="10" t="n"/>
+      <c r="F302" s="9" t="n">
+        <v>48.386</v>
+      </c>
     </row>
     <row r="303" ht="18" customHeight="1">
       <c r="A303" s="3" t="n"/>
@@ -6696,7 +7236,9 @@
           <t>48.164 = 48.164</t>
         </is>
       </c>
-      <c r="F303" s="10" t="n"/>
+      <c r="F303" s="9" t="n">
+        <v>48.164</v>
+      </c>
     </row>
     <row r="304" ht="18" customHeight="1">
       <c r="A304" s="3" t="n"/>
@@ -6716,7 +7258,9 @@
           <t>24.082 = 24.082</t>
         </is>
       </c>
-      <c r="F304" s="10" t="n"/>
+      <c r="F304" s="9" t="n">
+        <v>24.082</v>
+      </c>
     </row>
     <row r="305" ht="18" customHeight="1">
       <c r="A305" s="3" t="n"/>
@@ -6736,7 +7280,9 @@
           <t>23.212 = 23.212</t>
         </is>
       </c>
-      <c r="F305" s="10" t="n"/>
+      <c r="F305" s="9" t="n">
+        <v>23.212</v>
+      </c>
     </row>
     <row r="306" ht="18" customHeight="1">
       <c r="A306" s="3" t="n"/>
@@ -6756,7 +7302,9 @@
           <t>24.082 = 24.082</t>
         </is>
       </c>
-      <c r="F306" s="10" t="n"/>
+      <c r="F306" s="9" t="n">
+        <v>24.082</v>
+      </c>
     </row>
     <row r="307" ht="18" customHeight="1">
       <c r="A307" s="3" t="n"/>
@@ -6776,7 +7324,9 @@
           <t>24.082 = 24.082</t>
         </is>
       </c>
-      <c r="F307" s="10" t="n"/>
+      <c r="F307" s="9" t="n">
+        <v>24.082</v>
+      </c>
     </row>
     <row r="308" ht="18" customHeight="1">
       <c r="A308" s="3" t="n"/>
@@ -6796,7 +7346,9 @@
           <t>24.082 = 24.082</t>
         </is>
       </c>
-      <c r="F308" s="10" t="n"/>
+      <c r="F308" s="9" t="n">
+        <v>24.082</v>
+      </c>
     </row>
     <row r="309" ht="18" customHeight="1">
       <c r="A309" s="3" t="n"/>
@@ -6816,7 +7368,9 @@
           <t>24.082 + 2.718 = 26.8</t>
         </is>
       </c>
-      <c r="F309" s="10" t="n"/>
+      <c r="F309" s="9" t="n">
+        <v>26.8</v>
+      </c>
     </row>
     <row r="310" ht="18" customHeight="1">
       <c r="A310" s="3" t="n"/>
@@ -6836,7 +7390,9 @@
           <t>24.082 = 24.082</t>
         </is>
       </c>
-      <c r="F310" s="10" t="n"/>
+      <c r="F310" s="9" t="n">
+        <v>24.082</v>
+      </c>
     </row>
     <row r="311" ht="18" customHeight="1">
       <c r="A311" s="3" t="n"/>
@@ -6856,7 +7412,9 @@
           <t>55.376 = 55.376</t>
         </is>
       </c>
-      <c r="F311" s="10" t="n"/>
+      <c r="F311" s="9" t="n">
+        <v>55.376</v>
+      </c>
     </row>
     <row r="312" ht="18" customHeight="1">
       <c r="A312" s="3" t="n"/>
@@ -6876,7 +7434,9 @@
           <t>24.082 = 24.082</t>
         </is>
       </c>
-      <c r="F312" s="10" t="n"/>
+      <c r="F312" s="9" t="n">
+        <v>24.082</v>
+      </c>
     </row>
     <row r="313" ht="18" customHeight="1">
       <c r="A313" s="3" t="n"/>
@@ -6896,7 +7456,9 @@
           <t>24.082 = 24.082</t>
         </is>
       </c>
-      <c r="F313" s="10" t="n"/>
+      <c r="F313" s="9" t="n">
+        <v>24.082</v>
+      </c>
     </row>
     <row r="314" ht="18" customHeight="1">
       <c r="A314" s="3" t="n"/>
@@ -6916,7 +7478,9 @@
           <t>24.082 = 24.082</t>
         </is>
       </c>
-      <c r="F314" s="10" t="n"/>
+      <c r="F314" s="9" t="n">
+        <v>24.082</v>
+      </c>
     </row>
     <row r="315" ht="18" customHeight="1">
       <c r="A315" s="3" t="n"/>
@@ -6936,7 +7500,9 @@
           <t>24.082 + 2.718 = 26.8</t>
         </is>
       </c>
-      <c r="F315" s="10" t="n"/>
+      <c r="F315" s="9" t="n">
+        <v>26.8</v>
+      </c>
     </row>
     <row r="316" ht="18" customHeight="1">
       <c r="A316" s="3" t="n"/>
@@ -6956,7 +7522,9 @@
           <t>24.082 = 24.082</t>
         </is>
       </c>
-      <c r="F316" s="10" t="n"/>
+      <c r="F316" s="9" t="n">
+        <v>24.082</v>
+      </c>
     </row>
     <row r="317" ht="18" customHeight="1">
       <c r="A317" s="3" t="n"/>
@@ -6976,7 +7544,9 @@
           <t>55.376 = 55.376</t>
         </is>
       </c>
-      <c r="F317" s="10" t="n"/>
+      <c r="F317" s="9" t="n">
+        <v>55.376</v>
+      </c>
     </row>
     <row r="318" ht="18" customHeight="1">
       <c r="A318" s="3" t="n"/>
@@ -6996,7 +7566,9 @@
           <t>24.082 + 2.718 + 24.082 = 50.882</t>
         </is>
       </c>
-      <c r="F318" s="10" t="n"/>
+      <c r="F318" s="9" t="n">
+        <v>50.882</v>
+      </c>
     </row>
     <row r="319" ht="18" customHeight="1">
       <c r="A319" s="3" t="n"/>
@@ -7016,7 +7588,9 @@
           <t>24.082 + 2.718 + 24.082 = 50.882</t>
         </is>
       </c>
-      <c r="F319" s="10" t="n"/>
+      <c r="F319" s="9" t="n">
+        <v>50.882</v>
+      </c>
     </row>
     <row r="320" ht="18" customHeight="1">
       <c r="A320" s="3" t="n"/>
@@ -7036,7 +7610,9 @@
           <t>24.082 + 2.718 = 26.8</t>
         </is>
       </c>
-      <c r="F320" s="10" t="n"/>
+      <c r="F320" s="9" t="n">
+        <v>26.8</v>
+      </c>
     </row>
     <row r="321" ht="18" customHeight="1">
       <c r="A321" s="3" t="n"/>
@@ -7056,7 +7632,9 @@
           <t>23.212 = 23.212</t>
         </is>
       </c>
-      <c r="F321" s="10" t="n"/>
+      <c r="F321" s="9" t="n">
+        <v>23.212</v>
+      </c>
     </row>
     <row r="322" ht="32" customHeight="1">
       <c r="A322" s="3" t="n"/>
@@ -7072,7 +7650,9 @@
           <t>(31.48 + 21.294 + 11.606 + 48.386 + 48.164 + 24.082 + 23.212 + 24.082 + 24.082 + 24.082 + 26.8 + 24.082 + 55.376 + 24.082 + 24.082 + 24.082 + 26.8 + 24.082 + 55.376 + 50.882 + 50.882 + 26.8 + 23.212) ÷ 1000 = 0.717</t>
         </is>
       </c>
-      <c r="F322" s="10" t="n"/>
+      <c r="F322" s="10" t="n">
+        <v>0.717</v>
+      </c>
     </row>
     <row r="323" ht="18" customHeight="1">
       <c r="A323" s="3" t="n">
@@ -7099,7 +7679,7 @@
         </is>
       </c>
       <c r="F323" s="9" t="n">
-        <v>0.134</v>
+        <v>8.619999999999999</v>
       </c>
     </row>
     <row r="324" ht="18" customHeight="1">
@@ -7120,7 +7700,9 @@
           <t>12.13 = 12.13</t>
         </is>
       </c>
-      <c r="F324" s="10" t="n"/>
+      <c r="F324" s="9" t="n">
+        <v>12.13</v>
+      </c>
     </row>
     <row r="325" ht="18" customHeight="1">
       <c r="A325" s="3" t="n"/>
@@ -7140,7 +7722,9 @@
           <t>6.322 + 7.755 = 14.077</t>
         </is>
       </c>
-      <c r="F325" s="10" t="n"/>
+      <c r="F325" s="9" t="n">
+        <v>14.077</v>
+      </c>
     </row>
     <row r="326" ht="18" customHeight="1">
       <c r="A326" s="3" t="n"/>
@@ -7160,7 +7744,9 @@
           <t>9.588 + 9.104 = 18.692</t>
         </is>
       </c>
-      <c r="F326" s="10" t="n"/>
+      <c r="F326" s="9" t="n">
+        <v>18.692</v>
+      </c>
     </row>
     <row r="327" ht="18" customHeight="1">
       <c r="A327" s="3" t="n"/>
@@ -7180,7 +7766,9 @@
           <t>8.62 = 8.62</t>
         </is>
       </c>
-      <c r="F327" s="10" t="n"/>
+      <c r="F327" s="9" t="n">
+        <v>8.619999999999999</v>
+      </c>
     </row>
     <row r="328" ht="18" customHeight="1">
       <c r="A328" s="3" t="n"/>
@@ -7200,7 +7788,9 @@
           <t>12.13 = 12.13</t>
         </is>
       </c>
-      <c r="F328" s="10" t="n"/>
+      <c r="F328" s="9" t="n">
+        <v>12.13</v>
+      </c>
     </row>
     <row r="329" ht="18" customHeight="1">
       <c r="A329" s="3" t="n"/>
@@ -7220,7 +7810,9 @@
           <t>6.322 + 7.755 = 14.077</t>
         </is>
       </c>
-      <c r="F329" s="10" t="n"/>
+      <c r="F329" s="9" t="n">
+        <v>14.077</v>
+      </c>
     </row>
     <row r="330" ht="18" customHeight="1">
       <c r="A330" s="3" t="n"/>
@@ -7240,7 +7832,9 @@
           <t>9.104 + 9.588 = 18.692</t>
         </is>
       </c>
-      <c r="F330" s="10" t="n"/>
+      <c r="F330" s="9" t="n">
+        <v>18.692</v>
+      </c>
     </row>
     <row r="331" ht="18" customHeight="1">
       <c r="A331" s="3" t="n"/>
@@ -7260,7 +7854,9 @@
           <t>9.588 = 9.588</t>
         </is>
       </c>
-      <c r="F331" s="10" t="n"/>
+      <c r="F331" s="9" t="n">
+        <v>9.587999999999999</v>
+      </c>
     </row>
     <row r="332" ht="18" customHeight="1">
       <c r="A332" s="3" t="n"/>
@@ -7280,7 +7876,9 @@
           <t>8.757 + 8.241 = 16.998</t>
         </is>
       </c>
-      <c r="F332" s="10" t="n"/>
+      <c r="F332" s="9" t="n">
+        <v>16.998</v>
+      </c>
     </row>
     <row r="333" ht="18" customHeight="1">
       <c r="A333" s="3" t="n"/>
@@ -7296,7 +7894,9 @@
           <t>(8.62 + 12.13 + 14.077 + 18.692 + 8.62 + 12.13 + 14.077 + 18.692 + 9.588 + 16.998) ÷ 1000 = 0.134</t>
         </is>
       </c>
-      <c r="F333" s="10" t="n"/>
+      <c r="F333" s="10" t="n">
+        <v>0.134</v>
+      </c>
     </row>
     <row r="334" ht="18" customHeight="1">
       <c r="A334" s="3" t="n">
@@ -7323,7 +7923,7 @@
         </is>
       </c>
       <c r="F334" s="9" t="n">
-        <v>2.347</v>
+        <v>90.342</v>
       </c>
     </row>
     <row r="335" ht="18" customHeight="1">
@@ -7344,7 +7944,9 @@
           <t>38.658 = 38.658</t>
         </is>
       </c>
-      <c r="F335" s="10" t="n"/>
+      <c r="F335" s="9" t="n">
+        <v>38.658</v>
+      </c>
     </row>
     <row r="336" ht="18" customHeight="1">
       <c r="A336" s="3" t="n"/>
@@ -7364,7 +7966,9 @@
           <t>152.658 = 152.658</t>
         </is>
       </c>
-      <c r="F336" s="10" t="n"/>
+      <c r="F336" s="9" t="n">
+        <v>152.658</v>
+      </c>
     </row>
     <row r="337" ht="18" customHeight="1">
       <c r="A337" s="3" t="n"/>
@@ -7384,7 +7988,9 @@
           <t>12.728 + 16.395 = 29.123</t>
         </is>
       </c>
-      <c r="F337" s="10" t="n"/>
+      <c r="F337" s="9" t="n">
+        <v>29.123</v>
+      </c>
     </row>
     <row r="338" ht="18" customHeight="1">
       <c r="A338" s="3" t="n"/>
@@ -7404,7 +8010,9 @@
           <t>24.222 + 24.321 + 8.428 = 56.971</t>
         </is>
       </c>
-      <c r="F338" s="10" t="n"/>
+      <c r="F338" s="9" t="n">
+        <v>56.971</v>
+      </c>
     </row>
     <row r="339" ht="18" customHeight="1">
       <c r="A339" s="3" t="n"/>
@@ -7424,7 +8032,9 @@
           <t>76.377 = 76.377</t>
         </is>
       </c>
-      <c r="F339" s="10" t="n"/>
+      <c r="F339" s="9" t="n">
+        <v>76.377</v>
+      </c>
     </row>
     <row r="340" ht="18" customHeight="1">
       <c r="A340" s="3" t="n"/>
@@ -7444,7 +8054,9 @@
           <t>152.754 = 152.754</t>
         </is>
       </c>
-      <c r="F340" s="10" t="n"/>
+      <c r="F340" s="9" t="n">
+        <v>152.754</v>
+      </c>
     </row>
     <row r="341" ht="18" customHeight="1">
       <c r="A341" s="3" t="n"/>
@@ -7464,7 +8076,9 @@
           <t>76.377 + 74.106 = 150.483</t>
         </is>
       </c>
-      <c r="F341" s="10" t="n"/>
+      <c r="F341" s="9" t="n">
+        <v>150.483</v>
+      </c>
     </row>
     <row r="342" ht="18" customHeight="1">
       <c r="A342" s="3" t="n"/>
@@ -7484,7 +8098,9 @@
           <t>7.534 = 7.534</t>
         </is>
       </c>
-      <c r="F342" s="10" t="n"/>
+      <c r="F342" s="9" t="n">
+        <v>7.534</v>
+      </c>
     </row>
     <row r="343" ht="18" customHeight="1">
       <c r="A343" s="3" t="n"/>
@@ -7504,7 +8120,9 @@
           <t>15.068 = 15.068</t>
         </is>
       </c>
-      <c r="F343" s="10" t="n"/>
+      <c r="F343" s="9" t="n">
+        <v>15.068</v>
+      </c>
     </row>
     <row r="344" ht="18" customHeight="1">
       <c r="A344" s="3" t="n"/>
@@ -7524,7 +8142,9 @@
           <t>7.534 = 7.534</t>
         </is>
       </c>
-      <c r="F344" s="10" t="n"/>
+      <c r="F344" s="9" t="n">
+        <v>7.534</v>
+      </c>
     </row>
     <row r="345" ht="18" customHeight="1">
       <c r="A345" s="3" t="n"/>
@@ -7544,7 +8164,9 @@
           <t>15.068 = 15.068</t>
         </is>
       </c>
-      <c r="F345" s="10" t="n"/>
+      <c r="F345" s="9" t="n">
+        <v>15.068</v>
+      </c>
     </row>
     <row r="346" ht="18" customHeight="1">
       <c r="A346" s="3" t="n"/>
@@ -7564,7 +8186,9 @@
           <t>7.534 = 7.534</t>
         </is>
       </c>
-      <c r="F346" s="10" t="n"/>
+      <c r="F346" s="9" t="n">
+        <v>7.534</v>
+      </c>
     </row>
     <row r="347" ht="18" customHeight="1">
       <c r="A347" s="3" t="n"/>
@@ -7584,7 +8208,9 @@
           <t>24.222 + 24.321 + 8.428 = 56.971</t>
         </is>
       </c>
-      <c r="F347" s="10" t="n"/>
+      <c r="F347" s="9" t="n">
+        <v>56.971</v>
+      </c>
     </row>
     <row r="348" ht="18" customHeight="1">
       <c r="A348" s="3" t="n"/>
@@ -7604,7 +8230,9 @@
           <t>24.201 + 18.276 + 19.125 + 6.194 = 67.796</t>
         </is>
       </c>
-      <c r="F348" s="10" t="n"/>
+      <c r="F348" s="9" t="n">
+        <v>67.79600000000001</v>
+      </c>
     </row>
     <row r="349" ht="18" customHeight="1">
       <c r="A349" s="3" t="n"/>
@@ -7624,7 +8252,9 @@
           <t>152.754 = 152.754</t>
         </is>
       </c>
-      <c r="F349" s="10" t="n"/>
+      <c r="F349" s="9" t="n">
+        <v>152.754</v>
+      </c>
     </row>
     <row r="350" ht="18" customHeight="1">
       <c r="A350" s="3" t="n"/>
@@ -7644,7 +8274,9 @@
           <t>76.377 + 74.106 = 150.483</t>
         </is>
       </c>
-      <c r="F350" s="10" t="n"/>
+      <c r="F350" s="9" t="n">
+        <v>150.483</v>
+      </c>
     </row>
     <row r="351" ht="18" customHeight="1">
       <c r="A351" s="3" t="n"/>
@@ -7664,7 +8296,9 @@
           <t>6.194 = 6.194</t>
         </is>
       </c>
-      <c r="F351" s="10" t="n"/>
+      <c r="F351" s="9" t="n">
+        <v>6.194</v>
+      </c>
     </row>
     <row r="352" ht="18" customHeight="1">
       <c r="A352" s="3" t="n"/>
@@ -7684,7 +8318,9 @@
           <t>7.534 = 7.534</t>
         </is>
       </c>
-      <c r="F352" s="10" t="n"/>
+      <c r="F352" s="9" t="n">
+        <v>7.534</v>
+      </c>
     </row>
     <row r="353" ht="18" customHeight="1">
       <c r="A353" s="3" t="n"/>
@@ -7704,7 +8340,9 @@
           <t>15.068 = 15.068</t>
         </is>
       </c>
-      <c r="F353" s="10" t="n"/>
+      <c r="F353" s="9" t="n">
+        <v>15.068</v>
+      </c>
     </row>
     <row r="354" ht="18" customHeight="1">
       <c r="A354" s="3" t="n"/>
@@ -7724,7 +8362,9 @@
           <t>7.534 = 7.534</t>
         </is>
       </c>
-      <c r="F354" s="10" t="n"/>
+      <c r="F354" s="9" t="n">
+        <v>7.534</v>
+      </c>
     </row>
     <row r="355" ht="18" customHeight="1">
       <c r="A355" s="3" t="n"/>
@@ -7744,7 +8384,9 @@
           <t>15.068 = 15.068</t>
         </is>
       </c>
-      <c r="F355" s="10" t="n"/>
+      <c r="F355" s="9" t="n">
+        <v>15.068</v>
+      </c>
     </row>
     <row r="356" ht="18" customHeight="1">
       <c r="A356" s="3" t="n"/>
@@ -7764,7 +8406,9 @@
           <t>7.534 = 7.534</t>
         </is>
       </c>
-      <c r="F356" s="10" t="n"/>
+      <c r="F356" s="9" t="n">
+        <v>7.534</v>
+      </c>
     </row>
     <row r="357" ht="18" customHeight="1">
       <c r="A357" s="3" t="n"/>
@@ -7784,7 +8428,9 @@
           <t>24.222 + 24.321 + 8.428 = 56.971</t>
         </is>
       </c>
-      <c r="F357" s="10" t="n"/>
+      <c r="F357" s="9" t="n">
+        <v>56.971</v>
+      </c>
     </row>
     <row r="358" ht="18" customHeight="1">
       <c r="A358" s="3" t="n"/>
@@ -7804,7 +8450,9 @@
           <t>24.201 + 18.276 + 19.125 + 6.194 = 67.796</t>
         </is>
       </c>
-      <c r="F358" s="10" t="n"/>
+      <c r="F358" s="9" t="n">
+        <v>67.79600000000001</v>
+      </c>
     </row>
     <row r="359" ht="18" customHeight="1">
       <c r="A359" s="3" t="n"/>
@@ -7824,7 +8472,9 @@
           <t>152.754 = 152.754</t>
         </is>
       </c>
-      <c r="F359" s="10" t="n"/>
+      <c r="F359" s="9" t="n">
+        <v>152.754</v>
+      </c>
     </row>
     <row r="360" ht="18" customHeight="1">
       <c r="A360" s="3" t="n"/>
@@ -7844,7 +8494,9 @@
           <t>76.377 + 74.106 = 150.483</t>
         </is>
       </c>
-      <c r="F360" s="10" t="n"/>
+      <c r="F360" s="9" t="n">
+        <v>150.483</v>
+      </c>
     </row>
     <row r="361" ht="18" customHeight="1">
       <c r="A361" s="3" t="n"/>
@@ -7864,7 +8516,9 @@
           <t>6.194 = 6.194</t>
         </is>
       </c>
-      <c r="F361" s="10" t="n"/>
+      <c r="F361" s="9" t="n">
+        <v>6.194</v>
+      </c>
     </row>
     <row r="362" ht="18" customHeight="1">
       <c r="A362" s="3" t="n"/>
@@ -7884,7 +8538,9 @@
           <t>7.534 + 7.534 = 15.068</t>
         </is>
       </c>
-      <c r="F362" s="10" t="n"/>
+      <c r="F362" s="9" t="n">
+        <v>15.068</v>
+      </c>
     </row>
     <row r="363" ht="18" customHeight="1">
       <c r="A363" s="3" t="n"/>
@@ -7904,7 +8560,9 @@
           <t>7.534 + 7.534 = 15.068</t>
         </is>
       </c>
-      <c r="F363" s="10" t="n"/>
+      <c r="F363" s="9" t="n">
+        <v>15.068</v>
+      </c>
     </row>
     <row r="364" ht="18" customHeight="1">
       <c r="A364" s="3" t="n"/>
@@ -7924,7 +8582,9 @@
           <t>15.068 = 15.068</t>
         </is>
       </c>
-      <c r="F364" s="10" t="n"/>
+      <c r="F364" s="9" t="n">
+        <v>15.068</v>
+      </c>
     </row>
     <row r="365" ht="18" customHeight="1">
       <c r="A365" s="3" t="n"/>
@@ -7944,7 +8604,9 @@
           <t>24.222 + 24.321 + 8.428 = 56.971</t>
         </is>
       </c>
-      <c r="F365" s="10" t="n"/>
+      <c r="F365" s="9" t="n">
+        <v>56.971</v>
+      </c>
     </row>
     <row r="366" ht="18" customHeight="1">
       <c r="A366" s="3" t="n"/>
@@ -7964,7 +8626,9 @@
           <t>76.377 = 76.377</t>
         </is>
       </c>
-      <c r="F366" s="10" t="n"/>
+      <c r="F366" s="9" t="n">
+        <v>76.377</v>
+      </c>
     </row>
     <row r="367" ht="18" customHeight="1">
       <c r="A367" s="3" t="n"/>
@@ -7984,7 +8648,9 @@
           <t>77.655 + 76.377 = 154.032</t>
         </is>
       </c>
-      <c r="F367" s="10" t="n"/>
+      <c r="F367" s="9" t="n">
+        <v>154.032</v>
+      </c>
     </row>
     <row r="368" ht="18" customHeight="1">
       <c r="A368" s="3" t="n"/>
@@ -8004,7 +8670,9 @@
           <t>50.918 + 49.404 = 100.322</t>
         </is>
       </c>
-      <c r="F368" s="10" t="n"/>
+      <c r="F368" s="9" t="n">
+        <v>100.322</v>
+      </c>
     </row>
     <row r="369" ht="18" customHeight="1">
       <c r="A369" s="3" t="n"/>
@@ -8024,7 +8692,9 @@
           <t>16.752 = 16.752</t>
         </is>
       </c>
-      <c r="F369" s="10" t="n"/>
+      <c r="F369" s="9" t="n">
+        <v>16.752</v>
+      </c>
     </row>
     <row r="370" ht="18" customHeight="1">
       <c r="A370" s="3" t="n"/>
@@ -8044,7 +8714,9 @@
           <t>60.261 + 57.99 = 118.251</t>
         </is>
       </c>
-      <c r="F370" s="10" t="n"/>
+      <c r="F370" s="9" t="n">
+        <v>118.251</v>
+      </c>
     </row>
     <row r="371" ht="18" customHeight="1">
       <c r="A371" s="3" t="n"/>
@@ -8064,7 +8736,9 @@
           <t>11.892 + 17.073 = 28.965</t>
         </is>
       </c>
-      <c r="F371" s="10" t="n"/>
+      <c r="F371" s="9" t="n">
+        <v>28.965</v>
+      </c>
     </row>
     <row r="372" ht="18" customHeight="1">
       <c r="A372" s="3" t="n"/>
@@ -8084,7 +8758,9 @@
           <t>11.892 + 17.073 = 28.965</t>
         </is>
       </c>
-      <c r="F372" s="10" t="n"/>
+      <c r="F372" s="9" t="n">
+        <v>28.965</v>
+      </c>
     </row>
     <row r="373" ht="46" customHeight="1">
       <c r="A373" s="3" t="n"/>
@@ -8100,7 +8776,9 @@
           <t>(90.342 + 38.658 + 152.658 + 29.123 + 56.971 + 76.377 + 152.754 + 150.483 + 7.534 + 15.068 + 7.534 + 15.068 + 7.534 + 56.971 + 67.796 + 152.754 + 150.483 + 6.194 + 7.534 + 15.068 + 7.534 + 15.068 + 7.534 + 56.971 + 67.796 + 152.754 + 150.483 + 6.194 + 15.068 + 15.068 + 15.068 + 56.971 + 76.377 + 154.032 + 100.322 + 16.752 + 118.251 + 28.965 + 28.965) ÷ 1000 = 2.347</t>
         </is>
       </c>
-      <c r="F373" s="10" t="n"/>
+      <c r="F373" s="10" t="n">
+        <v>2.347</v>
+      </c>
     </row>
     <row r="374" ht="18" customHeight="1">
       <c r="A374" s="3" t="n">
@@ -8127,7 +8805,7 @@
         </is>
       </c>
       <c r="F374" s="9" t="n">
-        <v>2.172</v>
+        <v>327.572</v>
       </c>
     </row>
     <row r="375" ht="18" customHeight="1">
@@ -8148,7 +8826,9 @@
           <t>19.44 + 151.98 = 171.42</t>
         </is>
       </c>
-      <c r="F375" s="10" t="n"/>
+      <c r="F375" s="9" t="n">
+        <v>171.42</v>
+      </c>
     </row>
     <row r="376" ht="18" customHeight="1">
       <c r="A376" s="3" t="n"/>
@@ -8168,7 +8848,9 @@
           <t>41.262 = 41.262</t>
         </is>
       </c>
-      <c r="F376" s="10" t="n"/>
+      <c r="F376" s="9" t="n">
+        <v>41.262</v>
+      </c>
     </row>
     <row r="377" ht="18" customHeight="1">
       <c r="A377" s="3" t="n"/>
@@ -8188,7 +8870,9 @@
           <t>64.66 + 3.866 + 12.4 + 4.7 + 3.166 = 88.792</t>
         </is>
       </c>
-      <c r="F377" s="10" t="n"/>
+      <c r="F377" s="9" t="n">
+        <v>88.792</v>
+      </c>
     </row>
     <row r="378" ht="18" customHeight="1">
       <c r="A378" s="3" t="n"/>
@@ -8208,7 +8892,9 @@
           <t>55.944 + 7.658 + 13.94 + 16.6 + 4.816 + 39.612 = 138.57</t>
         </is>
       </c>
-      <c r="F378" s="10" t="n"/>
+      <c r="F378" s="9" t="n">
+        <v>138.57</v>
+      </c>
     </row>
     <row r="379" ht="18" customHeight="1">
       <c r="A379" s="3" t="n"/>
@@ -8228,7 +8914,9 @@
           <t>41.262 = 41.262</t>
         </is>
       </c>
-      <c r="F379" s="10" t="n"/>
+      <c r="F379" s="9" t="n">
+        <v>41.262</v>
+      </c>
     </row>
     <row r="380" ht="18" customHeight="1">
       <c r="A380" s="3" t="n"/>
@@ -8248,7 +8936,9 @@
           <t>41.262 = 41.262</t>
         </is>
       </c>
-      <c r="F380" s="10" t="n"/>
+      <c r="F380" s="9" t="n">
+        <v>41.262</v>
+      </c>
     </row>
     <row r="381" ht="18" customHeight="1">
       <c r="A381" s="3" t="n"/>
@@ -8268,7 +8958,9 @@
           <t>55.944 + 7.658 + 13.94 + 8.3 + 12.8 + 41.412 + 4.816 + 39.612 = 184.482</t>
         </is>
       </c>
-      <c r="F381" s="10" t="n"/>
+      <c r="F381" s="9" t="n">
+        <v>184.482</v>
+      </c>
     </row>
     <row r="382" ht="18" customHeight="1">
       <c r="A382" s="3" t="n"/>
@@ -8288,7 +8980,9 @@
           <t>21.492 + 20.292 = 41.784</t>
         </is>
       </c>
-      <c r="F382" s="10" t="n"/>
+      <c r="F382" s="9" t="n">
+        <v>41.784</v>
+      </c>
     </row>
     <row r="383" ht="18" customHeight="1">
       <c r="A383" s="3" t="n"/>
@@ -8308,7 +9002,9 @@
           <t>55.944 + 7.658 + 13.94 + 16.6 + 4.816 + 39.612 = 138.57</t>
         </is>
       </c>
-      <c r="F383" s="10" t="n"/>
+      <c r="F383" s="9" t="n">
+        <v>138.57</v>
+      </c>
     </row>
     <row r="384" ht="18" customHeight="1">
       <c r="A384" s="3" t="n"/>
@@ -8328,7 +9024,9 @@
           <t>41.262 = 41.262</t>
         </is>
       </c>
-      <c r="F384" s="10" t="n"/>
+      <c r="F384" s="9" t="n">
+        <v>41.262</v>
+      </c>
     </row>
     <row r="385" ht="18" customHeight="1">
       <c r="A385" s="3" t="n"/>
@@ -8348,7 +9046,9 @@
           <t>41.262 = 41.262</t>
         </is>
       </c>
-      <c r="F385" s="10" t="n"/>
+      <c r="F385" s="9" t="n">
+        <v>41.262</v>
+      </c>
     </row>
     <row r="386" ht="18" customHeight="1">
       <c r="A386" s="3" t="n"/>
@@ -8368,7 +9068,9 @@
           <t>55.944 + 7.658 + 13.94 + 8.3 + 12.8 + 41.412 + 4.816 + 39.612 = 184.482</t>
         </is>
       </c>
-      <c r="F386" s="10" t="n"/>
+      <c r="F386" s="9" t="n">
+        <v>184.482</v>
+      </c>
     </row>
     <row r="387" ht="18" customHeight="1">
       <c r="A387" s="3" t="n"/>
@@ -8388,7 +9090,9 @@
           <t>20.292 + 21.492 = 41.784</t>
         </is>
       </c>
-      <c r="F387" s="10" t="n"/>
+      <c r="F387" s="9" t="n">
+        <v>41.784</v>
+      </c>
     </row>
     <row r="388" ht="18" customHeight="1">
       <c r="A388" s="3" t="n"/>
@@ -8408,7 +9112,9 @@
           <t>56.964 + 15.136 + 16.6 + 75.99 + 56.964 + 15.136 + 9.72 + 16.6 + 75.99 = 339.1</t>
         </is>
       </c>
-      <c r="F388" s="10" t="n"/>
+      <c r="F388" s="9" t="n">
+        <v>339.1</v>
+      </c>
     </row>
     <row r="389" ht="18" customHeight="1">
       <c r="A389" s="3" t="n"/>
@@ -8428,7 +9134,9 @@
           <t>75.99 + 9.72 + 75.99 = 161.7</t>
         </is>
       </c>
-      <c r="F389" s="10" t="n"/>
+      <c r="F389" s="9" t="n">
+        <v>161.7</v>
+      </c>
     </row>
     <row r="390" ht="18" customHeight="1">
       <c r="A390" s="3" t="n"/>
@@ -8448,7 +9156,9 @@
           <t>75.99 = 75.99</t>
         </is>
       </c>
-      <c r="F390" s="10" t="n"/>
+      <c r="F390" s="9" t="n">
+        <v>75.98999999999999</v>
+      </c>
     </row>
     <row r="391" ht="18" customHeight="1">
       <c r="A391" s="3" t="n"/>
@@ -8468,7 +9178,9 @@
           <t>65.5 + 6.2 = 71.7</t>
         </is>
       </c>
-      <c r="F391" s="10" t="n"/>
+      <c r="F391" s="9" t="n">
+        <v>71.7</v>
+      </c>
     </row>
     <row r="392" ht="32" customHeight="1">
       <c r="A392" s="3" t="n"/>
@@ -8484,7 +9196,9 @@
           <t>(327.572 + 171.42 + 41.262 + 88.792 + 138.57 + 41.262 + 41.262 + 184.482 + 41.784 + 138.57 + 41.262 + 41.262 + 184.482 + 41.784 + 339.1 + 161.7 + 75.99 + 71.7) ÷ 1000 = 2.172</t>
         </is>
       </c>
-      <c r="F392" s="10" t="n"/>
+      <c r="F392" s="10" t="n">
+        <v>2.172</v>
+      </c>
     </row>
     <row r="393" ht="18" customHeight="1">
       <c r="A393" s="3" t="n">
@@ -8511,7 +9225,7 @@
         </is>
       </c>
       <c r="F393" s="9" t="n">
-        <v>2.778</v>
+        <v>286.602</v>
       </c>
     </row>
     <row r="394" ht="18" customHeight="1">
@@ -8532,7 +9246,9 @@
           <t>188.316 = 188.316</t>
         </is>
       </c>
-      <c r="F394" s="10" t="n"/>
+      <c r="F394" s="9" t="n">
+        <v>188.316</v>
+      </c>
     </row>
     <row r="395" ht="18" customHeight="1">
       <c r="A395" s="3" t="n"/>
@@ -8552,7 +9268,9 @@
           <t>54.93 + 54.702 = 109.632</t>
         </is>
       </c>
-      <c r="F395" s="10" t="n"/>
+      <c r="F395" s="9" t="n">
+        <v>109.632</v>
+      </c>
     </row>
     <row r="396" ht="18" customHeight="1">
       <c r="A396" s="3" t="n"/>
@@ -8572,7 +9290,9 @@
           <t>5.692 + 109.776 + 20.668 = 136.136</t>
         </is>
       </c>
-      <c r="F396" s="10" t="n"/>
+      <c r="F396" s="9" t="n">
+        <v>136.136</v>
+      </c>
     </row>
     <row r="397" ht="18" customHeight="1">
       <c r="A397" s="3" t="n"/>
@@ -8592,7 +9312,9 @@
           <t>69.318 + 18.476 + 10.581 + 16.362 + 5.99 + 49.41 = 170.137</t>
         </is>
       </c>
-      <c r="F397" s="10" t="n"/>
+      <c r="F397" s="9" t="n">
+        <v>170.137</v>
+      </c>
     </row>
     <row r="398" ht="18" customHeight="1">
       <c r="A398" s="3" t="n"/>
@@ -8612,7 +9334,9 @@
           <t>80.112 + 22.31 + 6.523 = 108.945</t>
         </is>
       </c>
-      <c r="F398" s="10" t="n"/>
+      <c r="F398" s="9" t="n">
+        <v>108.945</v>
+      </c>
     </row>
     <row r="399" ht="18" customHeight="1">
       <c r="A399" s="3" t="n"/>
@@ -8632,7 +9356,9 @@
           <t>2.846 + 54.888 + 10.334 + 15.996 + 5.99 + 49.41 = 139.464</t>
         </is>
       </c>
-      <c r="F399" s="10" t="n"/>
+      <c r="F399" s="9" t="n">
+        <v>139.464</v>
+      </c>
     </row>
     <row r="400" ht="18" customHeight="1">
       <c r="A400" s="3" t="n"/>
@@ -8652,7 +9378,9 @@
           <t>2.846 + 54.888 + 10.334 + 15.996 + 5.99 + 49.41 = 139.464</t>
         </is>
       </c>
-      <c r="F400" s="10" t="n"/>
+      <c r="F400" s="9" t="n">
+        <v>139.464</v>
+      </c>
     </row>
     <row r="401" ht="18" customHeight="1">
       <c r="A401" s="3" t="n"/>
@@ -8672,7 +9400,9 @@
           <t>69.318 + 18.15 + 10.581 + 16.362 + 5.99 + 49.41 = 169.811</t>
         </is>
       </c>
-      <c r="F401" s="10" t="n"/>
+      <c r="F401" s="9" t="n">
+        <v>169.811</v>
+      </c>
     </row>
     <row r="402" ht="18" customHeight="1">
       <c r="A402" s="3" t="n"/>
@@ -8692,7 +9422,9 @@
           <t>80.112 + 22.31 + 6.523 = 108.945</t>
         </is>
       </c>
-      <c r="F402" s="10" t="n"/>
+      <c r="F402" s="9" t="n">
+        <v>108.945</v>
+      </c>
     </row>
     <row r="403" ht="18" customHeight="1">
       <c r="A403" s="3" t="n"/>
@@ -8712,7 +9444,9 @@
           <t>80.112 + 4.836 + 15.314 + 39.036 = 139.298</t>
         </is>
       </c>
-      <c r="F403" s="10" t="n"/>
+      <c r="F403" s="9" t="n">
+        <v>139.298</v>
+      </c>
     </row>
     <row r="404" ht="18" customHeight="1">
       <c r="A404" s="3" t="n"/>
@@ -8732,7 +9466,9 @@
           <t>26.055 = 26.055</t>
         </is>
       </c>
-      <c r="F404" s="10" t="n"/>
+      <c r="F404" s="9" t="n">
+        <v>26.055</v>
+      </c>
     </row>
     <row r="405" ht="18" customHeight="1">
       <c r="A405" s="3" t="n"/>
@@ -8752,7 +9488,9 @@
           <t>2.846 + 54.888 + 10.334 + 15.996 + 5.99 + 49.41 = 139.464</t>
         </is>
       </c>
-      <c r="F405" s="10" t="n"/>
+      <c r="F405" s="9" t="n">
+        <v>139.464</v>
+      </c>
     </row>
     <row r="406" ht="18" customHeight="1">
       <c r="A406" s="3" t="n"/>
@@ -8772,7 +9510,9 @@
           <t>2.846 + 54.888 + 10.334 + 15.996 + 5.99 + 49.41 = 139.464</t>
         </is>
       </c>
-      <c r="F406" s="10" t="n"/>
+      <c r="F406" s="9" t="n">
+        <v>139.464</v>
+      </c>
     </row>
     <row r="407" ht="18" customHeight="1">
       <c r="A407" s="3" t="n"/>
@@ -8792,7 +9532,9 @@
           <t>69.318 + 18.15 + 10.581 + 16.362 + 5.99 + 49.41 = 169.811</t>
         </is>
       </c>
-      <c r="F407" s="10" t="n"/>
+      <c r="F407" s="9" t="n">
+        <v>169.811</v>
+      </c>
     </row>
     <row r="408" ht="18" customHeight="1">
       <c r="A408" s="3" t="n"/>
@@ -8812,7 +9554,9 @@
           <t>80.112 + 22.31 + 6.523 = 108.945</t>
         </is>
       </c>
-      <c r="F408" s="10" t="n"/>
+      <c r="F408" s="9" t="n">
+        <v>108.945</v>
+      </c>
     </row>
     <row r="409" ht="18" customHeight="1">
       <c r="A409" s="3" t="n"/>
@@ -8832,7 +9576,9 @@
           <t>80.112 + 4.836 + 15.314 + 39.036 = 139.298</t>
         </is>
       </c>
-      <c r="F409" s="10" t="n"/>
+      <c r="F409" s="9" t="n">
+        <v>139.298</v>
+      </c>
     </row>
     <row r="410" ht="18" customHeight="1">
       <c r="A410" s="3" t="n"/>
@@ -8852,7 +9598,9 @@
           <t>26.055 = 26.055</t>
         </is>
       </c>
-      <c r="F410" s="10" t="n"/>
+      <c r="F410" s="9" t="n">
+        <v>26.055</v>
+      </c>
     </row>
     <row r="411" ht="18" customHeight="1">
       <c r="A411" s="3" t="n"/>
@@ -8872,7 +9620,9 @@
           <t>56 + 10.334 + 56 + 10.334 = 132.668</t>
         </is>
       </c>
-      <c r="F411" s="10" t="n"/>
+      <c r="F411" s="9" t="n">
+        <v>132.668</v>
+      </c>
     </row>
     <row r="412" ht="18" customHeight="1">
       <c r="A412" s="3" t="n"/>
@@ -8892,7 +9642,9 @@
           <t>70.43 + 9.075 + 10.581 + 16.362 = 106.448</t>
         </is>
       </c>
-      <c r="F412" s="10" t="n"/>
+      <c r="F412" s="9" t="n">
+        <v>106.448</v>
+      </c>
     </row>
     <row r="413" ht="18" customHeight="1">
       <c r="A413" s="3" t="n"/>
@@ -8912,7 +9664,9 @@
           <t>82.088 + 11.155 = 93.243</t>
         </is>
       </c>
-      <c r="F413" s="10" t="n"/>
+      <c r="F413" s="9" t="n">
+        <v>93.24299999999999</v>
+      </c>
     </row>
     <row r="414" ht="32" customHeight="1">
       <c r="A414" s="3" t="n"/>
@@ -8928,7 +9682,9 @@
           <t>(286.602 + 188.316 + 109.632 + 136.136 + 170.137 + 108.945 + 139.464 + 139.464 + 169.811 + 108.945 + 139.298 + 26.055 + 139.464 + 139.464 + 169.811 + 108.945 + 139.298 + 26.055 + 132.668 + 106.448 + 93.243) ÷ 1000 = 2.778</t>
         </is>
       </c>
-      <c r="F414" s="10" t="n"/>
+      <c r="F414" s="10" t="n">
+        <v>2.778</v>
+      </c>
     </row>
     <row r="415" ht="18" customHeight="1">
       <c r="A415" s="3" t="n">
@@ -8955,7 +9711,7 @@
         </is>
       </c>
       <c r="F415" s="9" t="n">
-        <v>0.319</v>
+        <v>63.339</v>
       </c>
     </row>
     <row r="416" ht="18" customHeight="1">
@@ -8976,7 +9732,9 @@
           <t>63.117 = 63.117</t>
         </is>
       </c>
-      <c r="F416" s="10" t="n"/>
+      <c r="F416" s="9" t="n">
+        <v>63.117</v>
+      </c>
     </row>
     <row r="417" ht="18" customHeight="1">
       <c r="A417" s="3" t="n"/>
@@ -8996,7 +9754,9 @@
           <t>63.339 = 63.339</t>
         </is>
       </c>
-      <c r="F417" s="10" t="n"/>
+      <c r="F417" s="9" t="n">
+        <v>63.339</v>
+      </c>
     </row>
     <row r="418" ht="18" customHeight="1">
       <c r="A418" s="3" t="n"/>
@@ -9016,7 +9776,9 @@
           <t>63.117 = 63.117</t>
         </is>
       </c>
-      <c r="F418" s="10" t="n"/>
+      <c r="F418" s="9" t="n">
+        <v>63.117</v>
+      </c>
     </row>
     <row r="419" ht="18" customHeight="1">
       <c r="A419" s="3" t="n"/>
@@ -9036,7 +9798,9 @@
           <t>66.54 = 66.54</t>
         </is>
       </c>
-      <c r="F419" s="10" t="n"/>
+      <c r="F419" s="9" t="n">
+        <v>66.54000000000001</v>
+      </c>
     </row>
     <row r="420" ht="18" customHeight="1">
       <c r="A420" s="3" t="n"/>
@@ -9052,7 +9816,9 @@
           <t>(63.339 + 63.117 + 63.339 + 63.117 + 66.54) ÷ 1000 = 0.319</t>
         </is>
       </c>
-      <c r="F420" s="10" t="n"/>
+      <c r="F420" s="10" t="n">
+        <v>0.319</v>
+      </c>
     </row>
     <row r="421" ht="18" customHeight="1">
       <c r="A421" s="3" t="n">
@@ -9079,7 +9845,7 @@
         </is>
       </c>
       <c r="F421" s="9" t="n">
-        <v>1.029</v>
+        <v>3.08</v>
       </c>
     </row>
     <row r="422" ht="18" customHeight="1">
@@ -9100,7 +9866,9 @@
           <t>59.908 + 81.864 + 6.16 = 147.932</t>
         </is>
       </c>
-      <c r="F422" s="10" t="n"/>
+      <c r="F422" s="9" t="n">
+        <v>147.932</v>
+      </c>
     </row>
     <row r="423" ht="18" customHeight="1">
       <c r="A423" s="3" t="n"/>
@@ -9120,7 +9888,9 @@
           <t>3.08 = 3.08</t>
         </is>
       </c>
-      <c r="F423" s="10" t="n"/>
+      <c r="F423" s="9" t="n">
+        <v>3.08</v>
+      </c>
     </row>
     <row r="424" ht="18" customHeight="1">
       <c r="A424" s="3" t="n"/>
@@ -9140,7 +9910,9 @@
           <t>86.868 = 86.868</t>
         </is>
       </c>
-      <c r="F424" s="10" t="n"/>
+      <c r="F424" s="9" t="n">
+        <v>86.86799999999999</v>
+      </c>
     </row>
     <row r="425" ht="18" customHeight="1">
       <c r="A425" s="3" t="n"/>
@@ -9160,7 +9932,9 @@
           <t>3.08 = 3.08</t>
         </is>
       </c>
-      <c r="F425" s="10" t="n"/>
+      <c r="F425" s="9" t="n">
+        <v>3.08</v>
+      </c>
     </row>
     <row r="426" ht="18" customHeight="1">
       <c r="A426" s="3" t="n"/>
@@ -9180,7 +9954,9 @@
           <t>44.931 + 27.288 + 6.16 = 78.379</t>
         </is>
       </c>
-      <c r="F426" s="10" t="n"/>
+      <c r="F426" s="9" t="n">
+        <v>78.379</v>
+      </c>
     </row>
     <row r="427" ht="18" customHeight="1">
       <c r="A427" s="3" t="n"/>
@@ -9200,7 +9976,9 @@
           <t>44.931 + 27.288 + 6.16 = 78.379</t>
         </is>
       </c>
-      <c r="F427" s="10" t="n"/>
+      <c r="F427" s="9" t="n">
+        <v>78.379</v>
+      </c>
     </row>
     <row r="428" ht="18" customHeight="1">
       <c r="A428" s="3" t="n"/>
@@ -9220,7 +9998,9 @@
           <t>3.08 = 3.08</t>
         </is>
       </c>
-      <c r="F428" s="10" t="n"/>
+      <c r="F428" s="9" t="n">
+        <v>3.08</v>
+      </c>
     </row>
     <row r="429" ht="18" customHeight="1">
       <c r="A429" s="3" t="n"/>
@@ -9240,7 +10020,9 @@
           <t>6.16 = 6.16</t>
         </is>
       </c>
-      <c r="F429" s="10" t="n"/>
+      <c r="F429" s="9" t="n">
+        <v>6.16</v>
+      </c>
     </row>
     <row r="430" ht="18" customHeight="1">
       <c r="A430" s="3" t="n"/>
@@ -9260,7 +10042,9 @@
           <t>86.868 = 86.868</t>
         </is>
       </c>
-      <c r="F430" s="10" t="n"/>
+      <c r="F430" s="9" t="n">
+        <v>86.86799999999999</v>
+      </c>
     </row>
     <row r="431" ht="18" customHeight="1">
       <c r="A431" s="3" t="n"/>
@@ -9280,7 +10064,9 @@
           <t>77.676 = 77.676</t>
         </is>
       </c>
-      <c r="F431" s="10" t="n"/>
+      <c r="F431" s="9" t="n">
+        <v>77.676</v>
+      </c>
     </row>
     <row r="432" ht="18" customHeight="1">
       <c r="A432" s="3" t="n"/>
@@ -9300,7 +10086,9 @@
           <t>3.08 = 3.08</t>
         </is>
       </c>
-      <c r="F432" s="10" t="n"/>
+      <c r="F432" s="9" t="n">
+        <v>3.08</v>
+      </c>
     </row>
     <row r="433" ht="18" customHeight="1">
       <c r="A433" s="3" t="n"/>
@@ -9320,7 +10108,9 @@
           <t>44.931 + 27.288 + 6.16 = 78.379</t>
         </is>
       </c>
-      <c r="F433" s="10" t="n"/>
+      <c r="F433" s="9" t="n">
+        <v>78.379</v>
+      </c>
     </row>
     <row r="434" ht="18" customHeight="1">
       <c r="A434" s="3" t="n"/>
@@ -9340,7 +10130,9 @@
           <t>44.931 + 27.288 + 6.16 = 78.379</t>
         </is>
       </c>
-      <c r="F434" s="10" t="n"/>
+      <c r="F434" s="9" t="n">
+        <v>78.379</v>
+      </c>
     </row>
     <row r="435" ht="18" customHeight="1">
       <c r="A435" s="3" t="n"/>
@@ -9360,7 +10152,9 @@
           <t>3.08 = 3.08</t>
         </is>
       </c>
-      <c r="F435" s="10" t="n"/>
+      <c r="F435" s="9" t="n">
+        <v>3.08</v>
+      </c>
     </row>
     <row r="436" ht="18" customHeight="1">
       <c r="A436" s="3" t="n"/>
@@ -9380,7 +10174,9 @@
           <t>6.16 = 6.16</t>
         </is>
       </c>
-      <c r="F436" s="10" t="n"/>
+      <c r="F436" s="9" t="n">
+        <v>6.16</v>
+      </c>
     </row>
     <row r="437" ht="18" customHeight="1">
       <c r="A437" s="3" t="n"/>
@@ -9400,7 +10196,9 @@
           <t>86.868 = 86.868</t>
         </is>
       </c>
-      <c r="F437" s="10" t="n"/>
+      <c r="F437" s="9" t="n">
+        <v>86.86799999999999</v>
+      </c>
     </row>
     <row r="438" ht="18" customHeight="1">
       <c r="A438" s="3" t="n"/>
@@ -9420,7 +10218,9 @@
           <t>77.676 = 77.676</t>
         </is>
       </c>
-      <c r="F438" s="10" t="n"/>
+      <c r="F438" s="9" t="n">
+        <v>77.676</v>
+      </c>
     </row>
     <row r="439" ht="18" customHeight="1">
       <c r="A439" s="3" t="n"/>
@@ -9440,7 +10240,9 @@
           <t>29.036 + 29.954 + 29.036 + 29.954 = 117.98</t>
         </is>
       </c>
-      <c r="F439" s="10" t="n"/>
+      <c r="F439" s="9" t="n">
+        <v>117.98</v>
+      </c>
     </row>
     <row r="440" ht="18" customHeight="1">
       <c r="A440" s="3" t="n"/>
@@ -9460,7 +10262,9 @@
           <t>3.08 = 3.08</t>
         </is>
       </c>
-      <c r="F440" s="10" t="n"/>
+      <c r="F440" s="9" t="n">
+        <v>3.08</v>
+      </c>
     </row>
     <row r="441" ht="32" customHeight="1">
       <c r="A441" s="3" t="n"/>
@@ -9476,7 +10280,9 @@
           <t>(3.08 + 147.932 + 3.08 + 86.868 + 3.08 + 78.379 + 78.379 + 3.08 + 6.16 + 86.868 + 77.676 + 3.08 + 78.379 + 78.379 + 3.08 + 6.16 + 86.868 + 77.676 + 117.98 + 3.08) ÷ 1000 = 1.029</t>
         </is>
       </c>
-      <c r="F441" s="10" t="n"/>
+      <c r="F441" s="10" t="n">
+        <v>1.029</v>
+      </c>
     </row>
     <row r="442" ht="18" customHeight="1">
       <c r="A442" s="3" t="n">
@@ -9503,7 +10309,7 @@
         </is>
       </c>
       <c r="F442" s="9" t="n">
-        <v>2.37</v>
+        <v>72.411</v>
       </c>
     </row>
     <row r="443" ht="18" customHeight="1">
@@ -9524,7 +10330,9 @@
           <t>56.826 + 61.304 + 58.284 + 77.115 = 253.529</t>
         </is>
       </c>
-      <c r="F443" s="10" t="n"/>
+      <c r="F443" s="9" t="n">
+        <v>253.529</v>
+      </c>
     </row>
     <row r="444" ht="18" customHeight="1">
       <c r="A444" s="3" t="n"/>
@@ -9544,7 +10352,9 @@
           <t>35.94 + 39.2 + 48.248 + 47 + 54.242 + 50.26 = 274.89</t>
         </is>
       </c>
-      <c r="F444" s="10" t="n"/>
+      <c r="F444" s="9" t="n">
+        <v>274.89</v>
+      </c>
     </row>
     <row r="445" ht="18" customHeight="1">
       <c r="A445" s="3" t="n"/>
@@ -9564,7 +10374,9 @@
           <t>15.213 + 15.771 + 16.995 + 19.173 + 30.549 + 1.976 + 33.075 + 33.32 + 2.3 + 37.449 + 56.826 + 61.304 + 58.284 + 77.115 + 9.681 + 11.655 + 10.815 + 15.078 = 506.579</t>
         </is>
       </c>
-      <c r="F445" s="10" t="n"/>
+      <c r="F445" s="9" t="n">
+        <v>506.579</v>
+      </c>
     </row>
     <row r="446" ht="18" customHeight="1">
       <c r="A446" s="3" t="n"/>
@@ -9584,7 +10396,9 @@
           <t>50.26 + 54.242 + 47 + 48.248 + 39.2 + 35.94 = 274.89</t>
         </is>
       </c>
-      <c r="F446" s="10" t="n"/>
+      <c r="F446" s="9" t="n">
+        <v>274.89</v>
+      </c>
     </row>
     <row r="447" ht="18" customHeight="1">
       <c r="A447" s="3" t="n"/>
@@ -9604,7 +10418,9 @@
           <t>77.115 + 58.284 + 61.304 + 56.826 + 37.449 + 33.32 + 2.3 + 33.075 + 30.549 + 1.976 + 19.173 + 16.995 + 15.771 + 15.213 + 9.681 + 11.655 + 10.815 + 15.078 = 506.579</t>
         </is>
       </c>
-      <c r="F447" s="10" t="n"/>
+      <c r="F447" s="9" t="n">
+        <v>506.579</v>
+      </c>
     </row>
     <row r="448" ht="18" customHeight="1">
       <c r="A448" s="3" t="n"/>
@@ -9624,7 +10440,9 @@
           <t>14.913 + 22.496 + 15.399 + 34.884 + 56.826 + 61.304 + 58.284 + 77.115 = 341.221</t>
         </is>
       </c>
-      <c r="F448" s="10" t="n"/>
+      <c r="F448" s="9" t="n">
+        <v>341.221</v>
+      </c>
     </row>
     <row r="449" ht="18" customHeight="1">
       <c r="A449" s="3" t="n"/>
@@ -9644,7 +10462,9 @@
           <t>15.213 + 15.771 + 16.995 + 19.173 + 9.681 + 11.655 + 10.815 + 15.078 = 114.381</t>
         </is>
       </c>
-      <c r="F449" s="10" t="n"/>
+      <c r="F449" s="9" t="n">
+        <v>114.381</v>
+      </c>
     </row>
     <row r="450" ht="18" customHeight="1">
       <c r="A450" s="3" t="n"/>
@@ -9664,7 +10484,9 @@
           <t>4.125 + 6.854 + 4.137 + 10.557 = 25.673</t>
         </is>
       </c>
-      <c r="F450" s="10" t="n"/>
+      <c r="F450" s="9" t="n">
+        <v>25.673</v>
+      </c>
     </row>
     <row r="451" ht="18" customHeight="1">
       <c r="A451" s="3" t="n"/>
@@ -9680,7 +10502,9 @@
           <t>(72.411 + 253.529 + 274.89 + 506.579 + 274.89 + 506.579 + 341.221 + 114.381 + 25.673) ÷ 1000 = 2.370</t>
         </is>
       </c>
-      <c r="F451" s="10" t="n"/>
+      <c r="F451" s="10" t="n">
+        <v>2.37</v>
+      </c>
     </row>
     <row r="452" ht="18" customHeight="1">
       <c r="A452" s="3" t="n">
@@ -9707,7 +10531,7 @@
         </is>
       </c>
       <c r="F452" s="9" t="n">
-        <v>2.808</v>
+        <v>625.867</v>
       </c>
     </row>
     <row r="453" ht="18" customHeight="1">
@@ -9728,7 +10552,9 @@
           <t>40.824 + 46.746 + 17.766 + 85.512 + 42.944 + 27.084 + 121.94 + 62.307 + 56.925 + 81.54 = 583.588</t>
         </is>
       </c>
-      <c r="F453" s="10" t="n"/>
+      <c r="F453" s="9" t="n">
+        <v>583.588</v>
+      </c>
     </row>
     <row r="454" ht="18" customHeight="1">
       <c r="A454" s="3" t="n"/>
@@ -9748,7 +10574,9 @@
           <t>46.746 + 40.824 + 56.925 + 81.54 + 42.944 + 17.766 + 85.512 + 62.307 + 27.084 + 121.94 = 583.588</t>
         </is>
       </c>
-      <c r="F454" s="10" t="n"/>
+      <c r="F454" s="9" t="n">
+        <v>583.588</v>
+      </c>
     </row>
     <row r="455" ht="18" customHeight="1">
       <c r="A455" s="3" t="n"/>
@@ -9768,7 +10596,9 @@
           <t>48.12 + 49.35 + 69.82 + 56.925 + 81.54 + 42.944 + 17.766 + 85.512 + 62.307 + 27.084 + 121.94 = 663.308</t>
         </is>
       </c>
-      <c r="F455" s="10" t="n"/>
+      <c r="F455" s="9" t="n">
+        <v>663.308</v>
+      </c>
     </row>
     <row r="456" ht="18" customHeight="1">
       <c r="A456" s="3" t="n"/>
@@ -9788,7 +10618,9 @@
           <t>50.496 + 21.01 + 69.152 + 109.48 + 101.244 = 351.382</t>
         </is>
       </c>
-      <c r="F456" s="10" t="n"/>
+      <c r="F456" s="9" t="n">
+        <v>351.382</v>
+      </c>
     </row>
     <row r="457" ht="18" customHeight="1">
       <c r="A457" s="3" t="n"/>
@@ -9804,7 +10636,9 @@
           <t>(625.867 + 583.588 + 583.588 + 663.308 + 351.382) ÷ 1000 = 2.808</t>
         </is>
       </c>
-      <c r="F457" s="10" t="n"/>
+      <c r="F457" s="10" t="n">
+        <v>2.808</v>
+      </c>
     </row>
     <row r="458" ht="18" customHeight="1">
       <c r="A458" s="3" t="n">
@@ -9831,7 +10665,7 @@
         </is>
       </c>
       <c r="F458" s="9" t="n">
-        <v>6.289</v>
+        <v>1567.423</v>
       </c>
     </row>
     <row r="459" ht="18" customHeight="1">
@@ -9852,7 +10686,9 @@
           <t>252.896 + 124.68 + 336.148 + 131.064 + 130.416 + 176.16 + 165.592 + 158.144 = 1475.1</t>
         </is>
       </c>
-      <c r="F459" s="10" t="n"/>
+      <c r="F459" s="9" t="n">
+        <v>1475.1</v>
+      </c>
     </row>
     <row r="460" ht="18" customHeight="1">
       <c r="A460" s="3" t="n"/>
@@ -9872,7 +10708,9 @@
           <t>130.416 + 131.064 + 165.592 + 176.16 + 124.68 + 252.896 + 336.148 + 158.144 = 1475.1</t>
         </is>
       </c>
-      <c r="F460" s="10" t="n"/>
+      <c r="F460" s="9" t="n">
+        <v>1475.1</v>
+      </c>
     </row>
     <row r="461" ht="18" customHeight="1">
       <c r="A461" s="3" t="n"/>
@@ -9892,7 +10730,9 @@
           <t>221.284 + 110.832 + 385.704 + 260.799 + 353.84 + 165.592 + 131.064 + 141.96 = 1771.075</t>
         </is>
       </c>
-      <c r="F461" s="10" t="n"/>
+      <c r="F461" s="9" t="n">
+        <v>1771.075</v>
+      </c>
     </row>
     <row r="462" ht="18" customHeight="1">
       <c r="A462" s="3" t="n"/>
@@ -9908,7 +10748,9 @@
           <t>(1567.423 + 1475.1 + 1475.1 + 1771.075) ÷ 1000 = 6.289</t>
         </is>
       </c>
-      <c r="F462" s="10" t="n"/>
+      <c r="F462" s="10" t="n">
+        <v>6.289</v>
+      </c>
     </row>
     <row r="463" ht="18" customHeight="1">
       <c r="A463" s="3" t="n">
@@ -9935,7 +10777,7 @@
         </is>
       </c>
       <c r="F463" s="9" t="n">
-        <v>0.089</v>
+        <v>18.836</v>
       </c>
     </row>
     <row r="464" ht="18" customHeight="1">
@@ -9956,7 +10798,9 @@
           <t>15.408 + 7.922 = 23.33</t>
         </is>
       </c>
-      <c r="F464" s="10" t="n"/>
+      <c r="F464" s="9" t="n">
+        <v>23.33</v>
+      </c>
     </row>
     <row r="465" ht="18" customHeight="1">
       <c r="A465" s="3" t="n"/>
@@ -9976,7 +10820,9 @@
           <t>15.408 + 7.922 = 23.33</t>
         </is>
       </c>
-      <c r="F465" s="10" t="n"/>
+      <c r="F465" s="9" t="n">
+        <v>23.33</v>
+      </c>
     </row>
     <row r="466" ht="18" customHeight="1">
       <c r="A466" s="3" t="n"/>
@@ -9996,7 +10842,9 @@
           <t>15.408 + 7.922 = 23.33</t>
         </is>
       </c>
-      <c r="F466" s="10" t="n"/>
+      <c r="F466" s="9" t="n">
+        <v>23.33</v>
+      </c>
     </row>
     <row r="467" ht="18" customHeight="1">
       <c r="A467" s="3" t="n"/>
@@ -10012,7 +10860,9 @@
           <t>(18.836 + 23.33 + 23.33 + 23.33) ÷ 1000 = 0.089</t>
         </is>
       </c>
-      <c r="F467" s="10" t="n"/>
+      <c r="F467" s="10" t="n">
+        <v>0.089</v>
+      </c>
     </row>
     <row r="468" ht="18" customHeight="1">
       <c r="A468" s="3" t="n">
@@ -10039,7 +10889,7 @@
         </is>
       </c>
       <c r="F468" s="9" t="n">
-        <v>0.209</v>
+        <v>63.941</v>
       </c>
     </row>
     <row r="469" ht="18" customHeight="1">
@@ -10060,7 +10910,9 @@
           <t>13.587 + 11.277 + 11.991 + 11.376 = 48.231</t>
         </is>
       </c>
-      <c r="F469" s="10" t="n"/>
+      <c r="F469" s="9" t="n">
+        <v>48.231</v>
+      </c>
     </row>
     <row r="470" ht="18" customHeight="1">
       <c r="A470" s="3" t="n"/>
@@ -10080,7 +10932,9 @@
           <t>13.587 + 11.277 + 11.991 + 11.376 = 48.231</t>
         </is>
       </c>
-      <c r="F470" s="10" t="n"/>
+      <c r="F470" s="9" t="n">
+        <v>48.231</v>
+      </c>
     </row>
     <row r="471" ht="18" customHeight="1">
       <c r="A471" s="3" t="n"/>
@@ -10100,7 +10954,9 @@
           <t>13.587 + 11.277 + 11.991 + 11.376 = 48.231</t>
         </is>
       </c>
-      <c r="F471" s="10" t="n"/>
+      <c r="F471" s="9" t="n">
+        <v>48.231</v>
+      </c>
     </row>
     <row r="472" ht="18" customHeight="1">
       <c r="A472" s="3" t="n"/>
@@ -10116,7 +10972,9 @@
           <t>(63.941 + 48.231 + 48.231 + 48.231) ÷ 1000 = 0.209</t>
         </is>
       </c>
-      <c r="F472" s="10" t="n"/>
+      <c r="F472" s="10" t="n">
+        <v>0.209</v>
+      </c>
     </row>
     <row r="473" ht="18" customHeight="1">
       <c r="A473" s="3" t="n">
@@ -10143,7 +11001,7 @@
         </is>
       </c>
       <c r="F473" s="9" t="n">
-        <v>0.417</v>
+        <v>111.07</v>
       </c>
     </row>
     <row r="474" ht="18" customHeight="1">
@@ -10164,7 +11022,9 @@
           <t>22.24 + 7.39 + 29.83 + 11.12 + 31.37 = 101.95</t>
         </is>
       </c>
-      <c r="F474" s="10" t="n"/>
+      <c r="F474" s="9" t="n">
+        <v>101.95</v>
+      </c>
     </row>
     <row r="475" ht="18" customHeight="1">
       <c r="A475" s="3" t="n"/>
@@ -10184,7 +11044,9 @@
           <t>22.24 + 7.39 + 29.83 + 11.12 + 31.37 = 101.95</t>
         </is>
       </c>
-      <c r="F475" s="10" t="n"/>
+      <c r="F475" s="9" t="n">
+        <v>101.95</v>
+      </c>
     </row>
     <row r="476" ht="18" customHeight="1">
       <c r="A476" s="3" t="n"/>
@@ -10204,7 +11066,9 @@
           <t>22.24 + 7.39 + 29.83 + 11.12 + 31.37 = 101.95</t>
         </is>
       </c>
-      <c r="F476" s="10" t="n"/>
+      <c r="F476" s="9" t="n">
+        <v>101.95</v>
+      </c>
     </row>
     <row r="477" ht="18" customHeight="1">
       <c r="A477" s="3" t="n"/>
@@ -10220,7 +11084,9 @@
           <t>(111.07 + 101.95 + 101.95 + 101.95) ÷ 1000 = 0.417</t>
         </is>
       </c>
-      <c r="F477" s="10" t="n"/>
+      <c r="F477" s="10" t="n">
+        <v>0.417</v>
+      </c>
     </row>
     <row r="478" ht="18" customHeight="1">
       <c r="A478" s="3" t="n">
@@ -10247,7 +11113,7 @@
         </is>
       </c>
       <c r="F478" s="9" t="n">
-        <v>0.266</v>
+        <v>66.556</v>
       </c>
     </row>
     <row r="479" ht="18" customHeight="1">
@@ -10268,7 +11134,9 @@
           <t>11.704 + 5.783 + 15.741 + 11.724 + 5.792 + 15.771 = 66.515</t>
         </is>
       </c>
-      <c r="F479" s="10" t="n"/>
+      <c r="F479" s="9" t="n">
+        <v>66.515</v>
+      </c>
     </row>
     <row r="480" ht="18" customHeight="1">
       <c r="A480" s="3" t="n"/>
@@ -10288,7 +11156,9 @@
           <t>11.704 + 5.783 + 15.741 + 11.724 + 5.792 + 15.771 = 66.515</t>
         </is>
       </c>
-      <c r="F480" s="10" t="n"/>
+      <c r="F480" s="9" t="n">
+        <v>66.515</v>
+      </c>
     </row>
     <row r="481" ht="18" customHeight="1">
       <c r="A481" s="3" t="n"/>
@@ -10308,7 +11178,9 @@
           <t>11.704 + 5.783 + 15.741 + 11.724 + 5.792 + 15.771 = 66.515</t>
         </is>
       </c>
-      <c r="F481" s="10" t="n"/>
+      <c r="F481" s="9" t="n">
+        <v>66.515</v>
+      </c>
     </row>
     <row r="482" ht="18" customHeight="1">
       <c r="A482" s="3" t="n"/>
@@ -10324,7 +11196,9 @@
           <t>(66.556 + 66.515 + 66.515 + 66.515) ÷ 1000 = 0.266</t>
         </is>
       </c>
-      <c r="F482" s="10" t="n"/>
+      <c r="F482" s="10" t="n">
+        <v>0.266</v>
+      </c>
     </row>
     <row r="483" ht="18" customHeight="1">
       <c r="A483" s="3" t="n">
@@ -10351,7 +11225,7 @@
         </is>
       </c>
       <c r="F483" s="9" t="n">
-        <v>0.08799999999999999</v>
+        <v>1.701</v>
       </c>
     </row>
     <row r="484" ht="18" customHeight="1">
@@ -10372,7 +11246,9 @@
           <t>6.534 = 6.534</t>
         </is>
       </c>
-      <c r="F484" s="10" t="n"/>
+      <c r="F484" s="9" t="n">
+        <v>6.534</v>
+      </c>
     </row>
     <row r="485" ht="18" customHeight="1">
       <c r="A485" s="3" t="n"/>
@@ -10392,7 +11268,9 @@
           <t>3.213 = 3.213</t>
         </is>
       </c>
-      <c r="F485" s="10" t="n"/>
+      <c r="F485" s="9" t="n">
+        <v>3.213</v>
+      </c>
     </row>
     <row r="486" ht="18" customHeight="1">
       <c r="A486" s="3" t="n"/>
@@ -10412,7 +11290,9 @@
           <t>12.342 = 12.342</t>
         </is>
       </c>
-      <c r="F486" s="10" t="n"/>
+      <c r="F486" s="9" t="n">
+        <v>12.342</v>
+      </c>
     </row>
     <row r="487" ht="18" customHeight="1">
       <c r="A487" s="3" t="n"/>
@@ -10432,7 +11312,9 @@
           <t>3.213 = 3.213</t>
         </is>
       </c>
-      <c r="F487" s="10" t="n"/>
+      <c r="F487" s="9" t="n">
+        <v>3.213</v>
+      </c>
     </row>
     <row r="488" ht="18" customHeight="1">
       <c r="A488" s="3" t="n"/>
@@ -10452,7 +11334,9 @@
           <t>12.342 = 12.342</t>
         </is>
       </c>
-      <c r="F488" s="10" t="n"/>
+      <c r="F488" s="9" t="n">
+        <v>12.342</v>
+      </c>
     </row>
     <row r="489" ht="18" customHeight="1">
       <c r="A489" s="3" t="n"/>
@@ -10472,7 +11356,9 @@
           <t>3.213 = 3.213</t>
         </is>
       </c>
-      <c r="F489" s="10" t="n"/>
+      <c r="F489" s="9" t="n">
+        <v>3.213</v>
+      </c>
     </row>
     <row r="490" ht="18" customHeight="1">
       <c r="A490" s="3" t="n"/>
@@ -10492,7 +11378,9 @@
           <t>12.342 = 12.342</t>
         </is>
       </c>
-      <c r="F490" s="10" t="n"/>
+      <c r="F490" s="9" t="n">
+        <v>12.342</v>
+      </c>
     </row>
     <row r="491" ht="18" customHeight="1">
       <c r="A491" s="3" t="n"/>
@@ -10512,7 +11400,9 @@
           <t>3.213 = 3.213</t>
         </is>
       </c>
-      <c r="F491" s="10" t="n"/>
+      <c r="F491" s="9" t="n">
+        <v>3.213</v>
+      </c>
     </row>
     <row r="492" ht="18" customHeight="1">
       <c r="A492" s="3" t="n"/>
@@ -10532,7 +11422,9 @@
           <t>12.342 = 12.342</t>
         </is>
       </c>
-      <c r="F492" s="10" t="n"/>
+      <c r="F492" s="9" t="n">
+        <v>12.342</v>
+      </c>
     </row>
     <row r="493" ht="18" customHeight="1">
       <c r="A493" s="3" t="n"/>
@@ -10552,7 +11444,9 @@
           <t>5.292 + 2.835 + 2.646 = 10.773</t>
         </is>
       </c>
-      <c r="F493" s="10" t="n"/>
+      <c r="F493" s="9" t="n">
+        <v>10.773</v>
+      </c>
     </row>
     <row r="494" ht="18" customHeight="1">
       <c r="A494" s="3" t="n"/>
@@ -10572,7 +11466,9 @@
           <t>6.534 = 6.534</t>
         </is>
       </c>
-      <c r="F494" s="10" t="n"/>
+      <c r="F494" s="9" t="n">
+        <v>6.534</v>
+      </c>
     </row>
     <row r="495" ht="18" customHeight="1">
       <c r="A495" s="3" t="n"/>
@@ -10588,7 +11484,9 @@
           <t>(1.701 + 6.534 + 3.213 + 12.342 + 3.213 + 12.342 + 3.213 + 12.342 + 3.213 + 12.342 + 10.773 + 6.534) ÷ 1000 = 0.088</t>
         </is>
       </c>
-      <c r="F495" s="10" t="n"/>
+      <c r="F495" s="10" t="n">
+        <v>0.08799999999999999</v>
+      </c>
     </row>
     <row r="496" ht="18" customHeight="1">
       <c r="A496" s="3" t="n">
@@ -10615,7 +11513,7 @@
         </is>
       </c>
       <c r="F496" s="9" t="n">
-        <v>0.357</v>
+        <v>9.212</v>
       </c>
     </row>
     <row r="497" ht="18" customHeight="1">
@@ -10636,7 +11534,9 @@
           <t>17.532 + 10.104 = 27.636</t>
         </is>
       </c>
-      <c r="F497" s="10" t="n"/>
+      <c r="F497" s="9" t="n">
+        <v>27.636</v>
+      </c>
     </row>
     <row r="498" ht="18" customHeight="1">
       <c r="A498" s="3" t="n"/>
@@ -10656,7 +11556,9 @@
           <t>11.704 + 3.368 = 15.072</t>
         </is>
       </c>
-      <c r="F498" s="10" t="n"/>
+      <c r="F498" s="9" t="n">
+        <v>15.072</v>
+      </c>
     </row>
     <row r="499" ht="18" customHeight="1">
       <c r="A499" s="3" t="n"/>
@@ -10676,7 +11578,9 @@
           <t>35.112 + 10.104 = 45.216</t>
         </is>
       </c>
-      <c r="F499" s="10" t="n"/>
+      <c r="F499" s="9" t="n">
+        <v>45.216</v>
+      </c>
     </row>
     <row r="500" ht="18" customHeight="1">
       <c r="A500" s="3" t="n"/>
@@ -10696,7 +11600,9 @@
           <t>11.704 + 3.28 = 14.984</t>
         </is>
       </c>
-      <c r="F500" s="10" t="n"/>
+      <c r="F500" s="9" t="n">
+        <v>14.984</v>
+      </c>
     </row>
     <row r="501" ht="18" customHeight="1">
       <c r="A501" s="3" t="n"/>
@@ -10716,7 +11622,9 @@
           <t>35.112 + 9.84 = 44.952</t>
         </is>
       </c>
-      <c r="F501" s="10" t="n"/>
+      <c r="F501" s="9" t="n">
+        <v>44.952</v>
+      </c>
     </row>
     <row r="502" ht="18" customHeight="1">
       <c r="A502" s="3" t="n"/>
@@ -10736,7 +11644,9 @@
           <t>11.704 + 3.28 = 14.984</t>
         </is>
       </c>
-      <c r="F502" s="10" t="n"/>
+      <c r="F502" s="9" t="n">
+        <v>14.984</v>
+      </c>
     </row>
     <row r="503" ht="18" customHeight="1">
       <c r="A503" s="3" t="n"/>
@@ -10756,7 +11666,9 @@
           <t>35.112 + 9.84 = 44.952</t>
         </is>
       </c>
-      <c r="F503" s="10" t="n"/>
+      <c r="F503" s="9" t="n">
+        <v>44.952</v>
+      </c>
     </row>
     <row r="504" ht="18" customHeight="1">
       <c r="A504" s="3" t="n"/>
@@ -10776,7 +11688,9 @@
           <t>11.704 + 3.28 = 14.984</t>
         </is>
       </c>
-      <c r="F504" s="10" t="n"/>
+      <c r="F504" s="9" t="n">
+        <v>14.984</v>
+      </c>
     </row>
     <row r="505" ht="18" customHeight="1">
       <c r="A505" s="3" t="n"/>
@@ -10796,7 +11710,9 @@
           <t>35.112 + 9.84 = 44.952</t>
         </is>
       </c>
-      <c r="F505" s="10" t="n"/>
+      <c r="F505" s="9" t="n">
+        <v>44.952</v>
+      </c>
     </row>
     <row r="506" ht="18" customHeight="1">
       <c r="A506" s="3" t="n"/>
@@ -10816,7 +11732,9 @@
           <t>19.144 + 6.736 + 9.928 + 3.368 + 9.752 + 3.368 = 52.296</t>
         </is>
       </c>
-      <c r="F506" s="10" t="n"/>
+      <c r="F506" s="9" t="n">
+        <v>52.296</v>
+      </c>
     </row>
     <row r="507" ht="18" customHeight="1">
       <c r="A507" s="3" t="n"/>
@@ -10836,7 +11754,9 @@
           <t>18.06 + 9.84 = 27.9</t>
         </is>
       </c>
-      <c r="F507" s="10" t="n"/>
+      <c r="F507" s="9" t="n">
+        <v>27.9</v>
+      </c>
     </row>
     <row r="508" ht="18" customHeight="1">
       <c r="A508" s="3" t="n"/>
@@ -10852,7 +11772,9 @@
           <t>(9.212 + 27.636 + 15.072 + 45.216 + 14.984 + 44.952 + 14.984 + 44.952 + 14.984 + 44.952 + 52.296 + 27.9) ÷ 1000 = 0.357</t>
         </is>
       </c>
-      <c r="F508" s="10" t="n"/>
+      <c r="F508" s="10" t="n">
+        <v>0.357</v>
+      </c>
     </row>
     <row r="509" ht="18" customHeight="1">
       <c r="A509" s="3" t="n">
@@ -10879,7 +11801,7 @@
         </is>
       </c>
       <c r="F509" s="9" t="n">
-        <v>0</v>
+        <v>0.275</v>
       </c>
     </row>
     <row r="510" ht="18" customHeight="1">
@@ -10896,7 +11818,9 @@
           <t>(0.275) ÷ 1000 = 0.000</t>
         </is>
       </c>
-      <c r="F510" s="10" t="n"/>
+      <c r="F510" s="10" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="511" ht="18" customHeight="1">
       <c r="A511" s="3" t="n">
@@ -10923,7 +11847,7 @@
         </is>
       </c>
       <c r="F511" s="9" t="n">
-        <v>0.044</v>
+        <v>4.212</v>
       </c>
     </row>
     <row r="512" ht="18" customHeight="1">
@@ -10944,7 +11868,9 @@
           <t>10.368 = 10.368</t>
         </is>
       </c>
-      <c r="F512" s="10" t="n"/>
+      <c r="F512" s="9" t="n">
+        <v>10.368</v>
+      </c>
     </row>
     <row r="513" ht="18" customHeight="1">
       <c r="A513" s="3" t="n"/>
@@ -10964,7 +11890,9 @@
           <t>4.212 = 4.212</t>
         </is>
       </c>
-      <c r="F513" s="10" t="n"/>
+      <c r="F513" s="9" t="n">
+        <v>4.212</v>
+      </c>
     </row>
     <row r="514" ht="18" customHeight="1">
       <c r="A514" s="3" t="n"/>
@@ -10984,7 +11912,9 @@
           <t>5.184 = 5.184</t>
         </is>
       </c>
-      <c r="F514" s="10" t="n"/>
+      <c r="F514" s="9" t="n">
+        <v>5.184</v>
+      </c>
     </row>
     <row r="515" ht="18" customHeight="1">
       <c r="A515" s="3" t="n"/>
@@ -11004,7 +11934,9 @@
           <t>4.212 = 4.212</t>
         </is>
       </c>
-      <c r="F515" s="10" t="n"/>
+      <c r="F515" s="9" t="n">
+        <v>4.212</v>
+      </c>
     </row>
     <row r="516" ht="18" customHeight="1">
       <c r="A516" s="3" t="n"/>
@@ -11024,7 +11956,9 @@
           <t>5.184 = 5.184</t>
         </is>
       </c>
-      <c r="F516" s="10" t="n"/>
+      <c r="F516" s="9" t="n">
+        <v>5.184</v>
+      </c>
     </row>
     <row r="517" ht="18" customHeight="1">
       <c r="A517" s="3" t="n"/>
@@ -11044,7 +11978,9 @@
           <t>4.212 = 4.212</t>
         </is>
       </c>
-      <c r="F517" s="10" t="n"/>
+      <c r="F517" s="9" t="n">
+        <v>4.212</v>
+      </c>
     </row>
     <row r="518" ht="18" customHeight="1">
       <c r="A518" s="3" t="n"/>
@@ -11064,7 +12000,9 @@
           <t>5.184 = 5.184</t>
         </is>
       </c>
-      <c r="F518" s="10" t="n"/>
+      <c r="F518" s="9" t="n">
+        <v>5.184</v>
+      </c>
     </row>
     <row r="519" ht="18" customHeight="1">
       <c r="A519" s="3" t="n"/>
@@ -11084,7 +12022,9 @@
           <t>1.62 = 1.62</t>
         </is>
       </c>
-      <c r="F519" s="10" t="n"/>
+      <c r="F519" s="9" t="n">
+        <v>1.62</v>
+      </c>
     </row>
     <row r="520" ht="18" customHeight="1">
       <c r="A520" s="3" t="n"/>
@@ -11100,7 +12040,9 @@
           <t>(4.212 + 10.368 + 4.212 + 5.184 + 4.212 + 5.184 + 4.212 + 5.184 + 1.62) ÷ 1000 = 0.044</t>
         </is>
       </c>
-      <c r="F520" s="10" t="n"/>
+      <c r="F520" s="10" t="n">
+        <v>0.044</v>
+      </c>
     </row>
     <row r="521" ht="18" customHeight="1">
       <c r="A521" s="3" t="n">
@@ -11127,7 +12069,7 @@
         </is>
       </c>
       <c r="F521" s="9" t="n">
-        <v>0.001</v>
+        <v>1.224</v>
       </c>
     </row>
     <row r="522" ht="18" customHeight="1">
@@ -11144,7 +12086,9 @@
           <t>(1.224) ÷ 1000 = 0.001</t>
         </is>
       </c>
-      <c r="F522" s="10" t="n"/>
+      <c r="F522" s="10" t="n">
+        <v>0.001</v>
+      </c>
     </row>
     <row r="523" ht="18" customHeight="1">
       <c r="A523" s="3" t="n">
@@ -11171,7 +12115,7 @@
         </is>
       </c>
       <c r="F523" s="9" t="n">
-        <v>0.077</v>
+        <v>17.048</v>
       </c>
     </row>
     <row r="524" ht="18" customHeight="1">
@@ -11192,7 +12136,9 @@
           <t>17.048 = 17.048</t>
         </is>
       </c>
-      <c r="F524" s="10" t="n"/>
+      <c r="F524" s="9" t="n">
+        <v>17.048</v>
+      </c>
     </row>
     <row r="525" ht="18" customHeight="1">
       <c r="A525" s="3" t="n"/>
@@ -11212,7 +12158,9 @@
           <t>17.048 = 17.048</t>
         </is>
       </c>
-      <c r="F525" s="10" t="n"/>
+      <c r="F525" s="9" t="n">
+        <v>17.048</v>
+      </c>
     </row>
     <row r="526" ht="18" customHeight="1">
       <c r="A526" s="3" t="n"/>
@@ -11232,7 +12180,9 @@
           <t>17.048 = 17.048</t>
         </is>
       </c>
-      <c r="F526" s="10" t="n"/>
+      <c r="F526" s="9" t="n">
+        <v>17.048</v>
+      </c>
     </row>
     <row r="527" ht="18" customHeight="1">
       <c r="A527" s="3" t="n"/>
@@ -11252,7 +12202,9 @@
           <t>8.444 = 8.444</t>
         </is>
       </c>
-      <c r="F527" s="10" t="n"/>
+      <c r="F527" s="9" t="n">
+        <v>8.444000000000001</v>
+      </c>
     </row>
     <row r="528" ht="18" customHeight="1">
       <c r="A528" s="3" t="n"/>
@@ -11268,7 +12220,9 @@
           <t>(17.048 + 17.048 + 17.048 + 17.048 + 8.444) ÷ 1000 = 0.077</t>
         </is>
       </c>
-      <c r="F528" s="10" t="n"/>
+      <c r="F528" s="10" t="n">
+        <v>0.077</v>
+      </c>
     </row>
     <row r="529" ht="18" customHeight="1">
       <c r="A529" s="3" t="n">
@@ -11295,7 +12249,7 @@
         </is>
       </c>
       <c r="F529" s="9" t="n">
-        <v>0.146</v>
+        <v>58.56</v>
       </c>
     </row>
     <row r="530" ht="18" customHeight="1">
@@ -11316,7 +12270,9 @@
           <t>29.28 = 29.28</t>
         </is>
       </c>
-      <c r="F530" s="10" t="n"/>
+      <c r="F530" s="9" t="n">
+        <v>29.28</v>
+      </c>
     </row>
     <row r="531" ht="18" customHeight="1">
       <c r="A531" s="3" t="n"/>
@@ -11336,7 +12292,9 @@
           <t>29.28 = 29.28</t>
         </is>
       </c>
-      <c r="F531" s="10" t="n"/>
+      <c r="F531" s="9" t="n">
+        <v>29.28</v>
+      </c>
     </row>
     <row r="532" ht="18" customHeight="1">
       <c r="A532" s="3" t="n"/>
@@ -11356,7 +12314,9 @@
           <t>29.28 = 29.28</t>
         </is>
       </c>
-      <c r="F532" s="10" t="n"/>
+      <c r="F532" s="9" t="n">
+        <v>29.28</v>
+      </c>
     </row>
     <row r="533" ht="18" customHeight="1">
       <c r="A533" s="3" t="n"/>
@@ -11372,7 +12332,9 @@
           <t>(58.56 + 29.28 + 29.28 + 29.28) ÷ 1000 = 0.146</t>
         </is>
       </c>
-      <c r="F533" s="10" t="n"/>
+      <c r="F533" s="10" t="n">
+        <v>0.146</v>
+      </c>
     </row>
     <row r="534" ht="18" customHeight="1">
       <c r="A534" s="3" t="n">
@@ -11399,7 +12361,7 @@
         </is>
       </c>
       <c r="F534" s="9" t="n">
-        <v>0.021</v>
+        <v>17.181</v>
       </c>
     </row>
     <row r="535" ht="18" customHeight="1">
@@ -11420,7 +12382,9 @@
           <t>4.267 = 4.267</t>
         </is>
       </c>
-      <c r="F535" s="10" t="n"/>
+      <c r="F535" s="9" t="n">
+        <v>4.267</v>
+      </c>
     </row>
     <row r="536" ht="18" customHeight="1">
       <c r="A536" s="3" t="n"/>
@@ -11436,7 +12400,9 @@
           <t>(17.181 + 4.267) ÷ 1000 = 0.021</t>
         </is>
       </c>
-      <c r="F536" s="10" t="n"/>
+      <c r="F536" s="10" t="n">
+        <v>0.021</v>
+      </c>
     </row>
     <row r="537" ht="18" customHeight="1">
       <c r="A537" s="3" t="n">
@@ -11463,7 +12429,7 @@
         </is>
       </c>
       <c r="F537" s="9" t="n">
-        <v>0.08400000000000001</v>
+        <v>70.66200000000001</v>
       </c>
     </row>
     <row r="538" ht="18" customHeight="1">
@@ -11484,7 +12450,9 @@
           <t>6.394 + 6.948 = 13.342</t>
         </is>
       </c>
-      <c r="F538" s="10" t="n"/>
+      <c r="F538" s="9" t="n">
+        <v>13.342</v>
+      </c>
     </row>
     <row r="539" ht="18" customHeight="1">
       <c r="A539" s="3" t="n"/>
@@ -11500,7 +12468,9 @@
           <t>(70.662 + 13.342) ÷ 1000 = 0.084</t>
         </is>
       </c>
-      <c r="F539" s="10" t="n"/>
+      <c r="F539" s="10" t="n">
+        <v>0.08400000000000001</v>
+      </c>
     </row>
     <row r="540" ht="18" customHeight="1">
       <c r="A540" s="3" t="n">
@@ -11527,7 +12497,7 @@
         </is>
       </c>
       <c r="F540" s="9" t="n">
-        <v>0.006</v>
+        <v>6.04</v>
       </c>
     </row>
     <row r="541" ht="18" customHeight="1">
@@ -11544,7 +12514,9 @@
           <t>(6.04) ÷ 1000 = 0.006</t>
         </is>
       </c>
-      <c r="F541" s="10" t="n"/>
+      <c r="F541" s="10" t="n">
+        <v>0.006</v>
+      </c>
     </row>
     <row r="542" ht="18" customHeight="1">
       <c r="A542" s="3" t="n">
@@ -11571,7 +12543,7 @@
         </is>
       </c>
       <c r="F542" s="9" t="n">
-        <v>0.263</v>
+        <v>263.369</v>
       </c>
     </row>
     <row r="543" ht="18" customHeight="1">
@@ -11588,7 +12560,9 @@
           <t>(263.369) ÷ 1000 = 0.263</t>
         </is>
       </c>
-      <c r="F543" s="10" t="n"/>
+      <c r="F543" s="10" t="n">
+        <v>0.263</v>
+      </c>
     </row>
     <row r="544" ht="18" customHeight="1">
       <c r="A544" s="3" t="n">
@@ -11615,7 +12589,7 @@
         </is>
       </c>
       <c r="F544" s="5" t="n">
-        <v>13.83</v>
+        <v>9</v>
       </c>
     </row>
     <row r="545" ht="18" customHeight="1">
@@ -11636,7 +12610,9 @@
           <t>(0.8×2.1) = 1.68</t>
         </is>
       </c>
-      <c r="F545" s="8" t="n"/>
+      <c r="F545" s="5" t="n">
+        <v>1.68</v>
+      </c>
     </row>
     <row r="546" ht="18" customHeight="1">
       <c r="A546" s="3" t="n"/>
@@ -11656,7 +12632,9 @@
           <t>(1.5×2.1) = 3.15</t>
         </is>
       </c>
-      <c r="F546" s="8" t="n"/>
+      <c r="F546" s="5" t="n">
+        <v>3.15</v>
+      </c>
     </row>
     <row r="547" ht="18" customHeight="1">
       <c r="A547" s="3" t="n"/>
@@ -11672,7 +12650,9 @@
           <t>9 + 1.68 + 3.15 = 13.83 ≈ 13.83</t>
         </is>
       </c>
-      <c r="F547" s="8" t="n"/>
+      <c r="F547" s="8" t="n">
+        <v>13.83</v>
+      </c>
     </row>
     <row r="548" ht="18" customHeight="1">
       <c r="A548" s="3" t="n">
@@ -11699,7 +12679,7 @@
         </is>
       </c>
       <c r="F548" s="5" t="n">
-        <v>164.64</v>
+        <v>8.640000000000001</v>
       </c>
     </row>
     <row r="549" ht="18" customHeight="1">
@@ -11720,7 +12700,9 @@
           <t>[(2.4×1.8)]×2 = 8.64</t>
         </is>
       </c>
-      <c r="F549" s="8" t="n"/>
+      <c r="F549" s="5" t="n">
+        <v>8.640000000000001</v>
+      </c>
     </row>
     <row r="550" ht="18" customHeight="1">
       <c r="A550" s="3" t="n"/>
@@ -11740,7 +12722,9 @@
           <t>(1.8×1.8) = 3.24</t>
         </is>
       </c>
-      <c r="F550" s="8" t="n"/>
+      <c r="F550" s="5" t="n">
+        <v>3.24</v>
+      </c>
     </row>
     <row r="551" ht="18" customHeight="1">
       <c r="A551" s="3" t="n"/>
@@ -11760,7 +12744,9 @@
           <t>(1.8×1) = 1.8</t>
         </is>
       </c>
-      <c r="F551" s="8" t="n"/>
+      <c r="F551" s="5" t="n">
+        <v>1.8</v>
+      </c>
     </row>
     <row r="552" ht="18" customHeight="1">
       <c r="A552" s="3" t="n"/>
@@ -11780,7 +12766,9 @@
           <t>[(1.2×3.05)]×2 = 7.32</t>
         </is>
       </c>
-      <c r="F552" s="8" t="n"/>
+      <c r="F552" s="5" t="n">
+        <v>7.32</v>
+      </c>
     </row>
     <row r="553" ht="18" customHeight="1">
       <c r="A553" s="3" t="n"/>
@@ -11800,7 +12788,9 @@
           <t>(4×1.8) = 7.2</t>
         </is>
       </c>
-      <c r="F553" s="8" t="n"/>
+      <c r="F553" s="5" t="n">
+        <v>7.2</v>
+      </c>
     </row>
     <row r="554" ht="18" customHeight="1">
       <c r="A554" s="3" t="n"/>
@@ -11820,7 +12810,9 @@
           <t>[(2.4×3.2)]×2 = 15.36</t>
         </is>
       </c>
-      <c r="F554" s="8" t="n"/>
+      <c r="F554" s="5" t="n">
+        <v>15.36</v>
+      </c>
     </row>
     <row r="555" ht="18" customHeight="1">
       <c r="A555" s="3" t="n"/>
@@ -11840,7 +12832,9 @@
           <t>[(2.4×1.8)]×2 = 8.64</t>
         </is>
       </c>
-      <c r="F555" s="8" t="n"/>
+      <c r="F555" s="5" t="n">
+        <v>8.640000000000001</v>
+      </c>
     </row>
     <row r="556" ht="18" customHeight="1">
       <c r="A556" s="3" t="n"/>
@@ -11860,7 +12854,9 @@
           <t>[(1.8×1.8)]×2 = 6.48</t>
         </is>
       </c>
-      <c r="F556" s="8" t="n"/>
+      <c r="F556" s="5" t="n">
+        <v>6.48</v>
+      </c>
     </row>
     <row r="557" ht="18" customHeight="1">
       <c r="A557" s="3" t="n"/>
@@ -11880,7 +12876,9 @@
           <t>[(1.2×3.05)]×2 = 7.32</t>
         </is>
       </c>
-      <c r="F557" s="8" t="n"/>
+      <c r="F557" s="5" t="n">
+        <v>7.32</v>
+      </c>
     </row>
     <row r="558" ht="18" customHeight="1">
       <c r="A558" s="3" t="n"/>
@@ -11900,7 +12898,9 @@
           <t>(4×1.8) = 7.2</t>
         </is>
       </c>
-      <c r="F558" s="8" t="n"/>
+      <c r="F558" s="5" t="n">
+        <v>7.2</v>
+      </c>
     </row>
     <row r="559" ht="18" customHeight="1">
       <c r="A559" s="3" t="n"/>
@@ -11920,7 +12920,9 @@
           <t>[(2.4×3.2)]×2 = 15.36</t>
         </is>
       </c>
-      <c r="F559" s="8" t="n"/>
+      <c r="F559" s="5" t="n">
+        <v>15.36</v>
+      </c>
     </row>
     <row r="560" ht="18" customHeight="1">
       <c r="A560" s="3" t="n"/>
@@ -11940,7 +12942,9 @@
           <t>[(2.4×1.8)]×2 = 8.64</t>
         </is>
       </c>
-      <c r="F560" s="8" t="n"/>
+      <c r="F560" s="5" t="n">
+        <v>8.640000000000001</v>
+      </c>
     </row>
     <row r="561" ht="18" customHeight="1">
       <c r="A561" s="3" t="n"/>
@@ -11960,7 +12964,9 @@
           <t>[(1.8×1.8)]×2 = 6.48</t>
         </is>
       </c>
-      <c r="F561" s="8" t="n"/>
+      <c r="F561" s="5" t="n">
+        <v>6.48</v>
+      </c>
     </row>
     <row r="562" ht="18" customHeight="1">
       <c r="A562" s="3" t="n"/>
@@ -11980,7 +12986,9 @@
           <t>[(1.2×3.05)]×2 = 7.32</t>
         </is>
       </c>
-      <c r="F562" s="8" t="n"/>
+      <c r="F562" s="5" t="n">
+        <v>7.32</v>
+      </c>
     </row>
     <row r="563" ht="18" customHeight="1">
       <c r="A563" s="3" t="n"/>
@@ -12000,7 +13008,9 @@
           <t>(4×1.8) = 7.2</t>
         </is>
       </c>
-      <c r="F563" s="8" t="n"/>
+      <c r="F563" s="5" t="n">
+        <v>7.2</v>
+      </c>
     </row>
     <row r="564" ht="18" customHeight="1">
       <c r="A564" s="3" t="n"/>
@@ -12020,7 +13030,9 @@
           <t>[(2.4×3.2)]×2 = 15.36</t>
         </is>
       </c>
-      <c r="F564" s="8" t="n"/>
+      <c r="F564" s="5" t="n">
+        <v>15.36</v>
+      </c>
     </row>
     <row r="565" ht="18" customHeight="1">
       <c r="A565" s="3" t="n"/>
@@ -12040,7 +13052,9 @@
           <t>[(2.4×1.8)]×2 = 8.64</t>
         </is>
       </c>
-      <c r="F565" s="8" t="n"/>
+      <c r="F565" s="5" t="n">
+        <v>8.640000000000001</v>
+      </c>
     </row>
     <row r="566" ht="18" customHeight="1">
       <c r="A566" s="3" t="n"/>
@@ -12060,7 +13074,9 @@
           <t>[(1.8×1.8)]×2 = 6.48</t>
         </is>
       </c>
-      <c r="F566" s="8" t="n"/>
+      <c r="F566" s="5" t="n">
+        <v>6.48</v>
+      </c>
     </row>
     <row r="567" ht="18" customHeight="1">
       <c r="A567" s="3" t="n"/>
@@ -12080,7 +13096,9 @@
           <t>[(1.2×3.05)]×2 = 7.32</t>
         </is>
       </c>
-      <c r="F567" s="8" t="n"/>
+      <c r="F567" s="5" t="n">
+        <v>7.32</v>
+      </c>
     </row>
     <row r="568" ht="18" customHeight="1">
       <c r="A568" s="3" t="n"/>
@@ -12096,7 +13114,9 @@
           <t>8.64 + 8.64 + 3.24 + 1.8 + 7.32 + 7.2 + 15.36 + 8.64 + 6.48 + 7.32 + 7.2 + 15.36 + 8.64 + 6.48 + 7.32 + 7.2 + 15.36 + 8.64 + 6.48 + 7.32 = 164.64 ≈ 164.64</t>
         </is>
       </c>
-      <c r="F568" s="8" t="n"/>
+      <c r="F568" s="8" t="n">
+        <v>164.64</v>
+      </c>
     </row>
     <row r="569" ht="18" customHeight="1">
       <c r="A569" s="3" t="n">
@@ -12123,7 +13143,7 @@
         </is>
       </c>
       <c r="F569" s="5" t="n">
-        <v>219.3</v>
+        <v>219.2982</v>
       </c>
     </row>
     <row r="570" ht="18" customHeight="1">
@@ -12140,7 +13160,9 @@
           <t>219.2982 ≈ 219.30</t>
         </is>
       </c>
-      <c r="F570" s="8" t="n"/>
+      <c r="F570" s="8" t="n">
+        <v>219.3</v>
+      </c>
     </row>
     <row r="571" ht="18" customHeight="1">
       <c r="A571" s="3" t="n">
@@ -12167,7 +13189,7 @@
         </is>
       </c>
       <c r="F571" s="5" t="n">
-        <v>200.13</v>
+        <v>200.1282</v>
       </c>
     </row>
     <row r="572" ht="18" customHeight="1">
@@ -12184,7 +13206,9 @@
           <t>200.1282 ≈ 200.13</t>
         </is>
       </c>
-      <c r="F572" s="8" t="n"/>
+      <c r="F572" s="8" t="n">
+        <v>200.13</v>
+      </c>
     </row>
     <row r="573" ht="18" customHeight="1">
       <c r="A573" s="3" t="n">
@@ -12210,7 +13234,7 @@
           <t>计算书中无依据，需补充</t>
         </is>
       </c>
-      <c r="F573" s="8" t="inlineStr">
+      <c r="F573" s="5" t="inlineStr">
         <is>
           <t>需补充</t>
         </is>
@@ -12241,7 +13265,7 @@
         </is>
       </c>
       <c r="F574" s="5" t="n">
-        <v>4.58</v>
+        <v>4.5787</v>
       </c>
     </row>
     <row r="575" ht="18" customHeight="1">
@@ -12258,7 +13282,9 @@
           <t>4.5787 ≈ 4.58</t>
         </is>
       </c>
-      <c r="F575" s="8" t="n"/>
+      <c r="F575" s="8" t="n">
+        <v>4.58</v>
+      </c>
     </row>
     <row r="576" ht="18" customHeight="1">
       <c r="A576" s="3" t="n">
@@ -12285,7 +13311,7 @@
         </is>
       </c>
       <c r="F576" s="5" t="n">
-        <v>200.13</v>
+        <v>200.1282</v>
       </c>
     </row>
     <row r="577" ht="18" customHeight="1">
@@ -12302,7 +13328,9 @@
           <t>200.1282 ≈ 200.13</t>
         </is>
       </c>
-      <c r="F577" s="8" t="n"/>
+      <c r="F577" s="8" t="n">
+        <v>200.13</v>
+      </c>
     </row>
     <row r="578" ht="18" customHeight="1">
       <c r="A578" s="3" t="n">
@@ -12329,7 +13357,7 @@
         </is>
       </c>
       <c r="F578" s="5" t="n">
-        <v>796.17</v>
+        <v>172.0871</v>
       </c>
     </row>
     <row r="579" ht="18" customHeight="1">
@@ -12350,7 +13378,9 @@
           <t>(15.26×13.26)+1.8131-1.404-0.62-0.4428-0.7875 = 200.9065</t>
         </is>
       </c>
-      <c r="F579" s="8" t="n"/>
+      <c r="F579" s="5" t="n">
+        <v>200.9065</v>
+      </c>
     </row>
     <row r="580" ht="18" customHeight="1">
       <c r="A580" s="3" t="n"/>
@@ -12370,7 +13400,9 @@
           <t>(15.26×13.26)-1.404-0.62-0.4428 = 199.8808</t>
         </is>
       </c>
-      <c r="F580" s="8" t="n"/>
+      <c r="F580" s="5" t="n">
+        <v>199.8808</v>
+      </c>
     </row>
     <row r="581" ht="18" customHeight="1">
       <c r="A581" s="3" t="n"/>
@@ -12390,7 +13422,9 @@
           <t>(15.26×13.26)-1.404-0.62-0.4428 = 199.8808</t>
         </is>
       </c>
-      <c r="F581" s="8" t="n"/>
+      <c r="F581" s="5" t="n">
+        <v>199.8808</v>
+      </c>
     </row>
     <row r="582" ht="18" customHeight="1">
       <c r="A582" s="3" t="n"/>
@@ -12410,7 +13444,9 @@
           <t>(7.41×3.16) = 23.4156</t>
         </is>
       </c>
-      <c r="F582" s="8" t="n"/>
+      <c r="F582" s="5" t="n">
+        <v>23.4156</v>
+      </c>
     </row>
     <row r="583" ht="18" customHeight="1">
       <c r="A583" s="3" t="n"/>
@@ -12426,7 +13462,9 @@
           <t>172.0871 + 200.9065 + 199.8808 + 199.8808 + 23.4156 = 796.1708 ≈ 796.17</t>
         </is>
       </c>
-      <c r="F583" s="8" t="n"/>
+      <c r="F583" s="8" t="n">
+        <v>796.17</v>
+      </c>
     </row>
     <row r="584" ht="18" customHeight="1">
       <c r="A584" s="3" t="n">
@@ -12453,7 +13491,7 @@
         </is>
       </c>
       <c r="F584" s="5" t="n">
-        <v>4.58</v>
+        <v>4.5787</v>
       </c>
     </row>
     <row r="585" ht="18" customHeight="1">
@@ -12470,7 +13508,9 @@
           <t>4.5787 ≈ 4.58</t>
         </is>
       </c>
-      <c r="F585" s="8" t="n"/>
+      <c r="F585" s="8" t="n">
+        <v>4.58</v>
+      </c>
     </row>
     <row r="586" ht="18" customHeight="1">
       <c r="A586" s="3" t="n">
@@ -12497,7 +13537,7 @@
         </is>
       </c>
       <c r="F586" s="5" t="n">
-        <v>264.13</v>
+        <v>58.63</v>
       </c>
     </row>
     <row r="587" ht="18" customHeight="1">
@@ -12518,7 +13558,9 @@
           <t>13.26+1.425-0.905-1.2 + 15.02+1.64-1.02-1.8 + 13.26+1.9569-1.405-1.2 + 15.26-4.8 + [5.85+1.355-0.975]×2 = 61.9519</t>
         </is>
       </c>
-      <c r="F587" s="8" t="n"/>
+      <c r="F587" s="5" t="n">
+        <v>61.9519</v>
+      </c>
     </row>
     <row r="588" ht="18" customHeight="1">
       <c r="A588" s="3" t="n"/>
@@ -12538,7 +13580,9 @@
           <t>[5.85+1.355-0.975]×2 + 15.26-4.8 + 13.26+1.9569-1.405-1.2 + 15.02+1.64-1.02-1.8 + 13.26+1.425-0.905-1.2 = 61.9519</t>
         </is>
       </c>
-      <c r="F588" s="8" t="n"/>
+      <c r="F588" s="5" t="n">
+        <v>61.9519</v>
+      </c>
     </row>
     <row r="589" ht="18" customHeight="1">
       <c r="A589" s="3" t="n"/>
@@ -12558,7 +13602,9 @@
           <t>[5.85+1.355-0.975]×2 + 15.26-4.8 + 13.26+1.9569-1.405-1.2 + 15.02+1.64-1.02-1.8 + 13.26+1.425-0.905-1.2 = 61.9519</t>
         </is>
       </c>
-      <c r="F589" s="8" t="n"/>
+      <c r="F589" s="5" t="n">
+        <v>61.9519</v>
+      </c>
     </row>
     <row r="590" ht="18" customHeight="1">
       <c r="A590" s="3" t="n"/>
@@ -12578,7 +13624,9 @@
           <t>[3.16]×2 + 7.41 + 7.41-1.5 = 19.64</t>
         </is>
       </c>
-      <c r="F590" s="8" t="n"/>
+      <c r="F590" s="5" t="n">
+        <v>19.64</v>
+      </c>
     </row>
     <row r="591" ht="18" customHeight="1">
       <c r="A591" s="3" t="n"/>
@@ -12594,7 +13642,9 @@
           <t>58.63 + 61.9519 + 61.9519 + 61.9519 + 19.64 = 264.1257 ≈ 264.13</t>
         </is>
       </c>
-      <c r="F591" s="8" t="n"/>
+      <c r="F591" s="8" t="n">
+        <v>264.13</v>
+      </c>
     </row>
     <row r="592" ht="18" customHeight="1">
       <c r="A592" s="3" t="n">
@@ -12621,7 +13671,7 @@
         </is>
       </c>
       <c r="F592" s="5" t="n">
-        <v>770.35</v>
+        <v>161.8592</v>
       </c>
     </row>
     <row r="593" ht="32" customHeight="1">
@@ -12642,7 +13692,9 @@
           <t>13.74×3.6-5.004+5.565-6.605+6.7285-3.66 + 15.74×3.6-3.564+5.424-5.9+6.0475-22.56 + 13.74×3.6-5.904+6.4955-6.4675+6.5885-3.66 + 15.5×3.6-5.4+6.428-5.6+5.74-14.4 = 171.6845</t>
         </is>
       </c>
-      <c r="F593" s="8" t="n"/>
+      <c r="F593" s="5" t="n">
+        <v>171.6845</v>
+      </c>
     </row>
     <row r="594" ht="32" customHeight="1">
       <c r="A594" s="3" t="n"/>
@@ -12662,7 +13714,9 @@
           <t>13.74×3.6-5.004+5.565-6.605+6.7285-3.66 + 15.74×3.6-3.564+5.424-5.9+6.0475-22.56 + 13.74×3.6-5.904+6.4955-6.4675+6.5885-3.66 + 15.5×3.6-5.4+6.428-5.6+5.74-14.4 = 171.6845</t>
         </is>
       </c>
-      <c r="F594" s="8" t="n"/>
+      <c r="F594" s="5" t="n">
+        <v>171.6845</v>
+      </c>
     </row>
     <row r="595" ht="32" customHeight="1">
       <c r="A595" s="3" t="n"/>
@@ -12682,7 +13736,9 @@
           <t>13.74×3.6-5.004+5.565-6.605+6.7285-3.66 + 15.74×3.6-3.564+5.424-5.9+6.0475-22.56 + 13.74×3.6-5.904+6.4955-6.4675+6.5873-3.66 + 15.5×3.6-5.4+6.428-5.6+5.74-13.59 = 172.4933</t>
         </is>
       </c>
-      <c r="F595" s="8" t="n"/>
+      <c r="F595" s="5" t="n">
+        <v>172.4933</v>
+      </c>
     </row>
     <row r="596" ht="32" customHeight="1">
       <c r="A596" s="3" t="n"/>
@@ -12702,7 +13758,9 @@
           <t>(13.74×1.07+1.6344)-0.2843+0.4013+1.9356-4.0413 + (15.74×1.07+1.8744)-0.8662+1.3375+2.1118-4.5 + (5.85×1.07+0.6948)-0.2903+0.5403+0.8243-1.68 + (7.65×3.642+0.9108)-0.75+1.3932-2.22+2.2927+1.1166-1.5228 + (3.642×3.64+0.444)-1.47+1.3922-1.26+1.2915+0.5228-0.7352 + (12.1×1.07+1.4448)-0.0059+0.1391+1.7006-3.6213 = 92.6237</t>
         </is>
       </c>
-      <c r="F596" s="8" t="n"/>
+      <c r="F596" s="5" t="n">
+        <v>92.6237</v>
+      </c>
     </row>
     <row r="597" ht="18" customHeight="1">
       <c r="A597" s="3" t="n"/>
@@ -12718,7 +13776,9 @@
           <t>161.8592 + 171.6845 + 171.6845 + 172.4933 + 92.6237 = 770.3452 ≈ 770.35</t>
         </is>
       </c>
-      <c r="F597" s="8" t="n"/>
+      <c r="F597" s="8" t="n">
+        <v>770.35</v>
+      </c>
     </row>
     <row r="598" ht="32" customHeight="1">
       <c r="A598" s="3" t="n">
@@ -12745,7 +13805,7 @@
         </is>
       </c>
       <c r="F598" s="5" t="n">
-        <v>962.71</v>
+        <v>187.5849</v>
       </c>
     </row>
     <row r="599" ht="18" customHeight="1">
@@ -12766,7 +13826,9 @@
           <t>3.165×1.5-0.2475+0.2242-1.53-0.48+1.2 + [1.5×1.455-0.24+0.2205-0.7122+0.7122]×2 + 3.165×1.5-0.315 = 12.6727</t>
         </is>
       </c>
-      <c r="F599" s="8" t="n"/>
+      <c r="F599" s="5" t="n">
+        <v>12.6727</v>
+      </c>
     </row>
     <row r="600" ht="32" customHeight="1">
       <c r="A600" s="3" t="n"/>
@@ -12786,7 +13848,9 @@
           <t>46.3392-3.1814+4.8397-3.66-5.3027+5.2265 + (3.6×3.16+41.3344)-3.5734+5.486-15.12-3.617+4.337 + 46.8969-4.994+6.5147-3.66-5.5729+5.5078-0.11-0.4277 + 15.26×3.51-1.7901+1.696-22.56-4.5725+4.495 + 20.9313-3.47+4.6402-2.5926+2.5926 + 5.85×3.5-3.4125+4.5985-2.1938+2.1313 = 203.1701</t>
         </is>
       </c>
-      <c r="F600" s="8" t="n"/>
+      <c r="F600" s="5" t="n">
+        <v>203.1701</v>
+      </c>
     </row>
     <row r="601" ht="32" customHeight="1">
       <c r="A601" s="3" t="n"/>
@@ -12806,7 +13870,9 @@
           <t>20.9313-3.47+4.6402-2.5926+2.5926 + 5.85×3.5-3.4125+4.5985-2.1938+2.1313 + 15.26×3.51-1.7901+1.696-22.56-4.5725+4.495 + 46.8969-4.994+6.5147-3.66-5.5729+5.5078-0.11-0.4277 + (3.6×3.16+41.3344)-3.5734+5.486-15.12-3.617+4.337 + 46.3392-3.1814+4.8397-3.66-5.3027+5.2265 = 203.1701</t>
         </is>
       </c>
-      <c r="F601" s="8" t="n"/>
+      <c r="F601" s="5" t="n">
+        <v>203.1701</v>
+      </c>
     </row>
     <row r="602" ht="32" customHeight="1">
       <c r="A602" s="3" t="n"/>
@@ -12826,7 +13892,9 @@
           <t>20.9313-3.47+4.6402-2.5926+2.5926 + 20.528-3.428+4.5985-2.2313+2.1187 + 15.26×3.6-1.836+1.696-22.56-5.9+4.35 + 47.0211-5.0058+6.5137-3.66-5.6854+5.4953-0.11-0.4277 + (3.6×3.16+11.86×3.6)-3.672+5.5-13.59-5.6+4.5 + 46.374-3.201+4.8307-3.66-5.318+5.083 = 203.8336</t>
         </is>
       </c>
-      <c r="F602" s="8" t="n"/>
+      <c r="F602" s="5" t="n">
+        <v>203.8336</v>
+      </c>
     </row>
     <row r="603" ht="18" customHeight="1">
       <c r="A603" s="3" t="n"/>
@@ -12846,7 +13914,9 @@
           <t>3.16×3-0.03+0.029-0.315 + 21.542-0.0295+0.029-0.0525 + 3.16×2.9-0.029+0.0278 + 21.542-0.0295+0.029-3.15-0.4937+0.4937-0.0525 = 58.1547</t>
         </is>
       </c>
-      <c r="F603" s="8" t="n"/>
+      <c r="F603" s="5" t="n">
+        <v>58.1547</v>
+      </c>
     </row>
     <row r="604" ht="32" customHeight="1">
       <c r="A604" s="3" t="n"/>
@@ -12866,7 +13936,9 @@
           <t>(27.6045+0.9108)-0.4932+1.2343-3.15-2.3188+2.194 + (5.61×(1.07+0.12))-0.0107+0.0107 + (15.26×(1.07+0.12))-0.3082+0.2889 + (13.26×(1.07+0.12))-0.0053+0.0053 + (12.563+0.4152)-0.8532+1.272-0.945+0.9765 + (11.86×(1.07+0.12))-0.0053+0.0053 = 94.1189</t>
         </is>
       </c>
-      <c r="F604" s="8" t="n"/>
+      <c r="F604" s="5" t="n">
+        <v>94.1189</v>
+      </c>
     </row>
     <row r="605" ht="18" customHeight="1">
       <c r="A605" s="3" t="n"/>
@@ -12882,7 +13954,9 @@
           <t>187.5849 + 12.6727 + 203.1701 + 203.1701 + 203.8336 + 58.1547 + 94.1189 = 962.705 ≈ 962.71</t>
         </is>
       </c>
-      <c r="F605" s="8" t="n"/>
+      <c r="F605" s="8" t="n">
+        <v>962.71</v>
+      </c>
     </row>
     <row r="606" ht="18" customHeight="1">
       <c r="A606" s="3" t="n">
@@ -12909,7 +13983,7 @@
         </is>
       </c>
       <c r="F606" s="5" t="n">
-        <v>16.88</v>
+        <v>16.878</v>
       </c>
     </row>
     <row r="607" ht="18" customHeight="1">
@@ -12926,7 +14000,9 @@
           <t>16.878 ≈ 16.88</t>
         </is>
       </c>
-      <c r="F607" s="8" t="n"/>
+      <c r="F607" s="8" t="n">
+        <v>16.88</v>
+      </c>
     </row>
     <row r="608" ht="18" customHeight="1">
       <c r="A608" s="3" t="n">
@@ -12953,7 +14029,7 @@
         </is>
       </c>
       <c r="F608" s="5" t="n">
-        <v>908.76</v>
+        <v>192.2586</v>
       </c>
     </row>
     <row r="609" ht="32" customHeight="1">
@@ -12974,7 +14050,9 @@
           <t>(3×2.28)+2.7827+0.0141-0.9137-0.0137 + (15.26×1.38)+10.9493+0.0863-2.8487-0.085 + (4.33×3.15)+5.1219+0.0144-1.445-0.0145 + (5.73×2.28+8.73×2.05+11.88×4.45)+26.639+0.0678-7.4369-0.07 + (1.68×0.12+3.16×1.8)+4.661+0.0081-0.9994-0.0077 + (6.48×4.35+3.2×1.68+5.85×3.08)+21.8681+0.059-5.4175-0.062 = 235.7941</t>
         </is>
       </c>
-      <c r="F609" s="8" t="n"/>
+      <c r="F609" s="5" t="n">
+        <v>235.7941</v>
+      </c>
     </row>
     <row r="610" ht="32" customHeight="1">
       <c r="A610" s="3" t="n"/>
@@ -12994,7 +14072,9 @@
           <t>(8.78×5.73+6.5×3+4.45×3.15)+26.639+0.0678-7.4369-0.07 + (4.33×3.15)+5.1219+0.0144-1.445-0.0145 + (15.26×1.38)+10.9492+0.0863-2.8487-0.085 + (3×2.28)+2.7827+0.0141-0.9137-0.0137 + (6.48×4.35+3.2×1.68+5.85×3.08)+21.8681+0.059-5.4175-0.062 + (1.68×0.12+3.16×1.8)+4.661+0.0081-0.9994-0.0077 = 235.7941</t>
         </is>
       </c>
-      <c r="F610" s="8" t="n"/>
+      <c r="F610" s="5" t="n">
+        <v>235.7941</v>
+      </c>
     </row>
     <row r="611" ht="18" customHeight="1">
       <c r="A611" s="3" t="n"/>
@@ -13014,7 +14094,9 @@
           <t>77.2942+18.6475+0.1879-9.1212-0.1917 + (11.35×8.78)+30.8617+0.0536-8.4587-0.0542 + (1.68×0.12+3.16×1.8)+5.8422+0.0081-0.9994-0.0077 = 219.6049</t>
         </is>
       </c>
-      <c r="F611" s="8" t="n"/>
+      <c r="F611" s="5" t="n">
+        <v>219.6049</v>
+      </c>
     </row>
     <row r="612" ht="18" customHeight="1">
       <c r="A612" s="3" t="n"/>
@@ -13034,7 +14116,9 @@
           <t>(7.41×3.16)+2.686+0.0099-0.79-0.0099 = 25.3116</t>
         </is>
       </c>
-      <c r="F612" s="8" t="n"/>
+      <c r="F612" s="5" t="n">
+        <v>25.3116</v>
+      </c>
     </row>
     <row r="613" ht="18" customHeight="1">
       <c r="A613" s="3" t="n"/>
@@ -13050,7 +14134,9 @@
           <t>192.2586 + 235.7941 + 235.7941 + 219.6049 + 25.3116 = 908.7633 ≈ 908.76</t>
         </is>
       </c>
-      <c r="F613" s="8" t="n"/>
+      <c r="F613" s="8" t="n">
+        <v>908.76</v>
+      </c>
     </row>
     <row r="614" ht="18" customHeight="1">
       <c r="A614" s="3" t="n">
@@ -13077,7 +14163,7 @@
         </is>
       </c>
       <c r="F614" s="5" t="n">
-        <v>770.35</v>
+        <v>161.8592</v>
       </c>
     </row>
     <row r="615" ht="32" customHeight="1">
@@ -13098,7 +14184,9 @@
           <t>13.74×3.6-5.004+5.565-6.605+6.7285-3.66 + 15.74×3.6-3.564+5.424-5.9+6.0475-22.56 + 13.74×3.6-5.904+6.4955-6.4675+6.5885-3.66 + 15.5×3.6-5.4+6.428-5.6+5.74-14.4 = 171.6845</t>
         </is>
       </c>
-      <c r="F615" s="8" t="n"/>
+      <c r="F615" s="5" t="n">
+        <v>171.6845</v>
+      </c>
     </row>
     <row r="616" ht="32" customHeight="1">
       <c r="A616" s="3" t="n"/>
@@ -13118,7 +14206,9 @@
           <t>13.74×3.6-5.004+5.565-6.605+6.7285-3.66 + 15.74×3.6-3.564+5.424-5.9+6.0475-22.56 + 13.74×3.6-5.904+6.4955-6.4675+6.5885-3.66 + 15.5×3.6-5.4+6.428-5.6+5.74-14.4 = 171.6845</t>
         </is>
       </c>
-      <c r="F616" s="8" t="n"/>
+      <c r="F616" s="5" t="n">
+        <v>171.6845</v>
+      </c>
     </row>
     <row r="617" ht="32" customHeight="1">
       <c r="A617" s="3" t="n"/>
@@ -13138,7 +14228,9 @@
           <t>13.74×3.6-5.004+5.565-6.605+6.7285-3.66 + 15.74×3.6-3.564+5.424-5.9+6.0475-22.56 + 13.74×3.6-5.904+6.4955-6.4675+6.5873-3.66 + 15.5×3.6-5.4+6.428-5.6+5.74-13.59 = 172.4933</t>
         </is>
       </c>
-      <c r="F617" s="8" t="n"/>
+      <c r="F617" s="5" t="n">
+        <v>172.4933</v>
+      </c>
     </row>
     <row r="618" ht="32" customHeight="1">
       <c r="A618" s="3" t="n"/>
@@ -13158,7 +14250,9 @@
           <t>(13.74×1.07+1.6344)-0.2843+0.4013+1.9356-4.0413 + (15.74×1.07+1.8744)-0.8662+1.3375+2.1118-4.5 + (5.85×1.07+0.6948)-0.2903+0.5403+0.8243-1.68 + (7.65×3.642+0.9108)-0.75+1.3932-2.22+2.2927+1.1166-1.5228 + (3.642×3.64+0.444)-1.47+1.3922-1.26+1.2915+0.5228-0.7352 + (12.1×1.07+1.4448)-0.0059+0.1391+1.7006-3.6213 = 92.6237</t>
         </is>
       </c>
-      <c r="F618" s="8" t="n"/>
+      <c r="F618" s="5" t="n">
+        <v>92.6237</v>
+      </c>
     </row>
     <row r="619" ht="18" customHeight="1">
       <c r="A619" s="3" t="n"/>
@@ -13174,7 +14268,9 @@
           <t>161.8592 + 171.6845 + 171.6845 + 172.4933 + 92.6237 = 770.3452 ≈ 770.35</t>
         </is>
       </c>
-      <c r="F619" s="8" t="n"/>
+      <c r="F619" s="8" t="n">
+        <v>770.35</v>
+      </c>
     </row>
     <row r="620" ht="32" customHeight="1">
       <c r="A620" s="3" t="n">
@@ -13201,7 +14297,7 @@
         </is>
       </c>
       <c r="F620" s="5" t="n">
-        <v>962.71</v>
+        <v>187.5849</v>
       </c>
     </row>
     <row r="621" ht="18" customHeight="1">
@@ -13222,7 +14318,9 @@
           <t>3.165×1.5-0.2475+0.2242-1.53-0.48+1.2 + [1.5×1.455-0.24+0.2205-0.7122+0.7122]×2 + 3.165×1.5-0.315 = 12.6727</t>
         </is>
       </c>
-      <c r="F621" s="8" t="n"/>
+      <c r="F621" s="5" t="n">
+        <v>12.6727</v>
+      </c>
     </row>
     <row r="622" ht="32" customHeight="1">
       <c r="A622" s="3" t="n"/>
@@ -13242,7 +14340,9 @@
           <t>46.3392-3.1814+4.8397-3.66-5.3027+5.2265 + (3.6×3.16+41.3344)-3.5734+5.486-15.12-3.617+4.337 + 46.8969-4.994+6.5147-3.66-5.5729+5.5078-0.11-0.4277 + 15.26×3.51-1.7901+1.696-22.56-4.5725+4.495 + 20.9313-3.47+4.6402-2.5926+2.5926 + 5.85×3.5-3.4125+4.5985-2.1938+2.1313 = 203.1701</t>
         </is>
       </c>
-      <c r="F622" s="8" t="n"/>
+      <c r="F622" s="5" t="n">
+        <v>203.1701</v>
+      </c>
     </row>
     <row r="623" ht="32" customHeight="1">
       <c r="A623" s="3" t="n"/>
@@ -13262,7 +14362,9 @@
           <t>20.9313-3.47+4.6402-2.5926+2.5926 + 5.85×3.5-3.4125+4.5985-2.1938+2.1313 + 15.26×3.51-1.7901+1.696-22.56-4.5725+4.495 + 46.8969-4.994+6.5147-3.66-5.5729+5.5078-0.11-0.4277 + (3.6×3.16+41.3344)-3.5734+5.486-15.12-3.617+4.337 + 46.3392-3.1814+4.8397-3.66-5.3027+5.2265 = 203.1701</t>
         </is>
       </c>
-      <c r="F623" s="8" t="n"/>
+      <c r="F623" s="5" t="n">
+        <v>203.1701</v>
+      </c>
     </row>
     <row r="624" ht="32" customHeight="1">
       <c r="A624" s="3" t="n"/>
@@ -13282,7 +14384,9 @@
           <t>20.9313-3.47+4.6402-2.5926+2.5926 + 20.528-3.428+4.5985-2.2313+2.1187 + 15.26×3.6-1.836+1.696-22.56-5.9+4.35 + 47.0211-5.0058+6.5137-3.66-5.6854+5.4953-0.11-0.4277 + (3.6×3.16+11.86×3.6)-3.672+5.5-13.59-5.6+4.5 + 46.374-3.201+4.8307-3.66-5.318+5.083 = 203.8336</t>
         </is>
       </c>
-      <c r="F624" s="8" t="n"/>
+      <c r="F624" s="5" t="n">
+        <v>203.8336</v>
+      </c>
     </row>
     <row r="625" ht="18" customHeight="1">
       <c r="A625" s="3" t="n"/>
@@ -13302,7 +14406,9 @@
           <t>3.16×3-0.03+0.029-0.315 + 21.542-0.0295+0.029-0.0525 + 3.16×2.9-0.029+0.0278 + 21.542-0.0295+0.029-3.15-0.4937+0.4937-0.0525 = 58.1547</t>
         </is>
       </c>
-      <c r="F625" s="8" t="n"/>
+      <c r="F625" s="5" t="n">
+        <v>58.1547</v>
+      </c>
     </row>
     <row r="626" ht="32" customHeight="1">
       <c r="A626" s="3" t="n"/>
@@ -13322,7 +14428,9 @@
           <t>(27.6045+0.9108)-0.4932+1.2343-3.15-2.3188+2.194 + (5.61×(1.07+0.12))-0.0107+0.0107 + (15.26×(1.07+0.12))-0.3082+0.2889 + (13.26×(1.07+0.12))-0.0053+0.0053 + (12.563+0.4152)-0.8532+1.272-0.945+0.9765 + (11.86×(1.07+0.12))-0.0053+0.0053 = 94.1189</t>
         </is>
       </c>
-      <c r="F626" s="8" t="n"/>
+      <c r="F626" s="5" t="n">
+        <v>94.1189</v>
+      </c>
     </row>
     <row r="627" ht="18" customHeight="1">
       <c r="A627" s="3" t="n"/>
@@ -13338,7 +14446,9 @@
           <t>187.5849 + 12.6727 + 203.1701 + 203.1701 + 203.8336 + 58.1547 + 94.1189 = 962.705 ≈ 962.71</t>
         </is>
       </c>
-      <c r="F627" s="8" t="n"/>
+      <c r="F627" s="8" t="n">
+        <v>962.71</v>
+      </c>
     </row>
     <row r="628" ht="18" customHeight="1">
       <c r="A628" s="3" t="n">
@@ -13365,7 +14475,7 @@
         </is>
       </c>
       <c r="F628" s="5" t="n">
-        <v>908.76</v>
+        <v>192.2586</v>
       </c>
     </row>
     <row r="629" ht="32" customHeight="1">
@@ -13386,7 +14496,9 @@
           <t>(3×2.28)+2.7827+0.0141-0.9137-0.0137 + (15.26×1.38)+10.9493+0.0863-2.8487-0.085 + (4.33×3.15)+5.1219+0.0144-1.445-0.0145 + (5.73×2.28+8.73×2.05+11.88×4.45)+26.639+0.0678-7.4369-0.07 + (1.68×0.12+3.16×1.8)+4.661+0.0081-0.9994-0.0077 + (6.48×4.35+3.2×1.68+5.85×3.08)+21.8681+0.059-5.4175-0.062 = 235.7941</t>
         </is>
       </c>
-      <c r="F629" s="8" t="n"/>
+      <c r="F629" s="5" t="n">
+        <v>235.7941</v>
+      </c>
     </row>
     <row r="630" ht="32" customHeight="1">
       <c r="A630" s="3" t="n"/>
@@ -13406,7 +14518,9 @@
           <t>(8.78×5.73+6.5×3+4.45×3.15)+26.639+0.0678-7.4369-0.07 + (4.33×3.15)+5.1219+0.0144-1.445-0.0145 + (15.26×1.38)+10.9492+0.0863-2.8487-0.085 + (3×2.28)+2.7827+0.0141-0.9137-0.0137 + (6.48×4.35+3.2×1.68+5.85×3.08)+21.8681+0.059-5.4175-0.062 + (1.68×0.12+3.16×1.8)+4.661+0.0081-0.9994-0.0077 = 235.7941</t>
         </is>
       </c>
-      <c r="F630" s="8" t="n"/>
+      <c r="F630" s="5" t="n">
+        <v>235.7941</v>
+      </c>
     </row>
     <row r="631" ht="18" customHeight="1">
       <c r="A631" s="3" t="n"/>
@@ -13426,7 +14540,9 @@
           <t>77.2942+18.6475+0.1879-9.1212-0.1917 + (11.35×8.78)+30.8617+0.0536-8.4587-0.0542 + (1.68×0.12+3.16×1.8)+5.8422+0.0081-0.9994-0.0077 = 219.6049</t>
         </is>
       </c>
-      <c r="F631" s="8" t="n"/>
+      <c r="F631" s="5" t="n">
+        <v>219.6049</v>
+      </c>
     </row>
     <row r="632" ht="18" customHeight="1">
       <c r="A632" s="3" t="n"/>
@@ -13446,7 +14562,9 @@
           <t>(7.41×3.16)+2.686+0.0099-0.79-0.0099 = 25.3116</t>
         </is>
       </c>
-      <c r="F632" s="8" t="n"/>
+      <c r="F632" s="5" t="n">
+        <v>25.3116</v>
+      </c>
     </row>
     <row r="633" ht="18" customHeight="1">
       <c r="A633" s="3" t="n"/>
@@ -13462,82 +14580,54 @@
           <t>192.2586 + 235.7941 + 235.7941 + 219.6049 + 25.3116 = 908.7633 ≈ 908.76</t>
         </is>
       </c>
-      <c r="F633" s="8" t="n"/>
+      <c r="F633" s="8" t="n">
+        <v>908.76</v>
+      </c>
     </row>
   </sheetData>
-  <mergeCells count="214">
+  <mergeCells count="143">
     <mergeCell ref="A223:A269"/>
     <mergeCell ref="B374:B392"/>
     <mergeCell ref="B571:B572"/>
     <mergeCell ref="A144:A146"/>
-    <mergeCell ref="F109:F122"/>
     <mergeCell ref="B529:B533"/>
-    <mergeCell ref="F574:F575"/>
-    <mergeCell ref="F578:F583"/>
-    <mergeCell ref="F3:F4"/>
     <mergeCell ref="A7:A8"/>
-    <mergeCell ref="F584:F585"/>
-    <mergeCell ref="F571:F572"/>
     <mergeCell ref="B123:B125"/>
     <mergeCell ref="B23:B24"/>
     <mergeCell ref="A27:A28"/>
-    <mergeCell ref="F521:F522"/>
     <mergeCell ref="B299:B322"/>
     <mergeCell ref="B463:B467"/>
-    <mergeCell ref="F58:F108"/>
     <mergeCell ref="A534:A536"/>
     <mergeCell ref="A123:A125"/>
     <mergeCell ref="B126:B130"/>
-    <mergeCell ref="F184:F194"/>
-    <mergeCell ref="F270:F298"/>
     <mergeCell ref="A393:A414"/>
-    <mergeCell ref="F169:F183"/>
+    <mergeCell ref="A620:A627"/>
     <mergeCell ref="B29:B32"/>
-    <mergeCell ref="A620:A627"/>
-    <mergeCell ref="F483:F495"/>
     <mergeCell ref="A217:A222"/>
     <mergeCell ref="B540:B541"/>
-    <mergeCell ref="F523:F528"/>
     <mergeCell ref="B421:B441"/>
     <mergeCell ref="A442:A451"/>
     <mergeCell ref="B496:B508"/>
     <mergeCell ref="B458:B462"/>
-    <mergeCell ref="F11:F15"/>
     <mergeCell ref="A586:A591"/>
-    <mergeCell ref="F196:F200"/>
     <mergeCell ref="A323:A333"/>
-    <mergeCell ref="F548:F568"/>
     <mergeCell ref="A544:A547"/>
-    <mergeCell ref="F223:F269"/>
-    <mergeCell ref="F201:F216"/>
     <mergeCell ref="A473:A477"/>
-    <mergeCell ref="F144:F146"/>
     <mergeCell ref="B614:B619"/>
     <mergeCell ref="A165:A168"/>
     <mergeCell ref="A16:A20"/>
-    <mergeCell ref="F33:F57"/>
     <mergeCell ref="A334:A373"/>
-    <mergeCell ref="F334:F373"/>
     <mergeCell ref="B25:B26"/>
     <mergeCell ref="A463:A467"/>
-    <mergeCell ref="F569:F570"/>
-    <mergeCell ref="F458:F462"/>
-    <mergeCell ref="F7:F8"/>
     <mergeCell ref="A584:A585"/>
     <mergeCell ref="A540:A541"/>
-    <mergeCell ref="F598:F605"/>
     <mergeCell ref="B131:B143"/>
-    <mergeCell ref="F452:F457"/>
     <mergeCell ref="B27:B28"/>
     <mergeCell ref="B162:B164"/>
     <mergeCell ref="B509:B510"/>
     <mergeCell ref="B3:B4"/>
     <mergeCell ref="A608:A613"/>
-    <mergeCell ref="F534:F536"/>
     <mergeCell ref="A169:A183"/>
-    <mergeCell ref="F393:F414"/>
-    <mergeCell ref="F5:F6"/>
-    <mergeCell ref="F217:F222"/>
     <mergeCell ref="A628:A633"/>
     <mergeCell ref="A452:A457"/>
     <mergeCell ref="A158:A159"/>
@@ -13546,36 +14636,25 @@
     <mergeCell ref="B442:B451"/>
     <mergeCell ref="B270:B298"/>
     <mergeCell ref="B592:B597"/>
-    <mergeCell ref="F442:F451"/>
     <mergeCell ref="A511:A520"/>
     <mergeCell ref="A574:A575"/>
-    <mergeCell ref="F415:F420"/>
-    <mergeCell ref="F586:F591"/>
-    <mergeCell ref="F323:F333"/>
     <mergeCell ref="A21:A22"/>
     <mergeCell ref="B523:B528"/>
     <mergeCell ref="B537:B539"/>
-    <mergeCell ref="F592:F597"/>
     <mergeCell ref="A548:A568"/>
     <mergeCell ref="B109:B122"/>
-    <mergeCell ref="F9:F10"/>
     <mergeCell ref="A201:A216"/>
     <mergeCell ref="B473:B477"/>
     <mergeCell ref="A542:A543"/>
     <mergeCell ref="B574:B575"/>
     <mergeCell ref="B578:B583"/>
-    <mergeCell ref="F473:F477"/>
     <mergeCell ref="A23:A24"/>
-    <mergeCell ref="F165:F168"/>
     <mergeCell ref="A415:A420"/>
     <mergeCell ref="A569:A570"/>
-    <mergeCell ref="F463:F467"/>
-    <mergeCell ref="F147:F157"/>
     <mergeCell ref="B628:B633"/>
     <mergeCell ref="B158:B159"/>
     <mergeCell ref="A374:A392"/>
     <mergeCell ref="B223:B269"/>
-    <mergeCell ref="F540:F541"/>
     <mergeCell ref="A9:A10"/>
     <mergeCell ref="B58:B108"/>
     <mergeCell ref="B11:B15"/>
@@ -13585,18 +14664,14 @@
     <mergeCell ref="B160:B161"/>
     <mergeCell ref="A521:A522"/>
     <mergeCell ref="B483:B495"/>
-    <mergeCell ref="F608:F613"/>
     <mergeCell ref="A537:A539"/>
     <mergeCell ref="A496:A508"/>
     <mergeCell ref="A576:A577"/>
     <mergeCell ref="A126:A130"/>
     <mergeCell ref="B534:B536"/>
     <mergeCell ref="A109:A122"/>
-    <mergeCell ref="F511:F520"/>
     <mergeCell ref="B542:B543"/>
     <mergeCell ref="A614:A619"/>
-    <mergeCell ref="F21:F22"/>
-    <mergeCell ref="F123:F125"/>
     <mergeCell ref="A571:A572"/>
     <mergeCell ref="A421:A441"/>
     <mergeCell ref="B201:B216"/>
@@ -13604,15 +14679,9 @@
     <mergeCell ref="A529:A533"/>
     <mergeCell ref="B334:B373"/>
     <mergeCell ref="B569:B570"/>
-    <mergeCell ref="F468:F472"/>
-    <mergeCell ref="F542:F543"/>
-    <mergeCell ref="F23:F24"/>
     <mergeCell ref="A147:A157"/>
-    <mergeCell ref="F620:F627"/>
     <mergeCell ref="A483:A495"/>
     <mergeCell ref="B9:B10"/>
-    <mergeCell ref="F606:F607"/>
-    <mergeCell ref="F374:F392"/>
     <mergeCell ref="B544:B547"/>
     <mergeCell ref="B393:B414"/>
     <mergeCell ref="A29:A32"/>
@@ -13620,51 +14689,33 @@
     <mergeCell ref="A131:A143"/>
     <mergeCell ref="A458:A462"/>
     <mergeCell ref="B217:B222"/>
-    <mergeCell ref="F537:F539"/>
-    <mergeCell ref="F544:F547"/>
     <mergeCell ref="A162:A164"/>
-    <mergeCell ref="F496:F508"/>
     <mergeCell ref="A598:A605"/>
     <mergeCell ref="A509:A510"/>
-    <mergeCell ref="F16:F20"/>
-    <mergeCell ref="F299:F322"/>
     <mergeCell ref="A1:F1"/>
     <mergeCell ref="B608:B613"/>
-    <mergeCell ref="F126:F130"/>
     <mergeCell ref="B586:B591"/>
     <mergeCell ref="B323:B333"/>
-    <mergeCell ref="F29:F32"/>
     <mergeCell ref="A33:A57"/>
     <mergeCell ref="B21:B22"/>
     <mergeCell ref="A478:A482"/>
-    <mergeCell ref="F25:F26"/>
-    <mergeCell ref="F421:F441"/>
     <mergeCell ref="A468:A472"/>
     <mergeCell ref="B165:B168"/>
     <mergeCell ref="B511:B520"/>
-    <mergeCell ref="F529:F533"/>
     <mergeCell ref="B33:B57"/>
     <mergeCell ref="B147:B157"/>
-    <mergeCell ref="F628:F633"/>
-    <mergeCell ref="F158:F159"/>
     <mergeCell ref="B196:B200"/>
     <mergeCell ref="A606:A607"/>
     <mergeCell ref="A25:A26"/>
     <mergeCell ref="A3:A4"/>
-    <mergeCell ref="F160:F161"/>
-    <mergeCell ref="F614:F619"/>
     <mergeCell ref="B16:B20"/>
     <mergeCell ref="B606:B607"/>
     <mergeCell ref="A5:A6"/>
-    <mergeCell ref="F131:F143"/>
     <mergeCell ref="B598:B605"/>
-    <mergeCell ref="F27:F28"/>
-    <mergeCell ref="F162:F164"/>
+    <mergeCell ref="B452:B457"/>
     <mergeCell ref="A58:A108"/>
-    <mergeCell ref="B452:B457"/>
     <mergeCell ref="B548:B568"/>
     <mergeCell ref="A184:A194"/>
-    <mergeCell ref="F509:F510"/>
     <mergeCell ref="A578:A583"/>
     <mergeCell ref="A270:A298"/>
     <mergeCell ref="A592:A597"/>
@@ -13672,12 +14723,10 @@
     <mergeCell ref="A299:A322"/>
     <mergeCell ref="B5:B6"/>
     <mergeCell ref="B576:B577"/>
-    <mergeCell ref="F478:F482"/>
     <mergeCell ref="A196:A200"/>
     <mergeCell ref="B468:B472"/>
     <mergeCell ref="B521:B522"/>
     <mergeCell ref="B415:B420"/>
-    <mergeCell ref="F576:F577"/>
     <mergeCell ref="B620:B627"/>
     <mergeCell ref="B584:B585"/>
   </mergeCells>
@@ -13777,7 +14826,7 @@
           <t>m³</t>
         </is>
       </c>
-      <c r="F3" s="8" t="n">
+      <c r="F3" s="11" t="n">
         <v>200.42</v>
       </c>
     </row>
@@ -13806,7 +14855,7 @@
           <t>m³</t>
         </is>
       </c>
-      <c r="F4" s="8" t="n">
+      <c r="F4" s="11" t="n">
         <v>168.3</v>
       </c>
     </row>
@@ -13834,7 +14883,7 @@
           <t>m³</t>
         </is>
       </c>
-      <c r="F5" s="8" t="n">
+      <c r="F5" s="11" t="n">
         <v>192.88</v>
       </c>
     </row>
@@ -13862,7 +14911,7 @@
           <t>m³</t>
         </is>
       </c>
-      <c r="F6" s="8" t="n">
+      <c r="F6" s="11" t="n">
         <v>32.12</v>
       </c>
     </row>
@@ -13893,7 +14942,7 @@
           <t>m³</t>
         </is>
       </c>
-      <c r="F7" s="8" t="n">
+      <c r="F7" s="11" t="n">
         <v>113.02</v>
       </c>
     </row>
@@ -13924,7 +14973,7 @@
           <t>m³</t>
         </is>
       </c>
-      <c r="F8" s="8" t="n">
+      <c r="F8" s="11" t="n">
         <v>16.33</v>
       </c>
     </row>
@@ -13955,7 +15004,7 @@
           <t>m³</t>
         </is>
       </c>
-      <c r="F9" s="8" t="n">
+      <c r="F9" s="11" t="n">
         <v>25.36</v>
       </c>
     </row>
@@ -13985,7 +15034,7 @@
           <t>m³</t>
         </is>
       </c>
-      <c r="F10" s="8" t="n">
+      <c r="F10" s="11" t="n">
         <v>6.83</v>
       </c>
     </row>
@@ -14015,7 +15064,7 @@
           <t>m³</t>
         </is>
       </c>
-      <c r="F11" s="8" t="n">
+      <c r="F11" s="11" t="n">
         <v>17.67</v>
       </c>
     </row>
@@ -14045,7 +15094,7 @@
           <t>m³</t>
         </is>
       </c>
-      <c r="F12" s="8" t="n">
+      <c r="F12" s="11" t="n">
         <v>26.5</v>
       </c>
     </row>
@@ -14075,7 +15124,7 @@
           <t>m³</t>
         </is>
       </c>
-      <c r="F13" s="8" t="n">
+      <c r="F13" s="11" t="n">
         <v>22.71</v>
       </c>
     </row>
@@ -14105,7 +15154,7 @@
           <t>m³</t>
         </is>
       </c>
-      <c r="F14" s="8" t="n">
+      <c r="F14" s="11" t="n">
         <v>35.05</v>
       </c>
     </row>
@@ -14135,7 +15184,7 @@
           <t>m³</t>
         </is>
       </c>
-      <c r="F15" s="8" t="n">
+      <c r="F15" s="11" t="n">
         <v>70.15000000000001</v>
       </c>
     </row>
@@ -14164,7 +15213,7 @@
           <t>m³</t>
         </is>
       </c>
-      <c r="F16" s="8" t="n">
+      <c r="F16" s="11" t="n">
         <v>75.48999999999999</v>
       </c>
     </row>
@@ -14194,7 +15243,7 @@
           <t>m³</t>
         </is>
       </c>
-      <c r="F17" s="8" t="n">
+      <c r="F17" s="11" t="n">
         <v>0.38</v>
       </c>
     </row>
@@ -14224,7 +15273,7 @@
           <t>m³</t>
         </is>
       </c>
-      <c r="F18" s="8" t="n">
+      <c r="F18" s="11" t="n">
         <v>11.14</v>
       </c>
     </row>
@@ -14253,7 +15302,7 @@
           <t>m³</t>
         </is>
       </c>
-      <c r="F19" s="8" t="n">
+      <c r="F19" s="11" t="n">
         <v>6.9</v>
       </c>
     </row>
@@ -14283,7 +15332,7 @@
           <t>m³</t>
         </is>
       </c>
-      <c r="F20" s="8" t="n">
+      <c r="F20" s="11" t="n">
         <v>1.42</v>
       </c>
     </row>
@@ -14312,7 +15361,7 @@
           <t>m³</t>
         </is>
       </c>
-      <c r="F21" s="8" t="n">
+      <c r="F21" s="11" t="n">
         <v>2.37</v>
       </c>
     </row>
@@ -14341,7 +15390,7 @@
           <t>㎡</t>
         </is>
       </c>
-      <c r="F22" s="8" t="n">
+      <c r="F22" s="11" t="n">
         <v>31.76</v>
       </c>
     </row>
@@ -14370,7 +15419,7 @@
           <t>㎡</t>
         </is>
       </c>
-      <c r="F23" s="8" t="n">
+      <c r="F23" s="11" t="n">
         <v>7.64</v>
       </c>
     </row>
@@ -14400,7 +15449,7 @@
           <t>m³</t>
         </is>
       </c>
-      <c r="F24" s="8" t="n">
+      <c r="F24" s="11" t="n">
         <v>2.78</v>
       </c>
     </row>
@@ -14428,7 +15477,7 @@
           <t>t</t>
         </is>
       </c>
-      <c r="F25" s="10" t="n">
+      <c r="F25" s="9" t="n">
         <v>0.709</v>
       </c>
     </row>
@@ -14456,7 +15505,7 @@
           <t>t</t>
         </is>
       </c>
-      <c r="F26" s="10" t="n">
+      <c r="F26" s="9" t="n">
         <v>0.492</v>
       </c>
     </row>
@@ -14484,7 +15533,7 @@
           <t>t</t>
         </is>
       </c>
-      <c r="F27" s="10" t="n">
+      <c r="F27" s="9" t="n">
         <v>0.175</v>
       </c>
     </row>
@@ -14512,7 +15561,7 @@
           <t>t</t>
         </is>
       </c>
-      <c r="F28" s="10" t="n">
+      <c r="F28" s="9" t="n">
         <v>0</v>
       </c>
     </row>
@@ -14540,7 +15589,7 @@
           <t>t</t>
         </is>
       </c>
-      <c r="F29" s="10" t="n">
+      <c r="F29" s="9" t="n">
         <v>0.345</v>
       </c>
     </row>
@@ -14568,7 +15617,7 @@
           <t>t</t>
         </is>
       </c>
-      <c r="F30" s="10" t="n">
+      <c r="F30" s="9" t="n">
         <v>2.989</v>
       </c>
     </row>
@@ -14596,7 +15645,7 @@
           <t>t</t>
         </is>
       </c>
-      <c r="F31" s="10" t="n">
+      <c r="F31" s="9" t="n">
         <v>0.968</v>
       </c>
     </row>
@@ -14624,7 +15673,7 @@
           <t>t</t>
         </is>
       </c>
-      <c r="F32" s="10" t="n">
+      <c r="F32" s="9" t="n">
         <v>0.307</v>
       </c>
     </row>
@@ -14652,7 +15701,7 @@
           <t>t</t>
         </is>
       </c>
-      <c r="F33" s="10" t="n">
+      <c r="F33" s="9" t="n">
         <v>1.428</v>
       </c>
     </row>
@@ -14680,7 +15729,7 @@
           <t>t</t>
         </is>
       </c>
-      <c r="F34" s="10" t="n">
+      <c r="F34" s="9" t="n">
         <v>0.717</v>
       </c>
     </row>
@@ -14708,7 +15757,7 @@
           <t>t</t>
         </is>
       </c>
-      <c r="F35" s="10" t="n">
+      <c r="F35" s="9" t="n">
         <v>0.134</v>
       </c>
     </row>
@@ -14736,7 +15785,7 @@
           <t>t</t>
         </is>
       </c>
-      <c r="F36" s="10" t="n">
+      <c r="F36" s="9" t="n">
         <v>2.347</v>
       </c>
     </row>
@@ -14764,7 +15813,7 @@
           <t>t</t>
         </is>
       </c>
-      <c r="F37" s="10" t="n">
+      <c r="F37" s="9" t="n">
         <v>2.172</v>
       </c>
     </row>
@@ -14792,7 +15841,7 @@
           <t>t</t>
         </is>
       </c>
-      <c r="F38" s="10" t="n">
+      <c r="F38" s="9" t="n">
         <v>2.778</v>
       </c>
     </row>
@@ -14820,7 +15869,7 @@
           <t>t</t>
         </is>
       </c>
-      <c r="F39" s="10" t="n">
+      <c r="F39" s="9" t="n">
         <v>0.319</v>
       </c>
     </row>
@@ -14848,7 +15897,7 @@
           <t>t</t>
         </is>
       </c>
-      <c r="F40" s="10" t="n">
+      <c r="F40" s="9" t="n">
         <v>1.029</v>
       </c>
     </row>
@@ -14876,7 +15925,7 @@
           <t>t</t>
         </is>
       </c>
-      <c r="F41" s="10" t="n">
+      <c r="F41" s="9" t="n">
         <v>2.37</v>
       </c>
     </row>
@@ -14904,7 +15953,7 @@
           <t>t</t>
         </is>
       </c>
-      <c r="F42" s="10" t="n">
+      <c r="F42" s="9" t="n">
         <v>2.808</v>
       </c>
     </row>
@@ -14932,7 +15981,7 @@
           <t>t</t>
         </is>
       </c>
-      <c r="F43" s="10" t="n">
+      <c r="F43" s="9" t="n">
         <v>6.289</v>
       </c>
     </row>
@@ -14960,7 +16009,7 @@
           <t>t</t>
         </is>
       </c>
-      <c r="F44" s="10" t="n">
+      <c r="F44" s="9" t="n">
         <v>0.089</v>
       </c>
     </row>
@@ -14988,7 +16037,7 @@
           <t>t</t>
         </is>
       </c>
-      <c r="F45" s="10" t="n">
+      <c r="F45" s="9" t="n">
         <v>0.209</v>
       </c>
     </row>
@@ -15016,7 +16065,7 @@
           <t>t</t>
         </is>
       </c>
-      <c r="F46" s="10" t="n">
+      <c r="F46" s="9" t="n">
         <v>0.417</v>
       </c>
     </row>
@@ -15044,7 +16093,7 @@
           <t>t</t>
         </is>
       </c>
-      <c r="F47" s="10" t="n">
+      <c r="F47" s="9" t="n">
         <v>0.266</v>
       </c>
     </row>
@@ -15073,7 +16122,7 @@
           <t>t</t>
         </is>
       </c>
-      <c r="F48" s="10" t="n">
+      <c r="F48" s="9" t="n">
         <v>0.08799999999999999</v>
       </c>
     </row>
@@ -15102,7 +16151,7 @@
           <t>t</t>
         </is>
       </c>
-      <c r="F49" s="10" t="n">
+      <c r="F49" s="9" t="n">
         <v>0.357</v>
       </c>
     </row>
@@ -15131,7 +16180,7 @@
           <t>t</t>
         </is>
       </c>
-      <c r="F50" s="10" t="n">
+      <c r="F50" s="9" t="n">
         <v>0</v>
       </c>
     </row>
@@ -15160,7 +16209,7 @@
           <t>t</t>
         </is>
       </c>
-      <c r="F51" s="10" t="n">
+      <c r="F51" s="9" t="n">
         <v>0.044</v>
       </c>
     </row>
@@ -15189,7 +16238,7 @@
           <t>t</t>
         </is>
       </c>
-      <c r="F52" s="10" t="n">
+      <c r="F52" s="9" t="n">
         <v>0.001</v>
       </c>
     </row>
@@ -15218,7 +16267,7 @@
           <t>t</t>
         </is>
       </c>
-      <c r="F53" s="10" t="n">
+      <c r="F53" s="9" t="n">
         <v>0.077</v>
       </c>
     </row>
@@ -15247,7 +16296,7 @@
           <t>t</t>
         </is>
       </c>
-      <c r="F54" s="10" t="n">
+      <c r="F54" s="9" t="n">
         <v>0.146</v>
       </c>
     </row>
@@ -15276,7 +16325,7 @@
           <t>t</t>
         </is>
       </c>
-      <c r="F55" s="10" t="n">
+      <c r="F55" s="9" t="n">
         <v>0.021</v>
       </c>
     </row>
@@ -15305,7 +16354,7 @@
           <t>t</t>
         </is>
       </c>
-      <c r="F56" s="10" t="n">
+      <c r="F56" s="9" t="n">
         <v>0.08400000000000001</v>
       </c>
     </row>
@@ -15334,7 +16383,7 @@
           <t>t</t>
         </is>
       </c>
-      <c r="F57" s="10" t="n">
+      <c r="F57" s="9" t="n">
         <v>0.006</v>
       </c>
     </row>
@@ -15363,7 +16412,7 @@
           <t>t</t>
         </is>
       </c>
-      <c r="F58" s="10" t="n">
+      <c r="F58" s="9" t="n">
         <v>0.263</v>
       </c>
     </row>
@@ -15395,7 +16444,7 @@
           <t>㎡</t>
         </is>
       </c>
-      <c r="F59" s="8" t="n">
+      <c r="F59" s="11" t="n">
         <v>13.83</v>
       </c>
     </row>
@@ -15431,7 +16480,7 @@
           <t>㎡</t>
         </is>
       </c>
-      <c r="F60" s="8" t="n">
+      <c r="F60" s="11" t="n">
         <v>164.64</v>
       </c>
     </row>
@@ -15461,7 +16510,7 @@
           <t>㎡</t>
         </is>
       </c>
-      <c r="F61" s="8" t="n">
+      <c r="F61" s="11" t="n">
         <v>219.3</v>
       </c>
     </row>
@@ -15490,7 +16539,7 @@
           <t>㎡</t>
         </is>
       </c>
-      <c r="F62" s="8" t="n">
+      <c r="F62" s="11" t="n">
         <v>200.13</v>
       </c>
     </row>
@@ -15549,7 +16598,7 @@
           <t>㎡</t>
         </is>
       </c>
-      <c r="F64" s="8" t="n">
+      <c r="F64" s="11" t="n">
         <v>4.58</v>
       </c>
     </row>
@@ -15580,7 +16629,7 @@
           <t>㎡</t>
         </is>
       </c>
-      <c r="F65" s="8" t="n">
+      <c r="F65" s="11" t="n">
         <v>200.13</v>
       </c>
     </row>
@@ -15610,7 +16659,7 @@
           <t>㎡</t>
         </is>
       </c>
-      <c r="F66" s="8" t="n">
+      <c r="F66" s="11" t="n">
         <v>796.17</v>
       </c>
     </row>
@@ -15640,7 +16689,7 @@
           <t>㎡</t>
         </is>
       </c>
-      <c r="F67" s="8" t="n">
+      <c r="F67" s="11" t="n">
         <v>4.58</v>
       </c>
     </row>
@@ -15670,7 +16719,7 @@
           <t>m</t>
         </is>
       </c>
-      <c r="F68" s="8" t="n">
+      <c r="F68" s="11" t="n">
         <v>264.13</v>
       </c>
     </row>
@@ -15700,7 +16749,7 @@
           <t>㎡</t>
         </is>
       </c>
-      <c r="F69" s="8" t="n">
+      <c r="F69" s="11" t="n">
         <v>770.35</v>
       </c>
     </row>
@@ -15730,7 +16779,7 @@
           <t>㎡</t>
         </is>
       </c>
-      <c r="F70" s="8" t="n">
+      <c r="F70" s="11" t="n">
         <v>962.71</v>
       </c>
     </row>
@@ -15763,7 +16812,7 @@
           <t>㎡</t>
         </is>
       </c>
-      <c r="F71" s="8" t="n">
+      <c r="F71" s="11" t="n">
         <v>16.88</v>
       </c>
     </row>
@@ -15793,7 +16842,7 @@
           <t>㎡</t>
         </is>
       </c>
-      <c r="F72" s="8" t="n">
+      <c r="F72" s="11" t="n">
         <v>908.76</v>
       </c>
     </row>
@@ -15823,7 +16872,7 @@
           <t>㎡</t>
         </is>
       </c>
-      <c r="F73" s="8" t="n">
+      <c r="F73" s="11" t="n">
         <v>770.35</v>
       </c>
     </row>
@@ -15853,7 +16902,7 @@
           <t>㎡</t>
         </is>
       </c>
-      <c r="F74" s="8" t="n">
+      <c r="F74" s="11" t="n">
         <v>962.71</v>
       </c>
     </row>
@@ -15884,7 +16933,7 @@
           <t>㎡</t>
         </is>
       </c>
-      <c r="F75" s="8" t="n">
+      <c r="F75" s="11" t="n">
         <v>908.76</v>
       </c>
     </row>
@@ -15921,541 +16970,541 @@
   </cols>
   <sheetData>
     <row r="1">
-      <c r="A1" s="11" t="inlineStr">
+      <c r="A1" s="12" t="inlineStr">
         <is>
           <t>编制说明</t>
         </is>
       </c>
     </row>
     <row r="2">
-      <c r="A2" s="12" t="inlineStr">
+      <c r="A2" s="13" t="inlineStr">
         <is>
           <t>总体</t>
         </is>
       </c>
-      <c r="B2" s="12" t="n"/>
-      <c r="C2" s="12" t="inlineStr">
+      <c r="B2" s="13" t="n"/>
+      <c r="C2" s="13" t="inlineStr">
         <is>
           <t>数据来源：①广联达《绘图输入构件工程量计算书》（基础层~第5层）；②广联达《钢筋明细表》；③清单模板（74 项）。</t>
         </is>
       </c>
     </row>
     <row r="3">
-      <c r="A3" s="12" t="inlineStr">
+      <c r="A3" s="13" t="inlineStr">
         <is>
           <t>总体</t>
         </is>
       </c>
-      <c r="B3" s="12" t="n"/>
-      <c r="C3" s="12" t="inlineStr">
+      <c r="B3" s="13" t="n"/>
+      <c r="C3" s="13" t="inlineStr">
         <is>
           <t>计算书粒度：每层每个构件编号一行，同编号下计算式相同的图元合并为 [计算式]×n；每个清单项末行为小计。</t>
         </is>
       </c>
     </row>
     <row r="4">
-      <c r="A4" s="12" t="inlineStr">
+      <c r="A4" s="13" t="inlineStr">
         <is>
           <t>总体</t>
         </is>
       </c>
-      <c r="B4" s="12" t="n"/>
-      <c r="C4" s="12" t="inlineStr">
+      <c r="B4" s="13" t="n"/>
+      <c r="C4" s="13" t="inlineStr">
         <is>
           <t>计算式已去掉广联达的尖括号注释，仅保留数值式；各图元结果取广联达原值（4 位小数），清单工程量 m³/㎡/m 取 2 位小数，钢筋 t 取 3 位小数。</t>
         </is>
       </c>
     </row>
     <row r="5">
-      <c r="A5" s="12" t="inlineStr">
+      <c r="A5" s="13" t="inlineStr">
         <is>
           <t>总体</t>
         </is>
       </c>
-      <c r="B5" s="12" t="n"/>
-      <c r="C5" s="12" t="inlineStr">
+      <c r="B5" s="13" t="n"/>
+      <c r="C5" s="13" t="inlineStr">
         <is>
           <t>钢筋明细表导出的“级别”列为空，钢筋级别按清单模板“构件类型+直径→级别”对应关系归类；直径 12/14 过梁钢筋按模板标注 HPB300 保留。</t>
         </is>
       </c>
     </row>
     <row r="6">
-      <c r="A6" s="12" t="inlineStr">
+      <c r="A6" s="13" t="inlineStr">
         <is>
           <t>总体</t>
         </is>
       </c>
-      <c r="B6" s="12" t="n"/>
-      <c r="C6" s="12" t="inlineStr">
+      <c r="B6" s="13" t="n"/>
+      <c r="C6" s="13" t="inlineStr">
         <is>
           <t>钢筋校核：钢筋明细表总重 30182.028kg，已全部分配到各钢筋清单项（不含估算的屋面钢筋网片），分配合计 30182.028kg。</t>
         </is>
       </c>
     </row>
     <row r="7">
-      <c r="A7" s="12" t="inlineStr">
+      <c r="A7" s="13" t="inlineStr">
         <is>
           <t>总体</t>
         </is>
       </c>
-      <c r="B7" s="12" t="n"/>
-      <c r="C7" s="12" t="inlineStr">
+      <c r="B7" s="13" t="n"/>
+      <c r="C7" s="13" t="inlineStr">
         <is>
           <t>标注“需补充”的项目在计算书/钢筋表中无依据，需按图纸另行计算。</t>
         </is>
       </c>
     </row>
     <row r="8">
-      <c r="A8" s="12" t="n"/>
-      <c r="B8" s="12" t="n"/>
-      <c r="C8" s="12" t="n"/>
+      <c r="A8" s="13" t="n"/>
+      <c r="B8" s="13" t="n"/>
+      <c r="C8" s="13" t="n"/>
     </row>
     <row r="9">
-      <c r="A9" s="13" t="inlineStr">
+      <c r="A9" s="14" t="inlineStr">
         <is>
           <t>项目编码</t>
         </is>
       </c>
-      <c r="B9" s="13" t="inlineStr">
+      <c r="B9" s="14" t="inlineStr">
         <is>
           <t>项目名称</t>
         </is>
       </c>
-      <c r="C9" s="13" t="inlineStr">
+      <c r="C9" s="14" t="inlineStr">
         <is>
           <t>说明</t>
         </is>
       </c>
     </row>
     <row r="10">
-      <c r="A10" s="12" t="inlineStr">
+      <c r="A10" s="13" t="inlineStr">
         <is>
           <t>010102007001</t>
         </is>
       </c>
-      <c r="B10" s="12" t="inlineStr">
+      <c r="B10" s="13" t="inlineStr">
         <is>
           <t>回填方</t>
         </is>
       </c>
-      <c r="C10" s="12" t="inlineStr">
+      <c r="C10" s="13" t="inlineStr">
         <is>
           <t>按广联达大开挖土方的“素土回填体积”（基坑回填）汇总；房心回填未含。</t>
         </is>
       </c>
     </row>
     <row r="11">
-      <c r="A11" s="12" t="inlineStr">
+      <c r="A11" s="13" t="inlineStr">
         <is>
           <t>010103001001</t>
         </is>
       </c>
-      <c r="B11" s="12" t="inlineStr">
+      <c r="B11" s="13" t="inlineStr">
         <is>
           <t>平整场地</t>
         </is>
       </c>
-      <c r="C11" s="12" t="inlineStr">
+      <c r="C11" s="13" t="inlineStr">
         <is>
           <t>计算书中无平整场地构件，按首层建筑面积计取；清单模板单位为 m³，规范应为 m²，请核对。</t>
         </is>
       </c>
     </row>
     <row r="12">
-      <c r="A12" s="12" t="inlineStr">
+      <c r="A12" s="13" t="inlineStr">
         <is>
           <t>010103002001</t>
         </is>
       </c>
-      <c r="B12" s="12" t="inlineStr">
+      <c r="B12" s="13" t="inlineStr">
         <is>
           <t>余方弃置</t>
         </is>
       </c>
-      <c r="C12" s="12" t="inlineStr">
+      <c r="C12" s="13" t="inlineStr">
         <is>
           <t>余方弃置 = 挖方总量 − 基坑回填总量（推导值）。</t>
         </is>
       </c>
     </row>
     <row r="13">
-      <c r="A13" s="12" t="inlineStr">
+      <c r="A13" s="13" t="inlineStr">
         <is>
           <t>010501002001</t>
         </is>
       </c>
-      <c r="B13" s="12" t="inlineStr">
+      <c r="B13" s="13" t="inlineStr">
         <is>
           <t>楼地面垫层</t>
         </is>
       </c>
-      <c r="C13" s="12" t="inlineStr">
+      <c r="C13" s="13" t="inlineStr">
         <is>
           <t>计算书中无楼地面垫层构件，按首层各房间地面积×0.10m 推导。</t>
         </is>
       </c>
     </row>
     <row r="14">
-      <c r="A14" s="12" t="inlineStr">
+      <c r="A14" s="13" t="inlineStr">
         <is>
           <t>010501002002</t>
         </is>
       </c>
-      <c r="B14" s="12" t="inlineStr">
+      <c r="B14" s="13" t="inlineStr">
         <is>
           <t>楼地面垫层</t>
         </is>
       </c>
-      <c r="C14" s="12" t="inlineStr">
+      <c r="C14" s="13" t="inlineStr">
         <is>
           <t>计算书中无楼地面垫层构件，按首层各房间地面积×0.15m 推导。</t>
         </is>
       </c>
     </row>
     <row r="15">
-      <c r="A15" s="12" t="inlineStr">
+      <c r="A15" s="13" t="inlineStr">
         <is>
           <t>010502006001</t>
         </is>
       </c>
-      <c r="B15" s="12" t="inlineStr">
+      <c r="B15" s="13" t="inlineStr">
         <is>
           <t>钢筋混凝土柱</t>
         </is>
       </c>
-      <c r="C15" s="12" t="inlineStr">
+      <c r="C15" s="13" t="inlineStr">
         <is>
           <t>含各层框架柱 1KZ1~1KZ4 及梯柱 TZ；基础层柱为基础顶至±0.000 段。</t>
         </is>
       </c>
     </row>
     <row r="16">
-      <c r="A16" s="12" t="inlineStr">
+      <c r="A16" s="13" t="inlineStr">
         <is>
           <t>010502011001</t>
         </is>
       </c>
-      <c r="B16" s="12" t="inlineStr">
+      <c r="B16" s="13" t="inlineStr">
         <is>
           <t>钢筋混凝土梁</t>
         </is>
       </c>
-      <c r="C16" s="12" t="inlineStr">
+      <c r="C16" s="13" t="inlineStr">
         <is>
           <t>含基础梁 DKL/DL、各层框架梁 KL/WKL、次梁 L/WL；雨棚梁 YPL 计入“其他板(雨棚板)”。</t>
         </is>
       </c>
     </row>
     <row r="17">
-      <c r="A17" s="12" t="inlineStr">
+      <c r="A17" s="13" t="inlineStr">
         <is>
           <t>010502019001</t>
         </is>
       </c>
-      <c r="B17" s="12" t="inlineStr">
+      <c r="B17" s="13" t="inlineStr">
         <is>
           <t>其他板</t>
         </is>
       </c>
-      <c r="C17" s="12" t="inlineStr">
+      <c r="C17" s="13" t="inlineStr">
         <is>
           <t>广联达模型中未绘制雨棚板本体，仅有雨棚梁 YPL 与雨棚栏板 YP，此处为两者体积之和；雨棚板本体需补充。</t>
         </is>
       </c>
     </row>
     <row r="18">
-      <c r="A18" s="12" t="inlineStr">
+      <c r="A18" s="13" t="inlineStr">
         <is>
           <t>010502020001</t>
         </is>
       </c>
-      <c r="B18" s="12" t="inlineStr">
+      <c r="B18" s="13" t="inlineStr">
         <is>
           <t>楼梯</t>
         </is>
       </c>
-      <c r="C18" s="12" t="inlineStr">
+      <c r="C18" s="13" t="inlineStr">
         <is>
           <t>楼梯按广联达“梯段+梯梁+平台板”体积汇总（清单模板单位为 m³）。</t>
         </is>
       </c>
     </row>
     <row r="19">
-      <c r="A19" s="12" t="inlineStr">
+      <c r="A19" s="13" t="inlineStr">
         <is>
           <t>010506001001</t>
         </is>
       </c>
-      <c r="B19" s="12" t="inlineStr">
+      <c r="B19" s="13" t="inlineStr">
         <is>
           <t>现浇混凝土基础及联系梁钢筋</t>
         </is>
       </c>
-      <c r="C19" s="12" t="inlineStr">
+      <c r="C19" s="13" t="inlineStr">
         <is>
           <t>基础钢筋按独立基础 J-1/J-2/J-3 汇总（均为Φ12）；基础梁 DKL/DL 钢筋计入“现浇混凝土梁钢筋”对应直径。</t>
         </is>
       </c>
     </row>
     <row r="20">
-      <c r="A20" s="12" t="inlineStr">
+      <c r="A20" s="13" t="inlineStr">
         <is>
           <t>010506002003</t>
         </is>
       </c>
-      <c r="B20" s="12" t="inlineStr">
+      <c r="B20" s="13" t="inlineStr">
         <is>
           <t>现浇混凝土柱钢筋</t>
         </is>
       </c>
-      <c r="C20" s="12" t="inlineStr">
+      <c r="C20" s="13" t="inlineStr">
         <is>
           <t>钢筋明细表中柱构件无Φ16钢筋，工程量为 0。</t>
         </is>
       </c>
     </row>
     <row r="21">
-      <c r="A21" s="12" t="inlineStr">
+      <c r="A21" s="13" t="inlineStr">
         <is>
           <t>010506005001</t>
         </is>
       </c>
-      <c r="B21" s="12" t="inlineStr">
+      <c r="B21" s="13" t="inlineStr">
         <is>
           <t>现浇混凝土梁钢筋</t>
         </is>
       </c>
-      <c r="C21" s="12" t="inlineStr">
+      <c r="C21" s="13" t="inlineStr">
         <is>
           <t>含雨棚梁 YPL 钢筋（清单模板“雨蓬”项仅列Φ8）。</t>
         </is>
       </c>
     </row>
     <row r="22">
-      <c r="A22" s="12" t="inlineStr">
+      <c r="A22" s="13" t="inlineStr">
         <is>
           <t>010506005004</t>
         </is>
       </c>
-      <c r="B22" s="12" t="inlineStr">
+      <c r="B22" s="13" t="inlineStr">
         <is>
           <t>现浇混凝土梁钢筋</t>
         </is>
       </c>
-      <c r="C22" s="12" t="inlineStr">
+      <c r="C22" s="13" t="inlineStr">
         <is>
           <t>含雨棚梁 YPL 钢筋（清单模板“雨蓬”项仅列Φ8）。</t>
         </is>
       </c>
     </row>
     <row r="23">
-      <c r="A23" s="12" t="inlineStr">
+      <c r="A23" s="13" t="inlineStr">
         <is>
           <t>010506020001</t>
         </is>
       </c>
-      <c r="B23" s="12" t="inlineStr">
+      <c r="B23" s="13" t="inlineStr">
         <is>
           <t>钢筋网片</t>
         </is>
       </c>
-      <c r="C23" s="12" t="inlineStr">
+      <c r="C23" s="13" t="inlineStr">
         <is>
           <t>钢筋明细表中无屋面网片；按刚性层面积×Φ4@150双向估算：Φ4 单重 0.099kg/m，每 m² 用量 2/0.15×0.099≈1.316kg/m²。</t>
         </is>
       </c>
     </row>
     <row r="24">
-      <c r="A24" s="12" t="inlineStr">
+      <c r="A24" s="13" t="inlineStr">
         <is>
           <t>010902001001</t>
         </is>
       </c>
-      <c r="B24" s="12" t="inlineStr">
+      <c r="B24" s="13" t="inlineStr">
         <is>
           <t>屋面卷材防水</t>
         </is>
       </c>
-      <c r="C24" s="12" t="inlineStr">
+      <c r="C24" s="13" t="inlineStr">
         <is>
           <t>按广联达屋面“防水面积”（含 250 高卷边）汇总。</t>
         </is>
       </c>
     </row>
     <row r="25">
-      <c r="A25" s="12" t="inlineStr">
+      <c r="A25" s="13" t="inlineStr">
         <is>
           <t>010902004001</t>
         </is>
       </c>
-      <c r="B25" s="12" t="inlineStr">
+      <c r="B25" s="13" t="inlineStr">
         <is>
           <t>屋面刚性层</t>
         </is>
       </c>
-      <c r="C25" s="12" t="inlineStr">
+      <c r="C25" s="13" t="inlineStr">
         <is>
           <t>刚性层 = 屋面防水面积 − 卷边面积（水平投影）。</t>
         </is>
       </c>
     </row>
     <row r="26">
-      <c r="A26" s="12" t="inlineStr">
+      <c r="A26" s="13" t="inlineStr">
         <is>
           <t>010902005001</t>
         </is>
       </c>
-      <c r="B26" s="12" t="inlineStr">
+      <c r="B26" s="13" t="inlineStr">
         <is>
           <t>屋面排水管</t>
         </is>
       </c>
-      <c r="C26" s="12" t="inlineStr">
+      <c r="C26" s="13" t="inlineStr">
         <is>
           <t>计算书与钢筋表中均无雨水管信息，无法计取，需按图纸补充（根数×长度）。</t>
         </is>
       </c>
     </row>
     <row r="27">
-      <c r="A27" s="12" t="inlineStr">
+      <c r="A27" s="13" t="inlineStr">
         <is>
           <t>010904002001</t>
         </is>
       </c>
-      <c r="B27" s="12" t="inlineStr">
+      <c r="B27" s="13" t="inlineStr">
         <is>
           <t>楼地面涂膜防水</t>
         </is>
       </c>
-      <c r="C27" s="12" t="inlineStr">
+      <c r="C27" s="13" t="inlineStr">
         <is>
           <t>按首层卫生间地面积计取，未含上翻高度部分。</t>
         </is>
       </c>
     </row>
     <row r="28">
-      <c r="A28" s="12" t="inlineStr">
+      <c r="A28" s="13" t="inlineStr">
         <is>
           <t>011001001001</t>
         </is>
       </c>
-      <c r="B28" s="12" t="inlineStr">
+      <c r="B28" s="13" t="inlineStr">
         <is>
           <t>保温隔热屋面</t>
         </is>
       </c>
-      <c r="C28" s="12" t="inlineStr">
+      <c r="C28" s="13" t="inlineStr">
         <is>
           <t>保温层 = 屋面防水面积 − 卷边面积（水平投影）。</t>
         </is>
       </c>
     </row>
     <row r="29">
-      <c r="A29" s="12" t="inlineStr">
+      <c r="A29" s="13" t="inlineStr">
         <is>
           <t>011101001001</t>
         </is>
       </c>
-      <c r="B29" s="12" t="inlineStr">
+      <c r="B29" s="13" t="inlineStr">
         <is>
           <t>水泥砂浆楼地面</t>
         </is>
       </c>
-      <c r="C29" s="12" t="inlineStr">
+      <c r="C29" s="13" t="inlineStr">
         <is>
           <t>按各层“其他”房间地面积汇总（首层地面一并计入）。</t>
         </is>
       </c>
     </row>
     <row r="30">
-      <c r="A30" s="12" t="inlineStr">
+      <c r="A30" s="13" t="inlineStr">
         <is>
           <t>011105001001</t>
         </is>
       </c>
-      <c r="B30" s="12" t="inlineStr">
+      <c r="B30" s="13" t="inlineStr">
         <is>
           <t>水泥砂浆踢脚线</t>
         </is>
       </c>
-      <c r="C30" s="12" t="inlineStr">
+      <c r="C30" s="13" t="inlineStr">
         <is>
           <t>仅计“其他”房间踢脚；卫生间 2.1m 以下为瓷砖墙裙，不计踢脚。</t>
         </is>
       </c>
     </row>
     <row r="31">
-      <c r="A31" s="12" t="inlineStr">
+      <c r="A31" s="13" t="inlineStr">
         <is>
           <t>011201001002</t>
         </is>
       </c>
-      <c r="B31" s="12" t="inlineStr">
+      <c r="B31" s="13" t="inlineStr">
         <is>
           <t>墙、柱面一般抹灰</t>
         </is>
       </c>
-      <c r="C31" s="12" t="inlineStr">
+      <c r="C31" s="13" t="inlineStr">
         <is>
           <t>含各层房间内墙面（卫生间为墙裙以上部分）及第5层女儿墙内侧/楼梯间墙面。</t>
         </is>
       </c>
     </row>
     <row r="32">
-      <c r="A32" s="12" t="inlineStr">
+      <c r="A32" s="13" t="inlineStr">
         <is>
           <t>011404001001</t>
         </is>
       </c>
-      <c r="B32" s="12" t="inlineStr">
+      <c r="B32" s="13" t="inlineStr">
         <is>
           <t>墙面喷刷涂料</t>
         </is>
       </c>
-      <c r="C32" s="12" t="inlineStr">
+      <c r="C32" s="13" t="inlineStr">
         <is>
           <t>外墙涂料面积 = 外墙一般抹灰面积。</t>
         </is>
       </c>
     </row>
     <row r="33">
-      <c r="A33" s="12" t="inlineStr">
+      <c r="A33" s="13" t="inlineStr">
         <is>
           <t>011404001002</t>
         </is>
       </c>
-      <c r="B33" s="12" t="inlineStr">
+      <c r="B33" s="13" t="inlineStr">
         <is>
           <t>墙面喷刷涂料</t>
         </is>
       </c>
-      <c r="C33" s="12" t="inlineStr">
+      <c r="C33" s="13" t="inlineStr">
         <is>
           <t>内墙涂料面积 = 内墙一般抹灰面积。</t>
         </is>
       </c>
     </row>
     <row r="34">
-      <c r="A34" s="12" t="inlineStr">
+      <c r="A34" s="13" t="inlineStr">
         <is>
           <t>011404002001</t>
         </is>
       </c>
-      <c r="B34" s="12" t="inlineStr">
+      <c r="B34" s="13" t="inlineStr">
         <is>
           <t>天棚喷刷涂料</t>
         </is>
       </c>
-      <c r="C34" s="12" t="inlineStr">
+      <c r="C34" s="13" t="inlineStr">
         <is>
           <t>天棚涂料面积 = 天棚抹灰面积。</t>
         </is>
       </c>
     </row>
     <row r="35">
-      <c r="A35" s="12" t="n"/>
-      <c r="B35" s="12" t="n"/>
-      <c r="C35" s="12" t="n"/>
+      <c r="A35" s="13" t="n"/>
+      <c r="B35" s="13" t="n"/>
+      <c r="C35" s="13" t="n"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/工程量清单/工程量清单及计算书.xlsx
+++ b/工程量清单/工程量清单及计算书.xlsx
@@ -21,9 +21,8 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <numFmts count="2">
-    <numFmt numFmtId="164" formatCode="0.00##"/>
-    <numFmt numFmtId="165" formatCode="0.000"/>
+  <numFmts count="1">
+    <numFmt numFmtId="164" formatCode="0.000"/>
   </numFmts>
   <fonts count="4">
     <font>
@@ -87,7 +86,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="15">
+  <cellXfs count="16">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
@@ -101,8 +100,8 @@
     <xf numFmtId="0" fontId="3" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="164" fontId="3" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    <xf numFmtId="2" fontId="2" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
@@ -110,16 +109,19 @@
     <xf numFmtId="0" fontId="2" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="164" fontId="2" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="2" fontId="3" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="164" fontId="2" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="164" fontId="3" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="2" fontId="3" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="165" fontId="3" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="165" fontId="2" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="2" fontId="3" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="164" fontId="3" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
@@ -569,7 +571,7 @@
         </is>
       </c>
       <c r="F3" s="5" t="n">
-        <v>200.4156</v>
+        <v>200.42</v>
       </c>
     </row>
     <row r="4" ht="18" customHeight="1">
@@ -586,9 +588,7 @@
           <t>200.4156 ≈ 200.42</t>
         </is>
       </c>
-      <c r="F4" s="8" t="n">
-        <v>200.42</v>
-      </c>
+      <c r="F4" s="8" t="n"/>
     </row>
     <row r="5" ht="46" customHeight="1">
       <c r="A5" s="3" t="n">
@@ -615,7 +615,7 @@
         </is>
       </c>
       <c r="F5" s="5" t="n">
-        <v>168.2978</v>
+        <v>168.3</v>
       </c>
     </row>
     <row r="6" ht="18" customHeight="1">
@@ -632,9 +632,7 @@
           <t>168.2978 ≈ 168.30</t>
         </is>
       </c>
-      <c r="F6" s="8" t="n">
-        <v>168.3</v>
-      </c>
+      <c r="F6" s="8" t="n"/>
     </row>
     <row r="7" ht="18" customHeight="1">
       <c r="A7" s="3" t="n">
@@ -661,7 +659,7 @@
         </is>
       </c>
       <c r="F7" s="5" t="n">
-        <v>192.882</v>
+        <v>192.88</v>
       </c>
     </row>
     <row r="8" ht="18" customHeight="1">
@@ -678,9 +676,7 @@
           <t>192.882 ≈ 192.88</t>
         </is>
       </c>
-      <c r="F8" s="8" t="n">
-        <v>192.88</v>
-      </c>
+      <c r="F8" s="8" t="n"/>
     </row>
     <row r="9" ht="18" customHeight="1">
       <c r="A9" s="3" t="n">
@@ -707,7 +703,7 @@
         </is>
       </c>
       <c r="F9" s="5" t="n">
-        <v>32.1178</v>
+        <v>32.12</v>
       </c>
     </row>
     <row r="10" ht="18" customHeight="1">
@@ -724,9 +720,7 @@
           <t>32.1178 ≈ 32.12</t>
         </is>
       </c>
-      <c r="F10" s="8" t="n">
-        <v>32.12</v>
-      </c>
+      <c r="F10" s="8" t="n"/>
     </row>
     <row r="11" ht="32" customHeight="1">
       <c r="A11" s="3" t="n">
@@ -753,7 +747,7 @@
         </is>
       </c>
       <c r="F11" s="5" t="n">
-        <v>27.0403</v>
+        <v>113.02</v>
       </c>
     </row>
     <row r="12" ht="32" customHeight="1">
@@ -774,9 +768,7 @@
           <t>(13.625×3.6×0.24)-0.8784-0.9936-1.5972-0.096-0.023 + (15.38×3.6×0.24)-3.6288-1.1923-1.1712-0.4992 + (13.5×3.6×0.24)-0.8784-1.3167-1.5313-0.096-0.023 + (15.5×3.6×0.24)-5.4144-1.392-0.648-0.1382-0.0027 = 28.5958</t>
         </is>
       </c>
-      <c r="F12" s="5" t="n">
-        <v>28.5958</v>
-      </c>
+      <c r="F12" s="8" t="n"/>
     </row>
     <row r="13" ht="32" customHeight="1">
       <c r="A13" s="3" t="n"/>
@@ -796,9 +788,7 @@
           <t>(15.5×3.6×0.24)-5.4144-1.392-0.648-0.1382-0.0027 + (13.5×3.6×0.24)-0.8784-1.3167-1.5313-0.096-0.023 + (15.38×3.6×0.24)-3.6288-1.1923-1.1712-0.4992 + (13.625×3.6×0.24)-0.8784-0.9936-1.5972-0.096-0.023 = 28.5958</t>
         </is>
       </c>
-      <c r="F13" s="5" t="n">
-        <v>28.5958</v>
-      </c>
+      <c r="F13" s="8" t="n"/>
     </row>
     <row r="14" ht="32" customHeight="1">
       <c r="A14" s="3" t="n"/>
@@ -818,9 +808,7 @@
           <t>(15.5×3.6×0.24)-5.4144-1.392-0.648-0.1382-0.003 + (13.5×3.6×0.24)-0.8784-1.3167-1.5313-0.096-0.023 + (15.38×3.6×0.24)-3.2616-1.1923-1.344-0.4992 + (13.625×3.6×0.24)-0.8784-0.9936-1.5972-0.096-0.023 = 28.7899</t>
         </is>
       </c>
-      <c r="F14" s="5" t="n">
-        <v>28.7899</v>
-      </c>
+      <c r="F14" s="8" t="n"/>
     </row>
     <row r="15" ht="18" customHeight="1">
       <c r="A15" s="3" t="n"/>
@@ -836,9 +824,7 @@
           <t>27.0403 + 28.5958 + 28.5958 + 28.7899 = 113.0218 ≈ 113.02</t>
         </is>
       </c>
-      <c r="F15" s="8" t="n">
-        <v>113.02</v>
-      </c>
+      <c r="F15" s="8" t="n"/>
     </row>
     <row r="16" ht="18" customHeight="1">
       <c r="A16" s="3" t="n">
@@ -865,7 +851,7 @@
         </is>
       </c>
       <c r="F16" s="5" t="n">
-        <v>5.6237</v>
+        <v>16.33</v>
       </c>
     </row>
     <row r="17" ht="18" customHeight="1">
@@ -886,9 +872,7 @@
           <t>(5.85×3.6×0.24)-0.8424-0.6435 = 3.5685</t>
         </is>
       </c>
-      <c r="F17" s="5" t="n">
-        <v>3.5685</v>
-      </c>
+      <c r="F17" s="8" t="n"/>
     </row>
     <row r="18" ht="18" customHeight="1">
       <c r="A18" s="3" t="n"/>
@@ -908,9 +892,7 @@
           <t>(5.85×3.6×0.24)-0.8424-0.6435 = 3.5685</t>
         </is>
       </c>
-      <c r="F18" s="5" t="n">
-        <v>3.5685</v>
-      </c>
+      <c r="F18" s="8" t="n"/>
     </row>
     <row r="19" ht="18" customHeight="1">
       <c r="A19" s="3" t="n"/>
@@ -930,9 +912,7 @@
           <t>(5.85×3.6×0.24)-0.8424-0.6435 = 3.5685</t>
         </is>
       </c>
-      <c r="F19" s="5" t="n">
-        <v>3.5685</v>
-      </c>
+      <c r="F19" s="8" t="n"/>
     </row>
     <row r="20" ht="18" customHeight="1">
       <c r="A20" s="3" t="n"/>
@@ -948,9 +928,7 @@
           <t>5.6237 + 3.5685 + 3.5685 + 3.5685 = 16.3292 ≈ 16.33</t>
         </is>
       </c>
-      <c r="F20" s="8" t="n">
-        <v>16.33</v>
-      </c>
+      <c r="F20" s="8" t="n"/>
     </row>
     <row r="21" ht="46" customHeight="1">
       <c r="A21" s="3" t="n">
@@ -977,7 +955,7 @@
         </is>
       </c>
       <c r="F21" s="5" t="n">
-        <v>25.3624</v>
+        <v>25.36</v>
       </c>
     </row>
     <row r="22" ht="18" customHeight="1">
@@ -994,9 +972,7 @@
           <t>25.3624 ≈ 25.36</t>
         </is>
       </c>
-      <c r="F22" s="8" t="n">
-        <v>25.36</v>
-      </c>
+      <c r="F22" s="8" t="n"/>
     </row>
     <row r="23" ht="18" customHeight="1">
       <c r="A23" s="3" t="n">
@@ -1023,7 +999,7 @@
         </is>
       </c>
       <c r="F23" s="5" t="n">
-        <v>6.832</v>
+        <v>6.83</v>
       </c>
     </row>
     <row r="24" ht="18" customHeight="1">
@@ -1040,9 +1016,7 @@
           <t>6.832 ≈ 6.83</t>
         </is>
       </c>
-      <c r="F24" s="8" t="n">
-        <v>6.83</v>
-      </c>
+      <c r="F24" s="8" t="n"/>
     </row>
     <row r="25" ht="18" customHeight="1">
       <c r="A25" s="3" t="n">
@@ -1069,7 +1043,7 @@
         </is>
       </c>
       <c r="F25" s="5" t="n">
-        <v>17.6666</v>
+        <v>17.67</v>
       </c>
     </row>
     <row r="26" ht="18" customHeight="1">
@@ -1086,9 +1060,7 @@
           <t>17.6666 ≈ 17.67</t>
         </is>
       </c>
-      <c r="F26" s="8" t="n">
-        <v>17.67</v>
-      </c>
+      <c r="F26" s="8" t="n"/>
     </row>
     <row r="27" ht="18" customHeight="1">
       <c r="A27" s="3" t="n">
@@ -1115,7 +1087,7 @@
         </is>
       </c>
       <c r="F27" s="5" t="n">
-        <v>26.4999</v>
+        <v>26.5</v>
       </c>
     </row>
     <row r="28" ht="18" customHeight="1">
@@ -1132,9 +1104,7 @@
           <t>26.4999 ≈ 26.50</t>
         </is>
       </c>
-      <c r="F28" s="8" t="n">
-        <v>26.5</v>
-      </c>
+      <c r="F28" s="8" t="n"/>
     </row>
     <row r="29" ht="18" customHeight="1">
       <c r="A29" s="3" t="n">
@@ -1161,7 +1131,7 @@
         </is>
       </c>
       <c r="F29" s="5" t="n">
-        <v>8.614000000000001</v>
+        <v>22.71</v>
       </c>
     </row>
     <row r="30" ht="18" customHeight="1">
@@ -1182,9 +1152,7 @@
           <t>[1.5412]×8 = 12.3296</t>
         </is>
       </c>
-      <c r="F30" s="5" t="n">
-        <v>12.3296</v>
-      </c>
+      <c r="F30" s="8" t="n"/>
     </row>
     <row r="31" ht="18" customHeight="1">
       <c r="A31" s="3" t="n"/>
@@ -1204,9 +1172,7 @@
           <t>[0.8837]×2 = 1.7674</t>
         </is>
       </c>
-      <c r="F31" s="5" t="n">
-        <v>1.7674</v>
-      </c>
+      <c r="F31" s="8" t="n"/>
     </row>
     <row r="32" ht="18" customHeight="1">
       <c r="A32" s="3" t="n"/>
@@ -1222,9 +1188,7 @@
           <t>8.614 + 12.3296 + 1.7674 = 22.711 ≈ 22.71</t>
         </is>
       </c>
-      <c r="F32" s="8" t="n">
-        <v>22.71</v>
-      </c>
+      <c r="F32" s="8" t="n"/>
     </row>
     <row r="33" ht="18" customHeight="1">
       <c r="A33" s="3" t="n">
@@ -1251,7 +1215,7 @@
         </is>
       </c>
       <c r="F33" s="5" t="n">
-        <v>0.456</v>
+        <v>35.05</v>
       </c>
     </row>
     <row r="34" ht="18" customHeight="1">
@@ -1272,9 +1236,7 @@
           <t>[(0.35×0.4×1.55)-0.07]×9 = 1.323</t>
         </is>
       </c>
-      <c r="F34" s="5" t="n">
-        <v>1.323</v>
-      </c>
+      <c r="F34" s="8" t="n"/>
     </row>
     <row r="35" ht="18" customHeight="1">
       <c r="A35" s="3" t="n"/>
@@ -1294,9 +1256,7 @@
           <t>(0.4×0.4×1.55)-0.096 = 0.152</t>
         </is>
       </c>
-      <c r="F35" s="5" t="n">
-        <v>0.152</v>
-      </c>
+      <c r="F35" s="8" t="n"/>
     </row>
     <row r="36" ht="18" customHeight="1">
       <c r="A36" s="3" t="n"/>
@@ -1316,9 +1276,7 @@
           <t>(0.35×0.4×1.55)-0.07 = 0.147</t>
         </is>
       </c>
-      <c r="F36" s="5" t="n">
-        <v>0.147</v>
-      </c>
+      <c r="F36" s="8" t="n"/>
     </row>
     <row r="37" ht="18" customHeight="1">
       <c r="A37" s="3" t="n"/>
@@ -1338,9 +1296,7 @@
           <t>[(0.4×0.4×3.6)]×3 = 1.728</t>
         </is>
       </c>
-      <c r="F37" s="5" t="n">
-        <v>1.728</v>
-      </c>
+      <c r="F37" s="8" t="n"/>
     </row>
     <row r="38" ht="18" customHeight="1">
       <c r="A38" s="3" t="n"/>
@@ -1360,9 +1316,7 @@
           <t>[(0.35×0.4×3.6)]×9 = 4.536</t>
         </is>
       </c>
-      <c r="F38" s="5" t="n">
-        <v>4.536</v>
-      </c>
+      <c r="F38" s="8" t="n"/>
     </row>
     <row r="39" ht="18" customHeight="1">
       <c r="A39" s="3" t="n"/>
@@ -1382,9 +1336,7 @@
           <t>(0.4×0.4×3.6) = 0.576</t>
         </is>
       </c>
-      <c r="F39" s="5" t="n">
-        <v>0.576</v>
-      </c>
+      <c r="F39" s="8" t="n"/>
     </row>
     <row r="40" ht="18" customHeight="1">
       <c r="A40" s="3" t="n"/>
@@ -1404,9 +1356,7 @@
           <t>(0.35×0.4×3.6) = 0.504</t>
         </is>
       </c>
-      <c r="F40" s="5" t="n">
-        <v>0.504</v>
-      </c>
+      <c r="F40" s="8" t="n"/>
     </row>
     <row r="41" ht="18" customHeight="1">
       <c r="A41" s="3" t="n"/>
@@ -1426,9 +1376,7 @@
           <t>[(0.25×0.25×3.6)]×4 = 0.9</t>
         </is>
       </c>
-      <c r="F41" s="5" t="n">
-        <v>0.9</v>
-      </c>
+      <c r="F41" s="8" t="n"/>
     </row>
     <row r="42" ht="18" customHeight="1">
       <c r="A42" s="3" t="n"/>
@@ -1448,9 +1396,7 @@
           <t>[(0.4×0.4×3.6)]×3 = 1.728</t>
         </is>
       </c>
-      <c r="F42" s="5" t="n">
-        <v>1.728</v>
-      </c>
+      <c r="F42" s="8" t="n"/>
     </row>
     <row r="43" ht="18" customHeight="1">
       <c r="A43" s="3" t="n"/>
@@ -1470,9 +1416,7 @@
           <t>[(0.35×0.4×3.6)]×9 = 4.536</t>
         </is>
       </c>
-      <c r="F43" s="5" t="n">
-        <v>4.536</v>
-      </c>
+      <c r="F43" s="8" t="n"/>
     </row>
     <row r="44" ht="18" customHeight="1">
       <c r="A44" s="3" t="n"/>
@@ -1492,9 +1436,7 @@
           <t>(0.4×0.4×3.6) = 0.576</t>
         </is>
       </c>
-      <c r="F44" s="5" t="n">
-        <v>0.576</v>
-      </c>
+      <c r="F44" s="8" t="n"/>
     </row>
     <row r="45" ht="18" customHeight="1">
       <c r="A45" s="3" t="n"/>
@@ -1514,9 +1456,7 @@
           <t>(0.35×0.4×3.6) = 0.504</t>
         </is>
       </c>
-      <c r="F45" s="5" t="n">
-        <v>0.504</v>
-      </c>
+      <c r="F45" s="8" t="n"/>
     </row>
     <row r="46" ht="18" customHeight="1">
       <c r="A46" s="3" t="n"/>
@@ -1536,9 +1476,7 @@
           <t>[(0.25×0.25×3.6)]×4 = 0.9</t>
         </is>
       </c>
-      <c r="F46" s="5" t="n">
-        <v>0.9</v>
-      </c>
+      <c r="F46" s="8" t="n"/>
     </row>
     <row r="47" ht="18" customHeight="1">
       <c r="A47" s="3" t="n"/>
@@ -1558,9 +1496,7 @@
           <t>[(0.4×0.4×3.6)]×3 = 1.728</t>
         </is>
       </c>
-      <c r="F47" s="5" t="n">
-        <v>1.728</v>
-      </c>
+      <c r="F47" s="8" t="n"/>
     </row>
     <row r="48" ht="18" customHeight="1">
       <c r="A48" s="3" t="n"/>
@@ -1580,9 +1516,7 @@
           <t>[(0.35×0.4×3.6)]×9 = 4.536</t>
         </is>
       </c>
-      <c r="F48" s="5" t="n">
-        <v>4.536</v>
-      </c>
+      <c r="F48" s="8" t="n"/>
     </row>
     <row r="49" ht="18" customHeight="1">
       <c r="A49" s="3" t="n"/>
@@ -1602,9 +1536,7 @@
           <t>(0.4×0.4×3.6) = 0.576</t>
         </is>
       </c>
-      <c r="F49" s="5" t="n">
-        <v>0.576</v>
-      </c>
+      <c r="F49" s="8" t="n"/>
     </row>
     <row r="50" ht="18" customHeight="1">
       <c r="A50" s="3" t="n"/>
@@ -1624,9 +1556,7 @@
           <t>(0.35×0.4×3.6) = 0.504</t>
         </is>
       </c>
-      <c r="F50" s="5" t="n">
-        <v>0.504</v>
-      </c>
+      <c r="F50" s="8" t="n"/>
     </row>
     <row r="51" ht="18" customHeight="1">
       <c r="A51" s="3" t="n"/>
@@ -1646,9 +1576,7 @@
           <t>[(0.25×0.25×3.6)]×4 = 0.9</t>
         </is>
       </c>
-      <c r="F51" s="5" t="n">
-        <v>0.9</v>
-      </c>
+      <c r="F51" s="8" t="n"/>
     </row>
     <row r="52" ht="18" customHeight="1">
       <c r="A52" s="3" t="n"/>
@@ -1668,9 +1596,7 @@
           <t>[(0.4×0.4×3.6)]×3 = 1.728</t>
         </is>
       </c>
-      <c r="F52" s="5" t="n">
-        <v>1.728</v>
-      </c>
+      <c r="F52" s="8" t="n"/>
     </row>
     <row r="53" ht="18" customHeight="1">
       <c r="A53" s="3" t="n"/>
@@ -1690,9 +1616,7 @@
           <t>[(0.35×0.4×3.6)]×9 = 4.536</t>
         </is>
       </c>
-      <c r="F53" s="5" t="n">
-        <v>4.536</v>
-      </c>
+      <c r="F53" s="8" t="n"/>
     </row>
     <row r="54" ht="18" customHeight="1">
       <c r="A54" s="3" t="n"/>
@@ -1712,9 +1636,7 @@
           <t>(0.4×0.4×3.6) = 0.576</t>
         </is>
       </c>
-      <c r="F54" s="5" t="n">
-        <v>0.576</v>
-      </c>
+      <c r="F54" s="8" t="n"/>
     </row>
     <row r="55" ht="18" customHeight="1">
       <c r="A55" s="3" t="n"/>
@@ -1734,9 +1656,7 @@
           <t>(0.35×0.4×3.6) = 0.504</t>
         </is>
       </c>
-      <c r="F55" s="5" t="n">
-        <v>0.504</v>
-      </c>
+      <c r="F55" s="8" t="n"/>
     </row>
     <row r="56" ht="18" customHeight="1">
       <c r="A56" s="3" t="n"/>
@@ -1756,9 +1676,7 @@
           <t>[(0.25×0.25×3.6)]×4 = 0.9</t>
         </is>
       </c>
-      <c r="F56" s="5" t="n">
-        <v>0.9</v>
-      </c>
+      <c r="F56" s="8" t="n"/>
     </row>
     <row r="57" ht="32" customHeight="1">
       <c r="A57" s="3" t="n"/>
@@ -1774,9 +1692,7 @@
           <t>0.456 + 1.323 + 0.152 + 0.147 + 1.728 + 4.536 + 0.576 + 0.504 + 0.9 + 1.728 + 4.536 + 0.576 + 0.504 + 0.9 + 1.728 + 4.536 + 0.576 + 0.504 + 0.9 + 1.728 + 4.536 + 0.576 + 0.504 + 0.9 = 35.054 ≈ 35.05</t>
         </is>
       </c>
-      <c r="F57" s="8" t="n">
-        <v>35.05</v>
-      </c>
+      <c r="F57" s="8" t="n"/>
     </row>
     <row r="58" ht="18" customHeight="1">
       <c r="A58" s="3" t="n">
@@ -1803,7 +1719,7 @@
         </is>
       </c>
       <c r="F58" s="5" t="n">
-        <v>2.7183</v>
+        <v>70.15000000000001</v>
       </c>
     </row>
     <row r="59" ht="18" customHeight="1">
@@ -1824,9 +1740,7 @@
           <t>(0.3×0.55×12.25)-0.1897 = 1.8315</t>
         </is>
       </c>
-      <c r="F59" s="5" t="n">
-        <v>1.8315</v>
-      </c>
+      <c r="F59" s="8" t="n"/>
     </row>
     <row r="60" ht="18" customHeight="1">
       <c r="A60" s="3" t="n"/>
@@ -1846,9 +1760,7 @@
           <t>(0.25×0.4×8.875)-0.075 + (0.3×0.55×6.575)-0.066 = 1.8314</t>
         </is>
       </c>
-      <c r="F60" s="5" t="n">
-        <v>1.8314</v>
-      </c>
+      <c r="F60" s="8" t="n"/>
     </row>
     <row r="61" ht="18" customHeight="1">
       <c r="A61" s="3" t="n"/>
@@ -1868,9 +1780,7 @@
           <t>(0.25×0.35×3.375)-0.0394-0.0031 = 0.2528</t>
         </is>
       </c>
-      <c r="F61" s="5" t="n">
-        <v>0.2528</v>
-      </c>
+      <c r="F61" s="8" t="n"/>
     </row>
     <row r="62" ht="18" customHeight="1">
       <c r="A62" s="3" t="n"/>
@@ -1890,9 +1800,7 @@
           <t>(0.25×0.4×15.45)-0.145 = 1.4</t>
         </is>
       </c>
-      <c r="F62" s="5" t="n">
-        <v>1.4</v>
-      </c>
+      <c r="F62" s="8" t="n"/>
     </row>
     <row r="63" ht="18" customHeight="1">
       <c r="A63" s="3" t="n"/>
@@ -1912,9 +1820,7 @@
           <t>(0.25×0.35×3.4)-0.0284 = 0.2691</t>
         </is>
       </c>
-      <c r="F63" s="5" t="n">
-        <v>0.2691</v>
-      </c>
+      <c r="F63" s="8" t="n"/>
     </row>
     <row r="64" ht="18" customHeight="1">
       <c r="A64" s="3" t="n"/>
@@ -1934,9 +1840,7 @@
           <t>[(0.25×0.4×1.7)-0.02]×2 + (0.25×0.55×12.25)-0.1581 + (0.25×0.55×12.05)-0.1991-0.0009 = 3.2832</t>
         </is>
       </c>
-      <c r="F64" s="5" t="n">
-        <v>3.2832</v>
-      </c>
+      <c r="F64" s="8" t="n"/>
     </row>
     <row r="65" ht="18" customHeight="1">
       <c r="A65" s="3" t="n"/>
@@ -1956,9 +1860,7 @@
           <t>[(0.25×0.4×1.7)-0.02]×2 + (0.25×0.55×12.25)-0.165 + (0.25×0.55×12.05)-0.1375 = 3.3388</t>
         </is>
       </c>
-      <c r="F65" s="5" t="n">
-        <v>3.3388</v>
-      </c>
+      <c r="F65" s="8" t="n"/>
     </row>
     <row r="66" ht="18" customHeight="1">
       <c r="A66" s="3" t="n"/>
@@ -1978,9 +1880,7 @@
           <t>(0.25×0.4×1.625)-0.0125 + (0.25×0.55×12.125)-0.1787-0.0172 = 1.6213</t>
         </is>
       </c>
-      <c r="F66" s="5" t="n">
-        <v>1.6213</v>
-      </c>
+      <c r="F66" s="8" t="n"/>
     </row>
     <row r="67" ht="18" customHeight="1">
       <c r="A67" s="3" t="n"/>
@@ -2000,9 +1900,7 @@
           <t>(0.25×0.4×8.9)-0.0775 + (0.25×0.65×6.85)-0.1097 = 1.8159</t>
         </is>
       </c>
-      <c r="F67" s="5" t="n">
-        <v>1.8159</v>
-      </c>
+      <c r="F67" s="8" t="n"/>
     </row>
     <row r="68" ht="18" customHeight="1">
       <c r="A68" s="3" t="n"/>
@@ -2022,9 +1920,7 @@
           <t>(0.25×0.4×15.5)-0.175 = 1.375</t>
         </is>
       </c>
-      <c r="F68" s="5" t="n">
-        <v>1.375</v>
-      </c>
+      <c r="F68" s="8" t="n"/>
     </row>
     <row r="69" ht="18" customHeight="1">
       <c r="A69" s="3" t="n"/>
@@ -2044,9 +1940,7 @@
           <t>(0.25×0.4×15.5)-0.15 = 1.4</t>
         </is>
       </c>
-      <c r="F69" s="5" t="n">
-        <v>1.4</v>
-      </c>
+      <c r="F69" s="8" t="n"/>
     </row>
     <row r="70" ht="18" customHeight="1">
       <c r="A70" s="3" t="n"/>
@@ -2066,9 +1960,7 @@
           <t>(0.25×0.4×8.9)-0.05 + (0.25×0.4×3.2)-0.025 + (0.25×0.4×3.4)-0.025 = 1.45</t>
         </is>
       </c>
-      <c r="F70" s="5" t="n">
-        <v>1.45</v>
-      </c>
+      <c r="F70" s="8" t="n"/>
     </row>
     <row r="71" ht="18" customHeight="1">
       <c r="A71" s="3" t="n"/>
@@ -2088,9 +1980,7 @@
           <t>(0.25×0.4×1.7)-0.02 + (0.25×0.55×12.25)-0.1581 = 1.6763</t>
         </is>
       </c>
-      <c r="F71" s="5" t="n">
-        <v>1.6763</v>
-      </c>
+      <c r="F71" s="8" t="n"/>
     </row>
     <row r="72" ht="18" customHeight="1">
       <c r="A72" s="3" t="n"/>
@@ -2110,9 +2000,7 @@
           <t>(0.25×0.4×1.7)-0.02 + (0.25×0.55×12.25)-0.165 = 1.6694</t>
         </is>
       </c>
-      <c r="F72" s="5" t="n">
-        <v>1.6694</v>
-      </c>
+      <c r="F72" s="8" t="n"/>
     </row>
     <row r="73" ht="18" customHeight="1">
       <c r="A73" s="3" t="n"/>
@@ -2132,9 +2020,7 @@
           <t>(0.25×0.4×1.7)-0.02 + (0.25×0.55×12.05)-0.1375 = 1.6694</t>
         </is>
       </c>
-      <c r="F73" s="5" t="n">
-        <v>1.6694</v>
-      </c>
+      <c r="F73" s="8" t="n"/>
     </row>
     <row r="74" ht="18" customHeight="1">
       <c r="A74" s="3" t="n"/>
@@ -2154,9 +2040,7 @@
           <t>(0.25×0.4×1.625)-0.0125 + (0.25×0.55×12.125)-0.1787-0.0172 = 1.6213</t>
         </is>
       </c>
-      <c r="F74" s="5" t="n">
-        <v>1.6213</v>
-      </c>
+      <c r="F74" s="8" t="n"/>
     </row>
     <row r="75" ht="18" customHeight="1">
       <c r="A75" s="3" t="n"/>
@@ -2176,9 +2060,7 @@
           <t>(0.25×0.4×1.7)-0.02 + (0.25×0.55×12.05)-0.1986-0.0006 = 1.6077</t>
         </is>
       </c>
-      <c r="F75" s="5" t="n">
-        <v>1.6077</v>
-      </c>
+      <c r="F75" s="8" t="n"/>
     </row>
     <row r="76" ht="18" customHeight="1">
       <c r="A76" s="3" t="n"/>
@@ -2198,9 +2080,7 @@
           <t>(0.25×0.4×8.9)-0.0775 + (0.25×0.65×6.85)-0.1097 = 1.8159</t>
         </is>
       </c>
-      <c r="F76" s="5" t="n">
-        <v>1.8159</v>
-      </c>
+      <c r="F76" s="8" t="n"/>
     </row>
     <row r="77" ht="18" customHeight="1">
       <c r="A77" s="3" t="n"/>
@@ -2220,9 +2100,7 @@
           <t>(0.25×0.4×15.5)-0.175 = 1.375</t>
         </is>
       </c>
-      <c r="F77" s="5" t="n">
-        <v>1.375</v>
-      </c>
+      <c r="F77" s="8" t="n"/>
     </row>
     <row r="78" ht="18" customHeight="1">
       <c r="A78" s="3" t="n"/>
@@ -2242,9 +2120,7 @@
           <t>(0.25×0.4×15.5)-0.15 = 1.4</t>
         </is>
       </c>
-      <c r="F78" s="5" t="n">
-        <v>1.4</v>
-      </c>
+      <c r="F78" s="8" t="n"/>
     </row>
     <row r="79" ht="18" customHeight="1">
       <c r="A79" s="3" t="n"/>
@@ -2264,9 +2140,7 @@
           <t>(0.25×0.3×3)-0.0188 = 0.2062</t>
         </is>
       </c>
-      <c r="F79" s="5" t="n">
-        <v>0.2062</v>
-      </c>
+      <c r="F79" s="8" t="n"/>
     </row>
     <row r="80" ht="18" customHeight="1">
       <c r="A80" s="3" t="n"/>
@@ -2286,9 +2160,7 @@
           <t>(0.25×0.4×15.5)-0.1 = 1.45</t>
         </is>
       </c>
-      <c r="F80" s="5" t="n">
-        <v>1.45</v>
-      </c>
+      <c r="F80" s="8" t="n"/>
     </row>
     <row r="81" ht="18" customHeight="1">
       <c r="A81" s="3" t="n"/>
@@ -2308,9 +2180,7 @@
           <t>(0.25×0.4×4.45)-0.025 = 0.42</t>
         </is>
       </c>
-      <c r="F81" s="5" t="n">
-        <v>0.42</v>
-      </c>
+      <c r="F81" s="8" t="n"/>
     </row>
     <row r="82" ht="18" customHeight="1">
       <c r="A82" s="3" t="n"/>
@@ -2330,9 +2200,7 @@
           <t>(0.25×0.3×2.05)-0.0188 = 0.135</t>
         </is>
       </c>
-      <c r="F82" s="5" t="n">
-        <v>0.135</v>
-      </c>
+      <c r="F82" s="8" t="n"/>
     </row>
     <row r="83" ht="18" customHeight="1">
       <c r="A83" s="3" t="n"/>
@@ -2352,9 +2220,7 @@
           <t>(0.25×0.35×3.4)-0.0219 + (0.25×0.35×3.2)-0.0219 = 0.5337</t>
         </is>
       </c>
-      <c r="F83" s="5" t="n">
-        <v>0.5337</v>
-      </c>
+      <c r="F83" s="8" t="n"/>
     </row>
     <row r="84" ht="18" customHeight="1">
       <c r="A84" s="3" t="n"/>
@@ -2374,9 +2240,7 @@
           <t>(0.25×0.4×1.7)-0.02 + (0.25×0.55×12.25)-0.1581 = 1.6763</t>
         </is>
       </c>
-      <c r="F84" s="5" t="n">
-        <v>1.6763</v>
-      </c>
+      <c r="F84" s="8" t="n"/>
     </row>
     <row r="85" ht="18" customHeight="1">
       <c r="A85" s="3" t="n"/>
@@ -2396,9 +2260,7 @@
           <t>(0.25×0.4×1.7)-0.02 + (0.25×0.55×12.25)-0.165 = 1.6694</t>
         </is>
       </c>
-      <c r="F85" s="5" t="n">
-        <v>1.6694</v>
-      </c>
+      <c r="F85" s="8" t="n"/>
     </row>
     <row r="86" ht="18" customHeight="1">
       <c r="A86" s="3" t="n"/>
@@ -2418,9 +2280,7 @@
           <t>(0.25×0.4×1.7)-0.02 + (0.25×0.55×12.05)-0.1375 = 1.6694</t>
         </is>
       </c>
-      <c r="F86" s="5" t="n">
-        <v>1.6694</v>
-      </c>
+      <c r="F86" s="8" t="n"/>
     </row>
     <row r="87" ht="18" customHeight="1">
       <c r="A87" s="3" t="n"/>
@@ -2440,9 +2300,7 @@
           <t>(0.25×0.4×1.625)-0.0125 + (0.25×0.55×12.125)-0.1787-0.0172 = 1.6213</t>
         </is>
       </c>
-      <c r="F87" s="5" t="n">
-        <v>1.6213</v>
-      </c>
+      <c r="F87" s="8" t="n"/>
     </row>
     <row r="88" ht="18" customHeight="1">
       <c r="A88" s="3" t="n"/>
@@ -2462,9 +2320,7 @@
           <t>(0.25×0.4×1.7)-0.02 + (0.25×0.55×12.05)-0.1986-0.0006 = 1.6077</t>
         </is>
       </c>
-      <c r="F88" s="5" t="n">
-        <v>1.6077</v>
-      </c>
+      <c r="F88" s="8" t="n"/>
     </row>
     <row r="89" ht="18" customHeight="1">
       <c r="A89" s="3" t="n"/>
@@ -2484,9 +2340,7 @@
           <t>(0.25×0.4×8.9)-0.0775 + (0.25×0.65×6.85)-0.1097 = 1.8159</t>
         </is>
       </c>
-      <c r="F89" s="5" t="n">
-        <v>1.8159</v>
-      </c>
+      <c r="F89" s="8" t="n"/>
     </row>
     <row r="90" ht="18" customHeight="1">
       <c r="A90" s="3" t="n"/>
@@ -2506,9 +2360,7 @@
           <t>(0.25×0.4×15.5)-0.175 = 1.375</t>
         </is>
       </c>
-      <c r="F90" s="5" t="n">
-        <v>1.375</v>
-      </c>
+      <c r="F90" s="8" t="n"/>
     </row>
     <row r="91" ht="18" customHeight="1">
       <c r="A91" s="3" t="n"/>
@@ -2528,9 +2380,7 @@
           <t>(0.25×0.4×15.5)-0.15 = 1.4</t>
         </is>
       </c>
-      <c r="F91" s="5" t="n">
-        <v>1.4</v>
-      </c>
+      <c r="F91" s="8" t="n"/>
     </row>
     <row r="92" ht="18" customHeight="1">
       <c r="A92" s="3" t="n"/>
@@ -2550,9 +2400,7 @@
           <t>(0.25×0.3×3)-0.0188 = 0.2062</t>
         </is>
       </c>
-      <c r="F92" s="5" t="n">
-        <v>0.2062</v>
-      </c>
+      <c r="F92" s="8" t="n"/>
     </row>
     <row r="93" ht="18" customHeight="1">
       <c r="A93" s="3" t="n"/>
@@ -2572,9 +2420,7 @@
           <t>(0.25×0.4×15.5)-0.1 = 1.45</t>
         </is>
       </c>
-      <c r="F93" s="5" t="n">
-        <v>1.45</v>
-      </c>
+      <c r="F93" s="8" t="n"/>
     </row>
     <row r="94" ht="18" customHeight="1">
       <c r="A94" s="3" t="n"/>
@@ -2594,9 +2440,7 @@
           <t>(0.25×0.4×4.45)-0.025 = 0.42</t>
         </is>
       </c>
-      <c r="F94" s="5" t="n">
-        <v>0.42</v>
-      </c>
+      <c r="F94" s="8" t="n"/>
     </row>
     <row r="95" ht="18" customHeight="1">
       <c r="A95" s="3" t="n"/>
@@ -2616,9 +2460,7 @@
           <t>(0.25×0.3×2.05)-0.0188 = 0.135</t>
         </is>
       </c>
-      <c r="F95" s="5" t="n">
-        <v>0.135</v>
-      </c>
+      <c r="F95" s="8" t="n"/>
     </row>
     <row r="96" ht="18" customHeight="1">
       <c r="A96" s="3" t="n"/>
@@ -2638,9 +2480,7 @@
           <t>(0.25×0.35×3.2)-0.0219 + (0.25×0.35×3.4)-0.0219 = 0.5337</t>
         </is>
       </c>
-      <c r="F96" s="5" t="n">
-        <v>0.5337</v>
-      </c>
+      <c r="F96" s="8" t="n"/>
     </row>
     <row r="97" ht="18" customHeight="1">
       <c r="A97" s="3" t="n"/>
@@ -2660,9 +2500,7 @@
           <t>[(0.25×0.4×1.7)-0.02]×2 + (0.25×0.55×12.25)-0.1581 + (0.25×0.55×12.05)-0.1986-0.0006 = 3.284</t>
         </is>
       </c>
-      <c r="F97" s="5" t="n">
-        <v>3.284</v>
-      </c>
+      <c r="F97" s="8" t="n"/>
     </row>
     <row r="98" ht="18" customHeight="1">
       <c r="A98" s="3" t="n"/>
@@ -2682,9 +2520,7 @@
           <t>[(0.25×0.4×1.7)-0.02]×2 + (0.25×0.55×12.25)-0.165 + (0.25×0.55×12.05)-0.1375 = 3.3388</t>
         </is>
       </c>
-      <c r="F98" s="5" t="n">
-        <v>3.3388</v>
-      </c>
+      <c r="F98" s="8" t="n"/>
     </row>
     <row r="99" ht="18" customHeight="1">
       <c r="A99" s="3" t="n"/>
@@ -2704,9 +2540,7 @@
           <t>(0.25×0.4×1.625)-0.0125 + (0.25×0.55×12.125)-0.1787-0.0172 = 1.6213</t>
         </is>
       </c>
-      <c r="F99" s="5" t="n">
-        <v>1.6213</v>
-      </c>
+      <c r="F99" s="8" t="n"/>
     </row>
     <row r="100" ht="18" customHeight="1">
       <c r="A100" s="3" t="n"/>
@@ -2726,9 +2560,7 @@
           <t>(0.25×0.4×8.9)-0.0775 + (0.25×0.65×6.85)-0.1097 = 1.8159</t>
         </is>
       </c>
-      <c r="F100" s="5" t="n">
-        <v>1.8159</v>
-      </c>
+      <c r="F100" s="8" t="n"/>
     </row>
     <row r="101" ht="18" customHeight="1">
       <c r="A101" s="3" t="n"/>
@@ -2748,9 +2580,7 @@
           <t>(0.25×0.4×15.5)-0.175 = 1.375</t>
         </is>
       </c>
-      <c r="F101" s="5" t="n">
-        <v>1.375</v>
-      </c>
+      <c r="F101" s="8" t="n"/>
     </row>
     <row r="102" ht="18" customHeight="1">
       <c r="A102" s="3" t="n"/>
@@ -2770,9 +2600,7 @@
           <t>(0.25×0.4×15.5)-0.15 = 1.4</t>
         </is>
       </c>
-      <c r="F102" s="5" t="n">
-        <v>1.4</v>
-      </c>
+      <c r="F102" s="8" t="n"/>
     </row>
     <row r="103" ht="18" customHeight="1">
       <c r="A103" s="3" t="n"/>
@@ -2792,9 +2620,7 @@
           <t>(0.25×0.4×15.5)-0.1 = 1.45</t>
         </is>
       </c>
-      <c r="F103" s="5" t="n">
-        <v>1.45</v>
-      </c>
+      <c r="F103" s="8" t="n"/>
     </row>
     <row r="104" ht="18" customHeight="1">
       <c r="A104" s="3" t="n"/>
@@ -2814,9 +2640,7 @@
           <t>(0.25×0.35×3.4)-0.0219 = 0.2756</t>
         </is>
       </c>
-      <c r="F104" s="5" t="n">
-        <v>0.2756</v>
-      </c>
+      <c r="F104" s="8" t="n"/>
     </row>
     <row r="105" ht="18" customHeight="1">
       <c r="A105" s="3" t="n"/>
@@ -2836,9 +2660,7 @@
           <t>(0.25×0.4×12.1)-0.075 = 1.135</t>
         </is>
       </c>
-      <c r="F105" s="5" t="n">
-        <v>1.135</v>
-      </c>
+      <c r="F105" s="8" t="n"/>
     </row>
     <row r="106" ht="18" customHeight="1">
       <c r="A106" s="3" t="n"/>
@@ -2858,9 +2680,7 @@
           <t>(0.25×0.4×3.4) = 0.34</t>
         </is>
       </c>
-      <c r="F106" s="5" t="n">
-        <v>0.34</v>
-      </c>
+      <c r="F106" s="8" t="n"/>
     </row>
     <row r="107" ht="18" customHeight="1">
       <c r="A107" s="3" t="n"/>
@@ -2880,9 +2700,7 @@
           <t>(0.25×0.4×3.65) = 0.365</t>
         </is>
       </c>
-      <c r="F107" s="5" t="n">
-        <v>0.365</v>
-      </c>
+      <c r="F107" s="8" t="n"/>
     </row>
     <row r="108" ht="46" customHeight="1">
       <c r="A108" s="3" t="n"/>
@@ -2898,9 +2716,7 @@
           <t>2.7183 + 1.8315 + 1.8314 + 0.2528 + 1.4 + 0.2691 + 3.2832 + 3.3388 + 1.6213 + 1.8159 + 1.375 + 1.4 + 1.45 + 1.6763 + 1.6694 + 1.6694 + 1.6213 + 1.6077 + 1.8159 + 1.375 + 1.4 + 0.2062 + 1.45 + 0.42 + 0.135 + 0.5337 + 1.6763 + 1.6694 + 1.6694 + 1.6213 + 1.6077 + 1.8159 + 1.375 + 1.4 + 0.2062 + 1.45 + 0.42 + 0.135 + 0.5337 + 3.284 + 3.3388 + 1.6213 + 1.8159 + 1.375 + 1.4 + 1.45 + 0.2756 + 1.135 + 0.34 + 0.365 = 70.1477 ≈ 70.15</t>
         </is>
       </c>
-      <c r="F108" s="8" t="n">
-        <v>70.15000000000001</v>
-      </c>
+      <c r="F108" s="8" t="n"/>
     </row>
     <row r="109" ht="18" customHeight="1">
       <c r="A109" s="3" t="n">
@@ -2927,7 +2743,7 @@
         </is>
       </c>
       <c r="F109" s="5" t="n">
-        <v>5.2434</v>
+        <v>75.48999999999999</v>
       </c>
     </row>
     <row r="110" ht="32" customHeight="1">
@@ -2948,9 +2764,7 @@
           <t>((5.85×4.45)×0.12)-0.0238-0.282 + ((5.85×4.45)×0.12)-0.0211-0.2835 + ((6.15×4.45)×0.12)-0.022-0.2921 + ((6.15×4.45)×0.12)-0.0238-0.291 + ((3.4×1.945)×0.12)-0.0181-0.1382-0.0172 = 12.1968</t>
         </is>
       </c>
-      <c r="F110" s="5" t="n">
-        <v>12.1968</v>
-      </c>
+      <c r="F110" s="8" t="n"/>
     </row>
     <row r="111" ht="18" customHeight="1">
       <c r="A111" s="3" t="n"/>
@@ -2970,9 +2784,7 @@
           <t>((3.4×1.5)×0.09)-0.0025-0.1021 + ((3.2×1.5)×0.09)-0.0023-0.0979 + ((4.45×1.5)×0.09)-0.0042-0.124 + ((4.45×1.5)×0.09)-0.0045-0.1237 = 1.6313</t>
         </is>
       </c>
-      <c r="F111" s="5" t="n">
-        <v>1.6313</v>
-      </c>
+      <c r="F111" s="8" t="n"/>
     </row>
     <row r="112" ht="32" customHeight="1">
       <c r="A112" s="3" t="n"/>
@@ -2992,9 +2804,7 @@
           <t>((4.45×3.15)×0.1)-0.011-0.175 + ((6.15×3.2)×0.1)-0.0135-0.2162 + ((4.35×3.4)×0.1)-0.0062-0.1828 + ((3.2×2.4)×0.1)-0.0111-0.1237 + ((3.45×3.2)×0.1)-0.0127-0.1488 = 5.8196</t>
         </is>
       </c>
-      <c r="F112" s="5" t="n">
-        <v>5.8196</v>
-      </c>
+      <c r="F112" s="8" t="n"/>
     </row>
     <row r="113" ht="32" customHeight="1">
       <c r="A113" s="3" t="n"/>
@@ -3014,9 +2824,7 @@
           <t>((5.85×4.45)×0.12)-0.0238-0.282 + ((5.85×4.45)×0.12)-0.0211-0.2835 + ((2.05×1.8)×0.12)-0.0048-0.1039 + ((2.05×1.2)×0.12)-0.09 + ((6.15×4.45)×0.12)-0.022-0.2921 = 9.1466</t>
         </is>
       </c>
-      <c r="F113" s="5" t="n">
-        <v>9.146599999999999</v>
-      </c>
+      <c r="F113" s="8" t="n"/>
     </row>
     <row r="114" ht="32" customHeight="1">
       <c r="A114" s="3" t="n"/>
@@ -3036,9 +2844,7 @@
           <t>((3×2.4)×0.09)-0.0043-0.1122 + ((3.4×1.8)×0.09)-0.0079-0.1046 + ((3.2×1.5)×0.09)-0.0023-0.0979 + ((3.4×1.5)×0.09)-0.0025-0.1021 + ((4.45×1.5)×0.09)-0.0042-0.124 + ((4.45×1.5)×0.09)-0.0045-0.1237 + ((3.4×1.31)×0.09)-0.0107-0.0918 = 2.8992</t>
         </is>
       </c>
-      <c r="F114" s="5" t="n">
-        <v>2.8992</v>
-      </c>
+      <c r="F114" s="8" t="n"/>
     </row>
     <row r="115" ht="32" customHeight="1">
       <c r="A115" s="3" t="n"/>
@@ -3058,9 +2864,7 @@
           <t>((3.2×2.4)×0.1)-0.0111-0.1237 + ((6.15×3.2)×0.1)-0.0135-0.2162 + ((3.45×3.2)×0.1)-0.0127-0.1488 + ((4.35×3.4)×0.1)-0.0062-0.1828 + ((4.45×3.15)×0.1)-0.011-0.175 = 5.8196</t>
         </is>
       </c>
-      <c r="F115" s="5" t="n">
-        <v>5.8196</v>
-      </c>
+      <c r="F115" s="8" t="n"/>
     </row>
     <row r="116" ht="32" customHeight="1">
       <c r="A116" s="3" t="n"/>
@@ -3080,9 +2884,7 @@
           <t>((6.15×4.45)×0.12)-0.022-0.2921 + ((2.05×1.2)×0.12)-0.09 + ((5.85×4.45)×0.12)-0.0238-0.282 + ((2.05×1.8)×0.12)-0.0048-0.1039 + ((5.85×4.45)×0.12)-0.0211-0.2835 = 9.1466</t>
         </is>
       </c>
-      <c r="F116" s="5" t="n">
-        <v>9.146599999999999</v>
-      </c>
+      <c r="F116" s="8" t="n"/>
     </row>
     <row r="117" ht="32" customHeight="1">
       <c r="A117" s="3" t="n"/>
@@ -3102,9 +2904,7 @@
           <t>((4.45×1.5)×0.09)-0.0045-0.1237 + ((4.45×1.5)×0.09)-0.0042-0.124 + ((3.4×1.5)×0.09)-0.0025-0.1021 + ((3.2×1.5)×0.09)-0.0023-0.0979 + ((3.4×1.8)×0.09)-0.0079-0.1046 + ((3×2.4)×0.09)-0.0043-0.1122 + ((3.4×1.31)×0.09)-0.0107-0.0918 = 2.8992</t>
         </is>
       </c>
-      <c r="F117" s="5" t="n">
-        <v>2.8992</v>
-      </c>
+      <c r="F117" s="8" t="n"/>
     </row>
     <row r="118" ht="46" customHeight="1">
       <c r="A118" s="3" t="n"/>
@@ -3124,9 +2924,7 @@
           <t>((4.45×0.65)×0.1)-0.011-0.1125 + ((4.45×0.65)×0.1)-0.0096-0.1131 + ((3.2×0.65)×0.1)-0.0096-0.0819 + ((5.2×3.2)×0.1)-0.0142-0.1906 + ((6.15×3.2)×0.1)-0.0135-0.2163 + ((4.35×3.4)×0.1)-0.0062-0.1828 + ((3.4×1.5)×0.1)-0.0028-0.1134 + ((3.2×1.5)×0.1)-0.0025-0.1088 + ((4.45×1.5)×0.1)-0.0047-0.1378 + ((4.45×1.5)×0.1)-0.005-0.1375 = 6.7486</t>
         </is>
       </c>
-      <c r="F118" s="5" t="n">
-        <v>6.7486</v>
-      </c>
+      <c r="F118" s="8" t="n"/>
     </row>
     <row r="119" ht="18" customHeight="1">
       <c r="A119" s="3" t="n"/>
@@ -3146,9 +2944,7 @@
           <t>((5.2×4.45)×0.12)-0.0106-0.273 + ((5.2×4.45)×0.12)-0.0096-0.2737 + ((6.15×4.45)×0.12)-0.022-0.2921 + ((6.15×4.45)×0.12)-0.0238-0.291 = 10.9259</t>
         </is>
       </c>
-      <c r="F119" s="5" t="n">
-        <v>10.9259</v>
-      </c>
+      <c r="F119" s="8" t="n"/>
     </row>
     <row r="120" ht="18" customHeight="1">
       <c r="A120" s="3" t="n"/>
@@ -3168,9 +2964,7 @@
           <t>((3.4×1.8)×0.09)-0.0079-0.1046 + ((3.4×1.31)×0.09)-0.0107-0.0918 = 0.7365</t>
         </is>
       </c>
-      <c r="F120" s="5" t="n">
-        <v>0.7365</v>
-      </c>
+      <c r="F120" s="8" t="n"/>
     </row>
     <row r="121" ht="18" customHeight="1">
       <c r="A121" s="3" t="n"/>
@@ -3190,9 +2984,7 @@
           <t>((3.41×0.655)×0.1)-0.0426-0.0409 + ((7.005×3.41)×0.1)-0.07-0.1778 = 2.2807</t>
         </is>
       </c>
-      <c r="F121" s="5" t="n">
-        <v>2.2807</v>
-      </c>
+      <c r="F121" s="8" t="n"/>
     </row>
     <row r="122" ht="18" customHeight="1">
       <c r="A122" s="3" t="n"/>
@@ -3208,9 +3000,7 @@
           <t>5.2434 + 12.1968 + 1.6313 + 5.8196 + 9.1466 + 2.8992 + 5.8196 + 9.1466 + 2.8992 + 6.7486 + 10.9259 + 0.7365 + 2.2807 = 75.494 ≈ 75.49</t>
         </is>
       </c>
-      <c r="F122" s="8" t="n">
-        <v>75.48999999999999</v>
-      </c>
+      <c r="F122" s="8" t="n"/>
     </row>
     <row r="123" ht="18" customHeight="1">
       <c r="A123" s="3" t="n">
@@ -3237,7 +3027,7 @@
         </is>
       </c>
       <c r="F123" s="5" t="n">
-        <v>0.189</v>
+        <v>0.38</v>
       </c>
     </row>
     <row r="124" ht="18" customHeight="1">
@@ -3258,9 +3048,7 @@
           <t>(0.25×0.35×2.225) = 0.1947</t>
         </is>
       </c>
-      <c r="F124" s="5" t="n">
-        <v>0.1947</v>
-      </c>
+      <c r="F124" s="8" t="n"/>
     </row>
     <row r="125" ht="18" customHeight="1">
       <c r="A125" s="3" t="n"/>
@@ -3276,9 +3064,7 @@
           <t>0.189 + 0.1947 = 0.3837 ≈ 0.38</t>
         </is>
       </c>
-      <c r="F125" s="8" t="n">
-        <v>0.38</v>
-      </c>
+      <c r="F125" s="8" t="n"/>
     </row>
     <row r="126" ht="18" customHeight="1">
       <c r="A126" s="3" t="n">
@@ -3305,7 +3091,7 @@
         </is>
       </c>
       <c r="F126" s="5" t="n">
-        <v>2.8942</v>
+        <v>11.14</v>
       </c>
     </row>
     <row r="127" ht="18" customHeight="1">
@@ -3326,9 +3112,7 @@
           <t>1.8087+0.5499+0.3899 = 2.7485</t>
         </is>
       </c>
-      <c r="F127" s="5" t="n">
-        <v>2.7485</v>
-      </c>
+      <c r="F127" s="8" t="n"/>
     </row>
     <row r="128" ht="18" customHeight="1">
       <c r="A128" s="3" t="n"/>
@@ -3348,9 +3132,7 @@
           <t>1.8087+0.5499+0.3899 = 2.7485</t>
         </is>
       </c>
-      <c r="F128" s="5" t="n">
-        <v>2.7485</v>
-      </c>
+      <c r="F128" s="8" t="n"/>
     </row>
     <row r="129" ht="18" customHeight="1">
       <c r="A129" s="3" t="n"/>
@@ -3370,9 +3152,7 @@
           <t>1.8087+0.5499+0.3899 = 2.7485</t>
         </is>
       </c>
-      <c r="F129" s="5" t="n">
-        <v>2.7485</v>
-      </c>
+      <c r="F129" s="8" t="n"/>
     </row>
     <row r="130" ht="18" customHeight="1">
       <c r="A130" s="3" t="n"/>
@@ -3388,9 +3168,7 @@
           <t>2.8942 + 2.7485 + 2.7485 + 2.7485 = 11.1397 ≈ 11.14</t>
         </is>
       </c>
-      <c r="F130" s="8" t="n">
-        <v>11.14</v>
-      </c>
+      <c r="F130" s="8" t="n"/>
     </row>
     <row r="131" ht="18" customHeight="1">
       <c r="A131" s="3" t="n">
@@ -3417,7 +3195,7 @@
         </is>
       </c>
       <c r="F131" s="5" t="n">
-        <v>0.0969</v>
+        <v>6.9</v>
       </c>
     </row>
     <row r="132" ht="18" customHeight="1">
@@ -3438,9 +3216,7 @@
           <t>[(0.25×0.37)×1.55]×3 = 0.4302</t>
         </is>
       </c>
-      <c r="F132" s="5" t="n">
-        <v>0.4302</v>
-      </c>
+      <c r="F132" s="8" t="n"/>
     </row>
     <row r="133" ht="18" customHeight="1">
       <c r="A133" s="3" t="n"/>
@@ -3460,9 +3236,7 @@
           <t>(0.25×0.25)×3.6-0.025 = 0.2</t>
         </is>
       </c>
-      <c r="F133" s="5" t="n">
-        <v>0.2</v>
-      </c>
+      <c r="F133" s="8" t="n"/>
     </row>
     <row r="134" ht="18" customHeight="1">
       <c r="A134" s="3" t="n"/>
@@ -3482,9 +3256,7 @@
           <t>[(0.25×0.37)×3.6-0.025]×3 = 0.924</t>
         </is>
       </c>
-      <c r="F134" s="5" t="n">
-        <v>0.924</v>
-      </c>
+      <c r="F134" s="8" t="n"/>
     </row>
     <row r="135" ht="18" customHeight="1">
       <c r="A135" s="3" t="n"/>
@@ -3504,9 +3276,7 @@
           <t>(0.25×0.25)×3.6+0.0461-0.025 = 0.2461</t>
         </is>
       </c>
-      <c r="F135" s="5" t="n">
-        <v>0.2461</v>
-      </c>
+      <c r="F135" s="8" t="n"/>
     </row>
     <row r="136" ht="18" customHeight="1">
       <c r="A136" s="3" t="n"/>
@@ -3526,9 +3296,7 @@
           <t>[(0.25×0.37)×3.6+0.0461-0.025]×3 = 1.0623</t>
         </is>
       </c>
-      <c r="F136" s="5" t="n">
-        <v>1.0623</v>
-      </c>
+      <c r="F136" s="8" t="n"/>
     </row>
     <row r="137" ht="18" customHeight="1">
       <c r="A137" s="3" t="n"/>
@@ -3548,9 +3316,7 @@
           <t>(0.25×0.25)×3.6+0.0461-0.025 = 0.2461</t>
         </is>
       </c>
-      <c r="F137" s="5" t="n">
-        <v>0.2461</v>
-      </c>
+      <c r="F137" s="8" t="n"/>
     </row>
     <row r="138" ht="18" customHeight="1">
       <c r="A138" s="3" t="n"/>
@@ -3570,9 +3336,7 @@
           <t>[(0.25×0.37)×3.6+0.0461-0.025]×3 = 1.0623</t>
         </is>
       </c>
-      <c r="F138" s="5" t="n">
-        <v>1.0623</v>
-      </c>
+      <c r="F138" s="8" t="n"/>
     </row>
     <row r="139" ht="18" customHeight="1">
       <c r="A139" s="3" t="n"/>
@@ -3592,9 +3356,7 @@
           <t>(0.25×0.25)×3.6+0.0461-0.025 = 0.2461</t>
         </is>
       </c>
-      <c r="F139" s="5" t="n">
-        <v>0.2461</v>
-      </c>
+      <c r="F139" s="8" t="n"/>
     </row>
     <row r="140" ht="18" customHeight="1">
       <c r="A140" s="3" t="n"/>
@@ -3614,9 +3376,7 @@
           <t>[(0.25×0.37)×3.6+0.0461-0.025]×3 = 1.0623</t>
         </is>
       </c>
-      <c r="F140" s="5" t="n">
-        <v>1.0623</v>
-      </c>
+      <c r="F140" s="8" t="n"/>
     </row>
     <row r="141" ht="32" customHeight="1">
       <c r="A141" s="3" t="n"/>
@@ -3636,9 +3396,7 @@
           <t>(0.25×0.25)×3+0.0496-0.0049-0.0004-0.0002-0.0017 + (0.25×0.25)×3+0.0432-0.0049-0.0004-0.0017 + (0.25×0.25)×3+0.0496-0.0042-0.0002-0.0017 + (0.25×0.25)×3+0.0407-0.0021-0.0219-0.0065 = 0.8823</t>
         </is>
       </c>
-      <c r="F141" s="5" t="n">
-        <v>0.8823</v>
-      </c>
+      <c r="F141" s="8" t="n"/>
     </row>
     <row r="142" ht="18" customHeight="1">
       <c r="A142" s="3" t="n"/>
@@ -3658,9 +3416,7 @@
           <t>[(0.25×0.37)×1.6+0.0128-0.0121]×2 + (0.25×0.37)×1.6+0.0128-0.012 = 0.4462</t>
         </is>
       </c>
-      <c r="F142" s="5" t="n">
-        <v>0.4462</v>
-      </c>
+      <c r="F142" s="8" t="n"/>
     </row>
     <row r="143" ht="18" customHeight="1">
       <c r="A143" s="3" t="n"/>
@@ -3676,9 +3432,7 @@
           <t>0.0969 + 0.4302 + 0.2 + 0.924 + 0.2461 + 1.0623 + 0.2461 + 1.0623 + 0.2461 + 1.0623 + 0.8823 + 0.4462 = 6.9048 ≈ 6.90</t>
         </is>
       </c>
-      <c r="F143" s="8" t="n">
-        <v>6.9</v>
-      </c>
+      <c r="F143" s="8" t="n"/>
     </row>
     <row r="144" ht="18" customHeight="1">
       <c r="A144" s="3" t="n">
@@ -3705,7 +3459,7 @@
         </is>
       </c>
       <c r="F144" s="5" t="n">
-        <v>1.1142</v>
+        <v>1.42</v>
       </c>
     </row>
     <row r="145" ht="18" customHeight="1">
@@ -3726,9 +3480,7 @@
           <t>(0.24×0.4×3.65)-0.048 = 0.3024</t>
         </is>
       </c>
-      <c r="F145" s="5" t="n">
-        <v>0.3024</v>
-      </c>
+      <c r="F145" s="8" t="n"/>
     </row>
     <row r="146" ht="18" customHeight="1">
       <c r="A146" s="3" t="n"/>
@@ -3744,9 +3496,7 @@
           <t>1.1142 + 0.3024 = 1.4166 ≈ 1.42</t>
         </is>
       </c>
-      <c r="F146" s="8" t="n">
-        <v>1.42</v>
-      </c>
+      <c r="F146" s="8" t="n"/>
     </row>
     <row r="147" ht="18" customHeight="1">
       <c r="A147" s="3" t="n">
@@ -3773,7 +3523,7 @@
         </is>
       </c>
       <c r="F147" s="5" t="n">
-        <v>0.0022</v>
+        <v>2.37</v>
       </c>
     </row>
     <row r="148" ht="18" customHeight="1">
@@ -3794,9 +3544,7 @@
           <t>[(0.048×2.3)]×2 = 0.2208</t>
         </is>
       </c>
-      <c r="F148" s="5" t="n">
-        <v>0.2208</v>
-      </c>
+      <c r="F148" s="8" t="n"/>
     </row>
     <row r="149" ht="18" customHeight="1">
       <c r="A149" s="3" t="n"/>
@@ -3816,9 +3564,7 @@
           <t>[(0.048×2.9)]×4 = 0.5568</t>
         </is>
       </c>
-      <c r="F149" s="5" t="n">
-        <v>0.5568</v>
-      </c>
+      <c r="F149" s="8" t="n"/>
     </row>
     <row r="150" ht="18" customHeight="1">
       <c r="A150" s="3" t="n"/>
@@ -3838,9 +3584,7 @@
           <t>[(0.048×2.3)]×2 = 0.2208</t>
         </is>
       </c>
-      <c r="F150" s="5" t="n">
-        <v>0.2208</v>
-      </c>
+      <c r="F150" s="8" t="n"/>
     </row>
     <row r="151" ht="18" customHeight="1">
       <c r="A151" s="3" t="n"/>
@@ -3860,9 +3604,7 @@
           <t>[(0.048×2.9)]×2 = 0.2784</t>
         </is>
       </c>
-      <c r="F151" s="5" t="n">
-        <v>0.2784</v>
-      </c>
+      <c r="F151" s="8" t="n"/>
     </row>
     <row r="152" ht="18" customHeight="1">
       <c r="A152" s="3" t="n"/>
@@ -3882,9 +3624,7 @@
           <t>[(0.048×2.3)]×2 = 0.2208</t>
         </is>
       </c>
-      <c r="F152" s="5" t="n">
-        <v>0.2208</v>
-      </c>
+      <c r="F152" s="8" t="n"/>
     </row>
     <row r="153" ht="18" customHeight="1">
       <c r="A153" s="3" t="n"/>
@@ -3904,9 +3644,7 @@
           <t>[(0.048×2.9)]×2 = 0.2784</t>
         </is>
       </c>
-      <c r="F153" s="5" t="n">
-        <v>0.2784</v>
-      </c>
+      <c r="F153" s="8" t="n"/>
     </row>
     <row r="154" ht="18" customHeight="1">
       <c r="A154" s="3" t="n"/>
@@ -3926,9 +3664,7 @@
           <t>[(0.048×2.3)]×2 = 0.2208</t>
         </is>
       </c>
-      <c r="F154" s="5" t="n">
-        <v>0.2208</v>
-      </c>
+      <c r="F154" s="8" t="n"/>
     </row>
     <row r="155" ht="18" customHeight="1">
       <c r="A155" s="3" t="n"/>
@@ -3948,9 +3684,7 @@
           <t>[(0.048×2.9)]×2 = 0.2784</t>
         </is>
       </c>
-      <c r="F155" s="5" t="n">
-        <v>0.2784</v>
-      </c>
+      <c r="F155" s="8" t="n"/>
     </row>
     <row r="156" ht="18" customHeight="1">
       <c r="A156" s="3" t="n"/>
@@ -3970,9 +3704,7 @@
           <t>(0.048×2) = 0.096</t>
         </is>
       </c>
-      <c r="F156" s="5" t="n">
-        <v>0.096</v>
-      </c>
+      <c r="F156" s="8" t="n"/>
     </row>
     <row r="157" ht="18" customHeight="1">
       <c r="A157" s="3" t="n"/>
@@ -3988,9 +3720,7 @@
           <t>0.0022 + 0.2208 + 0.5568 + 0.2208 + 0.2784 + 0.2208 + 0.2784 + 0.2208 + 0.2784 + 0.096 = 2.3734 ≈ 2.37</t>
         </is>
       </c>
-      <c r="F157" s="8" t="n">
-        <v>2.37</v>
-      </c>
+      <c r="F157" s="8" t="n"/>
     </row>
     <row r="158" ht="18" customHeight="1">
       <c r="A158" s="3" t="n">
@@ -4017,7 +3747,7 @@
         </is>
       </c>
       <c r="F158" s="5" t="n">
-        <v>31.7629</v>
+        <v>31.76</v>
       </c>
     </row>
     <row r="159" ht="18" customHeight="1">
@@ -4034,9 +3764,7 @@
           <t>31.7629 ≈ 31.76</t>
         </is>
       </c>
-      <c r="F159" s="8" t="n">
-        <v>31.76</v>
-      </c>
+      <c r="F159" s="8" t="n"/>
     </row>
     <row r="160" ht="18" customHeight="1">
       <c r="A160" s="3" t="n">
@@ -4063,7 +3791,7 @@
         </is>
       </c>
       <c r="F160" s="5" t="n">
-        <v>7.641</v>
+        <v>7.64</v>
       </c>
     </row>
     <row r="161" ht="18" customHeight="1">
@@ -4080,9 +3808,7 @@
           <t>7.641 ≈ 7.64</t>
         </is>
       </c>
-      <c r="F161" s="8" t="n">
-        <v>7.64</v>
-      </c>
+      <c r="F161" s="8" t="n"/>
     </row>
     <row r="162" ht="18" customHeight="1">
       <c r="A162" s="3" t="n">
@@ -4109,7 +3835,7 @@
         </is>
       </c>
       <c r="F162" s="5" t="n">
-        <v>0.536</v>
+        <v>2.78</v>
       </c>
     </row>
     <row r="163" ht="18" customHeight="1">
@@ -4130,9 +3856,7 @@
           <t>(0.048×13.53) + (0.048×5.745) + (0.048×15.53) + (0.048×11.995) = 2.2464</t>
         </is>
       </c>
-      <c r="F163" s="5" t="n">
-        <v>2.2464</v>
-      </c>
+      <c r="F163" s="8" t="n"/>
     </row>
     <row r="164" ht="18" customHeight="1">
       <c r="A164" s="3" t="n"/>
@@ -4148,9 +3872,7 @@
           <t>0.536 + 2.2464 = 2.7824 ≈ 2.78</t>
         </is>
       </c>
-      <c r="F164" s="8" t="n">
-        <v>2.78</v>
-      </c>
+      <c r="F164" s="8" t="n"/>
     </row>
     <row r="165" ht="18" customHeight="1">
       <c r="A165" s="3" t="n">
@@ -4177,7 +3899,7 @@
         </is>
       </c>
       <c r="F165" s="9" t="n">
-        <v>290.472</v>
+        <v>0.709</v>
       </c>
     </row>
     <row r="166" ht="18" customHeight="1">
@@ -4198,9 +3920,7 @@
           <t>179.984 + 185.64 = 365.624</t>
         </is>
       </c>
-      <c r="F166" s="9" t="n">
-        <v>365.624</v>
-      </c>
+      <c r="F166" s="10" t="n"/>
     </row>
     <row r="167" ht="18" customHeight="1">
       <c r="A167" s="3" t="n"/>
@@ -4220,9 +3940,7 @@
           <t>25.586 + 26.82 = 52.406</t>
         </is>
       </c>
-      <c r="F167" s="9" t="n">
-        <v>52.406</v>
-      </c>
+      <c r="F167" s="10" t="n"/>
     </row>
     <row r="168" ht="18" customHeight="1">
       <c r="A168" s="3" t="n"/>
@@ -4238,9 +3956,7 @@
           <t>(290.472 + 365.624 + 52.406) ÷ 1000 = 0.709</t>
         </is>
       </c>
-      <c r="F168" s="10" t="n">
-        <v>0.709</v>
-      </c>
+      <c r="F168" s="10" t="n"/>
     </row>
     <row r="169" ht="18" customHeight="1">
       <c r="A169" s="3" t="n">
@@ -4267,7 +3983,7 @@
         </is>
       </c>
       <c r="F169" s="9" t="n">
-        <v>34.047</v>
+        <v>0.492</v>
       </c>
     </row>
     <row r="170" ht="18" customHeight="1">
@@ -4288,9 +4004,7 @@
           <t>3.783 = 3.783</t>
         </is>
       </c>
-      <c r="F170" s="9" t="n">
-        <v>3.783</v>
-      </c>
+      <c r="F170" s="10" t="n"/>
     </row>
     <row r="171" ht="18" customHeight="1">
       <c r="A171" s="3" t="n"/>
@@ -4310,9 +4024,7 @@
           <t>44.523 = 44.523</t>
         </is>
       </c>
-      <c r="F171" s="9" t="n">
-        <v>44.523</v>
-      </c>
+      <c r="F171" s="10" t="n"/>
     </row>
     <row r="172" ht="18" customHeight="1">
       <c r="A172" s="3" t="n"/>
@@ -4332,9 +4044,7 @@
           <t>4.947 = 4.947</t>
         </is>
       </c>
-      <c r="F172" s="9" t="n">
-        <v>4.947</v>
-      </c>
+      <c r="F172" s="10" t="n"/>
     </row>
     <row r="173" ht="18" customHeight="1">
       <c r="A173" s="3" t="n"/>
@@ -4354,9 +4064,7 @@
           <t>12.96 + 19.584 + 12.96 + 19.584 = 65.088</t>
         </is>
       </c>
-      <c r="F173" s="9" t="n">
-        <v>65.08799999999999</v>
-      </c>
+      <c r="F173" s="10" t="n"/>
     </row>
     <row r="174" ht="18" customHeight="1">
       <c r="A174" s="3" t="n"/>
@@ -4376,9 +4084,7 @@
           <t>44.523 = 44.523</t>
         </is>
       </c>
-      <c r="F174" s="9" t="n">
-        <v>44.523</v>
-      </c>
+      <c r="F174" s="10" t="n"/>
     </row>
     <row r="175" ht="18" customHeight="1">
       <c r="A175" s="3" t="n"/>
@@ -4398,9 +4104,7 @@
           <t>4.947 = 4.947</t>
         </is>
       </c>
-      <c r="F175" s="9" t="n">
-        <v>4.947</v>
-      </c>
+      <c r="F175" s="10" t="n"/>
     </row>
     <row r="176" ht="18" customHeight="1">
       <c r="A176" s="3" t="n"/>
@@ -4420,9 +4124,7 @@
           <t>12.24 + 19.584 + 12.24 + 19.584 = 63.648</t>
         </is>
       </c>
-      <c r="F176" s="9" t="n">
-        <v>63.648</v>
-      </c>
+      <c r="F176" s="10" t="n"/>
     </row>
     <row r="177" ht="18" customHeight="1">
       <c r="A177" s="3" t="n"/>
@@ -4442,9 +4144,7 @@
           <t>44.523 = 44.523</t>
         </is>
       </c>
-      <c r="F177" s="9" t="n">
-        <v>44.523</v>
-      </c>
+      <c r="F177" s="10" t="n"/>
     </row>
     <row r="178" ht="18" customHeight="1">
       <c r="A178" s="3" t="n"/>
@@ -4464,9 +4164,7 @@
           <t>4.947 = 4.947</t>
         </is>
       </c>
-      <c r="F178" s="9" t="n">
-        <v>4.947</v>
-      </c>
+      <c r="F178" s="10" t="n"/>
     </row>
     <row r="179" ht="18" customHeight="1">
       <c r="A179" s="3" t="n"/>
@@ -4486,9 +4184,7 @@
           <t>24.48 + 39.168 = 63.648</t>
         </is>
       </c>
-      <c r="F179" s="9" t="n">
-        <v>63.648</v>
-      </c>
+      <c r="F179" s="10" t="n"/>
     </row>
     <row r="180" ht="18" customHeight="1">
       <c r="A180" s="3" t="n"/>
@@ -4508,9 +4204,7 @@
           <t>44.523 = 44.523</t>
         </is>
       </c>
-      <c r="F180" s="9" t="n">
-        <v>44.523</v>
-      </c>
+      <c r="F180" s="10" t="n"/>
     </row>
     <row r="181" ht="18" customHeight="1">
       <c r="A181" s="3" t="n"/>
@@ -4530,9 +4224,7 @@
           <t>4.947 = 4.947</t>
         </is>
       </c>
-      <c r="F181" s="9" t="n">
-        <v>4.947</v>
-      </c>
+      <c r="F181" s="10" t="n"/>
     </row>
     <row r="182" ht="18" customHeight="1">
       <c r="A182" s="3" t="n"/>
@@ -4552,9 +4244,7 @@
           <t>24.48 + 39.168 = 63.648</t>
         </is>
       </c>
-      <c r="F182" s="9" t="n">
-        <v>63.648</v>
-      </c>
+      <c r="F182" s="10" t="n"/>
     </row>
     <row r="183" ht="18" customHeight="1">
       <c r="A183" s="3" t="n"/>
@@ -4570,9 +4260,7 @@
           <t>(34.047 + 3.783 + 44.523 + 4.947 + 65.088 + 44.523 + 4.947 + 63.648 + 44.523 + 4.947 + 63.648 + 44.523 + 4.947 + 63.648) ÷ 1000 = 0.492</t>
         </is>
       </c>
-      <c r="F183" s="10" t="n">
-        <v>0.492</v>
-      </c>
+      <c r="F183" s="10" t="n"/>
     </row>
     <row r="184" ht="18" customHeight="1">
       <c r="A184" s="3" t="n">
@@ -4599,7 +4287,7 @@
         </is>
       </c>
       <c r="F184" s="9" t="n">
-        <v>9.023999999999999</v>
+        <v>0.175</v>
       </c>
     </row>
     <row r="185" ht="18" customHeight="1">
@@ -4620,9 +4308,7 @@
           <t>6.768 = 6.768</t>
         </is>
       </c>
-      <c r="F185" s="9" t="n">
-        <v>6.768</v>
-      </c>
+      <c r="F185" s="10" t="n"/>
     </row>
     <row r="186" ht="18" customHeight="1">
       <c r="A186" s="3" t="n"/>
@@ -4642,9 +4328,7 @@
           <t>24.816 + 9.588 = 34.404</t>
         </is>
       </c>
-      <c r="F186" s="9" t="n">
-        <v>34.404</v>
-      </c>
+      <c r="F186" s="10" t="n"/>
     </row>
     <row r="187" ht="18" customHeight="1">
       <c r="A187" s="3" t="n"/>
@@ -4664,9 +4348,7 @@
           <t>9.588 = 9.588</t>
         </is>
       </c>
-      <c r="F187" s="9" t="n">
-        <v>9.587999999999999</v>
-      </c>
+      <c r="F187" s="10" t="n"/>
     </row>
     <row r="188" ht="18" customHeight="1">
       <c r="A188" s="3" t="n"/>
@@ -4686,9 +4368,7 @@
           <t>28.764 = 28.764</t>
         </is>
       </c>
-      <c r="F188" s="9" t="n">
-        <v>28.764</v>
-      </c>
+      <c r="F188" s="10" t="n"/>
     </row>
     <row r="189" ht="18" customHeight="1">
       <c r="A189" s="3" t="n"/>
@@ -4708,9 +4388,7 @@
           <t>9.588 = 9.588</t>
         </is>
       </c>
-      <c r="F189" s="9" t="n">
-        <v>9.587999999999999</v>
-      </c>
+      <c r="F189" s="10" t="n"/>
     </row>
     <row r="190" ht="18" customHeight="1">
       <c r="A190" s="3" t="n"/>
@@ -4730,9 +4408,7 @@
           <t>28.764 = 28.764</t>
         </is>
       </c>
-      <c r="F190" s="9" t="n">
-        <v>28.764</v>
-      </c>
+      <c r="F190" s="10" t="n"/>
     </row>
     <row r="191" ht="18" customHeight="1">
       <c r="A191" s="3" t="n"/>
@@ -4752,9 +4428,7 @@
           <t>9.588 = 9.588</t>
         </is>
       </c>
-      <c r="F191" s="9" t="n">
-        <v>9.587999999999999</v>
-      </c>
+      <c r="F191" s="10" t="n"/>
     </row>
     <row r="192" ht="18" customHeight="1">
       <c r="A192" s="3" t="n"/>
@@ -4774,9 +4448,7 @@
           <t>28.764 = 28.764</t>
         </is>
       </c>
-      <c r="F192" s="9" t="n">
-        <v>28.764</v>
-      </c>
+      <c r="F192" s="10" t="n"/>
     </row>
     <row r="193" ht="18" customHeight="1">
       <c r="A193" s="3" t="n"/>
@@ -4796,9 +4468,7 @@
           <t>9.588 = 9.588</t>
         </is>
       </c>
-      <c r="F193" s="9" t="n">
-        <v>9.587999999999999</v>
-      </c>
+      <c r="F193" s="10" t="n"/>
     </row>
     <row r="194" ht="18" customHeight="1">
       <c r="A194" s="3" t="n"/>
@@ -4814,9 +4484,7 @@
           <t>(9.024 + 6.768 + 34.404 + 9.588 + 28.764 + 9.588 + 28.764 + 9.588 + 28.764 + 9.588) ÷ 1000 = 0.175</t>
         </is>
       </c>
-      <c r="F194" s="10" t="n">
-        <v>0.175</v>
-      </c>
+      <c r="F194" s="10" t="n"/>
     </row>
     <row r="195" ht="18" customHeight="1">
       <c r="A195" s="3" t="n">
@@ -4842,7 +4510,7 @@
           <t>计算书中无依据，需补充</t>
         </is>
       </c>
-      <c r="F195" s="9" t="inlineStr">
+      <c r="F195" s="10" t="inlineStr">
         <is>
           <t>需补充</t>
         </is>
@@ -4873,7 +4541,7 @@
         </is>
       </c>
       <c r="F196" s="9" t="n">
-        <v>111.692</v>
+        <v>0.345</v>
       </c>
     </row>
     <row r="197" ht="18" customHeight="1">
@@ -4894,9 +4562,7 @@
           <t>41.08 + 2.9 + 4.924 + 41.08 = 89.984</t>
         </is>
       </c>
-      <c r="F197" s="9" t="n">
-        <v>89.98399999999999</v>
-      </c>
+      <c r="F197" s="10" t="n"/>
     </row>
     <row r="198" ht="18" customHeight="1">
       <c r="A198" s="3" t="n"/>
@@ -4916,9 +4582,7 @@
           <t>82.16 = 82.16</t>
         </is>
       </c>
-      <c r="F198" s="9" t="n">
-        <v>82.16</v>
-      </c>
+      <c r="F198" s="10" t="n"/>
     </row>
     <row r="199" ht="18" customHeight="1">
       <c r="A199" s="3" t="n"/>
@@ -4938,9 +4602,7 @@
           <t>34.56 + 26.456 = 61.016</t>
         </is>
       </c>
-      <c r="F199" s="9" t="n">
-        <v>61.016</v>
-      </c>
+      <c r="F199" s="10" t="n"/>
     </row>
     <row r="200" ht="18" customHeight="1">
       <c r="A200" s="3" t="n"/>
@@ -4956,9 +4618,7 @@
           <t>(111.692 + 89.984 + 82.16 + 61.016) ÷ 1000 = 0.345</t>
         </is>
       </c>
-      <c r="F200" s="10" t="n">
-        <v>0.345</v>
-      </c>
+      <c r="F200" s="10" t="n"/>
     </row>
     <row r="201" ht="18" customHeight="1">
       <c r="A201" s="3" t="n">
@@ -4985,7 +4645,7 @@
         </is>
       </c>
       <c r="F201" s="9" t="n">
-        <v>367.632</v>
+        <v>2.989</v>
       </c>
     </row>
     <row r="202" ht="18" customHeight="1">
@@ -5006,9 +4666,7 @@
           <t>21.18 + 27.48 = 48.66</t>
         </is>
       </c>
-      <c r="F202" s="9" t="n">
-        <v>48.66</v>
-      </c>
+      <c r="F202" s="10" t="n"/>
     </row>
     <row r="203" ht="18" customHeight="1">
       <c r="A203" s="3" t="n"/>
@@ -5028,9 +4686,7 @@
           <t>22.38 + 28.68 = 51.06</t>
         </is>
       </c>
-      <c r="F203" s="9" t="n">
-        <v>51.06</v>
-      </c>
+      <c r="F203" s="10" t="n"/>
     </row>
     <row r="204" ht="18" customHeight="1">
       <c r="A204" s="3" t="n"/>
@@ -5050,9 +4706,7 @@
           <t>518.4 = 518.4</t>
         </is>
       </c>
-      <c r="F204" s="9" t="n">
-        <v>518.4</v>
-      </c>
+      <c r="F204" s="10" t="n"/>
     </row>
     <row r="205" ht="18" customHeight="1">
       <c r="A205" s="3" t="n"/>
@@ -5072,9 +4726,7 @@
           <t>72 = 72</t>
         </is>
       </c>
-      <c r="F205" s="9" t="n">
-        <v>72</v>
-      </c>
+      <c r="F205" s="10" t="n"/>
     </row>
     <row r="206" ht="18" customHeight="1">
       <c r="A206" s="3" t="n"/>
@@ -5094,9 +4746,7 @@
           <t>72 = 72</t>
         </is>
       </c>
-      <c r="F206" s="9" t="n">
-        <v>72</v>
-      </c>
+      <c r="F206" s="10" t="n"/>
     </row>
     <row r="207" ht="18" customHeight="1">
       <c r="A207" s="3" t="n"/>
@@ -5116,9 +4766,7 @@
           <t>518.4 = 518.4</t>
         </is>
       </c>
-      <c r="F207" s="9" t="n">
-        <v>518.4</v>
-      </c>
+      <c r="F207" s="10" t="n"/>
     </row>
     <row r="208" ht="18" customHeight="1">
       <c r="A208" s="3" t="n"/>
@@ -5138,9 +4786,7 @@
           <t>72 = 72</t>
         </is>
       </c>
-      <c r="F208" s="9" t="n">
-        <v>72</v>
-      </c>
+      <c r="F208" s="10" t="n"/>
     </row>
     <row r="209" ht="18" customHeight="1">
       <c r="A209" s="3" t="n"/>
@@ -5160,9 +4806,7 @@
           <t>72 = 72</t>
         </is>
       </c>
-      <c r="F209" s="9" t="n">
-        <v>72</v>
-      </c>
+      <c r="F209" s="10" t="n"/>
     </row>
     <row r="210" ht="18" customHeight="1">
       <c r="A210" s="3" t="n"/>
@@ -5182,9 +4826,7 @@
           <t>518.4 = 518.4</t>
         </is>
       </c>
-      <c r="F210" s="9" t="n">
-        <v>518.4</v>
-      </c>
+      <c r="F210" s="10" t="n"/>
     </row>
     <row r="211" ht="18" customHeight="1">
       <c r="A211" s="3" t="n"/>
@@ -5204,9 +4846,7 @@
           <t>72 = 72</t>
         </is>
       </c>
-      <c r="F211" s="9" t="n">
-        <v>72</v>
-      </c>
+      <c r="F211" s="10" t="n"/>
     </row>
     <row r="212" ht="18" customHeight="1">
       <c r="A212" s="3" t="n"/>
@@ -5226,9 +4866,7 @@
           <t>72 = 72</t>
         </is>
       </c>
-      <c r="F212" s="9" t="n">
-        <v>72</v>
-      </c>
+      <c r="F212" s="10" t="n"/>
     </row>
     <row r="213" ht="18" customHeight="1">
       <c r="A213" s="3" t="n"/>
@@ -5248,9 +4886,7 @@
           <t>233.928 + 188.568 = 422.496</t>
         </is>
       </c>
-      <c r="F213" s="9" t="n">
-        <v>422.496</v>
-      </c>
+      <c r="F213" s="10" t="n"/>
     </row>
     <row r="214" ht="18" customHeight="1">
       <c r="A214" s="3" t="n"/>
@@ -5270,9 +4906,7 @@
           <t>18.42 + 10.476 + 14.64 + 12.996 = 56.532</t>
         </is>
       </c>
-      <c r="F214" s="9" t="n">
-        <v>56.532</v>
-      </c>
+      <c r="F214" s="10" t="n"/>
     </row>
     <row r="215" ht="18" customHeight="1">
       <c r="A215" s="3" t="n"/>
@@ -5292,9 +4926,7 @@
           <t>24.56 + 19.52 + 5.238 + 6.498 = 55.816</t>
         </is>
       </c>
-      <c r="F215" s="9" t="n">
-        <v>55.816</v>
-      </c>
+      <c r="F215" s="10" t="n"/>
     </row>
     <row r="216" ht="18" customHeight="1">
       <c r="A216" s="3" t="n"/>
@@ -5310,9 +4942,7 @@
           <t>(367.632 + 48.66 + 51.06 + 518.4 + 72 + 72 + 518.4 + 72 + 72 + 518.4 + 72 + 72 + 422.496 + 56.532 + 55.816) ÷ 1000 = 2.989</t>
         </is>
       </c>
-      <c r="F216" s="10" t="n">
-        <v>2.989</v>
-      </c>
+      <c r="F216" s="10" t="n"/>
     </row>
     <row r="217" ht="18" customHeight="1">
       <c r="A217" s="3" t="n">
@@ -5339,7 +4969,7 @@
         </is>
       </c>
       <c r="F217" s="9" t="n">
-        <v>117.356</v>
+        <v>0.968</v>
       </c>
     </row>
     <row r="218" ht="18" customHeight="1">
@@ -5360,9 +4990,7 @@
           <t>179.824 + 71.136 = 250.96</t>
         </is>
       </c>
-      <c r="F218" s="9" t="n">
-        <v>250.96</v>
-      </c>
+      <c r="F218" s="10" t="n"/>
     </row>
     <row r="219" ht="18" customHeight="1">
       <c r="A219" s="3" t="n"/>
@@ -5382,9 +5010,7 @@
           <t>213.408 = 213.408</t>
         </is>
       </c>
-      <c r="F219" s="9" t="n">
-        <v>213.408</v>
-      </c>
+      <c r="F219" s="10" t="n"/>
     </row>
     <row r="220" ht="18" customHeight="1">
       <c r="A220" s="3" t="n"/>
@@ -5404,9 +5030,7 @@
           <t>213.408 = 213.408</t>
         </is>
       </c>
-      <c r="F220" s="9" t="n">
-        <v>213.408</v>
-      </c>
+      <c r="F220" s="10" t="n"/>
     </row>
     <row r="221" ht="18" customHeight="1">
       <c r="A221" s="3" t="n"/>
@@ -5426,9 +5050,7 @@
           <t>96.864 + 76.116 = 172.98</t>
         </is>
       </c>
-      <c r="F221" s="9" t="n">
-        <v>172.98</v>
-      </c>
+      <c r="F221" s="10" t="n"/>
     </row>
     <row r="222" ht="18" customHeight="1">
       <c r="A222" s="3" t="n"/>
@@ -5444,9 +5066,7 @@
           <t>(117.356 + 250.96 + 213.408 + 213.408 + 172.98) ÷ 1000 = 0.968</t>
         </is>
       </c>
-      <c r="F222" s="10" t="n">
-        <v>0.968</v>
-      </c>
+      <c r="F222" s="10" t="n"/>
     </row>
     <row r="223" ht="18" customHeight="1">
       <c r="A223" s="3" t="n">
@@ -5473,7 +5093,7 @@
         </is>
       </c>
       <c r="F223" s="9" t="n">
-        <v>3.24</v>
+        <v>0.307</v>
       </c>
     </row>
     <row r="224" ht="18" customHeight="1">
@@ -5494,9 +5114,7 @@
           <t>2.16 = 2.16</t>
         </is>
       </c>
-      <c r="F224" s="9" t="n">
-        <v>2.16</v>
-      </c>
+      <c r="F224" s="10" t="n"/>
     </row>
     <row r="225" ht="18" customHeight="1">
       <c r="A225" s="3" t="n"/>
@@ -5516,9 +5134,7 @@
           <t>10.374 + 1.224 = 11.598</t>
         </is>
       </c>
-      <c r="F225" s="9" t="n">
-        <v>11.598</v>
-      </c>
+      <c r="F225" s="10" t="n"/>
     </row>
     <row r="226" ht="18" customHeight="1">
       <c r="A226" s="3" t="n"/>
@@ -5538,9 +5154,7 @@
           <t>3.584 = 3.584</t>
         </is>
       </c>
-      <c r="F226" s="9" t="n">
-        <v>3.584</v>
-      </c>
+      <c r="F226" s="10" t="n"/>
     </row>
     <row r="227" ht="18" customHeight="1">
       <c r="A227" s="3" t="n"/>
@@ -5560,9 +5174,7 @@
           <t>18.031 = 18.031</t>
         </is>
       </c>
-      <c r="F227" s="9" t="n">
-        <v>18.031</v>
-      </c>
+      <c r="F227" s="10" t="n"/>
     </row>
     <row r="228" ht="18" customHeight="1">
       <c r="A228" s="3" t="n"/>
@@ -5582,9 +5194,7 @@
           <t>3.584 = 3.584</t>
         </is>
       </c>
-      <c r="F228" s="9" t="n">
-        <v>3.584</v>
-      </c>
+      <c r="F228" s="10" t="n"/>
     </row>
     <row r="229" ht="18" customHeight="1">
       <c r="A229" s="3" t="n"/>
@@ -5604,9 +5214,7 @@
           <t>0.504 = 0.504</t>
         </is>
       </c>
-      <c r="F229" s="9" t="n">
-        <v>0.504</v>
-      </c>
+      <c r="F229" s="10" t="n"/>
     </row>
     <row r="230" ht="18" customHeight="1">
       <c r="A230" s="3" t="n"/>
@@ -5626,9 +5234,7 @@
           <t>4.788 = 4.788</t>
         </is>
       </c>
-      <c r="F230" s="9" t="n">
-        <v>4.788</v>
-      </c>
+      <c r="F230" s="10" t="n"/>
     </row>
     <row r="231" ht="18" customHeight="1">
       <c r="A231" s="3" t="n"/>
@@ -5648,9 +5254,7 @@
           <t>2.457 = 2.457</t>
         </is>
       </c>
-      <c r="F231" s="9" t="n">
-        <v>2.457</v>
-      </c>
+      <c r="F231" s="10" t="n"/>
     </row>
     <row r="232" ht="18" customHeight="1">
       <c r="A232" s="3" t="n"/>
@@ -5670,9 +5274,7 @@
           <t>2.142 = 2.142</t>
         </is>
       </c>
-      <c r="F232" s="9" t="n">
-        <v>2.142</v>
-      </c>
+      <c r="F232" s="10" t="n"/>
     </row>
     <row r="233" ht="18" customHeight="1">
       <c r="A233" s="3" t="n"/>
@@ -5692,9 +5294,7 @@
           <t>19.712 = 19.712</t>
         </is>
       </c>
-      <c r="F233" s="9" t="n">
-        <v>19.712</v>
-      </c>
+      <c r="F233" s="10" t="n"/>
     </row>
     <row r="234" ht="18" customHeight="1">
       <c r="A234" s="3" t="n"/>
@@ -5714,9 +5314,7 @@
           <t>2.394 = 2.394</t>
         </is>
       </c>
-      <c r="F234" s="9" t="n">
-        <v>2.394</v>
-      </c>
+      <c r="F234" s="10" t="n"/>
     </row>
     <row r="235" ht="18" customHeight="1">
       <c r="A235" s="3" t="n"/>
@@ -5736,9 +5334,7 @@
           <t>2.394 = 2.394</t>
         </is>
       </c>
-      <c r="F235" s="9" t="n">
-        <v>2.394</v>
-      </c>
+      <c r="F235" s="10" t="n"/>
     </row>
     <row r="236" ht="18" customHeight="1">
       <c r="A236" s="3" t="n"/>
@@ -5758,9 +5354,7 @@
           <t>2.394 = 2.394</t>
         </is>
       </c>
-      <c r="F236" s="9" t="n">
-        <v>2.394</v>
-      </c>
+      <c r="F236" s="10" t="n"/>
     </row>
     <row r="237" ht="18" customHeight="1">
       <c r="A237" s="3" t="n"/>
@@ -5780,9 +5374,7 @@
           <t>2.457 = 2.457</t>
         </is>
       </c>
-      <c r="F237" s="9" t="n">
-        <v>2.457</v>
-      </c>
+      <c r="F237" s="10" t="n"/>
     </row>
     <row r="238" ht="18" customHeight="1">
       <c r="A238" s="3" t="n"/>
@@ -5802,9 +5394,7 @@
           <t>2.394 = 2.394</t>
         </is>
       </c>
-      <c r="F238" s="9" t="n">
-        <v>2.394</v>
-      </c>
+      <c r="F238" s="10" t="n"/>
     </row>
     <row r="239" ht="18" customHeight="1">
       <c r="A239" s="3" t="n"/>
@@ -5824,9 +5414,7 @@
           <t>4.914 = 4.914</t>
         </is>
       </c>
-      <c r="F239" s="9" t="n">
-        <v>4.914</v>
-      </c>
+      <c r="F239" s="10" t="n"/>
     </row>
     <row r="240" ht="18" customHeight="1">
       <c r="A240" s="3" t="n"/>
@@ -5846,9 +5434,7 @@
           <t>18.688 = 18.688</t>
         </is>
       </c>
-      <c r="F240" s="9" t="n">
-        <v>18.688</v>
-      </c>
+      <c r="F240" s="10" t="n"/>
     </row>
     <row r="241" ht="18" customHeight="1">
       <c r="A241" s="3" t="n"/>
@@ -5868,9 +5454,7 @@
           <t>3.165 = 3.165</t>
         </is>
       </c>
-      <c r="F241" s="9" t="n">
-        <v>3.165</v>
-      </c>
+      <c r="F241" s="10" t="n"/>
     </row>
     <row r="242" ht="18" customHeight="1">
       <c r="A242" s="3" t="n"/>
@@ -5890,9 +5474,7 @@
           <t>19.712 = 19.712</t>
         </is>
       </c>
-      <c r="F242" s="9" t="n">
-        <v>19.712</v>
-      </c>
+      <c r="F242" s="10" t="n"/>
     </row>
     <row r="243" ht="18" customHeight="1">
       <c r="A243" s="3" t="n"/>
@@ -5912,9 +5494,7 @@
           <t>7.168 = 7.168</t>
         </is>
       </c>
-      <c r="F243" s="9" t="n">
-        <v>7.168</v>
-      </c>
+      <c r="F243" s="10" t="n"/>
     </row>
     <row r="244" ht="18" customHeight="1">
       <c r="A244" s="3" t="n"/>
@@ -5934,9 +5514,7 @@
           <t>2.11 = 2.11</t>
         </is>
       </c>
-      <c r="F244" s="9" t="n">
-        <v>2.11</v>
-      </c>
+      <c r="F244" s="10" t="n"/>
     </row>
     <row r="245" ht="18" customHeight="1">
       <c r="A245" s="3" t="n"/>
@@ -5956,9 +5534,7 @@
           <t>3.961 + 3.728 = 7.689</t>
         </is>
       </c>
-      <c r="F245" s="9" t="n">
-        <v>7.689</v>
-      </c>
+      <c r="F245" s="10" t="n"/>
     </row>
     <row r="246" ht="18" customHeight="1">
       <c r="A246" s="3" t="n"/>
@@ -5978,9 +5554,7 @@
           <t>2.394 = 2.394</t>
         </is>
       </c>
-      <c r="F246" s="9" t="n">
-        <v>2.394</v>
-      </c>
+      <c r="F246" s="10" t="n"/>
     </row>
     <row r="247" ht="18" customHeight="1">
       <c r="A247" s="3" t="n"/>
@@ -6000,9 +5574,7 @@
           <t>2.394 = 2.394</t>
         </is>
       </c>
-      <c r="F247" s="9" t="n">
-        <v>2.394</v>
-      </c>
+      <c r="F247" s="10" t="n"/>
     </row>
     <row r="248" ht="18" customHeight="1">
       <c r="A248" s="3" t="n"/>
@@ -6022,9 +5594,7 @@
           <t>2.394 = 2.394</t>
         </is>
       </c>
-      <c r="F248" s="9" t="n">
-        <v>2.394</v>
-      </c>
+      <c r="F248" s="10" t="n"/>
     </row>
     <row r="249" ht="18" customHeight="1">
       <c r="A249" s="3" t="n"/>
@@ -6044,9 +5614,7 @@
           <t>2.457 = 2.457</t>
         </is>
       </c>
-      <c r="F249" s="9" t="n">
-        <v>2.457</v>
-      </c>
+      <c r="F249" s="10" t="n"/>
     </row>
     <row r="250" ht="18" customHeight="1">
       <c r="A250" s="3" t="n"/>
@@ -6066,9 +5634,7 @@
           <t>2.394 = 2.394</t>
         </is>
       </c>
-      <c r="F250" s="9" t="n">
-        <v>2.394</v>
-      </c>
+      <c r="F250" s="10" t="n"/>
     </row>
     <row r="251" ht="18" customHeight="1">
       <c r="A251" s="3" t="n"/>
@@ -6088,9 +5654,7 @@
           <t>4.914 = 4.914</t>
         </is>
       </c>
-      <c r="F251" s="9" t="n">
-        <v>4.914</v>
-      </c>
+      <c r="F251" s="10" t="n"/>
     </row>
     <row r="252" ht="18" customHeight="1">
       <c r="A252" s="3" t="n"/>
@@ -6110,9 +5674,7 @@
           <t>18.688 = 18.688</t>
         </is>
       </c>
-      <c r="F252" s="9" t="n">
-        <v>18.688</v>
-      </c>
+      <c r="F252" s="10" t="n"/>
     </row>
     <row r="253" ht="18" customHeight="1">
       <c r="A253" s="3" t="n"/>
@@ -6132,9 +5694,7 @@
           <t>3.165 = 3.165</t>
         </is>
       </c>
-      <c r="F253" s="9" t="n">
-        <v>3.165</v>
-      </c>
+      <c r="F253" s="10" t="n"/>
     </row>
     <row r="254" ht="18" customHeight="1">
       <c r="A254" s="3" t="n"/>
@@ -6154,9 +5714,7 @@
           <t>19.712 = 19.712</t>
         </is>
       </c>
-      <c r="F254" s="9" t="n">
-        <v>19.712</v>
-      </c>
+      <c r="F254" s="10" t="n"/>
     </row>
     <row r="255" ht="18" customHeight="1">
       <c r="A255" s="3" t="n"/>
@@ -6176,9 +5734,7 @@
           <t>7.168 = 7.168</t>
         </is>
       </c>
-      <c r="F255" s="9" t="n">
-        <v>7.168</v>
-      </c>
+      <c r="F255" s="10" t="n"/>
     </row>
     <row r="256" ht="18" customHeight="1">
       <c r="A256" s="3" t="n"/>
@@ -6198,9 +5754,7 @@
           <t>2.11 = 2.11</t>
         </is>
       </c>
-      <c r="F256" s="9" t="n">
-        <v>2.11</v>
-      </c>
+      <c r="F256" s="10" t="n"/>
     </row>
     <row r="257" ht="18" customHeight="1">
       <c r="A257" s="3" t="n"/>
@@ -6220,9 +5774,7 @@
           <t>3.728 + 3.961 = 7.689</t>
         </is>
       </c>
-      <c r="F257" s="9" t="n">
-        <v>7.689</v>
-      </c>
+      <c r="F257" s="10" t="n"/>
     </row>
     <row r="258" ht="18" customHeight="1">
       <c r="A258" s="3" t="n"/>
@@ -6242,9 +5794,7 @@
           <t>2.394 + 2.394 = 4.788</t>
         </is>
       </c>
-      <c r="F258" s="9" t="n">
-        <v>4.788</v>
-      </c>
+      <c r="F258" s="10" t="n"/>
     </row>
     <row r="259" ht="18" customHeight="1">
       <c r="A259" s="3" t="n"/>
@@ -6264,9 +5814,7 @@
           <t>2.394 + 2.394 = 4.788</t>
         </is>
       </c>
-      <c r="F259" s="9" t="n">
-        <v>4.788</v>
-      </c>
+      <c r="F259" s="10" t="n"/>
     </row>
     <row r="260" ht="18" customHeight="1">
       <c r="A260" s="3" t="n"/>
@@ -6286,9 +5834,7 @@
           <t>2.457 = 2.457</t>
         </is>
       </c>
-      <c r="F260" s="9" t="n">
-        <v>2.457</v>
-      </c>
+      <c r="F260" s="10" t="n"/>
     </row>
     <row r="261" ht="18" customHeight="1">
       <c r="A261" s="3" t="n"/>
@@ -6308,9 +5854,7 @@
           <t>2.142 = 2.142</t>
         </is>
       </c>
-      <c r="F261" s="9" t="n">
-        <v>2.142</v>
-      </c>
+      <c r="F261" s="10" t="n"/>
     </row>
     <row r="262" ht="18" customHeight="1">
       <c r="A262" s="3" t="n"/>
@@ -6330,9 +5874,7 @@
           <t>18.688 = 18.688</t>
         </is>
       </c>
-      <c r="F262" s="9" t="n">
-        <v>18.688</v>
-      </c>
+      <c r="F262" s="10" t="n"/>
     </row>
     <row r="263" ht="18" customHeight="1">
       <c r="A263" s="3" t="n"/>
@@ -6352,9 +5894,7 @@
           <t>19.712 = 19.712</t>
         </is>
       </c>
-      <c r="F263" s="9" t="n">
-        <v>19.712</v>
-      </c>
+      <c r="F263" s="10" t="n"/>
     </row>
     <row r="264" ht="18" customHeight="1">
       <c r="A264" s="3" t="n"/>
@@ -6374,9 +5914,7 @@
           <t>3.961 = 3.961</t>
         </is>
       </c>
-      <c r="F264" s="9" t="n">
-        <v>3.961</v>
-      </c>
+      <c r="F264" s="10" t="n"/>
     </row>
     <row r="265" ht="18" customHeight="1">
       <c r="A265" s="3" t="n"/>
@@ -6396,9 +5934,7 @@
           <t>15.36 = 15.36</t>
         </is>
       </c>
-      <c r="F265" s="9" t="n">
-        <v>15.36</v>
-      </c>
+      <c r="F265" s="10" t="n"/>
     </row>
     <row r="266" ht="18" customHeight="1">
       <c r="A266" s="3" t="n"/>
@@ -6418,9 +5954,7 @@
           <t>4.608 = 4.608</t>
         </is>
       </c>
-      <c r="F266" s="9" t="n">
-        <v>4.608</v>
-      </c>
+      <c r="F266" s="10" t="n"/>
     </row>
     <row r="267" ht="18" customHeight="1">
       <c r="A267" s="3" t="n"/>
@@ -6440,9 +5974,7 @@
           <t>4.608 = 4.608</t>
         </is>
       </c>
-      <c r="F267" s="9" t="n">
-        <v>4.608</v>
-      </c>
+      <c r="F267" s="10" t="n"/>
     </row>
     <row r="268" ht="18" customHeight="1">
       <c r="A268" s="3" t="n"/>
@@ -6462,9 +5994,7 @@
           <t>3.495 = 3.495</t>
         </is>
       </c>
-      <c r="F268" s="9" t="n">
-        <v>3.495</v>
-      </c>
+      <c r="F268" s="10" t="n"/>
     </row>
     <row r="269" ht="46" customHeight="1">
       <c r="A269" s="3" t="n"/>
@@ -6480,9 +6010,7 @@
           <t>(3.24 + 2.16 + 11.598 + 3.584 + 18.031 + 3.584 + 0.504 + 4.788 + 2.457 + 2.142 + 19.712 + 2.394 + 2.394 + 2.394 + 2.457 + 2.394 + 4.914 + 18.688 + 3.165 + 19.712 + 7.168 + 2.11 + 7.689 + 2.394 + 2.394 + 2.394 + 2.457 + 2.394 + 4.914 + 18.688 + 3.165 + 19.712 + 7.168 + 2.11 + 7.689 + 4.788 + 4.788 + 2.457 + 2.142 + 18.688 + 19.712 + 3.961 + 15.36 + 4.608 + 4.608 + 3.495) ÷ 1000 = 0.307</t>
         </is>
       </c>
-      <c r="F269" s="10" t="n">
-        <v>0.307</v>
-      </c>
+      <c r="F269" s="10" t="n"/>
     </row>
     <row r="270" ht="18" customHeight="1">
       <c r="A270" s="3" t="n">
@@ -6509,7 +6037,7 @@
         </is>
       </c>
       <c r="F270" s="9" t="n">
-        <v>51.34</v>
+        <v>1.428</v>
       </c>
     </row>
     <row r="271" ht="18" customHeight="1">
@@ -6530,9 +6058,7 @@
           <t>34.428 = 34.428</t>
         </is>
       </c>
-      <c r="F271" s="9" t="n">
-        <v>34.428</v>
-      </c>
+      <c r="F271" s="10" t="n"/>
     </row>
     <row r="272" ht="18" customHeight="1">
       <c r="A272" s="3" t="n"/>
@@ -6552,9 +6078,7 @@
           <t>19.328 = 19.328</t>
         </is>
       </c>
-      <c r="F272" s="9" t="n">
-        <v>19.328</v>
-      </c>
+      <c r="F272" s="10" t="n"/>
     </row>
     <row r="273" ht="18" customHeight="1">
       <c r="A273" s="3" t="n"/>
@@ -6574,9 +6098,7 @@
           <t>6.454 = 6.454</t>
         </is>
       </c>
-      <c r="F273" s="9" t="n">
-        <v>6.454</v>
-      </c>
+      <c r="F273" s="10" t="n"/>
     </row>
     <row r="274" ht="18" customHeight="1">
       <c r="A274" s="3" t="n"/>
@@ -6596,9 +6118,7 @@
           <t>12.908 + 85.84 = 98.748</t>
         </is>
       </c>
-      <c r="F274" s="9" t="n">
-        <v>98.748</v>
-      </c>
+      <c r="F274" s="10" t="n"/>
     </row>
     <row r="275" ht="18" customHeight="1">
       <c r="A275" s="3" t="n"/>
@@ -6618,9 +6138,7 @@
           <t>6.454 + 42.92 = 49.374</t>
         </is>
       </c>
-      <c r="F275" s="9" t="n">
-        <v>49.374</v>
-      </c>
+      <c r="F275" s="10" t="n"/>
     </row>
     <row r="276" ht="18" customHeight="1">
       <c r="A276" s="3" t="n"/>
@@ -6640,9 +6158,7 @@
           <t>19.362 + 25.042 = 44.404</t>
         </is>
       </c>
-      <c r="F276" s="9" t="n">
-        <v>44.404</v>
-      </c>
+      <c r="F276" s="10" t="n"/>
     </row>
     <row r="277" ht="18" customHeight="1">
       <c r="A277" s="3" t="n"/>
@@ -6662,9 +6178,7 @@
           <t>45.178 = 45.178</t>
         </is>
       </c>
-      <c r="F277" s="9" t="n">
-        <v>45.178</v>
-      </c>
+      <c r="F277" s="10" t="n"/>
     </row>
     <row r="278" ht="18" customHeight="1">
       <c r="A278" s="3" t="n"/>
@@ -6684,9 +6198,7 @@
           <t>33.653 = 33.653</t>
         </is>
       </c>
-      <c r="F278" s="9" t="n">
-        <v>33.653</v>
-      </c>
+      <c r="F278" s="10" t="n"/>
     </row>
     <row r="279" ht="18" customHeight="1">
       <c r="A279" s="3" t="n"/>
@@ -6706,9 +6218,7 @@
           <t>6.454 + 36.54 = 42.994</t>
         </is>
       </c>
-      <c r="F279" s="9" t="n">
-        <v>42.994</v>
-      </c>
+      <c r="F279" s="10" t="n"/>
     </row>
     <row r="280" ht="18" customHeight="1">
       <c r="A280" s="3" t="n"/>
@@ -6728,9 +6238,7 @@
           <t>6.454 + 49.88 = 56.334</t>
         </is>
       </c>
-      <c r="F280" s="9" t="n">
-        <v>56.334</v>
-      </c>
+      <c r="F280" s="10" t="n"/>
     </row>
     <row r="281" ht="18" customHeight="1">
       <c r="A281" s="3" t="n"/>
@@ -6750,9 +6258,7 @@
           <t>6.454 + 46.4 = 52.854</t>
         </is>
       </c>
-      <c r="F281" s="9" t="n">
-        <v>52.854</v>
-      </c>
+      <c r="F281" s="10" t="n"/>
     </row>
     <row r="282" ht="18" customHeight="1">
       <c r="A282" s="3" t="n"/>
@@ -6772,9 +6278,7 @@
           <t>6.454 + 49.88 = 56.334</t>
         </is>
       </c>
-      <c r="F282" s="9" t="n">
-        <v>56.334</v>
-      </c>
+      <c r="F282" s="10" t="n"/>
     </row>
     <row r="283" ht="18" customHeight="1">
       <c r="A283" s="3" t="n"/>
@@ -6794,9 +6298,7 @@
           <t>6.454 + 46.4 = 52.854</t>
         </is>
       </c>
-      <c r="F283" s="9" t="n">
-        <v>52.854</v>
-      </c>
+      <c r="F283" s="10" t="n"/>
     </row>
     <row r="284" ht="18" customHeight="1">
       <c r="A284" s="3" t="n"/>
@@ -6816,9 +6318,7 @@
           <t>19.362 + 25.042 = 44.404</t>
         </is>
       </c>
-      <c r="F284" s="9" t="n">
-        <v>44.404</v>
-      </c>
+      <c r="F284" s="10" t="n"/>
     </row>
     <row r="285" ht="18" customHeight="1">
       <c r="A285" s="3" t="n"/>
@@ -6838,9 +6338,7 @@
           <t>47.944 = 47.944</t>
         </is>
       </c>
-      <c r="F285" s="9" t="n">
-        <v>47.944</v>
-      </c>
+      <c r="F285" s="10" t="n"/>
     </row>
     <row r="286" ht="18" customHeight="1">
       <c r="A286" s="3" t="n"/>
@@ -6860,9 +6358,7 @@
           <t>6.454 + 36.54 = 42.994</t>
         </is>
       </c>
-      <c r="F286" s="9" t="n">
-        <v>42.994</v>
-      </c>
+      <c r="F286" s="10" t="n"/>
     </row>
     <row r="287" ht="18" customHeight="1">
       <c r="A287" s="3" t="n"/>
@@ -6882,9 +6378,7 @@
           <t>6.454 + 49.88 = 56.334</t>
         </is>
       </c>
-      <c r="F287" s="9" t="n">
-        <v>56.334</v>
-      </c>
+      <c r="F287" s="10" t="n"/>
     </row>
     <row r="288" ht="18" customHeight="1">
       <c r="A288" s="3" t="n"/>
@@ -6904,9 +6398,7 @@
           <t>6.454 + 46.4 = 52.854</t>
         </is>
       </c>
-      <c r="F288" s="9" t="n">
-        <v>52.854</v>
-      </c>
+      <c r="F288" s="10" t="n"/>
     </row>
     <row r="289" ht="18" customHeight="1">
       <c r="A289" s="3" t="n"/>
@@ -6926,9 +6418,7 @@
           <t>6.454 + 49.88 = 56.334</t>
         </is>
       </c>
-      <c r="F289" s="9" t="n">
-        <v>56.334</v>
-      </c>
+      <c r="F289" s="10" t="n"/>
     </row>
     <row r="290" ht="18" customHeight="1">
       <c r="A290" s="3" t="n"/>
@@ -6948,9 +6438,7 @@
           <t>6.454 + 46.4 = 52.854</t>
         </is>
       </c>
-      <c r="F290" s="9" t="n">
-        <v>52.854</v>
-      </c>
+      <c r="F290" s="10" t="n"/>
     </row>
     <row r="291" ht="18" customHeight="1">
       <c r="A291" s="3" t="n"/>
@@ -6970,9 +6458,7 @@
           <t>19.362 + 25.042 = 44.404</t>
         </is>
       </c>
-      <c r="F291" s="9" t="n">
-        <v>44.404</v>
-      </c>
+      <c r="F291" s="10" t="n"/>
     </row>
     <row r="292" ht="18" customHeight="1">
       <c r="A292" s="3" t="n"/>
@@ -6992,9 +6478,7 @@
           <t>47.944 = 47.944</t>
         </is>
       </c>
-      <c r="F292" s="9" t="n">
-        <v>47.944</v>
-      </c>
+      <c r="F292" s="10" t="n"/>
     </row>
     <row r="293" ht="18" customHeight="1">
       <c r="A293" s="3" t="n"/>
@@ -7014,9 +6498,7 @@
           <t>6.454 + 36.54 + 6.454 + 36.54 = 85.988</t>
         </is>
       </c>
-      <c r="F293" s="9" t="n">
-        <v>85.988</v>
-      </c>
+      <c r="F293" s="10" t="n"/>
     </row>
     <row r="294" ht="18" customHeight="1">
       <c r="A294" s="3" t="n"/>
@@ -7036,9 +6518,7 @@
           <t>6.454 + 46.4 + 6.454 + 46.4 = 105.708</t>
         </is>
       </c>
-      <c r="F294" s="9" t="n">
-        <v>105.708</v>
-      </c>
+      <c r="F294" s="10" t="n"/>
     </row>
     <row r="295" ht="18" customHeight="1">
       <c r="A295" s="3" t="n"/>
@@ -7058,9 +6538,7 @@
           <t>6.454 + 49.88 = 56.334</t>
         </is>
       </c>
-      <c r="F295" s="9" t="n">
-        <v>56.334</v>
-      </c>
+      <c r="F295" s="10" t="n"/>
     </row>
     <row r="296" ht="18" customHeight="1">
       <c r="A296" s="3" t="n"/>
@@ -7080,9 +6558,7 @@
           <t>19.362 + 25.042 = 44.404</t>
         </is>
       </c>
-      <c r="F296" s="9" t="n">
-        <v>44.404</v>
-      </c>
+      <c r="F296" s="10" t="n"/>
     </row>
     <row r="297" ht="18" customHeight="1">
       <c r="A297" s="3" t="n"/>
@@ -7102,9 +6578,7 @@
           <t>45.178 = 45.178</t>
         </is>
       </c>
-      <c r="F297" s="9" t="n">
-        <v>45.178</v>
-      </c>
+      <c r="F297" s="10" t="n"/>
     </row>
     <row r="298" ht="32" customHeight="1">
       <c r="A298" s="3" t="n"/>
@@ -7120,9 +6594,7 @@
           <t>(51.34 + 34.428 + 19.328 + 6.454 + 98.748 + 49.374 + 44.404 + 45.178 + 33.653 + 42.994 + 56.334 + 52.854 + 56.334 + 52.854 + 44.404 + 47.944 + 42.994 + 56.334 + 52.854 + 56.334 + 52.854 + 44.404 + 47.944 + 85.988 + 105.708 + 56.334 + 44.404 + 45.178) ÷ 1000 = 1.428</t>
         </is>
       </c>
-      <c r="F298" s="10" t="n">
-        <v>1.428</v>
-      </c>
+      <c r="F298" s="10" t="n"/>
     </row>
     <row r="299" ht="18" customHeight="1">
       <c r="A299" s="3" t="n">
@@ -7149,7 +6621,7 @@
         </is>
       </c>
       <c r="F299" s="9" t="n">
-        <v>31.48</v>
+        <v>0.717</v>
       </c>
     </row>
     <row r="300" ht="18" customHeight="1">
@@ -7170,9 +6642,7 @@
           <t>21.294 = 21.294</t>
         </is>
       </c>
-      <c r="F300" s="9" t="n">
-        <v>21.294</v>
-      </c>
+      <c r="F300" s="10" t="n"/>
     </row>
     <row r="301" ht="18" customHeight="1">
       <c r="A301" s="3" t="n"/>
@@ -7192,9 +6662,7 @@
           <t>11.606 = 11.606</t>
         </is>
       </c>
-      <c r="F301" s="9" t="n">
-        <v>11.606</v>
-      </c>
+      <c r="F301" s="10" t="n"/>
     </row>
     <row r="302" ht="18" customHeight="1">
       <c r="A302" s="3" t="n"/>
@@ -7214,9 +6682,7 @@
           <t>24.304 + 24.082 = 48.386</t>
         </is>
       </c>
-      <c r="F302" s="9" t="n">
-        <v>48.386</v>
-      </c>
+      <c r="F302" s="10" t="n"/>
     </row>
     <row r="303" ht="18" customHeight="1">
       <c r="A303" s="3" t="n"/>
@@ -7236,9 +6702,7 @@
           <t>48.164 = 48.164</t>
         </is>
       </c>
-      <c r="F303" s="9" t="n">
-        <v>48.164</v>
-      </c>
+      <c r="F303" s="10" t="n"/>
     </row>
     <row r="304" ht="18" customHeight="1">
       <c r="A304" s="3" t="n"/>
@@ -7258,9 +6722,7 @@
           <t>24.082 = 24.082</t>
         </is>
       </c>
-      <c r="F304" s="9" t="n">
-        <v>24.082</v>
-      </c>
+      <c r="F304" s="10" t="n"/>
     </row>
     <row r="305" ht="18" customHeight="1">
       <c r="A305" s="3" t="n"/>
@@ -7280,9 +6742,7 @@
           <t>23.212 = 23.212</t>
         </is>
       </c>
-      <c r="F305" s="9" t="n">
-        <v>23.212</v>
-      </c>
+      <c r="F305" s="10" t="n"/>
     </row>
     <row r="306" ht="18" customHeight="1">
       <c r="A306" s="3" t="n"/>
@@ -7302,9 +6762,7 @@
           <t>24.082 = 24.082</t>
         </is>
       </c>
-      <c r="F306" s="9" t="n">
-        <v>24.082</v>
-      </c>
+      <c r="F306" s="10" t="n"/>
     </row>
     <row r="307" ht="18" customHeight="1">
       <c r="A307" s="3" t="n"/>
@@ -7324,9 +6782,7 @@
           <t>24.082 = 24.082</t>
         </is>
       </c>
-      <c r="F307" s="9" t="n">
-        <v>24.082</v>
-      </c>
+      <c r="F307" s="10" t="n"/>
     </row>
     <row r="308" ht="18" customHeight="1">
       <c r="A308" s="3" t="n"/>
@@ -7346,9 +6802,7 @@
           <t>24.082 = 24.082</t>
         </is>
       </c>
-      <c r="F308" s="9" t="n">
-        <v>24.082</v>
-      </c>
+      <c r="F308" s="10" t="n"/>
     </row>
     <row r="309" ht="18" customHeight="1">
       <c r="A309" s="3" t="n"/>
@@ -7368,9 +6822,7 @@
           <t>24.082 + 2.718 = 26.8</t>
         </is>
       </c>
-      <c r="F309" s="9" t="n">
-        <v>26.8</v>
-      </c>
+      <c r="F309" s="10" t="n"/>
     </row>
     <row r="310" ht="18" customHeight="1">
       <c r="A310" s="3" t="n"/>
@@ -7390,9 +6842,7 @@
           <t>24.082 = 24.082</t>
         </is>
       </c>
-      <c r="F310" s="9" t="n">
-        <v>24.082</v>
-      </c>
+      <c r="F310" s="10" t="n"/>
     </row>
     <row r="311" ht="18" customHeight="1">
       <c r="A311" s="3" t="n"/>
@@ -7412,9 +6862,7 @@
           <t>55.376 = 55.376</t>
         </is>
       </c>
-      <c r="F311" s="9" t="n">
-        <v>55.376</v>
-      </c>
+      <c r="F311" s="10" t="n"/>
     </row>
     <row r="312" ht="18" customHeight="1">
       <c r="A312" s="3" t="n"/>
@@ -7434,9 +6882,7 @@
           <t>24.082 = 24.082</t>
         </is>
       </c>
-      <c r="F312" s="9" t="n">
-        <v>24.082</v>
-      </c>
+      <c r="F312" s="10" t="n"/>
     </row>
     <row r="313" ht="18" customHeight="1">
       <c r="A313" s="3" t="n"/>
@@ -7456,9 +6902,7 @@
           <t>24.082 = 24.082</t>
         </is>
       </c>
-      <c r="F313" s="9" t="n">
-        <v>24.082</v>
-      </c>
+      <c r="F313" s="10" t="n"/>
     </row>
     <row r="314" ht="18" customHeight="1">
       <c r="A314" s="3" t="n"/>
@@ -7478,9 +6922,7 @@
           <t>24.082 = 24.082</t>
         </is>
       </c>
-      <c r="F314" s="9" t="n">
-        <v>24.082</v>
-      </c>
+      <c r="F314" s="10" t="n"/>
     </row>
     <row r="315" ht="18" customHeight="1">
       <c r="A315" s="3" t="n"/>
@@ -7500,9 +6942,7 @@
           <t>24.082 + 2.718 = 26.8</t>
         </is>
       </c>
-      <c r="F315" s="9" t="n">
-        <v>26.8</v>
-      </c>
+      <c r="F315" s="10" t="n"/>
     </row>
     <row r="316" ht="18" customHeight="1">
       <c r="A316" s="3" t="n"/>
@@ -7522,9 +6962,7 @@
           <t>24.082 = 24.082</t>
         </is>
       </c>
-      <c r="F316" s="9" t="n">
-        <v>24.082</v>
-      </c>
+      <c r="F316" s="10" t="n"/>
     </row>
     <row r="317" ht="18" customHeight="1">
       <c r="A317" s="3" t="n"/>
@@ -7544,9 +6982,7 @@
           <t>55.376 = 55.376</t>
         </is>
       </c>
-      <c r="F317" s="9" t="n">
-        <v>55.376</v>
-      </c>
+      <c r="F317" s="10" t="n"/>
     </row>
     <row r="318" ht="18" customHeight="1">
       <c r="A318" s="3" t="n"/>
@@ -7566,9 +7002,7 @@
           <t>24.082 + 2.718 + 24.082 = 50.882</t>
         </is>
       </c>
-      <c r="F318" s="9" t="n">
-        <v>50.882</v>
-      </c>
+      <c r="F318" s="10" t="n"/>
     </row>
     <row r="319" ht="18" customHeight="1">
       <c r="A319" s="3" t="n"/>
@@ -7588,9 +7022,7 @@
           <t>24.082 + 2.718 + 24.082 = 50.882</t>
         </is>
       </c>
-      <c r="F319" s="9" t="n">
-        <v>50.882</v>
-      </c>
+      <c r="F319" s="10" t="n"/>
     </row>
     <row r="320" ht="18" customHeight="1">
       <c r="A320" s="3" t="n"/>
@@ -7610,9 +7042,7 @@
           <t>24.082 + 2.718 = 26.8</t>
         </is>
       </c>
-      <c r="F320" s="9" t="n">
-        <v>26.8</v>
-      </c>
+      <c r="F320" s="10" t="n"/>
     </row>
     <row r="321" ht="18" customHeight="1">
       <c r="A321" s="3" t="n"/>
@@ -7632,9 +7062,7 @@
           <t>23.212 = 23.212</t>
         </is>
       </c>
-      <c r="F321" s="9" t="n">
-        <v>23.212</v>
-      </c>
+      <c r="F321" s="10" t="n"/>
     </row>
     <row r="322" ht="32" customHeight="1">
       <c r="A322" s="3" t="n"/>
@@ -7650,9 +7078,7 @@
           <t>(31.48 + 21.294 + 11.606 + 48.386 + 48.164 + 24.082 + 23.212 + 24.082 + 24.082 + 24.082 + 26.8 + 24.082 + 55.376 + 24.082 + 24.082 + 24.082 + 26.8 + 24.082 + 55.376 + 50.882 + 50.882 + 26.8 + 23.212) ÷ 1000 = 0.717</t>
         </is>
       </c>
-      <c r="F322" s="10" t="n">
-        <v>0.717</v>
-      </c>
+      <c r="F322" s="10" t="n"/>
     </row>
     <row r="323" ht="18" customHeight="1">
       <c r="A323" s="3" t="n">
@@ -7679,7 +7105,7 @@
         </is>
       </c>
       <c r="F323" s="9" t="n">
-        <v>8.619999999999999</v>
+        <v>0.134</v>
       </c>
     </row>
     <row r="324" ht="18" customHeight="1">
@@ -7700,9 +7126,7 @@
           <t>12.13 = 12.13</t>
         </is>
       </c>
-      <c r="F324" s="9" t="n">
-        <v>12.13</v>
-      </c>
+      <c r="F324" s="10" t="n"/>
     </row>
     <row r="325" ht="18" customHeight="1">
       <c r="A325" s="3" t="n"/>
@@ -7722,9 +7146,7 @@
           <t>6.322 + 7.755 = 14.077</t>
         </is>
       </c>
-      <c r="F325" s="9" t="n">
-        <v>14.077</v>
-      </c>
+      <c r="F325" s="10" t="n"/>
     </row>
     <row r="326" ht="18" customHeight="1">
       <c r="A326" s="3" t="n"/>
@@ -7744,9 +7166,7 @@
           <t>9.588 + 9.104 = 18.692</t>
         </is>
       </c>
-      <c r="F326" s="9" t="n">
-        <v>18.692</v>
-      </c>
+      <c r="F326" s="10" t="n"/>
     </row>
     <row r="327" ht="18" customHeight="1">
       <c r="A327" s="3" t="n"/>
@@ -7766,9 +7186,7 @@
           <t>8.62 = 8.62</t>
         </is>
       </c>
-      <c r="F327" s="9" t="n">
-        <v>8.619999999999999</v>
-      </c>
+      <c r="F327" s="10" t="n"/>
     </row>
     <row r="328" ht="18" customHeight="1">
       <c r="A328" s="3" t="n"/>
@@ -7788,9 +7206,7 @@
           <t>12.13 = 12.13</t>
         </is>
       </c>
-      <c r="F328" s="9" t="n">
-        <v>12.13</v>
-      </c>
+      <c r="F328" s="10" t="n"/>
     </row>
     <row r="329" ht="18" customHeight="1">
       <c r="A329" s="3" t="n"/>
@@ -7810,9 +7226,7 @@
           <t>6.322 + 7.755 = 14.077</t>
         </is>
       </c>
-      <c r="F329" s="9" t="n">
-        <v>14.077</v>
-      </c>
+      <c r="F329" s="10" t="n"/>
     </row>
     <row r="330" ht="18" customHeight="1">
       <c r="A330" s="3" t="n"/>
@@ -7832,9 +7246,7 @@
           <t>9.104 + 9.588 = 18.692</t>
         </is>
       </c>
-      <c r="F330" s="9" t="n">
-        <v>18.692</v>
-      </c>
+      <c r="F330" s="10" t="n"/>
     </row>
     <row r="331" ht="18" customHeight="1">
       <c r="A331" s="3" t="n"/>
@@ -7854,9 +7266,7 @@
           <t>9.588 = 9.588</t>
         </is>
       </c>
-      <c r="F331" s="9" t="n">
-        <v>9.587999999999999</v>
-      </c>
+      <c r="F331" s="10" t="n"/>
     </row>
     <row r="332" ht="18" customHeight="1">
       <c r="A332" s="3" t="n"/>
@@ -7876,9 +7286,7 @@
           <t>8.757 + 8.241 = 16.998</t>
         </is>
       </c>
-      <c r="F332" s="9" t="n">
-        <v>16.998</v>
-      </c>
+      <c r="F332" s="10" t="n"/>
     </row>
     <row r="333" ht="18" customHeight="1">
       <c r="A333" s="3" t="n"/>
@@ -7894,9 +7302,7 @@
           <t>(8.62 + 12.13 + 14.077 + 18.692 + 8.62 + 12.13 + 14.077 + 18.692 + 9.588 + 16.998) ÷ 1000 = 0.134</t>
         </is>
       </c>
-      <c r="F333" s="10" t="n">
-        <v>0.134</v>
-      </c>
+      <c r="F333" s="10" t="n"/>
     </row>
     <row r="334" ht="18" customHeight="1">
       <c r="A334" s="3" t="n">
@@ -7923,7 +7329,7 @@
         </is>
       </c>
       <c r="F334" s="9" t="n">
-        <v>90.342</v>
+        <v>2.347</v>
       </c>
     </row>
     <row r="335" ht="18" customHeight="1">
@@ -7944,9 +7350,7 @@
           <t>38.658 = 38.658</t>
         </is>
       </c>
-      <c r="F335" s="9" t="n">
-        <v>38.658</v>
-      </c>
+      <c r="F335" s="10" t="n"/>
     </row>
     <row r="336" ht="18" customHeight="1">
       <c r="A336" s="3" t="n"/>
@@ -7966,9 +7370,7 @@
           <t>152.658 = 152.658</t>
         </is>
       </c>
-      <c r="F336" s="9" t="n">
-        <v>152.658</v>
-      </c>
+      <c r="F336" s="10" t="n"/>
     </row>
     <row r="337" ht="18" customHeight="1">
       <c r="A337" s="3" t="n"/>
@@ -7988,9 +7390,7 @@
           <t>12.728 + 16.395 = 29.123</t>
         </is>
       </c>
-      <c r="F337" s="9" t="n">
-        <v>29.123</v>
-      </c>
+      <c r="F337" s="10" t="n"/>
     </row>
     <row r="338" ht="18" customHeight="1">
       <c r="A338" s="3" t="n"/>
@@ -8010,9 +7410,7 @@
           <t>24.222 + 24.321 + 8.428 = 56.971</t>
         </is>
       </c>
-      <c r="F338" s="9" t="n">
-        <v>56.971</v>
-      </c>
+      <c r="F338" s="10" t="n"/>
     </row>
     <row r="339" ht="18" customHeight="1">
       <c r="A339" s="3" t="n"/>
@@ -8032,9 +7430,7 @@
           <t>76.377 = 76.377</t>
         </is>
       </c>
-      <c r="F339" s="9" t="n">
-        <v>76.377</v>
-      </c>
+      <c r="F339" s="10" t="n"/>
     </row>
     <row r="340" ht="18" customHeight="1">
       <c r="A340" s="3" t="n"/>
@@ -8054,9 +7450,7 @@
           <t>152.754 = 152.754</t>
         </is>
       </c>
-      <c r="F340" s="9" t="n">
-        <v>152.754</v>
-      </c>
+      <c r="F340" s="10" t="n"/>
     </row>
     <row r="341" ht="18" customHeight="1">
       <c r="A341" s="3" t="n"/>
@@ -8076,9 +7470,7 @@
           <t>76.377 + 74.106 = 150.483</t>
         </is>
       </c>
-      <c r="F341" s="9" t="n">
-        <v>150.483</v>
-      </c>
+      <c r="F341" s="10" t="n"/>
     </row>
     <row r="342" ht="18" customHeight="1">
       <c r="A342" s="3" t="n"/>
@@ -8098,9 +7490,7 @@
           <t>7.534 = 7.534</t>
         </is>
       </c>
-      <c r="F342" s="9" t="n">
-        <v>7.534</v>
-      </c>
+      <c r="F342" s="10" t="n"/>
     </row>
     <row r="343" ht="18" customHeight="1">
       <c r="A343" s="3" t="n"/>
@@ -8120,9 +7510,7 @@
           <t>15.068 = 15.068</t>
         </is>
       </c>
-      <c r="F343" s="9" t="n">
-        <v>15.068</v>
-      </c>
+      <c r="F343" s="10" t="n"/>
     </row>
     <row r="344" ht="18" customHeight="1">
       <c r="A344" s="3" t="n"/>
@@ -8142,9 +7530,7 @@
           <t>7.534 = 7.534</t>
         </is>
       </c>
-      <c r="F344" s="9" t="n">
-        <v>7.534</v>
-      </c>
+      <c r="F344" s="10" t="n"/>
     </row>
     <row r="345" ht="18" customHeight="1">
       <c r="A345" s="3" t="n"/>
@@ -8164,9 +7550,7 @@
           <t>15.068 = 15.068</t>
         </is>
       </c>
-      <c r="F345" s="9" t="n">
-        <v>15.068</v>
-      </c>
+      <c r="F345" s="10" t="n"/>
     </row>
     <row r="346" ht="18" customHeight="1">
       <c r="A346" s="3" t="n"/>
@@ -8186,9 +7570,7 @@
           <t>7.534 = 7.534</t>
         </is>
       </c>
-      <c r="F346" s="9" t="n">
-        <v>7.534</v>
-      </c>
+      <c r="F346" s="10" t="n"/>
     </row>
     <row r="347" ht="18" customHeight="1">
       <c r="A347" s="3" t="n"/>
@@ -8208,9 +7590,7 @@
           <t>24.222 + 24.321 + 8.428 = 56.971</t>
         </is>
       </c>
-      <c r="F347" s="9" t="n">
-        <v>56.971</v>
-      </c>
+      <c r="F347" s="10" t="n"/>
     </row>
     <row r="348" ht="18" customHeight="1">
       <c r="A348" s="3" t="n"/>
@@ -8230,9 +7610,7 @@
           <t>24.201 + 18.276 + 19.125 + 6.194 = 67.796</t>
         </is>
       </c>
-      <c r="F348" s="9" t="n">
-        <v>67.79600000000001</v>
-      </c>
+      <c r="F348" s="10" t="n"/>
     </row>
     <row r="349" ht="18" customHeight="1">
       <c r="A349" s="3" t="n"/>
@@ -8252,9 +7630,7 @@
           <t>152.754 = 152.754</t>
         </is>
       </c>
-      <c r="F349" s="9" t="n">
-        <v>152.754</v>
-      </c>
+      <c r="F349" s="10" t="n"/>
     </row>
     <row r="350" ht="18" customHeight="1">
       <c r="A350" s="3" t="n"/>
@@ -8274,9 +7650,7 @@
           <t>76.377 + 74.106 = 150.483</t>
         </is>
       </c>
-      <c r="F350" s="9" t="n">
-        <v>150.483</v>
-      </c>
+      <c r="F350" s="10" t="n"/>
     </row>
     <row r="351" ht="18" customHeight="1">
       <c r="A351" s="3" t="n"/>
@@ -8296,9 +7670,7 @@
           <t>6.194 = 6.194</t>
         </is>
       </c>
-      <c r="F351" s="9" t="n">
-        <v>6.194</v>
-      </c>
+      <c r="F351" s="10" t="n"/>
     </row>
     <row r="352" ht="18" customHeight="1">
       <c r="A352" s="3" t="n"/>
@@ -8318,9 +7690,7 @@
           <t>7.534 = 7.534</t>
         </is>
       </c>
-      <c r="F352" s="9" t="n">
-        <v>7.534</v>
-      </c>
+      <c r="F352" s="10" t="n"/>
     </row>
     <row r="353" ht="18" customHeight="1">
       <c r="A353" s="3" t="n"/>
@@ -8340,9 +7710,7 @@
           <t>15.068 = 15.068</t>
         </is>
       </c>
-      <c r="F353" s="9" t="n">
-        <v>15.068</v>
-      </c>
+      <c r="F353" s="10" t="n"/>
     </row>
     <row r="354" ht="18" customHeight="1">
       <c r="A354" s="3" t="n"/>
@@ -8362,9 +7730,7 @@
           <t>7.534 = 7.534</t>
         </is>
       </c>
-      <c r="F354" s="9" t="n">
-        <v>7.534</v>
-      </c>
+      <c r="F354" s="10" t="n"/>
     </row>
     <row r="355" ht="18" customHeight="1">
       <c r="A355" s="3" t="n"/>
@@ -8384,9 +7750,7 @@
           <t>15.068 = 15.068</t>
         </is>
       </c>
-      <c r="F355" s="9" t="n">
-        <v>15.068</v>
-      </c>
+      <c r="F355" s="10" t="n"/>
     </row>
     <row r="356" ht="18" customHeight="1">
       <c r="A356" s="3" t="n"/>
@@ -8406,9 +7770,7 @@
           <t>7.534 = 7.534</t>
         </is>
       </c>
-      <c r="F356" s="9" t="n">
-        <v>7.534</v>
-      </c>
+      <c r="F356" s="10" t="n"/>
     </row>
     <row r="357" ht="18" customHeight="1">
       <c r="A357" s="3" t="n"/>
@@ -8428,9 +7790,7 @@
           <t>24.222 + 24.321 + 8.428 = 56.971</t>
         </is>
       </c>
-      <c r="F357" s="9" t="n">
-        <v>56.971</v>
-      </c>
+      <c r="F357" s="10" t="n"/>
     </row>
     <row r="358" ht="18" customHeight="1">
       <c r="A358" s="3" t="n"/>
@@ -8450,9 +7810,7 @@
           <t>24.201 + 18.276 + 19.125 + 6.194 = 67.796</t>
         </is>
       </c>
-      <c r="F358" s="9" t="n">
-        <v>67.79600000000001</v>
-      </c>
+      <c r="F358" s="10" t="n"/>
     </row>
     <row r="359" ht="18" customHeight="1">
       <c r="A359" s="3" t="n"/>
@@ -8472,9 +7830,7 @@
           <t>152.754 = 152.754</t>
         </is>
       </c>
-      <c r="F359" s="9" t="n">
-        <v>152.754</v>
-      </c>
+      <c r="F359" s="10" t="n"/>
     </row>
     <row r="360" ht="18" customHeight="1">
       <c r="A360" s="3" t="n"/>
@@ -8494,9 +7850,7 @@
           <t>76.377 + 74.106 = 150.483</t>
         </is>
       </c>
-      <c r="F360" s="9" t="n">
-        <v>150.483</v>
-      </c>
+      <c r="F360" s="10" t="n"/>
     </row>
     <row r="361" ht="18" customHeight="1">
       <c r="A361" s="3" t="n"/>
@@ -8516,9 +7870,7 @@
           <t>6.194 = 6.194</t>
         </is>
       </c>
-      <c r="F361" s="9" t="n">
-        <v>6.194</v>
-      </c>
+      <c r="F361" s="10" t="n"/>
     </row>
     <row r="362" ht="18" customHeight="1">
       <c r="A362" s="3" t="n"/>
@@ -8538,9 +7890,7 @@
           <t>7.534 + 7.534 = 15.068</t>
         </is>
       </c>
-      <c r="F362" s="9" t="n">
-        <v>15.068</v>
-      </c>
+      <c r="F362" s="10" t="n"/>
     </row>
     <row r="363" ht="18" customHeight="1">
       <c r="A363" s="3" t="n"/>
@@ -8560,9 +7910,7 @@
           <t>7.534 + 7.534 = 15.068</t>
         </is>
       </c>
-      <c r="F363" s="9" t="n">
-        <v>15.068</v>
-      </c>
+      <c r="F363" s="10" t="n"/>
     </row>
     <row r="364" ht="18" customHeight="1">
       <c r="A364" s="3" t="n"/>
@@ -8582,9 +7930,7 @@
           <t>15.068 = 15.068</t>
         </is>
       </c>
-      <c r="F364" s="9" t="n">
-        <v>15.068</v>
-      </c>
+      <c r="F364" s="10" t="n"/>
     </row>
     <row r="365" ht="18" customHeight="1">
       <c r="A365" s="3" t="n"/>
@@ -8604,9 +7950,7 @@
           <t>24.222 + 24.321 + 8.428 = 56.971</t>
         </is>
       </c>
-      <c r="F365" s="9" t="n">
-        <v>56.971</v>
-      </c>
+      <c r="F365" s="10" t="n"/>
     </row>
     <row r="366" ht="18" customHeight="1">
       <c r="A366" s="3" t="n"/>
@@ -8626,9 +7970,7 @@
           <t>76.377 = 76.377</t>
         </is>
       </c>
-      <c r="F366" s="9" t="n">
-        <v>76.377</v>
-      </c>
+      <c r="F366" s="10" t="n"/>
     </row>
     <row r="367" ht="18" customHeight="1">
       <c r="A367" s="3" t="n"/>
@@ -8648,9 +7990,7 @@
           <t>77.655 + 76.377 = 154.032</t>
         </is>
       </c>
-      <c r="F367" s="9" t="n">
-        <v>154.032</v>
-      </c>
+      <c r="F367" s="10" t="n"/>
     </row>
     <row r="368" ht="18" customHeight="1">
       <c r="A368" s="3" t="n"/>
@@ -8670,9 +8010,7 @@
           <t>50.918 + 49.404 = 100.322</t>
         </is>
       </c>
-      <c r="F368" s="9" t="n">
-        <v>100.322</v>
-      </c>
+      <c r="F368" s="10" t="n"/>
     </row>
     <row r="369" ht="18" customHeight="1">
       <c r="A369" s="3" t="n"/>
@@ -8692,9 +8030,7 @@
           <t>16.752 = 16.752</t>
         </is>
       </c>
-      <c r="F369" s="9" t="n">
-        <v>16.752</v>
-      </c>
+      <c r="F369" s="10" t="n"/>
     </row>
     <row r="370" ht="18" customHeight="1">
       <c r="A370" s="3" t="n"/>
@@ -8714,9 +8050,7 @@
           <t>60.261 + 57.99 = 118.251</t>
         </is>
       </c>
-      <c r="F370" s="9" t="n">
-        <v>118.251</v>
-      </c>
+      <c r="F370" s="10" t="n"/>
     </row>
     <row r="371" ht="18" customHeight="1">
       <c r="A371" s="3" t="n"/>
@@ -8736,9 +8070,7 @@
           <t>11.892 + 17.073 = 28.965</t>
         </is>
       </c>
-      <c r="F371" s="9" t="n">
-        <v>28.965</v>
-      </c>
+      <c r="F371" s="10" t="n"/>
     </row>
     <row r="372" ht="18" customHeight="1">
       <c r="A372" s="3" t="n"/>
@@ -8758,9 +8090,7 @@
           <t>11.892 + 17.073 = 28.965</t>
         </is>
       </c>
-      <c r="F372" s="9" t="n">
-        <v>28.965</v>
-      </c>
+      <c r="F372" s="10" t="n"/>
     </row>
     <row r="373" ht="46" customHeight="1">
       <c r="A373" s="3" t="n"/>
@@ -8776,9 +8106,7 @@
           <t>(90.342 + 38.658 + 152.658 + 29.123 + 56.971 + 76.377 + 152.754 + 150.483 + 7.534 + 15.068 + 7.534 + 15.068 + 7.534 + 56.971 + 67.796 + 152.754 + 150.483 + 6.194 + 7.534 + 15.068 + 7.534 + 15.068 + 7.534 + 56.971 + 67.796 + 152.754 + 150.483 + 6.194 + 15.068 + 15.068 + 15.068 + 56.971 + 76.377 + 154.032 + 100.322 + 16.752 + 118.251 + 28.965 + 28.965) ÷ 1000 = 2.347</t>
         </is>
       </c>
-      <c r="F373" s="10" t="n">
-        <v>2.347</v>
-      </c>
+      <c r="F373" s="10" t="n"/>
     </row>
     <row r="374" ht="18" customHeight="1">
       <c r="A374" s="3" t="n">
@@ -8805,7 +8133,7 @@
         </is>
       </c>
       <c r="F374" s="9" t="n">
-        <v>327.572</v>
+        <v>2.172</v>
       </c>
     </row>
     <row r="375" ht="18" customHeight="1">
@@ -8826,9 +8154,7 @@
           <t>19.44 + 151.98 = 171.42</t>
         </is>
       </c>
-      <c r="F375" s="9" t="n">
-        <v>171.42</v>
-      </c>
+      <c r="F375" s="10" t="n"/>
     </row>
     <row r="376" ht="18" customHeight="1">
       <c r="A376" s="3" t="n"/>
@@ -8848,9 +8174,7 @@
           <t>41.262 = 41.262</t>
         </is>
       </c>
-      <c r="F376" s="9" t="n">
-        <v>41.262</v>
-      </c>
+      <c r="F376" s="10" t="n"/>
     </row>
     <row r="377" ht="18" customHeight="1">
       <c r="A377" s="3" t="n"/>
@@ -8870,9 +8194,7 @@
           <t>64.66 + 3.866 + 12.4 + 4.7 + 3.166 = 88.792</t>
         </is>
       </c>
-      <c r="F377" s="9" t="n">
-        <v>88.792</v>
-      </c>
+      <c r="F377" s="10" t="n"/>
     </row>
     <row r="378" ht="18" customHeight="1">
       <c r="A378" s="3" t="n"/>
@@ -8892,9 +8214,7 @@
           <t>55.944 + 7.658 + 13.94 + 16.6 + 4.816 + 39.612 = 138.57</t>
         </is>
       </c>
-      <c r="F378" s="9" t="n">
-        <v>138.57</v>
-      </c>
+      <c r="F378" s="10" t="n"/>
     </row>
     <row r="379" ht="18" customHeight="1">
       <c r="A379" s="3" t="n"/>
@@ -8914,9 +8234,7 @@
           <t>41.262 = 41.262</t>
         </is>
       </c>
-      <c r="F379" s="9" t="n">
-        <v>41.262</v>
-      </c>
+      <c r="F379" s="10" t="n"/>
     </row>
     <row r="380" ht="18" customHeight="1">
       <c r="A380" s="3" t="n"/>
@@ -8936,9 +8254,7 @@
           <t>41.262 = 41.262</t>
         </is>
       </c>
-      <c r="F380" s="9" t="n">
-        <v>41.262</v>
-      </c>
+      <c r="F380" s="10" t="n"/>
     </row>
     <row r="381" ht="18" customHeight="1">
       <c r="A381" s="3" t="n"/>
@@ -8958,9 +8274,7 @@
           <t>55.944 + 7.658 + 13.94 + 8.3 + 12.8 + 41.412 + 4.816 + 39.612 = 184.482</t>
         </is>
       </c>
-      <c r="F381" s="9" t="n">
-        <v>184.482</v>
-      </c>
+      <c r="F381" s="10" t="n"/>
     </row>
     <row r="382" ht="18" customHeight="1">
       <c r="A382" s="3" t="n"/>
@@ -8980,9 +8294,7 @@
           <t>21.492 + 20.292 = 41.784</t>
         </is>
       </c>
-      <c r="F382" s="9" t="n">
-        <v>41.784</v>
-      </c>
+      <c r="F382" s="10" t="n"/>
     </row>
     <row r="383" ht="18" customHeight="1">
       <c r="A383" s="3" t="n"/>
@@ -9002,9 +8314,7 @@
           <t>55.944 + 7.658 + 13.94 + 16.6 + 4.816 + 39.612 = 138.57</t>
         </is>
       </c>
-      <c r="F383" s="9" t="n">
-        <v>138.57</v>
-      </c>
+      <c r="F383" s="10" t="n"/>
     </row>
     <row r="384" ht="18" customHeight="1">
       <c r="A384" s="3" t="n"/>
@@ -9024,9 +8334,7 @@
           <t>41.262 = 41.262</t>
         </is>
       </c>
-      <c r="F384" s="9" t="n">
-        <v>41.262</v>
-      </c>
+      <c r="F384" s="10" t="n"/>
     </row>
     <row r="385" ht="18" customHeight="1">
       <c r="A385" s="3" t="n"/>
@@ -9046,9 +8354,7 @@
           <t>41.262 = 41.262</t>
         </is>
       </c>
-      <c r="F385" s="9" t="n">
-        <v>41.262</v>
-      </c>
+      <c r="F385" s="10" t="n"/>
     </row>
     <row r="386" ht="18" customHeight="1">
       <c r="A386" s="3" t="n"/>
@@ -9068,9 +8374,7 @@
           <t>55.944 + 7.658 + 13.94 + 8.3 + 12.8 + 41.412 + 4.816 + 39.612 = 184.482</t>
         </is>
       </c>
-      <c r="F386" s="9" t="n">
-        <v>184.482</v>
-      </c>
+      <c r="F386" s="10" t="n"/>
     </row>
     <row r="387" ht="18" customHeight="1">
       <c r="A387" s="3" t="n"/>
@@ -9090,9 +8394,7 @@
           <t>20.292 + 21.492 = 41.784</t>
         </is>
       </c>
-      <c r="F387" s="9" t="n">
-        <v>41.784</v>
-      </c>
+      <c r="F387" s="10" t="n"/>
     </row>
     <row r="388" ht="18" customHeight="1">
       <c r="A388" s="3" t="n"/>
@@ -9112,9 +8414,7 @@
           <t>56.964 + 15.136 + 16.6 + 75.99 + 56.964 + 15.136 + 9.72 + 16.6 + 75.99 = 339.1</t>
         </is>
       </c>
-      <c r="F388" s="9" t="n">
-        <v>339.1</v>
-      </c>
+      <c r="F388" s="10" t="n"/>
     </row>
     <row r="389" ht="18" customHeight="1">
       <c r="A389" s="3" t="n"/>
@@ -9134,9 +8434,7 @@
           <t>75.99 + 9.72 + 75.99 = 161.7</t>
         </is>
       </c>
-      <c r="F389" s="9" t="n">
-        <v>161.7</v>
-      </c>
+      <c r="F389" s="10" t="n"/>
     </row>
     <row r="390" ht="18" customHeight="1">
       <c r="A390" s="3" t="n"/>
@@ -9156,9 +8454,7 @@
           <t>75.99 = 75.99</t>
         </is>
       </c>
-      <c r="F390" s="9" t="n">
-        <v>75.98999999999999</v>
-      </c>
+      <c r="F390" s="10" t="n"/>
     </row>
     <row r="391" ht="18" customHeight="1">
       <c r="A391" s="3" t="n"/>
@@ -9178,9 +8474,7 @@
           <t>65.5 + 6.2 = 71.7</t>
         </is>
       </c>
-      <c r="F391" s="9" t="n">
-        <v>71.7</v>
-      </c>
+      <c r="F391" s="10" t="n"/>
     </row>
     <row r="392" ht="32" customHeight="1">
       <c r="A392" s="3" t="n"/>
@@ -9196,9 +8490,7 @@
           <t>(327.572 + 171.42 + 41.262 + 88.792 + 138.57 + 41.262 + 41.262 + 184.482 + 41.784 + 138.57 + 41.262 + 41.262 + 184.482 + 41.784 + 339.1 + 161.7 + 75.99 + 71.7) ÷ 1000 = 2.172</t>
         </is>
       </c>
-      <c r="F392" s="10" t="n">
-        <v>2.172</v>
-      </c>
+      <c r="F392" s="10" t="n"/>
     </row>
     <row r="393" ht="18" customHeight="1">
       <c r="A393" s="3" t="n">
@@ -9225,7 +8517,7 @@
         </is>
       </c>
       <c r="F393" s="9" t="n">
-        <v>286.602</v>
+        <v>2.778</v>
       </c>
     </row>
     <row r="394" ht="18" customHeight="1">
@@ -9246,9 +8538,7 @@
           <t>188.316 = 188.316</t>
         </is>
       </c>
-      <c r="F394" s="9" t="n">
-        <v>188.316</v>
-      </c>
+      <c r="F394" s="10" t="n"/>
     </row>
     <row r="395" ht="18" customHeight="1">
       <c r="A395" s="3" t="n"/>
@@ -9268,9 +8558,7 @@
           <t>54.93 + 54.702 = 109.632</t>
         </is>
       </c>
-      <c r="F395" s="9" t="n">
-        <v>109.632</v>
-      </c>
+      <c r="F395" s="10" t="n"/>
     </row>
     <row r="396" ht="18" customHeight="1">
       <c r="A396" s="3" t="n"/>
@@ -9290,9 +8578,7 @@
           <t>5.692 + 109.776 + 20.668 = 136.136</t>
         </is>
       </c>
-      <c r="F396" s="9" t="n">
-        <v>136.136</v>
-      </c>
+      <c r="F396" s="10" t="n"/>
     </row>
     <row r="397" ht="18" customHeight="1">
       <c r="A397" s="3" t="n"/>
@@ -9312,9 +8598,7 @@
           <t>69.318 + 18.476 + 10.581 + 16.362 + 5.99 + 49.41 = 170.137</t>
         </is>
       </c>
-      <c r="F397" s="9" t="n">
-        <v>170.137</v>
-      </c>
+      <c r="F397" s="10" t="n"/>
     </row>
     <row r="398" ht="18" customHeight="1">
       <c r="A398" s="3" t="n"/>
@@ -9334,9 +8618,7 @@
           <t>80.112 + 22.31 + 6.523 = 108.945</t>
         </is>
       </c>
-      <c r="F398" s="9" t="n">
-        <v>108.945</v>
-      </c>
+      <c r="F398" s="10" t="n"/>
     </row>
     <row r="399" ht="18" customHeight="1">
       <c r="A399" s="3" t="n"/>
@@ -9356,9 +8638,7 @@
           <t>2.846 + 54.888 + 10.334 + 15.996 + 5.99 + 49.41 = 139.464</t>
         </is>
       </c>
-      <c r="F399" s="9" t="n">
-        <v>139.464</v>
-      </c>
+      <c r="F399" s="10" t="n"/>
     </row>
     <row r="400" ht="18" customHeight="1">
       <c r="A400" s="3" t="n"/>
@@ -9378,9 +8658,7 @@
           <t>2.846 + 54.888 + 10.334 + 15.996 + 5.99 + 49.41 = 139.464</t>
         </is>
       </c>
-      <c r="F400" s="9" t="n">
-        <v>139.464</v>
-      </c>
+      <c r="F400" s="10" t="n"/>
     </row>
     <row r="401" ht="18" customHeight="1">
       <c r="A401" s="3" t="n"/>
@@ -9400,9 +8678,7 @@
           <t>69.318 + 18.15 + 10.581 + 16.362 + 5.99 + 49.41 = 169.811</t>
         </is>
       </c>
-      <c r="F401" s="9" t="n">
-        <v>169.811</v>
-      </c>
+      <c r="F401" s="10" t="n"/>
     </row>
     <row r="402" ht="18" customHeight="1">
       <c r="A402" s="3" t="n"/>
@@ -9422,9 +8698,7 @@
           <t>80.112 + 22.31 + 6.523 = 108.945</t>
         </is>
       </c>
-      <c r="F402" s="9" t="n">
-        <v>108.945</v>
-      </c>
+      <c r="F402" s="10" t="n"/>
     </row>
     <row r="403" ht="18" customHeight="1">
       <c r="A403" s="3" t="n"/>
@@ -9444,9 +8718,7 @@
           <t>80.112 + 4.836 + 15.314 + 39.036 = 139.298</t>
         </is>
       </c>
-      <c r="F403" s="9" t="n">
-        <v>139.298</v>
-      </c>
+      <c r="F403" s="10" t="n"/>
     </row>
     <row r="404" ht="18" customHeight="1">
       <c r="A404" s="3" t="n"/>
@@ -9466,9 +8738,7 @@
           <t>26.055 = 26.055</t>
         </is>
       </c>
-      <c r="F404" s="9" t="n">
-        <v>26.055</v>
-      </c>
+      <c r="F404" s="10" t="n"/>
     </row>
     <row r="405" ht="18" customHeight="1">
       <c r="A405" s="3" t="n"/>
@@ -9488,9 +8758,7 @@
           <t>2.846 + 54.888 + 10.334 + 15.996 + 5.99 + 49.41 = 139.464</t>
         </is>
       </c>
-      <c r="F405" s="9" t="n">
-        <v>139.464</v>
-      </c>
+      <c r="F405" s="10" t="n"/>
     </row>
     <row r="406" ht="18" customHeight="1">
       <c r="A406" s="3" t="n"/>
@@ -9510,9 +8778,7 @@
           <t>2.846 + 54.888 + 10.334 + 15.996 + 5.99 + 49.41 = 139.464</t>
         </is>
       </c>
-      <c r="F406" s="9" t="n">
-        <v>139.464</v>
-      </c>
+      <c r="F406" s="10" t="n"/>
     </row>
     <row r="407" ht="18" customHeight="1">
       <c r="A407" s="3" t="n"/>
@@ -9532,9 +8798,7 @@
           <t>69.318 + 18.15 + 10.581 + 16.362 + 5.99 + 49.41 = 169.811</t>
         </is>
       </c>
-      <c r="F407" s="9" t="n">
-        <v>169.811</v>
-      </c>
+      <c r="F407" s="10" t="n"/>
     </row>
     <row r="408" ht="18" customHeight="1">
       <c r="A408" s="3" t="n"/>
@@ -9554,9 +8818,7 @@
           <t>80.112 + 22.31 + 6.523 = 108.945</t>
         </is>
       </c>
-      <c r="F408" s="9" t="n">
-        <v>108.945</v>
-      </c>
+      <c r="F408" s="10" t="n"/>
     </row>
     <row r="409" ht="18" customHeight="1">
       <c r="A409" s="3" t="n"/>
@@ -9576,9 +8838,7 @@
           <t>80.112 + 4.836 + 15.314 + 39.036 = 139.298</t>
         </is>
       </c>
-      <c r="F409" s="9" t="n">
-        <v>139.298</v>
-      </c>
+      <c r="F409" s="10" t="n"/>
     </row>
     <row r="410" ht="18" customHeight="1">
       <c r="A410" s="3" t="n"/>
@@ -9598,9 +8858,7 @@
           <t>26.055 = 26.055</t>
         </is>
       </c>
-      <c r="F410" s="9" t="n">
-        <v>26.055</v>
-      </c>
+      <c r="F410" s="10" t="n"/>
     </row>
     <row r="411" ht="18" customHeight="1">
       <c r="A411" s="3" t="n"/>
@@ -9620,9 +8878,7 @@
           <t>56 + 10.334 + 56 + 10.334 = 132.668</t>
         </is>
       </c>
-      <c r="F411" s="9" t="n">
-        <v>132.668</v>
-      </c>
+      <c r="F411" s="10" t="n"/>
     </row>
     <row r="412" ht="18" customHeight="1">
       <c r="A412" s="3" t="n"/>
@@ -9642,9 +8898,7 @@
           <t>70.43 + 9.075 + 10.581 + 16.362 = 106.448</t>
         </is>
       </c>
-      <c r="F412" s="9" t="n">
-        <v>106.448</v>
-      </c>
+      <c r="F412" s="10" t="n"/>
     </row>
     <row r="413" ht="18" customHeight="1">
       <c r="A413" s="3" t="n"/>
@@ -9664,9 +8918,7 @@
           <t>82.088 + 11.155 = 93.243</t>
         </is>
       </c>
-      <c r="F413" s="9" t="n">
-        <v>93.24299999999999</v>
-      </c>
+      <c r="F413" s="10" t="n"/>
     </row>
     <row r="414" ht="32" customHeight="1">
       <c r="A414" s="3" t="n"/>
@@ -9682,9 +8934,7 @@
           <t>(286.602 + 188.316 + 109.632 + 136.136 + 170.137 + 108.945 + 139.464 + 139.464 + 169.811 + 108.945 + 139.298 + 26.055 + 139.464 + 139.464 + 169.811 + 108.945 + 139.298 + 26.055 + 132.668 + 106.448 + 93.243) ÷ 1000 = 2.778</t>
         </is>
       </c>
-      <c r="F414" s="10" t="n">
-        <v>2.778</v>
-      </c>
+      <c r="F414" s="10" t="n"/>
     </row>
     <row r="415" ht="18" customHeight="1">
       <c r="A415" s="3" t="n">
@@ -9711,7 +8961,7 @@
         </is>
       </c>
       <c r="F415" s="9" t="n">
-        <v>63.339</v>
+        <v>0.319</v>
       </c>
     </row>
     <row r="416" ht="18" customHeight="1">
@@ -9732,9 +8982,7 @@
           <t>63.117 = 63.117</t>
         </is>
       </c>
-      <c r="F416" s="9" t="n">
-        <v>63.117</v>
-      </c>
+      <c r="F416" s="10" t="n"/>
     </row>
     <row r="417" ht="18" customHeight="1">
       <c r="A417" s="3" t="n"/>
@@ -9754,9 +9002,7 @@
           <t>63.339 = 63.339</t>
         </is>
       </c>
-      <c r="F417" s="9" t="n">
-        <v>63.339</v>
-      </c>
+      <c r="F417" s="10" t="n"/>
     </row>
     <row r="418" ht="18" customHeight="1">
       <c r="A418" s="3" t="n"/>
@@ -9776,9 +9022,7 @@
           <t>63.117 = 63.117</t>
         </is>
       </c>
-      <c r="F418" s="9" t="n">
-        <v>63.117</v>
-      </c>
+      <c r="F418" s="10" t="n"/>
     </row>
     <row r="419" ht="18" customHeight="1">
       <c r="A419" s="3" t="n"/>
@@ -9798,9 +9042,7 @@
           <t>66.54 = 66.54</t>
         </is>
       </c>
-      <c r="F419" s="9" t="n">
-        <v>66.54000000000001</v>
-      </c>
+      <c r="F419" s="10" t="n"/>
     </row>
     <row r="420" ht="18" customHeight="1">
       <c r="A420" s="3" t="n"/>
@@ -9816,9 +9058,7 @@
           <t>(63.339 + 63.117 + 63.339 + 63.117 + 66.54) ÷ 1000 = 0.319</t>
         </is>
       </c>
-      <c r="F420" s="10" t="n">
-        <v>0.319</v>
-      </c>
+      <c r="F420" s="10" t="n"/>
     </row>
     <row r="421" ht="18" customHeight="1">
       <c r="A421" s="3" t="n">
@@ -9845,7 +9085,7 @@
         </is>
       </c>
       <c r="F421" s="9" t="n">
-        <v>3.08</v>
+        <v>1.029</v>
       </c>
     </row>
     <row r="422" ht="18" customHeight="1">
@@ -9866,9 +9106,7 @@
           <t>59.908 + 81.864 + 6.16 = 147.932</t>
         </is>
       </c>
-      <c r="F422" s="9" t="n">
-        <v>147.932</v>
-      </c>
+      <c r="F422" s="10" t="n"/>
     </row>
     <row r="423" ht="18" customHeight="1">
       <c r="A423" s="3" t="n"/>
@@ -9888,9 +9126,7 @@
           <t>3.08 = 3.08</t>
         </is>
       </c>
-      <c r="F423" s="9" t="n">
-        <v>3.08</v>
-      </c>
+      <c r="F423" s="10" t="n"/>
     </row>
     <row r="424" ht="18" customHeight="1">
       <c r="A424" s="3" t="n"/>
@@ -9910,9 +9146,7 @@
           <t>86.868 = 86.868</t>
         </is>
       </c>
-      <c r="F424" s="9" t="n">
-        <v>86.86799999999999</v>
-      </c>
+      <c r="F424" s="10" t="n"/>
     </row>
     <row r="425" ht="18" customHeight="1">
       <c r="A425" s="3" t="n"/>
@@ -9932,9 +9166,7 @@
           <t>3.08 = 3.08</t>
         </is>
       </c>
-      <c r="F425" s="9" t="n">
-        <v>3.08</v>
-      </c>
+      <c r="F425" s="10" t="n"/>
     </row>
     <row r="426" ht="18" customHeight="1">
       <c r="A426" s="3" t="n"/>
@@ -9954,9 +9186,7 @@
           <t>44.931 + 27.288 + 6.16 = 78.379</t>
         </is>
       </c>
-      <c r="F426" s="9" t="n">
-        <v>78.379</v>
-      </c>
+      <c r="F426" s="10" t="n"/>
     </row>
     <row r="427" ht="18" customHeight="1">
       <c r="A427" s="3" t="n"/>
@@ -9976,9 +9206,7 @@
           <t>44.931 + 27.288 + 6.16 = 78.379</t>
         </is>
       </c>
-      <c r="F427" s="9" t="n">
-        <v>78.379</v>
-      </c>
+      <c r="F427" s="10" t="n"/>
     </row>
     <row r="428" ht="18" customHeight="1">
       <c r="A428" s="3" t="n"/>
@@ -9998,9 +9226,7 @@
           <t>3.08 = 3.08</t>
         </is>
       </c>
-      <c r="F428" s="9" t="n">
-        <v>3.08</v>
-      </c>
+      <c r="F428" s="10" t="n"/>
     </row>
     <row r="429" ht="18" customHeight="1">
       <c r="A429" s="3" t="n"/>
@@ -10020,9 +9246,7 @@
           <t>6.16 = 6.16</t>
         </is>
       </c>
-      <c r="F429" s="9" t="n">
-        <v>6.16</v>
-      </c>
+      <c r="F429" s="10" t="n"/>
     </row>
     <row r="430" ht="18" customHeight="1">
       <c r="A430" s="3" t="n"/>
@@ -10042,9 +9266,7 @@
           <t>86.868 = 86.868</t>
         </is>
       </c>
-      <c r="F430" s="9" t="n">
-        <v>86.86799999999999</v>
-      </c>
+      <c r="F430" s="10" t="n"/>
     </row>
     <row r="431" ht="18" customHeight="1">
       <c r="A431" s="3" t="n"/>
@@ -10064,9 +9286,7 @@
           <t>77.676 = 77.676</t>
         </is>
       </c>
-      <c r="F431" s="9" t="n">
-        <v>77.676</v>
-      </c>
+      <c r="F431" s="10" t="n"/>
     </row>
     <row r="432" ht="18" customHeight="1">
       <c r="A432" s="3" t="n"/>
@@ -10086,9 +9306,7 @@
           <t>3.08 = 3.08</t>
         </is>
       </c>
-      <c r="F432" s="9" t="n">
-        <v>3.08</v>
-      </c>
+      <c r="F432" s="10" t="n"/>
     </row>
     <row r="433" ht="18" customHeight="1">
       <c r="A433" s="3" t="n"/>
@@ -10108,9 +9326,7 @@
           <t>44.931 + 27.288 + 6.16 = 78.379</t>
         </is>
       </c>
-      <c r="F433" s="9" t="n">
-        <v>78.379</v>
-      </c>
+      <c r="F433" s="10" t="n"/>
     </row>
     <row r="434" ht="18" customHeight="1">
       <c r="A434" s="3" t="n"/>
@@ -10130,9 +9346,7 @@
           <t>44.931 + 27.288 + 6.16 = 78.379</t>
         </is>
       </c>
-      <c r="F434" s="9" t="n">
-        <v>78.379</v>
-      </c>
+      <c r="F434" s="10" t="n"/>
     </row>
     <row r="435" ht="18" customHeight="1">
       <c r="A435" s="3" t="n"/>
@@ -10152,9 +9366,7 @@
           <t>3.08 = 3.08</t>
         </is>
       </c>
-      <c r="F435" s="9" t="n">
-        <v>3.08</v>
-      </c>
+      <c r="F435" s="10" t="n"/>
     </row>
     <row r="436" ht="18" customHeight="1">
       <c r="A436" s="3" t="n"/>
@@ -10174,9 +9386,7 @@
           <t>6.16 = 6.16</t>
         </is>
       </c>
-      <c r="F436" s="9" t="n">
-        <v>6.16</v>
-      </c>
+      <c r="F436" s="10" t="n"/>
     </row>
     <row r="437" ht="18" customHeight="1">
       <c r="A437" s="3" t="n"/>
@@ -10196,9 +9406,7 @@
           <t>86.868 = 86.868</t>
         </is>
       </c>
-      <c r="F437" s="9" t="n">
-        <v>86.86799999999999</v>
-      </c>
+      <c r="F437" s="10" t="n"/>
     </row>
     <row r="438" ht="18" customHeight="1">
       <c r="A438" s="3" t="n"/>
@@ -10218,9 +9426,7 @@
           <t>77.676 = 77.676</t>
         </is>
       </c>
-      <c r="F438" s="9" t="n">
-        <v>77.676</v>
-      </c>
+      <c r="F438" s="10" t="n"/>
     </row>
     <row r="439" ht="18" customHeight="1">
       <c r="A439" s="3" t="n"/>
@@ -10240,9 +9446,7 @@
           <t>29.036 + 29.954 + 29.036 + 29.954 = 117.98</t>
         </is>
       </c>
-      <c r="F439" s="9" t="n">
-        <v>117.98</v>
-      </c>
+      <c r="F439" s="10" t="n"/>
     </row>
     <row r="440" ht="18" customHeight="1">
       <c r="A440" s="3" t="n"/>
@@ -10262,9 +9466,7 @@
           <t>3.08 = 3.08</t>
         </is>
       </c>
-      <c r="F440" s="9" t="n">
-        <v>3.08</v>
-      </c>
+      <c r="F440" s="10" t="n"/>
     </row>
     <row r="441" ht="32" customHeight="1">
       <c r="A441" s="3" t="n"/>
@@ -10280,9 +9482,7 @@
           <t>(3.08 + 147.932 + 3.08 + 86.868 + 3.08 + 78.379 + 78.379 + 3.08 + 6.16 + 86.868 + 77.676 + 3.08 + 78.379 + 78.379 + 3.08 + 6.16 + 86.868 + 77.676 + 117.98 + 3.08) ÷ 1000 = 1.029</t>
         </is>
       </c>
-      <c r="F441" s="10" t="n">
-        <v>1.029</v>
-      </c>
+      <c r="F441" s="10" t="n"/>
     </row>
     <row r="442" ht="18" customHeight="1">
       <c r="A442" s="3" t="n">
@@ -10309,7 +9509,7 @@
         </is>
       </c>
       <c r="F442" s="9" t="n">
-        <v>72.411</v>
+        <v>2.37</v>
       </c>
     </row>
     <row r="443" ht="18" customHeight="1">
@@ -10330,9 +9530,7 @@
           <t>56.826 + 61.304 + 58.284 + 77.115 = 253.529</t>
         </is>
       </c>
-      <c r="F443" s="9" t="n">
-        <v>253.529</v>
-      </c>
+      <c r="F443" s="10" t="n"/>
     </row>
     <row r="444" ht="18" customHeight="1">
       <c r="A444" s="3" t="n"/>
@@ -10352,9 +9550,7 @@
           <t>35.94 + 39.2 + 48.248 + 47 + 54.242 + 50.26 = 274.89</t>
         </is>
       </c>
-      <c r="F444" s="9" t="n">
-        <v>274.89</v>
-      </c>
+      <c r="F444" s="10" t="n"/>
     </row>
     <row r="445" ht="18" customHeight="1">
       <c r="A445" s="3" t="n"/>
@@ -10374,9 +9570,7 @@
           <t>15.213 + 15.771 + 16.995 + 19.173 + 30.549 + 1.976 + 33.075 + 33.32 + 2.3 + 37.449 + 56.826 + 61.304 + 58.284 + 77.115 + 9.681 + 11.655 + 10.815 + 15.078 = 506.579</t>
         </is>
       </c>
-      <c r="F445" s="9" t="n">
-        <v>506.579</v>
-      </c>
+      <c r="F445" s="10" t="n"/>
     </row>
     <row r="446" ht="18" customHeight="1">
       <c r="A446" s="3" t="n"/>
@@ -10396,9 +9590,7 @@
           <t>50.26 + 54.242 + 47 + 48.248 + 39.2 + 35.94 = 274.89</t>
         </is>
       </c>
-      <c r="F446" s="9" t="n">
-        <v>274.89</v>
-      </c>
+      <c r="F446" s="10" t="n"/>
     </row>
     <row r="447" ht="18" customHeight="1">
       <c r="A447" s="3" t="n"/>
@@ -10418,9 +9610,7 @@
           <t>77.115 + 58.284 + 61.304 + 56.826 + 37.449 + 33.32 + 2.3 + 33.075 + 30.549 + 1.976 + 19.173 + 16.995 + 15.771 + 15.213 + 9.681 + 11.655 + 10.815 + 15.078 = 506.579</t>
         </is>
       </c>
-      <c r="F447" s="9" t="n">
-        <v>506.579</v>
-      </c>
+      <c r="F447" s="10" t="n"/>
     </row>
     <row r="448" ht="18" customHeight="1">
       <c r="A448" s="3" t="n"/>
@@ -10440,9 +9630,7 @@
           <t>14.913 + 22.496 + 15.399 + 34.884 + 56.826 + 61.304 + 58.284 + 77.115 = 341.221</t>
         </is>
       </c>
-      <c r="F448" s="9" t="n">
-        <v>341.221</v>
-      </c>
+      <c r="F448" s="10" t="n"/>
     </row>
     <row r="449" ht="18" customHeight="1">
       <c r="A449" s="3" t="n"/>
@@ -10462,9 +9650,7 @@
           <t>15.213 + 15.771 + 16.995 + 19.173 + 9.681 + 11.655 + 10.815 + 15.078 = 114.381</t>
         </is>
       </c>
-      <c r="F449" s="9" t="n">
-        <v>114.381</v>
-      </c>
+      <c r="F449" s="10" t="n"/>
     </row>
     <row r="450" ht="18" customHeight="1">
       <c r="A450" s="3" t="n"/>
@@ -10484,9 +9670,7 @@
           <t>4.125 + 6.854 + 4.137 + 10.557 = 25.673</t>
         </is>
       </c>
-      <c r="F450" s="9" t="n">
-        <v>25.673</v>
-      </c>
+      <c r="F450" s="10" t="n"/>
     </row>
     <row r="451" ht="18" customHeight="1">
       <c r="A451" s="3" t="n"/>
@@ -10502,9 +9686,7 @@
           <t>(72.411 + 253.529 + 274.89 + 506.579 + 274.89 + 506.579 + 341.221 + 114.381 + 25.673) ÷ 1000 = 2.370</t>
         </is>
       </c>
-      <c r="F451" s="10" t="n">
-        <v>2.37</v>
-      </c>
+      <c r="F451" s="10" t="n"/>
     </row>
     <row r="452" ht="18" customHeight="1">
       <c r="A452" s="3" t="n">
@@ -10531,7 +9713,7 @@
         </is>
       </c>
       <c r="F452" s="9" t="n">
-        <v>625.867</v>
+        <v>2.808</v>
       </c>
     </row>
     <row r="453" ht="18" customHeight="1">
@@ -10552,9 +9734,7 @@
           <t>40.824 + 46.746 + 17.766 + 85.512 + 42.944 + 27.084 + 121.94 + 62.307 + 56.925 + 81.54 = 583.588</t>
         </is>
       </c>
-      <c r="F453" s="9" t="n">
-        <v>583.588</v>
-      </c>
+      <c r="F453" s="10" t="n"/>
     </row>
     <row r="454" ht="18" customHeight="1">
       <c r="A454" s="3" t="n"/>
@@ -10574,9 +9754,7 @@
           <t>46.746 + 40.824 + 56.925 + 81.54 + 42.944 + 17.766 + 85.512 + 62.307 + 27.084 + 121.94 = 583.588</t>
         </is>
       </c>
-      <c r="F454" s="9" t="n">
-        <v>583.588</v>
-      </c>
+      <c r="F454" s="10" t="n"/>
     </row>
     <row r="455" ht="18" customHeight="1">
       <c r="A455" s="3" t="n"/>
@@ -10596,9 +9774,7 @@
           <t>48.12 + 49.35 + 69.82 + 56.925 + 81.54 + 42.944 + 17.766 + 85.512 + 62.307 + 27.084 + 121.94 = 663.308</t>
         </is>
       </c>
-      <c r="F455" s="9" t="n">
-        <v>663.308</v>
-      </c>
+      <c r="F455" s="10" t="n"/>
     </row>
     <row r="456" ht="18" customHeight="1">
       <c r="A456" s="3" t="n"/>
@@ -10618,9 +9794,7 @@
           <t>50.496 + 21.01 + 69.152 + 109.48 + 101.244 = 351.382</t>
         </is>
       </c>
-      <c r="F456" s="9" t="n">
-        <v>351.382</v>
-      </c>
+      <c r="F456" s="10" t="n"/>
     </row>
     <row r="457" ht="18" customHeight="1">
       <c r="A457" s="3" t="n"/>
@@ -10636,9 +9810,7 @@
           <t>(625.867 + 583.588 + 583.588 + 663.308 + 351.382) ÷ 1000 = 2.808</t>
         </is>
       </c>
-      <c r="F457" s="10" t="n">
-        <v>2.808</v>
-      </c>
+      <c r="F457" s="10" t="n"/>
     </row>
     <row r="458" ht="18" customHeight="1">
       <c r="A458" s="3" t="n">
@@ -10665,7 +9837,7 @@
         </is>
       </c>
       <c r="F458" s="9" t="n">
-        <v>1567.423</v>
+        <v>6.289</v>
       </c>
     </row>
     <row r="459" ht="18" customHeight="1">
@@ -10686,9 +9858,7 @@
           <t>252.896 + 124.68 + 336.148 + 131.064 + 130.416 + 176.16 + 165.592 + 158.144 = 1475.1</t>
         </is>
       </c>
-      <c r="F459" s="9" t="n">
-        <v>1475.1</v>
-      </c>
+      <c r="F459" s="10" t="n"/>
     </row>
     <row r="460" ht="18" customHeight="1">
       <c r="A460" s="3" t="n"/>
@@ -10708,9 +9878,7 @@
           <t>130.416 + 131.064 + 165.592 + 176.16 + 124.68 + 252.896 + 336.148 + 158.144 = 1475.1</t>
         </is>
       </c>
-      <c r="F460" s="9" t="n">
-        <v>1475.1</v>
-      </c>
+      <c r="F460" s="10" t="n"/>
     </row>
     <row r="461" ht="18" customHeight="1">
       <c r="A461" s="3" t="n"/>
@@ -10730,9 +9898,7 @@
           <t>221.284 + 110.832 + 385.704 + 260.799 + 353.84 + 165.592 + 131.064 + 141.96 = 1771.075</t>
         </is>
       </c>
-      <c r="F461" s="9" t="n">
-        <v>1771.075</v>
-      </c>
+      <c r="F461" s="10" t="n"/>
     </row>
     <row r="462" ht="18" customHeight="1">
       <c r="A462" s="3" t="n"/>
@@ -10748,9 +9914,7 @@
           <t>(1567.423 + 1475.1 + 1475.1 + 1771.075) ÷ 1000 = 6.289</t>
         </is>
       </c>
-      <c r="F462" s="10" t="n">
-        <v>6.289</v>
-      </c>
+      <c r="F462" s="10" t="n"/>
     </row>
     <row r="463" ht="18" customHeight="1">
       <c r="A463" s="3" t="n">
@@ -10777,7 +9941,7 @@
         </is>
       </c>
       <c r="F463" s="9" t="n">
-        <v>18.836</v>
+        <v>0.089</v>
       </c>
     </row>
     <row r="464" ht="18" customHeight="1">
@@ -10798,9 +9962,7 @@
           <t>15.408 + 7.922 = 23.33</t>
         </is>
       </c>
-      <c r="F464" s="9" t="n">
-        <v>23.33</v>
-      </c>
+      <c r="F464" s="10" t="n"/>
     </row>
     <row r="465" ht="18" customHeight="1">
       <c r="A465" s="3" t="n"/>
@@ -10820,9 +9982,7 @@
           <t>15.408 + 7.922 = 23.33</t>
         </is>
       </c>
-      <c r="F465" s="9" t="n">
-        <v>23.33</v>
-      </c>
+      <c r="F465" s="10" t="n"/>
     </row>
     <row r="466" ht="18" customHeight="1">
       <c r="A466" s="3" t="n"/>
@@ -10842,9 +10002,7 @@
           <t>15.408 + 7.922 = 23.33</t>
         </is>
       </c>
-      <c r="F466" s="9" t="n">
-        <v>23.33</v>
-      </c>
+      <c r="F466" s="10" t="n"/>
     </row>
     <row r="467" ht="18" customHeight="1">
       <c r="A467" s="3" t="n"/>
@@ -10860,9 +10018,7 @@
           <t>(18.836 + 23.33 + 23.33 + 23.33) ÷ 1000 = 0.089</t>
         </is>
       </c>
-      <c r="F467" s="10" t="n">
-        <v>0.089</v>
-      </c>
+      <c r="F467" s="10" t="n"/>
     </row>
     <row r="468" ht="18" customHeight="1">
       <c r="A468" s="3" t="n">
@@ -10889,7 +10045,7 @@
         </is>
       </c>
       <c r="F468" s="9" t="n">
-        <v>63.941</v>
+        <v>0.209</v>
       </c>
     </row>
     <row r="469" ht="18" customHeight="1">
@@ -10910,9 +10066,7 @@
           <t>13.587 + 11.277 + 11.991 + 11.376 = 48.231</t>
         </is>
       </c>
-      <c r="F469" s="9" t="n">
-        <v>48.231</v>
-      </c>
+      <c r="F469" s="10" t="n"/>
     </row>
     <row r="470" ht="18" customHeight="1">
       <c r="A470" s="3" t="n"/>
@@ -10932,9 +10086,7 @@
           <t>13.587 + 11.277 + 11.991 + 11.376 = 48.231</t>
         </is>
       </c>
-      <c r="F470" s="9" t="n">
-        <v>48.231</v>
-      </c>
+      <c r="F470" s="10" t="n"/>
     </row>
     <row r="471" ht="18" customHeight="1">
       <c r="A471" s="3" t="n"/>
@@ -10954,9 +10106,7 @@
           <t>13.587 + 11.277 + 11.991 + 11.376 = 48.231</t>
         </is>
       </c>
-      <c r="F471" s="9" t="n">
-        <v>48.231</v>
-      </c>
+      <c r="F471" s="10" t="n"/>
     </row>
     <row r="472" ht="18" customHeight="1">
       <c r="A472" s="3" t="n"/>
@@ -10972,9 +10122,7 @@
           <t>(63.941 + 48.231 + 48.231 + 48.231) ÷ 1000 = 0.209</t>
         </is>
       </c>
-      <c r="F472" s="10" t="n">
-        <v>0.209</v>
-      </c>
+      <c r="F472" s="10" t="n"/>
     </row>
     <row r="473" ht="18" customHeight="1">
       <c r="A473" s="3" t="n">
@@ -11001,7 +10149,7 @@
         </is>
       </c>
       <c r="F473" s="9" t="n">
-        <v>111.07</v>
+        <v>0.417</v>
       </c>
     </row>
     <row r="474" ht="18" customHeight="1">
@@ -11022,9 +10170,7 @@
           <t>22.24 + 7.39 + 29.83 + 11.12 + 31.37 = 101.95</t>
         </is>
       </c>
-      <c r="F474" s="9" t="n">
-        <v>101.95</v>
-      </c>
+      <c r="F474" s="10" t="n"/>
     </row>
     <row r="475" ht="18" customHeight="1">
       <c r="A475" s="3" t="n"/>
@@ -11044,9 +10190,7 @@
           <t>22.24 + 7.39 + 29.83 + 11.12 + 31.37 = 101.95</t>
         </is>
       </c>
-      <c r="F475" s="9" t="n">
-        <v>101.95</v>
-      </c>
+      <c r="F475" s="10" t="n"/>
     </row>
     <row r="476" ht="18" customHeight="1">
       <c r="A476" s="3" t="n"/>
@@ -11066,9 +10210,7 @@
           <t>22.24 + 7.39 + 29.83 + 11.12 + 31.37 = 101.95</t>
         </is>
       </c>
-      <c r="F476" s="9" t="n">
-        <v>101.95</v>
-      </c>
+      <c r="F476" s="10" t="n"/>
     </row>
     <row r="477" ht="18" customHeight="1">
       <c r="A477" s="3" t="n"/>
@@ -11084,9 +10226,7 @@
           <t>(111.07 + 101.95 + 101.95 + 101.95) ÷ 1000 = 0.417</t>
         </is>
       </c>
-      <c r="F477" s="10" t="n">
-        <v>0.417</v>
-      </c>
+      <c r="F477" s="10" t="n"/>
     </row>
     <row r="478" ht="18" customHeight="1">
       <c r="A478" s="3" t="n">
@@ -11113,7 +10253,7 @@
         </is>
       </c>
       <c r="F478" s="9" t="n">
-        <v>66.556</v>
+        <v>0.266</v>
       </c>
     </row>
     <row r="479" ht="18" customHeight="1">
@@ -11134,9 +10274,7 @@
           <t>11.704 + 5.783 + 15.741 + 11.724 + 5.792 + 15.771 = 66.515</t>
         </is>
       </c>
-      <c r="F479" s="9" t="n">
-        <v>66.515</v>
-      </c>
+      <c r="F479" s="10" t="n"/>
     </row>
     <row r="480" ht="18" customHeight="1">
       <c r="A480" s="3" t="n"/>
@@ -11156,9 +10294,7 @@
           <t>11.704 + 5.783 + 15.741 + 11.724 + 5.792 + 15.771 = 66.515</t>
         </is>
       </c>
-      <c r="F480" s="9" t="n">
-        <v>66.515</v>
-      </c>
+      <c r="F480" s="10" t="n"/>
     </row>
     <row r="481" ht="18" customHeight="1">
       <c r="A481" s="3" t="n"/>
@@ -11178,9 +10314,7 @@
           <t>11.704 + 5.783 + 15.741 + 11.724 + 5.792 + 15.771 = 66.515</t>
         </is>
       </c>
-      <c r="F481" s="9" t="n">
-        <v>66.515</v>
-      </c>
+      <c r="F481" s="10" t="n"/>
     </row>
     <row r="482" ht="18" customHeight="1">
       <c r="A482" s="3" t="n"/>
@@ -11196,9 +10330,7 @@
           <t>(66.556 + 66.515 + 66.515 + 66.515) ÷ 1000 = 0.266</t>
         </is>
       </c>
-      <c r="F482" s="10" t="n">
-        <v>0.266</v>
-      </c>
+      <c r="F482" s="10" t="n"/>
     </row>
     <row r="483" ht="18" customHeight="1">
       <c r="A483" s="3" t="n">
@@ -11225,7 +10357,7 @@
         </is>
       </c>
       <c r="F483" s="9" t="n">
-        <v>1.701</v>
+        <v>0.08799999999999999</v>
       </c>
     </row>
     <row r="484" ht="18" customHeight="1">
@@ -11246,9 +10378,7 @@
           <t>6.534 = 6.534</t>
         </is>
       </c>
-      <c r="F484" s="9" t="n">
-        <v>6.534</v>
-      </c>
+      <c r="F484" s="10" t="n"/>
     </row>
     <row r="485" ht="18" customHeight="1">
       <c r="A485" s="3" t="n"/>
@@ -11268,9 +10398,7 @@
           <t>3.213 = 3.213</t>
         </is>
       </c>
-      <c r="F485" s="9" t="n">
-        <v>3.213</v>
-      </c>
+      <c r="F485" s="10" t="n"/>
     </row>
     <row r="486" ht="18" customHeight="1">
       <c r="A486" s="3" t="n"/>
@@ -11290,9 +10418,7 @@
           <t>12.342 = 12.342</t>
         </is>
       </c>
-      <c r="F486" s="9" t="n">
-        <v>12.342</v>
-      </c>
+      <c r="F486" s="10" t="n"/>
     </row>
     <row r="487" ht="18" customHeight="1">
       <c r="A487" s="3" t="n"/>
@@ -11312,9 +10438,7 @@
           <t>3.213 = 3.213</t>
         </is>
       </c>
-      <c r="F487" s="9" t="n">
-        <v>3.213</v>
-      </c>
+      <c r="F487" s="10" t="n"/>
     </row>
     <row r="488" ht="18" customHeight="1">
       <c r="A488" s="3" t="n"/>
@@ -11334,9 +10458,7 @@
           <t>12.342 = 12.342</t>
         </is>
       </c>
-      <c r="F488" s="9" t="n">
-        <v>12.342</v>
-      </c>
+      <c r="F488" s="10" t="n"/>
     </row>
     <row r="489" ht="18" customHeight="1">
       <c r="A489" s="3" t="n"/>
@@ -11356,9 +10478,7 @@
           <t>3.213 = 3.213</t>
         </is>
       </c>
-      <c r="F489" s="9" t="n">
-        <v>3.213</v>
-      </c>
+      <c r="F489" s="10" t="n"/>
     </row>
     <row r="490" ht="18" customHeight="1">
       <c r="A490" s="3" t="n"/>
@@ -11378,9 +10498,7 @@
           <t>12.342 = 12.342</t>
         </is>
       </c>
-      <c r="F490" s="9" t="n">
-        <v>12.342</v>
-      </c>
+      <c r="F490" s="10" t="n"/>
     </row>
     <row r="491" ht="18" customHeight="1">
       <c r="A491" s="3" t="n"/>
@@ -11400,9 +10518,7 @@
           <t>3.213 = 3.213</t>
         </is>
       </c>
-      <c r="F491" s="9" t="n">
-        <v>3.213</v>
-      </c>
+      <c r="F491" s="10" t="n"/>
     </row>
     <row r="492" ht="18" customHeight="1">
       <c r="A492" s="3" t="n"/>
@@ -11422,9 +10538,7 @@
           <t>12.342 = 12.342</t>
         </is>
       </c>
-      <c r="F492" s="9" t="n">
-        <v>12.342</v>
-      </c>
+      <c r="F492" s="10" t="n"/>
     </row>
     <row r="493" ht="18" customHeight="1">
       <c r="A493" s="3" t="n"/>
@@ -11444,9 +10558,7 @@
           <t>5.292 + 2.835 + 2.646 = 10.773</t>
         </is>
       </c>
-      <c r="F493" s="9" t="n">
-        <v>10.773</v>
-      </c>
+      <c r="F493" s="10" t="n"/>
     </row>
     <row r="494" ht="18" customHeight="1">
       <c r="A494" s="3" t="n"/>
@@ -11466,9 +10578,7 @@
           <t>6.534 = 6.534</t>
         </is>
       </c>
-      <c r="F494" s="9" t="n">
-        <v>6.534</v>
-      </c>
+      <c r="F494" s="10" t="n"/>
     </row>
     <row r="495" ht="18" customHeight="1">
       <c r="A495" s="3" t="n"/>
@@ -11484,9 +10594,7 @@
           <t>(1.701 + 6.534 + 3.213 + 12.342 + 3.213 + 12.342 + 3.213 + 12.342 + 3.213 + 12.342 + 10.773 + 6.534) ÷ 1000 = 0.088</t>
         </is>
       </c>
-      <c r="F495" s="10" t="n">
-        <v>0.08799999999999999</v>
-      </c>
+      <c r="F495" s="10" t="n"/>
     </row>
     <row r="496" ht="18" customHeight="1">
       <c r="A496" s="3" t="n">
@@ -11513,7 +10621,7 @@
         </is>
       </c>
       <c r="F496" s="9" t="n">
-        <v>9.212</v>
+        <v>0.357</v>
       </c>
     </row>
     <row r="497" ht="18" customHeight="1">
@@ -11534,9 +10642,7 @@
           <t>17.532 + 10.104 = 27.636</t>
         </is>
       </c>
-      <c r="F497" s="9" t="n">
-        <v>27.636</v>
-      </c>
+      <c r="F497" s="10" t="n"/>
     </row>
     <row r="498" ht="18" customHeight="1">
       <c r="A498" s="3" t="n"/>
@@ -11556,9 +10662,7 @@
           <t>11.704 + 3.368 = 15.072</t>
         </is>
       </c>
-      <c r="F498" s="9" t="n">
-        <v>15.072</v>
-      </c>
+      <c r="F498" s="10" t="n"/>
     </row>
     <row r="499" ht="18" customHeight="1">
       <c r="A499" s="3" t="n"/>
@@ -11578,9 +10682,7 @@
           <t>35.112 + 10.104 = 45.216</t>
         </is>
       </c>
-      <c r="F499" s="9" t="n">
-        <v>45.216</v>
-      </c>
+      <c r="F499" s="10" t="n"/>
     </row>
     <row r="500" ht="18" customHeight="1">
       <c r="A500" s="3" t="n"/>
@@ -11600,9 +10702,7 @@
           <t>11.704 + 3.28 = 14.984</t>
         </is>
       </c>
-      <c r="F500" s="9" t="n">
-        <v>14.984</v>
-      </c>
+      <c r="F500" s="10" t="n"/>
     </row>
     <row r="501" ht="18" customHeight="1">
       <c r="A501" s="3" t="n"/>
@@ -11622,9 +10722,7 @@
           <t>35.112 + 9.84 = 44.952</t>
         </is>
       </c>
-      <c r="F501" s="9" t="n">
-        <v>44.952</v>
-      </c>
+      <c r="F501" s="10" t="n"/>
     </row>
     <row r="502" ht="18" customHeight="1">
       <c r="A502" s="3" t="n"/>
@@ -11644,9 +10742,7 @@
           <t>11.704 + 3.28 = 14.984</t>
         </is>
       </c>
-      <c r="F502" s="9" t="n">
-        <v>14.984</v>
-      </c>
+      <c r="F502" s="10" t="n"/>
     </row>
     <row r="503" ht="18" customHeight="1">
       <c r="A503" s="3" t="n"/>
@@ -11666,9 +10762,7 @@
           <t>35.112 + 9.84 = 44.952</t>
         </is>
       </c>
-      <c r="F503" s="9" t="n">
-        <v>44.952</v>
-      </c>
+      <c r="F503" s="10" t="n"/>
     </row>
     <row r="504" ht="18" customHeight="1">
       <c r="A504" s="3" t="n"/>
@@ -11688,9 +10782,7 @@
           <t>11.704 + 3.28 = 14.984</t>
         </is>
       </c>
-      <c r="F504" s="9" t="n">
-        <v>14.984</v>
-      </c>
+      <c r="F504" s="10" t="n"/>
     </row>
     <row r="505" ht="18" customHeight="1">
       <c r="A505" s="3" t="n"/>
@@ -11710,9 +10802,7 @@
           <t>35.112 + 9.84 = 44.952</t>
         </is>
       </c>
-      <c r="F505" s="9" t="n">
-        <v>44.952</v>
-      </c>
+      <c r="F505" s="10" t="n"/>
     </row>
     <row r="506" ht="18" customHeight="1">
       <c r="A506" s="3" t="n"/>
@@ -11732,9 +10822,7 @@
           <t>19.144 + 6.736 + 9.928 + 3.368 + 9.752 + 3.368 = 52.296</t>
         </is>
       </c>
-      <c r="F506" s="9" t="n">
-        <v>52.296</v>
-      </c>
+      <c r="F506" s="10" t="n"/>
     </row>
     <row r="507" ht="18" customHeight="1">
       <c r="A507" s="3" t="n"/>
@@ -11754,9 +10842,7 @@
           <t>18.06 + 9.84 = 27.9</t>
         </is>
       </c>
-      <c r="F507" s="9" t="n">
-        <v>27.9</v>
-      </c>
+      <c r="F507" s="10" t="n"/>
     </row>
     <row r="508" ht="18" customHeight="1">
       <c r="A508" s="3" t="n"/>
@@ -11772,9 +10858,7 @@
           <t>(9.212 + 27.636 + 15.072 + 45.216 + 14.984 + 44.952 + 14.984 + 44.952 + 14.984 + 44.952 + 52.296 + 27.9) ÷ 1000 = 0.357</t>
         </is>
       </c>
-      <c r="F508" s="10" t="n">
-        <v>0.357</v>
-      </c>
+      <c r="F508" s="10" t="n"/>
     </row>
     <row r="509" ht="18" customHeight="1">
       <c r="A509" s="3" t="n">
@@ -11801,7 +10885,7 @@
         </is>
       </c>
       <c r="F509" s="9" t="n">
-        <v>0.275</v>
+        <v>0</v>
       </c>
     </row>
     <row r="510" ht="18" customHeight="1">
@@ -11818,9 +10902,7 @@
           <t>(0.275) ÷ 1000 = 0.000</t>
         </is>
       </c>
-      <c r="F510" s="10" t="n">
-        <v>0</v>
-      </c>
+      <c r="F510" s="10" t="n"/>
     </row>
     <row r="511" ht="18" customHeight="1">
       <c r="A511" s="3" t="n">
@@ -11847,7 +10929,7 @@
         </is>
       </c>
       <c r="F511" s="9" t="n">
-        <v>4.212</v>
+        <v>0.044</v>
       </c>
     </row>
     <row r="512" ht="18" customHeight="1">
@@ -11868,9 +10950,7 @@
           <t>10.368 = 10.368</t>
         </is>
       </c>
-      <c r="F512" s="9" t="n">
-        <v>10.368</v>
-      </c>
+      <c r="F512" s="10" t="n"/>
     </row>
     <row r="513" ht="18" customHeight="1">
       <c r="A513" s="3" t="n"/>
@@ -11890,9 +10970,7 @@
           <t>4.212 = 4.212</t>
         </is>
       </c>
-      <c r="F513" s="9" t="n">
-        <v>4.212</v>
-      </c>
+      <c r="F513" s="10" t="n"/>
     </row>
     <row r="514" ht="18" customHeight="1">
       <c r="A514" s="3" t="n"/>
@@ -11912,9 +10990,7 @@
           <t>5.184 = 5.184</t>
         </is>
       </c>
-      <c r="F514" s="9" t="n">
-        <v>5.184</v>
-      </c>
+      <c r="F514" s="10" t="n"/>
     </row>
     <row r="515" ht="18" customHeight="1">
       <c r="A515" s="3" t="n"/>
@@ -11934,9 +11010,7 @@
           <t>4.212 = 4.212</t>
         </is>
       </c>
-      <c r="F515" s="9" t="n">
-        <v>4.212</v>
-      </c>
+      <c r="F515" s="10" t="n"/>
     </row>
     <row r="516" ht="18" customHeight="1">
       <c r="A516" s="3" t="n"/>
@@ -11956,9 +11030,7 @@
           <t>5.184 = 5.184</t>
         </is>
       </c>
-      <c r="F516" s="9" t="n">
-        <v>5.184</v>
-      </c>
+      <c r="F516" s="10" t="n"/>
     </row>
     <row r="517" ht="18" customHeight="1">
       <c r="A517" s="3" t="n"/>
@@ -11978,9 +11050,7 @@
           <t>4.212 = 4.212</t>
         </is>
       </c>
-      <c r="F517" s="9" t="n">
-        <v>4.212</v>
-      </c>
+      <c r="F517" s="10" t="n"/>
     </row>
     <row r="518" ht="18" customHeight="1">
       <c r="A518" s="3" t="n"/>
@@ -12000,9 +11070,7 @@
           <t>5.184 = 5.184</t>
         </is>
       </c>
-      <c r="F518" s="9" t="n">
-        <v>5.184</v>
-      </c>
+      <c r="F518" s="10" t="n"/>
     </row>
     <row r="519" ht="18" customHeight="1">
       <c r="A519" s="3" t="n"/>
@@ -12022,9 +11090,7 @@
           <t>1.62 = 1.62</t>
         </is>
       </c>
-      <c r="F519" s="9" t="n">
-        <v>1.62</v>
-      </c>
+      <c r="F519" s="10" t="n"/>
     </row>
     <row r="520" ht="18" customHeight="1">
       <c r="A520" s="3" t="n"/>
@@ -12040,9 +11106,7 @@
           <t>(4.212 + 10.368 + 4.212 + 5.184 + 4.212 + 5.184 + 4.212 + 5.184 + 1.62) ÷ 1000 = 0.044</t>
         </is>
       </c>
-      <c r="F520" s="10" t="n">
-        <v>0.044</v>
-      </c>
+      <c r="F520" s="10" t="n"/>
     </row>
     <row r="521" ht="18" customHeight="1">
       <c r="A521" s="3" t="n">
@@ -12069,7 +11133,7 @@
         </is>
       </c>
       <c r="F521" s="9" t="n">
-        <v>1.224</v>
+        <v>0.001</v>
       </c>
     </row>
     <row r="522" ht="18" customHeight="1">
@@ -12086,9 +11150,7 @@
           <t>(1.224) ÷ 1000 = 0.001</t>
         </is>
       </c>
-      <c r="F522" s="10" t="n">
-        <v>0.001</v>
-      </c>
+      <c r="F522" s="10" t="n"/>
     </row>
     <row r="523" ht="18" customHeight="1">
       <c r="A523" s="3" t="n">
@@ -12115,7 +11177,7 @@
         </is>
       </c>
       <c r="F523" s="9" t="n">
-        <v>17.048</v>
+        <v>0.077</v>
       </c>
     </row>
     <row r="524" ht="18" customHeight="1">
@@ -12136,9 +11198,7 @@
           <t>17.048 = 17.048</t>
         </is>
       </c>
-      <c r="F524" s="9" t="n">
-        <v>17.048</v>
-      </c>
+      <c r="F524" s="10" t="n"/>
     </row>
     <row r="525" ht="18" customHeight="1">
       <c r="A525" s="3" t="n"/>
@@ -12158,9 +11218,7 @@
           <t>17.048 = 17.048</t>
         </is>
       </c>
-      <c r="F525" s="9" t="n">
-        <v>17.048</v>
-      </c>
+      <c r="F525" s="10" t="n"/>
     </row>
     <row r="526" ht="18" customHeight="1">
       <c r="A526" s="3" t="n"/>
@@ -12180,9 +11238,7 @@
           <t>17.048 = 17.048</t>
         </is>
       </c>
-      <c r="F526" s="9" t="n">
-        <v>17.048</v>
-      </c>
+      <c r="F526" s="10" t="n"/>
     </row>
     <row r="527" ht="18" customHeight="1">
       <c r="A527" s="3" t="n"/>
@@ -12202,9 +11258,7 @@
           <t>8.444 = 8.444</t>
         </is>
       </c>
-      <c r="F527" s="9" t="n">
-        <v>8.444000000000001</v>
-      </c>
+      <c r="F527" s="10" t="n"/>
     </row>
     <row r="528" ht="18" customHeight="1">
       <c r="A528" s="3" t="n"/>
@@ -12220,9 +11274,7 @@
           <t>(17.048 + 17.048 + 17.048 + 17.048 + 8.444) ÷ 1000 = 0.077</t>
         </is>
       </c>
-      <c r="F528" s="10" t="n">
-        <v>0.077</v>
-      </c>
+      <c r="F528" s="10" t="n"/>
     </row>
     <row r="529" ht="18" customHeight="1">
       <c r="A529" s="3" t="n">
@@ -12249,7 +11301,7 @@
         </is>
       </c>
       <c r="F529" s="9" t="n">
-        <v>58.56</v>
+        <v>0.146</v>
       </c>
     </row>
     <row r="530" ht="18" customHeight="1">
@@ -12270,9 +11322,7 @@
           <t>29.28 = 29.28</t>
         </is>
       </c>
-      <c r="F530" s="9" t="n">
-        <v>29.28</v>
-      </c>
+      <c r="F530" s="10" t="n"/>
     </row>
     <row r="531" ht="18" customHeight="1">
       <c r="A531" s="3" t="n"/>
@@ -12292,9 +11342,7 @@
           <t>29.28 = 29.28</t>
         </is>
       </c>
-      <c r="F531" s="9" t="n">
-        <v>29.28</v>
-      </c>
+      <c r="F531" s="10" t="n"/>
     </row>
     <row r="532" ht="18" customHeight="1">
       <c r="A532" s="3" t="n"/>
@@ -12314,9 +11362,7 @@
           <t>29.28 = 29.28</t>
         </is>
       </c>
-      <c r="F532" s="9" t="n">
-        <v>29.28</v>
-      </c>
+      <c r="F532" s="10" t="n"/>
     </row>
     <row r="533" ht="18" customHeight="1">
       <c r="A533" s="3" t="n"/>
@@ -12332,9 +11378,7 @@
           <t>(58.56 + 29.28 + 29.28 + 29.28) ÷ 1000 = 0.146</t>
         </is>
       </c>
-      <c r="F533" s="10" t="n">
-        <v>0.146</v>
-      </c>
+      <c r="F533" s="10" t="n"/>
     </row>
     <row r="534" ht="18" customHeight="1">
       <c r="A534" s="3" t="n">
@@ -12361,7 +11405,7 @@
         </is>
       </c>
       <c r="F534" s="9" t="n">
-        <v>17.181</v>
+        <v>0.021</v>
       </c>
     </row>
     <row r="535" ht="18" customHeight="1">
@@ -12382,9 +11426,7 @@
           <t>4.267 = 4.267</t>
         </is>
       </c>
-      <c r="F535" s="9" t="n">
-        <v>4.267</v>
-      </c>
+      <c r="F535" s="10" t="n"/>
     </row>
     <row r="536" ht="18" customHeight="1">
       <c r="A536" s="3" t="n"/>
@@ -12400,9 +11442,7 @@
           <t>(17.181 + 4.267) ÷ 1000 = 0.021</t>
         </is>
       </c>
-      <c r="F536" s="10" t="n">
-        <v>0.021</v>
-      </c>
+      <c r="F536" s="10" t="n"/>
     </row>
     <row r="537" ht="18" customHeight="1">
       <c r="A537" s="3" t="n">
@@ -12429,7 +11469,7 @@
         </is>
       </c>
       <c r="F537" s="9" t="n">
-        <v>70.66200000000001</v>
+        <v>0.08400000000000001</v>
       </c>
     </row>
     <row r="538" ht="18" customHeight="1">
@@ -12450,9 +11490,7 @@
           <t>6.394 + 6.948 = 13.342</t>
         </is>
       </c>
-      <c r="F538" s="9" t="n">
-        <v>13.342</v>
-      </c>
+      <c r="F538" s="10" t="n"/>
     </row>
     <row r="539" ht="18" customHeight="1">
       <c r="A539" s="3" t="n"/>
@@ -12468,9 +11506,7 @@
           <t>(70.662 + 13.342) ÷ 1000 = 0.084</t>
         </is>
       </c>
-      <c r="F539" s="10" t="n">
-        <v>0.08400000000000001</v>
-      </c>
+      <c r="F539" s="10" t="n"/>
     </row>
     <row r="540" ht="18" customHeight="1">
       <c r="A540" s="3" t="n">
@@ -12497,7 +11533,7 @@
         </is>
       </c>
       <c r="F540" s="9" t="n">
-        <v>6.04</v>
+        <v>0.006</v>
       </c>
     </row>
     <row r="541" ht="18" customHeight="1">
@@ -12514,9 +11550,7 @@
           <t>(6.04) ÷ 1000 = 0.006</t>
         </is>
       </c>
-      <c r="F541" s="10" t="n">
-        <v>0.006</v>
-      </c>
+      <c r="F541" s="10" t="n"/>
     </row>
     <row r="542" ht="18" customHeight="1">
       <c r="A542" s="3" t="n">
@@ -12543,7 +11577,7 @@
         </is>
       </c>
       <c r="F542" s="9" t="n">
-        <v>263.369</v>
+        <v>0.263</v>
       </c>
     </row>
     <row r="543" ht="18" customHeight="1">
@@ -12560,9 +11594,7 @@
           <t>(263.369) ÷ 1000 = 0.263</t>
         </is>
       </c>
-      <c r="F543" s="10" t="n">
-        <v>0.263</v>
-      </c>
+      <c r="F543" s="10" t="n"/>
     </row>
     <row r="544" ht="18" customHeight="1">
       <c r="A544" s="3" t="n">
@@ -12589,7 +11621,7 @@
         </is>
       </c>
       <c r="F544" s="5" t="n">
-        <v>9</v>
+        <v>13.83</v>
       </c>
     </row>
     <row r="545" ht="18" customHeight="1">
@@ -12610,9 +11642,7 @@
           <t>(0.8×2.1) = 1.68</t>
         </is>
       </c>
-      <c r="F545" s="5" t="n">
-        <v>1.68</v>
-      </c>
+      <c r="F545" s="8" t="n"/>
     </row>
     <row r="546" ht="18" customHeight="1">
       <c r="A546" s="3" t="n"/>
@@ -12632,9 +11662,7 @@
           <t>(1.5×2.1) = 3.15</t>
         </is>
       </c>
-      <c r="F546" s="5" t="n">
-        <v>3.15</v>
-      </c>
+      <c r="F546" s="8" t="n"/>
     </row>
     <row r="547" ht="18" customHeight="1">
       <c r="A547" s="3" t="n"/>
@@ -12650,9 +11678,7 @@
           <t>9 + 1.68 + 3.15 = 13.83 ≈ 13.83</t>
         </is>
       </c>
-      <c r="F547" s="8" t="n">
-        <v>13.83</v>
-      </c>
+      <c r="F547" s="8" t="n"/>
     </row>
     <row r="548" ht="18" customHeight="1">
       <c r="A548" s="3" t="n">
@@ -12679,7 +11705,7 @@
         </is>
       </c>
       <c r="F548" s="5" t="n">
-        <v>8.640000000000001</v>
+        <v>164.64</v>
       </c>
     </row>
     <row r="549" ht="18" customHeight="1">
@@ -12700,9 +11726,7 @@
           <t>[(2.4×1.8)]×2 = 8.64</t>
         </is>
       </c>
-      <c r="F549" s="5" t="n">
-        <v>8.640000000000001</v>
-      </c>
+      <c r="F549" s="8" t="n"/>
     </row>
     <row r="550" ht="18" customHeight="1">
       <c r="A550" s="3" t="n"/>
@@ -12722,9 +11746,7 @@
           <t>(1.8×1.8) = 3.24</t>
         </is>
       </c>
-      <c r="F550" s="5" t="n">
-        <v>3.24</v>
-      </c>
+      <c r="F550" s="8" t="n"/>
     </row>
     <row r="551" ht="18" customHeight="1">
       <c r="A551" s="3" t="n"/>
@@ -12744,9 +11766,7 @@
           <t>(1.8×1) = 1.8</t>
         </is>
       </c>
-      <c r="F551" s="5" t="n">
-        <v>1.8</v>
-      </c>
+      <c r="F551" s="8" t="n"/>
     </row>
     <row r="552" ht="18" customHeight="1">
       <c r="A552" s="3" t="n"/>
@@ -12766,9 +11786,7 @@
           <t>[(1.2×3.05)]×2 = 7.32</t>
         </is>
       </c>
-      <c r="F552" s="5" t="n">
-        <v>7.32</v>
-      </c>
+      <c r="F552" s="8" t="n"/>
     </row>
     <row r="553" ht="18" customHeight="1">
       <c r="A553" s="3" t="n"/>
@@ -12788,9 +11806,7 @@
           <t>(4×1.8) = 7.2</t>
         </is>
       </c>
-      <c r="F553" s="5" t="n">
-        <v>7.2</v>
-      </c>
+      <c r="F553" s="8" t="n"/>
     </row>
     <row r="554" ht="18" customHeight="1">
       <c r="A554" s="3" t="n"/>
@@ -12810,9 +11826,7 @@
           <t>[(2.4×3.2)]×2 = 15.36</t>
         </is>
       </c>
-      <c r="F554" s="5" t="n">
-        <v>15.36</v>
-      </c>
+      <c r="F554" s="8" t="n"/>
     </row>
     <row r="555" ht="18" customHeight="1">
       <c r="A555" s="3" t="n"/>
@@ -12832,9 +11846,7 @@
           <t>[(2.4×1.8)]×2 = 8.64</t>
         </is>
       </c>
-      <c r="F555" s="5" t="n">
-        <v>8.640000000000001</v>
-      </c>
+      <c r="F555" s="8" t="n"/>
     </row>
     <row r="556" ht="18" customHeight="1">
       <c r="A556" s="3" t="n"/>
@@ -12854,9 +11866,7 @@
           <t>[(1.8×1.8)]×2 = 6.48</t>
         </is>
       </c>
-      <c r="F556" s="5" t="n">
-        <v>6.48</v>
-      </c>
+      <c r="F556" s="8" t="n"/>
     </row>
     <row r="557" ht="18" customHeight="1">
       <c r="A557" s="3" t="n"/>
@@ -12876,9 +11886,7 @@
           <t>[(1.2×3.05)]×2 = 7.32</t>
         </is>
       </c>
-      <c r="F557" s="5" t="n">
-        <v>7.32</v>
-      </c>
+      <c r="F557" s="8" t="n"/>
     </row>
     <row r="558" ht="18" customHeight="1">
       <c r="A558" s="3" t="n"/>
@@ -12898,9 +11906,7 @@
           <t>(4×1.8) = 7.2</t>
         </is>
       </c>
-      <c r="F558" s="5" t="n">
-        <v>7.2</v>
-      </c>
+      <c r="F558" s="8" t="n"/>
     </row>
     <row r="559" ht="18" customHeight="1">
       <c r="A559" s="3" t="n"/>
@@ -12920,9 +11926,7 @@
           <t>[(2.4×3.2)]×2 = 15.36</t>
         </is>
       </c>
-      <c r="F559" s="5" t="n">
-        <v>15.36</v>
-      </c>
+      <c r="F559" s="8" t="n"/>
     </row>
     <row r="560" ht="18" customHeight="1">
       <c r="A560" s="3" t="n"/>
@@ -12942,9 +11946,7 @@
           <t>[(2.4×1.8)]×2 = 8.64</t>
         </is>
       </c>
-      <c r="F560" s="5" t="n">
-        <v>8.640000000000001</v>
-      </c>
+      <c r="F560" s="8" t="n"/>
     </row>
     <row r="561" ht="18" customHeight="1">
       <c r="A561" s="3" t="n"/>
@@ -12964,9 +11966,7 @@
           <t>[(1.8×1.8)]×2 = 6.48</t>
         </is>
       </c>
-      <c r="F561" s="5" t="n">
-        <v>6.48</v>
-      </c>
+      <c r="F561" s="8" t="n"/>
     </row>
     <row r="562" ht="18" customHeight="1">
       <c r="A562" s="3" t="n"/>
@@ -12986,9 +11986,7 @@
           <t>[(1.2×3.05)]×2 = 7.32</t>
         </is>
       </c>
-      <c r="F562" s="5" t="n">
-        <v>7.32</v>
-      </c>
+      <c r="F562" s="8" t="n"/>
     </row>
     <row r="563" ht="18" customHeight="1">
       <c r="A563" s="3" t="n"/>
@@ -13008,9 +12006,7 @@
           <t>(4×1.8) = 7.2</t>
         </is>
       </c>
-      <c r="F563" s="5" t="n">
-        <v>7.2</v>
-      </c>
+      <c r="F563" s="8" t="n"/>
     </row>
     <row r="564" ht="18" customHeight="1">
       <c r="A564" s="3" t="n"/>
@@ -13030,9 +12026,7 @@
           <t>[(2.4×3.2)]×2 = 15.36</t>
         </is>
       </c>
-      <c r="F564" s="5" t="n">
-        <v>15.36</v>
-      </c>
+      <c r="F564" s="8" t="n"/>
     </row>
     <row r="565" ht="18" customHeight="1">
       <c r="A565" s="3" t="n"/>
@@ -13052,9 +12046,7 @@
           <t>[(2.4×1.8)]×2 = 8.64</t>
         </is>
       </c>
-      <c r="F565" s="5" t="n">
-        <v>8.640000000000001</v>
-      </c>
+      <c r="F565" s="8" t="n"/>
     </row>
     <row r="566" ht="18" customHeight="1">
       <c r="A566" s="3" t="n"/>
@@ -13074,9 +12066,7 @@
           <t>[(1.8×1.8)]×2 = 6.48</t>
         </is>
       </c>
-      <c r="F566" s="5" t="n">
-        <v>6.48</v>
-      </c>
+      <c r="F566" s="8" t="n"/>
     </row>
     <row r="567" ht="18" customHeight="1">
       <c r="A567" s="3" t="n"/>
@@ -13096,9 +12086,7 @@
           <t>[(1.2×3.05)]×2 = 7.32</t>
         </is>
       </c>
-      <c r="F567" s="5" t="n">
-        <v>7.32</v>
-      </c>
+      <c r="F567" s="8" t="n"/>
     </row>
     <row r="568" ht="18" customHeight="1">
       <c r="A568" s="3" t="n"/>
@@ -13114,9 +12102,7 @@
           <t>8.64 + 8.64 + 3.24 + 1.8 + 7.32 + 7.2 + 15.36 + 8.64 + 6.48 + 7.32 + 7.2 + 15.36 + 8.64 + 6.48 + 7.32 + 7.2 + 15.36 + 8.64 + 6.48 + 7.32 = 164.64 ≈ 164.64</t>
         </is>
       </c>
-      <c r="F568" s="8" t="n">
-        <v>164.64</v>
-      </c>
+      <c r="F568" s="8" t="n"/>
     </row>
     <row r="569" ht="18" customHeight="1">
       <c r="A569" s="3" t="n">
@@ -13143,7 +12129,7 @@
         </is>
       </c>
       <c r="F569" s="5" t="n">
-        <v>219.2982</v>
+        <v>219.3</v>
       </c>
     </row>
     <row r="570" ht="18" customHeight="1">
@@ -13160,9 +12146,7 @@
           <t>219.2982 ≈ 219.30</t>
         </is>
       </c>
-      <c r="F570" s="8" t="n">
-        <v>219.3</v>
-      </c>
+      <c r="F570" s="8" t="n"/>
     </row>
     <row r="571" ht="18" customHeight="1">
       <c r="A571" s="3" t="n">
@@ -13189,7 +12173,7 @@
         </is>
       </c>
       <c r="F571" s="5" t="n">
-        <v>200.1282</v>
+        <v>200.13</v>
       </c>
     </row>
     <row r="572" ht="18" customHeight="1">
@@ -13206,9 +12190,7 @@
           <t>200.1282 ≈ 200.13</t>
         </is>
       </c>
-      <c r="F572" s="8" t="n">
-        <v>200.13</v>
-      </c>
+      <c r="F572" s="8" t="n"/>
     </row>
     <row r="573" ht="18" customHeight="1">
       <c r="A573" s="3" t="n">
@@ -13234,7 +12216,7 @@
           <t>计算书中无依据，需补充</t>
         </is>
       </c>
-      <c r="F573" s="5" t="inlineStr">
+      <c r="F573" s="8" t="inlineStr">
         <is>
           <t>需补充</t>
         </is>
@@ -13265,7 +12247,7 @@
         </is>
       </c>
       <c r="F574" s="5" t="n">
-        <v>4.5787</v>
+        <v>4.58</v>
       </c>
     </row>
     <row r="575" ht="18" customHeight="1">
@@ -13282,9 +12264,7 @@
           <t>4.5787 ≈ 4.58</t>
         </is>
       </c>
-      <c r="F575" s="8" t="n">
-        <v>4.58</v>
-      </c>
+      <c r="F575" s="8" t="n"/>
     </row>
     <row r="576" ht="18" customHeight="1">
       <c r="A576" s="3" t="n">
@@ -13311,7 +12291,7 @@
         </is>
       </c>
       <c r="F576" s="5" t="n">
-        <v>200.1282</v>
+        <v>200.13</v>
       </c>
     </row>
     <row r="577" ht="18" customHeight="1">
@@ -13328,9 +12308,7 @@
           <t>200.1282 ≈ 200.13</t>
         </is>
       </c>
-      <c r="F577" s="8" t="n">
-        <v>200.13</v>
-      </c>
+      <c r="F577" s="8" t="n"/>
     </row>
     <row r="578" ht="18" customHeight="1">
       <c r="A578" s="3" t="n">
@@ -13357,7 +12335,7 @@
         </is>
       </c>
       <c r="F578" s="5" t="n">
-        <v>172.0871</v>
+        <v>796.17</v>
       </c>
     </row>
     <row r="579" ht="18" customHeight="1">
@@ -13378,9 +12356,7 @@
           <t>(15.26×13.26)+1.8131-1.404-0.62-0.4428-0.7875 = 200.9065</t>
         </is>
       </c>
-      <c r="F579" s="5" t="n">
-        <v>200.9065</v>
-      </c>
+      <c r="F579" s="8" t="n"/>
     </row>
     <row r="580" ht="18" customHeight="1">
       <c r="A580" s="3" t="n"/>
@@ -13400,9 +12376,7 @@
           <t>(15.26×13.26)-1.404-0.62-0.4428 = 199.8808</t>
         </is>
       </c>
-      <c r="F580" s="5" t="n">
-        <v>199.8808</v>
-      </c>
+      <c r="F580" s="8" t="n"/>
     </row>
     <row r="581" ht="18" customHeight="1">
       <c r="A581" s="3" t="n"/>
@@ -13422,9 +12396,7 @@
           <t>(15.26×13.26)-1.404-0.62-0.4428 = 199.8808</t>
         </is>
       </c>
-      <c r="F581" s="5" t="n">
-        <v>199.8808</v>
-      </c>
+      <c r="F581" s="8" t="n"/>
     </row>
     <row r="582" ht="18" customHeight="1">
       <c r="A582" s="3" t="n"/>
@@ -13444,9 +12416,7 @@
           <t>(7.41×3.16) = 23.4156</t>
         </is>
       </c>
-      <c r="F582" s="5" t="n">
-        <v>23.4156</v>
-      </c>
+      <c r="F582" s="8" t="n"/>
     </row>
     <row r="583" ht="18" customHeight="1">
       <c r="A583" s="3" t="n"/>
@@ -13462,9 +12432,7 @@
           <t>172.0871 + 200.9065 + 199.8808 + 199.8808 + 23.4156 = 796.1708 ≈ 796.17</t>
         </is>
       </c>
-      <c r="F583" s="8" t="n">
-        <v>796.17</v>
-      </c>
+      <c r="F583" s="8" t="n"/>
     </row>
     <row r="584" ht="18" customHeight="1">
       <c r="A584" s="3" t="n">
@@ -13491,7 +12459,7 @@
         </is>
       </c>
       <c r="F584" s="5" t="n">
-        <v>4.5787</v>
+        <v>4.58</v>
       </c>
     </row>
     <row r="585" ht="18" customHeight="1">
@@ -13508,9 +12476,7 @@
           <t>4.5787 ≈ 4.58</t>
         </is>
       </c>
-      <c r="F585" s="8" t="n">
-        <v>4.58</v>
-      </c>
+      <c r="F585" s="8" t="n"/>
     </row>
     <row r="586" ht="18" customHeight="1">
       <c r="A586" s="3" t="n">
@@ -13537,7 +12503,7 @@
         </is>
       </c>
       <c r="F586" s="5" t="n">
-        <v>58.63</v>
+        <v>264.13</v>
       </c>
     </row>
     <row r="587" ht="18" customHeight="1">
@@ -13558,9 +12524,7 @@
           <t>13.26+1.425-0.905-1.2 + 15.02+1.64-1.02-1.8 + 13.26+1.9569-1.405-1.2 + 15.26-4.8 + [5.85+1.355-0.975]×2 = 61.9519</t>
         </is>
       </c>
-      <c r="F587" s="5" t="n">
-        <v>61.9519</v>
-      </c>
+      <c r="F587" s="8" t="n"/>
     </row>
     <row r="588" ht="18" customHeight="1">
       <c r="A588" s="3" t="n"/>
@@ -13580,9 +12544,7 @@
           <t>[5.85+1.355-0.975]×2 + 15.26-4.8 + 13.26+1.9569-1.405-1.2 + 15.02+1.64-1.02-1.8 + 13.26+1.425-0.905-1.2 = 61.9519</t>
         </is>
       </c>
-      <c r="F588" s="5" t="n">
-        <v>61.9519</v>
-      </c>
+      <c r="F588" s="8" t="n"/>
     </row>
     <row r="589" ht="18" customHeight="1">
       <c r="A589" s="3" t="n"/>
@@ -13602,9 +12564,7 @@
           <t>[5.85+1.355-0.975]×2 + 15.26-4.8 + 13.26+1.9569-1.405-1.2 + 15.02+1.64-1.02-1.8 + 13.26+1.425-0.905-1.2 = 61.9519</t>
         </is>
       </c>
-      <c r="F589" s="5" t="n">
-        <v>61.9519</v>
-      </c>
+      <c r="F589" s="8" t="n"/>
     </row>
     <row r="590" ht="18" customHeight="1">
       <c r="A590" s="3" t="n"/>
@@ -13624,9 +12584,7 @@
           <t>[3.16]×2 + 7.41 + 7.41-1.5 = 19.64</t>
         </is>
       </c>
-      <c r="F590" s="5" t="n">
-        <v>19.64</v>
-      </c>
+      <c r="F590" s="8" t="n"/>
     </row>
     <row r="591" ht="18" customHeight="1">
       <c r="A591" s="3" t="n"/>
@@ -13642,9 +12600,7 @@
           <t>58.63 + 61.9519 + 61.9519 + 61.9519 + 19.64 = 264.1257 ≈ 264.13</t>
         </is>
       </c>
-      <c r="F591" s="8" t="n">
-        <v>264.13</v>
-      </c>
+      <c r="F591" s="8" t="n"/>
     </row>
     <row r="592" ht="18" customHeight="1">
       <c r="A592" s="3" t="n">
@@ -13671,7 +12627,7 @@
         </is>
       </c>
       <c r="F592" s="5" t="n">
-        <v>161.8592</v>
+        <v>770.35</v>
       </c>
     </row>
     <row r="593" ht="32" customHeight="1">
@@ -13692,9 +12648,7 @@
           <t>13.74×3.6-5.004+5.565-6.605+6.7285-3.66 + 15.74×3.6-3.564+5.424-5.9+6.0475-22.56 + 13.74×3.6-5.904+6.4955-6.4675+6.5885-3.66 + 15.5×3.6-5.4+6.428-5.6+5.74-14.4 = 171.6845</t>
         </is>
       </c>
-      <c r="F593" s="5" t="n">
-        <v>171.6845</v>
-      </c>
+      <c r="F593" s="8" t="n"/>
     </row>
     <row r="594" ht="32" customHeight="1">
       <c r="A594" s="3" t="n"/>
@@ -13714,9 +12668,7 @@
           <t>13.74×3.6-5.004+5.565-6.605+6.7285-3.66 + 15.74×3.6-3.564+5.424-5.9+6.0475-22.56 + 13.74×3.6-5.904+6.4955-6.4675+6.5885-3.66 + 15.5×3.6-5.4+6.428-5.6+5.74-14.4 = 171.6845</t>
         </is>
       </c>
-      <c r="F594" s="5" t="n">
-        <v>171.6845</v>
-      </c>
+      <c r="F594" s="8" t="n"/>
     </row>
     <row r="595" ht="32" customHeight="1">
       <c r="A595" s="3" t="n"/>
@@ -13736,9 +12688,7 @@
           <t>13.74×3.6-5.004+5.565-6.605+6.7285-3.66 + 15.74×3.6-3.564+5.424-5.9+6.0475-22.56 + 13.74×3.6-5.904+6.4955-6.4675+6.5873-3.66 + 15.5×3.6-5.4+6.428-5.6+5.74-13.59 = 172.4933</t>
         </is>
       </c>
-      <c r="F595" s="5" t="n">
-        <v>172.4933</v>
-      </c>
+      <c r="F595" s="8" t="n"/>
     </row>
     <row r="596" ht="32" customHeight="1">
       <c r="A596" s="3" t="n"/>
@@ -13758,9 +12708,7 @@
           <t>(13.74×1.07+1.6344)-0.2843+0.4013+1.9356-4.0413 + (15.74×1.07+1.8744)-0.8662+1.3375+2.1118-4.5 + (5.85×1.07+0.6948)-0.2903+0.5403+0.8243-1.68 + (7.65×3.642+0.9108)-0.75+1.3932-2.22+2.2927+1.1166-1.5228 + (3.642×3.64+0.444)-1.47+1.3922-1.26+1.2915+0.5228-0.7352 + (12.1×1.07+1.4448)-0.0059+0.1391+1.7006-3.6213 = 92.6237</t>
         </is>
       </c>
-      <c r="F596" s="5" t="n">
-        <v>92.6237</v>
-      </c>
+      <c r="F596" s="8" t="n"/>
     </row>
     <row r="597" ht="18" customHeight="1">
       <c r="A597" s="3" t="n"/>
@@ -13776,9 +12724,7 @@
           <t>161.8592 + 171.6845 + 171.6845 + 172.4933 + 92.6237 = 770.3452 ≈ 770.35</t>
         </is>
       </c>
-      <c r="F597" s="8" t="n">
-        <v>770.35</v>
-      </c>
+      <c r="F597" s="8" t="n"/>
     </row>
     <row r="598" ht="32" customHeight="1">
       <c r="A598" s="3" t="n">
@@ -13805,7 +12751,7 @@
         </is>
       </c>
       <c r="F598" s="5" t="n">
-        <v>187.5849</v>
+        <v>962.71</v>
       </c>
     </row>
     <row r="599" ht="18" customHeight="1">
@@ -13826,9 +12772,7 @@
           <t>3.165×1.5-0.2475+0.2242-1.53-0.48+1.2 + [1.5×1.455-0.24+0.2205-0.7122+0.7122]×2 + 3.165×1.5-0.315 = 12.6727</t>
         </is>
       </c>
-      <c r="F599" s="5" t="n">
-        <v>12.6727</v>
-      </c>
+      <c r="F599" s="8" t="n"/>
     </row>
     <row r="600" ht="32" customHeight="1">
       <c r="A600" s="3" t="n"/>
@@ -13848,9 +12792,7 @@
           <t>46.3392-3.1814+4.8397-3.66-5.3027+5.2265 + (3.6×3.16+41.3344)-3.5734+5.486-15.12-3.617+4.337 + 46.8969-4.994+6.5147-3.66-5.5729+5.5078-0.11-0.4277 + 15.26×3.51-1.7901+1.696-22.56-4.5725+4.495 + 20.9313-3.47+4.6402-2.5926+2.5926 + 5.85×3.5-3.4125+4.5985-2.1938+2.1313 = 203.1701</t>
         </is>
       </c>
-      <c r="F600" s="5" t="n">
-        <v>203.1701</v>
-      </c>
+      <c r="F600" s="8" t="n"/>
     </row>
     <row r="601" ht="32" customHeight="1">
       <c r="A601" s="3" t="n"/>
@@ -13870,9 +12812,7 @@
           <t>20.9313-3.47+4.6402-2.5926+2.5926 + 5.85×3.5-3.4125+4.5985-2.1938+2.1313 + 15.26×3.51-1.7901+1.696-22.56-4.5725+4.495 + 46.8969-4.994+6.5147-3.66-5.5729+5.5078-0.11-0.4277 + (3.6×3.16+41.3344)-3.5734+5.486-15.12-3.617+4.337 + 46.3392-3.1814+4.8397-3.66-5.3027+5.2265 = 203.1701</t>
         </is>
       </c>
-      <c r="F601" s="5" t="n">
-        <v>203.1701</v>
-      </c>
+      <c r="F601" s="8" t="n"/>
     </row>
     <row r="602" ht="32" customHeight="1">
       <c r="A602" s="3" t="n"/>
@@ -13892,9 +12832,7 @@
           <t>20.9313-3.47+4.6402-2.5926+2.5926 + 20.528-3.428+4.5985-2.2313+2.1187 + 15.26×3.6-1.836+1.696-22.56-5.9+4.35 + 47.0211-5.0058+6.5137-3.66-5.6854+5.4953-0.11-0.4277 + (3.6×3.16+11.86×3.6)-3.672+5.5-13.59-5.6+4.5 + 46.374-3.201+4.8307-3.66-5.318+5.083 = 203.8336</t>
         </is>
       </c>
-      <c r="F602" s="5" t="n">
-        <v>203.8336</v>
-      </c>
+      <c r="F602" s="8" t="n"/>
     </row>
     <row r="603" ht="18" customHeight="1">
       <c r="A603" s="3" t="n"/>
@@ -13914,9 +12852,7 @@
           <t>3.16×3-0.03+0.029-0.315 + 21.542-0.0295+0.029-0.0525 + 3.16×2.9-0.029+0.0278 + 21.542-0.0295+0.029-3.15-0.4937+0.4937-0.0525 = 58.1547</t>
         </is>
       </c>
-      <c r="F603" s="5" t="n">
-        <v>58.1547</v>
-      </c>
+      <c r="F603" s="8" t="n"/>
     </row>
     <row r="604" ht="32" customHeight="1">
       <c r="A604" s="3" t="n"/>
@@ -13936,9 +12872,7 @@
           <t>(27.6045+0.9108)-0.4932+1.2343-3.15-2.3188+2.194 + (5.61×(1.07+0.12))-0.0107+0.0107 + (15.26×(1.07+0.12))-0.3082+0.2889 + (13.26×(1.07+0.12))-0.0053+0.0053 + (12.563+0.4152)-0.8532+1.272-0.945+0.9765 + (11.86×(1.07+0.12))-0.0053+0.0053 = 94.1189</t>
         </is>
       </c>
-      <c r="F604" s="5" t="n">
-        <v>94.1189</v>
-      </c>
+      <c r="F604" s="8" t="n"/>
     </row>
     <row r="605" ht="18" customHeight="1">
       <c r="A605" s="3" t="n"/>
@@ -13954,9 +12888,7 @@
           <t>187.5849 + 12.6727 + 203.1701 + 203.1701 + 203.8336 + 58.1547 + 94.1189 = 962.705 ≈ 962.71</t>
         </is>
       </c>
-      <c r="F605" s="8" t="n">
-        <v>962.71</v>
-      </c>
+      <c r="F605" s="8" t="n"/>
     </row>
     <row r="606" ht="18" customHeight="1">
       <c r="A606" s="3" t="n">
@@ -13983,7 +12915,7 @@
         </is>
       </c>
       <c r="F606" s="5" t="n">
-        <v>16.878</v>
+        <v>16.88</v>
       </c>
     </row>
     <row r="607" ht="18" customHeight="1">
@@ -14000,9 +12932,7 @@
           <t>16.878 ≈ 16.88</t>
         </is>
       </c>
-      <c r="F607" s="8" t="n">
-        <v>16.88</v>
-      </c>
+      <c r="F607" s="8" t="n"/>
     </row>
     <row r="608" ht="18" customHeight="1">
       <c r="A608" s="3" t="n">
@@ -14029,7 +12959,7 @@
         </is>
       </c>
       <c r="F608" s="5" t="n">
-        <v>192.2586</v>
+        <v>908.76</v>
       </c>
     </row>
     <row r="609" ht="32" customHeight="1">
@@ -14050,9 +12980,7 @@
           <t>(3×2.28)+2.7827+0.0141-0.9137-0.0137 + (15.26×1.38)+10.9493+0.0863-2.8487-0.085 + (4.33×3.15)+5.1219+0.0144-1.445-0.0145 + (5.73×2.28+8.73×2.05+11.88×4.45)+26.639+0.0678-7.4369-0.07 + (1.68×0.12+3.16×1.8)+4.661+0.0081-0.9994-0.0077 + (6.48×4.35+3.2×1.68+5.85×3.08)+21.8681+0.059-5.4175-0.062 = 235.7941</t>
         </is>
       </c>
-      <c r="F609" s="5" t="n">
-        <v>235.7941</v>
-      </c>
+      <c r="F609" s="8" t="n"/>
     </row>
     <row r="610" ht="32" customHeight="1">
       <c r="A610" s="3" t="n"/>
@@ -14072,9 +13000,7 @@
           <t>(8.78×5.73+6.5×3+4.45×3.15)+26.639+0.0678-7.4369-0.07 + (4.33×3.15)+5.1219+0.0144-1.445-0.0145 + (15.26×1.38)+10.9492+0.0863-2.8487-0.085 + (3×2.28)+2.7827+0.0141-0.9137-0.0137 + (6.48×4.35+3.2×1.68+5.85×3.08)+21.8681+0.059-5.4175-0.062 + (1.68×0.12+3.16×1.8)+4.661+0.0081-0.9994-0.0077 = 235.7941</t>
         </is>
       </c>
-      <c r="F610" s="5" t="n">
-        <v>235.7941</v>
-      </c>
+      <c r="F610" s="8" t="n"/>
     </row>
     <row r="611" ht="18" customHeight="1">
       <c r="A611" s="3" t="n"/>
@@ -14094,9 +13020,7 @@
           <t>77.2942+18.6475+0.1879-9.1212-0.1917 + (11.35×8.78)+30.8617+0.0536-8.4587-0.0542 + (1.68×0.12+3.16×1.8)+5.8422+0.0081-0.9994-0.0077 = 219.6049</t>
         </is>
       </c>
-      <c r="F611" s="5" t="n">
-        <v>219.6049</v>
-      </c>
+      <c r="F611" s="8" t="n"/>
     </row>
     <row r="612" ht="18" customHeight="1">
       <c r="A612" s="3" t="n"/>
@@ -14116,9 +13040,7 @@
           <t>(7.41×3.16)+2.686+0.0099-0.79-0.0099 = 25.3116</t>
         </is>
       </c>
-      <c r="F612" s="5" t="n">
-        <v>25.3116</v>
-      </c>
+      <c r="F612" s="8" t="n"/>
     </row>
     <row r="613" ht="18" customHeight="1">
       <c r="A613" s="3" t="n"/>
@@ -14134,9 +13056,7 @@
           <t>192.2586 + 235.7941 + 235.7941 + 219.6049 + 25.3116 = 908.7633 ≈ 908.76</t>
         </is>
       </c>
-      <c r="F613" s="8" t="n">
-        <v>908.76</v>
-      </c>
+      <c r="F613" s="8" t="n"/>
     </row>
     <row r="614" ht="18" customHeight="1">
       <c r="A614" s="3" t="n">
@@ -14163,7 +13083,7 @@
         </is>
       </c>
       <c r="F614" s="5" t="n">
-        <v>161.8592</v>
+        <v>770.35</v>
       </c>
     </row>
     <row r="615" ht="32" customHeight="1">
@@ -14184,9 +13104,7 @@
           <t>13.74×3.6-5.004+5.565-6.605+6.7285-3.66 + 15.74×3.6-3.564+5.424-5.9+6.0475-22.56 + 13.74×3.6-5.904+6.4955-6.4675+6.5885-3.66 + 15.5×3.6-5.4+6.428-5.6+5.74-14.4 = 171.6845</t>
         </is>
       </c>
-      <c r="F615" s="5" t="n">
-        <v>171.6845</v>
-      </c>
+      <c r="F615" s="8" t="n"/>
     </row>
     <row r="616" ht="32" customHeight="1">
       <c r="A616" s="3" t="n"/>
@@ -14206,9 +13124,7 @@
           <t>13.74×3.6-5.004+5.565-6.605+6.7285-3.66 + 15.74×3.6-3.564+5.424-5.9+6.0475-22.56 + 13.74×3.6-5.904+6.4955-6.4675+6.5885-3.66 + 15.5×3.6-5.4+6.428-5.6+5.74-14.4 = 171.6845</t>
         </is>
       </c>
-      <c r="F616" s="5" t="n">
-        <v>171.6845</v>
-      </c>
+      <c r="F616" s="8" t="n"/>
     </row>
     <row r="617" ht="32" customHeight="1">
       <c r="A617" s="3" t="n"/>
@@ -14228,9 +13144,7 @@
           <t>13.74×3.6-5.004+5.565-6.605+6.7285-3.66 + 15.74×3.6-3.564+5.424-5.9+6.0475-22.56 + 13.74×3.6-5.904+6.4955-6.4675+6.5873-3.66 + 15.5×3.6-5.4+6.428-5.6+5.74-13.59 = 172.4933</t>
         </is>
       </c>
-      <c r="F617" s="5" t="n">
-        <v>172.4933</v>
-      </c>
+      <c r="F617" s="8" t="n"/>
     </row>
     <row r="618" ht="32" customHeight="1">
       <c r="A618" s="3" t="n"/>
@@ -14250,9 +13164,7 @@
           <t>(13.74×1.07+1.6344)-0.2843+0.4013+1.9356-4.0413 + (15.74×1.07+1.8744)-0.8662+1.3375+2.1118-4.5 + (5.85×1.07+0.6948)-0.2903+0.5403+0.8243-1.68 + (7.65×3.642+0.9108)-0.75+1.3932-2.22+2.2927+1.1166-1.5228 + (3.642×3.64+0.444)-1.47+1.3922-1.26+1.2915+0.5228-0.7352 + (12.1×1.07+1.4448)-0.0059+0.1391+1.7006-3.6213 = 92.6237</t>
         </is>
       </c>
-      <c r="F618" s="5" t="n">
-        <v>92.6237</v>
-      </c>
+      <c r="F618" s="8" t="n"/>
     </row>
     <row r="619" ht="18" customHeight="1">
       <c r="A619" s="3" t="n"/>
@@ -14268,9 +13180,7 @@
           <t>161.8592 + 171.6845 + 171.6845 + 172.4933 + 92.6237 = 770.3452 ≈ 770.35</t>
         </is>
       </c>
-      <c r="F619" s="8" t="n">
-        <v>770.35</v>
-      </c>
+      <c r="F619" s="8" t="n"/>
     </row>
     <row r="620" ht="32" customHeight="1">
       <c r="A620" s="3" t="n">
@@ -14297,7 +13207,7 @@
         </is>
       </c>
       <c r="F620" s="5" t="n">
-        <v>187.5849</v>
+        <v>962.71</v>
       </c>
     </row>
     <row r="621" ht="18" customHeight="1">
@@ -14318,9 +13228,7 @@
           <t>3.165×1.5-0.2475+0.2242-1.53-0.48+1.2 + [1.5×1.455-0.24+0.2205-0.7122+0.7122]×2 + 3.165×1.5-0.315 = 12.6727</t>
         </is>
       </c>
-      <c r="F621" s="5" t="n">
-        <v>12.6727</v>
-      </c>
+      <c r="F621" s="8" t="n"/>
     </row>
     <row r="622" ht="32" customHeight="1">
       <c r="A622" s="3" t="n"/>
@@ -14340,9 +13248,7 @@
           <t>46.3392-3.1814+4.8397-3.66-5.3027+5.2265 + (3.6×3.16+41.3344)-3.5734+5.486-15.12-3.617+4.337 + 46.8969-4.994+6.5147-3.66-5.5729+5.5078-0.11-0.4277 + 15.26×3.51-1.7901+1.696-22.56-4.5725+4.495 + 20.9313-3.47+4.6402-2.5926+2.5926 + 5.85×3.5-3.4125+4.5985-2.1938+2.1313 = 203.1701</t>
         </is>
       </c>
-      <c r="F622" s="5" t="n">
-        <v>203.1701</v>
-      </c>
+      <c r="F622" s="8" t="n"/>
     </row>
     <row r="623" ht="32" customHeight="1">
       <c r="A623" s="3" t="n"/>
@@ -14362,9 +13268,7 @@
           <t>20.9313-3.47+4.6402-2.5926+2.5926 + 5.85×3.5-3.4125+4.5985-2.1938+2.1313 + 15.26×3.51-1.7901+1.696-22.56-4.5725+4.495 + 46.8969-4.994+6.5147-3.66-5.5729+5.5078-0.11-0.4277 + (3.6×3.16+41.3344)-3.5734+5.486-15.12-3.617+4.337 + 46.3392-3.1814+4.8397-3.66-5.3027+5.2265 = 203.1701</t>
         </is>
       </c>
-      <c r="F623" s="5" t="n">
-        <v>203.1701</v>
-      </c>
+      <c r="F623" s="8" t="n"/>
     </row>
     <row r="624" ht="32" customHeight="1">
       <c r="A624" s="3" t="n"/>
@@ -14384,9 +13288,7 @@
           <t>20.9313-3.47+4.6402-2.5926+2.5926 + 20.528-3.428+4.5985-2.2313+2.1187 + 15.26×3.6-1.836+1.696-22.56-5.9+4.35 + 47.0211-5.0058+6.5137-3.66-5.6854+5.4953-0.11-0.4277 + (3.6×3.16+11.86×3.6)-3.672+5.5-13.59-5.6+4.5 + 46.374-3.201+4.8307-3.66-5.318+5.083 = 203.8336</t>
         </is>
       </c>
-      <c r="F624" s="5" t="n">
-        <v>203.8336</v>
-      </c>
+      <c r="F624" s="8" t="n"/>
     </row>
     <row r="625" ht="18" customHeight="1">
       <c r="A625" s="3" t="n"/>
@@ -14406,9 +13308,7 @@
           <t>3.16×3-0.03+0.029-0.315 + 21.542-0.0295+0.029-0.0525 + 3.16×2.9-0.029+0.0278 + 21.542-0.0295+0.029-3.15-0.4937+0.4937-0.0525 = 58.1547</t>
         </is>
       </c>
-      <c r="F625" s="5" t="n">
-        <v>58.1547</v>
-      </c>
+      <c r="F625" s="8" t="n"/>
     </row>
     <row r="626" ht="32" customHeight="1">
       <c r="A626" s="3" t="n"/>
@@ -14428,9 +13328,7 @@
           <t>(27.6045+0.9108)-0.4932+1.2343-3.15-2.3188+2.194 + (5.61×(1.07+0.12))-0.0107+0.0107 + (15.26×(1.07+0.12))-0.3082+0.2889 + (13.26×(1.07+0.12))-0.0053+0.0053 + (12.563+0.4152)-0.8532+1.272-0.945+0.9765 + (11.86×(1.07+0.12))-0.0053+0.0053 = 94.1189</t>
         </is>
       </c>
-      <c r="F626" s="5" t="n">
-        <v>94.1189</v>
-      </c>
+      <c r="F626" s="8" t="n"/>
     </row>
     <row r="627" ht="18" customHeight="1">
       <c r="A627" s="3" t="n"/>
@@ -14446,9 +13344,7 @@
           <t>187.5849 + 12.6727 + 203.1701 + 203.1701 + 203.8336 + 58.1547 + 94.1189 = 962.705 ≈ 962.71</t>
         </is>
       </c>
-      <c r="F627" s="8" t="n">
-        <v>962.71</v>
-      </c>
+      <c r="F627" s="8" t="n"/>
     </row>
     <row r="628" ht="18" customHeight="1">
       <c r="A628" s="3" t="n">
@@ -14475,7 +13371,7 @@
         </is>
       </c>
       <c r="F628" s="5" t="n">
-        <v>192.2586</v>
+        <v>908.76</v>
       </c>
     </row>
     <row r="629" ht="32" customHeight="1">
@@ -14496,9 +13392,7 @@
           <t>(3×2.28)+2.7827+0.0141-0.9137-0.0137 + (15.26×1.38)+10.9493+0.0863-2.8487-0.085 + (4.33×3.15)+5.1219+0.0144-1.445-0.0145 + (5.73×2.28+8.73×2.05+11.88×4.45)+26.639+0.0678-7.4369-0.07 + (1.68×0.12+3.16×1.8)+4.661+0.0081-0.9994-0.0077 + (6.48×4.35+3.2×1.68+5.85×3.08)+21.8681+0.059-5.4175-0.062 = 235.7941</t>
         </is>
       </c>
-      <c r="F629" s="5" t="n">
-        <v>235.7941</v>
-      </c>
+      <c r="F629" s="8" t="n"/>
     </row>
     <row r="630" ht="32" customHeight="1">
       <c r="A630" s="3" t="n"/>
@@ -14518,9 +13412,7 @@
           <t>(8.78×5.73+6.5×3+4.45×3.15)+26.639+0.0678-7.4369-0.07 + (4.33×3.15)+5.1219+0.0144-1.445-0.0145 + (15.26×1.38)+10.9492+0.0863-2.8487-0.085 + (3×2.28)+2.7827+0.0141-0.9137-0.0137 + (6.48×4.35+3.2×1.68+5.85×3.08)+21.8681+0.059-5.4175-0.062 + (1.68×0.12+3.16×1.8)+4.661+0.0081-0.9994-0.0077 = 235.7941</t>
         </is>
       </c>
-      <c r="F630" s="5" t="n">
-        <v>235.7941</v>
-      </c>
+      <c r="F630" s="8" t="n"/>
     </row>
     <row r="631" ht="18" customHeight="1">
       <c r="A631" s="3" t="n"/>
@@ -14540,9 +13432,7 @@
           <t>77.2942+18.6475+0.1879-9.1212-0.1917 + (11.35×8.78)+30.8617+0.0536-8.4587-0.0542 + (1.68×0.12+3.16×1.8)+5.8422+0.0081-0.9994-0.0077 = 219.6049</t>
         </is>
       </c>
-      <c r="F631" s="5" t="n">
-        <v>219.6049</v>
-      </c>
+      <c r="F631" s="8" t="n"/>
     </row>
     <row r="632" ht="18" customHeight="1">
       <c r="A632" s="3" t="n"/>
@@ -14562,9 +13452,7 @@
           <t>(7.41×3.16)+2.686+0.0099-0.79-0.0099 = 25.3116</t>
         </is>
       </c>
-      <c r="F632" s="5" t="n">
-        <v>25.3116</v>
-      </c>
+      <c r="F632" s="8" t="n"/>
     </row>
     <row r="633" ht="18" customHeight="1">
       <c r="A633" s="3" t="n"/>
@@ -14580,54 +13468,82 @@
           <t>192.2586 + 235.7941 + 235.7941 + 219.6049 + 25.3116 = 908.7633 ≈ 908.76</t>
         </is>
       </c>
-      <c r="F633" s="8" t="n">
-        <v>908.76</v>
-      </c>
+      <c r="F633" s="8" t="n"/>
     </row>
   </sheetData>
-  <mergeCells count="143">
+  <mergeCells count="214">
     <mergeCell ref="A223:A269"/>
     <mergeCell ref="B374:B392"/>
     <mergeCell ref="B571:B572"/>
     <mergeCell ref="A144:A146"/>
+    <mergeCell ref="F109:F122"/>
     <mergeCell ref="B529:B533"/>
+    <mergeCell ref="F574:F575"/>
+    <mergeCell ref="F578:F583"/>
+    <mergeCell ref="F3:F4"/>
     <mergeCell ref="A7:A8"/>
+    <mergeCell ref="F584:F585"/>
+    <mergeCell ref="F571:F572"/>
     <mergeCell ref="B123:B125"/>
     <mergeCell ref="B23:B24"/>
     <mergeCell ref="A27:A28"/>
+    <mergeCell ref="F521:F522"/>
     <mergeCell ref="B299:B322"/>
     <mergeCell ref="B463:B467"/>
+    <mergeCell ref="F58:F108"/>
     <mergeCell ref="A534:A536"/>
     <mergeCell ref="A123:A125"/>
     <mergeCell ref="B126:B130"/>
+    <mergeCell ref="F184:F194"/>
+    <mergeCell ref="F270:F298"/>
     <mergeCell ref="A393:A414"/>
+    <mergeCell ref="F169:F183"/>
+    <mergeCell ref="B29:B32"/>
     <mergeCell ref="A620:A627"/>
-    <mergeCell ref="B29:B32"/>
+    <mergeCell ref="F483:F495"/>
     <mergeCell ref="A217:A222"/>
     <mergeCell ref="B540:B541"/>
+    <mergeCell ref="F523:F528"/>
     <mergeCell ref="B421:B441"/>
     <mergeCell ref="A442:A451"/>
     <mergeCell ref="B496:B508"/>
     <mergeCell ref="B458:B462"/>
+    <mergeCell ref="F11:F15"/>
     <mergeCell ref="A586:A591"/>
+    <mergeCell ref="F196:F200"/>
     <mergeCell ref="A323:A333"/>
+    <mergeCell ref="F548:F568"/>
     <mergeCell ref="A544:A547"/>
+    <mergeCell ref="F223:F269"/>
+    <mergeCell ref="F201:F216"/>
     <mergeCell ref="A473:A477"/>
+    <mergeCell ref="F144:F146"/>
     <mergeCell ref="B614:B619"/>
     <mergeCell ref="A165:A168"/>
     <mergeCell ref="A16:A20"/>
+    <mergeCell ref="F33:F57"/>
     <mergeCell ref="A334:A373"/>
+    <mergeCell ref="F334:F373"/>
     <mergeCell ref="B25:B26"/>
     <mergeCell ref="A463:A467"/>
+    <mergeCell ref="F569:F570"/>
+    <mergeCell ref="F458:F462"/>
+    <mergeCell ref="F7:F8"/>
     <mergeCell ref="A584:A585"/>
     <mergeCell ref="A540:A541"/>
+    <mergeCell ref="F598:F605"/>
     <mergeCell ref="B131:B143"/>
+    <mergeCell ref="F452:F457"/>
     <mergeCell ref="B27:B28"/>
     <mergeCell ref="B162:B164"/>
     <mergeCell ref="B509:B510"/>
     <mergeCell ref="B3:B4"/>
     <mergeCell ref="A608:A613"/>
+    <mergeCell ref="F534:F536"/>
     <mergeCell ref="A169:A183"/>
+    <mergeCell ref="F393:F414"/>
+    <mergeCell ref="F5:F6"/>
+    <mergeCell ref="F217:F222"/>
     <mergeCell ref="A628:A633"/>
     <mergeCell ref="A452:A457"/>
     <mergeCell ref="A158:A159"/>
@@ -14636,25 +13552,36 @@
     <mergeCell ref="B442:B451"/>
     <mergeCell ref="B270:B298"/>
     <mergeCell ref="B592:B597"/>
+    <mergeCell ref="F442:F451"/>
     <mergeCell ref="A511:A520"/>
     <mergeCell ref="A574:A575"/>
+    <mergeCell ref="F415:F420"/>
+    <mergeCell ref="F586:F591"/>
+    <mergeCell ref="F323:F333"/>
     <mergeCell ref="A21:A22"/>
     <mergeCell ref="B523:B528"/>
     <mergeCell ref="B537:B539"/>
+    <mergeCell ref="F592:F597"/>
     <mergeCell ref="A548:A568"/>
     <mergeCell ref="B109:B122"/>
+    <mergeCell ref="F9:F10"/>
     <mergeCell ref="A201:A216"/>
     <mergeCell ref="B473:B477"/>
     <mergeCell ref="A542:A543"/>
     <mergeCell ref="B574:B575"/>
     <mergeCell ref="B578:B583"/>
+    <mergeCell ref="F473:F477"/>
     <mergeCell ref="A23:A24"/>
+    <mergeCell ref="F165:F168"/>
     <mergeCell ref="A415:A420"/>
     <mergeCell ref="A569:A570"/>
+    <mergeCell ref="F463:F467"/>
+    <mergeCell ref="F147:F157"/>
     <mergeCell ref="B628:B633"/>
     <mergeCell ref="B158:B159"/>
     <mergeCell ref="A374:A392"/>
     <mergeCell ref="B223:B269"/>
+    <mergeCell ref="F540:F541"/>
     <mergeCell ref="A9:A10"/>
     <mergeCell ref="B58:B108"/>
     <mergeCell ref="B11:B15"/>
@@ -14664,14 +13591,18 @@
     <mergeCell ref="B160:B161"/>
     <mergeCell ref="A521:A522"/>
     <mergeCell ref="B483:B495"/>
+    <mergeCell ref="F608:F613"/>
     <mergeCell ref="A537:A539"/>
     <mergeCell ref="A496:A508"/>
     <mergeCell ref="A576:A577"/>
     <mergeCell ref="A126:A130"/>
     <mergeCell ref="B534:B536"/>
     <mergeCell ref="A109:A122"/>
+    <mergeCell ref="F511:F520"/>
     <mergeCell ref="B542:B543"/>
     <mergeCell ref="A614:A619"/>
+    <mergeCell ref="F21:F22"/>
+    <mergeCell ref="F123:F125"/>
     <mergeCell ref="A571:A572"/>
     <mergeCell ref="A421:A441"/>
     <mergeCell ref="B201:B216"/>
@@ -14679,9 +13610,15 @@
     <mergeCell ref="A529:A533"/>
     <mergeCell ref="B334:B373"/>
     <mergeCell ref="B569:B570"/>
+    <mergeCell ref="F468:F472"/>
+    <mergeCell ref="F542:F543"/>
+    <mergeCell ref="F23:F24"/>
     <mergeCell ref="A147:A157"/>
+    <mergeCell ref="F620:F627"/>
     <mergeCell ref="A483:A495"/>
     <mergeCell ref="B9:B10"/>
+    <mergeCell ref="F606:F607"/>
+    <mergeCell ref="F374:F392"/>
     <mergeCell ref="B544:B547"/>
     <mergeCell ref="B393:B414"/>
     <mergeCell ref="A29:A32"/>
@@ -14689,33 +13626,51 @@
     <mergeCell ref="A131:A143"/>
     <mergeCell ref="A458:A462"/>
     <mergeCell ref="B217:B222"/>
+    <mergeCell ref="F537:F539"/>
+    <mergeCell ref="F544:F547"/>
     <mergeCell ref="A162:A164"/>
+    <mergeCell ref="F496:F508"/>
     <mergeCell ref="A598:A605"/>
     <mergeCell ref="A509:A510"/>
+    <mergeCell ref="F16:F20"/>
+    <mergeCell ref="F299:F322"/>
     <mergeCell ref="A1:F1"/>
     <mergeCell ref="B608:B613"/>
+    <mergeCell ref="F126:F130"/>
     <mergeCell ref="B586:B591"/>
     <mergeCell ref="B323:B333"/>
+    <mergeCell ref="F29:F32"/>
     <mergeCell ref="A33:A57"/>
     <mergeCell ref="B21:B22"/>
     <mergeCell ref="A478:A482"/>
+    <mergeCell ref="F25:F26"/>
+    <mergeCell ref="F421:F441"/>
     <mergeCell ref="A468:A472"/>
     <mergeCell ref="B165:B168"/>
     <mergeCell ref="B511:B520"/>
+    <mergeCell ref="F529:F533"/>
     <mergeCell ref="B33:B57"/>
     <mergeCell ref="B147:B157"/>
+    <mergeCell ref="F628:F633"/>
+    <mergeCell ref="F158:F159"/>
     <mergeCell ref="B196:B200"/>
     <mergeCell ref="A606:A607"/>
     <mergeCell ref="A25:A26"/>
     <mergeCell ref="A3:A4"/>
+    <mergeCell ref="F160:F161"/>
+    <mergeCell ref="F614:F619"/>
     <mergeCell ref="B16:B20"/>
     <mergeCell ref="B606:B607"/>
     <mergeCell ref="A5:A6"/>
+    <mergeCell ref="F131:F143"/>
     <mergeCell ref="B598:B605"/>
+    <mergeCell ref="F27:F28"/>
+    <mergeCell ref="F162:F164"/>
+    <mergeCell ref="A58:A108"/>
     <mergeCell ref="B452:B457"/>
-    <mergeCell ref="A58:A108"/>
     <mergeCell ref="B548:B568"/>
     <mergeCell ref="A184:A194"/>
+    <mergeCell ref="F509:F510"/>
     <mergeCell ref="A578:A583"/>
     <mergeCell ref="A270:A298"/>
     <mergeCell ref="A592:A597"/>
@@ -14723,10 +13678,12 @@
     <mergeCell ref="A299:A322"/>
     <mergeCell ref="B5:B6"/>
     <mergeCell ref="B576:B577"/>
+    <mergeCell ref="F478:F482"/>
     <mergeCell ref="A196:A200"/>
     <mergeCell ref="B468:B472"/>
     <mergeCell ref="B521:B522"/>
     <mergeCell ref="B415:B420"/>
+    <mergeCell ref="F576:F577"/>
     <mergeCell ref="B620:B627"/>
     <mergeCell ref="B584:B585"/>
   </mergeCells>
@@ -15477,7 +14434,7 @@
           <t>t</t>
         </is>
       </c>
-      <c r="F25" s="9" t="n">
+      <c r="F25" s="12" t="n">
         <v>0.709</v>
       </c>
     </row>
@@ -15505,7 +14462,7 @@
           <t>t</t>
         </is>
       </c>
-      <c r="F26" s="9" t="n">
+      <c r="F26" s="12" t="n">
         <v>0.492</v>
       </c>
     </row>
@@ -15533,7 +14490,7 @@
           <t>t</t>
         </is>
       </c>
-      <c r="F27" s="9" t="n">
+      <c r="F27" s="12" t="n">
         <v>0.175</v>
       </c>
     </row>
@@ -15561,7 +14518,7 @@
           <t>t</t>
         </is>
       </c>
-      <c r="F28" s="9" t="n">
+      <c r="F28" s="12" t="n">
         <v>0</v>
       </c>
     </row>
@@ -15589,7 +14546,7 @@
           <t>t</t>
         </is>
       </c>
-      <c r="F29" s="9" t="n">
+      <c r="F29" s="12" t="n">
         <v>0.345</v>
       </c>
     </row>
@@ -15617,7 +14574,7 @@
           <t>t</t>
         </is>
       </c>
-      <c r="F30" s="9" t="n">
+      <c r="F30" s="12" t="n">
         <v>2.989</v>
       </c>
     </row>
@@ -15645,7 +14602,7 @@
           <t>t</t>
         </is>
       </c>
-      <c r="F31" s="9" t="n">
+      <c r="F31" s="12" t="n">
         <v>0.968</v>
       </c>
     </row>
@@ -15673,7 +14630,7 @@
           <t>t</t>
         </is>
       </c>
-      <c r="F32" s="9" t="n">
+      <c r="F32" s="12" t="n">
         <v>0.307</v>
       </c>
     </row>
@@ -15701,7 +14658,7 @@
           <t>t</t>
         </is>
       </c>
-      <c r="F33" s="9" t="n">
+      <c r="F33" s="12" t="n">
         <v>1.428</v>
       </c>
     </row>
@@ -15729,7 +14686,7 @@
           <t>t</t>
         </is>
       </c>
-      <c r="F34" s="9" t="n">
+      <c r="F34" s="12" t="n">
         <v>0.717</v>
       </c>
     </row>
@@ -15757,7 +14714,7 @@
           <t>t</t>
         </is>
       </c>
-      <c r="F35" s="9" t="n">
+      <c r="F35" s="12" t="n">
         <v>0.134</v>
       </c>
     </row>
@@ -15785,7 +14742,7 @@
           <t>t</t>
         </is>
       </c>
-      <c r="F36" s="9" t="n">
+      <c r="F36" s="12" t="n">
         <v>2.347</v>
       </c>
     </row>
@@ -15813,7 +14770,7 @@
           <t>t</t>
         </is>
       </c>
-      <c r="F37" s="9" t="n">
+      <c r="F37" s="12" t="n">
         <v>2.172</v>
       </c>
     </row>
@@ -15841,7 +14798,7 @@
           <t>t</t>
         </is>
       </c>
-      <c r="F38" s="9" t="n">
+      <c r="F38" s="12" t="n">
         <v>2.778</v>
       </c>
     </row>
@@ -15869,7 +14826,7 @@
           <t>t</t>
         </is>
       </c>
-      <c r="F39" s="9" t="n">
+      <c r="F39" s="12" t="n">
         <v>0.319</v>
       </c>
     </row>
@@ -15897,7 +14854,7 @@
           <t>t</t>
         </is>
       </c>
-      <c r="F40" s="9" t="n">
+      <c r="F40" s="12" t="n">
         <v>1.029</v>
       </c>
     </row>
@@ -15925,7 +14882,7 @@
           <t>t</t>
         </is>
       </c>
-      <c r="F41" s="9" t="n">
+      <c r="F41" s="12" t="n">
         <v>2.37</v>
       </c>
     </row>
@@ -15953,7 +14910,7 @@
           <t>t</t>
         </is>
       </c>
-      <c r="F42" s="9" t="n">
+      <c r="F42" s="12" t="n">
         <v>2.808</v>
       </c>
     </row>
@@ -15981,7 +14938,7 @@
           <t>t</t>
         </is>
       </c>
-      <c r="F43" s="9" t="n">
+      <c r="F43" s="12" t="n">
         <v>6.289</v>
       </c>
     </row>
@@ -16009,7 +14966,7 @@
           <t>t</t>
         </is>
       </c>
-      <c r="F44" s="9" t="n">
+      <c r="F44" s="12" t="n">
         <v>0.089</v>
       </c>
     </row>
@@ -16037,7 +14994,7 @@
           <t>t</t>
         </is>
       </c>
-      <c r="F45" s="9" t="n">
+      <c r="F45" s="12" t="n">
         <v>0.209</v>
       </c>
     </row>
@@ -16065,7 +15022,7 @@
           <t>t</t>
         </is>
       </c>
-      <c r="F46" s="9" t="n">
+      <c r="F46" s="12" t="n">
         <v>0.417</v>
       </c>
     </row>
@@ -16093,7 +15050,7 @@
           <t>t</t>
         </is>
       </c>
-      <c r="F47" s="9" t="n">
+      <c r="F47" s="12" t="n">
         <v>0.266</v>
       </c>
     </row>
@@ -16122,7 +15079,7 @@
           <t>t</t>
         </is>
       </c>
-      <c r="F48" s="9" t="n">
+      <c r="F48" s="12" t="n">
         <v>0.08799999999999999</v>
       </c>
     </row>
@@ -16151,7 +15108,7 @@
           <t>t</t>
         </is>
       </c>
-      <c r="F49" s="9" t="n">
+      <c r="F49" s="12" t="n">
         <v>0.357</v>
       </c>
     </row>
@@ -16180,7 +15137,7 @@
           <t>t</t>
         </is>
       </c>
-      <c r="F50" s="9" t="n">
+      <c r="F50" s="12" t="n">
         <v>0</v>
       </c>
     </row>
@@ -16209,7 +15166,7 @@
           <t>t</t>
         </is>
       </c>
-      <c r="F51" s="9" t="n">
+      <c r="F51" s="12" t="n">
         <v>0.044</v>
       </c>
     </row>
@@ -16238,7 +15195,7 @@
           <t>t</t>
         </is>
       </c>
-      <c r="F52" s="9" t="n">
+      <c r="F52" s="12" t="n">
         <v>0.001</v>
       </c>
     </row>
@@ -16267,7 +15224,7 @@
           <t>t</t>
         </is>
       </c>
-      <c r="F53" s="9" t="n">
+      <c r="F53" s="12" t="n">
         <v>0.077</v>
       </c>
     </row>
@@ -16296,7 +15253,7 @@
           <t>t</t>
         </is>
       </c>
-      <c r="F54" s="9" t="n">
+      <c r="F54" s="12" t="n">
         <v>0.146</v>
       </c>
     </row>
@@ -16325,7 +15282,7 @@
           <t>t</t>
         </is>
       </c>
-      <c r="F55" s="9" t="n">
+      <c r="F55" s="12" t="n">
         <v>0.021</v>
       </c>
     </row>
@@ -16354,7 +15311,7 @@
           <t>t</t>
         </is>
       </c>
-      <c r="F56" s="9" t="n">
+      <c r="F56" s="12" t="n">
         <v>0.08400000000000001</v>
       </c>
     </row>
@@ -16383,7 +15340,7 @@
           <t>t</t>
         </is>
       </c>
-      <c r="F57" s="9" t="n">
+      <c r="F57" s="12" t="n">
         <v>0.006</v>
       </c>
     </row>
@@ -16412,7 +15369,7 @@
           <t>t</t>
         </is>
       </c>
-      <c r="F58" s="9" t="n">
+      <c r="F58" s="12" t="n">
         <v>0.263</v>
       </c>
     </row>
@@ -16970,541 +15927,541 @@
   </cols>
   <sheetData>
     <row r="1">
-      <c r="A1" s="12" t="inlineStr">
+      <c r="A1" s="13" t="inlineStr">
         <is>
           <t>编制说明</t>
         </is>
       </c>
     </row>
     <row r="2">
-      <c r="A2" s="13" t="inlineStr">
+      <c r="A2" s="14" t="inlineStr">
         <is>
           <t>总体</t>
         </is>
       </c>
-      <c r="B2" s="13" t="n"/>
-      <c r="C2" s="13" t="inlineStr">
+      <c r="B2" s="14" t="n"/>
+      <c r="C2" s="14" t="inlineStr">
         <is>
           <t>数据来源：①广联达《绘图输入构件工程量计算书》（基础层~第5层）；②广联达《钢筋明细表》；③清单模板（74 项）。</t>
         </is>
       </c>
     </row>
     <row r="3">
-      <c r="A3" s="13" t="inlineStr">
+      <c r="A3" s="14" t="inlineStr">
         <is>
           <t>总体</t>
         </is>
       </c>
-      <c r="B3" s="13" t="n"/>
-      <c r="C3" s="13" t="inlineStr">
+      <c r="B3" s="14" t="n"/>
+      <c r="C3" s="14" t="inlineStr">
         <is>
           <t>计算书粒度：每层每个构件编号一行，同编号下计算式相同的图元合并为 [计算式]×n；每个清单项末行为小计。</t>
         </is>
       </c>
     </row>
     <row r="4">
-      <c r="A4" s="13" t="inlineStr">
+      <c r="A4" s="14" t="inlineStr">
         <is>
           <t>总体</t>
         </is>
       </c>
-      <c r="B4" s="13" t="n"/>
-      <c r="C4" s="13" t="inlineStr">
+      <c r="B4" s="14" t="n"/>
+      <c r="C4" s="14" t="inlineStr">
         <is>
           <t>计算式已去掉广联达的尖括号注释，仅保留数值式；各图元结果取广联达原值（4 位小数），清单工程量 m³/㎡/m 取 2 位小数，钢筋 t 取 3 位小数。</t>
         </is>
       </c>
     </row>
     <row r="5">
-      <c r="A5" s="13" t="inlineStr">
+      <c r="A5" s="14" t="inlineStr">
         <is>
           <t>总体</t>
         </is>
       </c>
-      <c r="B5" s="13" t="n"/>
-      <c r="C5" s="13" t="inlineStr">
+      <c r="B5" s="14" t="n"/>
+      <c r="C5" s="14" t="inlineStr">
         <is>
           <t>钢筋明细表导出的“级别”列为空，钢筋级别按清单模板“构件类型+直径→级别”对应关系归类；直径 12/14 过梁钢筋按模板标注 HPB300 保留。</t>
         </is>
       </c>
     </row>
     <row r="6">
-      <c r="A6" s="13" t="inlineStr">
+      <c r="A6" s="14" t="inlineStr">
         <is>
           <t>总体</t>
         </is>
       </c>
-      <c r="B6" s="13" t="n"/>
-      <c r="C6" s="13" t="inlineStr">
+      <c r="B6" s="14" t="n"/>
+      <c r="C6" s="14" t="inlineStr">
         <is>
           <t>钢筋校核：钢筋明细表总重 30182.028kg，已全部分配到各钢筋清单项（不含估算的屋面钢筋网片），分配合计 30182.028kg。</t>
         </is>
       </c>
     </row>
     <row r="7">
-      <c r="A7" s="13" t="inlineStr">
+      <c r="A7" s="14" t="inlineStr">
         <is>
           <t>总体</t>
         </is>
       </c>
-      <c r="B7" s="13" t="n"/>
-      <c r="C7" s="13" t="inlineStr">
+      <c r="B7" s="14" t="n"/>
+      <c r="C7" s="14" t="inlineStr">
         <is>
           <t>标注“需补充”的项目在计算书/钢筋表中无依据，需按图纸另行计算。</t>
         </is>
       </c>
     </row>
     <row r="8">
-      <c r="A8" s="13" t="n"/>
-      <c r="B8" s="13" t="n"/>
-      <c r="C8" s="13" t="n"/>
+      <c r="A8" s="14" t="n"/>
+      <c r="B8" s="14" t="n"/>
+      <c r="C8" s="14" t="n"/>
     </row>
     <row r="9">
-      <c r="A9" s="14" t="inlineStr">
+      <c r="A9" s="15" t="inlineStr">
         <is>
           <t>项目编码</t>
         </is>
       </c>
-      <c r="B9" s="14" t="inlineStr">
+      <c r="B9" s="15" t="inlineStr">
         <is>
           <t>项目名称</t>
         </is>
       </c>
-      <c r="C9" s="14" t="inlineStr">
+      <c r="C9" s="15" t="inlineStr">
         <is>
           <t>说明</t>
         </is>
       </c>
     </row>
     <row r="10">
-      <c r="A10" s="13" t="inlineStr">
+      <c r="A10" s="14" t="inlineStr">
         <is>
           <t>010102007001</t>
         </is>
       </c>
-      <c r="B10" s="13" t="inlineStr">
+      <c r="B10" s="14" t="inlineStr">
         <is>
           <t>回填方</t>
         </is>
       </c>
-      <c r="C10" s="13" t="inlineStr">
+      <c r="C10" s="14" t="inlineStr">
         <is>
           <t>按广联达大开挖土方的“素土回填体积”（基坑回填）汇总；房心回填未含。</t>
         </is>
       </c>
     </row>
     <row r="11">
-      <c r="A11" s="13" t="inlineStr">
+      <c r="A11" s="14" t="inlineStr">
         <is>
           <t>010103001001</t>
         </is>
       </c>
-      <c r="B11" s="13" t="inlineStr">
+      <c r="B11" s="14" t="inlineStr">
         <is>
           <t>平整场地</t>
         </is>
       </c>
-      <c r="C11" s="13" t="inlineStr">
+      <c r="C11" s="14" t="inlineStr">
         <is>
           <t>计算书中无平整场地构件，按首层建筑面积计取；清单模板单位为 m³，规范应为 m²，请核对。</t>
         </is>
       </c>
     </row>
     <row r="12">
-      <c r="A12" s="13" t="inlineStr">
+      <c r="A12" s="14" t="inlineStr">
         <is>
           <t>010103002001</t>
         </is>
       </c>
-      <c r="B12" s="13" t="inlineStr">
+      <c r="B12" s="14" t="inlineStr">
         <is>
           <t>余方弃置</t>
         </is>
       </c>
-      <c r="C12" s="13" t="inlineStr">
+      <c r="C12" s="14" t="inlineStr">
         <is>
           <t>余方弃置 = 挖方总量 − 基坑回填总量（推导值）。</t>
         </is>
       </c>
     </row>
     <row r="13">
-      <c r="A13" s="13" t="inlineStr">
+      <c r="A13" s="14" t="inlineStr">
         <is>
           <t>010501002001</t>
         </is>
       </c>
-      <c r="B13" s="13" t="inlineStr">
+      <c r="B13" s="14" t="inlineStr">
         <is>
           <t>楼地面垫层</t>
         </is>
       </c>
-      <c r="C13" s="13" t="inlineStr">
+      <c r="C13" s="14" t="inlineStr">
         <is>
           <t>计算书中无楼地面垫层构件，按首层各房间地面积×0.10m 推导。</t>
         </is>
       </c>
     </row>
     <row r="14">
-      <c r="A14" s="13" t="inlineStr">
+      <c r="A14" s="14" t="inlineStr">
         <is>
           <t>010501002002</t>
         </is>
       </c>
-      <c r="B14" s="13" t="inlineStr">
+      <c r="B14" s="14" t="inlineStr">
         <is>
           <t>楼地面垫层</t>
         </is>
       </c>
-      <c r="C14" s="13" t="inlineStr">
+      <c r="C14" s="14" t="inlineStr">
         <is>
           <t>计算书中无楼地面垫层构件，按首层各房间地面积×0.15m 推导。</t>
         </is>
       </c>
     </row>
     <row r="15">
-      <c r="A15" s="13" t="inlineStr">
+      <c r="A15" s="14" t="inlineStr">
         <is>
           <t>010502006001</t>
         </is>
       </c>
-      <c r="B15" s="13" t="inlineStr">
+      <c r="B15" s="14" t="inlineStr">
         <is>
           <t>钢筋混凝土柱</t>
         </is>
       </c>
-      <c r="C15" s="13" t="inlineStr">
+      <c r="C15" s="14" t="inlineStr">
         <is>
           <t>含各层框架柱 1KZ1~1KZ4 及梯柱 TZ；基础层柱为基础顶至±0.000 段。</t>
         </is>
       </c>
     </row>
     <row r="16">
-      <c r="A16" s="13" t="inlineStr">
+      <c r="A16" s="14" t="inlineStr">
         <is>
           <t>010502011001</t>
         </is>
       </c>
-      <c r="B16" s="13" t="inlineStr">
+      <c r="B16" s="14" t="inlineStr">
         <is>
           <t>钢筋混凝土梁</t>
         </is>
       </c>
-      <c r="C16" s="13" t="inlineStr">
+      <c r="C16" s="14" t="inlineStr">
         <is>
           <t>含基础梁 DKL/DL、各层框架梁 KL/WKL、次梁 L/WL；雨棚梁 YPL 计入“其他板(雨棚板)”。</t>
         </is>
       </c>
     </row>
     <row r="17">
-      <c r="A17" s="13" t="inlineStr">
+      <c r="A17" s="14" t="inlineStr">
         <is>
           <t>010502019001</t>
         </is>
       </c>
-      <c r="B17" s="13" t="inlineStr">
+      <c r="B17" s="14" t="inlineStr">
         <is>
           <t>其他板</t>
         </is>
       </c>
-      <c r="C17" s="13" t="inlineStr">
+      <c r="C17" s="14" t="inlineStr">
         <is>
           <t>广联达模型中未绘制雨棚板本体，仅有雨棚梁 YPL 与雨棚栏板 YP，此处为两者体积之和；雨棚板本体需补充。</t>
         </is>
       </c>
     </row>
     <row r="18">
-      <c r="A18" s="13" t="inlineStr">
+      <c r="A18" s="14" t="inlineStr">
         <is>
           <t>010502020001</t>
         </is>
       </c>
-      <c r="B18" s="13" t="inlineStr">
+      <c r="B18" s="14" t="inlineStr">
         <is>
           <t>楼梯</t>
         </is>
       </c>
-      <c r="C18" s="13" t="inlineStr">
+      <c r="C18" s="14" t="inlineStr">
         <is>
           <t>楼梯按广联达“梯段+梯梁+平台板”体积汇总（清单模板单位为 m³）。</t>
         </is>
       </c>
     </row>
     <row r="19">
-      <c r="A19" s="13" t="inlineStr">
+      <c r="A19" s="14" t="inlineStr">
         <is>
           <t>010506001001</t>
         </is>
       </c>
-      <c r="B19" s="13" t="inlineStr">
+      <c r="B19" s="14" t="inlineStr">
         <is>
           <t>现浇混凝土基础及联系梁钢筋</t>
         </is>
       </c>
-      <c r="C19" s="13" t="inlineStr">
+      <c r="C19" s="14" t="inlineStr">
         <is>
           <t>基础钢筋按独立基础 J-1/J-2/J-3 汇总（均为Φ12）；基础梁 DKL/DL 钢筋计入“现浇混凝土梁钢筋”对应直径。</t>
         </is>
       </c>
     </row>
     <row r="20">
-      <c r="A20" s="13" t="inlineStr">
+      <c r="A20" s="14" t="inlineStr">
         <is>
           <t>010506002003</t>
         </is>
       </c>
-      <c r="B20" s="13" t="inlineStr">
+      <c r="B20" s="14" t="inlineStr">
         <is>
           <t>现浇混凝土柱钢筋</t>
         </is>
       </c>
-      <c r="C20" s="13" t="inlineStr">
+      <c r="C20" s="14" t="inlineStr">
         <is>
           <t>钢筋明细表中柱构件无Φ16钢筋，工程量为 0。</t>
         </is>
       </c>
     </row>
     <row r="21">
-      <c r="A21" s="13" t="inlineStr">
+      <c r="A21" s="14" t="inlineStr">
         <is>
           <t>010506005001</t>
         </is>
       </c>
-      <c r="B21" s="13" t="inlineStr">
+      <c r="B21" s="14" t="inlineStr">
         <is>
           <t>现浇混凝土梁钢筋</t>
         </is>
       </c>
-      <c r="C21" s="13" t="inlineStr">
+      <c r="C21" s="14" t="inlineStr">
         <is>
           <t>含雨棚梁 YPL 钢筋（清单模板“雨蓬”项仅列Φ8）。</t>
         </is>
       </c>
     </row>
     <row r="22">
-      <c r="A22" s="13" t="inlineStr">
+      <c r="A22" s="14" t="inlineStr">
         <is>
           <t>010506005004</t>
         </is>
       </c>
-      <c r="B22" s="13" t="inlineStr">
+      <c r="B22" s="14" t="inlineStr">
         <is>
           <t>现浇混凝土梁钢筋</t>
         </is>
       </c>
-      <c r="C22" s="13" t="inlineStr">
+      <c r="C22" s="14" t="inlineStr">
         <is>
           <t>含雨棚梁 YPL 钢筋（清单模板“雨蓬”项仅列Φ8）。</t>
         </is>
       </c>
     </row>
     <row r="23">
-      <c r="A23" s="13" t="inlineStr">
+      <c r="A23" s="14" t="inlineStr">
         <is>
           <t>010506020001</t>
         </is>
       </c>
-      <c r="B23" s="13" t="inlineStr">
+      <c r="B23" s="14" t="inlineStr">
         <is>
           <t>钢筋网片</t>
         </is>
       </c>
-      <c r="C23" s="13" t="inlineStr">
+      <c r="C23" s="14" t="inlineStr">
         <is>
           <t>钢筋明细表中无屋面网片；按刚性层面积×Φ4@150双向估算：Φ4 单重 0.099kg/m，每 m² 用量 2/0.15×0.099≈1.316kg/m²。</t>
         </is>
       </c>
     </row>
     <row r="24">
-      <c r="A24" s="13" t="inlineStr">
+      <c r="A24" s="14" t="inlineStr">
         <is>
           <t>010902001001</t>
         </is>
       </c>
-      <c r="B24" s="13" t="inlineStr">
+      <c r="B24" s="14" t="inlineStr">
         <is>
           <t>屋面卷材防水</t>
         </is>
       </c>
-      <c r="C24" s="13" t="inlineStr">
+      <c r="C24" s="14" t="inlineStr">
         <is>
           <t>按广联达屋面“防水面积”（含 250 高卷边）汇总。</t>
         </is>
       </c>
     </row>
     <row r="25">
-      <c r="A25" s="13" t="inlineStr">
+      <c r="A25" s="14" t="inlineStr">
         <is>
           <t>010902004001</t>
         </is>
       </c>
-      <c r="B25" s="13" t="inlineStr">
+      <c r="B25" s="14" t="inlineStr">
         <is>
           <t>屋面刚性层</t>
         </is>
       </c>
-      <c r="C25" s="13" t="inlineStr">
+      <c r="C25" s="14" t="inlineStr">
         <is>
           <t>刚性层 = 屋面防水面积 − 卷边面积（水平投影）。</t>
         </is>
       </c>
     </row>
     <row r="26">
-      <c r="A26" s="13" t="inlineStr">
+      <c r="A26" s="14" t="inlineStr">
         <is>
           <t>010902005001</t>
         </is>
       </c>
-      <c r="B26" s="13" t="inlineStr">
+      <c r="B26" s="14" t="inlineStr">
         <is>
           <t>屋面排水管</t>
         </is>
       </c>
-      <c r="C26" s="13" t="inlineStr">
+      <c r="C26" s="14" t="inlineStr">
         <is>
           <t>计算书与钢筋表中均无雨水管信息，无法计取，需按图纸补充（根数×长度）。</t>
         </is>
       </c>
     </row>
     <row r="27">
-      <c r="A27" s="13" t="inlineStr">
+      <c r="A27" s="14" t="inlineStr">
         <is>
           <t>010904002001</t>
         </is>
       </c>
-      <c r="B27" s="13" t="inlineStr">
+      <c r="B27" s="14" t="inlineStr">
         <is>
           <t>楼地面涂膜防水</t>
         </is>
       </c>
-      <c r="C27" s="13" t="inlineStr">
+      <c r="C27" s="14" t="inlineStr">
         <is>
           <t>按首层卫生间地面积计取，未含上翻高度部分。</t>
         </is>
       </c>
     </row>
     <row r="28">
-      <c r="A28" s="13" t="inlineStr">
+      <c r="A28" s="14" t="inlineStr">
         <is>
           <t>011001001001</t>
         </is>
       </c>
-      <c r="B28" s="13" t="inlineStr">
+      <c r="B28" s="14" t="inlineStr">
         <is>
           <t>保温隔热屋面</t>
         </is>
       </c>
-      <c r="C28" s="13" t="inlineStr">
+      <c r="C28" s="14" t="inlineStr">
         <is>
           <t>保温层 = 屋面防水面积 − 卷边面积（水平投影）。</t>
         </is>
       </c>
     </row>
     <row r="29">
-      <c r="A29" s="13" t="inlineStr">
+      <c r="A29" s="14" t="inlineStr">
         <is>
           <t>011101001001</t>
         </is>
       </c>
-      <c r="B29" s="13" t="inlineStr">
+      <c r="B29" s="14" t="inlineStr">
         <is>
           <t>水泥砂浆楼地面</t>
         </is>
       </c>
-      <c r="C29" s="13" t="inlineStr">
+      <c r="C29" s="14" t="inlineStr">
         <is>
           <t>按各层“其他”房间地面积汇总（首层地面一并计入）。</t>
         </is>
       </c>
     </row>
     <row r="30">
-      <c r="A30" s="13" t="inlineStr">
+      <c r="A30" s="14" t="inlineStr">
         <is>
           <t>011105001001</t>
         </is>
       </c>
-      <c r="B30" s="13" t="inlineStr">
+      <c r="B30" s="14" t="inlineStr">
         <is>
           <t>水泥砂浆踢脚线</t>
         </is>
       </c>
-      <c r="C30" s="13" t="inlineStr">
+      <c r="C30" s="14" t="inlineStr">
         <is>
           <t>仅计“其他”房间踢脚；卫生间 2.1m 以下为瓷砖墙裙，不计踢脚。</t>
         </is>
       </c>
     </row>
     <row r="31">
-      <c r="A31" s="13" t="inlineStr">
+      <c r="A31" s="14" t="inlineStr">
         <is>
           <t>011201001002</t>
         </is>
       </c>
-      <c r="B31" s="13" t="inlineStr">
+      <c r="B31" s="14" t="inlineStr">
         <is>
           <t>墙、柱面一般抹灰</t>
         </is>
       </c>
-      <c r="C31" s="13" t="inlineStr">
+      <c r="C31" s="14" t="inlineStr">
         <is>
           <t>含各层房间内墙面（卫生间为墙裙以上部分）及第5层女儿墙内侧/楼梯间墙面。</t>
         </is>
       </c>
     </row>
     <row r="32">
-      <c r="A32" s="13" t="inlineStr">
+      <c r="A32" s="14" t="inlineStr">
         <is>
           <t>011404001001</t>
         </is>
       </c>
-      <c r="B32" s="13" t="inlineStr">
+      <c r="B32" s="14" t="inlineStr">
         <is>
           <t>墙面喷刷涂料</t>
         </is>
       </c>
-      <c r="C32" s="13" t="inlineStr">
+      <c r="C32" s="14" t="inlineStr">
         <is>
           <t>外墙涂料面积 = 外墙一般抹灰面积。</t>
         </is>
       </c>
     </row>
     <row r="33">
-      <c r="A33" s="13" t="inlineStr">
+      <c r="A33" s="14" t="inlineStr">
         <is>
           <t>011404001002</t>
         </is>
       </c>
-      <c r="B33" s="13" t="inlineStr">
+      <c r="B33" s="14" t="inlineStr">
         <is>
           <t>墙面喷刷涂料</t>
         </is>
       </c>
-      <c r="C33" s="13" t="inlineStr">
+      <c r="C33" s="14" t="inlineStr">
         <is>
           <t>内墙涂料面积 = 内墙一般抹灰面积。</t>
         </is>
       </c>
     </row>
     <row r="34">
-      <c r="A34" s="13" t="inlineStr">
+      <c r="A34" s="14" t="inlineStr">
         <is>
           <t>011404002001</t>
         </is>
       </c>
-      <c r="B34" s="13" t="inlineStr">
+      <c r="B34" s="14" t="inlineStr">
         <is>
           <t>天棚喷刷涂料</t>
         </is>
       </c>
-      <c r="C34" s="13" t="inlineStr">
+      <c r="C34" s="14" t="inlineStr">
         <is>
           <t>天棚涂料面积 = 天棚抹灰面积。</t>
         </is>
       </c>
     </row>
     <row r="35">
-      <c r="A35" s="13" t="n"/>
-      <c r="B35" s="13" t="n"/>
-      <c r="C35" s="13" t="n"/>
+      <c r="A35" s="14" t="n"/>
+      <c r="B35" s="14" t="n"/>
+      <c r="C35" s="14" t="n"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/工程量清单/工程量清单及计算书.xlsx
+++ b/工程量清单/工程量清单及计算书.xlsx
@@ -86,7 +86,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="16">
+  <cellXfs count="18">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
@@ -109,6 +109,9 @@
     <xf numFmtId="0" fontId="2" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
+    <xf numFmtId="2" fontId="2" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
     <xf numFmtId="2" fontId="3" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
@@ -116,6 +119,9 @@
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="164" fontId="3" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="164" fontId="2" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="2" fontId="3" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
@@ -588,7 +594,9 @@
           <t>200.4156 ≈ 200.42</t>
         </is>
       </c>
-      <c r="F4" s="8" t="n"/>
+      <c r="F4" s="8" t="n">
+        <v>200.42</v>
+      </c>
     </row>
     <row r="5" ht="46" customHeight="1">
       <c r="A5" s="3" t="n">
@@ -632,7 +640,9 @@
           <t>168.2978 ≈ 168.30</t>
         </is>
       </c>
-      <c r="F6" s="8" t="n"/>
+      <c r="F6" s="8" t="n">
+        <v>168.3</v>
+      </c>
     </row>
     <row r="7" ht="18" customHeight="1">
       <c r="A7" s="3" t="n">
@@ -676,7 +686,9 @@
           <t>192.882 ≈ 192.88</t>
         </is>
       </c>
-      <c r="F8" s="8" t="n"/>
+      <c r="F8" s="8" t="n">
+        <v>192.88</v>
+      </c>
     </row>
     <row r="9" ht="18" customHeight="1">
       <c r="A9" s="3" t="n">
@@ -720,7 +732,9 @@
           <t>32.1178 ≈ 32.12</t>
         </is>
       </c>
-      <c r="F10" s="8" t="n"/>
+      <c r="F10" s="8" t="n">
+        <v>32.12</v>
+      </c>
     </row>
     <row r="11" ht="32" customHeight="1">
       <c r="A11" s="3" t="n">
@@ -768,7 +782,7 @@
           <t>(13.625×3.6×0.24)-0.8784-0.9936-1.5972-0.096-0.023 + (15.38×3.6×0.24)-3.6288-1.1923-1.1712-0.4992 + (13.5×3.6×0.24)-0.8784-1.3167-1.5313-0.096-0.023 + (15.5×3.6×0.24)-5.4144-1.392-0.648-0.1382-0.0027 = 28.5958</t>
         </is>
       </c>
-      <c r="F12" s="8" t="n"/>
+      <c r="F12" s="9" t="n"/>
     </row>
     <row r="13" ht="32" customHeight="1">
       <c r="A13" s="3" t="n"/>
@@ -788,7 +802,7 @@
           <t>(15.5×3.6×0.24)-5.4144-1.392-0.648-0.1382-0.0027 + (13.5×3.6×0.24)-0.8784-1.3167-1.5313-0.096-0.023 + (15.38×3.6×0.24)-3.6288-1.1923-1.1712-0.4992 + (13.625×3.6×0.24)-0.8784-0.9936-1.5972-0.096-0.023 = 28.5958</t>
         </is>
       </c>
-      <c r="F13" s="8" t="n"/>
+      <c r="F13" s="9" t="n"/>
     </row>
     <row r="14" ht="32" customHeight="1">
       <c r="A14" s="3" t="n"/>
@@ -808,7 +822,7 @@
           <t>(15.5×3.6×0.24)-5.4144-1.392-0.648-0.1382-0.003 + (13.5×3.6×0.24)-0.8784-1.3167-1.5313-0.096-0.023 + (15.38×3.6×0.24)-3.2616-1.1923-1.344-0.4992 + (13.625×3.6×0.24)-0.8784-0.9936-1.5972-0.096-0.023 = 28.7899</t>
         </is>
       </c>
-      <c r="F14" s="8" t="n"/>
+      <c r="F14" s="9" t="n"/>
     </row>
     <row r="15" ht="18" customHeight="1">
       <c r="A15" s="3" t="n"/>
@@ -824,7 +838,9 @@
           <t>27.0403 + 28.5958 + 28.5958 + 28.7899 = 113.0218 ≈ 113.02</t>
         </is>
       </c>
-      <c r="F15" s="8" t="n"/>
+      <c r="F15" s="8" t="n">
+        <v>113.02</v>
+      </c>
     </row>
     <row r="16" ht="18" customHeight="1">
       <c r="A16" s="3" t="n">
@@ -872,7 +888,7 @@
           <t>(5.85×3.6×0.24)-0.8424-0.6435 = 3.5685</t>
         </is>
       </c>
-      <c r="F17" s="8" t="n"/>
+      <c r="F17" s="9" t="n"/>
     </row>
     <row r="18" ht="18" customHeight="1">
       <c r="A18" s="3" t="n"/>
@@ -892,7 +908,7 @@
           <t>(5.85×3.6×0.24)-0.8424-0.6435 = 3.5685</t>
         </is>
       </c>
-      <c r="F18" s="8" t="n"/>
+      <c r="F18" s="9" t="n"/>
     </row>
     <row r="19" ht="18" customHeight="1">
       <c r="A19" s="3" t="n"/>
@@ -912,7 +928,7 @@
           <t>(5.85×3.6×0.24)-0.8424-0.6435 = 3.5685</t>
         </is>
       </c>
-      <c r="F19" s="8" t="n"/>
+      <c r="F19" s="9" t="n"/>
     </row>
     <row r="20" ht="18" customHeight="1">
       <c r="A20" s="3" t="n"/>
@@ -928,7 +944,9 @@
           <t>5.6237 + 3.5685 + 3.5685 + 3.5685 = 16.3292 ≈ 16.33</t>
         </is>
       </c>
-      <c r="F20" s="8" t="n"/>
+      <c r="F20" s="8" t="n">
+        <v>16.33</v>
+      </c>
     </row>
     <row r="21" ht="46" customHeight="1">
       <c r="A21" s="3" t="n">
@@ -972,7 +990,9 @@
           <t>25.3624 ≈ 25.36</t>
         </is>
       </c>
-      <c r="F22" s="8" t="n"/>
+      <c r="F22" s="8" t="n">
+        <v>25.36</v>
+      </c>
     </row>
     <row r="23" ht="18" customHeight="1">
       <c r="A23" s="3" t="n">
@@ -1016,7 +1036,9 @@
           <t>6.832 ≈ 6.83</t>
         </is>
       </c>
-      <c r="F24" s="8" t="n"/>
+      <c r="F24" s="8" t="n">
+        <v>6.83</v>
+      </c>
     </row>
     <row r="25" ht="18" customHeight="1">
       <c r="A25" s="3" t="n">
@@ -1060,7 +1082,9 @@
           <t>17.6666 ≈ 17.67</t>
         </is>
       </c>
-      <c r="F26" s="8" t="n"/>
+      <c r="F26" s="8" t="n">
+        <v>17.67</v>
+      </c>
     </row>
     <row r="27" ht="18" customHeight="1">
       <c r="A27" s="3" t="n">
@@ -1104,7 +1128,9 @@
           <t>26.4999 ≈ 26.50</t>
         </is>
       </c>
-      <c r="F28" s="8" t="n"/>
+      <c r="F28" s="8" t="n">
+        <v>26.5</v>
+      </c>
     </row>
     <row r="29" ht="18" customHeight="1">
       <c r="A29" s="3" t="n">
@@ -1152,7 +1178,7 @@
           <t>[1.5412]×8 = 12.3296</t>
         </is>
       </c>
-      <c r="F30" s="8" t="n"/>
+      <c r="F30" s="9" t="n"/>
     </row>
     <row r="31" ht="18" customHeight="1">
       <c r="A31" s="3" t="n"/>
@@ -1172,7 +1198,7 @@
           <t>[0.8837]×2 = 1.7674</t>
         </is>
       </c>
-      <c r="F31" s="8" t="n"/>
+      <c r="F31" s="9" t="n"/>
     </row>
     <row r="32" ht="18" customHeight="1">
       <c r="A32" s="3" t="n"/>
@@ -1188,7 +1214,9 @@
           <t>8.614 + 12.3296 + 1.7674 = 22.711 ≈ 22.71</t>
         </is>
       </c>
-      <c r="F32" s="8" t="n"/>
+      <c r="F32" s="8" t="n">
+        <v>22.71</v>
+      </c>
     </row>
     <row r="33" ht="18" customHeight="1">
       <c r="A33" s="3" t="n">
@@ -1236,7 +1264,7 @@
           <t>[(0.35×0.4×1.55)-0.07]×9 = 1.323</t>
         </is>
       </c>
-      <c r="F34" s="8" t="n"/>
+      <c r="F34" s="9" t="n"/>
     </row>
     <row r="35" ht="18" customHeight="1">
       <c r="A35" s="3" t="n"/>
@@ -1256,7 +1284,7 @@
           <t>(0.4×0.4×1.55)-0.096 = 0.152</t>
         </is>
       </c>
-      <c r="F35" s="8" t="n"/>
+      <c r="F35" s="9" t="n"/>
     </row>
     <row r="36" ht="18" customHeight="1">
       <c r="A36" s="3" t="n"/>
@@ -1276,7 +1304,7 @@
           <t>(0.35×0.4×1.55)-0.07 = 0.147</t>
         </is>
       </c>
-      <c r="F36" s="8" t="n"/>
+      <c r="F36" s="9" t="n"/>
     </row>
     <row r="37" ht="18" customHeight="1">
       <c r="A37" s="3" t="n"/>
@@ -1296,7 +1324,7 @@
           <t>[(0.4×0.4×3.6)]×3 = 1.728</t>
         </is>
       </c>
-      <c r="F37" s="8" t="n"/>
+      <c r="F37" s="9" t="n"/>
     </row>
     <row r="38" ht="18" customHeight="1">
       <c r="A38" s="3" t="n"/>
@@ -1316,7 +1344,7 @@
           <t>[(0.35×0.4×3.6)]×9 = 4.536</t>
         </is>
       </c>
-      <c r="F38" s="8" t="n"/>
+      <c r="F38" s="9" t="n"/>
     </row>
     <row r="39" ht="18" customHeight="1">
       <c r="A39" s="3" t="n"/>
@@ -1336,7 +1364,7 @@
           <t>(0.4×0.4×3.6) = 0.576</t>
         </is>
       </c>
-      <c r="F39" s="8" t="n"/>
+      <c r="F39" s="9" t="n"/>
     </row>
     <row r="40" ht="18" customHeight="1">
       <c r="A40" s="3" t="n"/>
@@ -1356,7 +1384,7 @@
           <t>(0.35×0.4×3.6) = 0.504</t>
         </is>
       </c>
-      <c r="F40" s="8" t="n"/>
+      <c r="F40" s="9" t="n"/>
     </row>
     <row r="41" ht="18" customHeight="1">
       <c r="A41" s="3" t="n"/>
@@ -1376,7 +1404,7 @@
           <t>[(0.25×0.25×3.6)]×4 = 0.9</t>
         </is>
       </c>
-      <c r="F41" s="8" t="n"/>
+      <c r="F41" s="9" t="n"/>
     </row>
     <row r="42" ht="18" customHeight="1">
       <c r="A42" s="3" t="n"/>
@@ -1396,7 +1424,7 @@
           <t>[(0.4×0.4×3.6)]×3 = 1.728</t>
         </is>
       </c>
-      <c r="F42" s="8" t="n"/>
+      <c r="F42" s="9" t="n"/>
     </row>
     <row r="43" ht="18" customHeight="1">
       <c r="A43" s="3" t="n"/>
@@ -1416,7 +1444,7 @@
           <t>[(0.35×0.4×3.6)]×9 = 4.536</t>
         </is>
       </c>
-      <c r="F43" s="8" t="n"/>
+      <c r="F43" s="9" t="n"/>
     </row>
     <row r="44" ht="18" customHeight="1">
       <c r="A44" s="3" t="n"/>
@@ -1436,7 +1464,7 @@
           <t>(0.4×0.4×3.6) = 0.576</t>
         </is>
       </c>
-      <c r="F44" s="8" t="n"/>
+      <c r="F44" s="9" t="n"/>
     </row>
     <row r="45" ht="18" customHeight="1">
       <c r="A45" s="3" t="n"/>
@@ -1456,7 +1484,7 @@
           <t>(0.35×0.4×3.6) = 0.504</t>
         </is>
       </c>
-      <c r="F45" s="8" t="n"/>
+      <c r="F45" s="9" t="n"/>
     </row>
     <row r="46" ht="18" customHeight="1">
       <c r="A46" s="3" t="n"/>
@@ -1476,7 +1504,7 @@
           <t>[(0.25×0.25×3.6)]×4 = 0.9</t>
         </is>
       </c>
-      <c r="F46" s="8" t="n"/>
+      <c r="F46" s="9" t="n"/>
     </row>
     <row r="47" ht="18" customHeight="1">
       <c r="A47" s="3" t="n"/>
@@ -1496,7 +1524,7 @@
           <t>[(0.4×0.4×3.6)]×3 = 1.728</t>
         </is>
       </c>
-      <c r="F47" s="8" t="n"/>
+      <c r="F47" s="9" t="n"/>
     </row>
     <row r="48" ht="18" customHeight="1">
       <c r="A48" s="3" t="n"/>
@@ -1516,7 +1544,7 @@
           <t>[(0.35×0.4×3.6)]×9 = 4.536</t>
         </is>
       </c>
-      <c r="F48" s="8" t="n"/>
+      <c r="F48" s="9" t="n"/>
     </row>
     <row r="49" ht="18" customHeight="1">
       <c r="A49" s="3" t="n"/>
@@ -1536,7 +1564,7 @@
           <t>(0.4×0.4×3.6) = 0.576</t>
         </is>
       </c>
-      <c r="F49" s="8" t="n"/>
+      <c r="F49" s="9" t="n"/>
     </row>
     <row r="50" ht="18" customHeight="1">
       <c r="A50" s="3" t="n"/>
@@ -1556,7 +1584,7 @@
           <t>(0.35×0.4×3.6) = 0.504</t>
         </is>
       </c>
-      <c r="F50" s="8" t="n"/>
+      <c r="F50" s="9" t="n"/>
     </row>
     <row r="51" ht="18" customHeight="1">
       <c r="A51" s="3" t="n"/>
@@ -1576,7 +1604,7 @@
           <t>[(0.25×0.25×3.6)]×4 = 0.9</t>
         </is>
       </c>
-      <c r="F51" s="8" t="n"/>
+      <c r="F51" s="9" t="n"/>
     </row>
     <row r="52" ht="18" customHeight="1">
       <c r="A52" s="3" t="n"/>
@@ -1596,7 +1624,7 @@
           <t>[(0.4×0.4×3.6)]×3 = 1.728</t>
         </is>
       </c>
-      <c r="F52" s="8" t="n"/>
+      <c r="F52" s="9" t="n"/>
     </row>
     <row r="53" ht="18" customHeight="1">
       <c r="A53" s="3" t="n"/>
@@ -1616,7 +1644,7 @@
           <t>[(0.35×0.4×3.6)]×9 = 4.536</t>
         </is>
       </c>
-      <c r="F53" s="8" t="n"/>
+      <c r="F53" s="9" t="n"/>
     </row>
     <row r="54" ht="18" customHeight="1">
       <c r="A54" s="3" t="n"/>
@@ -1636,7 +1664,7 @@
           <t>(0.4×0.4×3.6) = 0.576</t>
         </is>
       </c>
-      <c r="F54" s="8" t="n"/>
+      <c r="F54" s="9" t="n"/>
     </row>
     <row r="55" ht="18" customHeight="1">
       <c r="A55" s="3" t="n"/>
@@ -1656,7 +1684,7 @@
           <t>(0.35×0.4×3.6) = 0.504</t>
         </is>
       </c>
-      <c r="F55" s="8" t="n"/>
+      <c r="F55" s="9" t="n"/>
     </row>
     <row r="56" ht="18" customHeight="1">
       <c r="A56" s="3" t="n"/>
@@ -1676,7 +1704,7 @@
           <t>[(0.25×0.25×3.6)]×4 = 0.9</t>
         </is>
       </c>
-      <c r="F56" s="8" t="n"/>
+      <c r="F56" s="9" t="n"/>
     </row>
     <row r="57" ht="32" customHeight="1">
       <c r="A57" s="3" t="n"/>
@@ -1692,7 +1720,9 @@
           <t>0.456 + 1.323 + 0.152 + 0.147 + 1.728 + 4.536 + 0.576 + 0.504 + 0.9 + 1.728 + 4.536 + 0.576 + 0.504 + 0.9 + 1.728 + 4.536 + 0.576 + 0.504 + 0.9 + 1.728 + 4.536 + 0.576 + 0.504 + 0.9 = 35.054 ≈ 35.05</t>
         </is>
       </c>
-      <c r="F57" s="8" t="n"/>
+      <c r="F57" s="8" t="n">
+        <v>35.05</v>
+      </c>
     </row>
     <row r="58" ht="18" customHeight="1">
       <c r="A58" s="3" t="n">
@@ -1740,7 +1770,7 @@
           <t>(0.3×0.55×12.25)-0.1897 = 1.8315</t>
         </is>
       </c>
-      <c r="F59" s="8" t="n"/>
+      <c r="F59" s="9" t="n"/>
     </row>
     <row r="60" ht="18" customHeight="1">
       <c r="A60" s="3" t="n"/>
@@ -1760,7 +1790,7 @@
           <t>(0.25×0.4×8.875)-0.075 + (0.3×0.55×6.575)-0.066 = 1.8314</t>
         </is>
       </c>
-      <c r="F60" s="8" t="n"/>
+      <c r="F60" s="9" t="n"/>
     </row>
     <row r="61" ht="18" customHeight="1">
       <c r="A61" s="3" t="n"/>
@@ -1780,7 +1810,7 @@
           <t>(0.25×0.35×3.375)-0.0394-0.0031 = 0.2528</t>
         </is>
       </c>
-      <c r="F61" s="8" t="n"/>
+      <c r="F61" s="9" t="n"/>
     </row>
     <row r="62" ht="18" customHeight="1">
       <c r="A62" s="3" t="n"/>
@@ -1800,7 +1830,7 @@
           <t>(0.25×0.4×15.45)-0.145 = 1.4</t>
         </is>
       </c>
-      <c r="F62" s="8" t="n"/>
+      <c r="F62" s="9" t="n"/>
     </row>
     <row r="63" ht="18" customHeight="1">
       <c r="A63" s="3" t="n"/>
@@ -1820,7 +1850,7 @@
           <t>(0.25×0.35×3.4)-0.0284 = 0.2691</t>
         </is>
       </c>
-      <c r="F63" s="8" t="n"/>
+      <c r="F63" s="9" t="n"/>
     </row>
     <row r="64" ht="18" customHeight="1">
       <c r="A64" s="3" t="n"/>
@@ -1840,7 +1870,7 @@
           <t>[(0.25×0.4×1.7)-0.02]×2 + (0.25×0.55×12.25)-0.1581 + (0.25×0.55×12.05)-0.1991-0.0009 = 3.2832</t>
         </is>
       </c>
-      <c r="F64" s="8" t="n"/>
+      <c r="F64" s="9" t="n"/>
     </row>
     <row r="65" ht="18" customHeight="1">
       <c r="A65" s="3" t="n"/>
@@ -1860,7 +1890,7 @@
           <t>[(0.25×0.4×1.7)-0.02]×2 + (0.25×0.55×12.25)-0.165 + (0.25×0.55×12.05)-0.1375 = 3.3388</t>
         </is>
       </c>
-      <c r="F65" s="8" t="n"/>
+      <c r="F65" s="9" t="n"/>
     </row>
     <row r="66" ht="18" customHeight="1">
       <c r="A66" s="3" t="n"/>
@@ -1880,7 +1910,7 @@
           <t>(0.25×0.4×1.625)-0.0125 + (0.25×0.55×12.125)-0.1787-0.0172 = 1.6213</t>
         </is>
       </c>
-      <c r="F66" s="8" t="n"/>
+      <c r="F66" s="9" t="n"/>
     </row>
     <row r="67" ht="18" customHeight="1">
       <c r="A67" s="3" t="n"/>
@@ -1900,7 +1930,7 @@
           <t>(0.25×0.4×8.9)-0.0775 + (0.25×0.65×6.85)-0.1097 = 1.8159</t>
         </is>
       </c>
-      <c r="F67" s="8" t="n"/>
+      <c r="F67" s="9" t="n"/>
     </row>
     <row r="68" ht="18" customHeight="1">
       <c r="A68" s="3" t="n"/>
@@ -1920,7 +1950,7 @@
           <t>(0.25×0.4×15.5)-0.175 = 1.375</t>
         </is>
       </c>
-      <c r="F68" s="8" t="n"/>
+      <c r="F68" s="9" t="n"/>
     </row>
     <row r="69" ht="18" customHeight="1">
       <c r="A69" s="3" t="n"/>
@@ -1940,7 +1970,7 @@
           <t>(0.25×0.4×15.5)-0.15 = 1.4</t>
         </is>
       </c>
-      <c r="F69" s="8" t="n"/>
+      <c r="F69" s="9" t="n"/>
     </row>
     <row r="70" ht="18" customHeight="1">
       <c r="A70" s="3" t="n"/>
@@ -1960,7 +1990,7 @@
           <t>(0.25×0.4×8.9)-0.05 + (0.25×0.4×3.2)-0.025 + (0.25×0.4×3.4)-0.025 = 1.45</t>
         </is>
       </c>
-      <c r="F70" s="8" t="n"/>
+      <c r="F70" s="9" t="n"/>
     </row>
     <row r="71" ht="18" customHeight="1">
       <c r="A71" s="3" t="n"/>
@@ -1980,7 +2010,7 @@
           <t>(0.25×0.4×1.7)-0.02 + (0.25×0.55×12.25)-0.1581 = 1.6763</t>
         </is>
       </c>
-      <c r="F71" s="8" t="n"/>
+      <c r="F71" s="9" t="n"/>
     </row>
     <row r="72" ht="18" customHeight="1">
       <c r="A72" s="3" t="n"/>
@@ -2000,7 +2030,7 @@
           <t>(0.25×0.4×1.7)-0.02 + (0.25×0.55×12.25)-0.165 = 1.6694</t>
         </is>
       </c>
-      <c r="F72" s="8" t="n"/>
+      <c r="F72" s="9" t="n"/>
     </row>
     <row r="73" ht="18" customHeight="1">
       <c r="A73" s="3" t="n"/>
@@ -2020,7 +2050,7 @@
           <t>(0.25×0.4×1.7)-0.02 + (0.25×0.55×12.05)-0.1375 = 1.6694</t>
         </is>
       </c>
-      <c r="F73" s="8" t="n"/>
+      <c r="F73" s="9" t="n"/>
     </row>
     <row r="74" ht="18" customHeight="1">
       <c r="A74" s="3" t="n"/>
@@ -2040,7 +2070,7 @@
           <t>(0.25×0.4×1.625)-0.0125 + (0.25×0.55×12.125)-0.1787-0.0172 = 1.6213</t>
         </is>
       </c>
-      <c r="F74" s="8" t="n"/>
+      <c r="F74" s="9" t="n"/>
     </row>
     <row r="75" ht="18" customHeight="1">
       <c r="A75" s="3" t="n"/>
@@ -2060,7 +2090,7 @@
           <t>(0.25×0.4×1.7)-0.02 + (0.25×0.55×12.05)-0.1986-0.0006 = 1.6077</t>
         </is>
       </c>
-      <c r="F75" s="8" t="n"/>
+      <c r="F75" s="9" t="n"/>
     </row>
     <row r="76" ht="18" customHeight="1">
       <c r="A76" s="3" t="n"/>
@@ -2080,7 +2110,7 @@
           <t>(0.25×0.4×8.9)-0.0775 + (0.25×0.65×6.85)-0.1097 = 1.8159</t>
         </is>
       </c>
-      <c r="F76" s="8" t="n"/>
+      <c r="F76" s="9" t="n"/>
     </row>
     <row r="77" ht="18" customHeight="1">
       <c r="A77" s="3" t="n"/>
@@ -2100,7 +2130,7 @@
           <t>(0.25×0.4×15.5)-0.175 = 1.375</t>
         </is>
       </c>
-      <c r="F77" s="8" t="n"/>
+      <c r="F77" s="9" t="n"/>
     </row>
     <row r="78" ht="18" customHeight="1">
       <c r="A78" s="3" t="n"/>
@@ -2120,7 +2150,7 @@
           <t>(0.25×0.4×15.5)-0.15 = 1.4</t>
         </is>
       </c>
-      <c r="F78" s="8" t="n"/>
+      <c r="F78" s="9" t="n"/>
     </row>
     <row r="79" ht="18" customHeight="1">
       <c r="A79" s="3" t="n"/>
@@ -2140,7 +2170,7 @@
           <t>(0.25×0.3×3)-0.0188 = 0.2062</t>
         </is>
       </c>
-      <c r="F79" s="8" t="n"/>
+      <c r="F79" s="9" t="n"/>
     </row>
     <row r="80" ht="18" customHeight="1">
       <c r="A80" s="3" t="n"/>
@@ -2160,7 +2190,7 @@
           <t>(0.25×0.4×15.5)-0.1 = 1.45</t>
         </is>
       </c>
-      <c r="F80" s="8" t="n"/>
+      <c r="F80" s="9" t="n"/>
     </row>
     <row r="81" ht="18" customHeight="1">
       <c r="A81" s="3" t="n"/>
@@ -2180,7 +2210,7 @@
           <t>(0.25×0.4×4.45)-0.025 = 0.42</t>
         </is>
       </c>
-      <c r="F81" s="8" t="n"/>
+      <c r="F81" s="9" t="n"/>
     </row>
     <row r="82" ht="18" customHeight="1">
       <c r="A82" s="3" t="n"/>
@@ -2200,7 +2230,7 @@
           <t>(0.25×0.3×2.05)-0.0188 = 0.135</t>
         </is>
       </c>
-      <c r="F82" s="8" t="n"/>
+      <c r="F82" s="9" t="n"/>
     </row>
     <row r="83" ht="18" customHeight="1">
       <c r="A83" s="3" t="n"/>
@@ -2220,7 +2250,7 @@
           <t>(0.25×0.35×3.4)-0.0219 + (0.25×0.35×3.2)-0.0219 = 0.5337</t>
         </is>
       </c>
-      <c r="F83" s="8" t="n"/>
+      <c r="F83" s="9" t="n"/>
     </row>
     <row r="84" ht="18" customHeight="1">
       <c r="A84" s="3" t="n"/>
@@ -2240,7 +2270,7 @@
           <t>(0.25×0.4×1.7)-0.02 + (0.25×0.55×12.25)-0.1581 = 1.6763</t>
         </is>
       </c>
-      <c r="F84" s="8" t="n"/>
+      <c r="F84" s="9" t="n"/>
     </row>
     <row r="85" ht="18" customHeight="1">
       <c r="A85" s="3" t="n"/>
@@ -2260,7 +2290,7 @@
           <t>(0.25×0.4×1.7)-0.02 + (0.25×0.55×12.25)-0.165 = 1.6694</t>
         </is>
       </c>
-      <c r="F85" s="8" t="n"/>
+      <c r="F85" s="9" t="n"/>
     </row>
     <row r="86" ht="18" customHeight="1">
       <c r="A86" s="3" t="n"/>
@@ -2280,7 +2310,7 @@
           <t>(0.25×0.4×1.7)-0.02 + (0.25×0.55×12.05)-0.1375 = 1.6694</t>
         </is>
       </c>
-      <c r="F86" s="8" t="n"/>
+      <c r="F86" s="9" t="n"/>
     </row>
     <row r="87" ht="18" customHeight="1">
       <c r="A87" s="3" t="n"/>
@@ -2300,7 +2330,7 @@
           <t>(0.25×0.4×1.625)-0.0125 + (0.25×0.55×12.125)-0.1787-0.0172 = 1.6213</t>
         </is>
       </c>
-      <c r="F87" s="8" t="n"/>
+      <c r="F87" s="9" t="n"/>
     </row>
     <row r="88" ht="18" customHeight="1">
       <c r="A88" s="3" t="n"/>
@@ -2320,7 +2350,7 @@
           <t>(0.25×0.4×1.7)-0.02 + (0.25×0.55×12.05)-0.1986-0.0006 = 1.6077</t>
         </is>
       </c>
-      <c r="F88" s="8" t="n"/>
+      <c r="F88" s="9" t="n"/>
     </row>
     <row r="89" ht="18" customHeight="1">
       <c r="A89" s="3" t="n"/>
@@ -2340,7 +2370,7 @@
           <t>(0.25×0.4×8.9)-0.0775 + (0.25×0.65×6.85)-0.1097 = 1.8159</t>
         </is>
       </c>
-      <c r="F89" s="8" t="n"/>
+      <c r="F89" s="9" t="n"/>
     </row>
     <row r="90" ht="18" customHeight="1">
       <c r="A90" s="3" t="n"/>
@@ -2360,7 +2390,7 @@
           <t>(0.25×0.4×15.5)-0.175 = 1.375</t>
         </is>
       </c>
-      <c r="F90" s="8" t="n"/>
+      <c r="F90" s="9" t="n"/>
     </row>
     <row r="91" ht="18" customHeight="1">
       <c r="A91" s="3" t="n"/>
@@ -2380,7 +2410,7 @@
           <t>(0.25×0.4×15.5)-0.15 = 1.4</t>
         </is>
       </c>
-      <c r="F91" s="8" t="n"/>
+      <c r="F91" s="9" t="n"/>
     </row>
     <row r="92" ht="18" customHeight="1">
       <c r="A92" s="3" t="n"/>
@@ -2400,7 +2430,7 @@
           <t>(0.25×0.3×3)-0.0188 = 0.2062</t>
         </is>
       </c>
-      <c r="F92" s="8" t="n"/>
+      <c r="F92" s="9" t="n"/>
     </row>
     <row r="93" ht="18" customHeight="1">
       <c r="A93" s="3" t="n"/>
@@ -2420,7 +2450,7 @@
           <t>(0.25×0.4×15.5)-0.1 = 1.45</t>
         </is>
       </c>
-      <c r="F93" s="8" t="n"/>
+      <c r="F93" s="9" t="n"/>
     </row>
     <row r="94" ht="18" customHeight="1">
       <c r="A94" s="3" t="n"/>
@@ -2440,7 +2470,7 @@
           <t>(0.25×0.4×4.45)-0.025 = 0.42</t>
         </is>
       </c>
-      <c r="F94" s="8" t="n"/>
+      <c r="F94" s="9" t="n"/>
     </row>
     <row r="95" ht="18" customHeight="1">
       <c r="A95" s="3" t="n"/>
@@ -2460,7 +2490,7 @@
           <t>(0.25×0.3×2.05)-0.0188 = 0.135</t>
         </is>
       </c>
-      <c r="F95" s="8" t="n"/>
+      <c r="F95" s="9" t="n"/>
     </row>
     <row r="96" ht="18" customHeight="1">
       <c r="A96" s="3" t="n"/>
@@ -2480,7 +2510,7 @@
           <t>(0.25×0.35×3.2)-0.0219 + (0.25×0.35×3.4)-0.0219 = 0.5337</t>
         </is>
       </c>
-      <c r="F96" s="8" t="n"/>
+      <c r="F96" s="9" t="n"/>
     </row>
     <row r="97" ht="18" customHeight="1">
       <c r="A97" s="3" t="n"/>
@@ -2500,7 +2530,7 @@
           <t>[(0.25×0.4×1.7)-0.02]×2 + (0.25×0.55×12.25)-0.1581 + (0.25×0.55×12.05)-0.1986-0.0006 = 3.284</t>
         </is>
       </c>
-      <c r="F97" s="8" t="n"/>
+      <c r="F97" s="9" t="n"/>
     </row>
     <row r="98" ht="18" customHeight="1">
       <c r="A98" s="3" t="n"/>
@@ -2520,7 +2550,7 @@
           <t>[(0.25×0.4×1.7)-0.02]×2 + (0.25×0.55×12.25)-0.165 + (0.25×0.55×12.05)-0.1375 = 3.3388</t>
         </is>
       </c>
-      <c r="F98" s="8" t="n"/>
+      <c r="F98" s="9" t="n"/>
     </row>
     <row r="99" ht="18" customHeight="1">
       <c r="A99" s="3" t="n"/>
@@ -2540,7 +2570,7 @@
           <t>(0.25×0.4×1.625)-0.0125 + (0.25×0.55×12.125)-0.1787-0.0172 = 1.6213</t>
         </is>
       </c>
-      <c r="F99" s="8" t="n"/>
+      <c r="F99" s="9" t="n"/>
     </row>
     <row r="100" ht="18" customHeight="1">
       <c r="A100" s="3" t="n"/>
@@ -2560,7 +2590,7 @@
           <t>(0.25×0.4×8.9)-0.0775 + (0.25×0.65×6.85)-0.1097 = 1.8159</t>
         </is>
       </c>
-      <c r="F100" s="8" t="n"/>
+      <c r="F100" s="9" t="n"/>
     </row>
     <row r="101" ht="18" customHeight="1">
       <c r="A101" s="3" t="n"/>
@@ -2580,7 +2610,7 @@
           <t>(0.25×0.4×15.5)-0.175 = 1.375</t>
         </is>
       </c>
-      <c r="F101" s="8" t="n"/>
+      <c r="F101" s="9" t="n"/>
     </row>
     <row r="102" ht="18" customHeight="1">
       <c r="A102" s="3" t="n"/>
@@ -2600,7 +2630,7 @@
           <t>(0.25×0.4×15.5)-0.15 = 1.4</t>
         </is>
       </c>
-      <c r="F102" s="8" t="n"/>
+      <c r="F102" s="9" t="n"/>
     </row>
     <row r="103" ht="18" customHeight="1">
       <c r="A103" s="3" t="n"/>
@@ -2620,7 +2650,7 @@
           <t>(0.25×0.4×15.5)-0.1 = 1.45</t>
         </is>
       </c>
-      <c r="F103" s="8" t="n"/>
+      <c r="F103" s="9" t="n"/>
     </row>
     <row r="104" ht="18" customHeight="1">
       <c r="A104" s="3" t="n"/>
@@ -2640,7 +2670,7 @@
           <t>(0.25×0.35×3.4)-0.0219 = 0.2756</t>
         </is>
       </c>
-      <c r="F104" s="8" t="n"/>
+      <c r="F104" s="9" t="n"/>
     </row>
     <row r="105" ht="18" customHeight="1">
       <c r="A105" s="3" t="n"/>
@@ -2660,7 +2690,7 @@
           <t>(0.25×0.4×12.1)-0.075 = 1.135</t>
         </is>
       </c>
-      <c r="F105" s="8" t="n"/>
+      <c r="F105" s="9" t="n"/>
     </row>
     <row r="106" ht="18" customHeight="1">
       <c r="A106" s="3" t="n"/>
@@ -2680,7 +2710,7 @@
           <t>(0.25×0.4×3.4) = 0.34</t>
         </is>
       </c>
-      <c r="F106" s="8" t="n"/>
+      <c r="F106" s="9" t="n"/>
     </row>
     <row r="107" ht="18" customHeight="1">
       <c r="A107" s="3" t="n"/>
@@ -2700,7 +2730,7 @@
           <t>(0.25×0.4×3.65) = 0.365</t>
         </is>
       </c>
-      <c r="F107" s="8" t="n"/>
+      <c r="F107" s="9" t="n"/>
     </row>
     <row r="108" ht="46" customHeight="1">
       <c r="A108" s="3" t="n"/>
@@ -2716,7 +2746,9 @@
           <t>2.7183 + 1.8315 + 1.8314 + 0.2528 + 1.4 + 0.2691 + 3.2832 + 3.3388 + 1.6213 + 1.8159 + 1.375 + 1.4 + 1.45 + 1.6763 + 1.6694 + 1.6694 + 1.6213 + 1.6077 + 1.8159 + 1.375 + 1.4 + 0.2062 + 1.45 + 0.42 + 0.135 + 0.5337 + 1.6763 + 1.6694 + 1.6694 + 1.6213 + 1.6077 + 1.8159 + 1.375 + 1.4 + 0.2062 + 1.45 + 0.42 + 0.135 + 0.5337 + 3.284 + 3.3388 + 1.6213 + 1.8159 + 1.375 + 1.4 + 1.45 + 0.2756 + 1.135 + 0.34 + 0.365 = 70.1477 ≈ 70.15</t>
         </is>
       </c>
-      <c r="F108" s="8" t="n"/>
+      <c r="F108" s="8" t="n">
+        <v>70.15000000000001</v>
+      </c>
     </row>
     <row r="109" ht="18" customHeight="1">
       <c r="A109" s="3" t="n">
@@ -2764,7 +2796,7 @@
           <t>((5.85×4.45)×0.12)-0.0238-0.282 + ((5.85×4.45)×0.12)-0.0211-0.2835 + ((6.15×4.45)×0.12)-0.022-0.2921 + ((6.15×4.45)×0.12)-0.0238-0.291 + ((3.4×1.945)×0.12)-0.0181-0.1382-0.0172 = 12.1968</t>
         </is>
       </c>
-      <c r="F110" s="8" t="n"/>
+      <c r="F110" s="9" t="n"/>
     </row>
     <row r="111" ht="18" customHeight="1">
       <c r="A111" s="3" t="n"/>
@@ -2784,7 +2816,7 @@
           <t>((3.4×1.5)×0.09)-0.0025-0.1021 + ((3.2×1.5)×0.09)-0.0023-0.0979 + ((4.45×1.5)×0.09)-0.0042-0.124 + ((4.45×1.5)×0.09)-0.0045-0.1237 = 1.6313</t>
         </is>
       </c>
-      <c r="F111" s="8" t="n"/>
+      <c r="F111" s="9" t="n"/>
     </row>
     <row r="112" ht="32" customHeight="1">
       <c r="A112" s="3" t="n"/>
@@ -2804,7 +2836,7 @@
           <t>((4.45×3.15)×0.1)-0.011-0.175 + ((6.15×3.2)×0.1)-0.0135-0.2162 + ((4.35×3.4)×0.1)-0.0062-0.1828 + ((3.2×2.4)×0.1)-0.0111-0.1237 + ((3.45×3.2)×0.1)-0.0127-0.1488 = 5.8196</t>
         </is>
       </c>
-      <c r="F112" s="8" t="n"/>
+      <c r="F112" s="9" t="n"/>
     </row>
     <row r="113" ht="32" customHeight="1">
       <c r="A113" s="3" t="n"/>
@@ -2824,7 +2856,7 @@
           <t>((5.85×4.45)×0.12)-0.0238-0.282 + ((5.85×4.45)×0.12)-0.0211-0.2835 + ((2.05×1.8)×0.12)-0.0048-0.1039 + ((2.05×1.2)×0.12)-0.09 + ((6.15×4.45)×0.12)-0.022-0.2921 = 9.1466</t>
         </is>
       </c>
-      <c r="F113" s="8" t="n"/>
+      <c r="F113" s="9" t="n"/>
     </row>
     <row r="114" ht="32" customHeight="1">
       <c r="A114" s="3" t="n"/>
@@ -2844,7 +2876,7 @@
           <t>((3×2.4)×0.09)-0.0043-0.1122 + ((3.4×1.8)×0.09)-0.0079-0.1046 + ((3.2×1.5)×0.09)-0.0023-0.0979 + ((3.4×1.5)×0.09)-0.0025-0.1021 + ((4.45×1.5)×0.09)-0.0042-0.124 + ((4.45×1.5)×0.09)-0.0045-0.1237 + ((3.4×1.31)×0.09)-0.0107-0.0918 = 2.8992</t>
         </is>
       </c>
-      <c r="F114" s="8" t="n"/>
+      <c r="F114" s="9" t="n"/>
     </row>
     <row r="115" ht="32" customHeight="1">
       <c r="A115" s="3" t="n"/>
@@ -2864,7 +2896,7 @@
           <t>((3.2×2.4)×0.1)-0.0111-0.1237 + ((6.15×3.2)×0.1)-0.0135-0.2162 + ((3.45×3.2)×0.1)-0.0127-0.1488 + ((4.35×3.4)×0.1)-0.0062-0.1828 + ((4.45×3.15)×0.1)-0.011-0.175 = 5.8196</t>
         </is>
       </c>
-      <c r="F115" s="8" t="n"/>
+      <c r="F115" s="9" t="n"/>
     </row>
     <row r="116" ht="32" customHeight="1">
       <c r="A116" s="3" t="n"/>
@@ -2884,7 +2916,7 @@
           <t>((6.15×4.45)×0.12)-0.022-0.2921 + ((2.05×1.2)×0.12)-0.09 + ((5.85×4.45)×0.12)-0.0238-0.282 + ((2.05×1.8)×0.12)-0.0048-0.1039 + ((5.85×4.45)×0.12)-0.0211-0.2835 = 9.1466</t>
         </is>
       </c>
-      <c r="F116" s="8" t="n"/>
+      <c r="F116" s="9" t="n"/>
     </row>
     <row r="117" ht="32" customHeight="1">
       <c r="A117" s="3" t="n"/>
@@ -2904,7 +2936,7 @@
           <t>((4.45×1.5)×0.09)-0.0045-0.1237 + ((4.45×1.5)×0.09)-0.0042-0.124 + ((3.4×1.5)×0.09)-0.0025-0.1021 + ((3.2×1.5)×0.09)-0.0023-0.0979 + ((3.4×1.8)×0.09)-0.0079-0.1046 + ((3×2.4)×0.09)-0.0043-0.1122 + ((3.4×1.31)×0.09)-0.0107-0.0918 = 2.8992</t>
         </is>
       </c>
-      <c r="F117" s="8" t="n"/>
+      <c r="F117" s="9" t="n"/>
     </row>
     <row r="118" ht="46" customHeight="1">
       <c r="A118" s="3" t="n"/>
@@ -2924,7 +2956,7 @@
           <t>((4.45×0.65)×0.1)-0.011-0.1125 + ((4.45×0.65)×0.1)-0.0096-0.1131 + ((3.2×0.65)×0.1)-0.0096-0.0819 + ((5.2×3.2)×0.1)-0.0142-0.1906 + ((6.15×3.2)×0.1)-0.0135-0.2163 + ((4.35×3.4)×0.1)-0.0062-0.1828 + ((3.4×1.5)×0.1)-0.0028-0.1134 + ((3.2×1.5)×0.1)-0.0025-0.1088 + ((4.45×1.5)×0.1)-0.0047-0.1378 + ((4.45×1.5)×0.1)-0.005-0.1375 = 6.7486</t>
         </is>
       </c>
-      <c r="F118" s="8" t="n"/>
+      <c r="F118" s="9" t="n"/>
     </row>
     <row r="119" ht="18" customHeight="1">
       <c r="A119" s="3" t="n"/>
@@ -2944,7 +2976,7 @@
           <t>((5.2×4.45)×0.12)-0.0106-0.273 + ((5.2×4.45)×0.12)-0.0096-0.2737 + ((6.15×4.45)×0.12)-0.022-0.2921 + ((6.15×4.45)×0.12)-0.0238-0.291 = 10.9259</t>
         </is>
       </c>
-      <c r="F119" s="8" t="n"/>
+      <c r="F119" s="9" t="n"/>
     </row>
     <row r="120" ht="18" customHeight="1">
       <c r="A120" s="3" t="n"/>
@@ -2964,7 +2996,7 @@
           <t>((3.4×1.8)×0.09)-0.0079-0.1046 + ((3.4×1.31)×0.09)-0.0107-0.0918 = 0.7365</t>
         </is>
       </c>
-      <c r="F120" s="8" t="n"/>
+      <c r="F120" s="9" t="n"/>
     </row>
     <row r="121" ht="18" customHeight="1">
       <c r="A121" s="3" t="n"/>
@@ -2984,7 +3016,7 @@
           <t>((3.41×0.655)×0.1)-0.0426-0.0409 + ((7.005×3.41)×0.1)-0.07-0.1778 = 2.2807</t>
         </is>
       </c>
-      <c r="F121" s="8" t="n"/>
+      <c r="F121" s="9" t="n"/>
     </row>
     <row r="122" ht="18" customHeight="1">
       <c r="A122" s="3" t="n"/>
@@ -3000,7 +3032,9 @@
           <t>5.2434 + 12.1968 + 1.6313 + 5.8196 + 9.1466 + 2.8992 + 5.8196 + 9.1466 + 2.8992 + 6.7486 + 10.9259 + 0.7365 + 2.2807 = 75.494 ≈ 75.49</t>
         </is>
       </c>
-      <c r="F122" s="8" t="n"/>
+      <c r="F122" s="8" t="n">
+        <v>75.48999999999999</v>
+      </c>
     </row>
     <row r="123" ht="18" customHeight="1">
       <c r="A123" s="3" t="n">
@@ -3048,7 +3082,7 @@
           <t>(0.25×0.35×2.225) = 0.1947</t>
         </is>
       </c>
-      <c r="F124" s="8" t="n"/>
+      <c r="F124" s="9" t="n"/>
     </row>
     <row r="125" ht="18" customHeight="1">
       <c r="A125" s="3" t="n"/>
@@ -3064,7 +3098,9 @@
           <t>0.189 + 0.1947 = 0.3837 ≈ 0.38</t>
         </is>
       </c>
-      <c r="F125" s="8" t="n"/>
+      <c r="F125" s="8" t="n">
+        <v>0.38</v>
+      </c>
     </row>
     <row r="126" ht="18" customHeight="1">
       <c r="A126" s="3" t="n">
@@ -3112,7 +3148,7 @@
           <t>1.8087+0.5499+0.3899 = 2.7485</t>
         </is>
       </c>
-      <c r="F127" s="8" t="n"/>
+      <c r="F127" s="9" t="n"/>
     </row>
     <row r="128" ht="18" customHeight="1">
       <c r="A128" s="3" t="n"/>
@@ -3132,7 +3168,7 @@
           <t>1.8087+0.5499+0.3899 = 2.7485</t>
         </is>
       </c>
-      <c r="F128" s="8" t="n"/>
+      <c r="F128" s="9" t="n"/>
     </row>
     <row r="129" ht="18" customHeight="1">
       <c r="A129" s="3" t="n"/>
@@ -3152,7 +3188,7 @@
           <t>1.8087+0.5499+0.3899 = 2.7485</t>
         </is>
       </c>
-      <c r="F129" s="8" t="n"/>
+      <c r="F129" s="9" t="n"/>
     </row>
     <row r="130" ht="18" customHeight="1">
       <c r="A130" s="3" t="n"/>
@@ -3168,7 +3204,9 @@
           <t>2.8942 + 2.7485 + 2.7485 + 2.7485 = 11.1397 ≈ 11.14</t>
         </is>
       </c>
-      <c r="F130" s="8" t="n"/>
+      <c r="F130" s="8" t="n">
+        <v>11.14</v>
+      </c>
     </row>
     <row r="131" ht="18" customHeight="1">
       <c r="A131" s="3" t="n">
@@ -3216,7 +3254,7 @@
           <t>[(0.25×0.37)×1.55]×3 = 0.4302</t>
         </is>
       </c>
-      <c r="F132" s="8" t="n"/>
+      <c r="F132" s="9" t="n"/>
     </row>
     <row r="133" ht="18" customHeight="1">
       <c r="A133" s="3" t="n"/>
@@ -3236,7 +3274,7 @@
           <t>(0.25×0.25)×3.6-0.025 = 0.2</t>
         </is>
       </c>
-      <c r="F133" s="8" t="n"/>
+      <c r="F133" s="9" t="n"/>
     </row>
     <row r="134" ht="18" customHeight="1">
       <c r="A134" s="3" t="n"/>
@@ -3256,7 +3294,7 @@
           <t>[(0.25×0.37)×3.6-0.025]×3 = 0.924</t>
         </is>
       </c>
-      <c r="F134" s="8" t="n"/>
+      <c r="F134" s="9" t="n"/>
     </row>
     <row r="135" ht="18" customHeight="1">
       <c r="A135" s="3" t="n"/>
@@ -3276,7 +3314,7 @@
           <t>(0.25×0.25)×3.6+0.0461-0.025 = 0.2461</t>
         </is>
       </c>
-      <c r="F135" s="8" t="n"/>
+      <c r="F135" s="9" t="n"/>
     </row>
     <row r="136" ht="18" customHeight="1">
       <c r="A136" s="3" t="n"/>
@@ -3296,7 +3334,7 @@
           <t>[(0.25×0.37)×3.6+0.0461-0.025]×3 = 1.0623</t>
         </is>
       </c>
-      <c r="F136" s="8" t="n"/>
+      <c r="F136" s="9" t="n"/>
     </row>
     <row r="137" ht="18" customHeight="1">
       <c r="A137" s="3" t="n"/>
@@ -3316,7 +3354,7 @@
           <t>(0.25×0.25)×3.6+0.0461-0.025 = 0.2461</t>
         </is>
       </c>
-      <c r="F137" s="8" t="n"/>
+      <c r="F137" s="9" t="n"/>
     </row>
     <row r="138" ht="18" customHeight="1">
       <c r="A138" s="3" t="n"/>
@@ -3336,7 +3374,7 @@
           <t>[(0.25×0.37)×3.6+0.0461-0.025]×3 = 1.0623</t>
         </is>
       </c>
-      <c r="F138" s="8" t="n"/>
+      <c r="F138" s="9" t="n"/>
     </row>
     <row r="139" ht="18" customHeight="1">
       <c r="A139" s="3" t="n"/>
@@ -3356,7 +3394,7 @@
           <t>(0.25×0.25)×3.6+0.0461-0.025 = 0.2461</t>
         </is>
       </c>
-      <c r="F139" s="8" t="n"/>
+      <c r="F139" s="9" t="n"/>
     </row>
     <row r="140" ht="18" customHeight="1">
       <c r="A140" s="3" t="n"/>
@@ -3376,7 +3414,7 @@
           <t>[(0.25×0.37)×3.6+0.0461-0.025]×3 = 1.0623</t>
         </is>
       </c>
-      <c r="F140" s="8" t="n"/>
+      <c r="F140" s="9" t="n"/>
     </row>
     <row r="141" ht="32" customHeight="1">
       <c r="A141" s="3" t="n"/>
@@ -3396,7 +3434,7 @@
           <t>(0.25×0.25)×3+0.0496-0.0049-0.0004-0.0002-0.0017 + (0.25×0.25)×3+0.0432-0.0049-0.0004-0.0017 + (0.25×0.25)×3+0.0496-0.0042-0.0002-0.0017 + (0.25×0.25)×3+0.0407-0.0021-0.0219-0.0065 = 0.8823</t>
         </is>
       </c>
-      <c r="F141" s="8" t="n"/>
+      <c r="F141" s="9" t="n"/>
     </row>
     <row r="142" ht="18" customHeight="1">
       <c r="A142" s="3" t="n"/>
@@ -3416,7 +3454,7 @@
           <t>[(0.25×0.37)×1.6+0.0128-0.0121]×2 + (0.25×0.37)×1.6+0.0128-0.012 = 0.4462</t>
         </is>
       </c>
-      <c r="F142" s="8" t="n"/>
+      <c r="F142" s="9" t="n"/>
     </row>
     <row r="143" ht="18" customHeight="1">
       <c r="A143" s="3" t="n"/>
@@ -3432,7 +3470,9 @@
           <t>0.0969 + 0.4302 + 0.2 + 0.924 + 0.2461 + 1.0623 + 0.2461 + 1.0623 + 0.2461 + 1.0623 + 0.8823 + 0.4462 = 6.9048 ≈ 6.90</t>
         </is>
       </c>
-      <c r="F143" s="8" t="n"/>
+      <c r="F143" s="8" t="n">
+        <v>6.9</v>
+      </c>
     </row>
     <row r="144" ht="18" customHeight="1">
       <c r="A144" s="3" t="n">
@@ -3480,7 +3520,7 @@
           <t>(0.24×0.4×3.65)-0.048 = 0.3024</t>
         </is>
       </c>
-      <c r="F145" s="8" t="n"/>
+      <c r="F145" s="9" t="n"/>
     </row>
     <row r="146" ht="18" customHeight="1">
       <c r="A146" s="3" t="n"/>
@@ -3496,7 +3536,9 @@
           <t>1.1142 + 0.3024 = 1.4166 ≈ 1.42</t>
         </is>
       </c>
-      <c r="F146" s="8" t="n"/>
+      <c r="F146" s="8" t="n">
+        <v>1.42</v>
+      </c>
     </row>
     <row r="147" ht="18" customHeight="1">
       <c r="A147" s="3" t="n">
@@ -3544,7 +3586,7 @@
           <t>[(0.048×2.3)]×2 = 0.2208</t>
         </is>
       </c>
-      <c r="F148" s="8" t="n"/>
+      <c r="F148" s="9" t="n"/>
     </row>
     <row r="149" ht="18" customHeight="1">
       <c r="A149" s="3" t="n"/>
@@ -3564,7 +3606,7 @@
           <t>[(0.048×2.9)]×4 = 0.5568</t>
         </is>
       </c>
-      <c r="F149" s="8" t="n"/>
+      <c r="F149" s="9" t="n"/>
     </row>
     <row r="150" ht="18" customHeight="1">
       <c r="A150" s="3" t="n"/>
@@ -3584,7 +3626,7 @@
           <t>[(0.048×2.3)]×2 = 0.2208</t>
         </is>
       </c>
-      <c r="F150" s="8" t="n"/>
+      <c r="F150" s="9" t="n"/>
     </row>
     <row r="151" ht="18" customHeight="1">
       <c r="A151" s="3" t="n"/>
@@ -3604,7 +3646,7 @@
           <t>[(0.048×2.9)]×2 = 0.2784</t>
         </is>
       </c>
-      <c r="F151" s="8" t="n"/>
+      <c r="F151" s="9" t="n"/>
     </row>
     <row r="152" ht="18" customHeight="1">
       <c r="A152" s="3" t="n"/>
@@ -3624,7 +3666,7 @@
           <t>[(0.048×2.3)]×2 = 0.2208</t>
         </is>
       </c>
-      <c r="F152" s="8" t="n"/>
+      <c r="F152" s="9" t="n"/>
     </row>
     <row r="153" ht="18" customHeight="1">
       <c r="A153" s="3" t="n"/>
@@ -3644,7 +3686,7 @@
           <t>[(0.048×2.9)]×2 = 0.2784</t>
         </is>
       </c>
-      <c r="F153" s="8" t="n"/>
+      <c r="F153" s="9" t="n"/>
     </row>
     <row r="154" ht="18" customHeight="1">
       <c r="A154" s="3" t="n"/>
@@ -3664,7 +3706,7 @@
           <t>[(0.048×2.3)]×2 = 0.2208</t>
         </is>
       </c>
-      <c r="F154" s="8" t="n"/>
+      <c r="F154" s="9" t="n"/>
     </row>
     <row r="155" ht="18" customHeight="1">
       <c r="A155" s="3" t="n"/>
@@ -3684,7 +3726,7 @@
           <t>[(0.048×2.9)]×2 = 0.2784</t>
         </is>
       </c>
-      <c r="F155" s="8" t="n"/>
+      <c r="F155" s="9" t="n"/>
     </row>
     <row r="156" ht="18" customHeight="1">
       <c r="A156" s="3" t="n"/>
@@ -3704,7 +3746,7 @@
           <t>(0.048×2) = 0.096</t>
         </is>
       </c>
-      <c r="F156" s="8" t="n"/>
+      <c r="F156" s="9" t="n"/>
     </row>
     <row r="157" ht="18" customHeight="1">
       <c r="A157" s="3" t="n"/>
@@ -3720,7 +3762,9 @@
           <t>0.0022 + 0.2208 + 0.5568 + 0.2208 + 0.2784 + 0.2208 + 0.2784 + 0.2208 + 0.2784 + 0.096 = 2.3734 ≈ 2.37</t>
         </is>
       </c>
-      <c r="F157" s="8" t="n"/>
+      <c r="F157" s="8" t="n">
+        <v>2.37</v>
+      </c>
     </row>
     <row r="158" ht="18" customHeight="1">
       <c r="A158" s="3" t="n">
@@ -3764,7 +3808,9 @@
           <t>31.7629 ≈ 31.76</t>
         </is>
       </c>
-      <c r="F159" s="8" t="n"/>
+      <c r="F159" s="8" t="n">
+        <v>31.76</v>
+      </c>
     </row>
     <row r="160" ht="18" customHeight="1">
       <c r="A160" s="3" t="n">
@@ -3808,7 +3854,9 @@
           <t>7.641 ≈ 7.64</t>
         </is>
       </c>
-      <c r="F161" s="8" t="n"/>
+      <c r="F161" s="8" t="n">
+        <v>7.64</v>
+      </c>
     </row>
     <row r="162" ht="18" customHeight="1">
       <c r="A162" s="3" t="n">
@@ -3856,7 +3904,7 @@
           <t>(0.048×13.53) + (0.048×5.745) + (0.048×15.53) + (0.048×11.995) = 2.2464</t>
         </is>
       </c>
-      <c r="F163" s="8" t="n"/>
+      <c r="F163" s="9" t="n"/>
     </row>
     <row r="164" ht="18" customHeight="1">
       <c r="A164" s="3" t="n"/>
@@ -3872,7 +3920,9 @@
           <t>0.536 + 2.2464 = 2.7824 ≈ 2.78</t>
         </is>
       </c>
-      <c r="F164" s="8" t="n"/>
+      <c r="F164" s="8" t="n">
+        <v>2.78</v>
+      </c>
     </row>
     <row r="165" ht="18" customHeight="1">
       <c r="A165" s="3" t="n">
@@ -3898,7 +3948,7 @@
           <t>142.8 + 147.672 = 290.472</t>
         </is>
       </c>
-      <c r="F165" s="9" t="n">
+      <c r="F165" s="10" t="n">
         <v>0.709</v>
       </c>
     </row>
@@ -3920,7 +3970,7 @@
           <t>179.984 + 185.64 = 365.624</t>
         </is>
       </c>
-      <c r="F166" s="10" t="n"/>
+      <c r="F166" s="11" t="n"/>
     </row>
     <row r="167" ht="18" customHeight="1">
       <c r="A167" s="3" t="n"/>
@@ -3940,7 +3990,7 @@
           <t>25.586 + 26.82 = 52.406</t>
         </is>
       </c>
-      <c r="F167" s="10" t="n"/>
+      <c r="F167" s="11" t="n"/>
     </row>
     <row r="168" ht="18" customHeight="1">
       <c r="A168" s="3" t="n"/>
@@ -3956,7 +4006,9 @@
           <t>(290.472 + 365.624 + 52.406) ÷ 1000 = 0.709</t>
         </is>
       </c>
-      <c r="F168" s="10" t="n"/>
+      <c r="F168" s="12" t="n">
+        <v>0.709</v>
+      </c>
     </row>
     <row r="169" ht="18" customHeight="1">
       <c r="A169" s="3" t="n">
@@ -3982,7 +4034,7 @@
           <t>34.047 = 34.047</t>
         </is>
       </c>
-      <c r="F169" s="9" t="n">
+      <c r="F169" s="10" t="n">
         <v>0.492</v>
       </c>
     </row>
@@ -4004,7 +4056,7 @@
           <t>3.783 = 3.783</t>
         </is>
       </c>
-      <c r="F170" s="10" t="n"/>
+      <c r="F170" s="11" t="n"/>
     </row>
     <row r="171" ht="18" customHeight="1">
       <c r="A171" s="3" t="n"/>
@@ -4024,7 +4076,7 @@
           <t>44.523 = 44.523</t>
         </is>
       </c>
-      <c r="F171" s="10" t="n"/>
+      <c r="F171" s="11" t="n"/>
     </row>
     <row r="172" ht="18" customHeight="1">
       <c r="A172" s="3" t="n"/>
@@ -4044,7 +4096,7 @@
           <t>4.947 = 4.947</t>
         </is>
       </c>
-      <c r="F172" s="10" t="n"/>
+      <c r="F172" s="11" t="n"/>
     </row>
     <row r="173" ht="18" customHeight="1">
       <c r="A173" s="3" t="n"/>
@@ -4064,7 +4116,7 @@
           <t>12.96 + 19.584 + 12.96 + 19.584 = 65.088</t>
         </is>
       </c>
-      <c r="F173" s="10" t="n"/>
+      <c r="F173" s="11" t="n"/>
     </row>
     <row r="174" ht="18" customHeight="1">
       <c r="A174" s="3" t="n"/>
@@ -4084,7 +4136,7 @@
           <t>44.523 = 44.523</t>
         </is>
       </c>
-      <c r="F174" s="10" t="n"/>
+      <c r="F174" s="11" t="n"/>
     </row>
     <row r="175" ht="18" customHeight="1">
       <c r="A175" s="3" t="n"/>
@@ -4104,7 +4156,7 @@
           <t>4.947 = 4.947</t>
         </is>
       </c>
-      <c r="F175" s="10" t="n"/>
+      <c r="F175" s="11" t="n"/>
     </row>
     <row r="176" ht="18" customHeight="1">
       <c r="A176" s="3" t="n"/>
@@ -4124,7 +4176,7 @@
           <t>12.24 + 19.584 + 12.24 + 19.584 = 63.648</t>
         </is>
       </c>
-      <c r="F176" s="10" t="n"/>
+      <c r="F176" s="11" t="n"/>
     </row>
     <row r="177" ht="18" customHeight="1">
       <c r="A177" s="3" t="n"/>
@@ -4144,7 +4196,7 @@
           <t>44.523 = 44.523</t>
         </is>
       </c>
-      <c r="F177" s="10" t="n"/>
+      <c r="F177" s="11" t="n"/>
     </row>
     <row r="178" ht="18" customHeight="1">
       <c r="A178" s="3" t="n"/>
@@ -4164,7 +4216,7 @@
           <t>4.947 = 4.947</t>
         </is>
       </c>
-      <c r="F178" s="10" t="n"/>
+      <c r="F178" s="11" t="n"/>
     </row>
     <row r="179" ht="18" customHeight="1">
       <c r="A179" s="3" t="n"/>
@@ -4184,7 +4236,7 @@
           <t>24.48 + 39.168 = 63.648</t>
         </is>
       </c>
-      <c r="F179" s="10" t="n"/>
+      <c r="F179" s="11" t="n"/>
     </row>
     <row r="180" ht="18" customHeight="1">
       <c r="A180" s="3" t="n"/>
@@ -4204,7 +4256,7 @@
           <t>44.523 = 44.523</t>
         </is>
       </c>
-      <c r="F180" s="10" t="n"/>
+      <c r="F180" s="11" t="n"/>
     </row>
     <row r="181" ht="18" customHeight="1">
       <c r="A181" s="3" t="n"/>
@@ -4224,7 +4276,7 @@
           <t>4.947 = 4.947</t>
         </is>
       </c>
-      <c r="F181" s="10" t="n"/>
+      <c r="F181" s="11" t="n"/>
     </row>
     <row r="182" ht="18" customHeight="1">
       <c r="A182" s="3" t="n"/>
@@ -4244,7 +4296,7 @@
           <t>24.48 + 39.168 = 63.648</t>
         </is>
       </c>
-      <c r="F182" s="10" t="n"/>
+      <c r="F182" s="11" t="n"/>
     </row>
     <row r="183" ht="18" customHeight="1">
       <c r="A183" s="3" t="n"/>
@@ -4260,7 +4312,9 @@
           <t>(34.047 + 3.783 + 44.523 + 4.947 + 65.088 + 44.523 + 4.947 + 63.648 + 44.523 + 4.947 + 63.648 + 44.523 + 4.947 + 63.648) ÷ 1000 = 0.492</t>
         </is>
       </c>
-      <c r="F183" s="10" t="n"/>
+      <c r="F183" s="12" t="n">
+        <v>0.492</v>
+      </c>
     </row>
     <row r="184" ht="18" customHeight="1">
       <c r="A184" s="3" t="n">
@@ -4286,7 +4340,7 @@
           <t>2.256 + 6.768 = 9.024</t>
         </is>
       </c>
-      <c r="F184" s="9" t="n">
+      <c r="F184" s="10" t="n">
         <v>0.175</v>
       </c>
     </row>
@@ -4308,7 +4362,7 @@
           <t>6.768 = 6.768</t>
         </is>
       </c>
-      <c r="F185" s="10" t="n"/>
+      <c r="F185" s="11" t="n"/>
     </row>
     <row r="186" ht="18" customHeight="1">
       <c r="A186" s="3" t="n"/>
@@ -4328,7 +4382,7 @@
           <t>24.816 + 9.588 = 34.404</t>
         </is>
       </c>
-      <c r="F186" s="10" t="n"/>
+      <c r="F186" s="11" t="n"/>
     </row>
     <row r="187" ht="18" customHeight="1">
       <c r="A187" s="3" t="n"/>
@@ -4348,7 +4402,7 @@
           <t>9.588 = 9.588</t>
         </is>
       </c>
-      <c r="F187" s="10" t="n"/>
+      <c r="F187" s="11" t="n"/>
     </row>
     <row r="188" ht="18" customHeight="1">
       <c r="A188" s="3" t="n"/>
@@ -4368,7 +4422,7 @@
           <t>28.764 = 28.764</t>
         </is>
       </c>
-      <c r="F188" s="10" t="n"/>
+      <c r="F188" s="11" t="n"/>
     </row>
     <row r="189" ht="18" customHeight="1">
       <c r="A189" s="3" t="n"/>
@@ -4388,7 +4442,7 @@
           <t>9.588 = 9.588</t>
         </is>
       </c>
-      <c r="F189" s="10" t="n"/>
+      <c r="F189" s="11" t="n"/>
     </row>
     <row r="190" ht="18" customHeight="1">
       <c r="A190" s="3" t="n"/>
@@ -4408,7 +4462,7 @@
           <t>28.764 = 28.764</t>
         </is>
       </c>
-      <c r="F190" s="10" t="n"/>
+      <c r="F190" s="11" t="n"/>
     </row>
     <row r="191" ht="18" customHeight="1">
       <c r="A191" s="3" t="n"/>
@@ -4428,7 +4482,7 @@
           <t>9.588 = 9.588</t>
         </is>
       </c>
-      <c r="F191" s="10" t="n"/>
+      <c r="F191" s="11" t="n"/>
     </row>
     <row r="192" ht="18" customHeight="1">
       <c r="A192" s="3" t="n"/>
@@ -4448,7 +4502,7 @@
           <t>28.764 = 28.764</t>
         </is>
       </c>
-      <c r="F192" s="10" t="n"/>
+      <c r="F192" s="11" t="n"/>
     </row>
     <row r="193" ht="18" customHeight="1">
       <c r="A193" s="3" t="n"/>
@@ -4468,7 +4522,7 @@
           <t>9.588 = 9.588</t>
         </is>
       </c>
-      <c r="F193" s="10" t="n"/>
+      <c r="F193" s="11" t="n"/>
     </row>
     <row r="194" ht="18" customHeight="1">
       <c r="A194" s="3" t="n"/>
@@ -4484,7 +4538,9 @@
           <t>(9.024 + 6.768 + 34.404 + 9.588 + 28.764 + 9.588 + 28.764 + 9.588 + 28.764 + 9.588) ÷ 1000 = 0.175</t>
         </is>
       </c>
-      <c r="F194" s="10" t="n"/>
+      <c r="F194" s="12" t="n">
+        <v>0.175</v>
+      </c>
     </row>
     <row r="195" ht="18" customHeight="1">
       <c r="A195" s="3" t="n">
@@ -4510,7 +4566,7 @@
           <t>计算书中无依据，需补充</t>
         </is>
       </c>
-      <c r="F195" s="10" t="inlineStr">
+      <c r="F195" s="11" t="inlineStr">
         <is>
           <t>需补充</t>
         </is>
@@ -4540,7 +4596,7 @@
           <t>6.508 + 10.56 + 41.08 + 6.508 + 10.56 + 8.976 + 6.95 + 12.3 + 8.25 = 111.692</t>
         </is>
       </c>
-      <c r="F196" s="9" t="n">
+      <c r="F196" s="10" t="n">
         <v>0.345</v>
       </c>
     </row>
@@ -4562,7 +4618,7 @@
           <t>41.08 + 2.9 + 4.924 + 41.08 = 89.984</t>
         </is>
       </c>
-      <c r="F197" s="10" t="n"/>
+      <c r="F197" s="11" t="n"/>
     </row>
     <row r="198" ht="18" customHeight="1">
       <c r="A198" s="3" t="n"/>
@@ -4582,7 +4638,7 @@
           <t>82.16 = 82.16</t>
         </is>
       </c>
-      <c r="F198" s="10" t="n"/>
+      <c r="F198" s="11" t="n"/>
     </row>
     <row r="199" ht="18" customHeight="1">
       <c r="A199" s="3" t="n"/>
@@ -4602,7 +4658,7 @@
           <t>34.56 + 26.456 = 61.016</t>
         </is>
       </c>
-      <c r="F199" s="10" t="n"/>
+      <c r="F199" s="11" t="n"/>
     </row>
     <row r="200" ht="18" customHeight="1">
       <c r="A200" s="3" t="n"/>
@@ -4618,7 +4674,9 @@
           <t>(111.692 + 89.984 + 82.16 + 61.016) ÷ 1000 = 0.345</t>
         </is>
       </c>
-      <c r="F200" s="10" t="n"/>
+      <c r="F200" s="12" t="n">
+        <v>0.345</v>
+      </c>
     </row>
     <row r="201" ht="18" customHeight="1">
       <c r="A201" s="3" t="n">
@@ -4644,7 +4702,7 @@
           <t>161.136 + 206.496 = 367.632</t>
         </is>
       </c>
-      <c r="F201" s="9" t="n">
+      <c r="F201" s="10" t="n">
         <v>2.989</v>
       </c>
     </row>
@@ -4666,7 +4724,7 @@
           <t>21.18 + 27.48 = 48.66</t>
         </is>
       </c>
-      <c r="F202" s="10" t="n"/>
+      <c r="F202" s="11" t="n"/>
     </row>
     <row r="203" ht="18" customHeight="1">
       <c r="A203" s="3" t="n"/>
@@ -4686,7 +4744,7 @@
           <t>22.38 + 28.68 = 51.06</t>
         </is>
       </c>
-      <c r="F203" s="10" t="n"/>
+      <c r="F203" s="11" t="n"/>
     </row>
     <row r="204" ht="18" customHeight="1">
       <c r="A204" s="3" t="n"/>
@@ -4706,7 +4764,7 @@
           <t>518.4 = 518.4</t>
         </is>
       </c>
-      <c r="F204" s="10" t="n"/>
+      <c r="F204" s="11" t="n"/>
     </row>
     <row r="205" ht="18" customHeight="1">
       <c r="A205" s="3" t="n"/>
@@ -4726,7 +4784,7 @@
           <t>72 = 72</t>
         </is>
       </c>
-      <c r="F205" s="10" t="n"/>
+      <c r="F205" s="11" t="n"/>
     </row>
     <row r="206" ht="18" customHeight="1">
       <c r="A206" s="3" t="n"/>
@@ -4746,7 +4804,7 @@
           <t>72 = 72</t>
         </is>
       </c>
-      <c r="F206" s="10" t="n"/>
+      <c r="F206" s="11" t="n"/>
     </row>
     <row r="207" ht="18" customHeight="1">
       <c r="A207" s="3" t="n"/>
@@ -4766,7 +4824,7 @@
           <t>518.4 = 518.4</t>
         </is>
       </c>
-      <c r="F207" s="10" t="n"/>
+      <c r="F207" s="11" t="n"/>
     </row>
     <row r="208" ht="18" customHeight="1">
       <c r="A208" s="3" t="n"/>
@@ -4786,7 +4844,7 @@
           <t>72 = 72</t>
         </is>
       </c>
-      <c r="F208" s="10" t="n"/>
+      <c r="F208" s="11" t="n"/>
     </row>
     <row r="209" ht="18" customHeight="1">
       <c r="A209" s="3" t="n"/>
@@ -4806,7 +4864,7 @@
           <t>72 = 72</t>
         </is>
       </c>
-      <c r="F209" s="10" t="n"/>
+      <c r="F209" s="11" t="n"/>
     </row>
     <row r="210" ht="18" customHeight="1">
       <c r="A210" s="3" t="n"/>
@@ -4826,7 +4884,7 @@
           <t>518.4 = 518.4</t>
         </is>
       </c>
-      <c r="F210" s="10" t="n"/>
+      <c r="F210" s="11" t="n"/>
     </row>
     <row r="211" ht="18" customHeight="1">
       <c r="A211" s="3" t="n"/>
@@ -4846,7 +4904,7 @@
           <t>72 = 72</t>
         </is>
       </c>
-      <c r="F211" s="10" t="n"/>
+      <c r="F211" s="11" t="n"/>
     </row>
     <row r="212" ht="18" customHeight="1">
       <c r="A212" s="3" t="n"/>
@@ -4866,7 +4924,7 @@
           <t>72 = 72</t>
         </is>
       </c>
-      <c r="F212" s="10" t="n"/>
+      <c r="F212" s="11" t="n"/>
     </row>
     <row r="213" ht="18" customHeight="1">
       <c r="A213" s="3" t="n"/>
@@ -4886,7 +4944,7 @@
           <t>233.928 + 188.568 = 422.496</t>
         </is>
       </c>
-      <c r="F213" s="10" t="n"/>
+      <c r="F213" s="11" t="n"/>
     </row>
     <row r="214" ht="18" customHeight="1">
       <c r="A214" s="3" t="n"/>
@@ -4906,7 +4964,7 @@
           <t>18.42 + 10.476 + 14.64 + 12.996 = 56.532</t>
         </is>
       </c>
-      <c r="F214" s="10" t="n"/>
+      <c r="F214" s="11" t="n"/>
     </row>
     <row r="215" ht="18" customHeight="1">
       <c r="A215" s="3" t="n"/>
@@ -4926,7 +4984,7 @@
           <t>24.56 + 19.52 + 5.238 + 6.498 = 55.816</t>
         </is>
       </c>
-      <c r="F215" s="10" t="n"/>
+      <c r="F215" s="11" t="n"/>
     </row>
     <row r="216" ht="18" customHeight="1">
       <c r="A216" s="3" t="n"/>
@@ -4942,7 +5000,9 @@
           <t>(367.632 + 48.66 + 51.06 + 518.4 + 72 + 72 + 518.4 + 72 + 72 + 518.4 + 72 + 72 + 422.496 + 56.532 + 55.816) ÷ 1000 = 2.989</t>
         </is>
       </c>
-      <c r="F216" s="10" t="n"/>
+      <c r="F216" s="12" t="n">
+        <v>2.989</v>
+      </c>
     </row>
     <row r="217" ht="18" customHeight="1">
       <c r="A217" s="3" t="n">
@@ -4968,7 +5028,7 @@
           <t>25.944 + 39.776 + 22.36 + 29.276 = 117.356</t>
         </is>
       </c>
-      <c r="F217" s="9" t="n">
+      <c r="F217" s="10" t="n">
         <v>0.968</v>
       </c>
     </row>
@@ -4990,7 +5050,7 @@
           <t>179.824 + 71.136 = 250.96</t>
         </is>
       </c>
-      <c r="F218" s="10" t="n"/>
+      <c r="F218" s="11" t="n"/>
     </row>
     <row r="219" ht="18" customHeight="1">
       <c r="A219" s="3" t="n"/>
@@ -5010,7 +5070,7 @@
           <t>213.408 = 213.408</t>
         </is>
       </c>
-      <c r="F219" s="10" t="n"/>
+      <c r="F219" s="11" t="n"/>
     </row>
     <row r="220" ht="18" customHeight="1">
       <c r="A220" s="3" t="n"/>
@@ -5030,7 +5090,7 @@
           <t>213.408 = 213.408</t>
         </is>
       </c>
-      <c r="F220" s="10" t="n"/>
+      <c r="F220" s="11" t="n"/>
     </row>
     <row r="221" ht="18" customHeight="1">
       <c r="A221" s="3" t="n"/>
@@ -5050,7 +5110,7 @@
           <t>96.864 + 76.116 = 172.98</t>
         </is>
       </c>
-      <c r="F221" s="10" t="n"/>
+      <c r="F221" s="11" t="n"/>
     </row>
     <row r="222" ht="18" customHeight="1">
       <c r="A222" s="3" t="n"/>
@@ -5066,7 +5126,9 @@
           <t>(117.356 + 250.96 + 213.408 + 213.408 + 172.98) ÷ 1000 = 0.968</t>
         </is>
       </c>
-      <c r="F222" s="10" t="n"/>
+      <c r="F222" s="12" t="n">
+        <v>0.968</v>
+      </c>
     </row>
     <row r="223" ht="18" customHeight="1">
       <c r="A223" s="3" t="n">
@@ -5092,7 +5154,7 @@
           <t>1.08 + 2.16 = 3.24</t>
         </is>
       </c>
-      <c r="F223" s="9" t="n">
+      <c r="F223" s="10" t="n">
         <v>0.307</v>
       </c>
     </row>
@@ -5114,7 +5176,7 @@
           <t>2.16 = 2.16</t>
         </is>
       </c>
-      <c r="F224" s="10" t="n"/>
+      <c r="F224" s="11" t="n"/>
     </row>
     <row r="225" ht="18" customHeight="1">
       <c r="A225" s="3" t="n"/>
@@ -5134,7 +5196,7 @@
           <t>10.374 + 1.224 = 11.598</t>
         </is>
       </c>
-      <c r="F225" s="10" t="n"/>
+      <c r="F225" s="11" t="n"/>
     </row>
     <row r="226" ht="18" customHeight="1">
       <c r="A226" s="3" t="n"/>
@@ -5154,7 +5216,7 @@
           <t>3.584 = 3.584</t>
         </is>
       </c>
-      <c r="F226" s="10" t="n"/>
+      <c r="F226" s="11" t="n"/>
     </row>
     <row r="227" ht="18" customHeight="1">
       <c r="A227" s="3" t="n"/>
@@ -5174,7 +5236,7 @@
           <t>18.031 = 18.031</t>
         </is>
       </c>
-      <c r="F227" s="10" t="n"/>
+      <c r="F227" s="11" t="n"/>
     </row>
     <row r="228" ht="18" customHeight="1">
       <c r="A228" s="3" t="n"/>
@@ -5194,7 +5256,7 @@
           <t>3.584 = 3.584</t>
         </is>
       </c>
-      <c r="F228" s="10" t="n"/>
+      <c r="F228" s="11" t="n"/>
     </row>
     <row r="229" ht="18" customHeight="1">
       <c r="A229" s="3" t="n"/>
@@ -5214,7 +5276,7 @@
           <t>0.504 = 0.504</t>
         </is>
       </c>
-      <c r="F229" s="10" t="n"/>
+      <c r="F229" s="11" t="n"/>
     </row>
     <row r="230" ht="18" customHeight="1">
       <c r="A230" s="3" t="n"/>
@@ -5234,7 +5296,7 @@
           <t>4.788 = 4.788</t>
         </is>
       </c>
-      <c r="F230" s="10" t="n"/>
+      <c r="F230" s="11" t="n"/>
     </row>
     <row r="231" ht="18" customHeight="1">
       <c r="A231" s="3" t="n"/>
@@ -5254,7 +5316,7 @@
           <t>2.457 = 2.457</t>
         </is>
       </c>
-      <c r="F231" s="10" t="n"/>
+      <c r="F231" s="11" t="n"/>
     </row>
     <row r="232" ht="18" customHeight="1">
       <c r="A232" s="3" t="n"/>
@@ -5274,7 +5336,7 @@
           <t>2.142 = 2.142</t>
         </is>
       </c>
-      <c r="F232" s="10" t="n"/>
+      <c r="F232" s="11" t="n"/>
     </row>
     <row r="233" ht="18" customHeight="1">
       <c r="A233" s="3" t="n"/>
@@ -5294,7 +5356,7 @@
           <t>19.712 = 19.712</t>
         </is>
       </c>
-      <c r="F233" s="10" t="n"/>
+      <c r="F233" s="11" t="n"/>
     </row>
     <row r="234" ht="18" customHeight="1">
       <c r="A234" s="3" t="n"/>
@@ -5314,7 +5376,7 @@
           <t>2.394 = 2.394</t>
         </is>
       </c>
-      <c r="F234" s="10" t="n"/>
+      <c r="F234" s="11" t="n"/>
     </row>
     <row r="235" ht="18" customHeight="1">
       <c r="A235" s="3" t="n"/>
@@ -5334,7 +5396,7 @@
           <t>2.394 = 2.394</t>
         </is>
       </c>
-      <c r="F235" s="10" t="n"/>
+      <c r="F235" s="11" t="n"/>
     </row>
     <row r="236" ht="18" customHeight="1">
       <c r="A236" s="3" t="n"/>
@@ -5354,7 +5416,7 @@
           <t>2.394 = 2.394</t>
         </is>
       </c>
-      <c r="F236" s="10" t="n"/>
+      <c r="F236" s="11" t="n"/>
     </row>
     <row r="237" ht="18" customHeight="1">
       <c r="A237" s="3" t="n"/>
@@ -5374,7 +5436,7 @@
           <t>2.457 = 2.457</t>
         </is>
       </c>
-      <c r="F237" s="10" t="n"/>
+      <c r="F237" s="11" t="n"/>
     </row>
     <row r="238" ht="18" customHeight="1">
       <c r="A238" s="3" t="n"/>
@@ -5394,7 +5456,7 @@
           <t>2.394 = 2.394</t>
         </is>
       </c>
-      <c r="F238" s="10" t="n"/>
+      <c r="F238" s="11" t="n"/>
     </row>
     <row r="239" ht="18" customHeight="1">
       <c r="A239" s="3" t="n"/>
@@ -5414,7 +5476,7 @@
           <t>4.914 = 4.914</t>
         </is>
       </c>
-      <c r="F239" s="10" t="n"/>
+      <c r="F239" s="11" t="n"/>
     </row>
     <row r="240" ht="18" customHeight="1">
       <c r="A240" s="3" t="n"/>
@@ -5434,7 +5496,7 @@
           <t>18.688 = 18.688</t>
         </is>
       </c>
-      <c r="F240" s="10" t="n"/>
+      <c r="F240" s="11" t="n"/>
     </row>
     <row r="241" ht="18" customHeight="1">
       <c r="A241" s="3" t="n"/>
@@ -5454,7 +5516,7 @@
           <t>3.165 = 3.165</t>
         </is>
       </c>
-      <c r="F241" s="10" t="n"/>
+      <c r="F241" s="11" t="n"/>
     </row>
     <row r="242" ht="18" customHeight="1">
       <c r="A242" s="3" t="n"/>
@@ -5474,7 +5536,7 @@
           <t>19.712 = 19.712</t>
         </is>
       </c>
-      <c r="F242" s="10" t="n"/>
+      <c r="F242" s="11" t="n"/>
     </row>
     <row r="243" ht="18" customHeight="1">
       <c r="A243" s="3" t="n"/>
@@ -5494,7 +5556,7 @@
           <t>7.168 = 7.168</t>
         </is>
       </c>
-      <c r="F243" s="10" t="n"/>
+      <c r="F243" s="11" t="n"/>
     </row>
     <row r="244" ht="18" customHeight="1">
       <c r="A244" s="3" t="n"/>
@@ -5514,7 +5576,7 @@
           <t>2.11 = 2.11</t>
         </is>
       </c>
-      <c r="F244" s="10" t="n"/>
+      <c r="F244" s="11" t="n"/>
     </row>
     <row r="245" ht="18" customHeight="1">
       <c r="A245" s="3" t="n"/>
@@ -5534,7 +5596,7 @@
           <t>3.961 + 3.728 = 7.689</t>
         </is>
       </c>
-      <c r="F245" s="10" t="n"/>
+      <c r="F245" s="11" t="n"/>
     </row>
     <row r="246" ht="18" customHeight="1">
       <c r="A246" s="3" t="n"/>
@@ -5554,7 +5616,7 @@
           <t>2.394 = 2.394</t>
         </is>
       </c>
-      <c r="F246" s="10" t="n"/>
+      <c r="F246" s="11" t="n"/>
     </row>
     <row r="247" ht="18" customHeight="1">
       <c r="A247" s="3" t="n"/>
@@ -5574,7 +5636,7 @@
           <t>2.394 = 2.394</t>
         </is>
       </c>
-      <c r="F247" s="10" t="n"/>
+      <c r="F247" s="11" t="n"/>
     </row>
     <row r="248" ht="18" customHeight="1">
       <c r="A248" s="3" t="n"/>
@@ -5594,7 +5656,7 @@
           <t>2.394 = 2.394</t>
         </is>
       </c>
-      <c r="F248" s="10" t="n"/>
+      <c r="F248" s="11" t="n"/>
     </row>
     <row r="249" ht="18" customHeight="1">
       <c r="A249" s="3" t="n"/>
@@ -5614,7 +5676,7 @@
           <t>2.457 = 2.457</t>
         </is>
       </c>
-      <c r="F249" s="10" t="n"/>
+      <c r="F249" s="11" t="n"/>
     </row>
     <row r="250" ht="18" customHeight="1">
       <c r="A250" s="3" t="n"/>
@@ -5634,7 +5696,7 @@
           <t>2.394 = 2.394</t>
         </is>
       </c>
-      <c r="F250" s="10" t="n"/>
+      <c r="F250" s="11" t="n"/>
     </row>
     <row r="251" ht="18" customHeight="1">
       <c r="A251" s="3" t="n"/>
@@ -5654,7 +5716,7 @@
           <t>4.914 = 4.914</t>
         </is>
       </c>
-      <c r="F251" s="10" t="n"/>
+      <c r="F251" s="11" t="n"/>
     </row>
     <row r="252" ht="18" customHeight="1">
       <c r="A252" s="3" t="n"/>
@@ -5674,7 +5736,7 @@
           <t>18.688 = 18.688</t>
         </is>
       </c>
-      <c r="F252" s="10" t="n"/>
+      <c r="F252" s="11" t="n"/>
     </row>
     <row r="253" ht="18" customHeight="1">
       <c r="A253" s="3" t="n"/>
@@ -5694,7 +5756,7 @@
           <t>3.165 = 3.165</t>
         </is>
       </c>
-      <c r="F253" s="10" t="n"/>
+      <c r="F253" s="11" t="n"/>
     </row>
     <row r="254" ht="18" customHeight="1">
       <c r="A254" s="3" t="n"/>
@@ -5714,7 +5776,7 @@
           <t>19.712 = 19.712</t>
         </is>
       </c>
-      <c r="F254" s="10" t="n"/>
+      <c r="F254" s="11" t="n"/>
     </row>
     <row r="255" ht="18" customHeight="1">
       <c r="A255" s="3" t="n"/>
@@ -5734,7 +5796,7 @@
           <t>7.168 = 7.168</t>
         </is>
       </c>
-      <c r="F255" s="10" t="n"/>
+      <c r="F255" s="11" t="n"/>
     </row>
     <row r="256" ht="18" customHeight="1">
       <c r="A256" s="3" t="n"/>
@@ -5754,7 +5816,7 @@
           <t>2.11 = 2.11</t>
         </is>
       </c>
-      <c r="F256" s="10" t="n"/>
+      <c r="F256" s="11" t="n"/>
     </row>
     <row r="257" ht="18" customHeight="1">
       <c r="A257" s="3" t="n"/>
@@ -5774,7 +5836,7 @@
           <t>3.728 + 3.961 = 7.689</t>
         </is>
       </c>
-      <c r="F257" s="10" t="n"/>
+      <c r="F257" s="11" t="n"/>
     </row>
     <row r="258" ht="18" customHeight="1">
       <c r="A258" s="3" t="n"/>
@@ -5794,7 +5856,7 @@
           <t>2.394 + 2.394 = 4.788</t>
         </is>
       </c>
-      <c r="F258" s="10" t="n"/>
+      <c r="F258" s="11" t="n"/>
     </row>
     <row r="259" ht="18" customHeight="1">
       <c r="A259" s="3" t="n"/>
@@ -5814,7 +5876,7 @@
           <t>2.394 + 2.394 = 4.788</t>
         </is>
       </c>
-      <c r="F259" s="10" t="n"/>
+      <c r="F259" s="11" t="n"/>
     </row>
     <row r="260" ht="18" customHeight="1">
       <c r="A260" s="3" t="n"/>
@@ -5834,7 +5896,7 @@
           <t>2.457 = 2.457</t>
         </is>
       </c>
-      <c r="F260" s="10" t="n"/>
+      <c r="F260" s="11" t="n"/>
     </row>
     <row r="261" ht="18" customHeight="1">
       <c r="A261" s="3" t="n"/>
@@ -5854,7 +5916,7 @@
           <t>2.142 = 2.142</t>
         </is>
       </c>
-      <c r="F261" s="10" t="n"/>
+      <c r="F261" s="11" t="n"/>
     </row>
     <row r="262" ht="18" customHeight="1">
       <c r="A262" s="3" t="n"/>
@@ -5874,7 +5936,7 @@
           <t>18.688 = 18.688</t>
         </is>
       </c>
-      <c r="F262" s="10" t="n"/>
+      <c r="F262" s="11" t="n"/>
     </row>
     <row r="263" ht="18" customHeight="1">
       <c r="A263" s="3" t="n"/>
@@ -5894,7 +5956,7 @@
           <t>19.712 = 19.712</t>
         </is>
       </c>
-      <c r="F263" s="10" t="n"/>
+      <c r="F263" s="11" t="n"/>
     </row>
     <row r="264" ht="18" customHeight="1">
       <c r="A264" s="3" t="n"/>
@@ -5914,7 +5976,7 @@
           <t>3.961 = 3.961</t>
         </is>
       </c>
-      <c r="F264" s="10" t="n"/>
+      <c r="F264" s="11" t="n"/>
     </row>
     <row r="265" ht="18" customHeight="1">
       <c r="A265" s="3" t="n"/>
@@ -5934,7 +5996,7 @@
           <t>15.36 = 15.36</t>
         </is>
       </c>
-      <c r="F265" s="10" t="n"/>
+      <c r="F265" s="11" t="n"/>
     </row>
     <row r="266" ht="18" customHeight="1">
       <c r="A266" s="3" t="n"/>
@@ -5954,7 +6016,7 @@
           <t>4.608 = 4.608</t>
         </is>
       </c>
-      <c r="F266" s="10" t="n"/>
+      <c r="F266" s="11" t="n"/>
     </row>
     <row r="267" ht="18" customHeight="1">
       <c r="A267" s="3" t="n"/>
@@ -5974,7 +6036,7 @@
           <t>4.608 = 4.608</t>
         </is>
       </c>
-      <c r="F267" s="10" t="n"/>
+      <c r="F267" s="11" t="n"/>
     </row>
     <row r="268" ht="18" customHeight="1">
       <c r="A268" s="3" t="n"/>
@@ -5994,7 +6056,7 @@
           <t>3.495 = 3.495</t>
         </is>
       </c>
-      <c r="F268" s="10" t="n"/>
+      <c r="F268" s="11" t="n"/>
     </row>
     <row r="269" ht="46" customHeight="1">
       <c r="A269" s="3" t="n"/>
@@ -6010,7 +6072,9 @@
           <t>(3.24 + 2.16 + 11.598 + 3.584 + 18.031 + 3.584 + 0.504 + 4.788 + 2.457 + 2.142 + 19.712 + 2.394 + 2.394 + 2.394 + 2.457 + 2.394 + 4.914 + 18.688 + 3.165 + 19.712 + 7.168 + 2.11 + 7.689 + 2.394 + 2.394 + 2.394 + 2.457 + 2.394 + 4.914 + 18.688 + 3.165 + 19.712 + 7.168 + 2.11 + 7.689 + 4.788 + 4.788 + 2.457 + 2.142 + 18.688 + 19.712 + 3.961 + 15.36 + 4.608 + 4.608 + 3.495) ÷ 1000 = 0.307</t>
         </is>
       </c>
-      <c r="F269" s="10" t="n"/>
+      <c r="F269" s="12" t="n">
+        <v>0.307</v>
+      </c>
     </row>
     <row r="270" ht="18" customHeight="1">
       <c r="A270" s="3" t="n">
@@ -6036,7 +6100,7 @@
           <t>16.912 + 34.428 = 51.34</t>
         </is>
       </c>
-      <c r="F270" s="9" t="n">
+      <c r="F270" s="10" t="n">
         <v>1.428</v>
       </c>
     </row>
@@ -6058,7 +6122,7 @@
           <t>34.428 = 34.428</t>
         </is>
       </c>
-      <c r="F271" s="10" t="n"/>
+      <c r="F271" s="11" t="n"/>
     </row>
     <row r="272" ht="18" customHeight="1">
       <c r="A272" s="3" t="n"/>
@@ -6078,7 +6142,7 @@
           <t>19.328 = 19.328</t>
         </is>
       </c>
-      <c r="F272" s="10" t="n"/>
+      <c r="F272" s="11" t="n"/>
     </row>
     <row r="273" ht="18" customHeight="1">
       <c r="A273" s="3" t="n"/>
@@ -6098,7 +6162,7 @@
           <t>6.454 = 6.454</t>
         </is>
       </c>
-      <c r="F273" s="10" t="n"/>
+      <c r="F273" s="11" t="n"/>
     </row>
     <row r="274" ht="18" customHeight="1">
       <c r="A274" s="3" t="n"/>
@@ -6118,7 +6182,7 @@
           <t>12.908 + 85.84 = 98.748</t>
         </is>
       </c>
-      <c r="F274" s="10" t="n"/>
+      <c r="F274" s="11" t="n"/>
     </row>
     <row r="275" ht="18" customHeight="1">
       <c r="A275" s="3" t="n"/>
@@ -6138,7 +6202,7 @@
           <t>6.454 + 42.92 = 49.374</t>
         </is>
       </c>
-      <c r="F275" s="10" t="n"/>
+      <c r="F275" s="11" t="n"/>
     </row>
     <row r="276" ht="18" customHeight="1">
       <c r="A276" s="3" t="n"/>
@@ -6158,7 +6222,7 @@
           <t>19.362 + 25.042 = 44.404</t>
         </is>
       </c>
-      <c r="F276" s="10" t="n"/>
+      <c r="F276" s="11" t="n"/>
     </row>
     <row r="277" ht="18" customHeight="1">
       <c r="A277" s="3" t="n"/>
@@ -6178,7 +6242,7 @@
           <t>45.178 = 45.178</t>
         </is>
       </c>
-      <c r="F277" s="10" t="n"/>
+      <c r="F277" s="11" t="n"/>
     </row>
     <row r="278" ht="18" customHeight="1">
       <c r="A278" s="3" t="n"/>
@@ -6198,7 +6262,7 @@
           <t>33.653 = 33.653</t>
         </is>
       </c>
-      <c r="F278" s="10" t="n"/>
+      <c r="F278" s="11" t="n"/>
     </row>
     <row r="279" ht="18" customHeight="1">
       <c r="A279" s="3" t="n"/>
@@ -6218,7 +6282,7 @@
           <t>6.454 + 36.54 = 42.994</t>
         </is>
       </c>
-      <c r="F279" s="10" t="n"/>
+      <c r="F279" s="11" t="n"/>
     </row>
     <row r="280" ht="18" customHeight="1">
       <c r="A280" s="3" t="n"/>
@@ -6238,7 +6302,7 @@
           <t>6.454 + 49.88 = 56.334</t>
         </is>
       </c>
-      <c r="F280" s="10" t="n"/>
+      <c r="F280" s="11" t="n"/>
     </row>
     <row r="281" ht="18" customHeight="1">
       <c r="A281" s="3" t="n"/>
@@ -6258,7 +6322,7 @@
           <t>6.454 + 46.4 = 52.854</t>
         </is>
       </c>
-      <c r="F281" s="10" t="n"/>
+      <c r="F281" s="11" t="n"/>
     </row>
     <row r="282" ht="18" customHeight="1">
       <c r="A282" s="3" t="n"/>
@@ -6278,7 +6342,7 @@
           <t>6.454 + 49.88 = 56.334</t>
         </is>
       </c>
-      <c r="F282" s="10" t="n"/>
+      <c r="F282" s="11" t="n"/>
     </row>
     <row r="283" ht="18" customHeight="1">
       <c r="A283" s="3" t="n"/>
@@ -6298,7 +6362,7 @@
           <t>6.454 + 46.4 = 52.854</t>
         </is>
       </c>
-      <c r="F283" s="10" t="n"/>
+      <c r="F283" s="11" t="n"/>
     </row>
     <row r="284" ht="18" customHeight="1">
       <c r="A284" s="3" t="n"/>
@@ -6318,7 +6382,7 @@
           <t>19.362 + 25.042 = 44.404</t>
         </is>
       </c>
-      <c r="F284" s="10" t="n"/>
+      <c r="F284" s="11" t="n"/>
     </row>
     <row r="285" ht="18" customHeight="1">
       <c r="A285" s="3" t="n"/>
@@ -6338,7 +6402,7 @@
           <t>47.944 = 47.944</t>
         </is>
       </c>
-      <c r="F285" s="10" t="n"/>
+      <c r="F285" s="11" t="n"/>
     </row>
     <row r="286" ht="18" customHeight="1">
       <c r="A286" s="3" t="n"/>
@@ -6358,7 +6422,7 @@
           <t>6.454 + 36.54 = 42.994</t>
         </is>
       </c>
-      <c r="F286" s="10" t="n"/>
+      <c r="F286" s="11" t="n"/>
     </row>
     <row r="287" ht="18" customHeight="1">
       <c r="A287" s="3" t="n"/>
@@ -6378,7 +6442,7 @@
           <t>6.454 + 49.88 = 56.334</t>
         </is>
       </c>
-      <c r="F287" s="10" t="n"/>
+      <c r="F287" s="11" t="n"/>
     </row>
     <row r="288" ht="18" customHeight="1">
       <c r="A288" s="3" t="n"/>
@@ -6398,7 +6462,7 @@
           <t>6.454 + 46.4 = 52.854</t>
         </is>
       </c>
-      <c r="F288" s="10" t="n"/>
+      <c r="F288" s="11" t="n"/>
     </row>
     <row r="289" ht="18" customHeight="1">
       <c r="A289" s="3" t="n"/>
@@ -6418,7 +6482,7 @@
           <t>6.454 + 49.88 = 56.334</t>
         </is>
       </c>
-      <c r="F289" s="10" t="n"/>
+      <c r="F289" s="11" t="n"/>
     </row>
     <row r="290" ht="18" customHeight="1">
       <c r="A290" s="3" t="n"/>
@@ -6438,7 +6502,7 @@
           <t>6.454 + 46.4 = 52.854</t>
         </is>
       </c>
-      <c r="F290" s="10" t="n"/>
+      <c r="F290" s="11" t="n"/>
     </row>
     <row r="291" ht="18" customHeight="1">
       <c r="A291" s="3" t="n"/>
@@ -6458,7 +6522,7 @@
           <t>19.362 + 25.042 = 44.404</t>
         </is>
       </c>
-      <c r="F291" s="10" t="n"/>
+      <c r="F291" s="11" t="n"/>
     </row>
     <row r="292" ht="18" customHeight="1">
       <c r="A292" s="3" t="n"/>
@@ -6478,7 +6542,7 @@
           <t>47.944 = 47.944</t>
         </is>
       </c>
-      <c r="F292" s="10" t="n"/>
+      <c r="F292" s="11" t="n"/>
     </row>
     <row r="293" ht="18" customHeight="1">
       <c r="A293" s="3" t="n"/>
@@ -6498,7 +6562,7 @@
           <t>6.454 + 36.54 + 6.454 + 36.54 = 85.988</t>
         </is>
       </c>
-      <c r="F293" s="10" t="n"/>
+      <c r="F293" s="11" t="n"/>
     </row>
     <row r="294" ht="18" customHeight="1">
       <c r="A294" s="3" t="n"/>
@@ -6518,7 +6582,7 @@
           <t>6.454 + 46.4 + 6.454 + 46.4 = 105.708</t>
         </is>
       </c>
-      <c r="F294" s="10" t="n"/>
+      <c r="F294" s="11" t="n"/>
     </row>
     <row r="295" ht="18" customHeight="1">
       <c r="A295" s="3" t="n"/>
@@ -6538,7 +6602,7 @@
           <t>6.454 + 49.88 = 56.334</t>
         </is>
       </c>
-      <c r="F295" s="10" t="n"/>
+      <c r="F295" s="11" t="n"/>
     </row>
     <row r="296" ht="18" customHeight="1">
       <c r="A296" s="3" t="n"/>
@@ -6558,7 +6622,7 @@
           <t>19.362 + 25.042 = 44.404</t>
         </is>
       </c>
-      <c r="F296" s="10" t="n"/>
+      <c r="F296" s="11" t="n"/>
     </row>
     <row r="297" ht="18" customHeight="1">
       <c r="A297" s="3" t="n"/>
@@ -6578,7 +6642,7 @@
           <t>45.178 = 45.178</t>
         </is>
       </c>
-      <c r="F297" s="10" t="n"/>
+      <c r="F297" s="11" t="n"/>
     </row>
     <row r="298" ht="32" customHeight="1">
       <c r="A298" s="3" t="n"/>
@@ -6594,7 +6658,9 @@
           <t>(51.34 + 34.428 + 19.328 + 6.454 + 98.748 + 49.374 + 44.404 + 45.178 + 33.653 + 42.994 + 56.334 + 52.854 + 56.334 + 52.854 + 44.404 + 47.944 + 42.994 + 56.334 + 52.854 + 56.334 + 52.854 + 44.404 + 47.944 + 85.988 + 105.708 + 56.334 + 44.404 + 45.178) ÷ 1000 = 1.428</t>
         </is>
       </c>
-      <c r="F298" s="10" t="n"/>
+      <c r="F298" s="12" t="n">
+        <v>1.428</v>
+      </c>
     </row>
     <row r="299" ht="18" customHeight="1">
       <c r="A299" s="3" t="n">
@@ -6620,7 +6686,7 @@
           <t>10.186 + 21.294 = 31.48</t>
         </is>
       </c>
-      <c r="F299" s="9" t="n">
+      <c r="F299" s="10" t="n">
         <v>0.717</v>
       </c>
     </row>
@@ -6642,7 +6708,7 @@
           <t>21.294 = 21.294</t>
         </is>
       </c>
-      <c r="F300" s="10" t="n"/>
+      <c r="F300" s="11" t="n"/>
     </row>
     <row r="301" ht="18" customHeight="1">
       <c r="A301" s="3" t="n"/>
@@ -6662,7 +6728,7 @@
           <t>11.606 = 11.606</t>
         </is>
       </c>
-      <c r="F301" s="10" t="n"/>
+      <c r="F301" s="11" t="n"/>
     </row>
     <row r="302" ht="18" customHeight="1">
       <c r="A302" s="3" t="n"/>
@@ -6682,7 +6748,7 @@
           <t>24.304 + 24.082 = 48.386</t>
         </is>
       </c>
-      <c r="F302" s="10" t="n"/>
+      <c r="F302" s="11" t="n"/>
     </row>
     <row r="303" ht="18" customHeight="1">
       <c r="A303" s="3" t="n"/>
@@ -6702,7 +6768,7 @@
           <t>48.164 = 48.164</t>
         </is>
       </c>
-      <c r="F303" s="10" t="n"/>
+      <c r="F303" s="11" t="n"/>
     </row>
     <row r="304" ht="18" customHeight="1">
       <c r="A304" s="3" t="n"/>
@@ -6722,7 +6788,7 @@
           <t>24.082 = 24.082</t>
         </is>
       </c>
-      <c r="F304" s="10" t="n"/>
+      <c r="F304" s="11" t="n"/>
     </row>
     <row r="305" ht="18" customHeight="1">
       <c r="A305" s="3" t="n"/>
@@ -6742,7 +6808,7 @@
           <t>23.212 = 23.212</t>
         </is>
       </c>
-      <c r="F305" s="10" t="n"/>
+      <c r="F305" s="11" t="n"/>
     </row>
     <row r="306" ht="18" customHeight="1">
       <c r="A306" s="3" t="n"/>
@@ -6762,7 +6828,7 @@
           <t>24.082 = 24.082</t>
         </is>
       </c>
-      <c r="F306" s="10" t="n"/>
+      <c r="F306" s="11" t="n"/>
     </row>
     <row r="307" ht="18" customHeight="1">
       <c r="A307" s="3" t="n"/>
@@ -6782,7 +6848,7 @@
           <t>24.082 = 24.082</t>
         </is>
       </c>
-      <c r="F307" s="10" t="n"/>
+      <c r="F307" s="11" t="n"/>
     </row>
     <row r="308" ht="18" customHeight="1">
       <c r="A308" s="3" t="n"/>
@@ -6802,7 +6868,7 @@
           <t>24.082 = 24.082</t>
         </is>
       </c>
-      <c r="F308" s="10" t="n"/>
+      <c r="F308" s="11" t="n"/>
     </row>
     <row r="309" ht="18" customHeight="1">
       <c r="A309" s="3" t="n"/>
@@ -6822,7 +6888,7 @@
           <t>24.082 + 2.718 = 26.8</t>
         </is>
       </c>
-      <c r="F309" s="10" t="n"/>
+      <c r="F309" s="11" t="n"/>
     </row>
     <row r="310" ht="18" customHeight="1">
       <c r="A310" s="3" t="n"/>
@@ -6842,7 +6908,7 @@
           <t>24.082 = 24.082</t>
         </is>
       </c>
-      <c r="F310" s="10" t="n"/>
+      <c r="F310" s="11" t="n"/>
     </row>
     <row r="311" ht="18" customHeight="1">
       <c r="A311" s="3" t="n"/>
@@ -6862,7 +6928,7 @@
           <t>55.376 = 55.376</t>
         </is>
       </c>
-      <c r="F311" s="10" t="n"/>
+      <c r="F311" s="11" t="n"/>
     </row>
     <row r="312" ht="18" customHeight="1">
       <c r="A312" s="3" t="n"/>
@@ -6882,7 +6948,7 @@
           <t>24.082 = 24.082</t>
         </is>
       </c>
-      <c r="F312" s="10" t="n"/>
+      <c r="F312" s="11" t="n"/>
     </row>
     <row r="313" ht="18" customHeight="1">
       <c r="A313" s="3" t="n"/>
@@ -6902,7 +6968,7 @@
           <t>24.082 = 24.082</t>
         </is>
       </c>
-      <c r="F313" s="10" t="n"/>
+      <c r="F313" s="11" t="n"/>
     </row>
     <row r="314" ht="18" customHeight="1">
       <c r="A314" s="3" t="n"/>
@@ -6922,7 +6988,7 @@
           <t>24.082 = 24.082</t>
         </is>
       </c>
-      <c r="F314" s="10" t="n"/>
+      <c r="F314" s="11" t="n"/>
     </row>
     <row r="315" ht="18" customHeight="1">
       <c r="A315" s="3" t="n"/>
@@ -6942,7 +7008,7 @@
           <t>24.082 + 2.718 = 26.8</t>
         </is>
       </c>
-      <c r="F315" s="10" t="n"/>
+      <c r="F315" s="11" t="n"/>
     </row>
     <row r="316" ht="18" customHeight="1">
       <c r="A316" s="3" t="n"/>
@@ -6962,7 +7028,7 @@
           <t>24.082 = 24.082</t>
         </is>
       </c>
-      <c r="F316" s="10" t="n"/>
+      <c r="F316" s="11" t="n"/>
     </row>
     <row r="317" ht="18" customHeight="1">
       <c r="A317" s="3" t="n"/>
@@ -6982,7 +7048,7 @@
           <t>55.376 = 55.376</t>
         </is>
       </c>
-      <c r="F317" s="10" t="n"/>
+      <c r="F317" s="11" t="n"/>
     </row>
     <row r="318" ht="18" customHeight="1">
       <c r="A318" s="3" t="n"/>
@@ -7002,7 +7068,7 @@
           <t>24.082 + 2.718 + 24.082 = 50.882</t>
         </is>
       </c>
-      <c r="F318" s="10" t="n"/>
+      <c r="F318" s="11" t="n"/>
     </row>
     <row r="319" ht="18" customHeight="1">
       <c r="A319" s="3" t="n"/>
@@ -7022,7 +7088,7 @@
           <t>24.082 + 2.718 + 24.082 = 50.882</t>
         </is>
       </c>
-      <c r="F319" s="10" t="n"/>
+      <c r="F319" s="11" t="n"/>
     </row>
     <row r="320" ht="18" customHeight="1">
       <c r="A320" s="3" t="n"/>
@@ -7042,7 +7108,7 @@
           <t>24.082 + 2.718 = 26.8</t>
         </is>
       </c>
-      <c r="F320" s="10" t="n"/>
+      <c r="F320" s="11" t="n"/>
     </row>
     <row r="321" ht="18" customHeight="1">
       <c r="A321" s="3" t="n"/>
@@ -7062,7 +7128,7 @@
           <t>23.212 = 23.212</t>
         </is>
       </c>
-      <c r="F321" s="10" t="n"/>
+      <c r="F321" s="11" t="n"/>
     </row>
     <row r="322" ht="32" customHeight="1">
       <c r="A322" s="3" t="n"/>
@@ -7078,7 +7144,9 @@
           <t>(31.48 + 21.294 + 11.606 + 48.386 + 48.164 + 24.082 + 23.212 + 24.082 + 24.082 + 24.082 + 26.8 + 24.082 + 55.376 + 24.082 + 24.082 + 24.082 + 26.8 + 24.082 + 55.376 + 50.882 + 50.882 + 26.8 + 23.212) ÷ 1000 = 0.717</t>
         </is>
       </c>
-      <c r="F322" s="10" t="n"/>
+      <c r="F322" s="12" t="n">
+        <v>0.717</v>
+      </c>
     </row>
     <row r="323" ht="18" customHeight="1">
       <c r="A323" s="3" t="n">
@@ -7104,7 +7172,7 @@
           <t>8.62 = 8.62</t>
         </is>
       </c>
-      <c r="F323" s="9" t="n">
+      <c r="F323" s="10" t="n">
         <v>0.134</v>
       </c>
     </row>
@@ -7126,7 +7194,7 @@
           <t>12.13 = 12.13</t>
         </is>
       </c>
-      <c r="F324" s="10" t="n"/>
+      <c r="F324" s="11" t="n"/>
     </row>
     <row r="325" ht="18" customHeight="1">
       <c r="A325" s="3" t="n"/>
@@ -7146,7 +7214,7 @@
           <t>6.322 + 7.755 = 14.077</t>
         </is>
       </c>
-      <c r="F325" s="10" t="n"/>
+      <c r="F325" s="11" t="n"/>
     </row>
     <row r="326" ht="18" customHeight="1">
       <c r="A326" s="3" t="n"/>
@@ -7166,7 +7234,7 @@
           <t>9.588 + 9.104 = 18.692</t>
         </is>
       </c>
-      <c r="F326" s="10" t="n"/>
+      <c r="F326" s="11" t="n"/>
     </row>
     <row r="327" ht="18" customHeight="1">
       <c r="A327" s="3" t="n"/>
@@ -7186,7 +7254,7 @@
           <t>8.62 = 8.62</t>
         </is>
       </c>
-      <c r="F327" s="10" t="n"/>
+      <c r="F327" s="11" t="n"/>
     </row>
     <row r="328" ht="18" customHeight="1">
       <c r="A328" s="3" t="n"/>
@@ -7206,7 +7274,7 @@
           <t>12.13 = 12.13</t>
         </is>
       </c>
-      <c r="F328" s="10" t="n"/>
+      <c r="F328" s="11" t="n"/>
     </row>
     <row r="329" ht="18" customHeight="1">
       <c r="A329" s="3" t="n"/>
@@ -7226,7 +7294,7 @@
           <t>6.322 + 7.755 = 14.077</t>
         </is>
       </c>
-      <c r="F329" s="10" t="n"/>
+      <c r="F329" s="11" t="n"/>
     </row>
     <row r="330" ht="18" customHeight="1">
       <c r="A330" s="3" t="n"/>
@@ -7246,7 +7314,7 @@
           <t>9.104 + 9.588 = 18.692</t>
         </is>
       </c>
-      <c r="F330" s="10" t="n"/>
+      <c r="F330" s="11" t="n"/>
     </row>
     <row r="331" ht="18" customHeight="1">
       <c r="A331" s="3" t="n"/>
@@ -7266,7 +7334,7 @@
           <t>9.588 = 9.588</t>
         </is>
       </c>
-      <c r="F331" s="10" t="n"/>
+      <c r="F331" s="11" t="n"/>
     </row>
     <row r="332" ht="18" customHeight="1">
       <c r="A332" s="3" t="n"/>
@@ -7286,7 +7354,7 @@
           <t>8.757 + 8.241 = 16.998</t>
         </is>
       </c>
-      <c r="F332" s="10" t="n"/>
+      <c r="F332" s="11" t="n"/>
     </row>
     <row r="333" ht="18" customHeight="1">
       <c r="A333" s="3" t="n"/>
@@ -7302,7 +7370,9 @@
           <t>(8.62 + 12.13 + 14.077 + 18.692 + 8.62 + 12.13 + 14.077 + 18.692 + 9.588 + 16.998) ÷ 1000 = 0.134</t>
         </is>
       </c>
-      <c r="F333" s="10" t="n"/>
+      <c r="F333" s="12" t="n">
+        <v>0.134</v>
+      </c>
     </row>
     <row r="334" ht="18" customHeight="1">
       <c r="A334" s="3" t="n">
@@ -7328,7 +7398,7 @@
           <t>90.342 = 90.342</t>
         </is>
       </c>
-      <c r="F334" s="9" t="n">
+      <c r="F334" s="10" t="n">
         <v>2.347</v>
       </c>
     </row>
@@ -7350,7 +7420,7 @@
           <t>38.658 = 38.658</t>
         </is>
       </c>
-      <c r="F335" s="10" t="n"/>
+      <c r="F335" s="11" t="n"/>
     </row>
     <row r="336" ht="18" customHeight="1">
       <c r="A336" s="3" t="n"/>
@@ -7370,7 +7440,7 @@
           <t>152.658 = 152.658</t>
         </is>
       </c>
-      <c r="F336" s="10" t="n"/>
+      <c r="F336" s="11" t="n"/>
     </row>
     <row r="337" ht="18" customHeight="1">
       <c r="A337" s="3" t="n"/>
@@ -7390,7 +7460,7 @@
           <t>12.728 + 16.395 = 29.123</t>
         </is>
       </c>
-      <c r="F337" s="10" t="n"/>
+      <c r="F337" s="11" t="n"/>
     </row>
     <row r="338" ht="18" customHeight="1">
       <c r="A338" s="3" t="n"/>
@@ -7410,7 +7480,7 @@
           <t>24.222 + 24.321 + 8.428 = 56.971</t>
         </is>
       </c>
-      <c r="F338" s="10" t="n"/>
+      <c r="F338" s="11" t="n"/>
     </row>
     <row r="339" ht="18" customHeight="1">
       <c r="A339" s="3" t="n"/>
@@ -7430,7 +7500,7 @@
           <t>76.377 = 76.377</t>
         </is>
       </c>
-      <c r="F339" s="10" t="n"/>
+      <c r="F339" s="11" t="n"/>
     </row>
     <row r="340" ht="18" customHeight="1">
       <c r="A340" s="3" t="n"/>
@@ -7450,7 +7520,7 @@
           <t>152.754 = 152.754</t>
         </is>
       </c>
-      <c r="F340" s="10" t="n"/>
+      <c r="F340" s="11" t="n"/>
     </row>
     <row r="341" ht="18" customHeight="1">
       <c r="A341" s="3" t="n"/>
@@ -7470,7 +7540,7 @@
           <t>76.377 + 74.106 = 150.483</t>
         </is>
       </c>
-      <c r="F341" s="10" t="n"/>
+      <c r="F341" s="11" t="n"/>
     </row>
     <row r="342" ht="18" customHeight="1">
       <c r="A342" s="3" t="n"/>
@@ -7490,7 +7560,7 @@
           <t>7.534 = 7.534</t>
         </is>
       </c>
-      <c r="F342" s="10" t="n"/>
+      <c r="F342" s="11" t="n"/>
     </row>
     <row r="343" ht="18" customHeight="1">
       <c r="A343" s="3" t="n"/>
@@ -7510,7 +7580,7 @@
           <t>15.068 = 15.068</t>
         </is>
       </c>
-      <c r="F343" s="10" t="n"/>
+      <c r="F343" s="11" t="n"/>
     </row>
     <row r="344" ht="18" customHeight="1">
       <c r="A344" s="3" t="n"/>
@@ -7530,7 +7600,7 @@
           <t>7.534 = 7.534</t>
         </is>
       </c>
-      <c r="F344" s="10" t="n"/>
+      <c r="F344" s="11" t="n"/>
     </row>
     <row r="345" ht="18" customHeight="1">
       <c r="A345" s="3" t="n"/>
@@ -7550,7 +7620,7 @@
           <t>15.068 = 15.068</t>
         </is>
       </c>
-      <c r="F345" s="10" t="n"/>
+      <c r="F345" s="11" t="n"/>
     </row>
     <row r="346" ht="18" customHeight="1">
       <c r="A346" s="3" t="n"/>
@@ -7570,7 +7640,7 @@
           <t>7.534 = 7.534</t>
         </is>
       </c>
-      <c r="F346" s="10" t="n"/>
+      <c r="F346" s="11" t="n"/>
     </row>
     <row r="347" ht="18" customHeight="1">
       <c r="A347" s="3" t="n"/>
@@ -7590,7 +7660,7 @@
           <t>24.222 + 24.321 + 8.428 = 56.971</t>
         </is>
       </c>
-      <c r="F347" s="10" t="n"/>
+      <c r="F347" s="11" t="n"/>
     </row>
     <row r="348" ht="18" customHeight="1">
       <c r="A348" s="3" t="n"/>
@@ -7610,7 +7680,7 @@
           <t>24.201 + 18.276 + 19.125 + 6.194 = 67.796</t>
         </is>
       </c>
-      <c r="F348" s="10" t="n"/>
+      <c r="F348" s="11" t="n"/>
     </row>
     <row r="349" ht="18" customHeight="1">
       <c r="A349" s="3" t="n"/>
@@ -7630,7 +7700,7 @@
           <t>152.754 = 152.754</t>
         </is>
       </c>
-      <c r="F349" s="10" t="n"/>
+      <c r="F349" s="11" t="n"/>
     </row>
     <row r="350" ht="18" customHeight="1">
       <c r="A350" s="3" t="n"/>
@@ -7650,7 +7720,7 @@
           <t>76.377 + 74.106 = 150.483</t>
         </is>
       </c>
-      <c r="F350" s="10" t="n"/>
+      <c r="F350" s="11" t="n"/>
     </row>
     <row r="351" ht="18" customHeight="1">
       <c r="A351" s="3" t="n"/>
@@ -7670,7 +7740,7 @@
           <t>6.194 = 6.194</t>
         </is>
       </c>
-      <c r="F351" s="10" t="n"/>
+      <c r="F351" s="11" t="n"/>
     </row>
     <row r="352" ht="18" customHeight="1">
       <c r="A352" s="3" t="n"/>
@@ -7690,7 +7760,7 @@
           <t>7.534 = 7.534</t>
         </is>
       </c>
-      <c r="F352" s="10" t="n"/>
+      <c r="F352" s="11" t="n"/>
     </row>
     <row r="353" ht="18" customHeight="1">
       <c r="A353" s="3" t="n"/>
@@ -7710,7 +7780,7 @@
           <t>15.068 = 15.068</t>
         </is>
       </c>
-      <c r="F353" s="10" t="n"/>
+      <c r="F353" s="11" t="n"/>
     </row>
     <row r="354" ht="18" customHeight="1">
       <c r="A354" s="3" t="n"/>
@@ -7730,7 +7800,7 @@
           <t>7.534 = 7.534</t>
         </is>
       </c>
-      <c r="F354" s="10" t="n"/>
+      <c r="F354" s="11" t="n"/>
     </row>
     <row r="355" ht="18" customHeight="1">
       <c r="A355" s="3" t="n"/>
@@ -7750,7 +7820,7 @@
           <t>15.068 = 15.068</t>
         </is>
       </c>
-      <c r="F355" s="10" t="n"/>
+      <c r="F355" s="11" t="n"/>
     </row>
     <row r="356" ht="18" customHeight="1">
       <c r="A356" s="3" t="n"/>
@@ -7770,7 +7840,7 @@
           <t>7.534 = 7.534</t>
         </is>
       </c>
-      <c r="F356" s="10" t="n"/>
+      <c r="F356" s="11" t="n"/>
     </row>
     <row r="357" ht="18" customHeight="1">
       <c r="A357" s="3" t="n"/>
@@ -7790,7 +7860,7 @@
           <t>24.222 + 24.321 + 8.428 = 56.971</t>
         </is>
       </c>
-      <c r="F357" s="10" t="n"/>
+      <c r="F357" s="11" t="n"/>
     </row>
     <row r="358" ht="18" customHeight="1">
       <c r="A358" s="3" t="n"/>
@@ -7810,7 +7880,7 @@
           <t>24.201 + 18.276 + 19.125 + 6.194 = 67.796</t>
         </is>
       </c>
-      <c r="F358" s="10" t="n"/>
+      <c r="F358" s="11" t="n"/>
     </row>
     <row r="359" ht="18" customHeight="1">
       <c r="A359" s="3" t="n"/>
@@ -7830,7 +7900,7 @@
           <t>152.754 = 152.754</t>
         </is>
       </c>
-      <c r="F359" s="10" t="n"/>
+      <c r="F359" s="11" t="n"/>
     </row>
     <row r="360" ht="18" customHeight="1">
       <c r="A360" s="3" t="n"/>
@@ -7850,7 +7920,7 @@
           <t>76.377 + 74.106 = 150.483</t>
         </is>
       </c>
-      <c r="F360" s="10" t="n"/>
+      <c r="F360" s="11" t="n"/>
     </row>
     <row r="361" ht="18" customHeight="1">
       <c r="A361" s="3" t="n"/>
@@ -7870,7 +7940,7 @@
           <t>6.194 = 6.194</t>
         </is>
       </c>
-      <c r="F361" s="10" t="n"/>
+      <c r="F361" s="11" t="n"/>
     </row>
     <row r="362" ht="18" customHeight="1">
       <c r="A362" s="3" t="n"/>
@@ -7890,7 +7960,7 @@
           <t>7.534 + 7.534 = 15.068</t>
         </is>
       </c>
-      <c r="F362" s="10" t="n"/>
+      <c r="F362" s="11" t="n"/>
     </row>
     <row r="363" ht="18" customHeight="1">
       <c r="A363" s="3" t="n"/>
@@ -7910,7 +7980,7 @@
           <t>7.534 + 7.534 = 15.068</t>
         </is>
       </c>
-      <c r="F363" s="10" t="n"/>
+      <c r="F363" s="11" t="n"/>
     </row>
     <row r="364" ht="18" customHeight="1">
       <c r="A364" s="3" t="n"/>
@@ -7930,7 +8000,7 @@
           <t>15.068 = 15.068</t>
         </is>
       </c>
-      <c r="F364" s="10" t="n"/>
+      <c r="F364" s="11" t="n"/>
     </row>
     <row r="365" ht="18" customHeight="1">
       <c r="A365" s="3" t="n"/>
@@ -7950,7 +8020,7 @@
           <t>24.222 + 24.321 + 8.428 = 56.971</t>
         </is>
       </c>
-      <c r="F365" s="10" t="n"/>
+      <c r="F365" s="11" t="n"/>
     </row>
     <row r="366" ht="18" customHeight="1">
       <c r="A366" s="3" t="n"/>
@@ -7970,7 +8040,7 @@
           <t>76.377 = 76.377</t>
         </is>
       </c>
-      <c r="F366" s="10" t="n"/>
+      <c r="F366" s="11" t="n"/>
     </row>
     <row r="367" ht="18" customHeight="1">
       <c r="A367" s="3" t="n"/>
@@ -7990,7 +8060,7 @@
           <t>77.655 + 76.377 = 154.032</t>
         </is>
       </c>
-      <c r="F367" s="10" t="n"/>
+      <c r="F367" s="11" t="n"/>
     </row>
     <row r="368" ht="18" customHeight="1">
       <c r="A368" s="3" t="n"/>
@@ -8010,7 +8080,7 @@
           <t>50.918 + 49.404 = 100.322</t>
         </is>
       </c>
-      <c r="F368" s="10" t="n"/>
+      <c r="F368" s="11" t="n"/>
     </row>
     <row r="369" ht="18" customHeight="1">
       <c r="A369" s="3" t="n"/>
@@ -8030,7 +8100,7 @@
           <t>16.752 = 16.752</t>
         </is>
       </c>
-      <c r="F369" s="10" t="n"/>
+      <c r="F369" s="11" t="n"/>
     </row>
     <row r="370" ht="18" customHeight="1">
       <c r="A370" s="3" t="n"/>
@@ -8050,7 +8120,7 @@
           <t>60.261 + 57.99 = 118.251</t>
         </is>
       </c>
-      <c r="F370" s="10" t="n"/>
+      <c r="F370" s="11" t="n"/>
     </row>
     <row r="371" ht="18" customHeight="1">
       <c r="A371" s="3" t="n"/>
@@ -8070,7 +8140,7 @@
           <t>11.892 + 17.073 = 28.965</t>
         </is>
       </c>
-      <c r="F371" s="10" t="n"/>
+      <c r="F371" s="11" t="n"/>
     </row>
     <row r="372" ht="18" customHeight="1">
       <c r="A372" s="3" t="n"/>
@@ -8090,7 +8160,7 @@
           <t>11.892 + 17.073 = 28.965</t>
         </is>
       </c>
-      <c r="F372" s="10" t="n"/>
+      <c r="F372" s="11" t="n"/>
     </row>
     <row r="373" ht="46" customHeight="1">
       <c r="A373" s="3" t="n"/>
@@ -8106,7 +8176,9 @@
           <t>(90.342 + 38.658 + 152.658 + 29.123 + 56.971 + 76.377 + 152.754 + 150.483 + 7.534 + 15.068 + 7.534 + 15.068 + 7.534 + 56.971 + 67.796 + 152.754 + 150.483 + 6.194 + 7.534 + 15.068 + 7.534 + 15.068 + 7.534 + 56.971 + 67.796 + 152.754 + 150.483 + 6.194 + 15.068 + 15.068 + 15.068 + 56.971 + 76.377 + 154.032 + 100.322 + 16.752 + 118.251 + 28.965 + 28.965) ÷ 1000 = 2.347</t>
         </is>
       </c>
-      <c r="F373" s="10" t="n"/>
+      <c r="F373" s="12" t="n">
+        <v>2.347</v>
+      </c>
     </row>
     <row r="374" ht="18" customHeight="1">
       <c r="A374" s="3" t="n">
@@ -8132,7 +8204,7 @@
           <t>56.444 + 10.47 + 75.99 + 55.944 + 7.658 + 13.94 + 9.72 + 16.6 + 75.99 + 4.816 = 327.572</t>
         </is>
       </c>
-      <c r="F374" s="9" t="n">
+      <c r="F374" s="10" t="n">
         <v>2.172</v>
       </c>
     </row>
@@ -8154,7 +8226,7 @@
           <t>19.44 + 151.98 = 171.42</t>
         </is>
       </c>
-      <c r="F375" s="10" t="n"/>
+      <c r="F375" s="11" t="n"/>
     </row>
     <row r="376" ht="18" customHeight="1">
       <c r="A376" s="3" t="n"/>
@@ -8174,7 +8246,7 @@
           <t>41.262 = 41.262</t>
         </is>
       </c>
-      <c r="F376" s="10" t="n"/>
+      <c r="F376" s="11" t="n"/>
     </row>
     <row r="377" ht="18" customHeight="1">
       <c r="A377" s="3" t="n"/>
@@ -8194,7 +8266,7 @@
           <t>64.66 + 3.866 + 12.4 + 4.7 + 3.166 = 88.792</t>
         </is>
       </c>
-      <c r="F377" s="10" t="n"/>
+      <c r="F377" s="11" t="n"/>
     </row>
     <row r="378" ht="18" customHeight="1">
       <c r="A378" s="3" t="n"/>
@@ -8214,7 +8286,7 @@
           <t>55.944 + 7.658 + 13.94 + 16.6 + 4.816 + 39.612 = 138.57</t>
         </is>
       </c>
-      <c r="F378" s="10" t="n"/>
+      <c r="F378" s="11" t="n"/>
     </row>
     <row r="379" ht="18" customHeight="1">
       <c r="A379" s="3" t="n"/>
@@ -8234,7 +8306,7 @@
           <t>41.262 = 41.262</t>
         </is>
       </c>
-      <c r="F379" s="10" t="n"/>
+      <c r="F379" s="11" t="n"/>
     </row>
     <row r="380" ht="18" customHeight="1">
       <c r="A380" s="3" t="n"/>
@@ -8254,7 +8326,7 @@
           <t>41.262 = 41.262</t>
         </is>
       </c>
-      <c r="F380" s="10" t="n"/>
+      <c r="F380" s="11" t="n"/>
     </row>
     <row r="381" ht="18" customHeight="1">
       <c r="A381" s="3" t="n"/>
@@ -8274,7 +8346,7 @@
           <t>55.944 + 7.658 + 13.94 + 8.3 + 12.8 + 41.412 + 4.816 + 39.612 = 184.482</t>
         </is>
       </c>
-      <c r="F381" s="10" t="n"/>
+      <c r="F381" s="11" t="n"/>
     </row>
     <row r="382" ht="18" customHeight="1">
       <c r="A382" s="3" t="n"/>
@@ -8294,7 +8366,7 @@
           <t>21.492 + 20.292 = 41.784</t>
         </is>
       </c>
-      <c r="F382" s="10" t="n"/>
+      <c r="F382" s="11" t="n"/>
     </row>
     <row r="383" ht="18" customHeight="1">
       <c r="A383" s="3" t="n"/>
@@ -8314,7 +8386,7 @@
           <t>55.944 + 7.658 + 13.94 + 16.6 + 4.816 + 39.612 = 138.57</t>
         </is>
       </c>
-      <c r="F383" s="10" t="n"/>
+      <c r="F383" s="11" t="n"/>
     </row>
     <row r="384" ht="18" customHeight="1">
       <c r="A384" s="3" t="n"/>
@@ -8334,7 +8406,7 @@
           <t>41.262 = 41.262</t>
         </is>
       </c>
-      <c r="F384" s="10" t="n"/>
+      <c r="F384" s="11" t="n"/>
     </row>
     <row r="385" ht="18" customHeight="1">
       <c r="A385" s="3" t="n"/>
@@ -8354,7 +8426,7 @@
           <t>41.262 = 41.262</t>
         </is>
       </c>
-      <c r="F385" s="10" t="n"/>
+      <c r="F385" s="11" t="n"/>
     </row>
     <row r="386" ht="18" customHeight="1">
       <c r="A386" s="3" t="n"/>
@@ -8374,7 +8446,7 @@
           <t>55.944 + 7.658 + 13.94 + 8.3 + 12.8 + 41.412 + 4.816 + 39.612 = 184.482</t>
         </is>
       </c>
-      <c r="F386" s="10" t="n"/>
+      <c r="F386" s="11" t="n"/>
     </row>
     <row r="387" ht="18" customHeight="1">
       <c r="A387" s="3" t="n"/>
@@ -8394,7 +8466,7 @@
           <t>20.292 + 21.492 = 41.784</t>
         </is>
       </c>
-      <c r="F387" s="10" t="n"/>
+      <c r="F387" s="11" t="n"/>
     </row>
     <row r="388" ht="18" customHeight="1">
       <c r="A388" s="3" t="n"/>
@@ -8414,7 +8486,7 @@
           <t>56.964 + 15.136 + 16.6 + 75.99 + 56.964 + 15.136 + 9.72 + 16.6 + 75.99 = 339.1</t>
         </is>
       </c>
-      <c r="F388" s="10" t="n"/>
+      <c r="F388" s="11" t="n"/>
     </row>
     <row r="389" ht="18" customHeight="1">
       <c r="A389" s="3" t="n"/>
@@ -8434,7 +8506,7 @@
           <t>75.99 + 9.72 + 75.99 = 161.7</t>
         </is>
       </c>
-      <c r="F389" s="10" t="n"/>
+      <c r="F389" s="11" t="n"/>
     </row>
     <row r="390" ht="18" customHeight="1">
       <c r="A390" s="3" t="n"/>
@@ -8454,7 +8526,7 @@
           <t>75.99 = 75.99</t>
         </is>
       </c>
-      <c r="F390" s="10" t="n"/>
+      <c r="F390" s="11" t="n"/>
     </row>
     <row r="391" ht="18" customHeight="1">
       <c r="A391" s="3" t="n"/>
@@ -8474,7 +8546,7 @@
           <t>65.5 + 6.2 = 71.7</t>
         </is>
       </c>
-      <c r="F391" s="10" t="n"/>
+      <c r="F391" s="11" t="n"/>
     </row>
     <row r="392" ht="32" customHeight="1">
       <c r="A392" s="3" t="n"/>
@@ -8490,7 +8562,9 @@
           <t>(327.572 + 171.42 + 41.262 + 88.792 + 138.57 + 41.262 + 41.262 + 184.482 + 41.784 + 138.57 + 41.262 + 41.262 + 184.482 + 41.784 + 339.1 + 161.7 + 75.99 + 71.7) ÷ 1000 = 2.172</t>
         </is>
       </c>
-      <c r="F392" s="10" t="n"/>
+      <c r="F392" s="12" t="n">
+        <v>2.172</v>
+      </c>
     </row>
     <row r="393" ht="18" customHeight="1">
       <c r="A393" s="3" t="n">
@@ -8516,7 +8590,7 @@
           <t>98.286 + 188.316 = 286.602</t>
         </is>
       </c>
-      <c r="F393" s="9" t="n">
+      <c r="F393" s="10" t="n">
         <v>2.778</v>
       </c>
     </row>
@@ -8538,7 +8612,7 @@
           <t>188.316 = 188.316</t>
         </is>
       </c>
-      <c r="F394" s="10" t="n"/>
+      <c r="F394" s="11" t="n"/>
     </row>
     <row r="395" ht="18" customHeight="1">
       <c r="A395" s="3" t="n"/>
@@ -8558,7 +8632,7 @@
           <t>54.93 + 54.702 = 109.632</t>
         </is>
       </c>
-      <c r="F395" s="10" t="n"/>
+      <c r="F395" s="11" t="n"/>
     </row>
     <row r="396" ht="18" customHeight="1">
       <c r="A396" s="3" t="n"/>
@@ -8578,7 +8652,7 @@
           <t>5.692 + 109.776 + 20.668 = 136.136</t>
         </is>
       </c>
-      <c r="F396" s="10" t="n"/>
+      <c r="F396" s="11" t="n"/>
     </row>
     <row r="397" ht="18" customHeight="1">
       <c r="A397" s="3" t="n"/>
@@ -8598,7 +8672,7 @@
           <t>69.318 + 18.476 + 10.581 + 16.362 + 5.99 + 49.41 = 170.137</t>
         </is>
       </c>
-      <c r="F397" s="10" t="n"/>
+      <c r="F397" s="11" t="n"/>
     </row>
     <row r="398" ht="18" customHeight="1">
       <c r="A398" s="3" t="n"/>
@@ -8618,7 +8692,7 @@
           <t>80.112 + 22.31 + 6.523 = 108.945</t>
         </is>
       </c>
-      <c r="F398" s="10" t="n"/>
+      <c r="F398" s="11" t="n"/>
     </row>
     <row r="399" ht="18" customHeight="1">
       <c r="A399" s="3" t="n"/>
@@ -8638,7 +8712,7 @@
           <t>2.846 + 54.888 + 10.334 + 15.996 + 5.99 + 49.41 = 139.464</t>
         </is>
       </c>
-      <c r="F399" s="10" t="n"/>
+      <c r="F399" s="11" t="n"/>
     </row>
     <row r="400" ht="18" customHeight="1">
       <c r="A400" s="3" t="n"/>
@@ -8658,7 +8732,7 @@
           <t>2.846 + 54.888 + 10.334 + 15.996 + 5.99 + 49.41 = 139.464</t>
         </is>
       </c>
-      <c r="F400" s="10" t="n"/>
+      <c r="F400" s="11" t="n"/>
     </row>
     <row r="401" ht="18" customHeight="1">
       <c r="A401" s="3" t="n"/>
@@ -8678,7 +8752,7 @@
           <t>69.318 + 18.15 + 10.581 + 16.362 + 5.99 + 49.41 = 169.811</t>
         </is>
       </c>
-      <c r="F401" s="10" t="n"/>
+      <c r="F401" s="11" t="n"/>
     </row>
     <row r="402" ht="18" customHeight="1">
       <c r="A402" s="3" t="n"/>
@@ -8698,7 +8772,7 @@
           <t>80.112 + 22.31 + 6.523 = 108.945</t>
         </is>
       </c>
-      <c r="F402" s="10" t="n"/>
+      <c r="F402" s="11" t="n"/>
     </row>
     <row r="403" ht="18" customHeight="1">
       <c r="A403" s="3" t="n"/>
@@ -8718,7 +8792,7 @@
           <t>80.112 + 4.836 + 15.314 + 39.036 = 139.298</t>
         </is>
       </c>
-      <c r="F403" s="10" t="n"/>
+      <c r="F403" s="11" t="n"/>
     </row>
     <row r="404" ht="18" customHeight="1">
       <c r="A404" s="3" t="n"/>
@@ -8738,7 +8812,7 @@
           <t>26.055 = 26.055</t>
         </is>
       </c>
-      <c r="F404" s="10" t="n"/>
+      <c r="F404" s="11" t="n"/>
     </row>
     <row r="405" ht="18" customHeight="1">
       <c r="A405" s="3" t="n"/>
@@ -8758,7 +8832,7 @@
           <t>2.846 + 54.888 + 10.334 + 15.996 + 5.99 + 49.41 = 139.464</t>
         </is>
       </c>
-      <c r="F405" s="10" t="n"/>
+      <c r="F405" s="11" t="n"/>
     </row>
     <row r="406" ht="18" customHeight="1">
       <c r="A406" s="3" t="n"/>
@@ -8778,7 +8852,7 @@
           <t>2.846 + 54.888 + 10.334 + 15.996 + 5.99 + 49.41 = 139.464</t>
         </is>
       </c>
-      <c r="F406" s="10" t="n"/>
+      <c r="F406" s="11" t="n"/>
     </row>
     <row r="407" ht="18" customHeight="1">
       <c r="A407" s="3" t="n"/>
@@ -8798,7 +8872,7 @@
           <t>69.318 + 18.15 + 10.581 + 16.362 + 5.99 + 49.41 = 169.811</t>
         </is>
       </c>
-      <c r="F407" s="10" t="n"/>
+      <c r="F407" s="11" t="n"/>
     </row>
     <row r="408" ht="18" customHeight="1">
       <c r="A408" s="3" t="n"/>
@@ -8818,7 +8892,7 @@
           <t>80.112 + 22.31 + 6.523 = 108.945</t>
         </is>
       </c>
-      <c r="F408" s="10" t="n"/>
+      <c r="F408" s="11" t="n"/>
     </row>
     <row r="409" ht="18" customHeight="1">
       <c r="A409" s="3" t="n"/>
@@ -8838,7 +8912,7 @@
           <t>80.112 + 4.836 + 15.314 + 39.036 = 139.298</t>
         </is>
       </c>
-      <c r="F409" s="10" t="n"/>
+      <c r="F409" s="11" t="n"/>
     </row>
     <row r="410" ht="18" customHeight="1">
       <c r="A410" s="3" t="n"/>
@@ -8858,7 +8932,7 @@
           <t>26.055 = 26.055</t>
         </is>
       </c>
-      <c r="F410" s="10" t="n"/>
+      <c r="F410" s="11" t="n"/>
     </row>
     <row r="411" ht="18" customHeight="1">
       <c r="A411" s="3" t="n"/>
@@ -8878,7 +8952,7 @@
           <t>56 + 10.334 + 56 + 10.334 = 132.668</t>
         </is>
       </c>
-      <c r="F411" s="10" t="n"/>
+      <c r="F411" s="11" t="n"/>
     </row>
     <row r="412" ht="18" customHeight="1">
       <c r="A412" s="3" t="n"/>
@@ -8898,7 +8972,7 @@
           <t>70.43 + 9.075 + 10.581 + 16.362 = 106.448</t>
         </is>
       </c>
-      <c r="F412" s="10" t="n"/>
+      <c r="F412" s="11" t="n"/>
     </row>
     <row r="413" ht="18" customHeight="1">
       <c r="A413" s="3" t="n"/>
@@ -8918,7 +8992,7 @@
           <t>82.088 + 11.155 = 93.243</t>
         </is>
       </c>
-      <c r="F413" s="10" t="n"/>
+      <c r="F413" s="11" t="n"/>
     </row>
     <row r="414" ht="32" customHeight="1">
       <c r="A414" s="3" t="n"/>
@@ -8934,7 +9008,9 @@
           <t>(286.602 + 188.316 + 109.632 + 136.136 + 170.137 + 108.945 + 139.464 + 139.464 + 169.811 + 108.945 + 139.298 + 26.055 + 139.464 + 139.464 + 169.811 + 108.945 + 139.298 + 26.055 + 132.668 + 106.448 + 93.243) ÷ 1000 = 2.778</t>
         </is>
       </c>
-      <c r="F414" s="10" t="n"/>
+      <c r="F414" s="12" t="n">
+        <v>2.778</v>
+      </c>
     </row>
     <row r="415" ht="18" customHeight="1">
       <c r="A415" s="3" t="n">
@@ -8960,7 +9036,7 @@
           <t>63.339 = 63.339</t>
         </is>
       </c>
-      <c r="F415" s="9" t="n">
+      <c r="F415" s="10" t="n">
         <v>0.319</v>
       </c>
     </row>
@@ -8982,7 +9058,7 @@
           <t>63.117 = 63.117</t>
         </is>
       </c>
-      <c r="F416" s="10" t="n"/>
+      <c r="F416" s="11" t="n"/>
     </row>
     <row r="417" ht="18" customHeight="1">
       <c r="A417" s="3" t="n"/>
@@ -9002,7 +9078,7 @@
           <t>63.339 = 63.339</t>
         </is>
       </c>
-      <c r="F417" s="10" t="n"/>
+      <c r="F417" s="11" t="n"/>
     </row>
     <row r="418" ht="18" customHeight="1">
       <c r="A418" s="3" t="n"/>
@@ -9022,7 +9098,7 @@
           <t>63.117 = 63.117</t>
         </is>
       </c>
-      <c r="F418" s="10" t="n"/>
+      <c r="F418" s="11" t="n"/>
     </row>
     <row r="419" ht="18" customHeight="1">
       <c r="A419" s="3" t="n"/>
@@ -9042,7 +9118,7 @@
           <t>66.54 = 66.54</t>
         </is>
       </c>
-      <c r="F419" s="10" t="n"/>
+      <c r="F419" s="11" t="n"/>
     </row>
     <row r="420" ht="18" customHeight="1">
       <c r="A420" s="3" t="n"/>
@@ -9058,7 +9134,9 @@
           <t>(63.339 + 63.117 + 63.339 + 63.117 + 66.54) ÷ 1000 = 0.319</t>
         </is>
       </c>
-      <c r="F420" s="10" t="n"/>
+      <c r="F420" s="12" t="n">
+        <v>0.319</v>
+      </c>
     </row>
     <row r="421" ht="18" customHeight="1">
       <c r="A421" s="3" t="n">
@@ -9084,7 +9162,7 @@
           <t>3.08 = 3.08</t>
         </is>
       </c>
-      <c r="F421" s="9" t="n">
+      <c r="F421" s="10" t="n">
         <v>1.029</v>
       </c>
     </row>
@@ -9106,7 +9184,7 @@
           <t>59.908 + 81.864 + 6.16 = 147.932</t>
         </is>
       </c>
-      <c r="F422" s="10" t="n"/>
+      <c r="F422" s="11" t="n"/>
     </row>
     <row r="423" ht="18" customHeight="1">
       <c r="A423" s="3" t="n"/>
@@ -9126,7 +9204,7 @@
           <t>3.08 = 3.08</t>
         </is>
       </c>
-      <c r="F423" s="10" t="n"/>
+      <c r="F423" s="11" t="n"/>
     </row>
     <row r="424" ht="18" customHeight="1">
       <c r="A424" s="3" t="n"/>
@@ -9146,7 +9224,7 @@
           <t>86.868 = 86.868</t>
         </is>
       </c>
-      <c r="F424" s="10" t="n"/>
+      <c r="F424" s="11" t="n"/>
     </row>
     <row r="425" ht="18" customHeight="1">
       <c r="A425" s="3" t="n"/>
@@ -9166,7 +9244,7 @@
           <t>3.08 = 3.08</t>
         </is>
       </c>
-      <c r="F425" s="10" t="n"/>
+      <c r="F425" s="11" t="n"/>
     </row>
     <row r="426" ht="18" customHeight="1">
       <c r="A426" s="3" t="n"/>
@@ -9186,7 +9264,7 @@
           <t>44.931 + 27.288 + 6.16 = 78.379</t>
         </is>
       </c>
-      <c r="F426" s="10" t="n"/>
+      <c r="F426" s="11" t="n"/>
     </row>
     <row r="427" ht="18" customHeight="1">
       <c r="A427" s="3" t="n"/>
@@ -9206,7 +9284,7 @@
           <t>44.931 + 27.288 + 6.16 = 78.379</t>
         </is>
       </c>
-      <c r="F427" s="10" t="n"/>
+      <c r="F427" s="11" t="n"/>
     </row>
     <row r="428" ht="18" customHeight="1">
       <c r="A428" s="3" t="n"/>
@@ -9226,7 +9304,7 @@
           <t>3.08 = 3.08</t>
         </is>
       </c>
-      <c r="F428" s="10" t="n"/>
+      <c r="F428" s="11" t="n"/>
     </row>
     <row r="429" ht="18" customHeight="1">
       <c r="A429" s="3" t="n"/>
@@ -9246,7 +9324,7 @@
           <t>6.16 = 6.16</t>
         </is>
       </c>
-      <c r="F429" s="10" t="n"/>
+      <c r="F429" s="11" t="n"/>
     </row>
     <row r="430" ht="18" customHeight="1">
       <c r="A430" s="3" t="n"/>
@@ -9266,7 +9344,7 @@
           <t>86.868 = 86.868</t>
         </is>
       </c>
-      <c r="F430" s="10" t="n"/>
+      <c r="F430" s="11" t="n"/>
     </row>
     <row r="431" ht="18" customHeight="1">
       <c r="A431" s="3" t="n"/>
@@ -9286,7 +9364,7 @@
           <t>77.676 = 77.676</t>
         </is>
       </c>
-      <c r="F431" s="10" t="n"/>
+      <c r="F431" s="11" t="n"/>
     </row>
     <row r="432" ht="18" customHeight="1">
       <c r="A432" s="3" t="n"/>
@@ -9306,7 +9384,7 @@
           <t>3.08 = 3.08</t>
         </is>
       </c>
-      <c r="F432" s="10" t="n"/>
+      <c r="F432" s="11" t="n"/>
     </row>
     <row r="433" ht="18" customHeight="1">
       <c r="A433" s="3" t="n"/>
@@ -9326,7 +9404,7 @@
           <t>44.931 + 27.288 + 6.16 = 78.379</t>
         </is>
       </c>
-      <c r="F433" s="10" t="n"/>
+      <c r="F433" s="11" t="n"/>
     </row>
     <row r="434" ht="18" customHeight="1">
       <c r="A434" s="3" t="n"/>
@@ -9346,7 +9424,7 @@
           <t>44.931 + 27.288 + 6.16 = 78.379</t>
         </is>
       </c>
-      <c r="F434" s="10" t="n"/>
+      <c r="F434" s="11" t="n"/>
     </row>
     <row r="435" ht="18" customHeight="1">
       <c r="A435" s="3" t="n"/>
@@ -9366,7 +9444,7 @@
           <t>3.08 = 3.08</t>
         </is>
       </c>
-      <c r="F435" s="10" t="n"/>
+      <c r="F435" s="11" t="n"/>
     </row>
     <row r="436" ht="18" customHeight="1">
       <c r="A436" s="3" t="n"/>
@@ -9386,7 +9464,7 @@
           <t>6.16 = 6.16</t>
         </is>
       </c>
-      <c r="F436" s="10" t="n"/>
+      <c r="F436" s="11" t="n"/>
     </row>
     <row r="437" ht="18" customHeight="1">
       <c r="A437" s="3" t="n"/>
@@ -9406,7 +9484,7 @@
           <t>86.868 = 86.868</t>
         </is>
       </c>
-      <c r="F437" s="10" t="n"/>
+      <c r="F437" s="11" t="n"/>
     </row>
     <row r="438" ht="18" customHeight="1">
       <c r="A438" s="3" t="n"/>
@@ -9426,7 +9504,7 @@
           <t>77.676 = 77.676</t>
         </is>
       </c>
-      <c r="F438" s="10" t="n"/>
+      <c r="F438" s="11" t="n"/>
     </row>
     <row r="439" ht="18" customHeight="1">
       <c r="A439" s="3" t="n"/>
@@ -9446,7 +9524,7 @@
           <t>29.036 + 29.954 + 29.036 + 29.954 = 117.98</t>
         </is>
       </c>
-      <c r="F439" s="10" t="n"/>
+      <c r="F439" s="11" t="n"/>
     </row>
     <row r="440" ht="18" customHeight="1">
       <c r="A440" s="3" t="n"/>
@@ -9466,7 +9544,7 @@
           <t>3.08 = 3.08</t>
         </is>
       </c>
-      <c r="F440" s="10" t="n"/>
+      <c r="F440" s="11" t="n"/>
     </row>
     <row r="441" ht="32" customHeight="1">
       <c r="A441" s="3" t="n"/>
@@ -9482,7 +9560,9 @@
           <t>(3.08 + 147.932 + 3.08 + 86.868 + 3.08 + 78.379 + 78.379 + 3.08 + 6.16 + 86.868 + 77.676 + 3.08 + 78.379 + 78.379 + 3.08 + 6.16 + 86.868 + 77.676 + 117.98 + 3.08) ÷ 1000 = 1.029</t>
         </is>
       </c>
-      <c r="F441" s="10" t="n"/>
+      <c r="F441" s="12" t="n">
+        <v>1.029</v>
+      </c>
     </row>
     <row r="442" ht="18" customHeight="1">
       <c r="A442" s="3" t="n">
@@ -9508,7 +9588,7 @@
           <t>16.596 + 16.926 + 18.54 + 20.349 = 72.411</t>
         </is>
       </c>
-      <c r="F442" s="9" t="n">
+      <c r="F442" s="10" t="n">
         <v>2.37</v>
       </c>
     </row>
@@ -9530,7 +9610,7 @@
           <t>56.826 + 61.304 + 58.284 + 77.115 = 253.529</t>
         </is>
       </c>
-      <c r="F443" s="10" t="n"/>
+      <c r="F443" s="11" t="n"/>
     </row>
     <row r="444" ht="18" customHeight="1">
       <c r="A444" s="3" t="n"/>
@@ -9550,7 +9630,7 @@
           <t>35.94 + 39.2 + 48.248 + 47 + 54.242 + 50.26 = 274.89</t>
         </is>
       </c>
-      <c r="F444" s="10" t="n"/>
+      <c r="F444" s="11" t="n"/>
     </row>
     <row r="445" ht="18" customHeight="1">
       <c r="A445" s="3" t="n"/>
@@ -9570,7 +9650,7 @@
           <t>15.213 + 15.771 + 16.995 + 19.173 + 30.549 + 1.976 + 33.075 + 33.32 + 2.3 + 37.449 + 56.826 + 61.304 + 58.284 + 77.115 + 9.681 + 11.655 + 10.815 + 15.078 = 506.579</t>
         </is>
       </c>
-      <c r="F445" s="10" t="n"/>
+      <c r="F445" s="11" t="n"/>
     </row>
     <row r="446" ht="18" customHeight="1">
       <c r="A446" s="3" t="n"/>
@@ -9590,7 +9670,7 @@
           <t>50.26 + 54.242 + 47 + 48.248 + 39.2 + 35.94 = 274.89</t>
         </is>
       </c>
-      <c r="F446" s="10" t="n"/>
+      <c r="F446" s="11" t="n"/>
     </row>
     <row r="447" ht="18" customHeight="1">
       <c r="A447" s="3" t="n"/>
@@ -9610,7 +9690,7 @@
           <t>77.115 + 58.284 + 61.304 + 56.826 + 37.449 + 33.32 + 2.3 + 33.075 + 30.549 + 1.976 + 19.173 + 16.995 + 15.771 + 15.213 + 9.681 + 11.655 + 10.815 + 15.078 = 506.579</t>
         </is>
       </c>
-      <c r="F447" s="10" t="n"/>
+      <c r="F447" s="11" t="n"/>
     </row>
     <row r="448" ht="18" customHeight="1">
       <c r="A448" s="3" t="n"/>
@@ -9630,7 +9710,7 @@
           <t>14.913 + 22.496 + 15.399 + 34.884 + 56.826 + 61.304 + 58.284 + 77.115 = 341.221</t>
         </is>
       </c>
-      <c r="F448" s="10" t="n"/>
+      <c r="F448" s="11" t="n"/>
     </row>
     <row r="449" ht="18" customHeight="1">
       <c r="A449" s="3" t="n"/>
@@ -9650,7 +9730,7 @@
           <t>15.213 + 15.771 + 16.995 + 19.173 + 9.681 + 11.655 + 10.815 + 15.078 = 114.381</t>
         </is>
       </c>
-      <c r="F449" s="10" t="n"/>
+      <c r="F449" s="11" t="n"/>
     </row>
     <row r="450" ht="18" customHeight="1">
       <c r="A450" s="3" t="n"/>
@@ -9670,7 +9750,7 @@
           <t>4.125 + 6.854 + 4.137 + 10.557 = 25.673</t>
         </is>
       </c>
-      <c r="F450" s="10" t="n"/>
+      <c r="F450" s="11" t="n"/>
     </row>
     <row r="451" ht="18" customHeight="1">
       <c r="A451" s="3" t="n"/>
@@ -9686,7 +9766,9 @@
           <t>(72.411 + 253.529 + 274.89 + 506.579 + 274.89 + 506.579 + 341.221 + 114.381 + 25.673) ÷ 1000 = 2.370</t>
         </is>
       </c>
-      <c r="F451" s="10" t="n"/>
+      <c r="F451" s="12" t="n">
+        <v>2.37</v>
+      </c>
     </row>
     <row r="452" ht="18" customHeight="1">
       <c r="A452" s="3" t="n">
@@ -9712,7 +9794,7 @@
           <t>60.72 + 122.16 + 174.2 + 81.54 + 55.272 + 54.135 + 77.84 = 625.867</t>
         </is>
       </c>
-      <c r="F452" s="9" t="n">
+      <c r="F452" s="10" t="n">
         <v>2.808</v>
       </c>
     </row>
@@ -9734,7 +9816,7 @@
           <t>40.824 + 46.746 + 17.766 + 85.512 + 42.944 + 27.084 + 121.94 + 62.307 + 56.925 + 81.54 = 583.588</t>
         </is>
       </c>
-      <c r="F453" s="10" t="n"/>
+      <c r="F453" s="11" t="n"/>
     </row>
     <row r="454" ht="18" customHeight="1">
       <c r="A454" s="3" t="n"/>
@@ -9754,7 +9836,7 @@
           <t>46.746 + 40.824 + 56.925 + 81.54 + 42.944 + 17.766 + 85.512 + 62.307 + 27.084 + 121.94 = 583.588</t>
         </is>
       </c>
-      <c r="F454" s="10" t="n"/>
+      <c r="F454" s="11" t="n"/>
     </row>
     <row r="455" ht="18" customHeight="1">
       <c r="A455" s="3" t="n"/>
@@ -9774,7 +9856,7 @@
           <t>48.12 + 49.35 + 69.82 + 56.925 + 81.54 + 42.944 + 17.766 + 85.512 + 62.307 + 27.084 + 121.94 = 663.308</t>
         </is>
       </c>
-      <c r="F455" s="10" t="n"/>
+      <c r="F455" s="11" t="n"/>
     </row>
     <row r="456" ht="18" customHeight="1">
       <c r="A456" s="3" t="n"/>
@@ -9794,7 +9876,7 @@
           <t>50.496 + 21.01 + 69.152 + 109.48 + 101.244 = 351.382</t>
         </is>
       </c>
-      <c r="F456" s="10" t="n"/>
+      <c r="F456" s="11" t="n"/>
     </row>
     <row r="457" ht="18" customHeight="1">
       <c r="A457" s="3" t="n"/>
@@ -9810,7 +9892,9 @@
           <t>(625.867 + 583.588 + 583.588 + 663.308 + 351.382) ÷ 1000 = 2.808</t>
         </is>
       </c>
-      <c r="F457" s="10" t="n"/>
+      <c r="F457" s="12" t="n">
+        <v>2.808</v>
+      </c>
     </row>
     <row r="458" ht="18" customHeight="1">
       <c r="A458" s="3" t="n">
@@ -9836,7 +9920,7 @@
           <t>252.896 + 124.68 + 444.144 + 131.064 + 260.799 + 353.84 = 1567.423</t>
         </is>
       </c>
-      <c r="F458" s="9" t="n">
+      <c r="F458" s="10" t="n">
         <v>6.289</v>
       </c>
     </row>
@@ -9858,7 +9942,7 @@
           <t>252.896 + 124.68 + 336.148 + 131.064 + 130.416 + 176.16 + 165.592 + 158.144 = 1475.1</t>
         </is>
       </c>
-      <c r="F459" s="10" t="n"/>
+      <c r="F459" s="11" t="n"/>
     </row>
     <row r="460" ht="18" customHeight="1">
       <c r="A460" s="3" t="n"/>
@@ -9878,7 +9962,7 @@
           <t>130.416 + 131.064 + 165.592 + 176.16 + 124.68 + 252.896 + 336.148 + 158.144 = 1475.1</t>
         </is>
       </c>
-      <c r="F460" s="10" t="n"/>
+      <c r="F460" s="11" t="n"/>
     </row>
     <row r="461" ht="18" customHeight="1">
       <c r="A461" s="3" t="n"/>
@@ -9898,7 +9982,7 @@
           <t>221.284 + 110.832 + 385.704 + 260.799 + 353.84 + 165.592 + 131.064 + 141.96 = 1771.075</t>
         </is>
       </c>
-      <c r="F461" s="10" t="n"/>
+      <c r="F461" s="11" t="n"/>
     </row>
     <row r="462" ht="18" customHeight="1">
       <c r="A462" s="3" t="n"/>
@@ -9914,7 +9998,9 @@
           <t>(1567.423 + 1475.1 + 1475.1 + 1771.075) ÷ 1000 = 6.289</t>
         </is>
       </c>
-      <c r="F462" s="10" t="n"/>
+      <c r="F462" s="12" t="n">
+        <v>6.289</v>
+      </c>
     </row>
     <row r="463" ht="18" customHeight="1">
       <c r="A463" s="3" t="n">
@@ -9940,7 +10026,7 @@
           <t>10.914 + 7.922 = 18.836</t>
         </is>
       </c>
-      <c r="F463" s="9" t="n">
+      <c r="F463" s="10" t="n">
         <v>0.089</v>
       </c>
     </row>
@@ -9962,7 +10048,7 @@
           <t>15.408 + 7.922 = 23.33</t>
         </is>
       </c>
-      <c r="F464" s="10" t="n"/>
+      <c r="F464" s="11" t="n"/>
     </row>
     <row r="465" ht="18" customHeight="1">
       <c r="A465" s="3" t="n"/>
@@ -9982,7 +10068,7 @@
           <t>15.408 + 7.922 = 23.33</t>
         </is>
       </c>
-      <c r="F465" s="10" t="n"/>
+      <c r="F465" s="11" t="n"/>
     </row>
     <row r="466" ht="18" customHeight="1">
       <c r="A466" s="3" t="n"/>
@@ -10002,7 +10088,7 @@
           <t>15.408 + 7.922 = 23.33</t>
         </is>
       </c>
-      <c r="F466" s="10" t="n"/>
+      <c r="F466" s="11" t="n"/>
     </row>
     <row r="467" ht="18" customHeight="1">
       <c r="A467" s="3" t="n"/>
@@ -10018,7 +10104,9 @@
           <t>(18.836 + 23.33 + 23.33 + 23.33) ÷ 1000 = 0.089</t>
         </is>
       </c>
-      <c r="F467" s="10" t="n"/>
+      <c r="F467" s="12" t="n">
+        <v>0.089</v>
+      </c>
     </row>
     <row r="468" ht="18" customHeight="1">
       <c r="A468" s="3" t="n">
@@ -10044,7 +10132,7 @@
           <t>9.707 + 15.33 + 12.53 + 13.734 + 12.64 = 63.941</t>
         </is>
       </c>
-      <c r="F468" s="9" t="n">
+      <c r="F468" s="10" t="n">
         <v>0.209</v>
       </c>
     </row>
@@ -10066,7 +10154,7 @@
           <t>13.587 + 11.277 + 11.991 + 11.376 = 48.231</t>
         </is>
       </c>
-      <c r="F469" s="10" t="n"/>
+      <c r="F469" s="11" t="n"/>
     </row>
     <row r="470" ht="18" customHeight="1">
       <c r="A470" s="3" t="n"/>
@@ -10086,7 +10174,7 @@
           <t>13.587 + 11.277 + 11.991 + 11.376 = 48.231</t>
         </is>
       </c>
-      <c r="F470" s="10" t="n"/>
+      <c r="F470" s="11" t="n"/>
     </row>
     <row r="471" ht="18" customHeight="1">
       <c r="A471" s="3" t="n"/>
@@ -10106,7 +10194,7 @@
           <t>13.587 + 11.277 + 11.991 + 11.376 = 48.231</t>
         </is>
       </c>
-      <c r="F471" s="10" t="n"/>
+      <c r="F471" s="11" t="n"/>
     </row>
     <row r="472" ht="18" customHeight="1">
       <c r="A472" s="3" t="n"/>
@@ -10122,7 +10210,9 @@
           <t>(63.941 + 48.231 + 48.231 + 48.231) ÷ 1000 = 0.209</t>
         </is>
       </c>
-      <c r="F472" s="10" t="n"/>
+      <c r="F472" s="12" t="n">
+        <v>0.209</v>
+      </c>
     </row>
     <row r="473" ht="18" customHeight="1">
       <c r="A473" s="3" t="n">
@@ -10148,7 +10238,7 @@
           <t>13.99 + 13.74 + 42.69 + 8.96 + 8.96 + 22.73 = 111.07</t>
         </is>
       </c>
-      <c r="F473" s="9" t="n">
+      <c r="F473" s="10" t="n">
         <v>0.417</v>
       </c>
     </row>
@@ -10170,7 +10260,7 @@
           <t>22.24 + 7.39 + 29.83 + 11.12 + 31.37 = 101.95</t>
         </is>
       </c>
-      <c r="F474" s="10" t="n"/>
+      <c r="F474" s="11" t="n"/>
     </row>
     <row r="475" ht="18" customHeight="1">
       <c r="A475" s="3" t="n"/>
@@ -10190,7 +10280,7 @@
           <t>22.24 + 7.39 + 29.83 + 11.12 + 31.37 = 101.95</t>
         </is>
       </c>
-      <c r="F475" s="10" t="n"/>
+      <c r="F475" s="11" t="n"/>
     </row>
     <row r="476" ht="18" customHeight="1">
       <c r="A476" s="3" t="n"/>
@@ -10210,7 +10300,7 @@
           <t>22.24 + 7.39 + 29.83 + 11.12 + 31.37 = 101.95</t>
         </is>
       </c>
-      <c r="F476" s="10" t="n"/>
+      <c r="F476" s="11" t="n"/>
     </row>
     <row r="477" ht="18" customHeight="1">
       <c r="A477" s="3" t="n"/>
@@ -10226,7 +10316,9 @@
           <t>(111.07 + 101.95 + 101.95 + 101.95) ÷ 1000 = 0.417</t>
         </is>
       </c>
-      <c r="F477" s="10" t="n"/>
+      <c r="F477" s="12" t="n">
+        <v>0.417</v>
+      </c>
     </row>
     <row r="478" ht="18" customHeight="1">
       <c r="A478" s="3" t="n">
@@ -10252,7 +10344,7 @@
           <t>11.718 + 5.789 + 15.762 + 11.724 + 5.792 + 15.771 = 66.556</t>
         </is>
       </c>
-      <c r="F478" s="9" t="n">
+      <c r="F478" s="10" t="n">
         <v>0.266</v>
       </c>
     </row>
@@ -10274,7 +10366,7 @@
           <t>11.704 + 5.783 + 15.741 + 11.724 + 5.792 + 15.771 = 66.515</t>
         </is>
       </c>
-      <c r="F479" s="10" t="n"/>
+      <c r="F479" s="11" t="n"/>
     </row>
     <row r="480" ht="18" customHeight="1">
       <c r="A480" s="3" t="n"/>
@@ -10294,7 +10386,7 @@
           <t>11.704 + 5.783 + 15.741 + 11.724 + 5.792 + 15.771 = 66.515</t>
         </is>
       </c>
-      <c r="F480" s="10" t="n"/>
+      <c r="F480" s="11" t="n"/>
     </row>
     <row r="481" ht="18" customHeight="1">
       <c r="A481" s="3" t="n"/>
@@ -10314,7 +10406,7 @@
           <t>11.704 + 5.783 + 15.741 + 11.724 + 5.792 + 15.771 = 66.515</t>
         </is>
       </c>
-      <c r="F481" s="10" t="n"/>
+      <c r="F481" s="11" t="n"/>
     </row>
     <row r="482" ht="18" customHeight="1">
       <c r="A482" s="3" t="n"/>
@@ -10330,7 +10422,9 @@
           <t>(66.556 + 66.515 + 66.515 + 66.515) ÷ 1000 = 0.266</t>
         </is>
       </c>
-      <c r="F482" s="10" t="n"/>
+      <c r="F482" s="12" t="n">
+        <v>0.266</v>
+      </c>
     </row>
     <row r="483" ht="18" customHeight="1">
       <c r="A483" s="3" t="n">
@@ -10356,7 +10450,7 @@
           <t>1.701 = 1.701</t>
         </is>
       </c>
-      <c r="F483" s="9" t="n">
+      <c r="F483" s="10" t="n">
         <v>0.08799999999999999</v>
       </c>
     </row>
@@ -10378,7 +10472,7 @@
           <t>6.534 = 6.534</t>
         </is>
       </c>
-      <c r="F484" s="10" t="n"/>
+      <c r="F484" s="11" t="n"/>
     </row>
     <row r="485" ht="18" customHeight="1">
       <c r="A485" s="3" t="n"/>
@@ -10398,7 +10492,7 @@
           <t>3.213 = 3.213</t>
         </is>
       </c>
-      <c r="F485" s="10" t="n"/>
+      <c r="F485" s="11" t="n"/>
     </row>
     <row r="486" ht="18" customHeight="1">
       <c r="A486" s="3" t="n"/>
@@ -10418,7 +10512,7 @@
           <t>12.342 = 12.342</t>
         </is>
       </c>
-      <c r="F486" s="10" t="n"/>
+      <c r="F486" s="11" t="n"/>
     </row>
     <row r="487" ht="18" customHeight="1">
       <c r="A487" s="3" t="n"/>
@@ -10438,7 +10532,7 @@
           <t>3.213 = 3.213</t>
         </is>
       </c>
-      <c r="F487" s="10" t="n"/>
+      <c r="F487" s="11" t="n"/>
     </row>
     <row r="488" ht="18" customHeight="1">
       <c r="A488" s="3" t="n"/>
@@ -10458,7 +10552,7 @@
           <t>12.342 = 12.342</t>
         </is>
       </c>
-      <c r="F488" s="10" t="n"/>
+      <c r="F488" s="11" t="n"/>
     </row>
     <row r="489" ht="18" customHeight="1">
       <c r="A489" s="3" t="n"/>
@@ -10478,7 +10572,7 @@
           <t>3.213 = 3.213</t>
         </is>
       </c>
-      <c r="F489" s="10" t="n"/>
+      <c r="F489" s="11" t="n"/>
     </row>
     <row r="490" ht="18" customHeight="1">
       <c r="A490" s="3" t="n"/>
@@ -10498,7 +10592,7 @@
           <t>12.342 = 12.342</t>
         </is>
       </c>
-      <c r="F490" s="10" t="n"/>
+      <c r="F490" s="11" t="n"/>
     </row>
     <row r="491" ht="18" customHeight="1">
       <c r="A491" s="3" t="n"/>
@@ -10518,7 +10612,7 @@
           <t>3.213 = 3.213</t>
         </is>
       </c>
-      <c r="F491" s="10" t="n"/>
+      <c r="F491" s="11" t="n"/>
     </row>
     <row r="492" ht="18" customHeight="1">
       <c r="A492" s="3" t="n"/>
@@ -10538,7 +10632,7 @@
           <t>12.342 = 12.342</t>
         </is>
       </c>
-      <c r="F492" s="10" t="n"/>
+      <c r="F492" s="11" t="n"/>
     </row>
     <row r="493" ht="18" customHeight="1">
       <c r="A493" s="3" t="n"/>
@@ -10558,7 +10652,7 @@
           <t>5.292 + 2.835 + 2.646 = 10.773</t>
         </is>
       </c>
-      <c r="F493" s="10" t="n"/>
+      <c r="F493" s="11" t="n"/>
     </row>
     <row r="494" ht="18" customHeight="1">
       <c r="A494" s="3" t="n"/>
@@ -10578,7 +10672,7 @@
           <t>6.534 = 6.534</t>
         </is>
       </c>
-      <c r="F494" s="10" t="n"/>
+      <c r="F494" s="11" t="n"/>
     </row>
     <row r="495" ht="18" customHeight="1">
       <c r="A495" s="3" t="n"/>
@@ -10594,7 +10688,9 @@
           <t>(1.701 + 6.534 + 3.213 + 12.342 + 3.213 + 12.342 + 3.213 + 12.342 + 3.213 + 12.342 + 10.773 + 6.534) ÷ 1000 = 0.088</t>
         </is>
       </c>
-      <c r="F495" s="10" t="n"/>
+      <c r="F495" s="12" t="n">
+        <v>0.08799999999999999</v>
+      </c>
     </row>
     <row r="496" ht="18" customHeight="1">
       <c r="A496" s="3" t="n">
@@ -10620,7 +10716,7 @@
           <t>5.844 + 3.368 = 9.212</t>
         </is>
       </c>
-      <c r="F496" s="9" t="n">
+      <c r="F496" s="10" t="n">
         <v>0.357</v>
       </c>
     </row>
@@ -10642,7 +10738,7 @@
           <t>17.532 + 10.104 = 27.636</t>
         </is>
       </c>
-      <c r="F497" s="10" t="n"/>
+      <c r="F497" s="11" t="n"/>
     </row>
     <row r="498" ht="18" customHeight="1">
       <c r="A498" s="3" t="n"/>
@@ -10662,7 +10758,7 @@
           <t>11.704 + 3.368 = 15.072</t>
         </is>
       </c>
-      <c r="F498" s="10" t="n"/>
+      <c r="F498" s="11" t="n"/>
     </row>
     <row r="499" ht="18" customHeight="1">
       <c r="A499" s="3" t="n"/>
@@ -10682,7 +10778,7 @@
           <t>35.112 + 10.104 = 45.216</t>
         </is>
       </c>
-      <c r="F499" s="10" t="n"/>
+      <c r="F499" s="11" t="n"/>
     </row>
     <row r="500" ht="18" customHeight="1">
       <c r="A500" s="3" t="n"/>
@@ -10702,7 +10798,7 @@
           <t>11.704 + 3.28 = 14.984</t>
         </is>
       </c>
-      <c r="F500" s="10" t="n"/>
+      <c r="F500" s="11" t="n"/>
     </row>
     <row r="501" ht="18" customHeight="1">
       <c r="A501" s="3" t="n"/>
@@ -10722,7 +10818,7 @@
           <t>35.112 + 9.84 = 44.952</t>
         </is>
       </c>
-      <c r="F501" s="10" t="n"/>
+      <c r="F501" s="11" t="n"/>
     </row>
     <row r="502" ht="18" customHeight="1">
       <c r="A502" s="3" t="n"/>
@@ -10742,7 +10838,7 @@
           <t>11.704 + 3.28 = 14.984</t>
         </is>
       </c>
-      <c r="F502" s="10" t="n"/>
+      <c r="F502" s="11" t="n"/>
     </row>
     <row r="503" ht="18" customHeight="1">
       <c r="A503" s="3" t="n"/>
@@ -10762,7 +10858,7 @@
           <t>35.112 + 9.84 = 44.952</t>
         </is>
       </c>
-      <c r="F503" s="10" t="n"/>
+      <c r="F503" s="11" t="n"/>
     </row>
     <row r="504" ht="18" customHeight="1">
       <c r="A504" s="3" t="n"/>
@@ -10782,7 +10878,7 @@
           <t>11.704 + 3.28 = 14.984</t>
         </is>
       </c>
-      <c r="F504" s="10" t="n"/>
+      <c r="F504" s="11" t="n"/>
     </row>
     <row r="505" ht="18" customHeight="1">
       <c r="A505" s="3" t="n"/>
@@ -10802,7 +10898,7 @@
           <t>35.112 + 9.84 = 44.952</t>
         </is>
       </c>
-      <c r="F505" s="10" t="n"/>
+      <c r="F505" s="11" t="n"/>
     </row>
     <row r="506" ht="18" customHeight="1">
       <c r="A506" s="3" t="n"/>
@@ -10822,7 +10918,7 @@
           <t>19.144 + 6.736 + 9.928 + 3.368 + 9.752 + 3.368 = 52.296</t>
         </is>
       </c>
-      <c r="F506" s="10" t="n"/>
+      <c r="F506" s="11" t="n"/>
     </row>
     <row r="507" ht="18" customHeight="1">
       <c r="A507" s="3" t="n"/>
@@ -10842,7 +10938,7 @@
           <t>18.06 + 9.84 = 27.9</t>
         </is>
       </c>
-      <c r="F507" s="10" t="n"/>
+      <c r="F507" s="11" t="n"/>
     </row>
     <row r="508" ht="18" customHeight="1">
       <c r="A508" s="3" t="n"/>
@@ -10858,7 +10954,9 @@
           <t>(9.212 + 27.636 + 15.072 + 45.216 + 14.984 + 44.952 + 14.984 + 44.952 + 14.984 + 44.952 + 52.296 + 27.9) ÷ 1000 = 0.357</t>
         </is>
       </c>
-      <c r="F508" s="10" t="n"/>
+      <c r="F508" s="12" t="n">
+        <v>0.357</v>
+      </c>
     </row>
     <row r="509" ht="18" customHeight="1">
       <c r="A509" s="3" t="n">
@@ -10884,7 +10982,7 @@
           <t>0.275 = 0.275</t>
         </is>
       </c>
-      <c r="F509" s="9" t="n">
+      <c r="F509" s="10" t="n">
         <v>0</v>
       </c>
     </row>
@@ -10902,7 +11000,9 @@
           <t>(0.275) ÷ 1000 = 0.000</t>
         </is>
       </c>
-      <c r="F510" s="10" t="n"/>
+      <c r="F510" s="12" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="511" ht="18" customHeight="1">
       <c r="A511" s="3" t="n">
@@ -10928,7 +11028,7 @@
           <t>4.212 = 4.212</t>
         </is>
       </c>
-      <c r="F511" s="9" t="n">
+      <c r="F511" s="10" t="n">
         <v>0.044</v>
       </c>
     </row>
@@ -10950,7 +11050,7 @@
           <t>10.368 = 10.368</t>
         </is>
       </c>
-      <c r="F512" s="10" t="n"/>
+      <c r="F512" s="11" t="n"/>
     </row>
     <row r="513" ht="18" customHeight="1">
       <c r="A513" s="3" t="n"/>
@@ -10970,7 +11070,7 @@
           <t>4.212 = 4.212</t>
         </is>
       </c>
-      <c r="F513" s="10" t="n"/>
+      <c r="F513" s="11" t="n"/>
     </row>
     <row r="514" ht="18" customHeight="1">
       <c r="A514" s="3" t="n"/>
@@ -10990,7 +11090,7 @@
           <t>5.184 = 5.184</t>
         </is>
       </c>
-      <c r="F514" s="10" t="n"/>
+      <c r="F514" s="11" t="n"/>
     </row>
     <row r="515" ht="18" customHeight="1">
       <c r="A515" s="3" t="n"/>
@@ -11010,7 +11110,7 @@
           <t>4.212 = 4.212</t>
         </is>
       </c>
-      <c r="F515" s="10" t="n"/>
+      <c r="F515" s="11" t="n"/>
     </row>
     <row r="516" ht="18" customHeight="1">
       <c r="A516" s="3" t="n"/>
@@ -11030,7 +11130,7 @@
           <t>5.184 = 5.184</t>
         </is>
       </c>
-      <c r="F516" s="10" t="n"/>
+      <c r="F516" s="11" t="n"/>
     </row>
     <row r="517" ht="18" customHeight="1">
       <c r="A517" s="3" t="n"/>
@@ -11050,7 +11150,7 @@
           <t>4.212 = 4.212</t>
         </is>
       </c>
-      <c r="F517" s="10" t="n"/>
+      <c r="F517" s="11" t="n"/>
     </row>
     <row r="518" ht="18" customHeight="1">
       <c r="A518" s="3" t="n"/>
@@ -11070,7 +11170,7 @@
           <t>5.184 = 5.184</t>
         </is>
       </c>
-      <c r="F518" s="10" t="n"/>
+      <c r="F518" s="11" t="n"/>
     </row>
     <row r="519" ht="18" customHeight="1">
       <c r="A519" s="3" t="n"/>
@@ -11090,7 +11190,7 @@
           <t>1.62 = 1.62</t>
         </is>
       </c>
-      <c r="F519" s="10" t="n"/>
+      <c r="F519" s="11" t="n"/>
     </row>
     <row r="520" ht="18" customHeight="1">
       <c r="A520" s="3" t="n"/>
@@ -11106,7 +11206,9 @@
           <t>(4.212 + 10.368 + 4.212 + 5.184 + 4.212 + 5.184 + 4.212 + 5.184 + 1.62) ÷ 1000 = 0.044</t>
         </is>
       </c>
-      <c r="F520" s="10" t="n"/>
+      <c r="F520" s="12" t="n">
+        <v>0.044</v>
+      </c>
     </row>
     <row r="521" ht="18" customHeight="1">
       <c r="A521" s="3" t="n">
@@ -11132,7 +11234,7 @@
           <t>1.224 = 1.224</t>
         </is>
       </c>
-      <c r="F521" s="9" t="n">
+      <c r="F521" s="10" t="n">
         <v>0.001</v>
       </c>
     </row>
@@ -11150,7 +11252,9 @@
           <t>(1.224) ÷ 1000 = 0.001</t>
         </is>
       </c>
-      <c r="F522" s="10" t="n"/>
+      <c r="F522" s="12" t="n">
+        <v>0.001</v>
+      </c>
     </row>
     <row r="523" ht="18" customHeight="1">
       <c r="A523" s="3" t="n">
@@ -11176,7 +11280,7 @@
           <t>17.048 = 17.048</t>
         </is>
       </c>
-      <c r="F523" s="9" t="n">
+      <c r="F523" s="10" t="n">
         <v>0.077</v>
       </c>
     </row>
@@ -11198,7 +11302,7 @@
           <t>17.048 = 17.048</t>
         </is>
       </c>
-      <c r="F524" s="10" t="n"/>
+      <c r="F524" s="11" t="n"/>
     </row>
     <row r="525" ht="18" customHeight="1">
       <c r="A525" s="3" t="n"/>
@@ -11218,7 +11322,7 @@
           <t>17.048 = 17.048</t>
         </is>
       </c>
-      <c r="F525" s="10" t="n"/>
+      <c r="F525" s="11" t="n"/>
     </row>
     <row r="526" ht="18" customHeight="1">
       <c r="A526" s="3" t="n"/>
@@ -11238,7 +11342,7 @@
           <t>17.048 = 17.048</t>
         </is>
       </c>
-      <c r="F526" s="10" t="n"/>
+      <c r="F526" s="11" t="n"/>
     </row>
     <row r="527" ht="18" customHeight="1">
       <c r="A527" s="3" t="n"/>
@@ -11258,7 +11362,7 @@
           <t>8.444 = 8.444</t>
         </is>
       </c>
-      <c r="F527" s="10" t="n"/>
+      <c r="F527" s="11" t="n"/>
     </row>
     <row r="528" ht="18" customHeight="1">
       <c r="A528" s="3" t="n"/>
@@ -11274,7 +11378,9 @@
           <t>(17.048 + 17.048 + 17.048 + 17.048 + 8.444) ÷ 1000 = 0.077</t>
         </is>
       </c>
-      <c r="F528" s="10" t="n"/>
+      <c r="F528" s="12" t="n">
+        <v>0.077</v>
+      </c>
     </row>
     <row r="529" ht="18" customHeight="1">
       <c r="A529" s="3" t="n">
@@ -11300,7 +11406,7 @@
           <t>58.56 = 58.56</t>
         </is>
       </c>
-      <c r="F529" s="9" t="n">
+      <c r="F529" s="10" t="n">
         <v>0.146</v>
       </c>
     </row>
@@ -11322,7 +11428,7 @@
           <t>29.28 = 29.28</t>
         </is>
       </c>
-      <c r="F530" s="10" t="n"/>
+      <c r="F530" s="11" t="n"/>
     </row>
     <row r="531" ht="18" customHeight="1">
       <c r="A531" s="3" t="n"/>
@@ -11342,7 +11448,7 @@
           <t>29.28 = 29.28</t>
         </is>
       </c>
-      <c r="F531" s="10" t="n"/>
+      <c r="F531" s="11" t="n"/>
     </row>
     <row r="532" ht="18" customHeight="1">
       <c r="A532" s="3" t="n"/>
@@ -11362,7 +11468,7 @@
           <t>29.28 = 29.28</t>
         </is>
       </c>
-      <c r="F532" s="10" t="n"/>
+      <c r="F532" s="11" t="n"/>
     </row>
     <row r="533" ht="18" customHeight="1">
       <c r="A533" s="3" t="n"/>
@@ -11378,7 +11484,9 @@
           <t>(58.56 + 29.28 + 29.28 + 29.28) ÷ 1000 = 0.146</t>
         </is>
       </c>
-      <c r="F533" s="10" t="n"/>
+      <c r="F533" s="12" t="n">
+        <v>0.146</v>
+      </c>
     </row>
     <row r="534" ht="18" customHeight="1">
       <c r="A534" s="3" t="n">
@@ -11404,7 +11512,7 @@
           <t>5.796 + 3.519 + 7.866 = 17.181</t>
         </is>
       </c>
-      <c r="F534" s="9" t="n">
+      <c r="F534" s="10" t="n">
         <v>0.021</v>
       </c>
     </row>
@@ -11426,7 +11534,7 @@
           <t>4.267 = 4.267</t>
         </is>
       </c>
-      <c r="F535" s="10" t="n"/>
+      <c r="F535" s="11" t="n"/>
     </row>
     <row r="536" ht="18" customHeight="1">
       <c r="A536" s="3" t="n"/>
@@ -11442,7 +11550,9 @@
           <t>(17.181 + 4.267) ÷ 1000 = 0.021</t>
         </is>
       </c>
-      <c r="F536" s="10" t="n"/>
+      <c r="F536" s="12" t="n">
+        <v>0.021</v>
+      </c>
     </row>
     <row r="537" ht="18" customHeight="1">
       <c r="A537" s="3" t="n">
@@ -11468,7 +11578,7 @@
           <t>14.478 + 14.2 + 6.93 + 6.394 + 14.46 + 14.2 = 70.662</t>
         </is>
       </c>
-      <c r="F537" s="9" t="n">
+      <c r="F537" s="10" t="n">
         <v>0.08400000000000001</v>
       </c>
     </row>
@@ -11490,7 +11600,7 @@
           <t>6.394 + 6.948 = 13.342</t>
         </is>
       </c>
-      <c r="F538" s="10" t="n"/>
+      <c r="F538" s="11" t="n"/>
     </row>
     <row r="539" ht="18" customHeight="1">
       <c r="A539" s="3" t="n"/>
@@ -11506,7 +11616,9 @@
           <t>(70.662 + 13.342) ÷ 1000 = 0.084</t>
         </is>
       </c>
-      <c r="F539" s="10" t="n"/>
+      <c r="F539" s="12" t="n">
+        <v>0.08400000000000001</v>
+      </c>
     </row>
     <row r="540" ht="18" customHeight="1">
       <c r="A540" s="3" t="n">
@@ -11532,7 +11644,7 @@
           <t>6.04 = 6.04</t>
         </is>
       </c>
-      <c r="F540" s="9" t="n">
+      <c r="F540" s="10" t="n">
         <v>0.006</v>
       </c>
     </row>
@@ -11550,7 +11662,9 @@
           <t>(6.04) ÷ 1000 = 0.006</t>
         </is>
       </c>
-      <c r="F541" s="10" t="n"/>
+      <c r="F541" s="12" t="n">
+        <v>0.006</v>
+      </c>
     </row>
     <row r="542" ht="18" customHeight="1">
       <c r="A542" s="3" t="n">
@@ -11576,7 +11690,7 @@
           <t>200.1282×1.316 = 263.369</t>
         </is>
       </c>
-      <c r="F542" s="9" t="n">
+      <c r="F542" s="10" t="n">
         <v>0.263</v>
       </c>
     </row>
@@ -11594,7 +11708,9 @@
           <t>(263.369) ÷ 1000 = 0.263</t>
         </is>
       </c>
-      <c r="F543" s="10" t="n"/>
+      <c r="F543" s="12" t="n">
+        <v>0.263</v>
+      </c>
     </row>
     <row r="544" ht="18" customHeight="1">
       <c r="A544" s="3" t="n">
@@ -11642,7 +11758,7 @@
           <t>(0.8×2.1) = 1.68</t>
         </is>
       </c>
-      <c r="F545" s="8" t="n"/>
+      <c r="F545" s="9" t="n"/>
     </row>
     <row r="546" ht="18" customHeight="1">
       <c r="A546" s="3" t="n"/>
@@ -11662,7 +11778,7 @@
           <t>(1.5×2.1) = 3.15</t>
         </is>
       </c>
-      <c r="F546" s="8" t="n"/>
+      <c r="F546" s="9" t="n"/>
     </row>
     <row r="547" ht="18" customHeight="1">
       <c r="A547" s="3" t="n"/>
@@ -11678,7 +11794,9 @@
           <t>9 + 1.68 + 3.15 = 13.83 ≈ 13.83</t>
         </is>
       </c>
-      <c r="F547" s="8" t="n"/>
+      <c r="F547" s="8" t="n">
+        <v>13.83</v>
+      </c>
     </row>
     <row r="548" ht="18" customHeight="1">
       <c r="A548" s="3" t="n">
@@ -11726,7 +11844,7 @@
           <t>[(2.4×1.8)]×2 = 8.64</t>
         </is>
       </c>
-      <c r="F549" s="8" t="n"/>
+      <c r="F549" s="9" t="n"/>
     </row>
     <row r="550" ht="18" customHeight="1">
       <c r="A550" s="3" t="n"/>
@@ -11746,7 +11864,7 @@
           <t>(1.8×1.8) = 3.24</t>
         </is>
       </c>
-      <c r="F550" s="8" t="n"/>
+      <c r="F550" s="9" t="n"/>
     </row>
     <row r="551" ht="18" customHeight="1">
       <c r="A551" s="3" t="n"/>
@@ -11766,7 +11884,7 @@
           <t>(1.8×1) = 1.8</t>
         </is>
       </c>
-      <c r="F551" s="8" t="n"/>
+      <c r="F551" s="9" t="n"/>
     </row>
     <row r="552" ht="18" customHeight="1">
       <c r="A552" s="3" t="n"/>
@@ -11786,7 +11904,7 @@
           <t>[(1.2×3.05)]×2 = 7.32</t>
         </is>
       </c>
-      <c r="F552" s="8" t="n"/>
+      <c r="F552" s="9" t="n"/>
     </row>
     <row r="553" ht="18" customHeight="1">
       <c r="A553" s="3" t="n"/>
@@ -11806,7 +11924,7 @@
           <t>(4×1.8) = 7.2</t>
         </is>
       </c>
-      <c r="F553" s="8" t="n"/>
+      <c r="F553" s="9" t="n"/>
     </row>
     <row r="554" ht="18" customHeight="1">
       <c r="A554" s="3" t="n"/>
@@ -11826,7 +11944,7 @@
           <t>[(2.4×3.2)]×2 = 15.36</t>
         </is>
       </c>
-      <c r="F554" s="8" t="n"/>
+      <c r="F554" s="9" t="n"/>
     </row>
     <row r="555" ht="18" customHeight="1">
       <c r="A555" s="3" t="n"/>
@@ -11846,7 +11964,7 @@
           <t>[(2.4×1.8)]×2 = 8.64</t>
         </is>
       </c>
-      <c r="F555" s="8" t="n"/>
+      <c r="F555" s="9" t="n"/>
     </row>
     <row r="556" ht="18" customHeight="1">
       <c r="A556" s="3" t="n"/>
@@ -11866,7 +11984,7 @@
           <t>[(1.8×1.8)]×2 = 6.48</t>
         </is>
       </c>
-      <c r="F556" s="8" t="n"/>
+      <c r="F556" s="9" t="n"/>
     </row>
     <row r="557" ht="18" customHeight="1">
       <c r="A557" s="3" t="n"/>
@@ -11886,7 +12004,7 @@
           <t>[(1.2×3.05)]×2 = 7.32</t>
         </is>
       </c>
-      <c r="F557" s="8" t="n"/>
+      <c r="F557" s="9" t="n"/>
     </row>
     <row r="558" ht="18" customHeight="1">
       <c r="A558" s="3" t="n"/>
@@ -11906,7 +12024,7 @@
           <t>(4×1.8) = 7.2</t>
         </is>
       </c>
-      <c r="F558" s="8" t="n"/>
+      <c r="F558" s="9" t="n"/>
     </row>
     <row r="559" ht="18" customHeight="1">
       <c r="A559" s="3" t="n"/>
@@ -11926,7 +12044,7 @@
           <t>[(2.4×3.2)]×2 = 15.36</t>
         </is>
       </c>
-      <c r="F559" s="8" t="n"/>
+      <c r="F559" s="9" t="n"/>
     </row>
     <row r="560" ht="18" customHeight="1">
       <c r="A560" s="3" t="n"/>
@@ -11946,7 +12064,7 @@
           <t>[(2.4×1.8)]×2 = 8.64</t>
         </is>
       </c>
-      <c r="F560" s="8" t="n"/>
+      <c r="F560" s="9" t="n"/>
     </row>
     <row r="561" ht="18" customHeight="1">
       <c r="A561" s="3" t="n"/>
@@ -11966,7 +12084,7 @@
           <t>[(1.8×1.8)]×2 = 6.48</t>
         </is>
       </c>
-      <c r="F561" s="8" t="n"/>
+      <c r="F561" s="9" t="n"/>
     </row>
     <row r="562" ht="18" customHeight="1">
       <c r="A562" s="3" t="n"/>
@@ -11986,7 +12104,7 @@
           <t>[(1.2×3.05)]×2 = 7.32</t>
         </is>
       </c>
-      <c r="F562" s="8" t="n"/>
+      <c r="F562" s="9" t="n"/>
     </row>
     <row r="563" ht="18" customHeight="1">
       <c r="A563" s="3" t="n"/>
@@ -12006,7 +12124,7 @@
           <t>(4×1.8) = 7.2</t>
         </is>
       </c>
-      <c r="F563" s="8" t="n"/>
+      <c r="F563" s="9" t="n"/>
     </row>
     <row r="564" ht="18" customHeight="1">
       <c r="A564" s="3" t="n"/>
@@ -12026,7 +12144,7 @@
           <t>[(2.4×3.2)]×2 = 15.36</t>
         </is>
       </c>
-      <c r="F564" s="8" t="n"/>
+      <c r="F564" s="9" t="n"/>
     </row>
     <row r="565" ht="18" customHeight="1">
       <c r="A565" s="3" t="n"/>
@@ -12046,7 +12164,7 @@
           <t>[(2.4×1.8)]×2 = 8.64</t>
         </is>
       </c>
-      <c r="F565" s="8" t="n"/>
+      <c r="F565" s="9" t="n"/>
     </row>
     <row r="566" ht="18" customHeight="1">
       <c r="A566" s="3" t="n"/>
@@ -12066,7 +12184,7 @@
           <t>[(1.8×1.8)]×2 = 6.48</t>
         </is>
       </c>
-      <c r="F566" s="8" t="n"/>
+      <c r="F566" s="9" t="n"/>
     </row>
     <row r="567" ht="18" customHeight="1">
       <c r="A567" s="3" t="n"/>
@@ -12086,7 +12204,7 @@
           <t>[(1.2×3.05)]×2 = 7.32</t>
         </is>
       </c>
-      <c r="F567" s="8" t="n"/>
+      <c r="F567" s="9" t="n"/>
     </row>
     <row r="568" ht="18" customHeight="1">
       <c r="A568" s="3" t="n"/>
@@ -12102,7 +12220,9 @@
           <t>8.64 + 8.64 + 3.24 + 1.8 + 7.32 + 7.2 + 15.36 + 8.64 + 6.48 + 7.32 + 7.2 + 15.36 + 8.64 + 6.48 + 7.32 + 7.2 + 15.36 + 8.64 + 6.48 + 7.32 = 164.64 ≈ 164.64</t>
         </is>
       </c>
-      <c r="F568" s="8" t="n"/>
+      <c r="F568" s="8" t="n">
+        <v>164.64</v>
+      </c>
     </row>
     <row r="569" ht="18" customHeight="1">
       <c r="A569" s="3" t="n">
@@ -12146,7 +12266,9 @@
           <t>219.2982 ≈ 219.30</t>
         </is>
       </c>
-      <c r="F570" s="8" t="n"/>
+      <c r="F570" s="8" t="n">
+        <v>219.3</v>
+      </c>
     </row>
     <row r="571" ht="18" customHeight="1">
       <c r="A571" s="3" t="n">
@@ -12190,7 +12312,9 @@
           <t>200.1282 ≈ 200.13</t>
         </is>
       </c>
-      <c r="F572" s="8" t="n"/>
+      <c r="F572" s="8" t="n">
+        <v>200.13</v>
+      </c>
     </row>
     <row r="573" ht="18" customHeight="1">
       <c r="A573" s="3" t="n">
@@ -12216,7 +12340,7 @@
           <t>计算书中无依据，需补充</t>
         </is>
       </c>
-      <c r="F573" s="8" t="inlineStr">
+      <c r="F573" s="9" t="inlineStr">
         <is>
           <t>需补充</t>
         </is>
@@ -12264,7 +12388,9 @@
           <t>4.5787 ≈ 4.58</t>
         </is>
       </c>
-      <c r="F575" s="8" t="n"/>
+      <c r="F575" s="8" t="n">
+        <v>4.58</v>
+      </c>
     </row>
     <row r="576" ht="18" customHeight="1">
       <c r="A576" s="3" t="n">
@@ -12308,7 +12434,9 @@
           <t>200.1282 ≈ 200.13</t>
         </is>
       </c>
-      <c r="F577" s="8" t="n"/>
+      <c r="F577" s="8" t="n">
+        <v>200.13</v>
+      </c>
     </row>
     <row r="578" ht="18" customHeight="1">
       <c r="A578" s="3" t="n">
@@ -12356,7 +12484,7 @@
           <t>(15.26×13.26)+1.8131-1.404-0.62-0.4428-0.7875 = 200.9065</t>
         </is>
       </c>
-      <c r="F579" s="8" t="n"/>
+      <c r="F579" s="9" t="n"/>
     </row>
     <row r="580" ht="18" customHeight="1">
       <c r="A580" s="3" t="n"/>
@@ -12376,7 +12504,7 @@
           <t>(15.26×13.26)-1.404-0.62-0.4428 = 199.8808</t>
         </is>
       </c>
-      <c r="F580" s="8" t="n"/>
+      <c r="F580" s="9" t="n"/>
     </row>
     <row r="581" ht="18" customHeight="1">
       <c r="A581" s="3" t="n"/>
@@ -12396,7 +12524,7 @@
           <t>(15.26×13.26)-1.404-0.62-0.4428 = 199.8808</t>
         </is>
       </c>
-      <c r="F581" s="8" t="n"/>
+      <c r="F581" s="9" t="n"/>
     </row>
     <row r="582" ht="18" customHeight="1">
       <c r="A582" s="3" t="n"/>
@@ -12416,7 +12544,7 @@
           <t>(7.41×3.16) = 23.4156</t>
         </is>
       </c>
-      <c r="F582" s="8" t="n"/>
+      <c r="F582" s="9" t="n"/>
     </row>
     <row r="583" ht="18" customHeight="1">
       <c r="A583" s="3" t="n"/>
@@ -12432,7 +12560,9 @@
           <t>172.0871 + 200.9065 + 199.8808 + 199.8808 + 23.4156 = 796.1708 ≈ 796.17</t>
         </is>
       </c>
-      <c r="F583" s="8" t="n"/>
+      <c r="F583" s="8" t="n">
+        <v>796.17</v>
+      </c>
     </row>
     <row r="584" ht="18" customHeight="1">
       <c r="A584" s="3" t="n">
@@ -12476,7 +12606,9 @@
           <t>4.5787 ≈ 4.58</t>
         </is>
       </c>
-      <c r="F585" s="8" t="n"/>
+      <c r="F585" s="8" t="n">
+        <v>4.58</v>
+      </c>
     </row>
     <row r="586" ht="18" customHeight="1">
       <c r="A586" s="3" t="n">
@@ -12524,7 +12656,7 @@
           <t>13.26+1.425-0.905-1.2 + 15.02+1.64-1.02-1.8 + 13.26+1.9569-1.405-1.2 + 15.26-4.8 + [5.85+1.355-0.975]×2 = 61.9519</t>
         </is>
       </c>
-      <c r="F587" s="8" t="n"/>
+      <c r="F587" s="9" t="n"/>
     </row>
     <row r="588" ht="18" customHeight="1">
       <c r="A588" s="3" t="n"/>
@@ -12544,7 +12676,7 @@
           <t>[5.85+1.355-0.975]×2 + 15.26-4.8 + 13.26+1.9569-1.405-1.2 + 15.02+1.64-1.02-1.8 + 13.26+1.425-0.905-1.2 = 61.9519</t>
         </is>
       </c>
-      <c r="F588" s="8" t="n"/>
+      <c r="F588" s="9" t="n"/>
     </row>
     <row r="589" ht="18" customHeight="1">
       <c r="A589" s="3" t="n"/>
@@ -12564,7 +12696,7 @@
           <t>[5.85+1.355-0.975]×2 + 15.26-4.8 + 13.26+1.9569-1.405-1.2 + 15.02+1.64-1.02-1.8 + 13.26+1.425-0.905-1.2 = 61.9519</t>
         </is>
       </c>
-      <c r="F589" s="8" t="n"/>
+      <c r="F589" s="9" t="n"/>
     </row>
     <row r="590" ht="18" customHeight="1">
       <c r="A590" s="3" t="n"/>
@@ -12584,7 +12716,7 @@
           <t>[3.16]×2 + 7.41 + 7.41-1.5 = 19.64</t>
         </is>
       </c>
-      <c r="F590" s="8" t="n"/>
+      <c r="F590" s="9" t="n"/>
     </row>
     <row r="591" ht="18" customHeight="1">
       <c r="A591" s="3" t="n"/>
@@ -12600,7 +12732,9 @@
           <t>58.63 + 61.9519 + 61.9519 + 61.9519 + 19.64 = 264.1257 ≈ 264.13</t>
         </is>
       </c>
-      <c r="F591" s="8" t="n"/>
+      <c r="F591" s="8" t="n">
+        <v>264.13</v>
+      </c>
     </row>
     <row r="592" ht="18" customHeight="1">
       <c r="A592" s="3" t="n">
@@ -12648,7 +12782,7 @@
           <t>13.74×3.6-5.004+5.565-6.605+6.7285-3.66 + 15.74×3.6-3.564+5.424-5.9+6.0475-22.56 + 13.74×3.6-5.904+6.4955-6.4675+6.5885-3.66 + 15.5×3.6-5.4+6.428-5.6+5.74-14.4 = 171.6845</t>
         </is>
       </c>
-      <c r="F593" s="8" t="n"/>
+      <c r="F593" s="9" t="n"/>
     </row>
     <row r="594" ht="32" customHeight="1">
       <c r="A594" s="3" t="n"/>
@@ -12668,7 +12802,7 @@
           <t>13.74×3.6-5.004+5.565-6.605+6.7285-3.66 + 15.74×3.6-3.564+5.424-5.9+6.0475-22.56 + 13.74×3.6-5.904+6.4955-6.4675+6.5885-3.66 + 15.5×3.6-5.4+6.428-5.6+5.74-14.4 = 171.6845</t>
         </is>
       </c>
-      <c r="F594" s="8" t="n"/>
+      <c r="F594" s="9" t="n"/>
     </row>
     <row r="595" ht="32" customHeight="1">
       <c r="A595" s="3" t="n"/>
@@ -12688,7 +12822,7 @@
           <t>13.74×3.6-5.004+5.565-6.605+6.7285-3.66 + 15.74×3.6-3.564+5.424-5.9+6.0475-22.56 + 13.74×3.6-5.904+6.4955-6.4675+6.5873-3.66 + 15.5×3.6-5.4+6.428-5.6+5.74-13.59 = 172.4933</t>
         </is>
       </c>
-      <c r="F595" s="8" t="n"/>
+      <c r="F595" s="9" t="n"/>
     </row>
     <row r="596" ht="32" customHeight="1">
       <c r="A596" s="3" t="n"/>
@@ -12708,7 +12842,7 @@
           <t>(13.74×1.07+1.6344)-0.2843+0.4013+1.9356-4.0413 + (15.74×1.07+1.8744)-0.8662+1.3375+2.1118-4.5 + (5.85×1.07+0.6948)-0.2903+0.5403+0.8243-1.68 + (7.65×3.642+0.9108)-0.75+1.3932-2.22+2.2927+1.1166-1.5228 + (3.642×3.64+0.444)-1.47+1.3922-1.26+1.2915+0.5228-0.7352 + (12.1×1.07+1.4448)-0.0059+0.1391+1.7006-3.6213 = 92.6237</t>
         </is>
       </c>
-      <c r="F596" s="8" t="n"/>
+      <c r="F596" s="9" t="n"/>
     </row>
     <row r="597" ht="18" customHeight="1">
       <c r="A597" s="3" t="n"/>
@@ -12724,7 +12858,9 @@
           <t>161.8592 + 171.6845 + 171.6845 + 172.4933 + 92.6237 = 770.3452 ≈ 770.35</t>
         </is>
       </c>
-      <c r="F597" s="8" t="n"/>
+      <c r="F597" s="8" t="n">
+        <v>770.35</v>
+      </c>
     </row>
     <row r="598" ht="32" customHeight="1">
       <c r="A598" s="3" t="n">
@@ -12772,7 +12908,7 @@
           <t>3.165×1.5-0.2475+0.2242-1.53-0.48+1.2 + [1.5×1.455-0.24+0.2205-0.7122+0.7122]×2 + 3.165×1.5-0.315 = 12.6727</t>
         </is>
       </c>
-      <c r="F599" s="8" t="n"/>
+      <c r="F599" s="9" t="n"/>
     </row>
     <row r="600" ht="32" customHeight="1">
       <c r="A600" s="3" t="n"/>
@@ -12792,7 +12928,7 @@
           <t>46.3392-3.1814+4.8397-3.66-5.3027+5.2265 + (3.6×3.16+41.3344)-3.5734+5.486-15.12-3.617+4.337 + 46.8969-4.994+6.5147-3.66-5.5729+5.5078-0.11-0.4277 + 15.26×3.51-1.7901+1.696-22.56-4.5725+4.495 + 20.9313-3.47+4.6402-2.5926+2.5926 + 5.85×3.5-3.4125+4.5985-2.1938+2.1313 = 203.1701</t>
         </is>
       </c>
-      <c r="F600" s="8" t="n"/>
+      <c r="F600" s="9" t="n"/>
     </row>
     <row r="601" ht="32" customHeight="1">
       <c r="A601" s="3" t="n"/>
@@ -12812,7 +12948,7 @@
           <t>20.9313-3.47+4.6402-2.5926+2.5926 + 5.85×3.5-3.4125+4.5985-2.1938+2.1313 + 15.26×3.51-1.7901+1.696-22.56-4.5725+4.495 + 46.8969-4.994+6.5147-3.66-5.5729+5.5078-0.11-0.4277 + (3.6×3.16+41.3344)-3.5734+5.486-15.12-3.617+4.337 + 46.3392-3.1814+4.8397-3.66-5.3027+5.2265 = 203.1701</t>
         </is>
       </c>
-      <c r="F601" s="8" t="n"/>
+      <c r="F601" s="9" t="n"/>
     </row>
     <row r="602" ht="32" customHeight="1">
       <c r="A602" s="3" t="n"/>
@@ -12832,7 +12968,7 @@
           <t>20.9313-3.47+4.6402-2.5926+2.5926 + 20.528-3.428+4.5985-2.2313+2.1187 + 15.26×3.6-1.836+1.696-22.56-5.9+4.35 + 47.0211-5.0058+6.5137-3.66-5.6854+5.4953-0.11-0.4277 + (3.6×3.16+11.86×3.6)-3.672+5.5-13.59-5.6+4.5 + 46.374-3.201+4.8307-3.66-5.318+5.083 = 203.8336</t>
         </is>
       </c>
-      <c r="F602" s="8" t="n"/>
+      <c r="F602" s="9" t="n"/>
     </row>
     <row r="603" ht="18" customHeight="1">
       <c r="A603" s="3" t="n"/>
@@ -12852,7 +12988,7 @@
           <t>3.16×3-0.03+0.029-0.315 + 21.542-0.0295+0.029-0.0525 + 3.16×2.9-0.029+0.0278 + 21.542-0.0295+0.029-3.15-0.4937+0.4937-0.0525 = 58.1547</t>
         </is>
       </c>
-      <c r="F603" s="8" t="n"/>
+      <c r="F603" s="9" t="n"/>
     </row>
     <row r="604" ht="32" customHeight="1">
       <c r="A604" s="3" t="n"/>
@@ -12872,7 +13008,7 @@
           <t>(27.6045+0.9108)-0.4932+1.2343-3.15-2.3188+2.194 + (5.61×(1.07+0.12))-0.0107+0.0107 + (15.26×(1.07+0.12))-0.3082+0.2889 + (13.26×(1.07+0.12))-0.0053+0.0053 + (12.563+0.4152)-0.8532+1.272-0.945+0.9765 + (11.86×(1.07+0.12))-0.0053+0.0053 = 94.1189</t>
         </is>
       </c>
-      <c r="F604" s="8" t="n"/>
+      <c r="F604" s="9" t="n"/>
     </row>
     <row r="605" ht="18" customHeight="1">
       <c r="A605" s="3" t="n"/>
@@ -12888,7 +13024,9 @@
           <t>187.5849 + 12.6727 + 203.1701 + 203.1701 + 203.8336 + 58.1547 + 94.1189 = 962.705 ≈ 962.71</t>
         </is>
       </c>
-      <c r="F605" s="8" t="n"/>
+      <c r="F605" s="8" t="n">
+        <v>962.71</v>
+      </c>
     </row>
     <row r="606" ht="18" customHeight="1">
       <c r="A606" s="3" t="n">
@@ -12932,7 +13070,9 @@
           <t>16.878 ≈ 16.88</t>
         </is>
       </c>
-      <c r="F607" s="8" t="n"/>
+      <c r="F607" s="8" t="n">
+        <v>16.88</v>
+      </c>
     </row>
     <row r="608" ht="18" customHeight="1">
       <c r="A608" s="3" t="n">
@@ -12980,7 +13120,7 @@
           <t>(3×2.28)+2.7827+0.0141-0.9137-0.0137 + (15.26×1.38)+10.9493+0.0863-2.8487-0.085 + (4.33×3.15)+5.1219+0.0144-1.445-0.0145 + (5.73×2.28+8.73×2.05+11.88×4.45)+26.639+0.0678-7.4369-0.07 + (1.68×0.12+3.16×1.8)+4.661+0.0081-0.9994-0.0077 + (6.48×4.35+3.2×1.68+5.85×3.08)+21.8681+0.059-5.4175-0.062 = 235.7941</t>
         </is>
       </c>
-      <c r="F609" s="8" t="n"/>
+      <c r="F609" s="9" t="n"/>
     </row>
     <row r="610" ht="32" customHeight="1">
       <c r="A610" s="3" t="n"/>
@@ -13000,7 +13140,7 @@
           <t>(8.78×5.73+6.5×3+4.45×3.15)+26.639+0.0678-7.4369-0.07 + (4.33×3.15)+5.1219+0.0144-1.445-0.0145 + (15.26×1.38)+10.9492+0.0863-2.8487-0.085 + (3×2.28)+2.7827+0.0141-0.9137-0.0137 + (6.48×4.35+3.2×1.68+5.85×3.08)+21.8681+0.059-5.4175-0.062 + (1.68×0.12+3.16×1.8)+4.661+0.0081-0.9994-0.0077 = 235.7941</t>
         </is>
       </c>
-      <c r="F610" s="8" t="n"/>
+      <c r="F610" s="9" t="n"/>
     </row>
     <row r="611" ht="18" customHeight="1">
       <c r="A611" s="3" t="n"/>
@@ -13020,7 +13160,7 @@
           <t>77.2942+18.6475+0.1879-9.1212-0.1917 + (11.35×8.78)+30.8617+0.0536-8.4587-0.0542 + (1.68×0.12+3.16×1.8)+5.8422+0.0081-0.9994-0.0077 = 219.6049</t>
         </is>
       </c>
-      <c r="F611" s="8" t="n"/>
+      <c r="F611" s="9" t="n"/>
     </row>
     <row r="612" ht="18" customHeight="1">
       <c r="A612" s="3" t="n"/>
@@ -13040,7 +13180,7 @@
           <t>(7.41×3.16)+2.686+0.0099-0.79-0.0099 = 25.3116</t>
         </is>
       </c>
-      <c r="F612" s="8" t="n"/>
+      <c r="F612" s="9" t="n"/>
     </row>
     <row r="613" ht="18" customHeight="1">
       <c r="A613" s="3" t="n"/>
@@ -13056,7 +13196,9 @@
           <t>192.2586 + 235.7941 + 235.7941 + 219.6049 + 25.3116 = 908.7633 ≈ 908.76</t>
         </is>
       </c>
-      <c r="F613" s="8" t="n"/>
+      <c r="F613" s="8" t="n">
+        <v>908.76</v>
+      </c>
     </row>
     <row r="614" ht="18" customHeight="1">
       <c r="A614" s="3" t="n">
@@ -13104,7 +13246,7 @@
           <t>13.74×3.6-5.004+5.565-6.605+6.7285-3.66 + 15.74×3.6-3.564+5.424-5.9+6.0475-22.56 + 13.74×3.6-5.904+6.4955-6.4675+6.5885-3.66 + 15.5×3.6-5.4+6.428-5.6+5.74-14.4 = 171.6845</t>
         </is>
       </c>
-      <c r="F615" s="8" t="n"/>
+      <c r="F615" s="9" t="n"/>
     </row>
     <row r="616" ht="32" customHeight="1">
       <c r="A616" s="3" t="n"/>
@@ -13124,7 +13266,7 @@
           <t>13.74×3.6-5.004+5.565-6.605+6.7285-3.66 + 15.74×3.6-3.564+5.424-5.9+6.0475-22.56 + 13.74×3.6-5.904+6.4955-6.4675+6.5885-3.66 + 15.5×3.6-5.4+6.428-5.6+5.74-14.4 = 171.6845</t>
         </is>
       </c>
-      <c r="F616" s="8" t="n"/>
+      <c r="F616" s="9" t="n"/>
     </row>
     <row r="617" ht="32" customHeight="1">
       <c r="A617" s="3" t="n"/>
@@ -13144,7 +13286,7 @@
           <t>13.74×3.6-5.004+5.565-6.605+6.7285-3.66 + 15.74×3.6-3.564+5.424-5.9+6.0475-22.56 + 13.74×3.6-5.904+6.4955-6.4675+6.5873-3.66 + 15.5×3.6-5.4+6.428-5.6+5.74-13.59 = 172.4933</t>
         </is>
       </c>
-      <c r="F617" s="8" t="n"/>
+      <c r="F617" s="9" t="n"/>
     </row>
     <row r="618" ht="32" customHeight="1">
       <c r="A618" s="3" t="n"/>
@@ -13164,7 +13306,7 @@
           <t>(13.74×1.07+1.6344)-0.2843+0.4013+1.9356-4.0413 + (15.74×1.07+1.8744)-0.8662+1.3375+2.1118-4.5 + (5.85×1.07+0.6948)-0.2903+0.5403+0.8243-1.68 + (7.65×3.642+0.9108)-0.75+1.3932-2.22+2.2927+1.1166-1.5228 + (3.642×3.64+0.444)-1.47+1.3922-1.26+1.2915+0.5228-0.7352 + (12.1×1.07+1.4448)-0.0059+0.1391+1.7006-3.6213 = 92.6237</t>
         </is>
       </c>
-      <c r="F618" s="8" t="n"/>
+      <c r="F618" s="9" t="n"/>
     </row>
     <row r="619" ht="18" customHeight="1">
       <c r="A619" s="3" t="n"/>
@@ -13180,7 +13322,9 @@
           <t>161.8592 + 171.6845 + 171.6845 + 172.4933 + 92.6237 = 770.3452 ≈ 770.35</t>
         </is>
       </c>
-      <c r="F619" s="8" t="n"/>
+      <c r="F619" s="8" t="n">
+        <v>770.35</v>
+      </c>
     </row>
     <row r="620" ht="32" customHeight="1">
       <c r="A620" s="3" t="n">
@@ -13228,7 +13372,7 @@
           <t>3.165×1.5-0.2475+0.2242-1.53-0.48+1.2 + [1.5×1.455-0.24+0.2205-0.7122+0.7122]×2 + 3.165×1.5-0.315 = 12.6727</t>
         </is>
       </c>
-      <c r="F621" s="8" t="n"/>
+      <c r="F621" s="9" t="n"/>
     </row>
     <row r="622" ht="32" customHeight="1">
       <c r="A622" s="3" t="n"/>
@@ -13248,7 +13392,7 @@
           <t>46.3392-3.1814+4.8397-3.66-5.3027+5.2265 + (3.6×3.16+41.3344)-3.5734+5.486-15.12-3.617+4.337 + 46.8969-4.994+6.5147-3.66-5.5729+5.5078-0.11-0.4277 + 15.26×3.51-1.7901+1.696-22.56-4.5725+4.495 + 20.9313-3.47+4.6402-2.5926+2.5926 + 5.85×3.5-3.4125+4.5985-2.1938+2.1313 = 203.1701</t>
         </is>
       </c>
-      <c r="F622" s="8" t="n"/>
+      <c r="F622" s="9" t="n"/>
     </row>
     <row r="623" ht="32" customHeight="1">
       <c r="A623" s="3" t="n"/>
@@ -13268,7 +13412,7 @@
           <t>20.9313-3.47+4.6402-2.5926+2.5926 + 5.85×3.5-3.4125+4.5985-2.1938+2.1313 + 15.26×3.51-1.7901+1.696-22.56-4.5725+4.495 + 46.8969-4.994+6.5147-3.66-5.5729+5.5078-0.11-0.4277 + (3.6×3.16+41.3344)-3.5734+5.486-15.12-3.617+4.337 + 46.3392-3.1814+4.8397-3.66-5.3027+5.2265 = 203.1701</t>
         </is>
       </c>
-      <c r="F623" s="8" t="n"/>
+      <c r="F623" s="9" t="n"/>
     </row>
     <row r="624" ht="32" customHeight="1">
       <c r="A624" s="3" t="n"/>
@@ -13288,7 +13432,7 @@
           <t>20.9313-3.47+4.6402-2.5926+2.5926 + 20.528-3.428+4.5985-2.2313+2.1187 + 15.26×3.6-1.836+1.696-22.56-5.9+4.35 + 47.0211-5.0058+6.5137-3.66-5.6854+5.4953-0.11-0.4277 + (3.6×3.16+11.86×3.6)-3.672+5.5-13.59-5.6+4.5 + 46.374-3.201+4.8307-3.66-5.318+5.083 = 203.8336</t>
         </is>
       </c>
-      <c r="F624" s="8" t="n"/>
+      <c r="F624" s="9" t="n"/>
     </row>
     <row r="625" ht="18" customHeight="1">
       <c r="A625" s="3" t="n"/>
@@ -13308,7 +13452,7 @@
           <t>3.16×3-0.03+0.029-0.315 + 21.542-0.0295+0.029-0.0525 + 3.16×2.9-0.029+0.0278 + 21.542-0.0295+0.029-3.15-0.4937+0.4937-0.0525 = 58.1547</t>
         </is>
       </c>
-      <c r="F625" s="8" t="n"/>
+      <c r="F625" s="9" t="n"/>
     </row>
     <row r="626" ht="32" customHeight="1">
       <c r="A626" s="3" t="n"/>
@@ -13328,7 +13472,7 @@
           <t>(27.6045+0.9108)-0.4932+1.2343-3.15-2.3188+2.194 + (5.61×(1.07+0.12))-0.0107+0.0107 + (15.26×(1.07+0.12))-0.3082+0.2889 + (13.26×(1.07+0.12))-0.0053+0.0053 + (12.563+0.4152)-0.8532+1.272-0.945+0.9765 + (11.86×(1.07+0.12))-0.0053+0.0053 = 94.1189</t>
         </is>
       </c>
-      <c r="F626" s="8" t="n"/>
+      <c r="F626" s="9" t="n"/>
     </row>
     <row r="627" ht="18" customHeight="1">
       <c r="A627" s="3" t="n"/>
@@ -13344,7 +13488,9 @@
           <t>187.5849 + 12.6727 + 203.1701 + 203.1701 + 203.8336 + 58.1547 + 94.1189 = 962.705 ≈ 962.71</t>
         </is>
       </c>
-      <c r="F627" s="8" t="n"/>
+      <c r="F627" s="8" t="n">
+        <v>962.71</v>
+      </c>
     </row>
     <row r="628" ht="18" customHeight="1">
       <c r="A628" s="3" t="n">
@@ -13392,7 +13538,7 @@
           <t>(3×2.28)+2.7827+0.0141-0.9137-0.0137 + (15.26×1.38)+10.9493+0.0863-2.8487-0.085 + (4.33×3.15)+5.1219+0.0144-1.445-0.0145 + (5.73×2.28+8.73×2.05+11.88×4.45)+26.639+0.0678-7.4369-0.07 + (1.68×0.12+3.16×1.8)+4.661+0.0081-0.9994-0.0077 + (6.48×4.35+3.2×1.68+5.85×3.08)+21.8681+0.059-5.4175-0.062 = 235.7941</t>
         </is>
       </c>
-      <c r="F629" s="8" t="n"/>
+      <c r="F629" s="9" t="n"/>
     </row>
     <row r="630" ht="32" customHeight="1">
       <c r="A630" s="3" t="n"/>
@@ -13412,7 +13558,7 @@
           <t>(8.78×5.73+6.5×3+4.45×3.15)+26.639+0.0678-7.4369-0.07 + (4.33×3.15)+5.1219+0.0144-1.445-0.0145 + (15.26×1.38)+10.9492+0.0863-2.8487-0.085 + (3×2.28)+2.7827+0.0141-0.9137-0.0137 + (6.48×4.35+3.2×1.68+5.85×3.08)+21.8681+0.059-5.4175-0.062 + (1.68×0.12+3.16×1.8)+4.661+0.0081-0.9994-0.0077 = 235.7941</t>
         </is>
       </c>
-      <c r="F630" s="8" t="n"/>
+      <c r="F630" s="9" t="n"/>
     </row>
     <row r="631" ht="18" customHeight="1">
       <c r="A631" s="3" t="n"/>
@@ -13432,7 +13578,7 @@
           <t>77.2942+18.6475+0.1879-9.1212-0.1917 + (11.35×8.78)+30.8617+0.0536-8.4587-0.0542 + (1.68×0.12+3.16×1.8)+5.8422+0.0081-0.9994-0.0077 = 219.6049</t>
         </is>
       </c>
-      <c r="F631" s="8" t="n"/>
+      <c r="F631" s="9" t="n"/>
     </row>
     <row r="632" ht="18" customHeight="1">
       <c r="A632" s="3" t="n"/>
@@ -13452,7 +13598,7 @@
           <t>(7.41×3.16)+2.686+0.0099-0.79-0.0099 = 25.3116</t>
         </is>
       </c>
-      <c r="F632" s="8" t="n"/>
+      <c r="F632" s="9" t="n"/>
     </row>
     <row r="633" ht="18" customHeight="1">
       <c r="A633" s="3" t="n"/>
@@ -13468,222 +13614,204 @@
           <t>192.2586 + 235.7941 + 235.7941 + 219.6049 + 25.3116 = 908.7633 ≈ 908.76</t>
         </is>
       </c>
-      <c r="F633" s="8" t="n"/>
+      <c r="F633" s="8" t="n">
+        <v>908.76</v>
+      </c>
     </row>
   </sheetData>
-  <mergeCells count="214">
+  <mergeCells count="194">
     <mergeCell ref="A223:A269"/>
+    <mergeCell ref="F374:F391"/>
     <mergeCell ref="B374:B392"/>
     <mergeCell ref="B571:B572"/>
     <mergeCell ref="A144:A146"/>
-    <mergeCell ref="F109:F122"/>
     <mergeCell ref="B529:B533"/>
-    <mergeCell ref="F574:F575"/>
-    <mergeCell ref="F578:F583"/>
-    <mergeCell ref="F3:F4"/>
+    <mergeCell ref="F196:F199"/>
     <mergeCell ref="A7:A8"/>
-    <mergeCell ref="F584:F585"/>
-    <mergeCell ref="F571:F572"/>
+    <mergeCell ref="F537:F538"/>
     <mergeCell ref="B123:B125"/>
     <mergeCell ref="B23:B24"/>
     <mergeCell ref="A27:A28"/>
-    <mergeCell ref="F521:F522"/>
     <mergeCell ref="B299:B322"/>
+    <mergeCell ref="F147:F156"/>
+    <mergeCell ref="F144:F145"/>
     <mergeCell ref="B463:B467"/>
-    <mergeCell ref="F58:F108"/>
     <mergeCell ref="A534:A536"/>
     <mergeCell ref="A123:A125"/>
     <mergeCell ref="B126:B130"/>
-    <mergeCell ref="F184:F194"/>
-    <mergeCell ref="F270:F298"/>
+    <mergeCell ref="F126:F129"/>
     <mergeCell ref="A393:A414"/>
-    <mergeCell ref="F169:F183"/>
+    <mergeCell ref="F458:F461"/>
+    <mergeCell ref="F29:F31"/>
     <mergeCell ref="B29:B32"/>
     <mergeCell ref="A620:A627"/>
-    <mergeCell ref="F483:F495"/>
     <mergeCell ref="A217:A222"/>
     <mergeCell ref="B540:B541"/>
-    <mergeCell ref="F523:F528"/>
     <mergeCell ref="B421:B441"/>
     <mergeCell ref="A442:A451"/>
     <mergeCell ref="B496:B508"/>
     <mergeCell ref="B458:B462"/>
-    <mergeCell ref="F11:F15"/>
     <mergeCell ref="A586:A591"/>
-    <mergeCell ref="F196:F200"/>
     <mergeCell ref="A323:A333"/>
-    <mergeCell ref="F548:F568"/>
     <mergeCell ref="A544:A547"/>
-    <mergeCell ref="F223:F269"/>
-    <mergeCell ref="F201:F216"/>
     <mergeCell ref="A473:A477"/>
-    <mergeCell ref="F144:F146"/>
+    <mergeCell ref="F614:F618"/>
     <mergeCell ref="B614:B619"/>
     <mergeCell ref="A165:A168"/>
     <mergeCell ref="A16:A20"/>
-    <mergeCell ref="F33:F57"/>
     <mergeCell ref="A334:A373"/>
-    <mergeCell ref="F334:F373"/>
     <mergeCell ref="B25:B26"/>
+    <mergeCell ref="F323:F332"/>
     <mergeCell ref="A463:A467"/>
-    <mergeCell ref="F569:F570"/>
-    <mergeCell ref="F458:F462"/>
-    <mergeCell ref="F7:F8"/>
     <mergeCell ref="A584:A585"/>
     <mergeCell ref="A540:A541"/>
-    <mergeCell ref="F598:F605"/>
     <mergeCell ref="B131:B143"/>
-    <mergeCell ref="F452:F457"/>
     <mergeCell ref="B27:B28"/>
     <mergeCell ref="B162:B164"/>
+    <mergeCell ref="F162:F163"/>
     <mergeCell ref="B509:B510"/>
+    <mergeCell ref="F544:F546"/>
     <mergeCell ref="B3:B4"/>
     <mergeCell ref="A608:A613"/>
-    <mergeCell ref="F534:F536"/>
+    <mergeCell ref="F16:F19"/>
     <mergeCell ref="A169:A183"/>
-    <mergeCell ref="F393:F414"/>
-    <mergeCell ref="F5:F6"/>
-    <mergeCell ref="F217:F222"/>
+    <mergeCell ref="F463:F466"/>
     <mergeCell ref="A628:A633"/>
     <mergeCell ref="A452:A457"/>
     <mergeCell ref="A158:A159"/>
+    <mergeCell ref="F478:F481"/>
+    <mergeCell ref="B478:B482"/>
     <mergeCell ref="A523:A528"/>
-    <mergeCell ref="B478:B482"/>
     <mergeCell ref="B442:B451"/>
     <mergeCell ref="B270:B298"/>
     <mergeCell ref="B592:B597"/>
-    <mergeCell ref="F442:F451"/>
     <mergeCell ref="A511:A520"/>
     <mergeCell ref="A574:A575"/>
-    <mergeCell ref="F415:F420"/>
-    <mergeCell ref="F586:F591"/>
-    <mergeCell ref="F323:F333"/>
+    <mergeCell ref="F608:F612"/>
+    <mergeCell ref="F299:F321"/>
+    <mergeCell ref="F529:F532"/>
     <mergeCell ref="A21:A22"/>
     <mergeCell ref="B523:B528"/>
     <mergeCell ref="B537:B539"/>
-    <mergeCell ref="F592:F597"/>
+    <mergeCell ref="F628:F632"/>
     <mergeCell ref="A548:A568"/>
     <mergeCell ref="B109:B122"/>
-    <mergeCell ref="F9:F10"/>
     <mergeCell ref="A201:A216"/>
     <mergeCell ref="B473:B477"/>
     <mergeCell ref="A542:A543"/>
     <mergeCell ref="B574:B575"/>
     <mergeCell ref="B578:B583"/>
-    <mergeCell ref="F473:F477"/>
+    <mergeCell ref="F578:F582"/>
     <mergeCell ref="A23:A24"/>
-    <mergeCell ref="F165:F168"/>
+    <mergeCell ref="F184:F193"/>
     <mergeCell ref="A415:A420"/>
+    <mergeCell ref="F511:F519"/>
     <mergeCell ref="A569:A570"/>
-    <mergeCell ref="F463:F467"/>
-    <mergeCell ref="F147:F157"/>
     <mergeCell ref="B628:B633"/>
     <mergeCell ref="B158:B159"/>
     <mergeCell ref="A374:A392"/>
     <mergeCell ref="B223:B269"/>
-    <mergeCell ref="F540:F541"/>
+    <mergeCell ref="F58:F107"/>
     <mergeCell ref="A9:A10"/>
     <mergeCell ref="B58:B108"/>
     <mergeCell ref="B11:B15"/>
+    <mergeCell ref="F131:F142"/>
     <mergeCell ref="B184:B194"/>
     <mergeCell ref="B7:B8"/>
     <mergeCell ref="B169:B183"/>
     <mergeCell ref="B160:B161"/>
+    <mergeCell ref="F169:F182"/>
+    <mergeCell ref="B483:B495"/>
     <mergeCell ref="A521:A522"/>
-    <mergeCell ref="B483:B495"/>
-    <mergeCell ref="F608:F613"/>
     <mergeCell ref="A537:A539"/>
     <mergeCell ref="A496:A508"/>
+    <mergeCell ref="F620:F626"/>
+    <mergeCell ref="F523:F527"/>
     <mergeCell ref="A576:A577"/>
     <mergeCell ref="A126:A130"/>
+    <mergeCell ref="F223:F268"/>
     <mergeCell ref="B534:B536"/>
     <mergeCell ref="A109:A122"/>
-    <mergeCell ref="F511:F520"/>
     <mergeCell ref="B542:B543"/>
     <mergeCell ref="A614:A619"/>
-    <mergeCell ref="F21:F22"/>
-    <mergeCell ref="F123:F125"/>
+    <mergeCell ref="F496:F507"/>
     <mergeCell ref="A571:A572"/>
+    <mergeCell ref="F201:F215"/>
+    <mergeCell ref="B201:B216"/>
     <mergeCell ref="A421:A441"/>
-    <mergeCell ref="B201:B216"/>
     <mergeCell ref="B144:B146"/>
     <mergeCell ref="A529:A533"/>
+    <mergeCell ref="F334:F372"/>
     <mergeCell ref="B334:B373"/>
     <mergeCell ref="B569:B570"/>
-    <mergeCell ref="F468:F472"/>
-    <mergeCell ref="F542:F543"/>
-    <mergeCell ref="F23:F24"/>
+    <mergeCell ref="F109:F121"/>
     <mergeCell ref="A147:A157"/>
-    <mergeCell ref="F620:F627"/>
+    <mergeCell ref="F598:F604"/>
     <mergeCell ref="A483:A495"/>
     <mergeCell ref="B9:B10"/>
-    <mergeCell ref="F606:F607"/>
-    <mergeCell ref="F374:F392"/>
     <mergeCell ref="B544:B547"/>
+    <mergeCell ref="F421:F440"/>
     <mergeCell ref="B393:B414"/>
     <mergeCell ref="A29:A32"/>
     <mergeCell ref="A11:A15"/>
+    <mergeCell ref="F442:F450"/>
     <mergeCell ref="A131:A143"/>
+    <mergeCell ref="F217:F221"/>
+    <mergeCell ref="B217:B222"/>
+    <mergeCell ref="F270:F297"/>
     <mergeCell ref="A458:A462"/>
-    <mergeCell ref="B217:B222"/>
-    <mergeCell ref="F537:F539"/>
-    <mergeCell ref="F544:F547"/>
     <mergeCell ref="A162:A164"/>
-    <mergeCell ref="F496:F508"/>
     <mergeCell ref="A598:A605"/>
+    <mergeCell ref="F483:F494"/>
     <mergeCell ref="A509:A510"/>
-    <mergeCell ref="F16:F20"/>
-    <mergeCell ref="F299:F322"/>
     <mergeCell ref="A1:F1"/>
     <mergeCell ref="B608:B613"/>
-    <mergeCell ref="F126:F130"/>
+    <mergeCell ref="F415:F419"/>
     <mergeCell ref="B586:B591"/>
+    <mergeCell ref="F586:F590"/>
     <mergeCell ref="B323:B333"/>
-    <mergeCell ref="F29:F32"/>
+    <mergeCell ref="F165:F167"/>
     <mergeCell ref="A33:A57"/>
+    <mergeCell ref="F11:F14"/>
     <mergeCell ref="B21:B22"/>
+    <mergeCell ref="F592:F596"/>
     <mergeCell ref="A478:A482"/>
-    <mergeCell ref="F25:F26"/>
-    <mergeCell ref="F421:F441"/>
+    <mergeCell ref="F473:F476"/>
+    <mergeCell ref="F548:F567"/>
     <mergeCell ref="A468:A472"/>
     <mergeCell ref="B165:B168"/>
     <mergeCell ref="B511:B520"/>
-    <mergeCell ref="F529:F533"/>
     <mergeCell ref="B33:B57"/>
     <mergeCell ref="B147:B157"/>
-    <mergeCell ref="F628:F633"/>
-    <mergeCell ref="F158:F159"/>
     <mergeCell ref="B196:B200"/>
     <mergeCell ref="A606:A607"/>
     <mergeCell ref="A25:A26"/>
     <mergeCell ref="A3:A4"/>
-    <mergeCell ref="F160:F161"/>
-    <mergeCell ref="F614:F619"/>
+    <mergeCell ref="F33:F56"/>
     <mergeCell ref="B16:B20"/>
     <mergeCell ref="B606:B607"/>
     <mergeCell ref="A5:A6"/>
-    <mergeCell ref="F131:F143"/>
     <mergeCell ref="B598:B605"/>
-    <mergeCell ref="F27:F28"/>
-    <mergeCell ref="F162:F164"/>
+    <mergeCell ref="F393:F413"/>
+    <mergeCell ref="F452:F456"/>
+    <mergeCell ref="B452:B457"/>
     <mergeCell ref="A58:A108"/>
-    <mergeCell ref="B452:B457"/>
     <mergeCell ref="B548:B568"/>
     <mergeCell ref="A184:A194"/>
-    <mergeCell ref="F509:F510"/>
     <mergeCell ref="A578:A583"/>
     <mergeCell ref="A270:A298"/>
     <mergeCell ref="A592:A597"/>
     <mergeCell ref="A160:A161"/>
     <mergeCell ref="A299:A322"/>
     <mergeCell ref="B5:B6"/>
+    <mergeCell ref="F534:F535"/>
+    <mergeCell ref="F123:F124"/>
     <mergeCell ref="B576:B577"/>
-    <mergeCell ref="F478:F482"/>
     <mergeCell ref="A196:A200"/>
+    <mergeCell ref="F468:F471"/>
     <mergeCell ref="B468:B472"/>
     <mergeCell ref="B521:B522"/>
     <mergeCell ref="B415:B420"/>
-    <mergeCell ref="F576:F577"/>
     <mergeCell ref="B620:B627"/>
     <mergeCell ref="B584:B585"/>
   </mergeCells>
@@ -13783,7 +13911,7 @@
           <t>m³</t>
         </is>
       </c>
-      <c r="F3" s="11" t="n">
+      <c r="F3" s="13" t="n">
         <v>200.42</v>
       </c>
     </row>
@@ -13812,7 +13940,7 @@
           <t>m³</t>
         </is>
       </c>
-      <c r="F4" s="11" t="n">
+      <c r="F4" s="13" t="n">
         <v>168.3</v>
       </c>
     </row>
@@ -13840,7 +13968,7 @@
           <t>m³</t>
         </is>
       </c>
-      <c r="F5" s="11" t="n">
+      <c r="F5" s="13" t="n">
         <v>192.88</v>
       </c>
     </row>
@@ -13868,7 +13996,7 @@
           <t>m³</t>
         </is>
       </c>
-      <c r="F6" s="11" t="n">
+      <c r="F6" s="13" t="n">
         <v>32.12</v>
       </c>
     </row>
@@ -13899,7 +14027,7 @@
           <t>m³</t>
         </is>
       </c>
-      <c r="F7" s="11" t="n">
+      <c r="F7" s="13" t="n">
         <v>113.02</v>
       </c>
     </row>
@@ -13930,7 +14058,7 @@
           <t>m³</t>
         </is>
       </c>
-      <c r="F8" s="11" t="n">
+      <c r="F8" s="13" t="n">
         <v>16.33</v>
       </c>
     </row>
@@ -13961,7 +14089,7 @@
           <t>m³</t>
         </is>
       </c>
-      <c r="F9" s="11" t="n">
+      <c r="F9" s="13" t="n">
         <v>25.36</v>
       </c>
     </row>
@@ -13991,7 +14119,7 @@
           <t>m³</t>
         </is>
       </c>
-      <c r="F10" s="11" t="n">
+      <c r="F10" s="13" t="n">
         <v>6.83</v>
       </c>
     </row>
@@ -14021,7 +14149,7 @@
           <t>m³</t>
         </is>
       </c>
-      <c r="F11" s="11" t="n">
+      <c r="F11" s="13" t="n">
         <v>17.67</v>
       </c>
     </row>
@@ -14051,7 +14179,7 @@
           <t>m³</t>
         </is>
       </c>
-      <c r="F12" s="11" t="n">
+      <c r="F12" s="13" t="n">
         <v>26.5</v>
       </c>
     </row>
@@ -14081,7 +14209,7 @@
           <t>m³</t>
         </is>
       </c>
-      <c r="F13" s="11" t="n">
+      <c r="F13" s="13" t="n">
         <v>22.71</v>
       </c>
     </row>
@@ -14111,7 +14239,7 @@
           <t>m³</t>
         </is>
       </c>
-      <c r="F14" s="11" t="n">
+      <c r="F14" s="13" t="n">
         <v>35.05</v>
       </c>
     </row>
@@ -14141,7 +14269,7 @@
           <t>m³</t>
         </is>
       </c>
-      <c r="F15" s="11" t="n">
+      <c r="F15" s="13" t="n">
         <v>70.15000000000001</v>
       </c>
     </row>
@@ -14170,7 +14298,7 @@
           <t>m³</t>
         </is>
       </c>
-      <c r="F16" s="11" t="n">
+      <c r="F16" s="13" t="n">
         <v>75.48999999999999</v>
       </c>
     </row>
@@ -14200,7 +14328,7 @@
           <t>m³</t>
         </is>
       </c>
-      <c r="F17" s="11" t="n">
+      <c r="F17" s="13" t="n">
         <v>0.38</v>
       </c>
     </row>
@@ -14230,7 +14358,7 @@
           <t>m³</t>
         </is>
       </c>
-      <c r="F18" s="11" t="n">
+      <c r="F18" s="13" t="n">
         <v>11.14</v>
       </c>
     </row>
@@ -14259,7 +14387,7 @@
           <t>m³</t>
         </is>
       </c>
-      <c r="F19" s="11" t="n">
+      <c r="F19" s="13" t="n">
         <v>6.9</v>
       </c>
     </row>
@@ -14289,7 +14417,7 @@
           <t>m³</t>
         </is>
       </c>
-      <c r="F20" s="11" t="n">
+      <c r="F20" s="13" t="n">
         <v>1.42</v>
       </c>
     </row>
@@ -14318,7 +14446,7 @@
           <t>m³</t>
         </is>
       </c>
-      <c r="F21" s="11" t="n">
+      <c r="F21" s="13" t="n">
         <v>2.37</v>
       </c>
     </row>
@@ -14347,7 +14475,7 @@
           <t>㎡</t>
         </is>
       </c>
-      <c r="F22" s="11" t="n">
+      <c r="F22" s="13" t="n">
         <v>31.76</v>
       </c>
     </row>
@@ -14376,7 +14504,7 @@
           <t>㎡</t>
         </is>
       </c>
-      <c r="F23" s="11" t="n">
+      <c r="F23" s="13" t="n">
         <v>7.64</v>
       </c>
     </row>
@@ -14406,7 +14534,7 @@
           <t>m³</t>
         </is>
       </c>
-      <c r="F24" s="11" t="n">
+      <c r="F24" s="13" t="n">
         <v>2.78</v>
       </c>
     </row>
@@ -14434,7 +14562,7 @@
           <t>t</t>
         </is>
       </c>
-      <c r="F25" s="12" t="n">
+      <c r="F25" s="14" t="n">
         <v>0.709</v>
       </c>
     </row>
@@ -14462,7 +14590,7 @@
           <t>t</t>
         </is>
       </c>
-      <c r="F26" s="12" t="n">
+      <c r="F26" s="14" t="n">
         <v>0.492</v>
       </c>
     </row>
@@ -14490,7 +14618,7 @@
           <t>t</t>
         </is>
       </c>
-      <c r="F27" s="12" t="n">
+      <c r="F27" s="14" t="n">
         <v>0.175</v>
       </c>
     </row>
@@ -14518,7 +14646,7 @@
           <t>t</t>
         </is>
       </c>
-      <c r="F28" s="12" t="n">
+      <c r="F28" s="14" t="n">
         <v>0</v>
       </c>
     </row>
@@ -14546,7 +14674,7 @@
           <t>t</t>
         </is>
       </c>
-      <c r="F29" s="12" t="n">
+      <c r="F29" s="14" t="n">
         <v>0.345</v>
       </c>
     </row>
@@ -14574,7 +14702,7 @@
           <t>t</t>
         </is>
       </c>
-      <c r="F30" s="12" t="n">
+      <c r="F30" s="14" t="n">
         <v>2.989</v>
       </c>
     </row>
@@ -14602,7 +14730,7 @@
           <t>t</t>
         </is>
       </c>
-      <c r="F31" s="12" t="n">
+      <c r="F31" s="14" t="n">
         <v>0.968</v>
       </c>
     </row>
@@ -14630,7 +14758,7 @@
           <t>t</t>
         </is>
       </c>
-      <c r="F32" s="12" t="n">
+      <c r="F32" s="14" t="n">
         <v>0.307</v>
       </c>
     </row>
@@ -14658,7 +14786,7 @@
           <t>t</t>
         </is>
       </c>
-      <c r="F33" s="12" t="n">
+      <c r="F33" s="14" t="n">
         <v>1.428</v>
       </c>
     </row>
@@ -14686,7 +14814,7 @@
           <t>t</t>
         </is>
       </c>
-      <c r="F34" s="12" t="n">
+      <c r="F34" s="14" t="n">
         <v>0.717</v>
       </c>
     </row>
@@ -14714,7 +14842,7 @@
           <t>t</t>
         </is>
       </c>
-      <c r="F35" s="12" t="n">
+      <c r="F35" s="14" t="n">
         <v>0.134</v>
       </c>
     </row>
@@ -14742,7 +14870,7 @@
           <t>t</t>
         </is>
       </c>
-      <c r="F36" s="12" t="n">
+      <c r="F36" s="14" t="n">
         <v>2.347</v>
       </c>
     </row>
@@ -14770,7 +14898,7 @@
           <t>t</t>
         </is>
       </c>
-      <c r="F37" s="12" t="n">
+      <c r="F37" s="14" t="n">
         <v>2.172</v>
       </c>
     </row>
@@ -14798,7 +14926,7 @@
           <t>t</t>
         </is>
       </c>
-      <c r="F38" s="12" t="n">
+      <c r="F38" s="14" t="n">
         <v>2.778</v>
       </c>
     </row>
@@ -14826,7 +14954,7 @@
           <t>t</t>
         </is>
       </c>
-      <c r="F39" s="12" t="n">
+      <c r="F39" s="14" t="n">
         <v>0.319</v>
       </c>
     </row>
@@ -14854,7 +14982,7 @@
           <t>t</t>
         </is>
       </c>
-      <c r="F40" s="12" t="n">
+      <c r="F40" s="14" t="n">
         <v>1.029</v>
       </c>
     </row>
@@ -14882,7 +15010,7 @@
           <t>t</t>
         </is>
       </c>
-      <c r="F41" s="12" t="n">
+      <c r="F41" s="14" t="n">
         <v>2.37</v>
       </c>
     </row>
@@ -14910,7 +15038,7 @@
           <t>t</t>
         </is>
       </c>
-      <c r="F42" s="12" t="n">
+      <c r="F42" s="14" t="n">
         <v>2.808</v>
       </c>
     </row>
@@ -14938,7 +15066,7 @@
           <t>t</t>
         </is>
       </c>
-      <c r="F43" s="12" t="n">
+      <c r="F43" s="14" t="n">
         <v>6.289</v>
       </c>
     </row>
@@ -14966,7 +15094,7 @@
           <t>t</t>
         </is>
       </c>
-      <c r="F44" s="12" t="n">
+      <c r="F44" s="14" t="n">
         <v>0.089</v>
       </c>
     </row>
@@ -14994,7 +15122,7 @@
           <t>t</t>
         </is>
       </c>
-      <c r="F45" s="12" t="n">
+      <c r="F45" s="14" t="n">
         <v>0.209</v>
       </c>
     </row>
@@ -15022,7 +15150,7 @@
           <t>t</t>
         </is>
       </c>
-      <c r="F46" s="12" t="n">
+      <c r="F46" s="14" t="n">
         <v>0.417</v>
       </c>
     </row>
@@ -15050,7 +15178,7 @@
           <t>t</t>
         </is>
       </c>
-      <c r="F47" s="12" t="n">
+      <c r="F47" s="14" t="n">
         <v>0.266</v>
       </c>
     </row>
@@ -15079,7 +15207,7 @@
           <t>t</t>
         </is>
       </c>
-      <c r="F48" s="12" t="n">
+      <c r="F48" s="14" t="n">
         <v>0.08799999999999999</v>
       </c>
     </row>
@@ -15108,7 +15236,7 @@
           <t>t</t>
         </is>
       </c>
-      <c r="F49" s="12" t="n">
+      <c r="F49" s="14" t="n">
         <v>0.357</v>
       </c>
     </row>
@@ -15137,7 +15265,7 @@
           <t>t</t>
         </is>
       </c>
-      <c r="F50" s="12" t="n">
+      <c r="F50" s="14" t="n">
         <v>0</v>
       </c>
     </row>
@@ -15166,7 +15294,7 @@
           <t>t</t>
         </is>
       </c>
-      <c r="F51" s="12" t="n">
+      <c r="F51" s="14" t="n">
         <v>0.044</v>
       </c>
     </row>
@@ -15195,7 +15323,7 @@
           <t>t</t>
         </is>
       </c>
-      <c r="F52" s="12" t="n">
+      <c r="F52" s="14" t="n">
         <v>0.001</v>
       </c>
     </row>
@@ -15224,7 +15352,7 @@
           <t>t</t>
         </is>
       </c>
-      <c r="F53" s="12" t="n">
+      <c r="F53" s="14" t="n">
         <v>0.077</v>
       </c>
     </row>
@@ -15253,7 +15381,7 @@
           <t>t</t>
         </is>
       </c>
-      <c r="F54" s="12" t="n">
+      <c r="F54" s="14" t="n">
         <v>0.146</v>
       </c>
     </row>
@@ -15282,7 +15410,7 @@
           <t>t</t>
         </is>
       </c>
-      <c r="F55" s="12" t="n">
+      <c r="F55" s="14" t="n">
         <v>0.021</v>
       </c>
     </row>
@@ -15311,7 +15439,7 @@
           <t>t</t>
         </is>
       </c>
-      <c r="F56" s="12" t="n">
+      <c r="F56" s="14" t="n">
         <v>0.08400000000000001</v>
       </c>
     </row>
@@ -15340,7 +15468,7 @@
           <t>t</t>
         </is>
       </c>
-      <c r="F57" s="12" t="n">
+      <c r="F57" s="14" t="n">
         <v>0.006</v>
       </c>
     </row>
@@ -15369,7 +15497,7 @@
           <t>t</t>
         </is>
       </c>
-      <c r="F58" s="12" t="n">
+      <c r="F58" s="14" t="n">
         <v>0.263</v>
       </c>
     </row>
@@ -15401,7 +15529,7 @@
           <t>㎡</t>
         </is>
       </c>
-      <c r="F59" s="11" t="n">
+      <c r="F59" s="13" t="n">
         <v>13.83</v>
       </c>
     </row>
@@ -15437,7 +15565,7 @@
           <t>㎡</t>
         </is>
       </c>
-      <c r="F60" s="11" t="n">
+      <c r="F60" s="13" t="n">
         <v>164.64</v>
       </c>
     </row>
@@ -15467,7 +15595,7 @@
           <t>㎡</t>
         </is>
       </c>
-      <c r="F61" s="11" t="n">
+      <c r="F61" s="13" t="n">
         <v>219.3</v>
       </c>
     </row>
@@ -15496,7 +15624,7 @@
           <t>㎡</t>
         </is>
       </c>
-      <c r="F62" s="11" t="n">
+      <c r="F62" s="13" t="n">
         <v>200.13</v>
       </c>
     </row>
@@ -15555,7 +15683,7 @@
           <t>㎡</t>
         </is>
       </c>
-      <c r="F64" s="11" t="n">
+      <c r="F64" s="13" t="n">
         <v>4.58</v>
       </c>
     </row>
@@ -15586,7 +15714,7 @@
           <t>㎡</t>
         </is>
       </c>
-      <c r="F65" s="11" t="n">
+      <c r="F65" s="13" t="n">
         <v>200.13</v>
       </c>
     </row>
@@ -15616,7 +15744,7 @@
           <t>㎡</t>
         </is>
       </c>
-      <c r="F66" s="11" t="n">
+      <c r="F66" s="13" t="n">
         <v>796.17</v>
       </c>
     </row>
@@ -15646,7 +15774,7 @@
           <t>㎡</t>
         </is>
       </c>
-      <c r="F67" s="11" t="n">
+      <c r="F67" s="13" t="n">
         <v>4.58</v>
       </c>
     </row>
@@ -15676,7 +15804,7 @@
           <t>m</t>
         </is>
       </c>
-      <c r="F68" s="11" t="n">
+      <c r="F68" s="13" t="n">
         <v>264.13</v>
       </c>
     </row>
@@ -15706,7 +15834,7 @@
           <t>㎡</t>
         </is>
       </c>
-      <c r="F69" s="11" t="n">
+      <c r="F69" s="13" t="n">
         <v>770.35</v>
       </c>
     </row>
@@ -15736,7 +15864,7 @@
           <t>㎡</t>
         </is>
       </c>
-      <c r="F70" s="11" t="n">
+      <c r="F70" s="13" t="n">
         <v>962.71</v>
       </c>
     </row>
@@ -15769,7 +15897,7 @@
           <t>㎡</t>
         </is>
       </c>
-      <c r="F71" s="11" t="n">
+      <c r="F71" s="13" t="n">
         <v>16.88</v>
       </c>
     </row>
@@ -15799,7 +15927,7 @@
           <t>㎡</t>
         </is>
       </c>
-      <c r="F72" s="11" t="n">
+      <c r="F72" s="13" t="n">
         <v>908.76</v>
       </c>
     </row>
@@ -15829,7 +15957,7 @@
           <t>㎡</t>
         </is>
       </c>
-      <c r="F73" s="11" t="n">
+      <c r="F73" s="13" t="n">
         <v>770.35</v>
       </c>
     </row>
@@ -15859,7 +15987,7 @@
           <t>㎡</t>
         </is>
       </c>
-      <c r="F74" s="11" t="n">
+      <c r="F74" s="13" t="n">
         <v>962.71</v>
       </c>
     </row>
@@ -15890,7 +16018,7 @@
           <t>㎡</t>
         </is>
       </c>
-      <c r="F75" s="11" t="n">
+      <c r="F75" s="13" t="n">
         <v>908.76</v>
       </c>
     </row>
@@ -15927,541 +16055,541 @@
   </cols>
   <sheetData>
     <row r="1">
-      <c r="A1" s="13" t="inlineStr">
+      <c r="A1" s="15" t="inlineStr">
         <is>
           <t>编制说明</t>
         </is>
       </c>
     </row>
     <row r="2">
-      <c r="A2" s="14" t="inlineStr">
+      <c r="A2" s="16" t="inlineStr">
         <is>
           <t>总体</t>
         </is>
       </c>
-      <c r="B2" s="14" t="n"/>
-      <c r="C2" s="14" t="inlineStr">
+      <c r="B2" s="16" t="n"/>
+      <c r="C2" s="16" t="inlineStr">
         <is>
           <t>数据来源：①广联达《绘图输入构件工程量计算书》（基础层~第5层）；②广联达《钢筋明细表》；③清单模板（74 项）。</t>
         </is>
       </c>
     </row>
     <row r="3">
-      <c r="A3" s="14" t="inlineStr">
+      <c r="A3" s="16" t="inlineStr">
         <is>
           <t>总体</t>
         </is>
       </c>
-      <c r="B3" s="14" t="n"/>
-      <c r="C3" s="14" t="inlineStr">
+      <c r="B3" s="16" t="n"/>
+      <c r="C3" s="16" t="inlineStr">
         <is>
           <t>计算书粒度：每层每个构件编号一行，同编号下计算式相同的图元合并为 [计算式]×n；每个清单项末行为小计。</t>
         </is>
       </c>
     </row>
     <row r="4">
-      <c r="A4" s="14" t="inlineStr">
+      <c r="A4" s="16" t="inlineStr">
         <is>
           <t>总体</t>
         </is>
       </c>
-      <c r="B4" s="14" t="n"/>
-      <c r="C4" s="14" t="inlineStr">
+      <c r="B4" s="16" t="n"/>
+      <c r="C4" s="16" t="inlineStr">
         <is>
           <t>计算式已去掉广联达的尖括号注释，仅保留数值式；各图元结果取广联达原值（4 位小数），清单工程量 m³/㎡/m 取 2 位小数，钢筋 t 取 3 位小数。</t>
         </is>
       </c>
     </row>
     <row r="5">
-      <c r="A5" s="14" t="inlineStr">
+      <c r="A5" s="16" t="inlineStr">
         <is>
           <t>总体</t>
         </is>
       </c>
-      <c r="B5" s="14" t="n"/>
-      <c r="C5" s="14" t="inlineStr">
+      <c r="B5" s="16" t="n"/>
+      <c r="C5" s="16" t="inlineStr">
         <is>
           <t>钢筋明细表导出的“级别”列为空，钢筋级别按清单模板“构件类型+直径→级别”对应关系归类；直径 12/14 过梁钢筋按模板标注 HPB300 保留。</t>
         </is>
       </c>
     </row>
     <row r="6">
-      <c r="A6" s="14" t="inlineStr">
+      <c r="A6" s="16" t="inlineStr">
         <is>
           <t>总体</t>
         </is>
       </c>
-      <c r="B6" s="14" t="n"/>
-      <c r="C6" s="14" t="inlineStr">
+      <c r="B6" s="16" t="n"/>
+      <c r="C6" s="16" t="inlineStr">
         <is>
           <t>钢筋校核：钢筋明细表总重 30182.028kg，已全部分配到各钢筋清单项（不含估算的屋面钢筋网片），分配合计 30182.028kg。</t>
         </is>
       </c>
     </row>
     <row r="7">
-      <c r="A7" s="14" t="inlineStr">
+      <c r="A7" s="16" t="inlineStr">
         <is>
           <t>总体</t>
         </is>
       </c>
-      <c r="B7" s="14" t="n"/>
-      <c r="C7" s="14" t="inlineStr">
+      <c r="B7" s="16" t="n"/>
+      <c r="C7" s="16" t="inlineStr">
         <is>
           <t>标注“需补充”的项目在计算书/钢筋表中无依据，需按图纸另行计算。</t>
         </is>
       </c>
     </row>
     <row r="8">
-      <c r="A8" s="14" t="n"/>
-      <c r="B8" s="14" t="n"/>
-      <c r="C8" s="14" t="n"/>
+      <c r="A8" s="16" t="n"/>
+      <c r="B8" s="16" t="n"/>
+      <c r="C8" s="16" t="n"/>
     </row>
     <row r="9">
-      <c r="A9" s="15" t="inlineStr">
+      <c r="A9" s="17" t="inlineStr">
         <is>
           <t>项目编码</t>
         </is>
       </c>
-      <c r="B9" s="15" t="inlineStr">
+      <c r="B9" s="17" t="inlineStr">
         <is>
           <t>项目名称</t>
         </is>
       </c>
-      <c r="C9" s="15" t="inlineStr">
+      <c r="C9" s="17" t="inlineStr">
         <is>
           <t>说明</t>
         </is>
       </c>
     </row>
     <row r="10">
-      <c r="A10" s="14" t="inlineStr">
+      <c r="A10" s="16" t="inlineStr">
         <is>
           <t>010102007001</t>
         </is>
       </c>
-      <c r="B10" s="14" t="inlineStr">
+      <c r="B10" s="16" t="inlineStr">
         <is>
           <t>回填方</t>
         </is>
       </c>
-      <c r="C10" s="14" t="inlineStr">
+      <c r="C10" s="16" t="inlineStr">
         <is>
           <t>按广联达大开挖土方的“素土回填体积”（基坑回填）汇总；房心回填未含。</t>
         </is>
       </c>
     </row>
     <row r="11">
-      <c r="A11" s="14" t="inlineStr">
+      <c r="A11" s="16" t="inlineStr">
         <is>
           <t>010103001001</t>
         </is>
       </c>
-      <c r="B11" s="14" t="inlineStr">
+      <c r="B11" s="16" t="inlineStr">
         <is>
           <t>平整场地</t>
         </is>
       </c>
-      <c r="C11" s="14" t="inlineStr">
+      <c r="C11" s="16" t="inlineStr">
         <is>
           <t>计算书中无平整场地构件，按首层建筑面积计取；清单模板单位为 m³，规范应为 m²，请核对。</t>
         </is>
       </c>
     </row>
     <row r="12">
-      <c r="A12" s="14" t="inlineStr">
+      <c r="A12" s="16" t="inlineStr">
         <is>
           <t>010103002001</t>
         </is>
       </c>
-      <c r="B12" s="14" t="inlineStr">
+      <c r="B12" s="16" t="inlineStr">
         <is>
           <t>余方弃置</t>
         </is>
       </c>
-      <c r="C12" s="14" t="inlineStr">
+      <c r="C12" s="16" t="inlineStr">
         <is>
           <t>余方弃置 = 挖方总量 − 基坑回填总量（推导值）。</t>
         </is>
       </c>
     </row>
     <row r="13">
-      <c r="A13" s="14" t="inlineStr">
+      <c r="A13" s="16" t="inlineStr">
         <is>
           <t>010501002001</t>
         </is>
       </c>
-      <c r="B13" s="14" t="inlineStr">
+      <c r="B13" s="16" t="inlineStr">
         <is>
           <t>楼地面垫层</t>
         </is>
       </c>
-      <c r="C13" s="14" t="inlineStr">
+      <c r="C13" s="16" t="inlineStr">
         <is>
           <t>计算书中无楼地面垫层构件，按首层各房间地面积×0.10m 推导。</t>
         </is>
       </c>
     </row>
     <row r="14">
-      <c r="A14" s="14" t="inlineStr">
+      <c r="A14" s="16" t="inlineStr">
         <is>
           <t>010501002002</t>
         </is>
       </c>
-      <c r="B14" s="14" t="inlineStr">
+      <c r="B14" s="16" t="inlineStr">
         <is>
           <t>楼地面垫层</t>
         </is>
       </c>
-      <c r="C14" s="14" t="inlineStr">
+      <c r="C14" s="16" t="inlineStr">
         <is>
           <t>计算书中无楼地面垫层构件，按首层各房间地面积×0.15m 推导。</t>
         </is>
       </c>
     </row>
     <row r="15">
-      <c r="A15" s="14" t="inlineStr">
+      <c r="A15" s="16" t="inlineStr">
         <is>
           <t>010502006001</t>
         </is>
       </c>
-      <c r="B15" s="14" t="inlineStr">
+      <c r="B15" s="16" t="inlineStr">
         <is>
           <t>钢筋混凝土柱</t>
         </is>
       </c>
-      <c r="C15" s="14" t="inlineStr">
+      <c r="C15" s="16" t="inlineStr">
         <is>
           <t>含各层框架柱 1KZ1~1KZ4 及梯柱 TZ；基础层柱为基础顶至±0.000 段。</t>
         </is>
       </c>
     </row>
     <row r="16">
-      <c r="A16" s="14" t="inlineStr">
+      <c r="A16" s="16" t="inlineStr">
         <is>
           <t>010502011001</t>
         </is>
       </c>
-      <c r="B16" s="14" t="inlineStr">
+      <c r="B16" s="16" t="inlineStr">
         <is>
           <t>钢筋混凝土梁</t>
         </is>
       </c>
-      <c r="C16" s="14" t="inlineStr">
+      <c r="C16" s="16" t="inlineStr">
         <is>
           <t>含基础梁 DKL/DL、各层框架梁 KL/WKL、次梁 L/WL；雨棚梁 YPL 计入“其他板(雨棚板)”。</t>
         </is>
       </c>
     </row>
     <row r="17">
-      <c r="A17" s="14" t="inlineStr">
+      <c r="A17" s="16" t="inlineStr">
         <is>
           <t>010502019001</t>
         </is>
       </c>
-      <c r="B17" s="14" t="inlineStr">
+      <c r="B17" s="16" t="inlineStr">
         <is>
           <t>其他板</t>
         </is>
       </c>
-      <c r="C17" s="14" t="inlineStr">
+      <c r="C17" s="16" t="inlineStr">
         <is>
           <t>广联达模型中未绘制雨棚板本体，仅有雨棚梁 YPL 与雨棚栏板 YP，此处为两者体积之和；雨棚板本体需补充。</t>
         </is>
       </c>
     </row>
     <row r="18">
-      <c r="A18" s="14" t="inlineStr">
+      <c r="A18" s="16" t="inlineStr">
         <is>
           <t>010502020001</t>
         </is>
       </c>
-      <c r="B18" s="14" t="inlineStr">
+      <c r="B18" s="16" t="inlineStr">
         <is>
           <t>楼梯</t>
         </is>
       </c>
-      <c r="C18" s="14" t="inlineStr">
+      <c r="C18" s="16" t="inlineStr">
         <is>
           <t>楼梯按广联达“梯段+梯梁+平台板”体积汇总（清单模板单位为 m³）。</t>
         </is>
       </c>
     </row>
     <row r="19">
-      <c r="A19" s="14" t="inlineStr">
+      <c r="A19" s="16" t="inlineStr">
         <is>
           <t>010506001001</t>
         </is>
       </c>
-      <c r="B19" s="14" t="inlineStr">
+      <c r="B19" s="16" t="inlineStr">
         <is>
           <t>现浇混凝土基础及联系梁钢筋</t>
         </is>
       </c>
-      <c r="C19" s="14" t="inlineStr">
+      <c r="C19" s="16" t="inlineStr">
         <is>
           <t>基础钢筋按独立基础 J-1/J-2/J-3 汇总（均为Φ12）；基础梁 DKL/DL 钢筋计入“现浇混凝土梁钢筋”对应直径。</t>
         </is>
       </c>
     </row>
     <row r="20">
-      <c r="A20" s="14" t="inlineStr">
+      <c r="A20" s="16" t="inlineStr">
         <is>
           <t>010506002003</t>
         </is>
       </c>
-      <c r="B20" s="14" t="inlineStr">
+      <c r="B20" s="16" t="inlineStr">
         <is>
           <t>现浇混凝土柱钢筋</t>
         </is>
       </c>
-      <c r="C20" s="14" t="inlineStr">
+      <c r="C20" s="16" t="inlineStr">
         <is>
           <t>钢筋明细表中柱构件无Φ16钢筋，工程量为 0。</t>
         </is>
       </c>
     </row>
     <row r="21">
-      <c r="A21" s="14" t="inlineStr">
+      <c r="A21" s="16" t="inlineStr">
         <is>
           <t>010506005001</t>
         </is>
       </c>
-      <c r="B21" s="14" t="inlineStr">
+      <c r="B21" s="16" t="inlineStr">
         <is>
           <t>现浇混凝土梁钢筋</t>
         </is>
       </c>
-      <c r="C21" s="14" t="inlineStr">
+      <c r="C21" s="16" t="inlineStr">
         <is>
           <t>含雨棚梁 YPL 钢筋（清单模板“雨蓬”项仅列Φ8）。</t>
         </is>
       </c>
     </row>
     <row r="22">
-      <c r="A22" s="14" t="inlineStr">
+      <c r="A22" s="16" t="inlineStr">
         <is>
           <t>010506005004</t>
         </is>
       </c>
-      <c r="B22" s="14" t="inlineStr">
+      <c r="B22" s="16" t="inlineStr">
         <is>
           <t>现浇混凝土梁钢筋</t>
         </is>
       </c>
-      <c r="C22" s="14" t="inlineStr">
+      <c r="C22" s="16" t="inlineStr">
         <is>
           <t>含雨棚梁 YPL 钢筋（清单模板“雨蓬”项仅列Φ8）。</t>
         </is>
       </c>
     </row>
     <row r="23">
-      <c r="A23" s="14" t="inlineStr">
+      <c r="A23" s="16" t="inlineStr">
         <is>
           <t>010506020001</t>
         </is>
       </c>
-      <c r="B23" s="14" t="inlineStr">
+      <c r="B23" s="16" t="inlineStr">
         <is>
           <t>钢筋网片</t>
         </is>
       </c>
-      <c r="C23" s="14" t="inlineStr">
+      <c r="C23" s="16" t="inlineStr">
         <is>
           <t>钢筋明细表中无屋面网片；按刚性层面积×Φ4@150双向估算：Φ4 单重 0.099kg/m，每 m² 用量 2/0.15×0.099≈1.316kg/m²。</t>
         </is>
       </c>
     </row>
     <row r="24">
-      <c r="A24" s="14" t="inlineStr">
+      <c r="A24" s="16" t="inlineStr">
         <is>
           <t>010902001001</t>
         </is>
       </c>
-      <c r="B24" s="14" t="inlineStr">
+      <c r="B24" s="16" t="inlineStr">
         <is>
           <t>屋面卷材防水</t>
         </is>
       </c>
-      <c r="C24" s="14" t="inlineStr">
+      <c r="C24" s="16" t="inlineStr">
         <is>
           <t>按广联达屋面“防水面积”（含 250 高卷边）汇总。</t>
         </is>
       </c>
     </row>
     <row r="25">
-      <c r="A25" s="14" t="inlineStr">
+      <c r="A25" s="16" t="inlineStr">
         <is>
           <t>010902004001</t>
         </is>
       </c>
-      <c r="B25" s="14" t="inlineStr">
+      <c r="B25" s="16" t="inlineStr">
         <is>
           <t>屋面刚性层</t>
         </is>
       </c>
-      <c r="C25" s="14" t="inlineStr">
+      <c r="C25" s="16" t="inlineStr">
         <is>
           <t>刚性层 = 屋面防水面积 − 卷边面积（水平投影）。</t>
         </is>
       </c>
     </row>
     <row r="26">
-      <c r="A26" s="14" t="inlineStr">
+      <c r="A26" s="16" t="inlineStr">
         <is>
           <t>010902005001</t>
         </is>
       </c>
-      <c r="B26" s="14" t="inlineStr">
+      <c r="B26" s="16" t="inlineStr">
         <is>
           <t>屋面排水管</t>
         </is>
       </c>
-      <c r="C26" s="14" t="inlineStr">
+      <c r="C26" s="16" t="inlineStr">
         <is>
           <t>计算书与钢筋表中均无雨水管信息，无法计取，需按图纸补充（根数×长度）。</t>
         </is>
       </c>
     </row>
     <row r="27">
-      <c r="A27" s="14" t="inlineStr">
+      <c r="A27" s="16" t="inlineStr">
         <is>
           <t>010904002001</t>
         </is>
       </c>
-      <c r="B27" s="14" t="inlineStr">
+      <c r="B27" s="16" t="inlineStr">
         <is>
           <t>楼地面涂膜防水</t>
         </is>
       </c>
-      <c r="C27" s="14" t="inlineStr">
+      <c r="C27" s="16" t="inlineStr">
         <is>
           <t>按首层卫生间地面积计取，未含上翻高度部分。</t>
         </is>
       </c>
     </row>
     <row r="28">
-      <c r="A28" s="14" t="inlineStr">
+      <c r="A28" s="16" t="inlineStr">
         <is>
           <t>011001001001</t>
         </is>
       </c>
-      <c r="B28" s="14" t="inlineStr">
+      <c r="B28" s="16" t="inlineStr">
         <is>
           <t>保温隔热屋面</t>
         </is>
       </c>
-      <c r="C28" s="14" t="inlineStr">
+      <c r="C28" s="16" t="inlineStr">
         <is>
           <t>保温层 = 屋面防水面积 − 卷边面积（水平投影）。</t>
         </is>
       </c>
     </row>
     <row r="29">
-      <c r="A29" s="14" t="inlineStr">
+      <c r="A29" s="16" t="inlineStr">
         <is>
           <t>011101001001</t>
         </is>
       </c>
-      <c r="B29" s="14" t="inlineStr">
+      <c r="B29" s="16" t="inlineStr">
         <is>
           <t>水泥砂浆楼地面</t>
         </is>
       </c>
-      <c r="C29" s="14" t="inlineStr">
+      <c r="C29" s="16" t="inlineStr">
         <is>
           <t>按各层“其他”房间地面积汇总（首层地面一并计入）。</t>
         </is>
       </c>
     </row>
     <row r="30">
-      <c r="A30" s="14" t="inlineStr">
+      <c r="A30" s="16" t="inlineStr">
         <is>
           <t>011105001001</t>
         </is>
       </c>
-      <c r="B30" s="14" t="inlineStr">
+      <c r="B30" s="16" t="inlineStr">
         <is>
           <t>水泥砂浆踢脚线</t>
         </is>
       </c>
-      <c r="C30" s="14" t="inlineStr">
+      <c r="C30" s="16" t="inlineStr">
         <is>
           <t>仅计“其他”房间踢脚；卫生间 2.1m 以下为瓷砖墙裙，不计踢脚。</t>
         </is>
       </c>
     </row>
     <row r="31">
-      <c r="A31" s="14" t="inlineStr">
+      <c r="A31" s="16" t="inlineStr">
         <is>
           <t>011201001002</t>
         </is>
       </c>
-      <c r="B31" s="14" t="inlineStr">
+      <c r="B31" s="16" t="inlineStr">
         <is>
           <t>墙、柱面一般抹灰</t>
         </is>
       </c>
-      <c r="C31" s="14" t="inlineStr">
+      <c r="C31" s="16" t="inlineStr">
         <is>
           <t>含各层房间内墙面（卫生间为墙裙以上部分）及第5层女儿墙内侧/楼梯间墙面。</t>
         </is>
       </c>
     </row>
     <row r="32">
-      <c r="A32" s="14" t="inlineStr">
+      <c r="A32" s="16" t="inlineStr">
         <is>
           <t>011404001001</t>
         </is>
       </c>
-      <c r="B32" s="14" t="inlineStr">
+      <c r="B32" s="16" t="inlineStr">
         <is>
           <t>墙面喷刷涂料</t>
         </is>
       </c>
-      <c r="C32" s="14" t="inlineStr">
+      <c r="C32" s="16" t="inlineStr">
         <is>
           <t>外墙涂料面积 = 外墙一般抹灰面积。</t>
         </is>
       </c>
     </row>
     <row r="33">
-      <c r="A33" s="14" t="inlineStr">
+      <c r="A33" s="16" t="inlineStr">
         <is>
           <t>011404001002</t>
         </is>
       </c>
-      <c r="B33" s="14" t="inlineStr">
+      <c r="B33" s="16" t="inlineStr">
         <is>
           <t>墙面喷刷涂料</t>
         </is>
       </c>
-      <c r="C33" s="14" t="inlineStr">
+      <c r="C33" s="16" t="inlineStr">
         <is>
           <t>内墙涂料面积 = 内墙一般抹灰面积。</t>
         </is>
       </c>
     </row>
     <row r="34">
-      <c r="A34" s="14" t="inlineStr">
+      <c r="A34" s="16" t="inlineStr">
         <is>
           <t>011404002001</t>
         </is>
       </c>
-      <c r="B34" s="14" t="inlineStr">
+      <c r="B34" s="16" t="inlineStr">
         <is>
           <t>天棚喷刷涂料</t>
         </is>
       </c>
-      <c r="C34" s="14" t="inlineStr">
+      <c r="C34" s="16" t="inlineStr">
         <is>
           <t>天棚涂料面积 = 天棚抹灰面积。</t>
         </is>
       </c>
     </row>
     <row r="35">
-      <c r="A35" s="14" t="n"/>
-      <c r="B35" s="14" t="n"/>
-      <c r="C35" s="14" t="n"/>
+      <c r="A35" s="16" t="n"/>
+      <c r="B35" s="16" t="n"/>
+      <c r="C35" s="16" t="n"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
